--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F39D8B3-3B45-4FA4-86B1-8CA7495104E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9E2342-9071-45EC-9817-A2F223F42E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="144">
   <si>
     <t>Option 1</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Biologie</t>
   </si>
   <si>
-    <t>ENSAM 2025</t>
-  </si>
-  <si>
     <t>Pascal</t>
   </si>
   <si>
@@ -172,15 +169,6 @@
   </si>
   <si>
     <t>Travail</t>
-  </si>
-  <si>
-    <t>FST 2025</t>
-  </si>
-  <si>
-    <t>ENSA 2025</t>
-  </si>
-  <si>
-    <t>ISTA 2025</t>
   </si>
   <si>
     <t>PHYSIQUE</t>
@@ -6184,6 +6172,15 @@
   </si>
   <si>
     <t>(R//R, C//C)</t>
+  </si>
+  <si>
+    <t>MEDECINE 2023</t>
+  </si>
+  <si>
+    <t>MEDECINE 2024</t>
+  </si>
+  <si>
+    <t>MEDECINE 2025</t>
   </si>
 </sst>
 </file>
@@ -7135,7 +7132,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>13</v>
@@ -7150,9 +7147,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -7167,24 +7164,24 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
+        <v>48</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="J2" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -7199,24 +7196,24 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
         <v>49</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="J3" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -7231,24 +7228,24 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" t="s">
         <v>50</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -7263,56 +7260,56 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" t="s">
         <v>51</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="J5" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" t="s">
-        <v>24</v>
+      <c r="I6" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="J6" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B7" s="4">
         <v>11</v>
@@ -7333,74 +7330,74 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" t="s">
         <v>49</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="J7" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
         <v>50</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="J8" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" t="s">
         <v>51</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="J9" s="3">
         <v>3</v>
@@ -7408,63 +7405,63 @@
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="J10" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" t="s">
-        <v>24</v>
+        <v>50</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="J11" s="3">
         <v>1</v>
@@ -7472,7 +7469,7 @@
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B12" s="4">
         <v>3</v>
@@ -7493,10 +7490,10 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="J12" s="3">
         <v>3</v>
@@ -7504,31 +7501,31 @@
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>39</v>
       </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J13" s="3">
         <v>3</v>
@@ -7536,31 +7533,31 @@
     </row>
     <row r="14" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J14" s="3">
         <v>2</v>
@@ -7568,31 +7565,31 @@
     </row>
     <row r="15" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="G15" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J15" s="3">
         <v>1</v>
@@ -7600,31 +7597,31 @@
     </row>
     <row r="16" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="G16" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J16" s="3">
         <v>2</v>
@@ -7632,31 +7629,31 @@
     </row>
     <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>90</v>
-      </c>
       <c r="G17" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J17" s="3">
         <v>3</v>
@@ -7664,31 +7661,31 @@
     </row>
     <row r="18" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="F18" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="G18" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J18" s="3">
         <v>2</v>
@@ -7696,31 +7693,31 @@
     </row>
     <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="F19" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="G19" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3">
         <v>1</v>
@@ -7728,31 +7725,31 @@
     </row>
     <row r="20" spans="1:10" ht="126" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="F20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>108</v>
-      </c>
       <c r="G20" s="15" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3">
         <v>1</v>
@@ -7760,31 +7757,31 @@
     </row>
     <row r="21" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>114</v>
-      </c>
       <c r="G21" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3">
         <v>3</v>
@@ -7792,31 +7789,31 @@
     </row>
     <row r="22" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3">
         <v>2</v>
@@ -7824,31 +7821,31 @@
     </row>
     <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="F23" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>123</v>
-      </c>
       <c r="G23" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="J23" s="3">
         <v>2</v>
@@ -7856,31 +7853,31 @@
     </row>
     <row r="24" spans="1:10" ht="330.75" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D24" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="J24" s="3">
         <v>1</v>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9E2342-9071-45EC-9817-A2F223F42E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25897079-558D-47D2-BD08-15B1C00A09BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="143">
   <si>
     <t>Option 1</t>
   </si>
@@ -178,9 +178,6 @@
   </si>
   <si>
     <t>SVT</t>
-  </si>
-  <si>
-    <t>Sciences</t>
   </si>
   <si>
     <t>Option 5</t>
@@ -6649,17 +6646,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF2F2F2F"/>
       </left>
       <right style="thin">
@@ -6671,15 +6657,6 @@
       <bottom style="thin">
         <color rgb="FF2F2F2F"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF2F2F2F"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -6698,19 +6675,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF343434"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF343434"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF2F2F2F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF343434"/>
@@ -6723,11 +6687,50 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2F2F2F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF2F2F2F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF2F2F2F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF343434"/>
       </left>
       <right/>
       <top style="thin">
         <color rgb="FF343434"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF343434"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF343434"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF2F2F2F"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -6736,68 +6739,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7119,7 +7142,7 @@
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -7132,7 +7155,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>13</v>
@@ -7143,743 +7166,743 @@
       <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>123</v>
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>122</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="I2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>124</v>
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="3">
+      <c r="I3" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>125</v>
+    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
+        <v>124</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="I4" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>126</v>
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="H5" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>127</v>
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
+        <v>126</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F6" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="I6" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="2">
+        <v>11</v>
+      </c>
+      <c r="C7" s="21">
+        <v>13</v>
+      </c>
+      <c r="D7" s="21">
+        <v>15</v>
+      </c>
+      <c r="E7" s="21">
+        <v>17</v>
+      </c>
+      <c r="F7" s="21">
+        <v>25</v>
+      </c>
+      <c r="G7" s="21">
+        <v>11</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
         <v>128</v>
-      </c>
-      <c r="B7" s="4">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4">
-        <v>15</v>
-      </c>
-      <c r="E7" s="4">
-        <v>17</v>
-      </c>
-      <c r="F7" s="4">
-        <v>25</v>
-      </c>
-      <c r="G7" s="4">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>129</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="F8" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>130</v>
+    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="28" t="s">
+        <v>129</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="F9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F9" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="H9" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>131</v>
+    <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
+        <v>130</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="F10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F10" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="H10" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>132</v>
+    <row r="11" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F11" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="I11" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J11" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="21">
+        <v>5</v>
+      </c>
+      <c r="D12" s="21">
+        <v>15</v>
+      </c>
+      <c r="E12" s="21">
+        <v>8</v>
+      </c>
+      <c r="F12" s="21">
+        <v>23</v>
+      </c>
+      <c r="G12" s="21">
+        <v>15</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="28" t="s">
         <v>133</v>
-      </c>
-      <c r="B12" s="4">
-        <v>3</v>
-      </c>
-      <c r="C12" s="4">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4">
-        <v>15</v>
-      </c>
-      <c r="E12" s="4">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4">
-        <v>23</v>
-      </c>
-      <c r="G12" s="4">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>134</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="F13" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="I13" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J13" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J14" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="G15" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="I15" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="I16" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J16" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="F17" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" s="7" t="s">
+      <c r="G17" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="I17" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="E19" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="F19" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="7" t="s">
+      <c r="G19" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J19" s="3">
+      <c r="I19" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J19" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="126" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="C20" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="F20" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="G20" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="C21" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="E21" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="F21" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="H21" s="7" t="s">
+      <c r="G21" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="I21" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="E22" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="F22" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="G22" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="I22" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="7" t="s">
+      <c r="G23" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="I23" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="330.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="C24" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="H24" s="7" t="s">
+      <c r="G24" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" s="20">
         <v>1</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25897079-558D-47D2-BD08-15B1C00A09BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C4F9D6-A52D-40C9-A851-686AA3F6BF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="224">
   <si>
     <t>Option 1</t>
   </si>
@@ -121,30 +121,6 @@
   </si>
   <si>
     <t>Rate</t>
-  </si>
-  <si>
-    <t>Astrologie</t>
-  </si>
-  <si>
-    <t>Nucléaire</t>
-  </si>
-  <si>
-    <t>Astrophysique</t>
-  </si>
-  <si>
-    <t>Atomique</t>
-  </si>
-  <si>
-    <t>U=R.I</t>
-  </si>
-  <si>
-    <t>I=U.R</t>
-  </si>
-  <si>
-    <t>P=U.I</t>
-  </si>
-  <si>
-    <t>P=R.I</t>
   </si>
   <si>
     <t>Inflammation</t>
@@ -1574,16 +1550,10 @@
     <t>Huminité</t>
   </si>
   <si>
-    <t>Statistique</t>
-  </si>
-  <si>
     <t>Bernard</t>
   </si>
   <si>
     <t>Reins</t>
-  </si>
-  <si>
-    <t>P=V/I</t>
   </si>
   <si>
     <r>
@@ -6000,9 +5970,6 @@
     <t>PCR</t>
   </si>
   <si>
-    <t>Etude des astres</t>
-  </si>
-  <si>
     <t>Auteur de la théorie de réaction dans l'eau</t>
   </si>
   <si>
@@ -6012,9 +5979,6 @@
     <t>Plus petit multiple commun de 3 et 5</t>
   </si>
   <si>
-    <t>Loi d'Ohm</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -6178,13 +6142,5653 @@
   </si>
   <si>
     <t>MEDECINE 2025</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">permet de relier l'actine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>yosi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">reste toujours </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fixée </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>su</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">r la tropomyosine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pendant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>cycle de contraction musculaire ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">une </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>faib</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>e affi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>nit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">é aux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ons calcium ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">partie de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'ac</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>tin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'un</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">it à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>yos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cache </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>le</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sites </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>liai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">son </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de la myosine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>actine.</t>
+    </r>
+  </si>
+  <si>
+    <t>MEDECINE 2021</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">bidirectionnelle, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">se fait dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sens </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">vers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">3' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et 3' vers 5' et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">permet la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>nthè</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">se </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux brins </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">antiparallèles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">aux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>brin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui servent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de matrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">unidirectionnelle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">se fait dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>se</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">5' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">vers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">3' et pem1et la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">nthèse de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>deu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">x brins </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">parallèles aux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">brins qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">servent de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">matrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">bidirectionnelle, se fait </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>se</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">5' vers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">3' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et pem1et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">synthèse </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>de deux bri ns antiparallèles aux brins qu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">i </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>servent de matrice ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">unidirectionnelle, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">se </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fait dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>se</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">5' vers 3' et permet la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">synthèse </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>deu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">brins antiparallèles aux brins </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">servent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de matrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">unidirectionnelle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">se </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fait </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>le sens 3' vers 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et permet la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">nthèse </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de deux brins antiparallèles aux brins </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">servent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>matrice.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">e sucre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ribose et par </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">une </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>base azotée d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fférente </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>suc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ribose </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et par </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>base</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>azo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ées </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>différentes ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sucre qui est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>désoxyr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ib</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ose et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">par </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">quatre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">bases </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>otées différentes ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sucre qui est un ribose et par pl usieurs bases azotées différentes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sucre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">désoxyTi bose </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">par </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a présence de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>base azotée u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>acile.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La synthèse </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ARN  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">se </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fait dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sens </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">3' vers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">5' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et s'arrête dans un codon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>stop ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Une </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>mol</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>écü</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>le d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF797979"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ARN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">interagit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>avec p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>lu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">urs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ribosomes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a fo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et se fait </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>dan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>le sens 5' vers 3' ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Une </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">molécule d'ARN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>interag</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">it </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">avec </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ribosome </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a fois et se </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fait </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">dans le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>se</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5' vers 3' ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La traduction </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">peut débuter dans Je noyau d'une </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>cellule eucaryote et s'achève toujours dans le cytoplasme ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">traduction </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">d'ADN se </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fait </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">toujours </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">dans le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>cytop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>asme d'une cellu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2D2D2D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">e eucaryote </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF676767"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">t </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF505050"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s'arrête </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3D3D3D"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>dans un codon stop.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">croisement monohybride </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">implique </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un seul parent, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>tandi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qu'un croisement dihybride </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">implique </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">parents </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un croisement monohybride </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">produit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>une seule progéniture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">alors </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qu'un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">croisement dihybride </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">produit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>x ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">n croisement monohybride est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>réali</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sé </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">une </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>seule fois</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">alors </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>qu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">'un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">croisement dihyb1ide </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>est</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> réalisé deux fois ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un croisement </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">monohybride </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">donne </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>rapport 9:3:3:1 alors qu'un croisement dihybride donne un rapp0113:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">il </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a obtenu très </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>peu d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">e </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sce</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ndant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ce </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>qui rendait l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>analy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>se s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">tatistique difficile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">les caractères </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">parentaux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">qui n'ont </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas été observés dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>so</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">nt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">réapparus dans </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">2, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ce qui suggère </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">que les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">facteurs héréditaires  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">n'ont </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas vraiment disparu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>dan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">F </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1 ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>l'analyse de la descendance F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">lui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>aura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">it permis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de découvrir la loi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">disjonction, mais pas la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>loi d'a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ssort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">iment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>indépendant ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">les phénotypes dominants </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">étaient </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ibles dan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">génération </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">2, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>mais pas dan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">l'analyse </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la descendance </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">lui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">aurait permis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>de décou</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>r l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">loi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>disjonction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">mais </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la loi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>homo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>gé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>néit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">é </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">es </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>hybrides.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>deu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">gènes sont </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ur </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>des chromo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">omes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>différent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">gènes sont tous </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">itués </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">près du centromère </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">gènes sont </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">és </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">au sexe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">deux gènes codent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pour la même </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">protéine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Les deux gènes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>so</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">nt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">éloignés </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">l'autre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sur le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ê</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">me </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chromosome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tous </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ses enfants ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">la moitié </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de ses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">filles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tous </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ses fils </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">la moitié </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de ses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fils </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>toutes ses filles.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">population de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>petite t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ille</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">accouplement aléatoire, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">lection, pas de migration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas de mutations </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">population de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">grande </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>tai lle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">accouplement </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">aléatoire, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>de sélection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">migration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et pas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">m utations </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">population de grande taille, accouplement aléatoire, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>les h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>é</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>é</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ygotes survivent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">mieux, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">migration et pas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de mutations </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">population de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">petite  taille, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">les individus </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">semblables s'accouplent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF828282"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sélection, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas de migration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas de mutations </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">population de grande </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>taille</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">accouplement </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>aléatoire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pas de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF606060"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>lection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">migration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">provenance d'autres populations </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4B4B4B"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pas de mutations.</t>
+    </r>
+  </si>
+  <si>
+    <t>les fibres de type I car elles contiennent moins de capillaires et ont une capacité anaérobie plus élevée que les fibres de type IIb ;</t>
+  </si>
+  <si>
+    <t>les fibres de type Ilb car elles contiennent moins de capillaires et ont une capacité anaérobie plus faible que les fibres de type 1 ;</t>
+  </si>
+  <si>
+    <t>Les fibres de type llb car elles contiennent plus de capillaires et ont une capacité aérobie plus importante que les fibres de type IIa ;</t>
+  </si>
+  <si>
+    <t>Les fibres de type lia car elles contiennent moins de capillaires que les fibres de type I  et ont une capacité anaérobie moins importante que les fibres de type Ilb ;</t>
+  </si>
+  <si>
+    <t>Les fibres de type 1car elles contiennent plus de capillaires et ont une capacité aérobie pl us importante que les fibres de type Ilb.</t>
+  </si>
+  <si>
+    <t>ARNm : 5'-A-C-U-G-C-A-C-A-A-3'</t>
+  </si>
+  <si>
+    <t>ARNm  : 5'-T-C-A-A-C-G-A-A-C-3'</t>
+  </si>
+  <si>
+    <t>ARNm  : 5'-C-A-A-G-C-A-A-C-U-3'</t>
+  </si>
+  <si>
+    <t>ARNm : 5'-U-C-A-A-C-G-A-A-C-3'</t>
+  </si>
+  <si>
+    <t>ARNm : 5'-A-A-C-A-C-G- U-C-A-3'</t>
+  </si>
+  <si>
+    <r>
+      <t>(H</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF898989"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>T/)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/ ' hl)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Hl , </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF565656"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">hl </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>T/ , t/)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(T</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF898989"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF565656"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">( t/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF898989"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF565656"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">mâles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7E7E7E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">femelle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1 mâle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF909090"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">femelles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">mâle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">I </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">femelle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">mâle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">I </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 femelles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">mâles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7E7E7E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>femelle.</t>
+    </r>
+  </si>
+  <si>
+    <t>ABCD</t>
+  </si>
+  <si>
+    <t>ADCB</t>
+  </si>
+  <si>
+    <t>CABD</t>
+  </si>
+  <si>
+    <t>BCAD</t>
+  </si>
+  <si>
+    <t>DBAC</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>TEST1</t>
+  </si>
+  <si>
+    <t>TEST2</t>
+  </si>
+  <si>
+    <t>TEST3</t>
+  </si>
+  <si>
+    <t>TEST4</t>
+  </si>
+  <si>
+    <t>TEST5</t>
+  </si>
+  <si>
+    <t>Dans le m uscle strié squelettiq ue, la troponi ne :</t>
+  </si>
+  <si>
+    <t>Concernant la réplication d'ADN, elle est :</t>
+  </si>
+  <si>
+    <t>L'ARN se distingue de I'ADN par :</t>
+  </si>
+  <si>
+    <t>À propos de la traduction :</t>
+  </si>
+  <si>
+    <t>Concernant le monohybridisme et le dihybridisme :</t>
+  </si>
+  <si>
+    <r>
+      <t>Il était important que Mendel examine non seulement la génération F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">dans ses expériences de reproduction, mais aussi la génération </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF383838"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2, car :</t>
+    </r>
+  </si>
+  <si>
+    <t>L'explication la plus probable d'un tau x élevé de crossing-over entre deux gènes est la suivante :</t>
+  </si>
+  <si>
+    <t>Un homme porteu r d'un allèle lié au chromosome X le transmettra à :</t>
+  </si>
+  <si>
+    <t>Les principes de l'équilibre de Hardy Weinberg sont :</t>
+  </si>
+  <si>
+    <t>C'était une image qu'on va adapter par la suite</t>
+  </si>
+  <si>
+    <t>La séquence d'ARNm transcrite à partir de la séquence d'ADN 5'-G-T-T-C-G-T-T-G-A-3' (brin transcrit) est :</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un animal se reprodui sant sexuellement possède deux gènes non liés, l'un pour la fonne de la tête (H). et l'autre pour la longueur de la queue (T). Son génotype est (H//h , </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF727272"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ii</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF3F3F3F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Lequel des génotypes suivants est possible dans un gamète de cet organisme '!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On croise deux variétés de plantes de pois, l'une  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF565656"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">fleurs axiales rouges et l'autre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF565656"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">à </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>fleurs terminales blanches. Tous les individus F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF727272"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ont des fleurs axiales rouges. Supposant un assortiment indépendant, sur 64 individus de la génération F2, combien d'entre eux devraient avoir des fleurs terminales rouges ?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chez </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">oiseaux, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sexe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">est </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>détermin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">é </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">par </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">couple chromosomique ZW. Les mâles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sont </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ZZ et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">femelles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>so</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">nt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ZW. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">allèle récessif </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">létal qui provoque </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">la mort </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">de l'embryon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">est parfois présent </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">sur </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">le chromosome Z chez </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>le</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pigeons. Quel serait  le rapport  des sexes dans  la progéniture  d'un  croisement  entre un  mâle hétérozygote  portant  ]'allèle létal et une femelle normale  '?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'emplacement relatif de quatre gènes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ur un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chromosome peut </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>êt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">re </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">cartographié à partir des </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>donnée</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF5E5E5E"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">suivantes sur </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF343434"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>fréquences de crossing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF494949"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>over. Fréquence de crossing-over entre les gènes : B et C 5 % ; B et A 30% ; A et  D 15% ; C et A 25 % ; C et D 40%. Laquelle des propositions suivantes représentent Jes positions relatives de ces quatre gènes sur le chromosome ?</t>
+    </r>
+  </si>
+  <si>
+    <t>Dans une population en équilibre de Hardy-Weinberg, la fréquence d'un allèle récessif pour un caractère héréditaire donné  est de 0,20. Le pourcen tage des individ us présentant le caractère dominant à la génération suivante est :</t>
+  </si>
+  <si>
+    <t>Q21M21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="64" x14ac:knownFonts="1">
+  <fonts count="103" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6208,6 +11812,7 @@
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -6612,6 +12217,247 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF505050"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2D2D2D"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF676767"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF797979"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF505050"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF606060"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4B4B4B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF383838"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF727272"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF383838"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF383838"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF383838"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF606060"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF606060"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF727272"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF4B4B4B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF828282"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF727272"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF565656"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF898989"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF565656"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF565656"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF565656"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF898989"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF898989"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF565656"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF565656"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF727272"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF494949"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF343434"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7E7E7E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF909090"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6621,7 +12467,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -6646,92 +12492,12 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF2F2F2F"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF2F2F2F"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FF2F2F2F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF2F2F2F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF343434"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF343434"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF343434"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF343434"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF343434"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF2F2F2F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF2F2F2F"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF2F2F2F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF2F2F2F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF343434"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF343434"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF343434"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF343434"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF2F2F2F"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -6739,55 +12505,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6820,7 +12541,97 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7125,785 +12936,1306 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K3" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="6">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6">
+        <v>15</v>
+      </c>
+      <c r="F8" s="6">
+        <v>17</v>
+      </c>
+      <c r="G8" s="6">
+        <v>25</v>
+      </c>
+      <c r="H8" s="6">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="39"/>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="39"/>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6">
+        <v>15</v>
+      </c>
+      <c r="F12" s="6">
+        <v>8</v>
+      </c>
+      <c r="G12" s="6">
+        <v>23</v>
+      </c>
+      <c r="H12" s="6">
+        <v>15</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>15</v>
+      <c r="E14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+    <row r="15" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="41"/>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K16" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="126" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K20" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K21" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K22" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K25" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K26" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K27" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K28" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K29" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K30" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K31" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K32" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K33" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K34" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="70.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K35" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="26">
+        <v>4</v>
+      </c>
+      <c r="D36" s="26">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="J2" s="20">
+      <c r="E36" s="31">
+        <v>12</v>
+      </c>
+      <c r="F36" s="32">
+        <v>24</v>
+      </c>
+      <c r="G36" s="26">
+        <v>36</v>
+      </c>
+      <c r="H36" s="26">
+        <v>4</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K36" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" s="20">
+    <row r="37" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A37" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" s="33"/>
+      <c r="C37" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K37" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="20">
-        <v>3</v>
+    <row r="38" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="36"/>
+      <c r="C38" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K38" s="37">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="J5" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="J6" s="20">
+    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="37"/>
+      <c r="C39" s="38">
+        <v>0.08</v>
+      </c>
+      <c r="D39" s="38">
+        <v>0.16</v>
+      </c>
+      <c r="E39" s="38">
+        <v>0.32</v>
+      </c>
+      <c r="F39" s="38">
+        <v>0.64</v>
+      </c>
+      <c r="G39" s="38">
+        <v>0.96</v>
+      </c>
+      <c r="H39" s="38">
+        <v>0.32</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K39" s="16">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="2">
-        <v>11</v>
-      </c>
-      <c r="C7" s="21">
-        <v>13</v>
-      </c>
-      <c r="D7" s="21">
-        <v>15</v>
-      </c>
-      <c r="E7" s="21">
-        <v>17</v>
-      </c>
-      <c r="F7" s="21">
-        <v>25</v>
-      </c>
-      <c r="G7" s="21">
-        <v>11</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="J7" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="J8" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J9" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J10" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J11" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="2">
-        <v>3</v>
-      </c>
-      <c r="C12" s="21">
-        <v>5</v>
-      </c>
-      <c r="D12" s="21">
-        <v>15</v>
-      </c>
-      <c r="E12" s="21">
-        <v>8</v>
-      </c>
-      <c r="F12" s="21">
-        <v>23</v>
-      </c>
-      <c r="G12" s="21">
-        <v>15</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J12" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J13" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J14" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J15" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J16" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J17" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J18" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J19" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="126" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J20" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J21" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J22" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J23" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="330.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J24" s="20">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C4F9D6-A52D-40C9-A851-686AA3F6BF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E521385-F8B0-490E-9396-28425CC6B1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="219">
   <si>
     <t>Option 1</t>
   </si>
@@ -11199,21 +11199,6 @@
   </si>
   <si>
     <t>Image</t>
-  </si>
-  <si>
-    <t>TEST1</t>
-  </si>
-  <si>
-    <t>TEST2</t>
-  </si>
-  <si>
-    <t>TEST3</t>
-  </si>
-  <si>
-    <t>TEST4</t>
-  </si>
-  <si>
-    <t>TEST5</t>
   </si>
   <si>
     <t>Dans le m uscle strié squelettiq ue, la troponi ne :</t>
@@ -12505,7 +12490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12631,6 +12616,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13020,25 +13008,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H3" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="I3" s="42" t="s">
         <v>40</v>
@@ -13046,15 +13016,15 @@
       <c r="J3" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="K3" s="43">
-        <v>3</v>
-      </c>
+      <c r="K3" s="43"/>
     </row>
     <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="39"/>
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
       <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
@@ -13076,8 +13046,8 @@
       <c r="I4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>49</v>
+      <c r="J4" s="44" t="s">
+        <v>136</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
@@ -13087,7 +13057,9 @@
       <c r="A5" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="39"/>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
@@ -13109,8 +13081,8 @@
       <c r="I5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>49</v>
+      <c r="J5" s="44" t="s">
+        <v>136</v>
       </c>
       <c r="K5" s="5">
         <v>3</v>
@@ -13120,7 +13092,9 @@
       <c r="A6" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="39"/>
+      <c r="B6" t="s">
+        <v>218</v>
+      </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
@@ -13142,8 +13116,8 @@
       <c r="I6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>128</v>
+      <c r="J6" s="44" t="s">
+        <v>136</v>
       </c>
       <c r="K6" s="5">
         <v>3</v>
@@ -13712,7 +13686,7 @@
     </row>
     <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="s">
@@ -13745,7 +13719,7 @@
     </row>
     <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="17" t="s">
@@ -13778,7 +13752,7 @@
     </row>
     <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="18" t="s">
@@ -13811,7 +13785,7 @@
     </row>
     <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="14" t="s">
@@ -13844,7 +13818,7 @@
     </row>
     <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
@@ -13877,7 +13851,7 @@
     </row>
     <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="23" t="s">
@@ -13910,7 +13884,7 @@
     </row>
     <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="21" t="s">
@@ -13943,7 +13917,7 @@
     </row>
     <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="23" t="s">
@@ -13976,7 +13950,7 @@
     </row>
     <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="24" t="s">
@@ -14009,7 +13983,7 @@
     </row>
     <row r="33" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="26" t="s">
@@ -14042,7 +14016,7 @@
     </row>
     <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19" t="s">
@@ -14075,7 +14049,7 @@
     </row>
     <row r="35" spans="1:11" ht="70.5" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="27" t="s">
@@ -14108,7 +14082,7 @@
     </row>
     <row r="36" spans="1:11" ht="69.75" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="26">
@@ -14141,7 +14115,7 @@
     </row>
     <row r="37" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B37" s="33"/>
       <c r="C37" s="34" t="s">
@@ -14174,7 +14148,7 @@
     </row>
     <row r="38" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B38" s="36"/>
       <c r="C38" s="26" t="s">
@@ -14207,7 +14181,7 @@
     </row>
     <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B39" s="37"/>
       <c r="C39" s="38">

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E521385-F8B0-490E-9396-28425CC6B1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9126BCEA-8BBB-45DA-8925-43214C8372E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="223">
   <si>
     <t>Option 1</t>
   </si>
@@ -11767,6 +11767,18 @@
   </si>
   <si>
     <t>Q21M21</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SIMPLE</t>
+  </si>
+  <si>
+    <t>GROUP</t>
+  </si>
+  <si>
+    <t>QUESTION</t>
   </si>
 </sst>
 </file>
@@ -12452,7 +12464,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -12486,11 +12498,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12620,6 +12658,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12924,1291 +13000,1396 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="5">
+      <c r="L2" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
     </row>
-    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="B4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="39"/>
+      <c r="D8" s="6">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>13</v>
+      </c>
+      <c r="F8" s="6">
+        <v>15</v>
+      </c>
+      <c r="G8" s="6">
+        <v>17</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <v>11</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="K4" s="5">
+      <c r="K8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="39"/>
+      <c r="D10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="F12" s="6">
+        <v>15</v>
+      </c>
+      <c r="G12" s="6">
+        <v>8</v>
+      </c>
+      <c r="H12" s="6">
+        <v>23</v>
+      </c>
+      <c r="I12" s="6">
+        <v>15</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="5">
-        <v>3</v>
+      <c r="K13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="K6" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K7" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="6">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6">
-        <v>13</v>
-      </c>
-      <c r="E8" s="6">
-        <v>15</v>
-      </c>
-      <c r="F8" s="6">
-        <v>17</v>
-      </c>
-      <c r="G8" s="6">
-        <v>25</v>
-      </c>
-      <c r="H8" s="6">
-        <v>11</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K9" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K10" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="6">
-        <v>3</v>
-      </c>
-      <c r="D12" s="6">
-        <v>5</v>
-      </c>
-      <c r="E12" s="6">
-        <v>15</v>
-      </c>
-      <c r="F12" s="6">
-        <v>8</v>
-      </c>
-      <c r="G12" s="6">
-        <v>23</v>
-      </c>
-      <c r="H12" s="6">
-        <v>15</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K12" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K13" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="41"/>
+      <c r="D14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
+    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K15" s="5">
+      <c r="L15" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10" t="s">
-        <v>72</v>
-      </c>
+      <c r="C16" s="9"/>
       <c r="D16" s="10" t="s">
         <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="G16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="I16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="5">
+      <c r="L16" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K17" s="5">
+      <c r="L17" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="I18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="J18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="5">
+      <c r="L18" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="126" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K19" s="5">
+      <c r="L19" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="J20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="K20" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K20" s="5">
+      <c r="L20" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B21" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="G21" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="K21" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K21" s="5">
+      <c r="L21" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="8"/>
+      <c r="D22" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K22" s="5">
+      <c r="L22" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="F23" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K23" s="5">
+      <c r="L23" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="H24" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H24" s="14" t="s">
+      <c r="I24" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="J24" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="K24" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K24" s="16">
+      <c r="L24" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="E25" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="F25" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="G25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="H25" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="I25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="J25" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="K25" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K25" s="16">
+      <c r="L25" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="13"/>
+      <c r="D26" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="E26" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="F26" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="H26" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="I26" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="J26" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="K26" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K26" s="16">
+      <c r="L26" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="19"/>
+      <c r="D27" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="F27" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="G27" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="H27" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="I27" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="J27" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="K27" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K27" s="16">
+      <c r="L27" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19"/>
+      <c r="D28" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="F28" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="G28" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="H28" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="I28" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="J28" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="K28" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K28" s="16">
+      <c r="L28" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="13"/>
+      <c r="D29" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="E29" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="F29" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="G29" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="H29" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="I29" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="J29" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="K29" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K29" s="16">
+      <c r="L29" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B30" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="E30" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="F30" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="G30" s="23" t="s">
         <v>164</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>165</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="J30" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="K30" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K30" s="16">
+      <c r="L30" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B31" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="13"/>
+      <c r="D31" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="E31" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="G31" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="H31" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="I31" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="J31" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="K31" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K31" s="16">
+      <c r="L31" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="E32" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="F32" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="G32" s="23" t="s">
         <v>174</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>175</v>
       </c>
       <c r="H32" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="K32" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K32" s="16">
+      <c r="L32" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
+    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="25"/>
+      <c r="D33" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="E33" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="F33" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="G33" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="H33" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="I33" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="J33" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="K33" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K33" s="16">
+      <c r="L33" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="19"/>
+      <c r="D34" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="E34" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="F34" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="G34" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="H34" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="I34" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="J34" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="K34" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K34" s="16">
+      <c r="L34" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="70.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
+    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B35" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="19"/>
+      <c r="D35" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="E35" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="F35" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="G35" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="G35" s="30" t="s">
+      <c r="H35" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="I35" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="J35" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="K35" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K35" s="16">
+      <c r="L35" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="69.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="26">
+      <c r="C36" s="19"/>
+      <c r="D36" s="26">
         <v>4</v>
       </c>
-      <c r="D36" s="26">
+      <c r="E36" s="26">
         <v>8</v>
       </c>
-      <c r="E36" s="31">
+      <c r="F36" s="31">
         <v>12</v>
       </c>
-      <c r="F36" s="32">
+      <c r="G36" s="32">
         <v>24</v>
       </c>
-      <c r="G36" s="26">
+      <c r="H36" s="26">
         <v>36</v>
       </c>
-      <c r="H36" s="26">
+      <c r="I36" s="26">
         <v>4</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="J36" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="K36" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K36" s="16">
+      <c r="L36" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
+    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="33"/>
+      <c r="D37" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="E37" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="E37" s="34" t="s">
+      <c r="F37" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="G37" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="G37" s="34" t="s">
+      <c r="H37" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="H37" s="34" t="s">
+      <c r="I37" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="J37" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="K37" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K37" s="16">
+      <c r="L37" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
+    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="36"/>
+      <c r="D38" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="E38" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="F38" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="G38" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="H38" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="H38" s="26" t="s">
+      <c r="I38" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="J38" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="K38" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K38" s="37">
+      <c r="L38" s="37">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
+    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="B39" s="37"/>
-      <c r="C39" s="38">
+      <c r="C39" s="37"/>
+      <c r="D39" s="38">
         <v>0.08</v>
       </c>
-      <c r="D39" s="38">
+      <c r="E39" s="38">
         <v>0.16</v>
       </c>
-      <c r="E39" s="38">
+      <c r="F39" s="38">
         <v>0.32</v>
       </c>
-      <c r="F39" s="38">
+      <c r="G39" s="38">
         <v>0.64</v>
       </c>
-      <c r="G39" s="38">
+      <c r="H39" s="38">
         <v>0.96</v>
       </c>
-      <c r="H39" s="38">
+      <c r="I39" s="38">
         <v>0.32</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="J39" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="K39" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K39" s="16">
+      <c r="L39" s="16">
         <v>2</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9126BCEA-8BBB-45DA-8925-43214C8372E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B4EB59-82F8-4BE8-8FFE-DEBD19CCD290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="219">
   <si>
     <t>Option 1</t>
   </si>
@@ -11767,18 +11767,6 @@
   </si>
   <si>
     <t>Q21M21</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>SIMPLE</t>
-  </si>
-  <si>
-    <t>GROUP</t>
-  </si>
-  <si>
-    <t>QUESTION</t>
   </si>
 </sst>
 </file>
@@ -12464,7 +12452,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -12498,37 +12486,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12658,44 +12620,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13000,1396 +12924,1291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K3" s="43"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="K6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="5">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="6">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6">
+        <v>15</v>
+      </c>
+      <c r="F8" s="6">
+        <v>17</v>
+      </c>
+      <c r="G8" s="6">
+        <v>25</v>
+      </c>
+      <c r="H8" s="6">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="5">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="39"/>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="39"/>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6">
         <v>15</v>
       </c>
+      <c r="F12" s="6">
+        <v>8</v>
+      </c>
+      <c r="G12" s="6">
+        <v>23</v>
+      </c>
+      <c r="H12" s="6">
+        <v>15</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" s="5">
+    <row r="13" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L3" s="43"/>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="L7" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="6">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6">
-        <v>13</v>
-      </c>
-      <c r="F8" s="6">
-        <v>15</v>
-      </c>
-      <c r="G8" s="6">
-        <v>17</v>
-      </c>
-      <c r="H8" s="6">
-        <v>25</v>
-      </c>
-      <c r="I8" s="6">
-        <v>11</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="L8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="L9" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L10" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="6">
-        <v>3</v>
-      </c>
-      <c r="E12" s="6">
-        <v>5</v>
-      </c>
-      <c r="F12" s="6">
-        <v>15</v>
-      </c>
-      <c r="G12" s="6">
-        <v>8</v>
-      </c>
-      <c r="H12" s="6">
-        <v>23</v>
-      </c>
-      <c r="I12" s="6">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L12" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L13" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" s="48" t="s">
+    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="D14" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>54</v>
+      <c r="I14" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="41"/>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="L14" s="5">
-        <v>1</v>
+      <c r="K15" s="5">
+        <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L15" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="49" t="s">
+    <row r="16" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="D16" s="10" t="s">
         <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>74</v>
+      <c r="I16" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="5">
+      <c r="K16" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B17" s="49" t="s">
+    <row r="17" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="D17" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="7" t="s">
         <v>80</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>81</v>
+      <c r="I17" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="J18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="L17" s="5">
-        <v>2</v>
+      <c r="K18" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="50" t="s">
+    <row r="19" spans="1:11" ht="126" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="E19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>92</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>93</v>
+      <c r="I19" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="J20" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="L19" s="5">
-        <v>1</v>
+      <c r="K20" s="5">
+        <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L20" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B21" s="50" t="s">
+    <row r="21" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="D21" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="F21" s="11" t="s">
         <v>124</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="I21" s="8" t="s">
-        <v>102</v>
+      <c r="I21" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K21" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="L21" s="5">
+      <c r="K22" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="52" t="s">
+    <row r="23" spans="1:11" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="10" t="s">
+      <c r="B23" s="37"/>
+      <c r="C23" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="D23" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="E23" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="12" t="s">
         <v>127</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>111</v>
+      <c r="I23" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K23" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L23" s="5">
+      <c r="J24" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="15" t="s">
+    <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K24" s="15" t="s">
+      <c r="J25" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L24" s="16">
+      <c r="K25" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K26" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K27" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K28" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K29" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L25" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L26" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L27" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L28" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L29" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B30" s="54" t="s">
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="D30" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F30" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="F30" s="23" t="s">
         <v>164</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>165</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="I30" s="21" t="s">
-        <v>165</v>
+      <c r="I30" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="J30" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K30" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="J31" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L30" s="16">
+      <c r="K31" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L31" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="54" t="s">
+    <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="24" t="s">
+      <c r="B32" s="19"/>
+      <c r="C32" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="D32" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="E32" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="F32" s="23" t="s">
         <v>174</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="H32" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="I32" s="21" t="s">
-        <v>175</v>
+      <c r="I32" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="J32" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K32" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="I33" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="J33" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L32" s="16">
+      <c r="K33" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B33" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="J33" s="15" t="s">
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I34" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K33" s="15" t="s">
+      <c r="J34" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L33" s="16">
+      <c r="K34" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="70.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K35" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="26">
+        <v>4</v>
+      </c>
+      <c r="D36" s="26">
+        <v>8</v>
+      </c>
+      <c r="E36" s="31">
+        <v>12</v>
+      </c>
+      <c r="F36" s="32">
+        <v>24</v>
+      </c>
+      <c r="G36" s="26">
+        <v>36</v>
+      </c>
+      <c r="H36" s="26">
+        <v>4</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K36" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B34" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="J34" s="15" t="s">
+    <row r="37" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A37" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" s="33"/>
+      <c r="C37" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K34" s="15" t="s">
+      <c r="J37" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L34" s="16">
+      <c r="K37" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="54" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="H35" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="J35" s="15" t="s">
+    <row r="38" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B38" s="36"/>
+      <c r="C38" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="J38" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L35" s="16">
+      <c r="K38" s="37">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B36" s="54" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="26">
-        <v>4</v>
-      </c>
-      <c r="E36" s="26">
-        <v>8</v>
-      </c>
-      <c r="F36" s="31">
-        <v>12</v>
-      </c>
-      <c r="G36" s="32">
-        <v>24</v>
-      </c>
-      <c r="H36" s="26">
-        <v>36</v>
-      </c>
-      <c r="I36" s="26">
-        <v>4</v>
-      </c>
-      <c r="J36" s="15" t="s">
+    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39" s="37"/>
+      <c r="C39" s="38">
+        <v>0.08</v>
+      </c>
+      <c r="D39" s="38">
+        <v>0.16</v>
+      </c>
+      <c r="E39" s="38">
+        <v>0.32</v>
+      </c>
+      <c r="F39" s="38">
+        <v>0.64</v>
+      </c>
+      <c r="G39" s="38">
+        <v>0.96</v>
+      </c>
+      <c r="H39" s="38">
+        <v>0.32</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K36" s="15" t="s">
+      <c r="J39" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L36" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>215</v>
-      </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="F37" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L37" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B38" s="57" t="s">
-        <v>216</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L38" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B39" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="38">
-        <v>0.08</v>
-      </c>
-      <c r="E39" s="38">
-        <v>0.16</v>
-      </c>
-      <c r="F39" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="G39" s="38">
-        <v>0.64</v>
-      </c>
-      <c r="H39" s="38">
-        <v>0.96</v>
-      </c>
-      <c r="I39" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K39" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L39" s="16">
+      <c r="K39" s="16">
         <v>2</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\VER_01_02_26\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B4EB59-82F8-4BE8-8FFE-DEBD19CCD290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C8CDE0-A403-4AB2-A6CC-7A2AF6D12FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="223">
   <si>
     <t>Option 1</t>
   </si>
@@ -11767,6 +11767,18 @@
   </si>
   <si>
     <t>Q21M21</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SIMPLE</t>
+  </si>
+  <si>
+    <t>GROUP</t>
+  </si>
+  <si>
+    <t>QUESTION</t>
   </si>
 </sst>
 </file>
@@ -12452,7 +12464,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -12486,11 +12498,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12620,6 +12658,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12924,1291 +13000,1402 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="5">
+      <c r="L2" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
     </row>
-    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="K4" s="5">
+      <c r="K7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="39"/>
+      <c r="D8" s="6">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>13</v>
+      </c>
+      <c r="F8" s="6">
+        <v>15</v>
+      </c>
+      <c r="G8" s="6">
+        <v>17</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <v>11</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="39"/>
+      <c r="D10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="5">
+      <c r="F12" s="6">
+        <v>15</v>
+      </c>
+      <c r="G12" s="6">
+        <v>8</v>
+      </c>
+      <c r="H12" s="6">
+        <v>23</v>
+      </c>
+      <c r="I12" s="6">
+        <v>15</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L12" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="K6" s="5">
-        <v>3</v>
+    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K7" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="6">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6">
-        <v>13</v>
-      </c>
-      <c r="E8" s="6">
-        <v>15</v>
-      </c>
-      <c r="F8" s="6">
-        <v>17</v>
-      </c>
-      <c r="G8" s="6">
-        <v>25</v>
-      </c>
-      <c r="H8" s="6">
-        <v>11</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K9" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K10" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="6">
-        <v>3</v>
-      </c>
-      <c r="D12" s="6">
-        <v>5</v>
-      </c>
-      <c r="E12" s="6">
-        <v>15</v>
-      </c>
-      <c r="F12" s="6">
-        <v>8</v>
-      </c>
-      <c r="G12" s="6">
-        <v>23</v>
-      </c>
-      <c r="H12" s="6">
-        <v>15</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K12" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K13" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="41"/>
+      <c r="D14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
+    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K15" s="5">
+      <c r="L15" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10" t="s">
-        <v>72</v>
-      </c>
+      <c r="C16" s="9"/>
       <c r="D16" s="10" t="s">
         <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="G16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="I16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="5">
+      <c r="L16" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K17" s="5">
+      <c r="L17" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="I18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="J18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="5">
+      <c r="L18" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="126" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K19" s="5">
+      <c r="L19" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="J20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="K20" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K20" s="5">
+      <c r="L20" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B21" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="G21" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="K21" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K21" s="5">
+      <c r="L21" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="8"/>
+      <c r="D22" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K22" s="5">
+      <c r="L22" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="F23" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K23" s="5">
+      <c r="L23" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="H24" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H24" s="14" t="s">
+      <c r="I24" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="J24" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="K24" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K24" s="16">
+      <c r="L24" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="E25" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="F25" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="G25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="H25" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="I25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="J25" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="K25" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K25" s="16">
+      <c r="L25" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="13"/>
+      <c r="D26" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="E26" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="F26" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="H26" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="I26" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="J26" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="K26" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K26" s="16">
+      <c r="L26" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="19"/>
+      <c r="D27" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="F27" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="G27" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="H27" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="I27" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="J27" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="K27" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K27" s="16">
+      <c r="L27" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19"/>
+      <c r="D28" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="F28" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="G28" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="H28" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="I28" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="J28" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="K28" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K28" s="16">
+      <c r="L28" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="13"/>
+      <c r="D29" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="E29" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="F29" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="G29" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="H29" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="I29" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="J29" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="K29" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K29" s="16">
+      <c r="L29" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B30" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="E30" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="F30" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="G30" s="23" t="s">
         <v>164</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>165</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="J30" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="K30" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K30" s="16">
+      <c r="L30" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B31" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="13"/>
+      <c r="D31" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="E31" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="G31" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="H31" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="I31" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="J31" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="K31" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K31" s="16">
+      <c r="L31" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="E32" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="F32" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="G32" s="23" t="s">
         <v>174</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>175</v>
       </c>
       <c r="H32" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="K32" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K32" s="16">
+      <c r="L32" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
+    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="25"/>
+      <c r="D33" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="E33" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="F33" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="G33" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="H33" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="I33" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="J33" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="K33" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K33" s="16">
+      <c r="L33" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="19"/>
+      <c r="D34" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="E34" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="F34" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="G34" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="H34" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="I34" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="J34" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="K34" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K34" s="16">
+      <c r="L34" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="70.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
+    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B35" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="19"/>
+      <c r="D35" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="E35" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="F35" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="G35" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="G35" s="30" t="s">
+      <c r="H35" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="I35" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="J35" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="K35" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K35" s="16">
+      <c r="L35" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="69.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="26">
+      <c r="C36" s="19"/>
+      <c r="D36" s="26">
         <v>4</v>
       </c>
-      <c r="D36" s="26">
+      <c r="E36" s="26">
         <v>8</v>
       </c>
-      <c r="E36" s="31">
+      <c r="F36" s="31">
         <v>12</v>
       </c>
-      <c r="F36" s="32">
+      <c r="G36" s="32">
         <v>24</v>
       </c>
-      <c r="G36" s="26">
+      <c r="H36" s="26">
         <v>36</v>
       </c>
-      <c r="H36" s="26">
+      <c r="I36" s="26">
         <v>4</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="J36" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="K36" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K36" s="16">
+      <c r="L36" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
+    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="33"/>
+      <c r="D37" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="E37" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="E37" s="34" t="s">
+      <c r="F37" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="G37" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="G37" s="34" t="s">
+      <c r="H37" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="H37" s="34" t="s">
+      <c r="I37" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="J37" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="K37" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K37" s="16">
+      <c r="L37" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
+    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="36"/>
+      <c r="D38" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="E38" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="F38" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="G38" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="H38" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="H38" s="26" t="s">
+      <c r="I38" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="J38" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="K38" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K38" s="37">
+      <c r="L38" s="37">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
+    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="B39" s="37"/>
-      <c r="C39" s="38">
+      <c r="C39" s="37"/>
+      <c r="D39" s="38">
         <v>0.08</v>
       </c>
-      <c r="D39" s="38">
+      <c r="E39" s="38">
         <v>0.16</v>
       </c>
-      <c r="E39" s="38">
+      <c r="F39" s="38">
         <v>0.32</v>
       </c>
-      <c r="F39" s="38">
+      <c r="G39" s="38">
         <v>0.64</v>
       </c>
-      <c r="G39" s="38">
+      <c r="H39" s="38">
         <v>0.96</v>
       </c>
-      <c r="H39" s="38">
+      <c r="I39" s="38">
         <v>0.32</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="J39" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="K39" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K39" s="16">
+      <c r="L39" s="16">
         <v>2</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\VER_01_02_26\MED-CONTEST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C8CDE0-A403-4AB2-A6CC-7A2AF6D12FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C2C200-5F6C-4B7E-B2D9-96767F319AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="224">
   <si>
     <t>Option 1</t>
   </si>
@@ -11779,6 +11779,9 @@
   </si>
   <si>
     <t>QUESTION</t>
+  </si>
+  <si>
+    <t>IM22-11</t>
   </si>
 </sst>
 </file>
@@ -12528,7 +12531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12696,6 +12699,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13000,7 +13004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -14399,6 +14403,44 @@
         <v>2</v>
       </c>
     </row>
+    <row r="40" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="59" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L40" s="16">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C2C200-5F6C-4B7E-B2D9-96767F319AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC2AD1A-080B-4767-AD19-27F888E7935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="230">
   <si>
     <t>Option 1</t>
   </si>
@@ -11782,6 +11804,24 @@
   </si>
   <si>
     <t>IM22-11</t>
+  </si>
+  <si>
+    <t>$\lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=0}^{n-1}{f\left(a+k\frac{b-a}{n}\right)=\ \lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=1}^{n}{f\left(a+k\frac{b-a}{n}\right)=\ \int_{a}^{b}f\left(x\right)dx}}\ }}$</t>
+  </si>
+  <si>
+    <t>$\lim\below{n\rightarrow\infty}{U_n=\ -\infty}$</t>
+  </si>
+  <si>
+    <t>$U_{n+1}=\ -1-\ \frac{1}{4\ U_n}$</t>
+  </si>
+  <si>
+    <t>$U_{n+1}=\ {(U_n)}^{2024}$</t>
+  </si>
+  <si>
+    <t>${U_0\ +\ U_1\ +\ ....\ +\ U}_n=\ {(2)}^{(n+1)}\ -1$</t>
+  </si>
+  <si>
+    <t>${U_0\ +\ U_1\ +\ ....\ +\ U}_n=\ (n+1)(n+3)$</t>
   </si>
 </sst>
 </file>
@@ -12717,6 +12757,70 @@
 </styleSheet>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -13004,7 +13108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -13056,7 +13160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>220</v>
       </c>
@@ -13092,7 +13196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>221</v>
       </c>
@@ -13113,7 +13217,7 @@
       </c>
       <c r="L3" s="43"/>
     </row>
-    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>222</v>
       </c>
@@ -13147,7 +13251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>222</v>
       </c>
@@ -13181,7 +13285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>222</v>
       </c>
@@ -13215,7 +13319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>220</v>
       </c>
@@ -13251,7 +13355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>220</v>
       </c>
@@ -13287,7 +13391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>220</v>
       </c>
@@ -13323,7 +13427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>220</v>
       </c>
@@ -13359,7 +13463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>220</v>
       </c>
@@ -13395,7 +13499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>220</v>
       </c>
@@ -13431,7 +13535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="63" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>220</v>
       </c>
@@ -13467,7 +13571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="63" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>220</v>
       </c>
@@ -13503,7 +13607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="94.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>220</v>
       </c>
@@ -13539,7 +13643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>220</v>
       </c>
@@ -13575,7 +13679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="94.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>220</v>
       </c>
@@ -13611,7 +13715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="78.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>220</v>
       </c>
@@ -13647,7 +13751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="126" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>220</v>
       </c>
@@ -13683,7 +13787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>220</v>
       </c>
@@ -13719,7 +13823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>220</v>
       </c>
@@ -13755,7 +13859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>220</v>
       </c>
@@ -13791,7 +13895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="283.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>220</v>
       </c>
@@ -13827,7 +13931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>220</v>
       </c>
@@ -13863,7 +13967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>220</v>
       </c>
@@ -13899,7 +14003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>220</v>
       </c>
@@ -13935,7 +14039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>220</v>
       </c>
@@ -13971,7 +14075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>220</v>
       </c>
@@ -14007,7 +14111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>220</v>
       </c>
@@ -14043,7 +14147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>220</v>
       </c>
@@ -14079,7 +14183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>220</v>
       </c>
@@ -14115,7 +14219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>220</v>
       </c>
@@ -14151,7 +14255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>220</v>
       </c>
@@ -14187,7 +14291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>220</v>
       </c>
@@ -14223,7 +14327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="70.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>220</v>
       </c>
@@ -14259,7 +14363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="69.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>220</v>
       </c>
@@ -14295,7 +14399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>220</v>
       </c>
@@ -14331,7 +14435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>220</v>
       </c>
@@ -14367,7 +14471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>220</v>
       </c>
@@ -14407,8 +14511,8 @@
       <c r="A40" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="B40" t="s">
-        <v>223</v>
+      <c r="B40" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="C40" t="s">
         <v>223</v>
@@ -14438,6 +14542,41 @@
         <v>136</v>
       </c>
       <c r="L40" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="59" t="s">
+        <v>220</v>
+      </c>
+      <c r="B41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L41" s="16">
         <v>1</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC2AD1A-080B-4767-AD19-27F888E7935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32DC4F3-3C78-4FB4-8B99-800B920BF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC2AD1A-080B-4767-AD19-27F888E7935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E1886F-718F-4DCD-92FC-B3076ACBE53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,30 +24,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="230">
   <si>
     <t>Option 1</t>
   </si>
@@ -11803,9 +11781,6 @@
     <t>QUESTION</t>
   </si>
   <si>
-    <t>IM22-11</t>
-  </si>
-  <si>
     <t>$\lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=0}^{n-1}{f\left(a+k\frac{b-a}{n}\right)=\ \lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=1}^{n}{f\left(a+k\frac{b-a}{n}\right)=\ \int_{a}^{b}f\left(x\right)dx}}\ }}$</t>
   </si>
   <si>
@@ -11822,6 +11797,9 @@
   </si>
   <si>
     <t>${U_0\ +\ U_1\ +\ ....\ +\ U}_n=\ (n+1)(n+3)$</t>
+  </si>
+  <si>
+    <t>LA QUESTION A POSER $U_{n+1}=\ {(U_n)}^{2024}$ EST RELATIVE 0 L'IMAGE A COTE</t>
   </si>
 </sst>
 </file>
@@ -12757,70 +12735,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -13160,7 +13074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>220</v>
       </c>
@@ -13196,7 +13110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>221</v>
       </c>
@@ -13217,7 +13131,7 @@
       </c>
       <c r="L3" s="43"/>
     </row>
-    <row r="4" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>222</v>
       </c>
@@ -13251,7 +13165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>222</v>
       </c>
@@ -13285,7 +13199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>222</v>
       </c>
@@ -13319,7 +13233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>220</v>
       </c>
@@ -13355,7 +13269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>220</v>
       </c>
@@ -13391,7 +13305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>220</v>
       </c>
@@ -13427,7 +13341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>220</v>
       </c>
@@ -13463,7 +13377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>220</v>
       </c>
@@ -13499,7 +13413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>220</v>
       </c>
@@ -13535,7 +13449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="63" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>220</v>
       </c>
@@ -13571,7 +13485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="63" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>220</v>
       </c>
@@ -13607,7 +13521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="94.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>220</v>
       </c>
@@ -13643,7 +13557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>220</v>
       </c>
@@ -13679,7 +13593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="94.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>220</v>
       </c>
@@ -13715,7 +13629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="78.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>220</v>
       </c>
@@ -13751,7 +13665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="126" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>220</v>
       </c>
@@ -13787,7 +13701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>220</v>
       </c>
@@ -13823,7 +13737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>220</v>
       </c>
@@ -13859,7 +13773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>220</v>
       </c>
@@ -13895,7 +13809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="283.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>220</v>
       </c>
@@ -13931,7 +13845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>220</v>
       </c>
@@ -13967,7 +13881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>220</v>
       </c>
@@ -14003,7 +13917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>220</v>
       </c>
@@ -14039,7 +13953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>220</v>
       </c>
@@ -14075,7 +13989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>220</v>
       </c>
@@ -14111,7 +14025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>220</v>
       </c>
@@ -14147,7 +14061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>220</v>
       </c>
@@ -14183,7 +14097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>220</v>
       </c>
@@ -14219,7 +14133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>220</v>
       </c>
@@ -14255,7 +14169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>220</v>
       </c>
@@ -14291,7 +14205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>220</v>
       </c>
@@ -14327,7 +14241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="70.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>220</v>
       </c>
@@ -14363,7 +14277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="69.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>220</v>
       </c>
@@ -14399,7 +14313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>220</v>
       </c>
@@ -14435,7 +14349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>220</v>
       </c>
@@ -14471,7 +14385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>220</v>
       </c>
@@ -14511,11 +14425,11 @@
       <c r="A40" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="B40" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C40" t="s">
-        <v>223</v>
+      <c r="B40" t="s">
+        <v>229</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>166</v>
@@ -14550,25 +14464,25 @@
         <v>220</v>
       </c>
       <c r="B41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D41" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="E41" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="F41" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="G41" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="H41" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="H41" s="21" t="s">
-        <v>229</v>
-      </c>
       <c r="I41" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J41" s="15" t="s">
         <v>42</v>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32DC4F3-3C78-4FB4-8B99-800B920BF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345CF74E-2E03-48EE-BC44-644174188C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,30 +24,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="231">
   <si>
     <t>Option 1</t>
   </si>
@@ -11803,9 +11781,6 @@
     <t>QUESTION</t>
   </si>
   <si>
-    <t>IM22-11</t>
-  </si>
-  <si>
     <t>$\lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=0}^{n-1}{f\left(a+k\frac{b-a}{n}\right)=\ \lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=1}^{n}{f\left(a+k\frac{b-a}{n}\right)=\ \int_{a}^{b}f\left(x\right)dx}}\ }}$</t>
   </si>
   <si>
@@ -11822,6 +11797,12 @@
   </si>
   <si>
     <t>${U_0\ +\ U_1\ +\ ....\ +\ U}_n=\ (n+1)(n+3)$</t>
+  </si>
+  <si>
+    <t>LA QUESTION A POSER $U_{n+1}=\ {(U_n)}^{2024}$ EST RELATIVE 0 L'IMAGE A COTE</t>
+  </si>
+  <si>
+    <t>Q22M22</t>
   </si>
 </sst>
 </file>
@@ -12757,70 +12738,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -13160,7 +13077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>220</v>
       </c>
@@ -13196,7 +13113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>221</v>
       </c>
@@ -13217,7 +13134,7 @@
       </c>
       <c r="L3" s="43"/>
     </row>
-    <row r="4" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>222</v>
       </c>
@@ -13251,7 +13168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>222</v>
       </c>
@@ -13285,7 +13202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>222</v>
       </c>
@@ -13319,7 +13236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>220</v>
       </c>
@@ -13355,7 +13272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>220</v>
       </c>
@@ -13391,7 +13308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>220</v>
       </c>
@@ -13427,7 +13344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>220</v>
       </c>
@@ -13463,7 +13380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>220</v>
       </c>
@@ -13499,7 +13416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>220</v>
       </c>
@@ -13535,7 +13452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="63" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>220</v>
       </c>
@@ -13571,7 +13488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="63" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>220</v>
       </c>
@@ -13607,7 +13524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="94.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>220</v>
       </c>
@@ -13643,7 +13560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>220</v>
       </c>
@@ -13679,7 +13596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="94.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>220</v>
       </c>
@@ -13715,7 +13632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="78.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>220</v>
       </c>
@@ -13751,7 +13668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="126" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>220</v>
       </c>
@@ -13787,7 +13704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>220</v>
       </c>
@@ -13823,7 +13740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>220</v>
       </c>
@@ -13859,7 +13776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="47.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>220</v>
       </c>
@@ -13895,7 +13812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="283.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>220</v>
       </c>
@@ -13931,7 +13848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>220</v>
       </c>
@@ -13967,7 +13884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>220</v>
       </c>
@@ -14003,7 +13920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>220</v>
       </c>
@@ -14039,7 +13956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>220</v>
       </c>
@@ -14075,7 +13992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>220</v>
       </c>
@@ -14111,7 +14028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>220</v>
       </c>
@@ -14147,7 +14064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>220</v>
       </c>
@@ -14183,7 +14100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>220</v>
       </c>
@@ -14219,7 +14136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>220</v>
       </c>
@@ -14255,7 +14172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>220</v>
       </c>
@@ -14291,7 +14208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>220</v>
       </c>
@@ -14327,7 +14244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="70.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>220</v>
       </c>
@@ -14363,7 +14280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="69.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>220</v>
       </c>
@@ -14399,7 +14316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>220</v>
       </c>
@@ -14435,7 +14352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>220</v>
       </c>
@@ -14471,7 +14388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>220</v>
       </c>
@@ -14511,11 +14428,11 @@
       <c r="A40" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="B40" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C40" t="s">
-        <v>223</v>
+      <c r="B40" t="s">
+        <v>229</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>166</v>
@@ -14550,25 +14467,25 @@
         <v>220</v>
       </c>
       <c r="B41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D41" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="E41" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="F41" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="G41" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="H41" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="H41" s="21" t="s">
-        <v>229</v>
-      </c>
       <c r="I41" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J41" s="15" t="s">
         <v>42</v>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,18 +5,29 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamch\OneDrive\Desktop\TEMPLATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345CF74E-2E03-48EE-BC44-644174188C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B378B1-BAB7-423B-AE2C-473F9FE1EF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="383">
   <si>
     <t>Option 1</t>
   </si>
@@ -121,30 +132,6 @@
   </si>
   <si>
     <t>Rate</t>
-  </si>
-  <si>
-    <t>Inflammation</t>
-  </si>
-  <si>
-    <t>hypertension</t>
-  </si>
-  <si>
-    <t>glycémie</t>
-  </si>
-  <si>
-    <t>infection</t>
-  </si>
-  <si>
-    <t>Puissance</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Force</t>
-  </si>
-  <si>
-    <t>Travail</t>
   </si>
   <si>
     <t>PHYSIQUE</t>
@@ -1542,12 +1529,6 @@
   </si>
   <si>
     <t>Physiologie</t>
-  </si>
-  <si>
-    <t>Pression</t>
-  </si>
-  <si>
-    <t>Huminité</t>
   </si>
   <si>
     <t>Bernard</t>
@@ -5959,15 +5940,6 @@
   </si>
   <si>
     <t>Quelle est la différence entre la souris et le rat ?</t>
-  </si>
-  <si>
-    <t>Dimension de R.T</t>
-  </si>
-  <si>
-    <t>plus petit nombre premier supérieur à 10</t>
-  </si>
-  <si>
-    <t>PCR</t>
   </si>
   <si>
     <t>Auteur de la théorie de réaction dans l'eau</t>
@@ -11781,9 +11753,6 @@
     <t>QUESTION</t>
   </si>
   <si>
-    <t>$\lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=0}^{n-1}{f\left(a+k\frac{b-a}{n}\right)=\ \lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=1}^{n}{f\left(a+k\frac{b-a}{n}\right)=\ \int_{a}^{b}f\left(x\right)dx}}\ }}$</t>
-  </si>
-  <si>
     <t>$\lim\below{n\rightarrow\infty}{U_n=\ -\infty}$</t>
   </si>
   <si>
@@ -11803,6 +11772,530 @@
   </si>
   <si>
     <t>Q22M22</t>
+  </si>
+  <si>
+    <t>(A) : $𝒛=√𝟏𝟎+𝟓√𝟐𝟐−𝒊√𝟏𝟎−𝟓√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(B) : $𝒛=√𝟐+√𝟐𝟐−𝒊√𝟐−√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(C) : $𝒛=√𝟏𝟎+𝟓√𝟐𝟐+𝒊√𝟏𝟎−𝟓√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(D) : $𝒛=√𝟐+√𝟐𝟐+𝒊√𝟐−√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(E) : $𝒛=√𝟏𝟎+𝟓√𝟐𝟐−𝒊√𝟏𝟎+𝟓√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>$U_{\mathrm{n}}=\frac{1}{2}+\frac{1}{2^{2}}+\frac{1}{2^{3}}+\cdots+\frac{1}{2^{n}}$ et $\boldsymbol{\operatorname { l n }}\left(V_{\mathrm{n}}\right)=U_{\mathrm{n}} \boldsymbol{\operatorname { l n }}(2)$; alors :</t>
+  </si>
+  <si>
+    <t>Pour tout $n$ entier et $n \geq 1$, on pose: 
+$U_{\mathrm{n}}=\frac{1}{2}+\frac{1}{2^{2}}+\frac{1}{2^{3}}+\cdots+\frac{1}{2^{n}}$      et       $\boldsymbol{\operatorname { l n }}\left(V_{\mathrm{n}}\right)=U_{\mathrm{n}} \boldsymbol{\operatorname { l n }}(2)$;       alors :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(A): $\lim _{n \rightarrow+\infty} U_{n}=1$ et $\lim _{n \rightarrow+\infty} V_{n}=\ln (2)$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $\lim _{n \rightarrow+\infty} U_{n}=\frac{1}{2}$ et $\lim _{n \rightarrow+\infty} V_{n}=\ln (2)$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C): $\lim _{n \rightarrow+\infty} U_{n}=2$ et $\lim _{n \rightarrow+\infty} V_{n}=1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $\lim _{n \rightarrow+\infty} U_{n}=\frac{1}{2}$ et $\lim _{n \rightarrow+\infty} V_{n}=2$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(E): $\lim _{\mathbf{n} \rightarrow+\infty} \mathbf{U}_{\mathbf{n}}=\mathbf{1}$ et $\lim _{\mathbf{n} \rightarrow+\infty} V_{\mathbf{n}}=\mathbf{2}$</t>
+  </si>
+  <si>
+    <t>Soit $\mathbf{f}$ une fonction définie sur $] 0 ;+\infty\left[\operatorname{par}: \boldsymbol{f}(\boldsymbol{x})=\frac{\sqrt{\boldsymbol{x}}}{\sqrt{\boldsymbol{x}+\mathbf{2} \sqrt{\boldsymbol{x}}}}\right.$          Alors $\lim _{x \rightarrow 0^{+}} f(x)$ est égale à :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $\mathbf{0}$;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(E): la limite n'existe pas</t>
+  </si>
+  <si>
+    <t>Soit $\mathbf{f}$ une fonction réelle tels que $\boldsymbol{f}(\mathbf{1})=\mathbf{3}$ et $\boldsymbol{f}^{\prime}(\mathbf{1})=-\mathbf{3}$      
+La courbe de la fonction f admet au point $\boldsymbol{A}(\mathbf{1} ; \mathbf{3})$ une tangente d'équation</t>
+  </si>
+  <si>
+    <t>Soit $\mathbf{g}$ une fonction définie sur $] 0 ;+\infty\left[\right.$ par $: \boldsymbol{g}(\boldsymbol{x})=\frac{(\mathbf{2 x})^{\boldsymbol{x}}}{\boldsymbol{x}^{\mathbf{2 x}}}$        Alors $\lim _{\mathbf{x} \rightarrow+\infty} \mathbf{g}(\mathbf{x})$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soient $\mathbf{f}$ et $\mathbf{g}$ deux fonctions définies par : $\boldsymbol{f}(\boldsymbol{x})=\boldsymbol{\operatorname { l n }}(\boldsymbol{x}-\mathbf{1})$ et $\boldsymbol{g}(\boldsymbol{x})=\sqrt{\boldsymbol{x}+\mathbf{1}}$    Alors le domaine de définition de gof est</t>
+  </si>
+  <si>
+    <t>Dans $\mathbb{C}$, si $\mathrm{z}=\sqrt{5} e^{-i \frac{\pi}{8}}$ alors :</t>
+  </si>
+  <si>
+    <t>Le nombre complexe $z=\left(\frac{1}{\sqrt{2}}(1-i \sqrt{3})\right)^{18}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Pour $z \in \mathbb{C}-\{1\}$, l'ensemble des points $M$ d'affixe $z$ tels que $\frac{z+1}{z-1} \in i \mathbb{R}$ est :</t>
+  </si>
+  <si>
+    <t>Pour tout $n$ entier et $n \geq 2$, on pose: $$U_{n}=\left(1-\frac{1}{2^{2}}\right) \times\left(1-\frac{1}{3^{2}}\right) \times \ldots \times\left(1-\frac{1}{n^{2}}\right)$$    Alors $\lim _{n \rightarrow+\infty} U_{n}$ est égale à :</t>
+  </si>
+  <si>
+    <t>(A) $: Z=\frac{\sqrt{10+5 \sqrt{2}}}{2}-\frac{i \sqrt{10-5 \sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(B) $: Z=\frac{\sqrt{2+\sqrt{2}}}{2}-\frac{i \sqrt{2-\sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(C) $: Z=\frac{\sqrt{10+5 \sqrt{2}}}{2}+\frac{i \sqrt{10-5 \sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(D) $: z=\frac{\sqrt{2+\sqrt{2}}}{2}+\frac{i \sqrt{2-\sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(E): $Z=\frac{\sqrt{10+5 \sqrt{2}}}{2}-\frac{i \sqrt{10+5 \sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(E): $z=\frac{1}{2}-i \frac{\sqrt{3}}{2}$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{C}):+\infty$</t>
+  </si>
+  <si>
+    <t>(E): la limite n'existe pas</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{\frac{\pi}{6}}^{\frac{\pi}{4}} \frac{1}{\sin (x) \tan (x)}$ dx est égale à :</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{0}^{\frac{\pi}{2}} \frac{\sin (2 \mathrm{x})}{1+\sin ^{2}(x)} \mathrm{dx}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soit f une fonction réelle définie par $f(x)=x+x^{2} \sin \left(\frac{1}{x}\right)$ si $x \neq 0$ et $f(0)=0$    Alors :</t>
+  </si>
+  <si>
+    <t>$(A): 0$</t>
+  </si>
+  <si>
+    <t>$(B): \ln (2)+1$</t>
+  </si>
+  <si>
+    <t>$(C): \boldsymbol{f}^{\prime}(\mathbf{0})=\mathbf{1} \quad ;  \boldsymbol{\operatorname { s i n }}\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right)+\boldsymbol{\operatorname { c o s }}\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right)$</t>
+  </si>
+  <si>
+    <t>(E): $\boldsymbol{f}$ est dérivable en 0 et $\boldsymbol{f}^{\prime}(0)=2$</t>
+  </si>
+  <si>
+    <t>$(E): \frac{\mathbf{8} \times \mathbf{3}^{\boldsymbol{n}}}{\mathbf{1 1}^{\boldsymbol{n} \boldsymbol{-} \mathbf{1}}}$</t>
+  </si>
+  <si>
+    <t>(B): $z=\frac{\sqrt{3}}{2}-\frac{1}{2} i$</t>
+  </si>
+  <si>
+    <t>(A): z=-512</t>
+  </si>
+  <si>
+    <t>(C): z=512</t>
+  </si>
+  <si>
+    <t>(D): z=251</t>
+  </si>
+  <si>
+    <t>(C): Le cercle de centre $O$ et de rayon 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (D): la droite (Ox)</t>
+  </si>
+  <si>
+    <t>$(A): 1 \quad$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{B}): \quad \mathbf{0} \quad $</t>
+  </si>
+  <si>
+    <t>(D): $\frac{\mathbf{1}}{\mathbf{2}} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(A): $+\infty$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $\mathbf{0}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C): $\mathbf{1} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $\frac{\mathbf{1}}{\mathbf{2}} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C): 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $\mathbf{0} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(A): \mathbf{y}=\mathbf{3 x}-\mathbf{2}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(B): \mathbf{y}=\mathbf{3 x}-\mathbf{6}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(C): \mathbf{y}=-\mathbf{3 x}+\mathbf{6}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(E): \mathbf{y}=-\mathbf{3 x}+\mathbf{2}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(A): $[-\mathbf{1} ;+\infty[$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $] \mathbf{1} ;+\infty[\quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C) : $\left[\mathbf{1}+\frac{\mathbf{1}}{\boldsymbol{e}} ;+\infty[\right.$</t>
+  </si>
+  <si>
+    <t>(D): $\frac{\sqrt{\mathbf{2}}}{\mathbf{2}}-\frac{\mathbf{1}}{\mathbf{2}} \quad$</t>
+  </si>
+  <si>
+    <t>(A): $\frac{1}{2}-\frac{\sqrt{2}}{2}$</t>
+  </si>
+  <si>
+    <t>(B): $2-\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(C): $\sqrt{2}-2$</t>
+  </si>
+  <si>
+    <t>(C): $\ln (2) \quad$</t>
+  </si>
+  <si>
+    <t>(D): $1 \quad$</t>
+  </si>
+  <si>
+    <t>(E):$-\ln (2)$</t>
+  </si>
+  <si>
+    <t>Dans l'espace rapporté à un repère orthonormé $\operatorname{direct}(O, \vec{\imath}, \vec{\jmath}, \vec{k})$    Soit les plans $(P): x-y-z+2=0$ et $\left(P^{\prime}\right): x+z-2=0$ et la droite $(\Delta)$ telle que $\left\{\begin{array}{l}x=1+t;     \\ y=2+2 t;     \\ z=1-t\end{array} ;(t \in \mathbb{R})\right.$, alors :</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{A}):(\Delta) \subset(\boldsymbol{P})$</t>
+  </si>
+  <si>
+    <t>(A): $\frac{\mathbf{8} \times \mathbf{3}^{\boldsymbol{n}}}{\mathbf{1 1}^{\boldsymbol{n}}} \quad$</t>
+  </si>
+  <si>
+    <t>(B): $\frac{\mathbf{8 n} \times \mathbf{3}^{\boldsymbol{n}}}{\mathbf{1 1}^{\boldsymbol{n}}}$</t>
+  </si>
+  <si>
+    <t>(C): $\frac{8 n \times 3^{n-1}}{11^{n}} \quad$</t>
+  </si>
+  <si>
+    <t>(D): $\frac{\mathbf{8}^{\boldsymbol{n}} \times \mathbf{3}^{\boldsymbol{n - 1}}}{\mathbf{1 1}^{\boldsymbol{n}}}$</t>
+  </si>
+  <si>
+    <t>Une urne contient 5 boules bleus, 4 boules blanches et 3 boules noires. Les boules sont indiscernables au toucher.  On tire au hasard et simultanément 3 boules de ce sac, on répète cette expérience n fois de suite ( $n \geq  5$ ) en remettant dans l'urne les boules tirées après chaque tirage, La probabilité d'obtenir 3 boules de couleurs deux à deux distinctes ( $n-1$ ) fois exactement est :</t>
+  </si>
+  <si>
+    <t>$(C): \boldsymbol{f}^{\prime}(\mathbf{0})=\mathbf{1} \quad$</t>
+  </si>
+  <si>
+    <t>$(A): f$ est dérivable en $0 \quad$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{B}):(\Delta) \perp(\boldsymbol{P})$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{C}):(\Delta) \cap(\boldsymbol{P})=\emptyset$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{D}):(\Delta) \cap\left(\boldsymbol{P}^{\prime}\right)=\emptyset $</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{E}):(\Delta) \perp\left(\boldsymbol{P}^{\prime}\right)$</t>
+  </si>
+  <si>
+    <t>$\quad(\boldsymbol{E}): $\mathbf{1}-\sqrt{\mathbf{2}}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $] \boldsymbol{e} ;+\infty[\quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(E): $] \boldsymbol{-e} ;+\infty[\quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(D): \mathbf{y}=\mathbf{3 x}$</t>
+  </si>
+  <si>
+    <t>(B) : La droite $(O y)$ privée du point (0,1)</t>
+  </si>
+  <si>
+    <t>(A) : La droite $(O x)$ privée du point (1,0)</t>
+  </si>
+  <si>
+    <t>(E) : Le cercle de centre $O$ et de rayon 1 privée du point (1,0)</t>
+  </si>
+  <si>
+    <t>$ (B): \mathbf{f}^{\prime}(\mathbf{0})=\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{D}):\text{ Pour tout } \boldsymbol{x} \neq \mathbf{0}, \quad \boldsymbol{f}(\boldsymbol{x}) = \mathbf{1} + \mathbf{2}\boldsymbol{x}\sin\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right) + \cos\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right)$</t>
+  </si>
+  <si>
+    <t>Soit $I=\int_{0}^{\pi}|\cos x| d x$. Quelle est la valeur de $I$ ?</t>
+  </si>
+  <si>
+    <t>Quelle est la valeur de l'intégrale définie suivante : $J=\int_{0}^{1} \frac{1-x^{2}}{\left(1+x^{2}\right)^{2}}$</t>
+  </si>
+  <si>
+    <t>Soit la suite ( $U_{n}$ ) définie par : $U_{1}=1$ et pour tout $n \geq 1$,$$U_{n+1}=\sqrt{2+U_{n}}$$. Quelle est la limite de la suite ( $\boldsymbol{U}_{\boldsymbol{n}}$ ) ?</t>
+  </si>
+  <si>
+    <t>Soient $a$ et $b$ deux nombres complexes tels que : $a \neq b$ et $|a|=1$. Quelle est la valeur de :$$\left|\frac{a-b}{1-\bar{a} b}\right|$$</t>
+  </si>
+  <si>
+    <t>Soit $C=1+\cos \frac{\pi}{5}+\cos \frac{2 \pi}{5}+\cdots+\cos \frac{9 \pi}{5}$ et $S=\sin \frac{\pi}{5}+\sin \frac{2 \pi}{5}+\cdots+\sin \frac{9 \pi}{5}$. Quelle est la valeur de $\mathbf{z}=\mathbf{C}+\mathbf{i S}$.</t>
+  </si>
+  <si>
+    <t>Soit la fonction $\boldsymbol{f}(\boldsymbol{x})=\sin \boldsymbol{x}+\cos \boldsymbol{x}$. Quelle est la valeur maximale de $\mathbf{f}(\mathbf{x})$ sur $\mathbb{R}$ ?</t>
+  </si>
+  <si>
+    <t>Résoudre dans $R$ 1'équation : $\frac{e^{2 x-1}}{\sqrt{e^{2 x+4}}}=e^{-x}$. Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>Une urne $U$ contient 9 boules : dont 5 boules rouges numérotées de 1 à 5 et 4 boule noires numérotées de 1 à 4 . On suppose que les boules sont indiscernables au toucher. On tire simultanément deux boules de l'urne. On considère les deux événements $A$ : « les deux boules tirées sont de mème couleur» et $B$ « les deux boules tirés portent un numéro pair». Calculer $\boldsymbol{P}_{\bar{A}}(\boldsymbol{B})$ ?</t>
+  </si>
+  <si>
+    <t>On lance deux dés équilibrés à 6 faces. Quelle est la probabilité d'obtenir au moins un 6 ?</t>
+  </si>
+  <si>
+    <t>Soient les points : $A(1,1,-2), B(0,5,5), C(6,-3,-5), D(1,2,0)$, Levecteur $\overrightarrow{A D}$ appartient-il au plan vectoriel engendré par $\overrightarrow{\mathrm{AB}} \boldsymbol{e} \boldsymbol{t}. Autrement dit, existe-t-il des réels $x$ et y tels que : $\overrightarrow{A D}=x \overrightarrow{A B}+y \overrightarrow{A C}$ ? \overrightarrow{\mathrm{AC}}$</t>
+  </si>
+  <si>
+    <t>Soient $\vec{u}(1,2,-1), \vec{v}(3,6,-3), \vec{w}(0,1,1)$. Quelle est la valeur de ce produit $(\overrightarrow{\boldsymbol{u}} \wedge \overrightarrow{\boldsymbol{v}}), \overrightarrow{\boldsymbol{w}}$</t>
+  </si>
+  <si>
+    <t>La fonction $f: f(x)=\frac{\ln (x+1)}{x+e^{x}}$ admet au point $0(0,0)$ une tangente d'équation :</t>
+  </si>
+  <si>
+    <t>On considère le nombre complexe : $z=(1+i)^{20}$ Quelle est la partie imaginaire de $z$ ?</t>
+  </si>
+  <si>
+    <t>(A): 0</t>
+  </si>
+  <si>
+    <t>(B): .1</t>
+  </si>
+  <si>
+    <t>(C): 2</t>
+  </si>
+  <si>
+    <t>(D): $\pi$</t>
+  </si>
+  <si>
+    <t>(E) : Aucune des réponses n'est juste</t>
+  </si>
+  <si>
+    <t>A) $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>В) $\frac{\pi}{4}$</t>
+  </si>
+  <si>
+    <t>C) $\frac{1}{4}$</t>
+  </si>
+  <si>
+    <t>D) 0</t>
+  </si>
+  <si>
+    <t>E). Aucune des réponses n'est juste</t>
+  </si>
+  <si>
+    <t>A) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>B) $\mathbf{1}+\sqrt{\mathbf{2}}$</t>
+  </si>
+  <si>
+    <t>C) la suite est divergente</t>
+  </si>
+  <si>
+    <t>D) 2</t>
+  </si>
+  <si>
+    <t>E) Aucune des réponses n'est juste</t>
+  </si>
+  <si>
+    <t>A) 0</t>
+  </si>
+  <si>
+    <t>B) 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C) 2</t>
+  </si>
+  <si>
+    <t>D) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>A) 1</t>
+  </si>
+  <si>
+    <t>B) 2</t>
+  </si>
+  <si>
+    <t>C) -1</t>
+  </si>
+  <si>
+    <t>А) 0</t>
+  </si>
+  <si>
+    <t>B) $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>C) 1</t>
+  </si>
+  <si>
+    <t>D) -1</t>
+  </si>
+  <si>
+    <t>В) $\sqrt{2}+1$</t>
+  </si>
+  <si>
+    <t>C) 2</t>
+  </si>
+  <si>
+    <t>А) $x=1$</t>
+  </si>
+  <si>
+    <t>В) $x=0$</t>
+  </si>
+  <si>
+    <t>C) $x=\frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>D) $x=-1$</t>
+  </si>
+  <si>
+    <t>A) $\frac{\mathbf{1}}{\mathbf{1 8}}$</t>
+  </si>
+  <si>
+    <t>B) $\frac{17}{18}$</t>
+  </si>
+  <si>
+    <t>C) $\frac{2}{9}$</t>
+  </si>
+  <si>
+    <t>D) $\frac{1}{5}$</t>
+  </si>
+  <si>
+    <t>E) Aucune des réponses $n^{\prime}$ est juste</t>
+  </si>
+  <si>
+    <t>A) $\frac{1}{6}$</t>
+  </si>
+  <si>
+    <t>В) $\frac{11}{36}$</t>
+  </si>
+  <si>
+    <t>C) $\frac{5}{36}$</t>
+  </si>
+  <si>
+    <t>D) $\frac{25}{36}$</t>
+  </si>
+  <si>
+    <t>A) Oui, pour $x=, \frac{1}{4}, y=, \frac{1}{8}$</t>
+  </si>
+  <si>
+    <t>B) oui, pour $x=\frac{5}{16}, y=\frac{1}{16}$</t>
+  </si>
+  <si>
+    <t>C) Oui, pour $x=\frac{1}{2}, y=\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>D) Non, car le vecteur $\overrightarrow{A D}$ n'est pas une combinaison linéaire de $\overrightarrow{A B}$ et $\overrightarrow{A C}$</t>
+  </si>
+  <si>
+    <t>B) 3</t>
+  </si>
+  <si>
+    <t>D. 2</t>
+  </si>
+  <si>
+    <t>А) $y=x$</t>
+  </si>
+  <si>
+    <t>В) $y=x+1$</t>
+  </si>
+  <si>
+    <t>C) $y=-2 x$</t>
+  </si>
+  <si>
+    <t>D) $y=x-1$</t>
+  </si>
+  <si>
+    <t>A) $2^{10}$</t>
+  </si>
+  <si>
+    <t>B) $-2^{10}$</t>
+  </si>
+  <si>
+    <t>C) 0</t>
+  </si>
+  <si>
+    <t>On définit la fonction : $f(x)=\left\{\begin{array}{l}\frac{\sqrt{1+x}-1}{x}, x \neq 0 \\      a, x=0\end{array}\right.$. Pour quelle valeur de $\boldsymbol{a}$ la fonction $\boldsymbol{f}$ est-elle continue en $\boldsymbol{x}=\mathbf{0}$ ?</t>
+  </si>
+  <si>
+    <t>\section*{Propagation d'une onde le long d'une corde : }.     Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $\nu$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 \mathrm{~s}$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.</t>
+  </si>
+  <si>
+    <t>\begin{figure}      \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=265&amp;width=939&amp;top_left_y=752&amp;top_left_x=133}     \captionsetup{labelformat=empty}       \caption{Figure 1}     \end{figure}    \begin{figure}     \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=216&amp;width=552&amp;top_left_y=803&amp;top_left_x=1237}     \captionsetup{labelformat=empty}    \caption{Figure 2}      \end{figure}</t>
+  </si>
+  <si>
+    <t>Q21. Les valeurs de la longueur d'onde et de la célérité de propagation de l'onde le long de la corde sont :</t>
+  </si>
+  <si>
+    <t>$\mathbf{A}$ &amp; $\lambda=0,40 \mathrm{~m}$  \\ $v=0,25 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{B}$ &amp; $\lambda=0,08 \mathrm{~m}$  \\ $v=0,80 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{C}$ &amp; $\lambda=0,40 \mathrm{~m}$  \\ $\mathbf{C}$ &amp; $v=2,5 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{D}=0,40 \mathrm{~m}$  \\  $\mathbf{D}$ &amp; $v=5,0 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\lambda=0,80 \mathrm{~m}$  \\ $\mathbf{E}$ &amp; $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
   </si>
 </sst>
 </file>
@@ -12488,7 +12981,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -12515,44 +13008,16 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12673,54 +13138,31 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13025,7 +13467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -13033,7 +13475,8 @@
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" customWidth="1"/>
+    <col min="8" max="8" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.7109375" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" customWidth="1"/>
     <col min="11" max="11" width="21.140625" customWidth="1"/>
@@ -13041,13 +13484,13 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -13062,7 +13505,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
@@ -13079,10 +13522,10 @@
     </row>
     <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>112</v>
+        <v>207</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="C2" s="39"/>
       <c r="D2" s="3" t="s">
@@ -13098,16 +13541,16 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="L2" s="5">
         <v>2</v>
@@ -13115,10 +13558,11 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -13126,57 +13570,57 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="42" t="s">
-        <v>40</v>
+      <c r="J3" s="43" t="s">
+        <v>32</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L3" s="43"/>
+        <v>123</v>
+      </c>
+      <c r="L3" s="44"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>113</v>
+        <v>209</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>103</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="58" t="s">
+      <c r="H4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="44"/>
+      <c r="K4" s="42"/>
       <c r="L4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>114</v>
+        <v>209</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>104</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
@@ -13191,26 +13635,26 @@
         <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="44"/>
+      <c r="K5" s="42"/>
       <c r="L5" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>115</v>
+        <v>209</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>20</v>
@@ -13225,48 +13669,48 @@
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="44"/>
+      <c r="K6" s="42"/>
       <c r="L6" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>116</v>
+        <v>207</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="39"/>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L7" s="5">
         <v>2</v>
@@ -13274,35 +13718,35 @@
     </row>
     <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>117</v>
+        <v>207</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>107</v>
       </c>
       <c r="C8" s="39"/>
-      <c r="D8" s="6">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6">
-        <v>13</v>
-      </c>
-      <c r="F8" s="6">
-        <v>15</v>
-      </c>
-      <c r="G8" s="6">
-        <v>17</v>
-      </c>
-      <c r="H8" s="6">
-        <v>25</v>
-      </c>
-      <c r="I8" s="6">
-        <v>11</v>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L8" s="5">
         <v>1</v>
@@ -13310,1192 +13754,2175 @@
     </row>
     <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>118</v>
+        <v>207</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>108</v>
       </c>
       <c r="C9" s="39"/>
-      <c r="D9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>3</v>
+      </c>
+      <c r="E9" s="6">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6">
+        <v>15</v>
+      </c>
+      <c r="G9" s="6">
+        <v>8</v>
+      </c>
+      <c r="H9" s="6">
+        <v>23</v>
+      </c>
+      <c r="I9" s="6">
+        <v>15</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="K9" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L9" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>42</v>
+        <v>207</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="L10" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="8" t="s">
         <v>42</v>
       </c>
+      <c r="E11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K11" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="L11" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="41"/>
+      <c r="D12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="6">
-        <v>3</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="H21" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="16">
         <v>5</v>
-      </c>
-      <c r="F12" s="6">
-        <v>15</v>
-      </c>
-      <c r="G12" s="6">
-        <v>8</v>
-      </c>
-      <c r="H12" s="6">
-        <v>23</v>
-      </c>
-      <c r="I12" s="6">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L12" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L13" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L15" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L16" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L17" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L19" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L20" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L21" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L23" s="5">
-        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="13"/>
+        <v>207</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="19"/>
       <c r="D24" s="14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K24" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="L24" s="16">
+      <c r="G25" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L25" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L26" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L25" s="16">
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L29" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L26" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L27" s="16">
+    <row r="30" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="16">
         <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L28" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L29" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B30" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L30" s="16">
-        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F31" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="E31" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="F31" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="I31" s="23" t="s">
-        <v>166</v>
+      <c r="G31" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L31" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>210</v>
+        <v>207</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>200</v>
       </c>
       <c r="C32" s="19"/>
-      <c r="D32" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="21" t="s">
+      <c r="D32" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="E32" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="F32" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="I32" s="21" t="s">
-        <v>175</v>
+      <c r="G32" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>174</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L32" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B33" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>179</v>
+        <v>207</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="26">
+        <v>4</v>
+      </c>
+      <c r="E33" s="26">
+        <v>8</v>
+      </c>
+      <c r="F33" s="31">
+        <v>12</v>
+      </c>
+      <c r="G33" s="32">
+        <v>24</v>
+      </c>
+      <c r="H33" s="26">
+        <v>36</v>
+      </c>
+      <c r="I33" s="26">
+        <v>4</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L33" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B34" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="H34" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="F34" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>182</v>
+      <c r="I34" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L34" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="54" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C35" s="36"/>
+      <c r="D35" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="G35" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="H35" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="H35" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>187</v>
+      <c r="I35" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L35" s="16">
+        <v>123</v>
+      </c>
+      <c r="L35" s="37">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B36" s="54" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="26">
-        <v>4</v>
-      </c>
-      <c r="E36" s="26">
-        <v>8</v>
-      </c>
-      <c r="F36" s="31">
-        <v>12</v>
-      </c>
-      <c r="G36" s="32">
-        <v>24</v>
-      </c>
-      <c r="H36" s="26">
-        <v>36</v>
-      </c>
-      <c r="I36" s="26">
-        <v>4</v>
+        <v>207</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="38">
+        <v>0.08</v>
+      </c>
+      <c r="E36" s="38">
+        <v>0.16</v>
+      </c>
+      <c r="F36" s="38">
+        <v>0.32</v>
+      </c>
+      <c r="G36" s="38">
+        <v>0.64</v>
+      </c>
+      <c r="H36" s="38">
+        <v>0.96</v>
+      </c>
+      <c r="I36" s="38">
+        <v>0.32</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L36" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B37" s="56" t="s">
+    <row r="37" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="F37" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>191</v>
+      <c r="C37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>153</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L37" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B38" s="57" t="s">
-        <v>216</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>196</v>
+      <c r="H38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L38" s="37">
+        <v>123</v>
+      </c>
+      <c r="L38" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B39" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="38">
-        <v>0.08</v>
-      </c>
-      <c r="E39" s="38">
-        <v>0.16</v>
-      </c>
-      <c r="F39" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="G39" s="38">
-        <v>0.64</v>
-      </c>
-      <c r="H39" s="38">
-        <v>0.96</v>
-      </c>
-      <c r="I39" s="38">
-        <v>0.32</v>
+    <row r="39" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>212</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L39" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59" t="s">
-        <v>220</v>
-      </c>
-      <c r="B40" t="s">
-        <v>229</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>166</v>
+      <c r="A40" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="46" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="F40" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="G40" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="H40" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="I40" s="46" t="s">
+        <v>239</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L40" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59" t="s">
-        <v>220</v>
-      </c>
-      <c r="B41" t="s">
-        <v>223</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>226</v>
+      <c r="A41" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="E41" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="F41" s="46" t="s">
+        <v>257</v>
+      </c>
+      <c r="G41" s="46" t="s">
+        <v>258</v>
+      </c>
+      <c r="H41" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="I41" s="46" t="s">
+        <v>257</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L41" s="16">
         <v>1</v>
       </c>
+    </row>
+    <row r="42" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="F42" s="46" t="s">
+        <v>259</v>
+      </c>
+      <c r="G42" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="H42" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="I42" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L42" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="E43" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="F43" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="G43" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="H43" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="I43" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L43" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A44" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="E44" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F44" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G44" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="H44" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="I44" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="J44" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L44" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A45" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="E45" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="F45" s="46" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="H45" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="I45" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="J45" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L45" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A46" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>268</v>
+      </c>
+      <c r="F46" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="G46" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="H46" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="I46" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="J46" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L46" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="F47" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="G47" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="H47" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="I47" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="J47" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L47" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A48" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B48" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="E48" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="F48" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="G48" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="H48" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="I48" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="J48" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L48" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="46" t="s">
+        <v>279</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="F49" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="G49" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H49" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="I49" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="J49" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L49" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B50" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="46" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="F50" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="G50" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="H50" s="46" t="s">
+        <v>284</v>
+      </c>
+      <c r="I50" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="J50" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L50" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B51" s="46" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="E51" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="F51" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="G51" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="H51" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="I51" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="J51" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L51" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="E52" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="F52" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="G52" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="H52" s="46" t="s">
+        <v>253</v>
+      </c>
+      <c r="I52" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="J52" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L52" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A53" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="E53" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="F53" s="46" t="s">
+        <v>289</v>
+      </c>
+      <c r="G53" s="46" t="s">
+        <v>290</v>
+      </c>
+      <c r="H53" s="46" t="s">
+        <v>254</v>
+      </c>
+      <c r="I53" s="46" t="s">
+        <v>289</v>
+      </c>
+      <c r="J53" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L53" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="E54" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="F54" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="G54" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="H54" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="I54" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="J54" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L54" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B55" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="E55" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="F55" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="G55" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="H55" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="I55" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="J55" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L55" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B56" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="E56" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="F56" s="46" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="H56" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I56" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="J56" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L56" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B57" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="E57" s="46" t="s">
+        <v>336</v>
+      </c>
+      <c r="F57" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="G57" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H57" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I57" s="46" t="s">
+        <v>336</v>
+      </c>
+      <c r="J57" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L57" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B58" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="E58" s="46" t="s">
+        <v>340</v>
+      </c>
+      <c r="F58" s="46" t="s">
+        <v>341</v>
+      </c>
+      <c r="G58" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="H58" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I58" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="J58" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L58" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A59" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="46" t="s">
+        <v>342</v>
+      </c>
+      <c r="E59" s="46" t="s">
+        <v>343</v>
+      </c>
+      <c r="F59" s="46" t="s">
+        <v>344</v>
+      </c>
+      <c r="G59" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="H59" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I59" s="46" t="s">
+        <v>343</v>
+      </c>
+      <c r="J59" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L59" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="E60" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="F60" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="G60" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H60" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I60" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="J60" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L60" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B61" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="F61" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="G61" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="H61" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I61" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="J61" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L61" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A62" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B62" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>353</v>
+      </c>
+      <c r="F62" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="G62" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="H62" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="I62" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="J62" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L62" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B63" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="F63" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="G63" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="H63" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I63" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="J63" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L63" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A64" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B64" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="E64" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="F64" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="G64" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="H64" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I64" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="J64" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L64" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A65" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B65" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F65" s="46" t="s">
+        <v>341</v>
+      </c>
+      <c r="G65" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="H65" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I65" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="J65" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L65" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B66" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="F66" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="G66" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="H66" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I66" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="J66" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L66" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="E67" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="F67" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="G67" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H67" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I67" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="J67" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L67" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B68" s="48" t="s">
+        <v>375</v>
+      </c>
+      <c r="C68" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="J68" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K68" s="42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B69" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="D69" s="48" t="s">
+        <v>378</v>
+      </c>
+      <c r="E69" s="48" t="s">
+        <v>379</v>
+      </c>
+      <c r="F69" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="G69" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="H69" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="L69" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="48"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345CF74E-2E03-48EE-BC44-644174188C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF468BB3-224F-4849-9B0A-0916B1F81689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="455">
   <si>
     <t>Option 1</t>
   </si>
@@ -99,54 +110,6 @@
     <t>Biologie</t>
   </si>
   <si>
-    <t>Pascal</t>
-  </si>
-  <si>
-    <t>Newton</t>
-  </si>
-  <si>
-    <t>Archimède</t>
-  </si>
-  <si>
-    <t>Maxwell</t>
-  </si>
-  <si>
-    <t>Pancréas</t>
-  </si>
-  <si>
-    <t>Foie</t>
-  </si>
-  <si>
-    <t>Vésicule</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Inflammation</t>
-  </si>
-  <si>
-    <t>hypertension</t>
-  </si>
-  <si>
-    <t>glycémie</t>
-  </si>
-  <si>
-    <t>infection</t>
-  </si>
-  <si>
-    <t>Puissance</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Force</t>
-  </si>
-  <si>
-    <t>Travail</t>
-  </si>
-  <si>
     <t>PHYSIQUE</t>
   </si>
   <si>
@@ -690,9 +653,6 @@
       </rPr>
       <t>cytoplasme.</t>
     </r>
-  </si>
-  <si>
-    <t>MEDECINE 2022</t>
   </si>
   <si>
     <r>
@@ -1542,18 +1502,6 @@
   </si>
   <si>
     <t>Physiologie</t>
-  </si>
-  <si>
-    <t>Pression</t>
-  </si>
-  <si>
-    <t>Huminité</t>
-  </si>
-  <si>
-    <t>Bernard</t>
-  </si>
-  <si>
-    <t>Reins</t>
   </si>
   <si>
     <r>
@@ -5959,24 +5907,6 @@
   </si>
   <si>
     <t>Quelle est la différence entre la souris et le rat ?</t>
-  </si>
-  <si>
-    <t>Dimension de R.T</t>
-  </si>
-  <si>
-    <t>plus petit nombre premier supérieur à 10</t>
-  </si>
-  <si>
-    <t>PCR</t>
-  </si>
-  <si>
-    <t>Auteur de la théorie de réaction dans l'eau</t>
-  </si>
-  <si>
-    <t>Responsable de l'insuline</t>
-  </si>
-  <si>
-    <t>Plus petit multiple commun de 3 et 5</t>
   </si>
   <si>
     <r>
@@ -11781,9 +11711,6 @@
     <t>QUESTION</t>
   </si>
   <si>
-    <t>$\lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=0}^{n-1}{f\left(a+k\frac{b-a}{n}\right)=\ \lim\below{n\rightarrow\infty}{\frac{b-a}{n}\ \sum_{k=1}^{n}{f\left(a+k\frac{b-a}{n}\right)=\ \int_{a}^{b}f\left(x\right)dx}}\ }}$</t>
-  </si>
-  <si>
     <t>$\lim\below{n\rightarrow\infty}{U_n=\ -\infty}$</t>
   </si>
   <si>
@@ -11803,13 +11730,820 @@
   </si>
   <si>
     <t>Q22M22</t>
+  </si>
+  <si>
+    <t>(A) : $𝒛=√𝟏𝟎+𝟓√𝟐𝟐−𝒊√𝟏𝟎−𝟓√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(B) : $𝒛=√𝟐+√𝟐𝟐−𝒊√𝟐−√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(C) : $𝒛=√𝟏𝟎+𝟓√𝟐𝟐+𝒊√𝟏𝟎−𝟓√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(D) : $𝒛=√𝟐+√𝟐𝟐+𝒊√𝟐−√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>(E) : $𝒛=√𝟏𝟎+𝟓√𝟐𝟐−𝒊√𝟏𝟎+𝟓√𝟐𝟐$</t>
+  </si>
+  <si>
+    <t>$U_{\mathrm{n}}=\frac{1}{2}+\frac{1}{2^{2}}+\frac{1}{2^{3}}+\cdots+\frac{1}{2^{n}}$ et $\boldsymbol{\operatorname { l n }}\left(V_{\mathrm{n}}\right)=U_{\mathrm{n}} \boldsymbol{\operatorname { l n }}(2)$; alors :</t>
+  </si>
+  <si>
+    <t>Pour tout $n$ entier et $n \geq 1$, on pose: 
+$U_{\mathrm{n}}=\frac{1}{2}+\frac{1}{2^{2}}+\frac{1}{2^{3}}+\cdots+\frac{1}{2^{n}}$      et       $\boldsymbol{\operatorname { l n }}\left(V_{\mathrm{n}}\right)=U_{\mathrm{n}} \boldsymbol{\operatorname { l n }}(2)$;       alors :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(A): $\lim _{n \rightarrow+\infty} U_{n}=1$ et $\lim _{n \rightarrow+\infty} V_{n}=\ln (2)$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $\lim _{n \rightarrow+\infty} U_{n}=\frac{1}{2}$ et $\lim _{n \rightarrow+\infty} V_{n}=\ln (2)$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C): $\lim _{n \rightarrow+\infty} U_{n}=2$ et $\lim _{n \rightarrow+\infty} V_{n}=1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $\lim _{n \rightarrow+\infty} U_{n}=\frac{1}{2}$ et $\lim _{n \rightarrow+\infty} V_{n}=2$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(E): $\lim _{\mathbf{n} \rightarrow+\infty} \mathbf{U}_{\mathbf{n}}=\mathbf{1}$ et $\lim _{\mathbf{n} \rightarrow+\infty} V_{\mathbf{n}}=\mathbf{2}$</t>
+  </si>
+  <si>
+    <t>Soit $\mathbf{f}$ une fonction définie sur $] 0 ;+\infty\left[\operatorname{par}: \boldsymbol{f}(\boldsymbol{x})=\frac{\sqrt{\boldsymbol{x}}}{\sqrt{\boldsymbol{x}+\mathbf{2} \sqrt{\boldsymbol{x}}}}\right.$          Alors $\lim _{x \rightarrow 0^{+}} f(x)$ est égale à :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $\mathbf{0}$;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(E): la limite n'existe pas</t>
+  </si>
+  <si>
+    <t>Soit $\mathbf{f}$ une fonction réelle tels que $\boldsymbol{f}(\mathbf{1})=\mathbf{3}$ et $\boldsymbol{f}^{\prime}(\mathbf{1})=-\mathbf{3}$      
+La courbe de la fonction f admet au point $\boldsymbol{A}(\mathbf{1} ; \mathbf{3})$ une tangente d'équation</t>
+  </si>
+  <si>
+    <t>Soit $\mathbf{g}$ une fonction définie sur $] 0 ;+\infty\left[\right.$ par $: \boldsymbol{g}(\boldsymbol{x})=\frac{(\mathbf{2 x})^{\boldsymbol{x}}}{\boldsymbol{x}^{\mathbf{2 x}}}$        Alors $\lim _{\mathbf{x} \rightarrow+\infty} \mathbf{g}(\mathbf{x})$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soient $\mathbf{f}$ et $\mathbf{g}$ deux fonctions définies par : $\boldsymbol{f}(\boldsymbol{x})=\boldsymbol{\operatorname { l n }}(\boldsymbol{x}-\mathbf{1})$ et $\boldsymbol{g}(\boldsymbol{x})=\sqrt{\boldsymbol{x}+\mathbf{1}}$    Alors le domaine de définition de gof est</t>
+  </si>
+  <si>
+    <t>Dans $\mathbb{C}$, si $\mathrm{z}=\sqrt{5} e^{-i \frac{\pi}{8}}$ alors :</t>
+  </si>
+  <si>
+    <t>Le nombre complexe $z=\left(\frac{1}{\sqrt{2}}(1-i \sqrt{3})\right)^{18}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Pour $z \in \mathbb{C}-\{1\}$, l'ensemble des points $M$ d'affixe $z$ tels que $\frac{z+1}{z-1} \in i \mathbb{R}$ est :</t>
+  </si>
+  <si>
+    <t>Pour tout $n$ entier et $n \geq 2$, on pose: $$U_{n}=\left(1-\frac{1}{2^{2}}\right) \times\left(1-\frac{1}{3^{2}}\right) \times \ldots \times\left(1-\frac{1}{n^{2}}\right)$$    Alors $\lim _{n \rightarrow+\infty} U_{n}$ est égale à :</t>
+  </si>
+  <si>
+    <t>(A) $: Z=\frac{\sqrt{10+5 \sqrt{2}}}{2}-\frac{i \sqrt{10-5 \sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(B) $: Z=\frac{\sqrt{2+\sqrt{2}}}{2}-\frac{i \sqrt{2-\sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(C) $: Z=\frac{\sqrt{10+5 \sqrt{2}}}{2}+\frac{i \sqrt{10-5 \sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(D) $: z=\frac{\sqrt{2+\sqrt{2}}}{2}+\frac{i \sqrt{2-\sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(E): $Z=\frac{\sqrt{10+5 \sqrt{2}}}{2}-\frac{i \sqrt{10+5 \sqrt{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(E): $z=\frac{1}{2}-i \frac{\sqrt{3}}{2}$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{C}):+\infty$</t>
+  </si>
+  <si>
+    <t>(E): la limite n'existe pas</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{\frac{\pi}{6}}^{\frac{\pi}{4}} \frac{1}{\sin (x) \tan (x)}$ dx est égale à :</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{0}^{\frac{\pi}{2}} \frac{\sin (2 \mathrm{x})}{1+\sin ^{2}(x)} \mathrm{dx}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soit f une fonction réelle définie par $f(x)=x+x^{2} \sin \left(\frac{1}{x}\right)$ si $x \neq 0$ et $f(0)=0$    Alors :</t>
+  </si>
+  <si>
+    <t>$(A): 0$</t>
+  </si>
+  <si>
+    <t>$(B): \ln (2)+1$</t>
+  </si>
+  <si>
+    <t>$(C): \boldsymbol{f}^{\prime}(\mathbf{0})=\mathbf{1} \quad ;  \boldsymbol{\operatorname { s i n }}\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right)+\boldsymbol{\operatorname { c o s }}\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right)$</t>
+  </si>
+  <si>
+    <t>(E): $\boldsymbol{f}$ est dérivable en 0 et $\boldsymbol{f}^{\prime}(0)=2$</t>
+  </si>
+  <si>
+    <t>$(E): \frac{\mathbf{8} \times \mathbf{3}^{\boldsymbol{n}}}{\mathbf{1 1}^{\boldsymbol{n} \boldsymbol{-} \mathbf{1}}}$</t>
+  </si>
+  <si>
+    <t>(B): $z=\frac{\sqrt{3}}{2}-\frac{1}{2} i$</t>
+  </si>
+  <si>
+    <t>(A): z=-512</t>
+  </si>
+  <si>
+    <t>(C): z=512</t>
+  </si>
+  <si>
+    <t>(D): z=251</t>
+  </si>
+  <si>
+    <t>(C): Le cercle de centre $O$ et de rayon 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (D): la droite (Ox)</t>
+  </si>
+  <si>
+    <t>$(A): 1 \quad$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{B}): \quad \mathbf{0} \quad $</t>
+  </si>
+  <si>
+    <t>(D): $\frac{\mathbf{1}}{\mathbf{2}} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(A): $+\infty$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $\mathbf{0}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C): $\mathbf{1} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $\frac{\mathbf{1}}{\mathbf{2}} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C): 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $\mathbf{0} \quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(A): \mathbf{y}=\mathbf{3 x}-\mathbf{2}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(B): \mathbf{y}=\mathbf{3 x}-\mathbf{6}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(C): \mathbf{y}=-\mathbf{3 x}+\mathbf{6}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(E): \mathbf{y}=-\mathbf{3 x}+\mathbf{2}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(A): $[-\mathbf{1} ;+\infty[$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(B): $] \mathbf{1} ;+\infty[\quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(C) : $\left[\mathbf{1}+\frac{\mathbf{1}}{\boldsymbol{e}} ;+\infty[\right.$</t>
+  </si>
+  <si>
+    <t>(D): $\frac{\sqrt{\mathbf{2}}}{\mathbf{2}}-\frac{\mathbf{1}}{\mathbf{2}} \quad$</t>
+  </si>
+  <si>
+    <t>(A): $\frac{1}{2}-\frac{\sqrt{2}}{2}$</t>
+  </si>
+  <si>
+    <t>(B): $2-\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(C): $\sqrt{2}-2$</t>
+  </si>
+  <si>
+    <t>(C): $\ln (2) \quad$</t>
+  </si>
+  <si>
+    <t>(D): $1 \quad$</t>
+  </si>
+  <si>
+    <t>(E):$-\ln (2)$</t>
+  </si>
+  <si>
+    <t>Dans l'espace rapporté à un repère orthonormé $\operatorname{direct}(O, \vec{\imath}, \vec{\jmath}, \vec{k})$    Soit les plans $(P): x-y-z+2=0$ et $\left(P^{\prime}\right): x+z-2=0$ et la droite $(\Delta)$ telle que $\left\{\begin{array}{l}x=1+t;     \\ y=2+2 t;     \\ z=1-t\end{array} ;(t \in \mathbb{R})\right.$, alors :</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{A}):(\Delta) \subset(\boldsymbol{P})$</t>
+  </si>
+  <si>
+    <t>(A): $\frac{\mathbf{8} \times \mathbf{3}^{\boldsymbol{n}}}{\mathbf{1 1}^{\boldsymbol{n}}} \quad$</t>
+  </si>
+  <si>
+    <t>(B): $\frac{\mathbf{8 n} \times \mathbf{3}^{\boldsymbol{n}}}{\mathbf{1 1}^{\boldsymbol{n}}}$</t>
+  </si>
+  <si>
+    <t>(C): $\frac{8 n \times 3^{n-1}}{11^{n}} \quad$</t>
+  </si>
+  <si>
+    <t>(D): $\frac{\mathbf{8}^{\boldsymbol{n}} \times \mathbf{3}^{\boldsymbol{n - 1}}}{\mathbf{1 1}^{\boldsymbol{n}}}$</t>
+  </si>
+  <si>
+    <t>Une urne contient 5 boules bleus, 4 boules blanches et 3 boules noires. Les boules sont indiscernables au toucher.  On tire au hasard et simultanément 3 boules de ce sac, on répète cette expérience n fois de suite ( $n \geq  5$ ) en remettant dans l'urne les boules tirées après chaque tirage, La probabilité d'obtenir 3 boules de couleurs deux à deux distinctes ( $n-1$ ) fois exactement est :</t>
+  </si>
+  <si>
+    <t>$(C): \boldsymbol{f}^{\prime}(\mathbf{0})=\mathbf{1} \quad$</t>
+  </si>
+  <si>
+    <t>$(A): f$ est dérivable en $0 \quad$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{B}):(\Delta) \perp(\boldsymbol{P})$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{C}):(\Delta) \cap(\boldsymbol{P})=\emptyset$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{D}):(\Delta) \cap\left(\boldsymbol{P}^{\prime}\right)=\emptyset $</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{E}):(\Delta) \perp\left(\boldsymbol{P}^{\prime}\right)$</t>
+  </si>
+  <si>
+    <t>$\quad(\boldsymbol{E}): $\mathbf{1}-\sqrt{\mathbf{2}}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(D): $] \boldsymbol{e} ;+\infty[\quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+(E): $] \boldsymbol{-e} ;+\infty[\quad$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$(D): \mathbf{y}=\mathbf{3 x}$</t>
+  </si>
+  <si>
+    <t>(B) : La droite $(O y)$ privée du point (0,1)</t>
+  </si>
+  <si>
+    <t>(A) : La droite $(O x)$ privée du point (1,0)</t>
+  </si>
+  <si>
+    <t>(E) : Le cercle de centre $O$ et de rayon 1 privée du point (1,0)</t>
+  </si>
+  <si>
+    <t>$ (B): \mathbf{f}^{\prime}(\mathbf{0})=\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>$(\boldsymbol{D}):\text{ Pour tout } \boldsymbol{x} \neq \mathbf{0}, \quad \boldsymbol{f}(\boldsymbol{x}) = \mathbf{1} + \mathbf{2}\boldsymbol{x}\sin\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right) + \cos\left(\frac{\mathbf{1}}{\boldsymbol{x}}\right)$</t>
+  </si>
+  <si>
+    <t>Soit $I=\int_{0}^{\pi}|\cos x| d x$. Quelle est la valeur de $I$ ?</t>
+  </si>
+  <si>
+    <t>Quelle est la valeur de l'intégrale définie suivante : $J=\int_{0}^{1} \frac{1-x^{2}}{\left(1+x^{2}\right)^{2}}$</t>
+  </si>
+  <si>
+    <t>Soit la suite ( $U_{n}$ ) définie par : $U_{1}=1$ et pour tout $n \geq 1$,$$U_{n+1}=\sqrt{2+U_{n}}$$. Quelle est la limite de la suite ( $\boldsymbol{U}_{\boldsymbol{n}}$ ) ?</t>
+  </si>
+  <si>
+    <t>Soient $a$ et $b$ deux nombres complexes tels que : $a \neq b$ et $|a|=1$. Quelle est la valeur de :$$\left|\frac{a-b}{1-\bar{a} b}\right|$$</t>
+  </si>
+  <si>
+    <t>Soit la fonction $\boldsymbol{f}(\boldsymbol{x})=\sin \boldsymbol{x}+\cos \boldsymbol{x}$. Quelle est la valeur maximale de $\mathbf{f}(\mathbf{x})$ sur $\mathbb{R}$ ?</t>
+  </si>
+  <si>
+    <t>On lance deux dés équilibrés à 6 faces. Quelle est la probabilité d'obtenir au moins un 6 ?</t>
+  </si>
+  <si>
+    <t>La fonction $f: f(x)=\frac{\ln (x+1)}{x+e^{x}}$ admet au point $0(0,0)$ une tangente d'équation :</t>
+  </si>
+  <si>
+    <t>On considère le nombre complexe : $z=(1+i)^{20}$ Quelle est la partie imaginaire de $z$ ?</t>
+  </si>
+  <si>
+    <t>(A): 0</t>
+  </si>
+  <si>
+    <t>(C): 2</t>
+  </si>
+  <si>
+    <t>(D): $\pi$</t>
+  </si>
+  <si>
+    <t>(E) : Aucune des réponses n'est juste</t>
+  </si>
+  <si>
+    <t>A) $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>В) $\frac{\pi}{4}$</t>
+  </si>
+  <si>
+    <t>C) $\frac{1}{4}$</t>
+  </si>
+  <si>
+    <t>D) 0</t>
+  </si>
+  <si>
+    <t>A) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>B) $\mathbf{1}+\sqrt{\mathbf{2}}$</t>
+  </si>
+  <si>
+    <t>C) la suite est divergente</t>
+  </si>
+  <si>
+    <t>D) 2</t>
+  </si>
+  <si>
+    <t>E) Aucune des réponses n'est juste</t>
+  </si>
+  <si>
+    <t>A) 0</t>
+  </si>
+  <si>
+    <t>B) 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C) 2</t>
+  </si>
+  <si>
+    <t>D) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>A) 1</t>
+  </si>
+  <si>
+    <t>B) 2</t>
+  </si>
+  <si>
+    <t>C) -1</t>
+  </si>
+  <si>
+    <t>А) 0</t>
+  </si>
+  <si>
+    <t>B) $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>C) 1</t>
+  </si>
+  <si>
+    <t>D) -1</t>
+  </si>
+  <si>
+    <t>В) $\sqrt{2}+1$</t>
+  </si>
+  <si>
+    <t>C) 2</t>
+  </si>
+  <si>
+    <t>C) $x=\frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>A) $\frac{\mathbf{1}}{\mathbf{1 8}}$</t>
+  </si>
+  <si>
+    <t>B) $\frac{17}{18}$</t>
+  </si>
+  <si>
+    <t>C) $\frac{2}{9}$</t>
+  </si>
+  <si>
+    <t>D) $\frac{1}{5}$</t>
+  </si>
+  <si>
+    <t>E) Aucune des réponses $n^{\prime}$ est juste</t>
+  </si>
+  <si>
+    <t>A) $\frac{1}{6}$</t>
+  </si>
+  <si>
+    <t>В) $\frac{11}{36}$</t>
+  </si>
+  <si>
+    <t>C) $\frac{5}{36}$</t>
+  </si>
+  <si>
+    <t>D) $\frac{25}{36}$</t>
+  </si>
+  <si>
+    <t>A) Oui, pour $x=, \frac{1}{4}, y=, \frac{1}{8}$</t>
+  </si>
+  <si>
+    <t>B) oui, pour $x=\frac{5}{16}, y=\frac{1}{16}$</t>
+  </si>
+  <si>
+    <t>C) Oui, pour $x=\frac{1}{2}, y=\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>D) Non, car le vecteur $\overrightarrow{A D}$ n'est pas une combinaison linéaire de $\overrightarrow{A B}$ et $\overrightarrow{A C}$</t>
+  </si>
+  <si>
+    <t>B) 3</t>
+  </si>
+  <si>
+    <t>А) $y=x$</t>
+  </si>
+  <si>
+    <t>В) $y=x+1$</t>
+  </si>
+  <si>
+    <t>C) $y=-2 x$</t>
+  </si>
+  <si>
+    <t>D) $y=x-1$</t>
+  </si>
+  <si>
+    <t>A) $2^{10}$</t>
+  </si>
+  <si>
+    <t>B) $-2^{10}$</t>
+  </si>
+  <si>
+    <t>C) 0</t>
+  </si>
+  <si>
+    <t>\section*{Propagation d'une onde le long d'une corde : }.     Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $\nu$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 \mathrm{~s}$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.</t>
+  </si>
+  <si>
+    <t>\begin{figure}      \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=265&amp;width=939&amp;top_left_y=752&amp;top_left_x=133}     \captionsetup{labelformat=empty}       \caption{Figure 1}     \end{figure}    \begin{figure}     \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=216&amp;width=552&amp;top_left_y=803&amp;top_left_x=1237}     \captionsetup{labelformat=empty}    \caption{Figure 2}      \end{figure}</t>
+  </si>
+  <si>
+    <t>Q21. Les valeurs de la longueur d'onde et de la célérité de propagation de l'onde le long de la corde sont :</t>
+  </si>
+  <si>
+    <t>$\mathbf{A}$ &amp; $\lambda=0,40 \mathrm{~m}$  \\ $v=0,25 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{B}$ &amp; $\lambda=0,08 \mathrm{~m}$  \\ $v=0,80 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{C}$ &amp; $\lambda=0,40 \mathrm{~m}$  \\ $\mathbf{C}$ &amp; $v=2,5 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{D}=0,40 \mathrm{~m}$  \\  $\mathbf{D}$ &amp; $v=5,0 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\lambda=0,80 \mathrm{~m}$  \\ $\mathbf{E}$ &amp; $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>CECI EST UN TEST D'INSERTION D'IMAGE</t>
+  </si>
+  <si>
+    <t>Une urne $U$ contient 9 boules : dont 5 boules rouges numérotées de 1 à 5 et 4 boules noires numérotées de 1 à 4 . On suppose que les boules sont indiscernables au toucher. On tire simultanément deux boules de l'urne. On considère les deux événements $A$ : « les deux boules tirées sont de mème couleur» et $B$ « les deux boules tirés portent un numéro pair». Calculer $\boldsymbol{P}_{\bar{A}}(\boldsymbol{B})$ ?</t>
+  </si>
+  <si>
+    <t>Soient les points : $A(1,1,-2), B(0,5,5), C(6,-3,-5), D(1,2,0)$,
+Levecteur $\overrightarrow{A D}$ appartient-il au plan vectoriel engendré par $\overrightarrow{\mathrm{AB}} \boldsymbol{e} \boldsymbol{t} \overrightarrow{\mathrm{AC}}$
+Autrement dit, existe-t-il des réels $x$ et y tels que : $\overrightarrow{A D}=x \overrightarrow{A B}+y \overrightarrow{A C}$ ?</t>
+  </si>
+  <si>
+    <t>Soient $\vec{u}(1,2,-1), \vec{v}(3,6,-3), \vec{w}(0,1,1)$.
+Quelle est la valeur de ce produit $(\overrightarrow{\boldsymbol{u}} \wedge \overrightarrow{\boldsymbol{v}}), \overrightarrow{\boldsymbol{w}}$</t>
+  </si>
+  <si>
+    <t>А) $x =1$</t>
+  </si>
+  <si>
+    <t>В) $x = 0$</t>
+  </si>
+  <si>
+    <t>C) $x = \frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>D) $x = -1$</t>
+  </si>
+  <si>
+    <r>
+      <t>Résoudre dans $R$ 1'équation : $</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\frac{e^{2 x-1}}{\sqrt{e^{2 x+4}}}=e^{-x}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>$. Quelle est la bonne réponse?</t>
+    </r>
+  </si>
+  <si>
+    <t>On définit la fonction : $f(x)=\left\{\begin{array}{l}\frac{\sqrt{1+x}-1}{x}, x \neq 0 \\                 a, x=0\end{array}\right.$. Pour quelle valeur de $\boldsymbol{a}$ la fonction $\boldsymbol{f}$ est-elle continue en $\boldsymbol{x}=\mathbf{0}$ ?</t>
+  </si>
+  <si>
+    <t>Soient      $C=1+\cos \frac{\pi}{5}+\cos \frac{2 \pi}{5}+\cdots+\cos \frac{9 \pi}{5}$       et        $S=\sin \frac{\pi}{5}+\sin \frac{2 \pi}{5}+\cdots+\sin \frac{9 \pi}{5}$.   Quelle est la valeur de $\mathbf{z}=\mathbf{C}+\mathbf{i S}$.</t>
+  </si>
+  <si>
+    <t>(B): 1</t>
+  </si>
+  <si>
+    <t>On considère la fonction f définie par : $\boldsymbol{f}(\boldsymbol{x})=\boldsymbol{x}-\frac{(\boldsymbol{\operatorname { l n }}(\boldsymbol{x}))^{\mathbf{2}}}{\boldsymbol{x}}$</t>
+  </si>
+  <si>
+    <t>La fonction $\mathrm{f}: \boldsymbol{f}(\boldsymbol{x})=\mathbf{2} \boldsymbol{\operatorname { l n }}\left(\frac{\boldsymbol{e}^{\boldsymbol{x}}+\mathbf{2}}{\sqrt{1+\boldsymbol{e}^{\boldsymbol{x}}}}\right)$ admet une asymptote horizontale ou oblique lorsque $\mathbf{x}$ tend vers $-\infty$ ou $+\infty$. Quelle est l'équation de cette asymptote?</t>
+  </si>
+  <si>
+    <t>(E): $y=-\mathbf{2} \boldsymbol{x}$</t>
+  </si>
+  <si>
+    <t>$(E): x_{0}=\varnothing$ (ensemble vide)</t>
+  </si>
+  <si>
+    <t>Soit $z=\frac{(1-i)^{10}}{(1+i \sqrt{3})^{4}}$; Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>$(E): \arg z=\frac{\pi}{2}[2 \pi]$</t>
+  </si>
+  <si>
+    <t>Soient $z_{1}, z_{2}$, et $z_{3}$ trois nombres complexes distincts ayant le même cube, c'est-à-dire $\left(z_{1}\right)^{3}=\left(z_{2}\right)^{3}=\left(z_{3}\right)^{3}$. Quelles sont les valeurs possibles de $z_{1}, z_{2}$, et $z_{3}$ ?</t>
+  </si>
+  <si>
+    <t>$(B): z_{1}=1, z_{2}=\omega, z_{3}=\omega^{2}$ où $\omega=e^{2 \pi i / 3}$</t>
+  </si>
+  <si>
+    <t>(C): $z_{1}=1, z_{2}=\frac{1}{2}+i \frac{\sqrt{3}}{2}, z_{3}=-\frac{1}{2}-i \frac{\sqrt{3}}{2}$;</t>
+  </si>
+  <si>
+    <t>$(D): z_{1}=2, z_{2}=-1, z_{3}=1 ;$</t>
+  </si>
+  <si>
+    <t>$(E): z_{1}=1, z_{2}=-\omega, z_{3}=-\omega^{2}$ où $\omega=e^{2 \pi i / 3}$</t>
+  </si>
+  <si>
+    <t>Soit dans l'espace muni d'un repère orthonormé direct $(0, \vec{\imath}, \vec{\jmath}, \overrightarrow{\boldsymbol{k}})$ les points $\mathrm{A}(0 ; 3 ; 1), \mathrm{B}(-1 ; 3 ; 0)$ et $\mathrm{C}(0 ; 5 ; 0)$. La sphère $(\mathrm{S})$ a pour équation : $x^{2}+y^{2}+z^{2}-4 x-5=0$ Quelles sont les coordonnées du point de tangence H du plan (ABC) et de la sphère (S) ?</t>
+  </si>
+  <si>
+    <t>$(E):(0 ;-1 ; 2)$</t>
+  </si>
+  <si>
+    <t>On suppose que 2000 personnes ont envoyé un-SMS dans le cadre d'un mini-jeu télé qui consistait à répondre à une question à 2 choix. La société qui gère ce "jeu-SMS" sélectionne 30 SMS au hasard parmi les 2000. On note $\Omega$ l'ensemble de tous les sous-ensembles de 30 SMS (distincts). Combien d'éléments contient-il?</t>
+  </si>
+  <si>
+    <t>(E): 2000</t>
+  </si>
+  <si>
+    <t>On considère maintenant que vous faites partie des personnes qui ont envoyé un SMS. Quelle est la probabilité que vous soyez sélectionné(e) parmi les 2000 participants?</t>
+  </si>
+  <si>
+    <t>Soit $U_{n}=\ln \left(1+\mathrm{n} e^{-n}\right), n \in \mathbb{N}$ Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>Soit la suite $w(n)$ définie par $w_{0}=1$ et $w_{n+1}=\frac{w_{n}+3}{2 w_{n}+4}$ et on pose $y_{n}=\frac{4}{2+w_{n}} ; y_{n+1}$ vérifie la relation suivante:</t>
+  </si>
+  <si>
+    <t>$(E): y_{n+1}=\frac{32}{20+y_{n}}$</t>
+  </si>
+  <si>
+    <t>Soit (E) l'équation : $\boldsymbol{x}^{\boldsymbol{x}}=(\sqrt{\boldsymbol{x}})^{\boldsymbol{x}+\mathbf{1}}$ Quelle est la bonne réponse ?</t>
+  </si>
+  <si>
+    <t>Calculer l'intégrale suivante : $\int \frac{\boldsymbol{\operatorname { c o s }} \boldsymbol{x} \boldsymbol{d} \boldsymbol{x}}{\mathbf{2}+\boldsymbol{\operatorname { s i n }} \boldsymbol{x}}$</t>
+  </si>
+  <si>
+    <t>(E): $\quad \frac{1}{2} \ln |2+\cos x|+C$</t>
+  </si>
+  <si>
+    <t>Soit $f(x)=\left(1+\frac{1}{x}\right)^{\boldsymbol{x}}$, Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>(A): $\quad \boldsymbol{D}_{\boldsymbol{f}}=\boldsymbol{]} \mathbf{0},+\infty[$;</t>
+  </si>
+  <si>
+    <t>$(E): \quad D_{f}=[-\mathbf{1}, \mathbf{1}]$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(A): f^{\prime}=1+\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}} </t>
+  </si>
+  <si>
+    <t>(B): f^{\prime}=1-\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}}</t>
+  </si>
+  <si>
+    <t>(C): f^{\prime}=-1+\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}}$</t>
+  </si>
+  <si>
+    <t>$(D): f^{\prime}=-1-\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}}</t>
+  </si>
+  <si>
+    <t>(E): f^{\prime}=1+\frac{2 \ln (x)+(\ln (x))^{2}}{x^{2}}$</t>
+  </si>
+  <si>
+    <t>$(A): y=2 x $</t>
+  </si>
+  <si>
+    <t>$(B): \mathbf{y}=\mathbf{x} $</t>
+  </si>
+  <si>
+    <t>$(C): \quad \mathbf{y}=\mathbf{0} $</t>
+  </si>
+  <si>
+    <t>$(D): y=-2 \ln (2) $</t>
+  </si>
+  <si>
+    <t>On considère la fonction $g$ définie par : $g(x)=\frac{x^{2}+1}{x+1}$. Déterminer le point $\mathrm{x}_{0}$ où la tangente à $\mathrm{C}_{g}$ est parallèle à la droite d'équation $\mathrm{y}=\mathrm{x}$.</t>
+  </si>
+  <si>
+    <t>(A): $x_{0}=0$</t>
+  </si>
+  <si>
+    <t>(B): $x_{0}=-1$</t>
+  </si>
+  <si>
+    <t>$(C): x_{0}=1 $</t>
+  </si>
+  <si>
+    <t>(D): $x_{0}=2$</t>
+  </si>
+  <si>
+    <t>(A): $|\boldsymbol{Z}|=\mathbf{4}$</t>
+  </si>
+  <si>
+    <t>(D): $\arg z=\frac{3 \pi}{2}[2 \pi]$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(B):|z|=\frac{1}{2} </t>
+  </si>
+  <si>
+    <t>(A): $z_{1}=1, z_{2}=i, z_{3}=-i$</t>
+  </si>
+  <si>
+    <t>(A): ( $2 ; 2 ; \sqrt{5}$ )</t>
+  </si>
+  <si>
+    <t>(B): (2;3;1)</t>
+  </si>
+  <si>
+    <t>$(C):(2 ; 2 ; 1) $</t>
+  </si>
+  <si>
+    <t>(D): (0; 1; 2)</t>
+  </si>
+  <si>
+    <t>$(A): A_{2000}^{30} $</t>
+  </si>
+  <si>
+    <t>$(B): C_{2000}^{30} $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(C): 1970 </t>
+  </si>
+  <si>
+    <t>(D): $\frac{\mathbf{2 0 0 0} \text { ! }}{\mathbf{3 0} \text { ! }}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A): 0.12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(B): 0.03 </t>
+  </si>
+  <si>
+    <t>(C): 0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D): 0.02 </t>
+  </si>
+  <si>
+    <t>(E): 0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A): La suite $\left(U_{n}\right)$ est bomée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D): La suite $\left(U_{n}\right)$ est divergente </t>
+  </si>
+  <si>
+    <t>(E): $\lim _{n \rightarrow+\infty} U_{n}=0$</t>
+  </si>
+  <si>
+    <t>(A): $\quad y_{n+1}=\frac{23}{6+y_{n}}$</t>
+  </si>
+  <si>
+    <t>(B): $y_{n+1}=\frac{32}{6+y_{n}}$</t>
+  </si>
+  <si>
+    <t>(C) $: y_{n+1}=\frac{.6}{32+y_{n}}$</t>
+  </si>
+  <si>
+    <t>(D): $y_{n+1}=\frac{6}{32+y_{n}}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(A): \quad \mathbf{x}=1$ est une solution </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(B): \quad \mathbf{x}=2$ est une solution </t>
+  </si>
+  <si>
+    <t>$(C): \quad \mathbf{x}=\mathbf{0}$ est une solution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(D): \quad \mathbf{x}=\mathbf{e}$ est une solution </t>
+  </si>
+  <si>
+    <t>(E): l'équation (E) n'admet pas de solution.</t>
+  </si>
+  <si>
+    <t>(A): $\quad \frac{1}{2} \ln |2+\sin x|+C$</t>
+  </si>
+  <si>
+    <t>(B): $\quad \ln |2+\sin x|+C $</t>
+  </si>
+  <si>
+    <t>(C): $\quad-\ln |2+\sin x|+C$</t>
+  </si>
+  <si>
+    <t>(D): $\quad \ln |2+\cos x|+C$</t>
+  </si>
+  <si>
+    <t>(B):$\boldsymbol{D}_{\boldsymbol{f}}=\mathbb{R}^{*} \quad $</t>
+  </si>
+  <si>
+    <t>$($ C $\left.): \boldsymbol{D}_{\boldsymbol{f}}=\right]-\infty,-\mathbf{1}[\cup] \mathbf{0},+\infty[$</t>
+  </si>
+  <si>
+    <t>(D): $\left.\quad \boldsymbol{D}_{\boldsymbol{f}}=\right]-\mathbf{1}, \mathbf{1}[$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A): f est majorée </t>
+  </si>
+  <si>
+    <t>(C) :$$\lim _{x \rightarrow 0^{+}} f(x)=-\infty $$</t>
+  </si>
+  <si>
+    <t>$(B):|z|=\frac{1}{2} $</t>
+  </si>
+  <si>
+    <t>$(C): \arg z=\frac{\pi}{6}[2 \pi] $</t>
+  </si>
+  <si>
+    <t>$(B): \lim _{n \rightarrow+\infty} U_{n}=+\infty $</t>
+  </si>
+  <si>
+    <t>$(C): \lim _{n \rightarrow+\infty} U_{n}=1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D): f est croissante </t>
+  </si>
+  <si>
+    <t>$$(E): \lim _{x \rightarrow 1^{-}} f(x)=-1$$</t>
+  </si>
+  <si>
+    <t>$(E):  D_{f}=[-\mathbf{1}, \mathbf{1}]$</t>
+  </si>
+  <si>
+    <t>Soit $f(x)=x \sin (\pi x)-\ln (x)-1$ définie sur $] 0,1$ ]. Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>$\boldsymbol{(} \boldsymbol{B})$ : Il existe $c \in] 0,1$ ] tel que $f(c)=0$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="103" x14ac:knownFonts="1">
+  <fonts count="104" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12479,6 +13213,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -12488,7 +13229,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -12511,48 +13252,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12566,9 +13270,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
@@ -12673,54 +13374,28 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13025,7 +13700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -13033,7 +13708,8 @@
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" customWidth="1"/>
+    <col min="8" max="8" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.7109375" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" customWidth="1"/>
     <col min="11" max="11" width="21.140625" customWidth="1"/>
@@ -13041,13 +13717,13 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -13062,7 +13738,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
@@ -13079,12 +13755,12 @@
     </row>
     <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="39"/>
+        <v>193</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="38"/>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
@@ -13098,16 +13774,16 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>49</v>
+        <v>24</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>109</v>
       </c>
       <c r="L2" s="5">
         <v>2</v>
@@ -13115,10 +13791,13 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>194</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -13127,57 +13806,53 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="42" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="L3" s="43"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="58" t="s">
+      <c r="H4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="44"/>
+      <c r="K4" s="41"/>
       <c r="L4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>218</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
@@ -13191,27 +13866,25 @@
         <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="44"/>
+      <c r="K5" s="41"/>
       <c r="L5" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>218</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
@@ -13225,336 +13898,336 @@
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="44"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>116</v>
+        <v>193</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>47</v>
       </c>
       <c r="C7" s="39"/>
-      <c r="D7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>40</v>
+      <c r="D7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L7" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="6">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6">
-        <v>13</v>
-      </c>
-      <c r="F8" s="6">
-        <v>15</v>
-      </c>
-      <c r="G8" s="6">
-        <v>17</v>
-      </c>
-      <c r="H8" s="6">
-        <v>25</v>
-      </c>
-      <c r="I8" s="6">
-        <v>11</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>41</v>
+        <v>193</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="40"/>
+      <c r="D8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="L9" s="5">
+      <c r="H12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
+    <row r="15" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L10" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="6">
-        <v>3</v>
-      </c>
-      <c r="E12" s="6">
-        <v>5</v>
-      </c>
-      <c r="F12" s="6">
-        <v>15</v>
-      </c>
-      <c r="G12" s="6">
-        <v>8</v>
-      </c>
-      <c r="H12" s="6">
-        <v>23</v>
-      </c>
-      <c r="I12" s="6">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L12" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L13" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="K15" s="4" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="L15" s="5">
         <v>2</v>
@@ -13562,938 +14235,2302 @@
     </row>
     <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>74</v>
+        <v>193</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L22" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="5">
-        <v>3</v>
+      <c r="F23" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L23" s="15">
+        <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L17" s="5">
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L18" s="5">
+    <row r="27" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L27" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="126" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L19" s="5">
+    <row r="29" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L29" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L20" s="5">
-        <v>3</v>
+    <row r="30" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="25">
+        <v>4</v>
+      </c>
+      <c r="E30" s="25">
+        <v>8</v>
+      </c>
+      <c r="F30" s="30">
+        <v>12</v>
+      </c>
+      <c r="G30" s="31">
+        <v>24</v>
+      </c>
+      <c r="H30" s="25">
+        <v>36</v>
+      </c>
+      <c r="I30" s="25">
+        <v>4</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L30" s="15">
+        <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="8" t="s">
+    <row r="31" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="32"/>
+      <c r="D31" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L31" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="35"/>
+      <c r="D32" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37">
+        <v>0.08</v>
+      </c>
+      <c r="E33" s="37">
+        <v>0.16</v>
+      </c>
+      <c r="F33" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="G33" s="37">
+        <v>0.64</v>
+      </c>
+      <c r="H33" s="37">
+        <v>0.96</v>
+      </c>
+      <c r="I33" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L33" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L34" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L36" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="I37" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L21" s="5">
-        <v>2</v>
+      <c r="L37" s="15">
+        <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L22" s="5">
-        <v>2</v>
+    <row r="38" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="I38" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L38" s="15">
+        <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="L23" s="5">
+    <row r="39" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>288</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="I39" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L39" s="15">
         <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L24" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L25" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L26" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L27" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L28" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L29" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B30" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L30" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L31" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>210</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L32" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B33" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L33" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B34" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L34" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="54" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="H35" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L35" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B36" s="54" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="26">
-        <v>4</v>
-      </c>
-      <c r="E36" s="26">
-        <v>8</v>
-      </c>
-      <c r="F36" s="31">
-        <v>12</v>
-      </c>
-      <c r="G36" s="32">
-        <v>24</v>
-      </c>
-      <c r="H36" s="26">
-        <v>36</v>
-      </c>
-      <c r="I36" s="26">
-        <v>4</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L36" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>215</v>
-      </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="F37" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L37" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B38" s="57" t="s">
-        <v>216</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L38" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B39" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="38">
-        <v>0.08</v>
-      </c>
-      <c r="E39" s="38">
-        <v>0.16</v>
-      </c>
-      <c r="F39" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="G39" s="38">
-        <v>0.64</v>
-      </c>
-      <c r="H39" s="38">
-        <v>0.96</v>
-      </c>
-      <c r="I39" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K39" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L39" s="16">
-        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="I40" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L40" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A41" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="H41" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="I41" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L41" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A42" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="G42" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="I42" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L42" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A43" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="H43" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="I43" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="J43" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L43" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A44" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="E44" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="F44" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="G44" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="H44" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="I44" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="J44" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L44" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A45" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="B40" t="s">
-        <v>229</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L40" s="16">
+      <c r="C45" s="3"/>
+      <c r="D45" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="H45" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="I45" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="J45" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L45" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59" t="s">
-        <v>220</v>
-      </c>
-      <c r="B41" t="s">
-        <v>223</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="J41" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="L41" s="16">
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="F46" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="G46" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="H46" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="I46" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="J46" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L46" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="G47" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="H47" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="I47" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="J47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L47" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A48" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B48" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="F48" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="G48" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="H48" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="I48" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="J48" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L48" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A49" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="E49" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="F49" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>292</v>
+      </c>
+      <c r="H49" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="I49" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="J49" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L49" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A50" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="F50" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="G50" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="H50" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="I50" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="J50" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L50" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="45" t="s">
+        <v>301</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>368</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>303</v>
+      </c>
+      <c r="H51" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="I51" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="J51" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L51" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="45" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="E52" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="F52" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="G52" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="H52" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I52" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="J52" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L52" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>310</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>311</v>
+      </c>
+      <c r="G53" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="H53" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I53" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="J53" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L53" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="45" t="s">
+        <v>296</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="F54" s="45" t="s">
+        <v>316</v>
+      </c>
+      <c r="G54" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="H54" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I54" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="J54" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L54" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A55" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="E55" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="F55" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="G55" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="H55" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I55" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="J55" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L55" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A56" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="E56" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F56" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="G56" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="H56" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I56" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="J56" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L56" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B57" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>325</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>326</v>
+      </c>
+      <c r="G57" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="H57" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I57" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="J57" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L57" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="E58" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="F58" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="G58" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="H58" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I58" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="J58" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L58" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A59" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="F59" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="G59" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="H59" s="45" t="s">
+        <v>332</v>
+      </c>
+      <c r="I59" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="J59" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L59" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="E60" s="45" t="s">
+        <v>334</v>
+      </c>
+      <c r="F60" s="45" t="s">
+        <v>335</v>
+      </c>
+      <c r="G60" s="45" t="s">
+        <v>336</v>
+      </c>
+      <c r="H60" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I60" s="45" t="s">
+        <v>334</v>
+      </c>
+      <c r="J60" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L60" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A61" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="E61" s="45" t="s">
+        <v>338</v>
+      </c>
+      <c r="F61" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="G61" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I61" s="45" t="s">
+        <v>338</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L61" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="E62" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="F62" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="G62" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="H62" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I62" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L62" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B63" s="45" t="s">
+        <v>299</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>343</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="G63" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I63" s="45" t="s">
+        <v>343</v>
+      </c>
+      <c r="J63" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L63" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>347</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="G64" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="H64" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I64" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L64" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>350</v>
+      </c>
+      <c r="J65" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" s="41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="47" t="s">
+        <v>351</v>
+      </c>
+      <c r="D66" s="47" t="s">
+        <v>352</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>353</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>354</v>
+      </c>
+      <c r="G66" s="48" t="s">
+        <v>355</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>356</v>
+      </c>
+      <c r="I66" s="47" t="s">
+        <v>353</v>
+      </c>
+      <c r="J66" s="42"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="B67" s="47" t="s">
+        <v>369</v>
+      </c>
+      <c r="D67" s="47" t="s">
+        <v>394</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="F67" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="I67" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="J67" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L67" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A68" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="47" t="s">
+        <v>370</v>
+      </c>
+      <c r="D68" s="47" t="s">
+        <v>399</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="F68" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="G68" s="47" t="s">
+        <v>402</v>
+      </c>
+      <c r="H68" s="47" t="s">
+        <v>371</v>
+      </c>
+      <c r="I68" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L68" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A69" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B69" s="47" t="s">
+        <v>403</v>
+      </c>
+      <c r="D69" s="47" t="s">
+        <v>404</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>405</v>
+      </c>
+      <c r="F69" s="47" t="s">
+        <v>406</v>
+      </c>
+      <c r="G69" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="H69" s="47" t="s">
+        <v>372</v>
+      </c>
+      <c r="I69" s="47" t="s">
+        <v>371</v>
+      </c>
+      <c r="J69" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L69" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="47" t="s">
+        <v>373</v>
+      </c>
+      <c r="D70" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="F70" s="47" t="s">
+        <v>447</v>
+      </c>
+      <c r="G70" s="47" t="s">
+        <v>409</v>
+      </c>
+      <c r="H70" s="47" t="s">
+        <v>374</v>
+      </c>
+      <c r="I70" s="47" t="s">
+        <v>406</v>
+      </c>
+      <c r="J70" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L70" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A71" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B71" s="47" t="s">
+        <v>375</v>
+      </c>
+      <c r="D71" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="E71" s="47" t="s">
+        <v>376</v>
+      </c>
+      <c r="F71" s="47" t="s">
+        <v>377</v>
+      </c>
+      <c r="G71" s="47" t="s">
+        <v>378</v>
+      </c>
+      <c r="H71" s="47" t="s">
+        <v>379</v>
+      </c>
+      <c r="I71" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="J71" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L71" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A72" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" s="47" t="s">
+        <v>380</v>
+      </c>
+      <c r="D72" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="E72" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="F72" s="47" t="s">
+        <v>414</v>
+      </c>
+      <c r="G72" s="47" t="s">
+        <v>415</v>
+      </c>
+      <c r="H72" s="47" t="s">
+        <v>381</v>
+      </c>
+      <c r="I72" s="47" t="s">
+        <v>378</v>
+      </c>
+      <c r="J72" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L72" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A73" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" s="47" t="s">
+        <v>382</v>
+      </c>
+      <c r="D73" s="47" t="s">
+        <v>416</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>417</v>
+      </c>
+      <c r="F73" s="47" t="s">
+        <v>418</v>
+      </c>
+      <c r="G73" s="47" t="s">
+        <v>419</v>
+      </c>
+      <c r="H73" s="47" t="s">
+        <v>383</v>
+      </c>
+      <c r="I73" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L73" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" s="47" t="s">
+        <v>384</v>
+      </c>
+      <c r="D74" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="E74" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="F74" s="47" t="s">
+        <v>422</v>
+      </c>
+      <c r="G74" s="47" t="s">
+        <v>423</v>
+      </c>
+      <c r="H74" s="47" t="s">
+        <v>424</v>
+      </c>
+      <c r="I74" s="47" t="s">
+        <v>418</v>
+      </c>
+      <c r="J74" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L74" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A75" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="47" t="s">
+        <v>385</v>
+      </c>
+      <c r="D75" s="47" t="s">
+        <v>425</v>
+      </c>
+      <c r="E75" s="47" t="s">
+        <v>448</v>
+      </c>
+      <c r="F75" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="G75" s="47" t="s">
+        <v>426</v>
+      </c>
+      <c r="H75" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="I75" s="47" t="s">
+        <v>424</v>
+      </c>
+      <c r="J75" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L75" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="47" t="s">
+        <v>386</v>
+      </c>
+      <c r="D76" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="E76" s="47" t="s">
+        <v>429</v>
+      </c>
+      <c r="F76" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="G76" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="H76" s="47" t="s">
+        <v>387</v>
+      </c>
+      <c r="I76" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="J76" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L76" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A77" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B77" s="47" t="s">
+        <v>388</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>432</v>
+      </c>
+      <c r="E77" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="F77" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="G77" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="H77" s="47" t="s">
+        <v>436</v>
+      </c>
+      <c r="I77" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="J77" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L77" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A78" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="47" t="s">
+        <v>389</v>
+      </c>
+      <c r="D78" s="47" t="s">
+        <v>437</v>
+      </c>
+      <c r="E78" s="47" t="s">
+        <v>438</v>
+      </c>
+      <c r="F78" s="47" t="s">
+        <v>439</v>
+      </c>
+      <c r="G78" s="47" t="s">
+        <v>440</v>
+      </c>
+      <c r="H78" s="47" t="s">
+        <v>390</v>
+      </c>
+      <c r="I78" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="J78" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L78" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A79" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B79" s="47" t="s">
+        <v>391</v>
+      </c>
+      <c r="D79" s="47" t="s">
+        <v>392</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>441</v>
+      </c>
+      <c r="F79" s="47" t="s">
+        <v>442</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>393</v>
+      </c>
+      <c r="I79" s="47" t="s">
+        <v>439</v>
+      </c>
+      <c r="J79" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L79" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A80" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B80" s="47" t="s">
+        <v>453</v>
+      </c>
+      <c r="D80" s="47" t="s">
+        <v>444</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="F80" s="47" t="s">
+        <v>445</v>
+      </c>
+      <c r="G80" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="H80" s="47" t="s">
+        <v>451</v>
+      </c>
+      <c r="I80" s="47" t="s">
+        <v>452</v>
+      </c>
+      <c r="J80" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L80" s="46">
         <v>1</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamch\OneDrive\Desktop\TEMPLATE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B378B1-BAB7-423B-AE2C-473F9FE1EF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68849DBE-56F2-457B-A8CA-B59F690A5009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="454">
   <si>
     <t>Option 1</t>
   </si>
@@ -110,30 +110,6 @@
     <t>Biologie</t>
   </si>
   <si>
-    <t>Pascal</t>
-  </si>
-  <si>
-    <t>Newton</t>
-  </si>
-  <si>
-    <t>Archimède</t>
-  </si>
-  <si>
-    <t>Maxwell</t>
-  </si>
-  <si>
-    <t>Pancréas</t>
-  </si>
-  <si>
-    <t>Foie</t>
-  </si>
-  <si>
-    <t>Vésicule</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
     <t>PHYSIQUE</t>
   </si>
   <si>
@@ -677,9 +653,6 @@
       </rPr>
       <t>cytoplasme.</t>
     </r>
-  </si>
-  <si>
-    <t>MEDECINE 2022</t>
   </si>
   <si>
     <r>
@@ -1529,12 +1502,6 @@
   </si>
   <si>
     <t>Physiologie</t>
-  </si>
-  <si>
-    <t>Bernard</t>
-  </si>
-  <si>
-    <t>Reins</t>
   </si>
   <si>
     <r>
@@ -5940,15 +5907,6 @@
   </si>
   <si>
     <t>Quelle est la différence entre la souris et le rat ?</t>
-  </si>
-  <si>
-    <t>Auteur de la théorie de réaction dans l'eau</t>
-  </si>
-  <si>
-    <t>Responsable de l'insuline</t>
-  </si>
-  <si>
-    <t>Plus petit multiple commun de 3 et 5</t>
   </si>
   <si>
     <r>
@@ -12082,27 +12040,12 @@
     <t>Soient $a$ et $b$ deux nombres complexes tels que : $a \neq b$ et $|a|=1$. Quelle est la valeur de :$$\left|\frac{a-b}{1-\bar{a} b}\right|$$</t>
   </si>
   <si>
-    <t>Soit $C=1+\cos \frac{\pi}{5}+\cos \frac{2 \pi}{5}+\cdots+\cos \frac{9 \pi}{5}$ et $S=\sin \frac{\pi}{5}+\sin \frac{2 \pi}{5}+\cdots+\sin \frac{9 \pi}{5}$. Quelle est la valeur de $\mathbf{z}=\mathbf{C}+\mathbf{i S}$.</t>
-  </si>
-  <si>
     <t>Soit la fonction $\boldsymbol{f}(\boldsymbol{x})=\sin \boldsymbol{x}+\cos \boldsymbol{x}$. Quelle est la valeur maximale de $\mathbf{f}(\mathbf{x})$ sur $\mathbb{R}$ ?</t>
   </si>
   <si>
-    <t>Résoudre dans $R$ 1'équation : $\frac{e^{2 x-1}}{\sqrt{e^{2 x+4}}}=e^{-x}$. Quelle est la bonne réponse?</t>
-  </si>
-  <si>
-    <t>Une urne $U$ contient 9 boules : dont 5 boules rouges numérotées de 1 à 5 et 4 boule noires numérotées de 1 à 4 . On suppose que les boules sont indiscernables au toucher. On tire simultanément deux boules de l'urne. On considère les deux événements $A$ : « les deux boules tirées sont de mème couleur» et $B$ « les deux boules tirés portent un numéro pair». Calculer $\boldsymbol{P}_{\bar{A}}(\boldsymbol{B})$ ?</t>
-  </si>
-  <si>
     <t>On lance deux dés équilibrés à 6 faces. Quelle est la probabilité d'obtenir au moins un 6 ?</t>
   </si>
   <si>
-    <t>Soient les points : $A(1,1,-2), B(0,5,5), C(6,-3,-5), D(1,2,0)$, Levecteur $\overrightarrow{A D}$ appartient-il au plan vectoriel engendré par $\overrightarrow{\mathrm{AB}} \boldsymbol{e} \boldsymbol{t}. Autrement dit, existe-t-il des réels $x$ et y tels que : $\overrightarrow{A D}=x \overrightarrow{A B}+y \overrightarrow{A C}$ ? \overrightarrow{\mathrm{AC}}$</t>
-  </si>
-  <si>
-    <t>Soient $\vec{u}(1,2,-1), \vec{v}(3,6,-3), \vec{w}(0,1,1)$. Quelle est la valeur de ce produit $(\overrightarrow{\boldsymbol{u}} \wedge \overrightarrow{\boldsymbol{v}}), \overrightarrow{\boldsymbol{w}}$</t>
-  </si>
-  <si>
     <t>La fonction $f: f(x)=\frac{\ln (x+1)}{x+e^{x}}$ admet au point $0(0,0)$ une tangente d'équation :</t>
   </si>
   <si>
@@ -12112,9 +12055,6 @@
     <t>(A): 0</t>
   </si>
   <si>
-    <t>(B): .1</t>
-  </si>
-  <si>
     <t>(C): 2</t>
   </si>
   <si>
@@ -12136,9 +12076,6 @@
     <t>D) 0</t>
   </si>
   <si>
-    <t>E). Aucune des réponses n'est juste</t>
-  </si>
-  <si>
     <t>A) $\sqrt{2}$</t>
   </si>
   <si>
@@ -12193,18 +12130,9 @@
     <t>C) 2</t>
   </si>
   <si>
-    <t>А) $x=1$</t>
-  </si>
-  <si>
-    <t>В) $x=0$</t>
-  </si>
-  <si>
     <t>C) $x=\frac{3}{2}$</t>
   </si>
   <si>
-    <t>D) $x=-1$</t>
-  </si>
-  <si>
     <t>A) $\frac{\mathbf{1}}{\mathbf{1 8}}$</t>
   </si>
   <si>
@@ -12247,9 +12175,6 @@
     <t>B) 3</t>
   </si>
   <si>
-    <t>D. 2</t>
-  </si>
-  <si>
     <t>А) $y=x$</t>
   </si>
   <si>
@@ -12271,15 +12196,6 @@
     <t>C) 0</t>
   </si>
   <si>
-    <t>On définit la fonction : $f(x)=\left\{\begin{array}{l}\frac{\sqrt{1+x}-1}{x}, x \neq 0 \\      a, x=0\end{array}\right.$. Pour quelle valeur de $\boldsymbol{a}$ la fonction $\boldsymbol{f}$ est-elle continue en $\boldsymbol{x}=\mathbf{0}$ ?</t>
-  </si>
-  <si>
-    <t>\section*{Propagation d'une onde le long d'une corde : }.     Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $\nu$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 \mathrm{~s}$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.</t>
-  </si>
-  <si>
-    <t>\begin{figure}      \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=265&amp;width=939&amp;top_left_y=752&amp;top_left_x=133}     \captionsetup{labelformat=empty}       \caption{Figure 1}     \end{figure}    \begin{figure}     \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=216&amp;width=552&amp;top_left_y=803&amp;top_left_x=1237}     \captionsetup{labelformat=empty}    \caption{Figure 2}      \end{figure}</t>
-  </si>
-  <si>
     <t>Q21. Les valeurs de la longueur d'onde et de la célérité de propagation de l'onde le long de la corde sont :</t>
   </si>
   <si>
@@ -12296,13 +12212,335 @@
   </si>
   <si>
     <t>$\lambda=0,80 \mathrm{~m}$  \\ $\mathbf{E}$ &amp; $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>CECI EST UN TEST D'INSERTION D'IMAGE</t>
+  </si>
+  <si>
+    <t>Une urne $U$ contient 9 boules : dont 5 boules rouges numérotées de 1 à 5 et 4 boules noires numérotées de 1 à 4 . On suppose que les boules sont indiscernables au toucher. On tire simultanément deux boules de l'urne. On considère les deux événements $A$ : « les deux boules tirées sont de mème couleur» et $B$ « les deux boules tirés portent un numéro pair». Calculer $\boldsymbol{P}_{\bar{A}}(\boldsymbol{B})$ ?</t>
+  </si>
+  <si>
+    <t>Soient les points : $A(1,1,-2), B(0,5,5), C(6,-3,-5), D(1,2,0)$,
+Levecteur $\overrightarrow{A D}$ appartient-il au plan vectoriel engendré par $\overrightarrow{\mathrm{AB}} \boldsymbol{e} \boldsymbol{t} \overrightarrow{\mathrm{AC}}$
+Autrement dit, existe-t-il des réels $x$ et y tels que : $\overrightarrow{A D}=x \overrightarrow{A B}+y \overrightarrow{A C}$ ?</t>
+  </si>
+  <si>
+    <t>Soient $\vec{u}(1,2,-1), \vec{v}(3,6,-3), \vec{w}(0,1,1)$.
+Quelle est la valeur de ce produit $(\overrightarrow{\boldsymbol{u}} \wedge \overrightarrow{\boldsymbol{v}}), \overrightarrow{\boldsymbol{w}}$</t>
+  </si>
+  <si>
+    <t>А) $x =1$</t>
+  </si>
+  <si>
+    <t>В) $x = 0$</t>
+  </si>
+  <si>
+    <t>C) $x = \frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>D) $x = -1$</t>
+  </si>
+  <si>
+    <r>
+      <t>Résoudre dans $R$ 1'équation : $</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\frac{e^{2 x-1}}{\sqrt{e^{2 x+4}}}=e^{-x}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>$. Quelle est la bonne réponse?</t>
+    </r>
+  </si>
+  <si>
+    <t>On définit la fonction : $f(x)=\left\{\begin{array}{l}\frac{\sqrt{1+x}-1}{x}, x \neq 0 \\                 a, x=0\end{array}\right.$. Pour quelle valeur de $\boldsymbol{a}$ la fonction $\boldsymbol{f}$ est-elle continue en $\boldsymbol{x}=\mathbf{0}$ ?</t>
+  </si>
+  <si>
+    <t>Soient      $C=1+\cos \frac{\pi}{5}+\cos \frac{2 \pi}{5}+\cdots+\cos \frac{9 \pi}{5}$       et        $S=\sin \frac{\pi}{5}+\sin \frac{2 \pi}{5}+\cdots+\sin \frac{9 \pi}{5}$.   Quelle est la valeur de $\mathbf{z}=\mathbf{C}+\mathbf{i S}$.</t>
+  </si>
+  <si>
+    <t>(B): 1</t>
+  </si>
+  <si>
+    <t>On considère la fonction f définie par : $\boldsymbol{f}(\boldsymbol{x})=\boldsymbol{x}-\frac{(\boldsymbol{\operatorname { l n }}(\boldsymbol{x}))^{\mathbf{2}}}{\boldsymbol{x}}$</t>
+  </si>
+  <si>
+    <t>La fonction $\mathrm{f}: \boldsymbol{f}(\boldsymbol{x})=\mathbf{2} \boldsymbol{\operatorname { l n }}\left(\frac{\boldsymbol{e}^{\boldsymbol{x}}+\mathbf{2}}{\sqrt{1+\boldsymbol{e}^{\boldsymbol{x}}}}\right)$ admet une asymptote horizontale ou oblique lorsque $\mathbf{x}$ tend vers $-\infty$ ou $+\infty$. Quelle est l'équation de cette asymptote?</t>
+  </si>
+  <si>
+    <t>(E): $y=-\mathbf{2} \boldsymbol{x}$</t>
+  </si>
+  <si>
+    <t>$(E): x_{0}=\varnothing$ (ensemble vide)</t>
+  </si>
+  <si>
+    <t>Soit $z=\frac{(1-i)^{10}}{(1+i \sqrt{3})^{4}}$; Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>$(E): \arg z=\frac{\pi}{2}[2 \pi]$</t>
+  </si>
+  <si>
+    <t>Soient $z_{1}, z_{2}$, et $z_{3}$ trois nombres complexes distincts ayant le même cube, c'est-à-dire $\left(z_{1}\right)^{3}=\left(z_{2}\right)^{3}=\left(z_{3}\right)^{3}$. Quelles sont les valeurs possibles de $z_{1}, z_{2}$, et $z_{3}$ ?</t>
+  </si>
+  <si>
+    <t>$(B): z_{1}=1, z_{2}=\omega, z_{3}=\omega^{2}$ où $\omega=e^{2 \pi i / 3}$</t>
+  </si>
+  <si>
+    <t>(C): $z_{1}=1, z_{2}=\frac{1}{2}+i \frac{\sqrt{3}}{2}, z_{3}=-\frac{1}{2}-i \frac{\sqrt{3}}{2}$;</t>
+  </si>
+  <si>
+    <t>$(D): z_{1}=2, z_{2}=-1, z_{3}=1 ;$</t>
+  </si>
+  <si>
+    <t>$(E): z_{1}=1, z_{2}=-\omega, z_{3}=-\omega^{2}$ où $\omega=e^{2 \pi i / 3}$</t>
+  </si>
+  <si>
+    <t>Soit dans l'espace muni d'un repère orthonormé direct $(0, \vec{\imath}, \vec{\jmath}, \overrightarrow{\boldsymbol{k}})$ les points $\mathrm{A}(0 ; 3 ; 1), \mathrm{B}(-1 ; 3 ; 0)$ et $\mathrm{C}(0 ; 5 ; 0)$. La sphère $(\mathrm{S})$ a pour équation : $x^{2}+y^{2}+z^{2}-4 x-5=0$ Quelles sont les coordonnées du point de tangence H du plan (ABC) et de la sphère (S) ?</t>
+  </si>
+  <si>
+    <t>$(E):(0 ;-1 ; 2)$</t>
+  </si>
+  <si>
+    <t>On suppose que 2000 personnes ont envoyé un-SMS dans le cadre d'un mini-jeu télé qui consistait à répondre à une question à 2 choix. La société qui gère ce "jeu-SMS" sélectionne 30 SMS au hasard parmi les 2000. On note $\Omega$ l'ensemble de tous les sous-ensembles de 30 SMS (distincts). Combien d'éléments contient-il?</t>
+  </si>
+  <si>
+    <t>(E): 2000</t>
+  </si>
+  <si>
+    <t>On considère maintenant que vous faites partie des personnes qui ont envoyé un SMS. Quelle est la probabilité que vous soyez sélectionné(e) parmi les 2000 participants?</t>
+  </si>
+  <si>
+    <t>Soit $U_{n}=\ln \left(1+\mathrm{n} e^{-n}\right), n \in \mathbb{N}$ Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>Soit la suite $w(n)$ définie par $w_{0}=1$ et $w_{n+1}=\frac{w_{n}+3}{2 w_{n}+4}$ et on pose $y_{n}=\frac{4}{2+w_{n}} ; y_{n+1}$ vérifie la relation suivante:</t>
+  </si>
+  <si>
+    <t>$(E): y_{n+1}=\frac{32}{20+y_{n}}$</t>
+  </si>
+  <si>
+    <t>Soit (E) l'équation : $\boldsymbol{x}^{\boldsymbol{x}}=(\sqrt{\boldsymbol{x}})^{\boldsymbol{x}+\mathbf{1}}$ Quelle est la bonne réponse ?</t>
+  </si>
+  <si>
+    <t>Calculer l'intégrale suivante : $\int \frac{\boldsymbol{\operatorname { c o s }} \boldsymbol{x} \boldsymbol{d} \boldsymbol{x}}{\mathbf{2}+\boldsymbol{\operatorname { s i n }} \boldsymbol{x}}$</t>
+  </si>
+  <si>
+    <t>(E): $\quad \frac{1}{2} \ln |2+\cos x|+C$</t>
+  </si>
+  <si>
+    <t>Soit $f(x)=\left(1+\frac{1}{x}\right)^{\boldsymbol{x}}$, Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>(A): $\quad \boldsymbol{D}_{\boldsymbol{f}}=\boldsymbol{]} \mathbf{0},+\infty[$;</t>
+  </si>
+  <si>
+    <t>$(E): \quad D_{f}=[-\mathbf{1}, \mathbf{1}]$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(A): f^{\prime}=1+\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}} </t>
+  </si>
+  <si>
+    <t>(B): f^{\prime}=1-\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}}</t>
+  </si>
+  <si>
+    <t>(C): f^{\prime}=-1+\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}}$</t>
+  </si>
+  <si>
+    <t>$(D): f^{\prime}=-1-\frac{2 \ln (x)-(\ln (x))^{2}}{x^{2}}</t>
+  </si>
+  <si>
+    <t>(E): f^{\prime}=1+\frac{2 \ln (x)+(\ln (x))^{2}}{x^{2}}$</t>
+  </si>
+  <si>
+    <t>$(A): y=2 x $</t>
+  </si>
+  <si>
+    <t>$(B): \mathbf{y}=\mathbf{x} $</t>
+  </si>
+  <si>
+    <t>$(C): \quad \mathbf{y}=\mathbf{0} $</t>
+  </si>
+  <si>
+    <t>$(D): y=-2 \ln (2) $</t>
+  </si>
+  <si>
+    <t>On considère la fonction $g$ définie par : $g(x)=\frac{x^{2}+1}{x+1}$. Déterminer le point $\mathrm{x}_{0}$ où la tangente à $\mathrm{C}_{g}$ est parallèle à la droite d'équation $\mathrm{y}=\mathrm{x}$.</t>
+  </si>
+  <si>
+    <t>(A): $x_{0}=0$</t>
+  </si>
+  <si>
+    <t>(B): $x_{0}=-1$</t>
+  </si>
+  <si>
+    <t>$(C): x_{0}=1 $</t>
+  </si>
+  <si>
+    <t>(D): $x_{0}=2$</t>
+  </si>
+  <si>
+    <t>(A): $|\boldsymbol{Z}|=\mathbf{4}$</t>
+  </si>
+  <si>
+    <t>(D): $\arg z=\frac{3 \pi}{2}[2 \pi]$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(B):|z|=\frac{1}{2} </t>
+  </si>
+  <si>
+    <t>(A): $z_{1}=1, z_{2}=i, z_{3}=-i$</t>
+  </si>
+  <si>
+    <t>(A): ( $2 ; 2 ; \sqrt{5}$ )</t>
+  </si>
+  <si>
+    <t>(B): (2;3;1)</t>
+  </si>
+  <si>
+    <t>$(C):(2 ; 2 ; 1) $</t>
+  </si>
+  <si>
+    <t>(D): (0; 1; 2)</t>
+  </si>
+  <si>
+    <t>$(A): A_{2000}^{30} $</t>
+  </si>
+  <si>
+    <t>$(B): C_{2000}^{30} $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(C): 1970 </t>
+  </si>
+  <si>
+    <t>(D): $\frac{\mathbf{2 0 0 0} \text { ! }}{\mathbf{3 0} \text { ! }}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A): 0.12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(B): 0.03 </t>
+  </si>
+  <si>
+    <t>(C): 0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D): 0.02 </t>
+  </si>
+  <si>
+    <t>(E): 0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A): La suite $\left(U_{n}\right)$ est bomée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D): La suite $\left(U_{n}\right)$ est divergente </t>
+  </si>
+  <si>
+    <t>(E): $\lim _{n \rightarrow+\infty} U_{n}=0$</t>
+  </si>
+  <si>
+    <t>(A): $\quad y_{n+1}=\frac{23}{6+y_{n}}$</t>
+  </si>
+  <si>
+    <t>(B): $y_{n+1}=\frac{32}{6+y_{n}}$</t>
+  </si>
+  <si>
+    <t>(C) $: y_{n+1}=\frac{.6}{32+y_{n}}$</t>
+  </si>
+  <si>
+    <t>(D): $y_{n+1}=\frac{6}{32+y_{n}}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(A): \quad \mathbf{x}=1$ est une solution </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(B): \quad \mathbf{x}=2$ est une solution </t>
+  </si>
+  <si>
+    <t>$(C): \quad \mathbf{x}=\mathbf{0}$ est une solution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(D): \quad \mathbf{x}=\mathbf{e}$ est une solution </t>
+  </si>
+  <si>
+    <t>(E): l'équation (E) n'admet pas de solution.</t>
+  </si>
+  <si>
+    <t>(A): $\quad \frac{1}{2} \ln |2+\sin x|+C$</t>
+  </si>
+  <si>
+    <t>(B): $\quad \ln |2+\sin x|+C $</t>
+  </si>
+  <si>
+    <t>(C): $\quad-\ln |2+\sin x|+C$</t>
+  </si>
+  <si>
+    <t>(D): $\quad \ln |2+\cos x|+C$</t>
+  </si>
+  <si>
+    <t>(B):$\boldsymbol{D}_{\boldsymbol{f}}=\mathbb{R}^{*} \quad $</t>
+  </si>
+  <si>
+    <t>$($ C $\left.): \boldsymbol{D}_{\boldsymbol{f}}=\right]-\infty,-\mathbf{1}[\cup] \mathbf{0},+\infty[$</t>
+  </si>
+  <si>
+    <t>(D): $\left.\quad \boldsymbol{D}_{\boldsymbol{f}}=\right]-\mathbf{1}, \mathbf{1}[$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A): f est majorée </t>
+  </si>
+  <si>
+    <t>(C) :$$\lim _{x \rightarrow 0^{+}} f(x)=-\infty $$</t>
+  </si>
+  <si>
+    <t>$(B):|z|=\frac{1}{2} $</t>
+  </si>
+  <si>
+    <t>$(C): \arg z=\frac{\pi}{6}[2 \pi] $</t>
+  </si>
+  <si>
+    <t>$(B): \lim _{n \rightarrow+\infty} U_{n}=+\infty $</t>
+  </si>
+  <si>
+    <t>$(C): \lim _{n \rightarrow+\infty} U_{n}=1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D): f est croissante </t>
+  </si>
+  <si>
+    <t>$$(E): \lim _{x \rightarrow 1^{-}} f(x)=-1$$</t>
+  </si>
+  <si>
+    <t>$(E):  D_{f}=[-\mathbf{1}, \mathbf{1}]$</t>
+  </si>
+  <si>
+    <t>Soit $f(x)=x \sin (\pi x)-\ln (x)-1$ définie sur $] 0,1$ ]. Quelle est la bonne réponse?</t>
+  </si>
+  <si>
+    <t>$\boldsymbol{(} \boldsymbol{B})$ : Il existe $c \in] 0,1$ ] tel que $f(c)=0$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propagation d'une onde le long d'une corde : Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $\nu$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 \mathrm{~s}$. Le front d'onde se trouve à l'instant $t_{1}$ à la distance $S F=80 \mathrm{cm}$ de $S$.  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="103" x14ac:knownFonts="1">
+  <fonts count="104" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12972,6 +13210,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -12981,7 +13226,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -13004,20 +13249,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -13031,9 +13267,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
@@ -13159,9 +13392,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13467,7 +13697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -13484,13 +13714,13 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -13505,7 +13735,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
@@ -13522,12 +13752,12 @@
     </row>
     <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="39"/>
+        <v>193</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="38"/>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
@@ -13541,16 +13771,16 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>109</v>
       </c>
       <c r="L2" s="5">
         <v>2</v>
@@ -13558,11 +13788,13 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>194</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -13570,24 +13802,22 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="43" t="s">
-        <v>32</v>
+      <c r="J3" s="42" t="s">
+        <v>24</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="44"/>
+        <v>109</v>
+      </c>
+      <c r="L3" s="43"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
@@ -13601,27 +13831,25 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="42"/>
+      <c r="K4" s="41"/>
       <c r="L4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
@@ -13635,27 +13863,25 @@
         <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="42"/>
+      <c r="K5" s="41"/>
       <c r="L5" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
@@ -13669,2260 +13895,2641 @@
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="42"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="C7" s="39"/>
-      <c r="D7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="K7" s="4" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="L7" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="40"/>
+      <c r="D8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="F8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K8" s="4" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="L8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="6">
+        <v>193</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="5">
         <v>3</v>
       </c>
-      <c r="E9" s="6">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6">
-        <v>15</v>
-      </c>
-      <c r="G9" s="6">
-        <v>8</v>
-      </c>
-      <c r="H9" s="6">
-        <v>23</v>
-      </c>
-      <c r="I9" s="6">
-        <v>15</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L9" s="5">
+    </row>
+    <row r="11" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L10" s="5">
+    <row r="15" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L12" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L17" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="G20" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L18" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L20" s="5">
-        <v>1</v>
+      <c r="L20" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="15" t="s">
+      <c r="G21" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="L21" s="16">
+      <c r="H21" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L22" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L23" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L22" s="16">
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L23" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L24" s="16">
+    <row r="27" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L27" s="15">
         <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L25" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I26" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L26" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L27" s="16">
-        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="25">
+        <v>4</v>
+      </c>
+      <c r="E30" s="25">
+        <v>8</v>
+      </c>
+      <c r="F30" s="30">
+        <v>12</v>
+      </c>
+      <c r="G30" s="31">
+        <v>24</v>
+      </c>
+      <c r="H30" s="25">
+        <v>36</v>
+      </c>
+      <c r="I30" s="25">
+        <v>4</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L30" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="32"/>
+      <c r="D31" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L31" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="35"/>
+      <c r="D32" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37">
+        <v>0.08</v>
+      </c>
+      <c r="E33" s="37">
+        <v>0.16</v>
+      </c>
+      <c r="F33" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="G33" s="37">
+        <v>0.64</v>
+      </c>
+      <c r="H33" s="37">
+        <v>0.96</v>
+      </c>
+      <c r="I33" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L33" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L34" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="I35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L28" s="16">
+      <c r="E36" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L36" s="15">
         <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L29" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="G30" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L30" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L31" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="H32" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="J32" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L32" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="26">
-        <v>4</v>
-      </c>
-      <c r="E33" s="26">
-        <v>8</v>
-      </c>
-      <c r="F33" s="31">
-        <v>12</v>
-      </c>
-      <c r="G33" s="32">
-        <v>24</v>
-      </c>
-      <c r="H33" s="26">
-        <v>36</v>
-      </c>
-      <c r="I33" s="26">
-        <v>4</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L33" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="E34" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="F34" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="G34" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="H34" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="I34" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L34" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="F35" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L35" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B36" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="38">
-        <v>0.08</v>
-      </c>
-      <c r="E36" s="38">
-        <v>0.16</v>
-      </c>
-      <c r="F36" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="G36" s="38">
-        <v>0.64</v>
-      </c>
-      <c r="H36" s="38">
-        <v>0.96</v>
-      </c>
-      <c r="I36" s="38">
-        <v>0.32</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L36" s="16">
-        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L37" s="16">
+      <c r="A37" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="I37" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L37" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L38" s="16">
+    <row r="38" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="I38" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L38" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>222</v>
+      <c r="A39" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>223</v>
       </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="H39" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L39" s="16">
+      <c r="D39" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>288</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="I39" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L39" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B40" s="46" t="s">
-        <v>235</v>
+      <c r="A40" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>224</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="E40" s="46" t="s">
-        <v>240</v>
-      </c>
-      <c r="F40" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="G40" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="H40" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="I40" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L40" s="16">
+      <c r="D40" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="I40" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L40" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B41" s="46" t="s">
-        <v>236</v>
+    <row r="41" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A41" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>209</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="46" t="s">
+      <c r="D41" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="H41" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="I41" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L41" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A42" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="G42" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="I42" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L42" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A43" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="G43" s="45" t="s">
         <v>256</v>
       </c>
-      <c r="E41" s="46" t="s">
-        <v>255</v>
-      </c>
-      <c r="F41" s="46" t="s">
+      <c r="H43" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="I43" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="J43" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L43" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A44" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="G41" s="46" t="s">
+      <c r="E44" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="H41" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="I41" s="46" t="s">
-        <v>257</v>
-      </c>
-      <c r="J41" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L41" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B42" s="46" t="s">
-        <v>237</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="E42" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="F42" s="46" t="s">
+      <c r="F44" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="G42" s="46" t="s">
+      <c r="G44" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="H44" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="H42" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="I42" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L42" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B43" s="46" t="s">
-        <v>238</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="E43" s="46" t="s">
-        <v>262</v>
-      </c>
-      <c r="F43" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="G43" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="H43" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="I43" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L43" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B44" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="E44" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="F44" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G44" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="H44" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="I44" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="J44" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L44" s="47">
+      <c r="I44" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="J44" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L44" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B45" s="46" t="s">
-        <v>229</v>
+      <c r="A45" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" s="45" t="s">
+        <v>220</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="46" t="s">
+      <c r="D45" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="H45" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="I45" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="J45" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L45" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="F46" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="G46" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="E45" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="F45" s="46" t="s">
+      <c r="H46" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="I46" s="45" t="s">
         <v>266</v>
       </c>
-      <c r="G45" s="46" t="s">
-        <v>267</v>
-      </c>
-      <c r="H45" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="I45" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="J45" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L45" s="47">
+      <c r="J46" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L46" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A46" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B46" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="E46" s="46" t="s">
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="F47" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="F46" s="46" t="s">
+      <c r="G47" s="45" t="s">
         <v>269</v>
       </c>
-      <c r="G46" s="46" t="s">
+      <c r="H47" s="45" t="s">
         <v>270</v>
       </c>
-      <c r="H46" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="I46" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="J46" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L46" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B47" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="E47" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="F47" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="G47" s="46" t="s">
-        <v>301</v>
-      </c>
-      <c r="H47" s="46" t="s">
-        <v>274</v>
-      </c>
-      <c r="I47" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="J47" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L47" s="47">
+      <c r="I47" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="J47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L47" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A48" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B48" s="46" t="s">
-        <v>234</v>
+      <c r="A48" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B48" s="45" t="s">
+        <v>271</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="46" t="s">
+      <c r="D48" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="F48" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="G48" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="H48" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="I48" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="J48" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L48" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A49" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="E49" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="F49" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>292</v>
+      </c>
+      <c r="H49" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="I49" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="J49" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L49" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A50" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="F50" s="45" t="s">
         <v>275</v>
       </c>
-      <c r="E48" s="46" t="s">
+      <c r="G50" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="F48" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="G48" s="46" t="s">
-        <v>299</v>
-      </c>
-      <c r="H48" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="I48" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="J48" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K48" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L48" s="47">
+      <c r="H50" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="I50" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="J50" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L50" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B49" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="46" t="s">
-        <v>279</v>
-      </c>
-      <c r="E49" s="46" t="s">
-        <v>280</v>
-      </c>
-      <c r="F49" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="G49" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="H49" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="I49" s="46" t="s">
-        <v>280</v>
-      </c>
-      <c r="J49" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L49" s="47">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="45" t="s">
+        <v>301</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>303</v>
+      </c>
+      <c r="H51" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="I51" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="J51" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L51" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B50" s="46" t="s">
-        <v>248</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="E50" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="F50" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="G50" s="46" t="s">
-        <v>283</v>
-      </c>
-      <c r="H50" s="46" t="s">
-        <v>284</v>
-      </c>
-      <c r="I50" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="J50" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K50" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L50" s="47">
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="45" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="E52" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="F52" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="G52" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="H52" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I52" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="J52" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L52" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A51" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B51" s="46" t="s">
-        <v>285</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="E51" s="46" t="s">
-        <v>294</v>
-      </c>
-      <c r="F51" s="46" t="s">
+    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="45" t="s">
         <v>295</v>
       </c>
-      <c r="G51" s="46" t="s">
+      <c r="C53" s="3"/>
+      <c r="D53" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>310</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>311</v>
+      </c>
+      <c r="G53" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="H53" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I53" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="J53" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L53" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="H51" s="46" t="s">
-        <v>297</v>
-      </c>
-      <c r="I51" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="J51" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K51" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L51" s="47">
+      <c r="C54" s="3"/>
+      <c r="D54" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="F54" s="45" t="s">
+        <v>316</v>
+      </c>
+      <c r="G54" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="H54" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I54" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="J54" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L54" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="46" t="s">
-        <v>249</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="46" t="s">
-        <v>293</v>
-      </c>
-      <c r="E52" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="F52" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="G52" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="H52" s="46" t="s">
-        <v>253</v>
-      </c>
-      <c r="I52" s="46" t="s">
-        <v>252</v>
-      </c>
-      <c r="J52" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L52" s="47">
+    <row r="55" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A55" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="E55" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="F55" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="G55" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="H55" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I55" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="J55" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L55" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B53" s="46" t="s">
-        <v>291</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="E53" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="F53" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="G53" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="H53" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="I53" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="J53" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K53" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L53" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B54" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="46" t="s">
-        <v>320</v>
-      </c>
-      <c r="E54" s="46" t="s">
+    <row r="56" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A56" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="45" t="s">
         <v>321</v>
       </c>
-      <c r="F54" s="46" t="s">
+      <c r="E56" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="G54" s="46" t="s">
+      <c r="F56" s="45" t="s">
         <v>323</v>
       </c>
-      <c r="H54" s="46" t="s">
+      <c r="G56" s="45" t="s">
         <v>324</v>
       </c>
-      <c r="I54" s="46" t="s">
+      <c r="H56" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I56" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="J54" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K54" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L54" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B55" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="E55" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="F55" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="G55" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="H55" s="46" t="s">
-        <v>329</v>
-      </c>
-      <c r="I55" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="J55" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K55" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L55" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A56" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B56" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="E56" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="F56" s="46" t="s">
-        <v>332</v>
-      </c>
-      <c r="G56" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="H56" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I56" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="J56" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K56" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L56" s="47">
+      <c r="J56" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L56" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B57" s="46" t="s">
-        <v>310</v>
+      <c r="A57" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B57" s="45" t="s">
+        <v>297</v>
       </c>
       <c r="C57" s="3"/>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>325</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>326</v>
+      </c>
+      <c r="G57" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="H57" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I57" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="J57" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L57" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E58" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="F58" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="G58" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="H58" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I58" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="J58" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L58" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A59" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" s="45" t="s">
+        <v>356</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="F59" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="G59" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="H59" s="45" t="s">
+        <v>332</v>
+      </c>
+      <c r="I59" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="J59" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L59" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="E60" s="45" t="s">
+        <v>334</v>
+      </c>
+      <c r="F60" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="E57" s="46" t="s">
+      <c r="G60" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="F57" s="46" t="s">
+      <c r="H60" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I60" s="45" t="s">
+        <v>334</v>
+      </c>
+      <c r="J60" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L60" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A61" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="45" t="s">
         <v>337</v>
       </c>
-      <c r="G57" s="46" t="s">
+      <c r="E61" s="45" t="s">
         <v>338</v>
       </c>
-      <c r="H57" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I57" s="46" t="s">
-        <v>336</v>
-      </c>
-      <c r="J57" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K57" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L57" s="47">
+      <c r="F61" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="G61" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I61" s="45" t="s">
+        <v>338</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L61" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A58" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B58" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="E58" s="46" t="s">
-        <v>340</v>
-      </c>
-      <c r="F58" s="46" t="s">
+    <row r="62" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="E62" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="G58" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="H58" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I58" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="J58" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K58" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L58" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A59" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B59" s="46" t="s">
-        <v>374</v>
-      </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="46" t="s">
-        <v>342</v>
-      </c>
-      <c r="E59" s="46" t="s">
-        <v>343</v>
-      </c>
-      <c r="F59" s="46" t="s">
-        <v>344</v>
-      </c>
-      <c r="G59" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="H59" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I59" s="46" t="s">
-        <v>343</v>
-      </c>
-      <c r="J59" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K59" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L59" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A60" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B60" s="46" t="s">
+      <c r="F62" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="G62" s="45" t="s">
         <v>312</v>
       </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="E60" s="46" t="s">
-        <v>346</v>
-      </c>
-      <c r="F60" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="G60" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="H60" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I60" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="J60" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K60" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L60" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B61" s="46" t="s">
+      <c r="H62" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="46" t="s">
-        <v>348</v>
-      </c>
-      <c r="E61" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="F61" s="46" t="s">
-        <v>350</v>
-      </c>
-      <c r="G61" s="46" t="s">
-        <v>351</v>
-      </c>
-      <c r="H61" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I61" s="46" t="s">
-        <v>350</v>
-      </c>
-      <c r="J61" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K61" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L61" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="120" x14ac:dyDescent="0.25">
-      <c r="A62" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B62" s="46" t="s">
+      <c r="I62" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="46" t="s">
-        <v>352</v>
-      </c>
-      <c r="E62" s="46" t="s">
-        <v>353</v>
-      </c>
-      <c r="F62" s="46" t="s">
-        <v>354</v>
-      </c>
-      <c r="G62" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="H62" s="46" t="s">
-        <v>356</v>
-      </c>
-      <c r="I62" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="J62" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K62" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L62" s="47">
+      <c r="J62" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L62" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B63" s="46" t="s">
-        <v>315</v>
+      <c r="A63" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B63" s="45" t="s">
+        <v>299</v>
       </c>
       <c r="C63" s="3"/>
-      <c r="D63" s="46" t="s">
-        <v>357</v>
-      </c>
-      <c r="E63" s="46" t="s">
-        <v>358</v>
-      </c>
-      <c r="F63" s="46" t="s">
-        <v>359</v>
-      </c>
-      <c r="G63" s="46" t="s">
-        <v>360</v>
-      </c>
-      <c r="H63" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I63" s="46" t="s">
-        <v>358</v>
-      </c>
-      <c r="J63" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K63" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L63" s="47">
+      <c r="D63" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>343</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="G63" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I63" s="45" t="s">
+        <v>343</v>
+      </c>
+      <c r="J63" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L63" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A64" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B64" s="46" t="s">
-        <v>316</v>
+    <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" s="45" t="s">
+        <v>300</v>
       </c>
       <c r="C64" s="3"/>
-      <c r="D64" s="46" t="s">
-        <v>361</v>
-      </c>
-      <c r="E64" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="F64" s="46" t="s">
-        <v>363</v>
-      </c>
-      <c r="G64" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="H64" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I64" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="J64" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L64" s="47">
+      <c r="D64" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>347</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="G64" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="H64" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="I64" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L64" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A65" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B65" s="46" t="s">
-        <v>317</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="E65" s="46" t="s">
-        <v>365</v>
-      </c>
-      <c r="F65" s="46" t="s">
-        <v>341</v>
-      </c>
-      <c r="G65" s="46" t="s">
-        <v>366</v>
-      </c>
-      <c r="H65" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I65" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="J65" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K65" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L65" s="47">
+    <row r="65" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="47" t="s">
+        <v>453</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="J65" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" s="41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="D66" s="47" t="s">
+        <v>350</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>351</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>352</v>
+      </c>
+      <c r="G66" s="48" t="s">
+        <v>353</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>354</v>
+      </c>
+      <c r="I66" s="47" t="s">
+        <v>351</v>
+      </c>
+      <c r="J66" s="42"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B66" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="46" t="s">
+    <row r="67" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="B67" s="47" t="s">
         <v>367</v>
       </c>
-      <c r="E66" s="46" t="s">
+      <c r="D67" s="47" t="s">
+        <v>392</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>393</v>
+      </c>
+      <c r="F67" s="47" t="s">
+        <v>394</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="I67" s="47" t="s">
+        <v>393</v>
+      </c>
+      <c r="J67" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L67" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A68" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="47" t="s">
         <v>368</v>
       </c>
-      <c r="F66" s="46" t="s">
+      <c r="D68" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="F68" s="47" t="s">
+        <v>399</v>
+      </c>
+      <c r="G68" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="H68" s="47" t="s">
         <v>369</v>
       </c>
-      <c r="G66" s="46" t="s">
+      <c r="I68" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L68" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A69" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B69" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="D69" s="47" t="s">
+        <v>402</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>403</v>
+      </c>
+      <c r="F69" s="47" t="s">
+        <v>404</v>
+      </c>
+      <c r="G69" s="47" t="s">
+        <v>405</v>
+      </c>
+      <c r="H69" s="47" t="s">
         <v>370</v>
       </c>
-      <c r="H66" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I66" s="46" t="s">
-        <v>368</v>
-      </c>
-      <c r="J66" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K66" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L66" s="47">
+      <c r="I69" s="47" t="s">
+        <v>369</v>
+      </c>
+      <c r="J69" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L69" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B67" s="46" t="s">
-        <v>319</v>
-      </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="46" t="s">
+    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="47" t="s">
         <v>371</v>
       </c>
-      <c r="E67" s="46" t="s">
+      <c r="D70" s="47" t="s">
+        <v>406</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>444</v>
+      </c>
+      <c r="F70" s="47" t="s">
+        <v>445</v>
+      </c>
+      <c r="G70" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="H70" s="47" t="s">
         <v>372</v>
       </c>
-      <c r="F67" s="46" t="s">
+      <c r="I70" s="47" t="s">
+        <v>404</v>
+      </c>
+      <c r="J70" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L70" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A71" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B71" s="47" t="s">
         <v>373</v>
       </c>
-      <c r="G67" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="H67" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="I67" s="46" t="s">
-        <v>373</v>
-      </c>
-      <c r="J67" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="K67" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L67" s="47">
+      <c r="D71" s="47" t="s">
+        <v>409</v>
+      </c>
+      <c r="E71" s="47" t="s">
+        <v>374</v>
+      </c>
+      <c r="F71" s="47" t="s">
+        <v>375</v>
+      </c>
+      <c r="G71" s="47" t="s">
+        <v>376</v>
+      </c>
+      <c r="H71" s="47" t="s">
+        <v>377</v>
+      </c>
+      <c r="I71" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="J71" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L71" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B68" s="48" t="s">
-        <v>375</v>
-      </c>
-      <c r="C68" s="48" t="s">
+    <row r="72" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A72" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" s="47" t="s">
+        <v>378</v>
+      </c>
+      <c r="D72" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="E72" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="F72" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="G72" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="H72" s="47" t="s">
+        <v>379</v>
+      </c>
+      <c r="I72" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="J68" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K68" s="42" t="s">
-        <v>117</v>
+      <c r="J72" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L72" s="46">
+        <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B69" s="48" t="s">
-        <v>377</v>
-      </c>
-      <c r="D69" s="48" t="s">
-        <v>378</v>
-      </c>
-      <c r="E69" s="48" t="s">
-        <v>379</v>
-      </c>
-      <c r="F69" s="49" t="s">
+    <row r="73" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A73" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" s="47" t="s">
         <v>380</v>
       </c>
-      <c r="G69" s="49" t="s">
+      <c r="D73" s="47" t="s">
+        <v>414</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>415</v>
+      </c>
+      <c r="F73" s="47" t="s">
+        <v>416</v>
+      </c>
+      <c r="G73" s="47" t="s">
+        <v>417</v>
+      </c>
+      <c r="H73" s="47" t="s">
         <v>381</v>
       </c>
-      <c r="H69" s="49" t="s">
+      <c r="I73" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L73" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" s="47" t="s">
         <v>382</v>
       </c>
-      <c r="L69" s="50">
-        <v>2</v>
+      <c r="D74" s="47" t="s">
+        <v>418</v>
+      </c>
+      <c r="E74" s="47" t="s">
+        <v>419</v>
+      </c>
+      <c r="F74" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="G74" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="H74" s="47" t="s">
+        <v>422</v>
+      </c>
+      <c r="I74" s="47" t="s">
+        <v>416</v>
+      </c>
+      <c r="J74" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L74" s="46">
+        <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B70" s="48"/>
+    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A75" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="47" t="s">
+        <v>383</v>
+      </c>
+      <c r="D75" s="47" t="s">
+        <v>423</v>
+      </c>
+      <c r="E75" s="47" t="s">
+        <v>446</v>
+      </c>
+      <c r="F75" s="47" t="s">
+        <v>447</v>
+      </c>
+      <c r="G75" s="47" t="s">
+        <v>424</v>
+      </c>
+      <c r="H75" s="47" t="s">
+        <v>425</v>
+      </c>
+      <c r="I75" s="47" t="s">
+        <v>422</v>
+      </c>
+      <c r="J75" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L75" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="47" t="s">
+        <v>384</v>
+      </c>
+      <c r="D76" s="47" t="s">
+        <v>426</v>
+      </c>
+      <c r="E76" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="F76" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="G76" s="47" t="s">
+        <v>429</v>
+      </c>
+      <c r="H76" s="47" t="s">
+        <v>385</v>
+      </c>
+      <c r="I76" s="47" t="s">
+        <v>425</v>
+      </c>
+      <c r="J76" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L76" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A77" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B77" s="47" t="s">
+        <v>386</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="E77" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="F77" s="47" t="s">
+        <v>432</v>
+      </c>
+      <c r="G77" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="H77" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="I77" s="47" t="s">
+        <v>426</v>
+      </c>
+      <c r="J77" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L77" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A78" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="47" t="s">
+        <v>387</v>
+      </c>
+      <c r="D78" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="E78" s="47" t="s">
+        <v>436</v>
+      </c>
+      <c r="F78" s="47" t="s">
+        <v>437</v>
+      </c>
+      <c r="G78" s="47" t="s">
+        <v>438</v>
+      </c>
+      <c r="H78" s="47" t="s">
+        <v>388</v>
+      </c>
+      <c r="I78" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="J78" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L78" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A79" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B79" s="47" t="s">
+        <v>389</v>
+      </c>
+      <c r="D79" s="47" t="s">
+        <v>390</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>439</v>
+      </c>
+      <c r="F79" s="47" t="s">
+        <v>440</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>441</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>391</v>
+      </c>
+      <c r="I79" s="47" t="s">
+        <v>437</v>
+      </c>
+      <c r="J79" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L79" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A80" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B80" s="47" t="s">
+        <v>451</v>
+      </c>
+      <c r="D80" s="47" t="s">
+        <v>442</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>452</v>
+      </c>
+      <c r="F80" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="G80" s="47" t="s">
+        <v>448</v>
+      </c>
+      <c r="H80" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="I80" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="J80" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L80" s="46">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF468BB3-224F-4849-9B0A-0916B1F81689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1859F96-324A-4BFE-A515-57205A714459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="897">
   <si>
     <t>Option 1</t>
   </si>
@@ -50,30 +50,6 @@
     <t>Option 4</t>
   </si>
   <si>
-    <t>Victor Hugo</t>
-  </si>
-  <si>
-    <t>Stendhal</t>
-  </si>
-  <si>
-    <t>Zola</t>
-  </si>
-  <si>
-    <t>Balzac</t>
-  </si>
-  <si>
-    <t>m.a</t>
-  </si>
-  <si>
-    <t>m.v</t>
-  </si>
-  <si>
-    <t>m.v2</t>
-  </si>
-  <si>
-    <t>m.g</t>
-  </si>
-  <si>
     <t>Texte de la question</t>
   </si>
   <si>
@@ -86,28 +62,7 @@
     <t>Note</t>
   </si>
   <si>
-    <t>proportionnelle au temps</t>
-  </si>
-  <si>
-    <t>Inversement proportionnelle à la distance</t>
-  </si>
-  <si>
-    <t>proportionnelle à la distance</t>
-  </si>
-  <si>
     <t>Matière</t>
-  </si>
-  <si>
-    <t>Même</t>
-  </si>
-  <si>
-    <t>Taille</t>
-  </si>
-  <si>
-    <t>Mode de vie</t>
-  </si>
-  <si>
-    <t>Biologie</t>
   </si>
   <si>
     <t>PHYSIQUE</t>
@@ -1490,18 +1445,6 @@
       </rPr>
       <t>formation  des gamètes.</t>
     </r>
-  </si>
-  <si>
-    <t>a.g</t>
-  </si>
-  <si>
-    <t>proportionnelle au température</t>
-  </si>
-  <si>
-    <t>Moniac</t>
-  </si>
-  <si>
-    <t>Physiologie</t>
   </si>
   <si>
     <r>
@@ -5895,18 +5838,6 @@
       </rPr>
       <t>(R//r, c//c)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">PFD est F = </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La vitesse est </t>
-  </si>
-  <si>
-    <t>Qui a écrit 'Le Rouge et le Noir' ?</t>
-  </si>
-  <si>
-    <t>Quelle est la différence entre la souris et le rat ?</t>
   </si>
   <si>
     <r>
@@ -12196,12 +12127,6 @@
     <t>C) 0</t>
   </si>
   <si>
-    <t>\section*{Propagation d'une onde le long d'une corde : }.     Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $\nu$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 \mathrm{~s}$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.</t>
-  </si>
-  <si>
-    <t>\begin{figure}      \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=265&amp;width=939&amp;top_left_y=752&amp;top_left_x=133}     \captionsetup{labelformat=empty}       \caption{Figure 1}     \end{figure}    \begin{figure}     \includegraphics[alt={},max width=\textwidth]{https://cdn.mathpix.com/cropped/279e22aa-95a9-45ef-a751-9e3ff09a38fe-1.jpg?height=216&amp;width=552&amp;top_left_y=803&amp;top_left_x=1237}     \captionsetup{labelformat=empty}    \caption{Figure 2}      \end{figure}</t>
-  </si>
-  <si>
     <t>Q21. Les valeurs de la longueur d'onde et de la célérité de propagation de l'onde le long de la corde sont :</t>
   </si>
   <si>
@@ -12218,9 +12143,6 @@
   </si>
   <si>
     <t>$\lambda=0,80 \mathrm{~m}$  \\ $\mathbf{E}$ &amp; $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
-  </si>
-  <si>
-    <t>CECI EST UN TEST D'INSERTION D'IMAGE</t>
   </si>
   <si>
     <t>Une urne $U$ contient 9 boules : dont 5 boules rouges numérotées de 1 à 5 et 4 boules noires numérotées de 1 à 4 . On suppose que les boules sont indiscernables au toucher. On tire simultanément deux boules de l'urne. On considère les deux événements $A$ : « les deux boules tirées sont de mème couleur» et $B$ « les deux boules tirés portent un numéro pair». Calculer $\boldsymbol{P}_{\bar{A}}(\boldsymbol{B})$ ?</t>
@@ -12537,6 +12459,1410 @@
   </si>
   <si>
     <t>$\boldsymbol{(} \boldsymbol{B})$ : Il existe $c \in] 0,1$ ] tel que $f(c)=0$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propagation d'une onde le long d'une corde : Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $\nu$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 \mathrm{~s}$. Le front d'onde se trouve à l'instant $t_{1}$ à la distance $S F=80 \mathrm{cm}$ de $S$.  </t>
+  </si>
+  <si>
+    <t>Dans $\mathbb{C}$, l'ensemble des solutions de l'équation $\frac{2 z-1}{z+1}=z$ est:</t>
+  </si>
+  <si>
+    <t>Si $\boldsymbol{f}$ est une solution sur $\mathbb{R}$ de l'équation différentielle $\boldsymbol{y}^{\prime \prime}+\mathbf{2} \boldsymbol{y}^{\prime}+\mathbf{4} \boldsymbol{y}=\mathbf{0}$ alors $\boldsymbol{g}=\mathbf{2} \boldsymbol{f}$ est une solution sur $\mathbb{R}$ de l'équation différentielle :</t>
+  </si>
+  <si>
+    <t>Si $z=e^{i x}-e^{-i x}$ avec $\left.x \in\right] 0 ; \pi[$, alors $|z|$ est égale à :</t>
+  </si>
+  <si>
+    <t>$\lim _{n \rightarrow+\infty} n-\sqrt{n^{2}-n}$ est égale à:</t>
+  </si>
+  <si>
+    <t>Dans $\mathbb{C}$, si $\arg (i z) \equiv \frac{7 \pi}{6}[\mathbf{2} \pi]$ et $|z|=\sqrt{2}$ alors la partie imaginaire de $z^{3}$ est :</t>
+  </si>
+  <si>
+    <t>Dans l'espace rapporté à un repère orthonormé $\operatorname{direct}(O, \vec{\imath}, \vec{\jmath}, \vec{k})$, on considère les deux points $\boldsymbol{A}(\mathbf{1} ; \mathbf{2} ; \mathbf{3})$ et $\boldsymbol{B}(\mathbf{2} ; \mathbf{0} ; \mathbf{1})$. L'ensemble des points $M(x ; y ; z)$ équidistants des points A et B est</t>
+  </si>
+  <si>
+    <t>(A) $\left\{-1 ; \frac{1}{2}\right\}$</t>
+  </si>
+  <si>
+    <t>(B) $\{1+i \sqrt{3} ; 1-i \sqrt{3}\}$</t>
+  </si>
+  <si>
+    <t>(C) $\left\{\frac{1+i \sqrt{3}}{2} ; \frac{1-i \sqrt{3}}{2}\right\}$</t>
+  </si>
+  <si>
+    <t>(D) $\{i \sqrt{3} ;-i \sqrt{3}\}$</t>
+  </si>
+  <si>
+    <t>(E) Autre réponse</t>
+  </si>
+  <si>
+    <t>(A) $\boldsymbol{y}^{\prime \prime}+\mathbf{2} \boldsymbol{y}^{\prime}+\mathbf{4} \boldsymbol{y}=\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>(B) $\boldsymbol{y}^{\prime \prime}+\boldsymbol{y}^{\prime}+\boldsymbol{y}=\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>(C) $\boldsymbol{y}^{\prime \prime}+\mathbf{4} \boldsymbol{y}^{\prime}+\mathbf{4} \boldsymbol{y}=\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>(D) $\mathbf{2 \boldsymbol { y } ^ { \prime \prime } + \mathbf { 4 } \boldsymbol { y } ^ { \prime } + \boldsymbol { y } = \mathbf { 0 }}$</t>
+  </si>
+  <si>
+    <t>(E) Autre</t>
+  </si>
+  <si>
+    <t>(A) 2</t>
+  </si>
+  <si>
+    <t>(B) $2 \cos x$</t>
+  </si>
+  <si>
+    <t>(C) $2 \cos \frac{x}{2}$</t>
+  </si>
+  <si>
+    <t>(D) $2 \sin x$</t>
+  </si>
+  <si>
+    <t>(E) $2 \sin \frac{x}{2}$</t>
+  </si>
+  <si>
+    <t>(A) $-\infty$</t>
+  </si>
+  <si>
+    <t>(B) $\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>(C) $\mathbf{1} / \mathbf{2}$</t>
+  </si>
+  <si>
+    <t>(D) $\mathbf{1}$</t>
+  </si>
+  <si>
+    <t>(A) $\mathbf{0}$</t>
+  </si>
+  <si>
+    <t>(B) $\mathbf{2} \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(C) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(D) $-\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(E) $-\mathbf{2} \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(A) Le plan $x-y+z=6$</t>
+  </si>
+  <si>
+    <t>(B) Le plan $2 x-4 y-4 z=-9$</t>
+  </si>
+  <si>
+    <t>(C) Le plan $2 x-4 y-4 z=9$</t>
+  </si>
+  <si>
+    <t>(D) La droite : $x+y+z=6$ et $2 x-4 y-4 z=-9$</t>
+  </si>
+  <si>
+    <t>MEDECINE 2022</t>
+  </si>
+  <si>
+    <t>Soit $a \in \mathbb{R}^{*}$. Si $\int_{0}^{1} \frac{\mathrm{e}^{\mathrm{ax}}}{\mathrm{e}^{\mathrm{ax}}+1} \mathrm{dx}=\frac{1}{a}$ alors a est égal à :</t>
+  </si>
+  <si>
+    <t>Le plan complexe est rapporté à un repère orthonormé direct Soit $z$ un nombre complexe et $\Omega, M$ et $M^{\prime}$ les points d'affixes respectivement $-\frac{\sqrt{3}}{3}$, $z$ et $z^{\prime}$ tel que : $z^{\prime}=(1+i \sqrt{3}) z+i$, alors une mesure de l'angle $\left(\overrightarrow{\Omega M} ; \overrightarrow{\Omega M^{\prime}}\right)$ est :</t>
+  </si>
+  <si>
+    <t>ABCD est un carré de coté 1. On place les points E et F respectivement sur les coté $[A B]$ ET $[B C]$ tels que $B E=C F=x$ La valeur de x pour laquelle l'aire du triangle EFD est minimale est :</t>
+  </si>
+  <si>
+    <t>Dans $\mathbb{C}$, si $|z|-z=3-i \sqrt{3}$ alors $|z|$ est égale à :</t>
+  </si>
+  <si>
+    <t>Le plan complexe est rapporté à un repère orthonormé direct Soient A et $B$ les points d'affixes respectives -i et $i$ L'ensemble des points $M$ d'affixe $z$ tel que $\left|\frac{i z-1}{\bar{z}+i}\right|=1$ est :</t>
+  </si>
+  <si>
+    <t>Soit $x \in \mathbb{R}^{*} ; \lim _{n \rightarrow+\infty}\left(1+\frac{x}{7 n}\right)^{29 n}=2022$ alors $x$ est égal à :</t>
+  </si>
+  <si>
+    <t>Dans l'espace rapporté à un repère orthonormé $\operatorname{direct}(\boldsymbol{O}, \vec{\imath}, \vec{\jmath}, \vec{k})$, on considère le plan (P) d'équation $\mathbf{3} \boldsymbol{x}-\mathbf{2} \boldsymbol{z}+\mathbf{3}=\mathbf{0}$ On dispose d'un dé régulier dont les faces sont numérotées de 1 à 6 On lance le dé et on obtient ainsi de manière équiprobable un nombre a( $\mathbf{1} \leq \boldsymbol{a} \leq \mathbf{6}$ ) La probabilité que le point $\boldsymbol{A}\leftboldsymbol{a}^{\mathbf{2}} \boldsymbol{;} \mathbf{2} \boldsymbol{a} \boldsymbol{;} \mathbf{6} \boldsymbol{a}-\mathbf{3}\right)$ appartient au plan (P) est.</t>
+  </si>
+  <si>
+    <t>Soit $\boldsymbol{f}$ la fonction définit sur $\mathbb{R}$ par $\boldsymbol{f}(\mathbf{x})=\mathbf{2} \mathbf{e}^{\mathbf{3} \boldsymbol{x}}-\mathbf{6}$ La primitive de la fonction sur $\mathbb{R}$ dont la courbe coupe l'axe des ordonnées en 3 est définit par :</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{0}^{3} \frac{\mathrm{x}^{2}+2}{\sqrt{x^{3}+6 x+4}} \mathrm{dx}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Si $\left(v_{n}\right)_{n\in \mathbb{N}^{*}}$ est une suite telle que : $\left(\forall n \in \mathbb{N}^{*}\right): v_{1}+v_{2}+\cdots+v_{n-1}+v_{n}=2 n^{2}+n$ Alors :</t>
+  </si>
+  <si>
+    <t>Soit $f$ la fonction définit sur $\mathbb{R}$ par : $(\forall x \in \mathbb{R}): f(2 x-1)=x^{2}+3 x$ Alors $f(1)+f^{\prime}(1)$ est égale à</t>
+  </si>
+  <si>
+    <t>Si pour tout entier naturel n , $I_{n}=\int_{1}^{\mathrm{e}} \mathrm{x}(\ln \mathrm{x})^{n} \mathrm{dx}$. Alors $\left(\forall n \in \mathbb{N}^{*}\right): 2 I_{n+1}+(n+1) I_{n}$ égal à :</t>
+  </si>
+  <si>
+    <t>Soit $\boldsymbol{f}$ la fonction définie sur $\mathbb{R}$ par : $f(x)=\sum_{k=0}^{k=n} x^{k}=1+x+x^{2}+\cdots+x^{n}$ Et (C) sa courbe dans un repère orthonormé L'équation réduite de la tangente à ( $\mathbf{C}$ ) au point d'abscisse 1 est :</t>
+  </si>
+  <si>
+    <t>Soit la suite $\left(\boldsymbol{u}_{\boldsymbol{n}}\right)_{\boldsymbol{n} \in \mathbb{N}}$ définit par : $\left.\boldsymbol{u}_{\mathbf{0}} \in\right] \mathbf{0} ; \mathbf{1}\left[\right.$ et $(\forall \boldsymbol{n} \in \mathbb{N}): \boldsymbol{u}_{\boldsymbol{n+1}}=\boldsymbol{f}\left\boldsymbol{u}_{\boldsymbol{n}}\right)$ Ou $\boldsymbol{f}$ la fonction définie sur $[\mathbf{0} ; \mathbf{1}]$ par : $\boldsymbol{f}(\mathbf{x})=\frac{\sqrt{x}}{\sqrt{x}+\sqrt{1-x}}$. On a alors :</t>
+  </si>
+  <si>
+    <t>(A) $\ln (e-1)$</t>
+  </si>
+  <si>
+    <t>(B) $\mathbf{2 e}-\mathbf{1}$</t>
+  </si>
+  <si>
+    <t>(C) $\ln (\mathbf{2 e}+\mathbf{1})$</t>
+  </si>
+  <si>
+    <t>(D) $\ln (\mathbf{2 e}-\mathbf{1})$</t>
+  </si>
+  <si>
+    <t>(E) $\mathbf{2 e}+\mathbf{1}$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{\mathbf{2} \boldsymbol{\pi}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{\boldsymbol{\pi}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(C) $-\frac{\mathbf{2} \boldsymbol{\pi}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(D) $-\frac{\boldsymbol{\pi}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>(A) 0</t>
+  </si>
+  <si>
+    <t>(B) $\frac{1}{4}$</t>
+  </si>
+  <si>
+    <t>(C) $\frac{\mathbf{1}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{\mathbf{1}}{\mathbf{2}}$</t>
+  </si>
+  <si>
+    <t>(B) 2</t>
+  </si>
+  <si>
+    <t>(C) $2 \sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(D) $3 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(E) $7 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(A) La médiatrice du $[A B]$</t>
+  </si>
+  <si>
+    <t>(B) La droite ( $\boldsymbol{A} \boldsymbol{B}$ )</t>
+  </si>
+  <si>
+    <t>(C) La droite (AB) privé du point B</t>
+  </si>
+  <si>
+    <t>(D) Le cercle de diamètre $[A B]$</t>
+  </si>
+  <si>
+    <t>(E) Le cercle de diamètre $\boldsymbol{[} \boldsymbol{A B} \boldsymbol{]}$ privé du point B</t>
+  </si>
+  <si>
+    <t>(A) $\frac{29}{7} \ln 2022$</t>
+  </si>
+  <si>
+    <t>(B) $2022 \ln \frac{7}{29}$</t>
+  </si>
+  <si>
+    <t>(C) $2022 \ln \frac{29}{7}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{7}{29} \ln 2022$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{1}{6}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{1}{3}$</t>
+  </si>
+  <si>
+    <t>(C) $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(A) $F(x) = \frac{2}{3} e^{3 x}-6 x-\frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(B) $F(x) = \frac{2}{3} e^{3 x}-6 x+\frac{7}{3}$</t>
+  </si>
+  <si>
+    <t>(C) $F(x) = \frac{2}{3} e^{3 x}-6 x-\frac{7}{3}$</t>
+  </si>
+  <si>
+    <t>(D) $F(x) = \frac{2}{3} e^{3 x}-6 x+\frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{\mathbf{1}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{\mathbf{8}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(C) $\frac{\mathbf{10}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{\mathbf{14}}{\mathbf{3}}$</t>
+  </si>
+  <si>
+    <t>(A) $v_{8}=31$</t>
+  </si>
+  <si>
+    <t>(B) $v_{8}=53$</t>
+  </si>
+  <si>
+    <t>(C) $v_{8}=54$</t>
+  </si>
+  <si>
+    <t>(D) $v_{8}=62$</t>
+  </si>
+  <si>
+    <t>(E) $v_{8}=64$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{5}{2}$</t>
+  </si>
+  <si>
+    <t>(B) 4</t>
+  </si>
+  <si>
+    <t>(C) $\frac{9}{2}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{13}{2}$</t>
+  </si>
+  <si>
+    <t>(A) $e$</t>
+  </si>
+  <si>
+    <t>(B) $e^{2}$</t>
+  </si>
+  <si>
+    <t>(C) 1</t>
+  </si>
+  <si>
+    <t>(D) $\frac{e-1}{2}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{e+1}{2}$</t>
+  </si>
+  <si>
+    <t>(A) $y=\frac{n(n+1)}{2} x-\frac{(n-2)(n+1)}{2}$</t>
+  </si>
+  <si>
+    <t>(B) $y=\frac{n(n-1)}{2} x-\frac{(n-2)(n+1)}{2}$</t>
+  </si>
+  <si>
+    <t>(C) $y=\frac{n(n+1)}{2} x+\frac{(n-2)(n+1)}{2}$</t>
+  </si>
+  <si>
+    <t>(D) $y=\frac{n(n-1)}{2} x-\frac{n^{2}-1}{2}$</t>
+  </si>
+  <si>
+    <t>(A) $\lim _{n \rightarrow+\infty} u_{n}=0$</t>
+  </si>
+  <si>
+    <t>(B) $\lim _{n \rightarrow+\infty} u_{n}=\frac{1}{3}$</t>
+  </si>
+  <si>
+    <t>(C) $\lim _{n \rightarrow+\infty} u_{n}=1$</t>
+  </si>
+  <si>
+    <t>(D) $\lim _{n \rightarrow+\infty} u_{n}=+\infty$</t>
+  </si>
+  <si>
+    <t>$\lim _{x \rightarrow 0} \frac{\sqrt{\ln (e+x)}-1}{\sqrt{x+1}-1}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Si $f(x)=\frac{1}{1-x} \ln \left(1+\frac{1}{x}\right)$ alors $f^{\prime}(x)$ est égale à :</t>
+  </si>
+  <si>
+    <t>Le nombre complexe $\left(\frac{7-15 i}{15+7 i}\right)^{2021}$ est égal à :</t>
+  </si>
+  <si>
+    <t>Si $x \in] 0,1\left[\right.$, alors $\lim _{n \rightarrow+\infty}\left(1-x+x^{2}-x^{3}+\ldots \ldots \ldots+(-1)^{n} x^{n}\right)$ est égale à :</t>
+  </si>
+  <si>
+    <t>Dans $\mathbb{R}$, le nombre de solutions de l'équation $x^{5}+x-1=0$ est :</t>
+  </si>
+  <si>
+    <t>Dans l'ensemble $\mathbb{C}, \mathbf{s i}|z| \bar{z}=15-20 i$ alors $|(1+i) z|$ est égal à :</t>
+  </si>
+  <si>
+    <t>Si $f$ est la fonction définie sur $\mathbb{R}^{*}$ par $f(x)=\frac{\sqrt{\ln \left(1+x^{2}\right)}}{x}$ alors :</t>
+  </si>
+  <si>
+    <t>$\left(u_{n}\right)_{n \geq 0}$ est la suite définie par: $u_{0}=1$ et pour tout $n \in \mathbb{N}, u_{n+1}=u_{n}^{2}+u_{n}$. La limite de la suite $\left(u_{n}\right)_{n \geq 0}$ si elle existe, est égale à :</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{0}^{1} \frac{x}{1+e^{-x^{2}}} d x$ est égale à :</t>
+  </si>
+  <si>
+    <t>Si $f(1)=4$ et $\left(\forall x \in \mathbb{R}_{+}^{*}\right) ; f^{\prime}(x)=2 x+\ln x$ alors $f(e)$ est égale à :</t>
+  </si>
+  <si>
+    <t>Dans l'ensemble $\mathbb{C}$, si $z=1+i(1+\sqrt{2})$ alors :</t>
+  </si>
+  <si>
+    <t>Si $\int_{1}^{2} f^{\prime}(x) f^{\prime \prime}(x) d x=8$ et $f^{\prime}(2)-f^{\prime}(1)=2$ alors $f^{\prime}(2)+f^{\prime}(1)$ est égal à :</t>
+  </si>
+  <si>
+    <t>Soit $q \in \mathbb{R}$.Pour tout $n \in \mathbb{N}^{*}$ on pose $S_{n}=\sum_{k=1}^{k=n} q^{k}$. Si la suite $\left(S_{n}\right)_{n \in \mathbb{N}^{*}}$ est convergente et $\lim _{n \rightarrow+\infty} S_{n}=4$, alors $q$ est égal à :</t>
+  </si>
+  <si>
+    <t>L'intégrale $I=\int_{\frac{\pi}{6}}^{\frac{\pi}{3}} \frac{\sin x}{\sin x+\cos x} d x$ est égale à :</t>
+  </si>
+  <si>
+    <t>Dans l'ensemble $\mathbb{C}$, si $\left|z_{1}\right|=\left|z_{2}\right|=1$ et $\left|z_{1}+z_{2}\right|=\sqrt{3}$ alors $\left|z_{1}-z_{2}\right|$ est égal à:</t>
+  </si>
+  <si>
+    <t>$\left(u_{n}\right)_{n \geq 0}$ est la suite définie par : $u_{0}=0, u_{1}=1$ et pour tout $n \in \mathbb{N}^{*}, u_{n}=\sqrt{\frac{u_{n+1}^{2}+u_{n-1}^{2}}{2}} \lim _{n \rightarrow-\infty} u_{n}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soient $(a ; b) \in \mathbb{R}^{2}$ et $f$ la fonction définie sur $\mathbb{R}$ par : $$f(x)=\left\{\begin{array}{lll}a x+b &amp; , &amp; \text { si } \\\frac{1}{x+1} &amp; , &amp; \text { si } \\&amp; x&gt;0\end{array}\right.$$. La fonction $f$ est dérivable en 0 si et seulement si :</t>
+  </si>
+  <si>
+    <t>Soient $(a ; b) \in \mathbb{R}^{2}$ et $f$ la fonction définie sur $\mathbb{R}$ par: $f(x)=3 x^{2}+2 a x+b$ Si $\int_{-1}^{1} f(x) d x&lt;2$ alors le nombre de solutions dans $\mathbb{R}$ de l'équation $f(x)=0$ est :</t>
+  </si>
+  <si>
+    <t>Le plan complexe est rapporté à un repère orthonormé direct $(O, \vec{u}, \vec{v})$ et $\alpha \in] 0 ; \frac{\pi}{2}[$, Soient $z_{1}$ et $z_{2}$ les deux solutions de l'équation d'inconnue $z$, $$(E): z^{2}-\sin (2 \alpha) z+\sin ^{2}(\alpha)=0$$, La valeur de $\alpha$ pour laquelle les points $O, M\left(z_{1}\right)$ et $M\left(z_{2}\right)$ sont les sommets d'un triangle équilatéral est :</t>
+  </si>
+  <si>
+    <t>Pour tout entier naturel non nul $n$ et pour tout réel $x$ on pose : $f_{n}(x)=e^{-x}-n x$ Ona :</t>
+  </si>
+  <si>
+    <t>(A) $\frac{1}{2 e}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{1}{e}$</t>
+  </si>
+  <si>
+    <t>D $e$</t>
+  </si>
+  <si>
+    <t>(E) $2 e$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{1}{(1-x)^{2}} \ln \left(1+\frac{1}{x}\right)+\frac{1}{x\left(1-x^{2}\right)}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{1}{(1-x)^{2}} \ln \left(1+\frac{1}{x}\right)-\frac{1}{x\left(1-x^{2}\right)}$</t>
+  </si>
+  <si>
+    <t>(C) $\frac{1}{1-x^{2}} \ln \left(1+\frac{1}{x}\right)-\frac{1}{x\left(1-x^{2}\right)}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{1}{(1-x)^{2}} \ln \left(1+\frac{1}{x}\right)-\frac{1}{x(1-x)^{2}}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{1}{(1-x)^{2}} \ln \left(1+\frac{1}{x}\right)-\frac{1}{\left(1-x^{2}\right)}$</t>
+  </si>
+  <si>
+    <t>(A) $i$</t>
+  </si>
+  <si>
+    <t>(B) -1</t>
+  </si>
+  <si>
+    <t>(C) $7-15 i$</t>
+  </si>
+  <si>
+    <t>(D) $-i$</t>
+  </si>
+  <si>
+    <t>(E) $7+15 i$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{1}{x-1}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{1}{1-x}$</t>
+  </si>
+  <si>
+    <t>D) $\frac{-1}{1+x}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{1}{1+x}$</t>
+  </si>
+  <si>
+    <t>(B) 1</t>
+  </si>
+  <si>
+    <t>(C) 2</t>
+  </si>
+  <si>
+    <t>D 3</t>
+  </si>
+  <si>
+    <t>E 5</t>
+  </si>
+  <si>
+    <t>(A) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(B) $2 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(C) $3 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(D) $4 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>E $5 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(A) $\lim _{x \rightarrow 0} f(x)=1$</t>
+  </si>
+  <si>
+    <t>(B) $\lim _{x \rightarrow 0} f(x)=-1$</t>
+  </si>
+  <si>
+    <t>(C) $\lim _{x \rightarrow 0} f(x)=\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>D $\lim _{x \rightarrow 0} f(x)=0$</t>
+  </si>
+  <si>
+    <t>$E$ La fonction $f$ n'admet pas de limite en 0</t>
+  </si>
+  <si>
+    <t>(A) 1</t>
+  </si>
+  <si>
+    <t>(B) $+\infty$</t>
+  </si>
+  <si>
+    <t>(C) : 0</t>
+  </si>
+  <si>
+    <t>(D) :  -1</t>
+  </si>
+  <si>
+    <t>(E) :  Autre valeur</t>
+  </si>
+  <si>
+    <t>(A) $\sqrt{\ln \left(\frac{1+e}{2}\right)}$</t>
+  </si>
+  <si>
+    <t>(B) $\ln \sqrt{1+e}$</t>
+  </si>
+  <si>
+    <t>(C) $\ln (1+e)$</t>
+  </si>
+  <si>
+    <t>$D \ln \sqrt{\frac{1+e}{2}}$</t>
+  </si>
+  <si>
+    <t>E) $\sqrt{\ln (1+e)}$</t>
+  </si>
+  <si>
+    <t>(A) $e^{2}$</t>
+  </si>
+  <si>
+    <t>(B) $e+4$</t>
+  </si>
+  <si>
+    <t>(C) $e^{2}+4$</t>
+  </si>
+  <si>
+    <t>(D) $e$</t>
+  </si>
+  <si>
+    <t>E 4</t>
+  </si>
+  <si>
+    <t>A $|z|=2 \sqrt{2} \cos \frac{\pi}{8}$ et $\arg z \equiv \frac{3 \pi}{8}[2 \pi]$</t>
+  </si>
+  <si>
+    <t>B $|z|=2 \sqrt{2} \cos \frac{\pi}{8}$ et $\arg z \equiv \frac{\pi}{8}$ [2π]</t>
+  </si>
+  <si>
+    <t>(C) $|z|=2 \sqrt{2} \cos \frac{3 \pi}{8}$ et $\arg z \equiv \frac{3 \pi}{8} \quad[2 \pi]$</t>
+  </si>
+  <si>
+    <t>D $|z|=2 \sqrt{2} \cos \frac{3 \pi}{8}$ et $\arg z \equiv \frac{\pi}{8}$ [2 $\pi$ ]</t>
+  </si>
+  <si>
+    <t>E $|z|=2 \cos \frac{\pi}{8} \quad$ et $\quad \arg z \equiv \frac{3 \pi}{8} \quad[2 \pi]$</t>
+  </si>
+  <si>
+    <t>(A) 4</t>
+  </si>
+  <si>
+    <t>(B) 6</t>
+  </si>
+  <si>
+    <t>(C) 8</t>
+  </si>
+  <si>
+    <t>(D) 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(E) : 12 </t>
+  </si>
+  <si>
+    <t>(A) $\frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{3}{4}$</t>
+  </si>
+  <si>
+    <t>(C) $\frac{4}{5}$</t>
+  </si>
+  <si>
+    <t>D $\frac{5}{6}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{6}{7}$</t>
+  </si>
+  <si>
+    <t>(A) $\frac{\pi}{3}$</t>
+  </si>
+  <si>
+    <t>(B) $\frac{\pi}{4}$</t>
+  </si>
+  <si>
+    <t>(C) $\frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{\pi}{8}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{\pi}{12}$</t>
+  </si>
+  <si>
+    <t>(B) 3</t>
+  </si>
+  <si>
+    <t>(C) $\sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(D) 2</t>
+  </si>
+  <si>
+    <t>E $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>C 1</t>
+  </si>
+  <si>
+    <t>(D) $\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>E $\frac{\sqrt{2}}{2}$</t>
+  </si>
+  <si>
+    <t>(A) $a=1$ et $b=1$</t>
+  </si>
+  <si>
+    <t>(B) $a=-1$ et $b=1$</t>
+  </si>
+  <si>
+    <t>(C) $a=2$ et $b=1$</t>
+  </si>
+  <si>
+    <t>D $a=-1$ et $b=-1$</t>
+  </si>
+  <si>
+    <t>E $a=-1$ et $b=0$</t>
+  </si>
+  <si>
+    <t>(D) 3</t>
+  </si>
+  <si>
+    <t>(E) 4</t>
+  </si>
+  <si>
+    <t>(C) $\frac{\pi}{5}$</t>
+  </si>
+  <si>
+    <t>(D) $\frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>(E) $\frac{\pi}{8}$</t>
+  </si>
+  <si>
+    <t>(A) $\left(\forall n \in \mathbb{N}^{*}\right),\left(\exists!a_{n} \in\right] 0 ; 1[), f_{n}\left(a_{n}\right)=0$ et $\lim _{n \rightarrow+\infty} n a_{n}=1$</t>
+  </si>
+  <si>
+    <t>B $\left(\forall n \in \mathbb{N}^{*}\right),\left(\exists!a_{n} \in\right] 0 ; 1[) \quad f_{n}\left(a_{n}\right)=0$ et $\lim _{n \rightarrow+\infty} n a_{n}=0$</t>
+  </si>
+  <si>
+    <t>${C}\left(\forall n \in \mathbb{N}^{*}\right),\left(\exists!a_{n} \in\right] 0 ; 1[) \quad f_{n}\left(a_{n}\right)=0 \quad$ et $\quad \lim _{n \rightarrow+\infty} n a_{n}=e$</t>
+  </si>
+  <si>
+    <t>$D\left(\forall n \in \mathbb{N}^{*}\right),\left(\exists!a_{n} \in\right]-1 ; 0[) \quad f_{n}\left(a_{n}\right)=0$ et $\lim _{n \rightarrow+\infty} n a_{n}=0$</t>
+  </si>
+  <si>
+    <t>E $\left(\forall n \in \mathbb{N}^{*}\right),\left(\exists!a_{n} \in\right]-1 ; 0[) \quad f_{n}\left(a_{n}\right)=0$ et $\lim _{n \rightarrow+\infty} n a_{n}=1$</t>
+  </si>
+  <si>
+    <t>Q 1 - Si $z$ est le nombre complexe de module $\sqrt{2}$ et d'argument $\frac{\pi}{3}$, alors $z^{8}$ est égal à :</t>
+  </si>
+  <si>
+    <t>Q 2 - Si $\theta$ est un nombre réel, alors $\cos ^{3} \theta$ est égal à :</t>
+  </si>
+  <si>
+    <t>Q 3 - Si $x \in] 0 ; 1$, alors $\lim _{n \rightarrow+\infty}(1-x)^{n}(1+x)^{n}$ est égal à:</t>
+  </si>
+  <si>
+    <t>Q 4 - Le domaine de définition de la fonction $f$ définie par $f(x)=\frac{1}{x-1} \ln \left(1+\frac{1}{x}\right)$ est :</t>
+  </si>
+  <si>
+    <t>Q 5 - Si $f(x)=\left(x^{2}-x\right) e^{\frac{1}{x}}$, alors $f^{\prime}(x)$ est égale à :</t>
+  </si>
+  <si>
+    <t>Q 6 - Si $z$ est un nombre complexe tel que : $\arg (z-1) \equiv \frac{2 \pi}{3}[2 \pi]$ et $\arg (z+1) \equiv \frac{\pi}{3}[2 \pi]$, alors $z$ est égal à :</t>
+  </si>
+  <si>
+    <t>Q7 - Si $z=1+e^{i \frac{\ell}{z}}$ où $\left.\theta \in\right]-\pi ; \pi[$, alors $|z|$ est égal à :</t>
+  </si>
+  <si>
+    <t>Q8 - On a $\lim _{n \rightarrow+\infty}\left(\frac{n-1}{n+1}\right)^{2 n}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Q9- Si $\left(u_{n}\right)_{n \in N^{*}}$ est une suite géométrique de premier terme $u_{1}=2$ et de raison $q=\frac{1}{3}$, alors le produit $u_{1} \times u_{2} \times u_{3} \times \cdots \times u_{n}(n \leq 1)$ est égal à:</t>
+  </si>
+  <si>
+    <t>Q 10 - Si $(\forall x \in \mathbb{R}) ; f(x)=(x-5)(x-4)(x-3)(x-2)(x-1)$, alors $f^{\prime}(1)$ est égal à :</t>
+  </si>
+  <si>
+    <t>Q 11 - Soit $f$ la fonction définie par : $f(x)=\frac{2 \ln x}{x\left(1+(\ln x)^{2}\right)}$. La primitive de $f$ sur $10 ;+\infty[$ qui s'annule en 1 est :</t>
+  </si>
+  <si>
+    <t>Q 12 - L'intégrale $\int_{0}^{1} \frac{2 t+3}{t+2} d t$ est égale à :</t>
+  </si>
+  <si>
+    <t>Q 13 - Le plan complexe est rapporté à un repère orthonormé direct ( $O ; \ddot{u} ; \vec{v}$ ). L'ensemble des points $M$ d'affixe $z$ tel que : $z+\frac{1}{z} \in \mathbb{R}$ est : :</t>
+  </si>
+  <si>
+    <t>Q 14 - Soit $\left(w_{n}\right)_{n \in N}$ la suite définie par: $w_{0}=\frac{1}{2}$ et $(\forall n \in N) ; w_{n+1}=\left(w_{n}-1\right)^{2}+1$. Si $\left(w_{n}\right)_{n \in N}$ est convergente alors $\lim _{n \rightarrow+\infty} w_{n}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Q 15 - Soit $a \in j 0$; $+\infty$ et $f$ la fonction définie par: $f(x)=1+x \ln \left(\sqrt{1+\frac{a}{x}}\right)$, alors $\lim _{x \rightarrow+\infty} f(x)$ est égale à :</t>
+  </si>
+  <si>
+    <t>Q 16 - Soit $A B C$ un triangle isocèle en $A$ tel que : $A B=A B=10$. L'aire maximale du triangle $A B C$ est :</t>
+  </si>
+  <si>
+    <t>Q 17 - Si $\left(\forall x \in \mathbb{R}_{+}^{\circ}\right) ; f(x)=x^{3}+3 \ln x+1$, alors le nombre dérivé $\left(f^{-1}\right)^{\prime}(2)$ est égal à :</t>
+  </si>
+  <si>
+    <t>Q 18 - L'intégrale $\int_{0}^{1} \sin (x) e^{x} d x$ est égale à :</t>
+  </si>
+  <si>
+    <t>Q 19 - On considère la fonction $f$ définie : $(\forall x \in \mathbb{R}) ; f(x)=e^{-\frac{x^{2}}{2}}$. Un encadrement de $f^{\prime}(x)$ surl'intervalle $[0 ; 1]$ est :</t>
+  </si>
+  <si>
+    <t>Q 20 - Soit $f(x)=\sqrt{x^{3}}+2 x^{2}+3-a x \sqrt{x}+b$ où $a$ et $b$ sont des réels. $f$ admet une limite finie en $+\infty$ si et seulement si :</t>
+  </si>
+  <si>
+    <t>(A) : $8+i 8 \sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(B) : $-8+i 8 \sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(C) : $-8-i 8 \sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(D) : $8-i 8 \sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(E) : $4+i 4 \sqrt{3}$</t>
+  </si>
+  <si>
+    <t>(A) : $\frac{1}{8}(\cos 3 \theta+3 \cos \theta)$</t>
+  </si>
+  <si>
+    <t>(B) : $\frac{1}{4}(\sin 3 \theta+3 \sin \theta)$</t>
+  </si>
+  <si>
+    <t>(C) : $\frac{1}{8}(\sin 3 \theta+3 \sin \theta)$</t>
+  </si>
+  <si>
+    <t>(D) : $\frac{1}{4}(\cos 3 \theta+3 \cos \theta)$</t>
+  </si>
+  <si>
+    <t>(E) : $\frac{1}{8}(3 \cos \theta-\cos 3 \theta)$</t>
+  </si>
+  <si>
+    <t>(A) $+\infty$</t>
+  </si>
+  <si>
+    <t>(B) $-\infty$</t>
+  </si>
+  <si>
+    <t>(D) : -1</t>
+  </si>
+  <si>
+    <t>(E) : Autre</t>
+  </si>
+  <si>
+    <t>(A) : $]-\infty ;-1[\cup] 0 ;+\infty[$</t>
+  </si>
+  <si>
+    <t>(B) : $-\infty ;-1[\cup] 1 ;+\infty \mid$</t>
+  </si>
+  <si>
+    <t>(C) : ]-1; 1[</t>
+  </si>
+  <si>
+    <t>(D) : $]-1 ; 1[U] 1 ;+\infty \mid$</t>
+  </si>
+  <si>
+    <t>(E) : $1-\infty ;-1|\cup| 0 ; 1[\cup|1 ;+\infty|$</t>
+  </si>
+  <si>
+    <t>(A) : $(2 x-1) e^{\frac{1}{x}}$</t>
+  </si>
+  <si>
+    <t>(B) : $\left(1-\frac{1}{x}\right) e^{\frac{1}{x}}$</t>
+  </si>
+  <si>
+    <t>(C) : $\left(\frac{1}{x}-1\right) e^{\frac{1}{x}}$</t>
+  </si>
+  <si>
+    <t>(D) : $\left(2 x-2+\frac{1}{x}\right) e^{\frac{1}{x}}$</t>
+  </si>
+  <si>
+    <t>(E) : $\left(2 x-\frac{1}{x}\right) e^{\frac{1}{x}}$</t>
+  </si>
+  <si>
+    <t>(A) : $\sqrt{3} i$</t>
+  </si>
+  <si>
+    <t>(B) : $2 \sqrt{3} i$</t>
+  </si>
+  <si>
+    <t>(C) : $-\sqrt{3} i$</t>
+  </si>
+  <si>
+    <t>(D) : $-2 \sqrt{3} i$</t>
+  </si>
+  <si>
+    <t>(E) : $1+\sqrt{3} i$</t>
+  </si>
+  <si>
+    <t>(A) : 2</t>
+  </si>
+  <si>
+    <t>(B) : $2 \cos \frac{\theta}{2}$</t>
+  </si>
+  <si>
+    <t>(C) : $2 \cos \frac{\theta+\pi}{4}$</t>
+  </si>
+  <si>
+    <t>(D) : $cos \frac{\theta+\pi}{4}$</t>
+  </si>
+  <si>
+    <t>(E) : $2 \cos \frac{\theta}{4}$</t>
+  </si>
+  <si>
+    <t>(A) : 0</t>
+  </si>
+  <si>
+    <t>(B) : $e^{-4}$</t>
+  </si>
+  <si>
+    <t>(C) : $e^{4}$</t>
+  </si>
+  <si>
+    <t>(D) : $e$</t>
+  </si>
+  <si>
+    <t>(E) : 1</t>
+  </si>
+  <si>
+    <t>(A) : $2^{n} \cdot 3^{\frac{n(n-1)}{2}}$</t>
+  </si>
+  <si>
+    <t>(B) : $\frac{2^{n}}{3^{\frac{n(n-1)}{2}}}$</t>
+  </si>
+  <si>
+    <t>(C) : $\frac{2^{n}}{3^{\frac{n(n+1)}{2}}}$</t>
+  </si>
+  <si>
+    <t>(D) : $2^{n} \cdot 3^{\frac{n(n+1)}{2}}$</t>
+  </si>
+  <si>
+    <t>(E) : $\frac{1}{2^{n} \cdot 3^{\frac{n(n-1)}{2}}}$</t>
+  </si>
+  <si>
+    <t>(A) : 24</t>
+  </si>
+  <si>
+    <t>(B) : 1</t>
+  </si>
+  <si>
+    <t>(D) : 5</t>
+  </si>
+  <si>
+    <t>(E) : -24</t>
+  </si>
+  <si>
+    <t>(A) : $\ln \left((\ln x)^{2}+1\right)$</t>
+  </si>
+  <si>
+    <t>(B) : $2 \ln \left((\ln x)^{2}+1\right)$</t>
+  </si>
+  <si>
+    <t>(C) : $\frac{x \ln x}{\ln x+1}$</t>
+  </si>
+  <si>
+    <t>(D) : $\frac{2 \ln x}{(\ln x)^{2}+1}$</t>
+  </si>
+  <si>
+    <t>(E) : $(\ln x)^{2}$</t>
+  </si>
+  <si>
+    <t>(A) : $\ln \frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>(B) : $2+\ln \frac{3}{2}$</t>
+  </si>
+  <si>
+    <t>(C) : $2-\ln \frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(D) : $2+\ln \frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(E) : $\ln \frac{2}{3}$</t>
+  </si>
+  <si>
+    <t>(A) : L'axe des réels privé du point $O$.</t>
+  </si>
+  <si>
+    <t>(B) : Le cercle de centre $O$ et de rayon 1</t>
+  </si>
+  <si>
+    <t>(C) : L'axe des réels privé des points $A(-1)$ et $B(1)$</t>
+  </si>
+  <si>
+    <t>(D) : Le cercle de centre $O$ et de rayon 1 privé des points $A(-1)$ et $B(1)$</t>
+  </si>
+  <si>
+    <t>(E) : L'axe des réels privé du point $O$ union le cercle de centre $O$ et de rayon 1</t>
+  </si>
+  <si>
+    <t>(B) : 2</t>
+  </si>
+  <si>
+    <t>(C) : 1</t>
+  </si>
+  <si>
+    <t>(D) : $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>(E) : -1</t>
+  </si>
+  <si>
+    <t>(A) : 1</t>
+  </si>
+  <si>
+    <t>(B) : $1+\frac{a}{x}$</t>
+  </si>
+  <si>
+    <t>(C) : $1+a$</t>
+  </si>
+  <si>
+    <t>(D) : $+\infty$</t>
+  </si>
+  <si>
+    <t>(E) : a</t>
+  </si>
+  <si>
+    <t>(A) : $25 \frac{\sqrt{2}}{2}$</t>
+  </si>
+  <si>
+    <t>(B) : 50</t>
+  </si>
+  <si>
+    <t>(C) : 100</t>
+  </si>
+  <si>
+    <t>(D) : 10</t>
+  </si>
+  <si>
+    <t>(E) : $5 \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(A) : $\frac{\sqrt{1}}{3}$</t>
+  </si>
+  <si>
+    <t>(B) : $\frac{1}{6}$</t>
+  </si>
+  <si>
+    <t>(C) : $\frac{1}{5}$</t>
+  </si>
+  <si>
+    <t>(D) : $\frac{1}{4}$</t>
+  </si>
+  <si>
+    <t>(E) : $\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>(A) : $\frac{1+e^{\frac{\pi}{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(B) : $\frac{e+e^{\frac{\pi}{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(C) : $\frac{1-e^{\frac{\pi}{2}}}{2}$</t>
+  </si>
+  <si>
+    <t>(D) : $1+e^{\frac{\pi}{2}}$</t>
+  </si>
+  <si>
+    <t>(E) : $1-e^{\frac{\pi}{2}}$</t>
+  </si>
+  <si>
+    <t>(A) : $0 \leq f^{\prime}(x) \leq \frac{1}{\sqrt{e}}$</t>
+  </si>
+  <si>
+    <t>(B) : $-\frac{1}{\sqrt{e}} \leq f^{\prime}(x) \leq 0$</t>
+  </si>
+  <si>
+    <t>(C) : $-\frac{1}{2} \leq f^{\prime}(x) \leq 0$</t>
+  </si>
+  <si>
+    <t>(D) : $-\frac{1}{\sqrt{e}} \leq f^{\prime}(x) \leq-\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>(E) : $0 \leq f^{\prime}(x) \leq \sqrt{2}$</t>
+  </si>
+  <si>
+    <t>(A) : $a&gt;0$ et $b&gt;0$</t>
+  </si>
+  <si>
+    <t>(B) : $a=1$ et $b&gt;0$</t>
+  </si>
+  <si>
+    <t>(C) : $a=1$ et $b=2$</t>
+  </si>
+  <si>
+    <t>(D) : $a=1$ et $b=0$</t>
+  </si>
+  <si>
+    <t>(E) : $a&gt;0$ et $b=0$</t>
+  </si>
+  <si>
+    <t>MEDECINE 2020</t>
+  </si>
+  <si>
+    <t>CHIMIE</t>
+  </si>
+  <si>
+    <t>\section*{Suivi temporel d'une transformation chimique : ( 6 points)} On verse dans un bécher le volume $V=2.10^{-4} m^{3}$ d'une solution ( $S_{B}$ ) d'hydroxyde de sodium de concentration molaire $C_{B}=10 \mathrm{~mol} \cdot \mathrm{~m}^{-3}$, et on y ajoute, à l'instant $t_{0}=0$, une quantité de matière $n_{E}$ de méthanoate de méthyle égale à la quantité de matière $n_{B}$ d'hydroxyde de sodium dans la solution ( $S_{B}$ ). On suppose que le volume de la solution reste constant $\left(V=2.10^{-4} \mathrm{~m}^{3}\right)$. On modélise la transformation qui se produit dans le milieu réactionnel par l'équation chimique: $$\mathrm{HCO}_{2} \mathrm{CH}_{3(\ell)}+\mathrm{HO}_{(a q)}^{-} \rightarrow \mathrm{HCO}_{2(a q)}^{-}+\mathrm{CH}_{3} \mathrm{OH}_{(\ell)}$$ La courbe de la figure ci-dessous représente les variations de la conductivité $\sigma$ du mélange au cours du temps. L'expression de la conductivité $\sigma$ à l'instant $t$ est: $\sigma=-72 . x+0,25$ ( $S . m^{-1}$ ), avec $x$ l'avancement de la réaction. \section*{Données :} - Conductivités molaires ioniques $\lambda_{t}$ des ions présents dans le mélange réactionnel : \begin{tabular}{|c|c|c|c|} \hline Ion &amp; $\mathrm{Na}^{+}$ &amp; $\mathrm{HO}^{-}$ &amp; $\mathrm{HCO}_{2}^{-}$ \\ \hline$\lambda\left(m S . m^{2} . \mathrm{mol}^{-1}\right)$ &amp; 5,01 &amp; 19,9 &amp; 5,46 \\ \hline \end{tabular} - On néglige l'effet des ions $\mathrm{H}_{3} \mathrm{O}^{+}$sur la conductivité du mélange ; - $75 \div 52=1,44$</t>
+  </si>
+  <si>
+    <t>CH22F1</t>
+  </si>
+  <si>
+    <t>Q41. La valeur de l'avancement maximal de la réaction est:</t>
+  </si>
+  <si>
+    <t>Q42. La valeur du temps de demi-réaction est :</t>
+  </si>
+  <si>
+    <t>Q43. L'expression de la vitesse volumique de la réaction est :</t>
+  </si>
+  <si>
+    <t>Q44. La valeur de la vitesse volumique de la réaction à l'instant $t_{0}=0$ est :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A) : $x_{\text {max }}=2.10^{-4} \mathrm{~mol}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(B) :  $x_{\text {max }}=2.10^{-3} \mathrm{~mol}$ </t>
+  </si>
+  <si>
+    <t>(C) : $x_{\text {max }}=1.10^{-4} \mathrm{~mol}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(D) : $x_{\text {max }}=1.10^{-3} \mathrm{~mol}$ </t>
+  </si>
+  <si>
+    <t>(E) : $x_{\text {max }}=3.10^{-3} \mathrm{~mol}$</t>
+  </si>
+  <si>
+    <t>(A) : $t_{1 / 2}=36 \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(B) : $t_{1 / 2}=32 \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(C) : $t_{1 / 2}=20 \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(D) : $t_{1 / 2}=12 \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(E) : $t_{1 / 2}=10 \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(A) : $v=-\frac{1}{72 . V} \cdot \frac{d \sigma}{d t}$</t>
+  </si>
+  <si>
+    <t>(B) : $v=-\frac{1}{36 . V} \cdot \frac{d \sigma}{d t}$</t>
+  </si>
+  <si>
+    <t>(C) : $v=-\frac{1}{V} \cdot \frac{d \sigma}{d t}$</t>
+  </si>
+  <si>
+    <t>(D) : $v=-\frac{1}{32 . V} \cdot \frac{d \sigma}{d t}$</t>
+  </si>
+  <si>
+    <t>(E) : $v=-\frac{1}{42 . V} \cdot \frac{d \sigma}{d t}$</t>
+  </si>
+  <si>
+    <t>(B) : $v=0,82 \mathrm{~mol} \cdot \mathrm{~m}^{-3} \cdot \mathrm{~min} \mathrm{i}^{-1}$</t>
+  </si>
+  <si>
+    <t>(D) : $v=0,52 \mathrm{~mol} \cdot \mathrm{~m}^{-3} \cdot \mathrm{~min}^{-1}$</t>
+  </si>
+  <si>
+    <t>(E) : $v=0,32 \mathrm{~mol} \cdot \mathrm{~m}^{-3} \cdot \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(A) : $v=1,23 \mathrm{~mol} \cdot \mathrm{~m}^{-3} \cdot \mathrm{~min}^{-1}$\mathrm{~mol} \cdot \mathrm{~m}^{-3} \cdot \mathrm{~min}$</t>
+  </si>
+  <si>
+    <t>(C) : $v=1,05 $</t>
+  </si>
+  <si>
+    <t>\section*{Solution aqueuse d'acide éthanoïque : (4 points)}. Une solution aqueuse ( $S$ ) d'acide éthanoïque de concentration molaire $C=1.10^{-3} \mathrm{~mol} . L^{-1}$ a une conductivité $\sigma=5,2 \mathrm{mS} . \mathrm{m}^{-1}$. \section*{Données :} - Conductivités molaires ioniques : $$\lambda\left(\mathrm{H}_{3} \mathrm{O}^{+}\right)=\lambda_{1}=35,0 \mathrm{mS} \cdot \mathrm{~m}^{2} \cdot \mathrm{~mol}^{-1} \quad ; \quad \lambda\left(\mathrm{CH}_{3} \mathrm{CO}_{2}^{-}\right)=\lambda_{2}=4,1 \mathrm{mS} \cdot \mathrm{~m}^{2} \cdot \mathrm{~mol}^{-1} $$- On néglige l'effet des ions $\mathrm{HO}^{-}$sur la conductivité de la solution.- $52 \div 391=0,133 ; 10^{0,63}=4,26$</t>
+  </si>
+  <si>
+    <t>Q45. La valeur de la concentration molaire effective de l'ion oxonium en solution ( $S$ ) est:</t>
+  </si>
+  <si>
+    <t>Q46. On dilue 10 fois la solution $(S)$ pour obtenir une solution $\left(S_{1}\right)$ de concentration molaire $C_{1}$ et de $p H=4,37$. La valeur du taux d'avancement final de la réaction qui a eu lieu dans la solution $\left(S_{1}\right)$ est :</t>
+  </si>
+  <si>
+    <t>(A) : $\left[\mathrm{H}_{3} \mathrm{O}^{+}\right]=1,33 \cdot 10^{-3} \mathrm{~mol} \cdot \mathrm{~L}^{-1}$</t>
+  </si>
+  <si>
+    <t>(B) : $\left[\mathrm{H}_{3} \mathrm{O}^{+}\right]=1,33 \cdot 10^{-2} \mathrm{~mol} \cdot \mathrm{~L}^{-1}$</t>
+  </si>
+  <si>
+    <t>(C)  : $\left[\mathrm{H}_{3} \mathrm{O}^{+}\right]=1,33 \cdot 10^{-6} \mathrm{~mol} \cdot \mathrm{~L}^{-1}$</t>
+  </si>
+  <si>
+    <t>(D) : $\left[\mathrm{H}_{3} \mathrm{O}^{+}\right]=1,33 \cdot 10^{-4} \mathrm{~mol} \cdot \mathrm{~L}^{-1}$</t>
+  </si>
+  <si>
+    <t>(E) : $\left[\mathrm{H}_{3} \mathrm{O}^{+}\right]=1,33 \cdot 10^{-5} \mathrm{~mol} \cdot \mathrm{~L}^{-1}$</t>
+  </si>
+  <si>
+    <t>(A) : $\tau_{1}=0,133$</t>
+  </si>
+  <si>
+    <t>(B) : $\tau_{1}=0,042$</t>
+  </si>
+  <si>
+    <t>(C) : $\tau_{1}=0,260$</t>
+  </si>
+  <si>
+    <t>(D) : $\tau_{1}=0,013$</t>
+  </si>
+  <si>
+    <t>(E) : $\tau_{1}=0,426$</t>
+  </si>
+  <si>
+    <t>\section*{Solution aqueuse d'acide méthanoique : (5 points)}. Soit une solution aqueuse d'acide méthanoïque $H C O O H$ de concentration molaire $C$. On note $K_{A}$ la constante d'acidité du couple ( $\mathrm{HCOOH}_{\text {(aq) }} / \mathrm{HCOO}_{\text {(aq) }}^{-}$).</t>
+  </si>
+  <si>
+    <t>Q47. Le taux d'avancement final de la réaction entre l'acide méthanoïque et l'eau a pour expression :</t>
+  </si>
+  <si>
+    <t>Q48. L'expression de la concentration molaire $C$ est :</t>
+  </si>
+  <si>
+    <t>(A) : $\tau=\frac{1}{1+10^{p H-p K_{A}}}$</t>
+  </si>
+  <si>
+    <t>(B) : $\tau=\frac{1}{1-10^{p K_{A}-p H}}$</t>
+  </si>
+  <si>
+    <t>(C) : $\tau=\frac{1}{1+10^{p K_{A}-p H}}$</t>
+  </si>
+  <si>
+    <t>(D) : $\tau=\frac{1}{1+10^{-\left(p K_{A}+p H\right)}}$</t>
+  </si>
+  <si>
+    <t>(E) : $\tau=\frac{1}{1+10^{p K_{A}+p H}}$</t>
+  </si>
+  <si>
+    <t>(A) : $10^{-p H}+10^{p K_{A}+2 p H}$</t>
+  </si>
+  <si>
+    <t>(B) : $10^{-p H}+10^{p K_{A}-2 p H}$</t>
+  </si>
+  <si>
+    <t>(C) : $10^{-p K_{A}}+10^{-2 p H}$</t>
+  </si>
+  <si>
+    <t>(D) : $10^{-p H}+10^{2 p H-p K_{A}}$</t>
+  </si>
+  <si>
+    <t>(E) : $10^{-2 p H}+10^{p K_{A}-p H}$</t>
+  </si>
+  <si>
+    <t>\section*{Réaction entre l'acide éthanoique et l'ammoniaque : (3 points)}. On mélange un volume d'une solution aqueuse d'acide éthanoïque contenant la quantité de matière initiale $n_{i}\left(\mathrm{CH}_{3} \mathrm{COOH}\right)$, avec un volume d'une solution aqueuse d'ammoniaque contenant la même quantité de matière initiale $n_{i}\left(\mathrm{NH}_{3}\right)=n_{i}\left(\mathrm{CH}_{3} \mathrm{COOH}\right)$. L'équation modélisant la réaction entre l'acide $\mathrm{CH}_{3} \mathrm{COOH}$ et la base $\mathrm{NH}_{3}$ s'écrit : $$\mathrm{CH}_{3} \mathrm{COOH}_{(a q)}+\mathrm{NH}_{3(a q)} \rightleftharpoons \mathrm{CH}_{3} \mathrm{COO}_{(a q)}^{-}+\mathrm{NH}_{4(a q)}^{+}$$. Données: $p K_{A}\left(\mathrm{CH}_{3} \mathrm{COOH}_{(a q)} / \mathrm{CH}_{3} \mathrm{COO}_{(a q)}^{-}\right)=p K_{A 1} \quad ; \quad p K_{A}\left(N H_{4(a q)}^{+} / N H_{3(a q)}\right)=p K_{A 2}$</t>
+  </si>
+  <si>
+    <t>Q49. L'expression de la constante d'équilibre associée à l'équation de la réaction étudiée est :</t>
+  </si>
+  <si>
+    <t>Q50. L'expression de l'avancement final de cette réaction est :</t>
+  </si>
+  <si>
+    <t>(A) : $K=10^{p K_{A 2}+p K_{A 1}}$</t>
+  </si>
+  <si>
+    <t>(B) : $K=10^{p K_{A 1}-p K_{A 2}}$</t>
+  </si>
+  <si>
+    <t>(C) : $K=\frac{K_{A 2}}{K_{A 1}}$</t>
+  </si>
+  <si>
+    <t>(D) : $K=K_{A 1} \cdot K_{A 2}$</t>
+  </si>
+  <si>
+    <t>(E) : $K=10^{p K_{A 2}-p K_{A 1}}$</t>
+  </si>
+  <si>
+    <t>(A) : $x_{f}=\frac{n_{i} \cdot \sqrt{K}}{1+\sqrt{K}}$</t>
+  </si>
+  <si>
+    <t>(B) : $x_{f}=\frac{n_{i} \cdot(1+\sqrt{K})}{\sqrt{K}}$</t>
+  </si>
+  <si>
+    <t>(C) : $x_{f}=\frac{n_{i} \cdot \sqrt{K}}{1-\sqrt{K}}$</t>
+  </si>
+  <si>
+    <t>(D) : $x_{f}=\frac{1+\sqrt{K}}{n_{i} \cdot \sqrt{K}}$</t>
+  </si>
+  <si>
+    <t>(E) : $x_{f}=\frac{\sqrt{K}}{n_{i} \cdot(1+\sqrt{K})}$</t>
+  </si>
+  <si>
+    <t>\section*{Critère d'évolution d'un système chimique : (4 points)}. On considère un système chimique obtenu en mélangeant : - le volume $V_{1}=15,0 m L$ de solution d'acide borique $H_{3} B O_{3}$ de concentration molaire $C_{1}=1,10 \times 10^{-2} \mathrm{~mol} . L^{-1}$; - le volume $V_{2}=15,0 m L$ de solution de borate de sodium $\mathrm{Na}_{(a q)}^{+}+\mathrm{H}_{2} \mathrm{BO}_{3(a q)}^{-}$de concentration molaire $C_{2}=1,20 \times 10^{-2} \mathrm{~mol} . L^{-1}$; - le volume $V_{3}=10,0 m L$ de solution de méthylamine $\mathrm{CH}_{3} \mathrm{NH}_{2}$ de concentration molaire $C_{3}=2,00 \times 10^{-2} \mathrm{~mol} . L^{-1}$; - le volume $V_{4}=10,0 m L$ de solution de chlorure de méthylammonium, $\mathrm{CH}_{3} \mathrm{NH}_{3(a q)}^{+}+\mathrm{Cl}_{(a q)}^{-}$de concentration molaire $C_{4}=1,50 \times 10^{-2} \mathrm{~mol} . \mathrm{L}^{-1}$. L'équation la réaction modélisant la transformation qui se produit dans le mélange est: $$\mathrm{H}_{3} \mathrm{BO}_{3(\mathrm{aq})}+\mathrm{CH}_{3} \mathrm{NH}_{2(\mathrm{aq})} \rightleftharpoons \mathrm{H}_{2} \mathrm{BO}_{3(\mathrm{aq})}^{-}+\mathrm{CH}_{3} \mathrm{NH}_{3(\mathrm{aq})}^{+}$$ \section*{Données :} - $p K_{A}\left(H_{3} B O_{3(a q)} / H_{2} B O_{3(a q)}^{-}\right)=p K_{A 1}=9,20 \quad ; \quad p K_{A}\left(C H_{3} N H_{3(a q)}^{+} / C H_{3} N H_{2(a q)}\right)=p K_{A 2}=10,7$. - $10^{0,5}=3,16 \quad ; \quad \underline{\log } \frac{725}{2775}=-0,58 \quad ; \quad \log \frac{3075}{375}=0,9$</t>
+  </si>
+  <si>
+    <t>Q51. La valeur du quotient de réaction à l'état initial du système est :</t>
+  </si>
+  <si>
+    <t>Q52. L'avancement final de la réaction est $x_{f}=1,275.10^{-4} \mathrm{~mol}$. La valeur du $p H$ du mélange est :</t>
+  </si>
+  <si>
+    <t>(A) : $Q_{r, i}=0,918$</t>
+  </si>
+  <si>
+    <t>(B) : $Q_{r, i}=1,22$</t>
+  </si>
+  <si>
+    <t>(C} : $Q_{r, i}=1,318$</t>
+  </si>
+  <si>
+    <t>(D) : $Q_{r, i}=0,818$</t>
+  </si>
+  <si>
+    <t>(E) : $Q_{r, i}=1$</t>
+  </si>
+  <si>
+    <t>(A) : $p H=10,1$</t>
+  </si>
+  <si>
+    <t>(B) : $p H=11,1$</t>
+  </si>
+  <si>
+    <t>(C) : $p H=9,95$</t>
+  </si>
+  <si>
+    <t>(D) : $p H=8,1$</t>
+  </si>
+  <si>
+    <t>(E) : $p H=5,1$</t>
+  </si>
+  <si>
+    <t>\section*{Pile (Cadmium/Argent) : (8 points)}. On réalise la pile (Cadmium/Argent) en utilisant une lame d'argent $A g_{(s)}$ plongée dans une solution aqueuse de nitrate d'argent $A g_{(a q)}^{+}+N O_{3(a q)}^{-}$de concentration molaire initiale $C_{1}=0,4 m o l . L^{-1}$ et une lame de cadmium $\mathrm{Cd}_{(s)}$ plongée dans une solution aqueuse de nitrate de cadmium $\mathrm{Cd}_{(a q)}^{2+}+2 \mathrm{NO}_{3(a q)}^{-}$de concentration molaire initiale $C_{2}=0,2 \mathrm{~mol} \cdot L^{-1}$. Les deux solutions sont reliées par un pont salin. On branche entre les deux électrodes de la pile un conducteur ohmique montée en série avec un ampèremètre et un interrupteur. On ferme le circuit à un l'instant $t_{0}=0$. Un courant électrique d'intensité constante circule dans le circuit. \section*{Données:} - Les deux solutions ont le même volume $V=250 m L$; - $M(\mathrm{Ag})=107,87 \mathrm{~g} \cdot \mathrm{~mol}^{-1}$; - La valeur de la constante d'équilibre associée à l'équation chimique : $$2 A g_{(\mathrm{aq})}^{+}+C d_{(s)} \underset{2}{\leftrightarrows} \frac{1}{\leftrightarrows} 2 A g_{(s)}+C d_{(\mathrm{aq})}^{2+} \quad \text { est: } K=5.10^{40} \text { à } 25^{\circ} \mathrm{C} ;$$ - La quantité de matière de la partie immergée de l'électrode consommable est en excès ; - $F$ constante de Faraday.</t>
+  </si>
+  <si>
+    <t>Q53. L'expression de l'avancement de la réaction lors du fonctionnement la pile à un instant $\boldsymbol{t}$ est :</t>
+  </si>
+  <si>
+    <t>Q54. À un instant $t_{1}$, les concentrations molaires effectives des ions $A g_{(a q)}^{+}$et $C d_{(a q)}^{2+}$ sont : $\left[A g_{(a q)}^{+}\right]_{1}=8.10^{-2} \mathrm{~mol} . .^{-1}$ et $\left[C d_{(a q)}^{2+}\right]_{1}=0,36 \mathrm{~mol} . .^{-1}$. \section*{La valeur du quotient de réaction à l'instant $t_{1}$ est :}</t>
+  </si>
+  <si>
+    <t>Q55. La valeur de la masse d'argent déposé sur l'électrode d'argent lorsque la pile sera usée est:</t>
+  </si>
+  <si>
+    <t>(A) : $x=\frac{F}{I . t}$</t>
+  </si>
+  <si>
+    <t>(B) : $x=\frac{2 F}{I . t}$</t>
+  </si>
+  <si>
+    <t>(C) : $x=\frac{I}{2 F . t}$</t>
+  </si>
+  <si>
+    <t>(D) : $x=\frac{I . t}{F}$</t>
+  </si>
+  <si>
+    <t>(E) : $x=\frac{I . t}{2 F}$</t>
+  </si>
+  <si>
+    <t>(A) : $Q_{r, 1}=1,25$</t>
+  </si>
+  <si>
+    <t>(B) : $Q_{r, 1}=45,6$</t>
+  </si>
+  <si>
+    <t>(C) : $Q_{r, 1}=56,2$</t>
+  </si>
+  <si>
+    <t>(D) : $Q_{r, 1}=4,56$</t>
+  </si>
+  <si>
+    <t>(E) : $Q_{r, 1}=5,62$</t>
+  </si>
+  <si>
+    <t>(A) : $m(A g)=5,398 \mathrm{~g}$</t>
+  </si>
+  <si>
+    <t>(B) : $m(A g)=1,078 \mathrm{mg}$</t>
+  </si>
+  <si>
+    <t>(C) : $m(A g)=1,078 \mathrm{~g}$</t>
+  </si>
+  <si>
+    <t>(D) : $m(A g)=10,787 \mathrm{mg}$</t>
+  </si>
+  <si>
+    <t>(E) : $m(A g)=10,787 \mathrm{~g}$</t>
+  </si>
+  <si>
+    <t>Q56. Le dispositif utilisé pour préparer cet ester s'appelle:</t>
+  </si>
+  <si>
+    <t>Q57. L'acide ( $A$ ) utilisé est :</t>
+  </si>
+  <si>
+    <t>Q58. La valeur de la constante d'équilibre associée à l'équation de la réaction qui s'est produite est :</t>
+  </si>
+  <si>
+    <t>Q59. La valeur du rendement de cette réaction est :</t>
+  </si>
+  <si>
+    <t>Q60. Lors de la synthèse industrielle de l'ester ( $E$ ), on préfère utiliser un autre réactif ( $D$ ) à la place de l'acide $(A)$, pour que la réaction soit rapide et totale. \section*{La formule semi-développée du réactif ( $D$ ) est :}</t>
+  </si>
+  <si>
+    <t>(A) : montage de distillation fractionnée</t>
+  </si>
+  <si>
+    <t>(B) : montage de chauffage à reflux</t>
+  </si>
+  <si>
+    <t>(C) : montage d'hydrodistillation</t>
+  </si>
+  <si>
+    <t>(D) : montage d'extraction par solvant</t>
+  </si>
+  <si>
+    <t>(E) : montage de chauffage sous vide</t>
+  </si>
+  <si>
+    <t>(A) : L'acide butanoïque</t>
+  </si>
+  <si>
+    <t>(B) : L'acide 3-methyl butanoïque</t>
+  </si>
+  <si>
+    <t>(C) : L'acide pentatonique</t>
+  </si>
+  <si>
+    <t>(D) : L'acide propanoïque</t>
+  </si>
+  <si>
+    <t>(E) : L'acide 2-methyl butanoïque</t>
+  </si>
+  <si>
+    <t>(A) : $K=3,85$</t>
+  </si>
+  <si>
+    <t>(B) : $K=4,5$</t>
+  </si>
+  <si>
+    <t>(C} : $K=4,2$</t>
+  </si>
+  <si>
+    <t>(D) : $K=3,8$</t>
+  </si>
+  <si>
+    <t>(E} : $K=4$</t>
+  </si>
+  <si>
+    <t>(A) : $65 \%$</t>
+  </si>
+  <si>
+    <t>(B) : $69 \%$</t>
+  </si>
+  <si>
+    <t>(C) : $67 \%$</t>
+  </si>
+  <si>
+    <t>(D) : $64 \%$</t>
+  </si>
+  <si>
+    <t>(E) : $68 \%$</t>
+  </si>
+  <si>
+    <t>(A) : &lt;smiles&gt;CCCC(=O)OC(=O)CCC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(B) : &lt;smiles&gt;CCCOC(=O)CCC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(C) : &lt;smiles&gt;CC(C)CC(=O)OC(=O)CC(C)C&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(D) : &lt;smiles&gt;CCC(C)C(=O)OC(=O)C(C)CC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(E) : &lt;smiles&gt;CCCCCOCCCC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>\section*{Méthode de contrôle de l'évolution d'un système chimique : ( $\mathbf{1 0}$ points)} On réalise un mélange équimolaire contenant $n_{0}=0,12 \mathrm{~mol}$ d'un acide ( $A$ ) et $n_{0}=0,12 \mathrm{~mol}$ d'un alcool (B). On ajoute au mélange quelques gouttes d'acide sulfurique concentré et quelques grains de pierre ponce. Le dispositif expérimental utilisée est représenté sur la figure cicontre. À la fin de la transformation on obtient la masse $m(E)=12,64 g$ d'un ester ( $E$ ). \begin{table} \captionsetup{labelformat=empty} \caption{Données : $79 \div 39=2$} \begin{tabular}{|l|l|l|} \hline Composé organique &amp; Formule semi-développée &amp; Masse molaire \\ \hline L'alcool (B) &amp; &lt;smiles&gt;CC(C)CCCO&lt;/smiles&gt; &amp; \\ \hline L'ester (E) &amp; &lt;smiles&gt;CCCC(=O)OCCC(C)C&lt;/smiles&gt; &amp; $M(E)=158 \mathrm{~g} . \mathrm{mol}^{-1}$ \\ \hline \end{tabular} \end{table} \begin{figure} \captionsetup{labelformat=empty} \caption{Données : $79 \div 39=2$} \includegraphics[alt={},max width=\textwidth]</t>
+  </si>
+  <si>
+    <t>CH22F2</t>
   </si>
 </sst>
 </file>
@@ -13229,7 +14555,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -13252,11 +14578,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -13367,7 +14713,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -13379,9 +14724,6 @@
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -13395,6 +14737,37 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13700,7 +15073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -13717,13 +15090,13 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -13738,2799 +15111,5373 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="41" t="s">
-        <v>109</v>
+      <c r="K2" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="L2" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="L3" s="43"/>
+      <c r="F4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="41"/>
+        <v>170</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="L5" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="5">
-        <v>3</v>
+      <c r="H7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="63" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L7" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="126" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>37</v>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="6" t="s">
-        <v>38</v>
+        <v>170</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>56</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L9" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>53</v>
+        <v>170</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L10" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>60</v>
+        <v>170</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L11" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>65</v>
+        <v>170</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="126" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L15" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="L13" s="5">
-        <v>1</v>
+      <c r="F17" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="15">
+        <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L15" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="7" t="s">
+    <row r="18" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L16" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="283.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>109</v>
       </c>
       <c r="L18" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="E19" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="F19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="G19" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>113</v>
+      <c r="H19" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L19" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>177</v>
+        <v>170</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>159</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="D20" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="E20" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="F20" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="G20" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="H20" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="22" t="s">
         <v>116</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L20" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C21" s="18"/>
-      <c r="D21" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="13" t="s">
+      <c r="D21" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="E21" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="G21" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>122</v>
+      <c r="H21" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>125</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L21" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="21" t="s">
+      <c r="E22" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="F22" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>122</v>
+      <c r="G22" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>129</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L22" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="E23" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="F23" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="G23" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="I23" s="12" t="s">
         <v>132</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L23" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C24" s="18"/>
-      <c r="D24" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="F24" s="20" t="s">
+      <c r="D24" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="E24" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="F24" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="I24" s="20" t="s">
-        <v>138</v>
+      <c r="G24" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>137</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L24" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F25" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="25">
+        <v>4</v>
+      </c>
+      <c r="E25" s="25">
+        <v>8</v>
+      </c>
+      <c r="F25" s="30">
+        <v>12</v>
+      </c>
+      <c r="G25" s="31">
+        <v>24</v>
+      </c>
+      <c r="H25" s="25">
+        <v>36</v>
+      </c>
+      <c r="I25" s="25">
+        <v>4</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L25" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="32"/>
+      <c r="D26" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="E26" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="F26" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="I25" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L25" s="15">
+      <c r="G26" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L26" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="F26" s="20" t="s">
+    <row r="27" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="35"/>
+      <c r="D27" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="E27" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="F27" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="I26" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L26" s="15">
+      <c r="G27" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37">
+        <v>0.08</v>
+      </c>
+      <c r="E28" s="37">
+        <v>0.16</v>
+      </c>
+      <c r="F28" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="G28" s="37">
+        <v>0.64</v>
+      </c>
+      <c r="H28" s="37">
+        <v>0.96</v>
+      </c>
+      <c r="I28" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L28" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L27" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L28" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="70.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="I29" s="27" t="s">
-        <v>160</v>
+    <row r="29" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>116</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L29" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="69.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="25">
-        <v>4</v>
-      </c>
-      <c r="E30" s="25">
-        <v>8</v>
-      </c>
-      <c r="F30" s="30">
-        <v>12</v>
-      </c>
-      <c r="G30" s="31">
-        <v>24</v>
-      </c>
-      <c r="H30" s="25">
-        <v>36</v>
-      </c>
-      <c r="I30" s="25">
-        <v>4</v>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" s="54"/>
+      <c r="C30" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L30" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="F31" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="G31" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="H31" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>164</v>
+    <row r="31" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>175</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="L31" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E32" s="25" t="s">
+    <row r="32" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="F32" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="H32" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="25" t="s">
-        <v>169</v>
+      <c r="B32" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="G32" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="H32" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="I32" s="43" t="s">
+        <v>202</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L32" s="36">
+        <v>78</v>
+      </c>
+      <c r="L32" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="37">
-        <v>0.08</v>
-      </c>
-      <c r="E33" s="37">
-        <v>0.16</v>
-      </c>
-      <c r="F33" s="37">
-        <v>0.32</v>
-      </c>
-      <c r="G33" s="37">
-        <v>0.64</v>
-      </c>
-      <c r="H33" s="37">
-        <v>0.96</v>
-      </c>
-      <c r="I33" s="37">
-        <v>0.32</v>
+    <row r="33" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="G33" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="H33" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>220</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="L33" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>139</v>
+      <c r="A34" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="H34" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="I34" s="43" t="s">
+        <v>267</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="L34" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>204</v>
+    <row r="35" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="G35" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H35" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="I35" s="43" t="s">
+        <v>226</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="L35" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="44" t="s">
+    <row r="36" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A36" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="H36" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="I36" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="J36" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L36" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A37" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="G37" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="I37" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="B36" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="22" t="s">
+      <c r="J37" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L37" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A38" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="G38" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="H38" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="I38" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="J38" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L38" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A39" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="H39" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="I39" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="J39" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L39" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A40" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="F36" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L36" s="15">
+      <c r="C40" s="3"/>
+      <c r="D40" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="H40" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="I40" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="J40" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L40" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B37" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="E37" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="F37" s="45" t="s">
-        <v>227</v>
-      </c>
-      <c r="G37" s="45" t="s">
-        <v>228</v>
-      </c>
-      <c r="H37" s="45" t="s">
-        <v>229</v>
-      </c>
-      <c r="I37" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L37" s="15">
+    <row r="41" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="H41" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="I41" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="J41" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L41" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B38" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="E38" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="F38" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="H38" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="I38" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L38" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B39" s="45" t="s">
-        <v>223</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="45" t="s">
-        <v>289</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>288</v>
-      </c>
-      <c r="F39" s="45" t="s">
+    <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="F42" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G42" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="H39" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="I39" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L39" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B40" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="45" t="s">
+      <c r="H42" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="E40" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="F40" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="G40" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="H40" s="45" t="s">
-        <v>232</v>
-      </c>
-      <c r="I40" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L40" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A41" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B41" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="E41" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="G41" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="H41" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="I41" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="J41" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L41" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A42" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B42" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="E42" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="F42" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="H42" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="I42" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="J42" s="42" t="s">
-        <v>25</v>
+      <c r="I42" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="J42" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L42" s="46">
+        <v>78</v>
+      </c>
+      <c r="L42" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A43" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" s="45" t="s">
-        <v>219</v>
+      <c r="A43" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>248</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="45" t="s">
+      <c r="D43" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="H43" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="I43" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="J43" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L43" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A44" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="G44" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="H44" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="I44" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="J44" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L44" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A45" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="43" t="s">
         <v>250</v>
       </c>
-      <c r="E43" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="F43" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="G43" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="H43" s="45" t="s">
+      <c r="E45" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="F45" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="G45" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="H45" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="I43" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="J43" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L43" s="46">
+      <c r="I45" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="J45" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L45" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A44" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B44" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="E44" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="F44" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="G44" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="H44" s="45" t="s">
-        <v>260</v>
-      </c>
-      <c r="I44" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="J44" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L44" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A45" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B45" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="E45" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="F45" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="G45" s="45" t="s">
-        <v>285</v>
-      </c>
-      <c r="H45" s="45" t="s">
-        <v>286</v>
-      </c>
-      <c r="I45" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="J45" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L45" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B46" s="45" t="s">
-        <v>233</v>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B46" s="55" t="s">
+        <v>270</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="E46" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="F46" s="45" t="s">
-        <v>267</v>
-      </c>
-      <c r="G46" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="H46" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="I46" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="J46" s="42" t="s">
-        <v>25</v>
+      <c r="D46" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="F46" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="G46" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="H46" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="I46" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="J46" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L46" s="46">
+        <v>80</v>
+      </c>
+      <c r="L46" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B47" s="45" t="s">
-        <v>234</v>
+      <c r="A47" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" s="55" t="s">
+        <v>271</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="E47" s="45" t="s">
-        <v>237</v>
-      </c>
-      <c r="F47" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="G47" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="H47" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="I47" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="J47" s="42" t="s">
-        <v>25</v>
+      <c r="D47" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="F47" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="G47" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="H47" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I47" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="J47" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L47" s="46">
+        <v>80</v>
+      </c>
+      <c r="L47" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A48" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B48" s="45" t="s">
-        <v>271</v>
+    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B48" s="55" t="s">
+        <v>272</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E48" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="F48" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="G48" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="H48" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="I48" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="J48" s="42" t="s">
-        <v>25</v>
+      <c r="D48" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="F48" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="G48" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I48" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="J48" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L48" s="46">
+        <v>80</v>
+      </c>
+      <c r="L48" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="A49" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B49" s="45" t="s">
-        <v>235</v>
+    <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" s="55" t="s">
+        <v>273</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="45" t="s">
-        <v>279</v>
-      </c>
-      <c r="E49" s="45" t="s">
+      <c r="D49" s="43" t="s">
         <v>291</v>
       </c>
-      <c r="F49" s="45" t="s">
-        <v>278</v>
-      </c>
-      <c r="G49" s="45" t="s">
+      <c r="E49" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="H49" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="I49" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="J49" s="42" t="s">
-        <v>25</v>
+      <c r="F49" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="G49" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="H49" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I49" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="J49" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L49" s="46">
+        <v>80</v>
+      </c>
+      <c r="L49" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A50" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B50" s="45" t="s">
+    <row r="50" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" s="55" t="s">
+        <v>341</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="F50" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="G50" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="H50" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I50" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="J50" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L50" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A51" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" s="55" t="s">
+        <v>340</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="G51" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="H51" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I51" s="43" t="s">
+        <v>299</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L51" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="55" t="s">
+        <v>274</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="43" t="s">
+        <v>303</v>
+      </c>
+      <c r="G52" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="H52" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I52" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="J52" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L52" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" s="55" t="s">
+        <v>339</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="43" t="s">
+        <v>335</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>336</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="G53" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="H53" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I53" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="J53" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L53" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A54" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="E54" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="F54" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G54" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="H54" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="I54" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="J54" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L54" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="E55" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="F55" s="43" t="s">
+        <v>312</v>
+      </c>
+      <c r="G55" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="H55" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I55" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="J55" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L55" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A56" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="43" t="s">
+        <v>314</v>
+      </c>
+      <c r="E56" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="F56" s="43" t="s">
+        <v>316</v>
+      </c>
+      <c r="G56" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="H56" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I56" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="J56" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L56" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A57" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" s="55" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="G57" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="H57" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I57" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="J57" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L57" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="E58" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="F58" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="G58" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="H58" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I58" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="J58" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L58" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="55" t="s">
         <v>277</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="E50" s="45" t="s">
-        <v>274</v>
-      </c>
-      <c r="F50" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="G50" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="H50" s="45" t="s">
-        <v>240</v>
-      </c>
-      <c r="I50" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="J50" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K50" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L50" s="46">
+      <c r="C59" s="3"/>
+      <c r="D59" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>324</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>325</v>
+      </c>
+      <c r="G59" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="H59" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I59" s="43" t="s">
+        <v>325</v>
+      </c>
+      <c r="J59" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L59" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B51" s="45" t="s">
-        <v>293</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="45" t="s">
-        <v>301</v>
-      </c>
-      <c r="E51" s="45" t="s">
+    <row r="60" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>429</v>
+      </c>
+      <c r="C60" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="J60" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="K60" s="40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="D61" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="E61" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="F61" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="G61" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="H61" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="I61" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="J61" s="41"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="B62" s="56" t="s">
+        <v>343</v>
+      </c>
+      <c r="D62" s="45" t="s">
         <v>368</v>
       </c>
-      <c r="F51" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="G51" s="45" t="s">
-        <v>303</v>
-      </c>
-      <c r="H51" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="I51" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J51" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K51" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L51" s="46">
+      <c r="E62" s="45" t="s">
+        <v>369</v>
+      </c>
+      <c r="F62" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="G62" s="45" t="s">
+        <v>371</v>
+      </c>
+      <c r="H62" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="I62" s="45" t="s">
+        <v>369</v>
+      </c>
+      <c r="J62" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L62" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B52" s="45" t="s">
-        <v>294</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="E52" s="45" t="s">
-        <v>306</v>
-      </c>
-      <c r="F52" s="45" t="s">
-        <v>307</v>
-      </c>
-      <c r="G52" s="45" t="s">
-        <v>308</v>
-      </c>
-      <c r="H52" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I52" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="J52" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L52" s="46">
+    <row r="63" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A63" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B63" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="D63" s="45" t="s">
+        <v>373</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>374</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>375</v>
+      </c>
+      <c r="G63" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="I63" s="45" t="s">
+        <v>374</v>
+      </c>
+      <c r="J63" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L63" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B53" s="45" t="s">
-        <v>295</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="E53" s="45" t="s">
-        <v>310</v>
-      </c>
-      <c r="F53" s="45" t="s">
-        <v>311</v>
-      </c>
-      <c r="G53" s="45" t="s">
-        <v>312</v>
-      </c>
-      <c r="H53" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I53" s="45" t="s">
-        <v>312</v>
-      </c>
-      <c r="J53" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L53" s="46">
+    <row r="64" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A64" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B64" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="D64" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>380</v>
+      </c>
+      <c r="G64" s="45" t="s">
+        <v>381</v>
+      </c>
+      <c r="H64" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="I64" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="J64" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L64" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B54" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="E54" s="45" t="s">
-        <v>315</v>
-      </c>
-      <c r="F54" s="45" t="s">
-        <v>316</v>
-      </c>
-      <c r="G54" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="H54" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I54" s="45" t="s">
-        <v>315</v>
-      </c>
-      <c r="J54" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K54" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L54" s="46">
+    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B65" s="56" t="s">
+        <v>347</v>
+      </c>
+      <c r="D65" s="45" t="s">
+        <v>382</v>
+      </c>
+      <c r="E65" s="45" t="s">
+        <v>420</v>
+      </c>
+      <c r="F65" s="45" t="s">
+        <v>421</v>
+      </c>
+      <c r="G65" s="45" t="s">
+        <v>383</v>
+      </c>
+      <c r="H65" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="I65" s="45" t="s">
+        <v>380</v>
+      </c>
+      <c r="J65" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L65" s="44">
         <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A55" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B55" s="45" t="s">
-        <v>367</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="E55" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="F55" s="45" t="s">
-        <v>320</v>
-      </c>
-      <c r="G55" s="45" t="s">
-        <v>308</v>
-      </c>
-      <c r="H55" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I55" s="45" t="s">
-        <v>308</v>
-      </c>
-      <c r="J55" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K55" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L55" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A56" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B56" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="45" t="s">
-        <v>321</v>
-      </c>
-      <c r="E56" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="F56" s="45" t="s">
-        <v>323</v>
-      </c>
-      <c r="G56" s="45" t="s">
-        <v>324</v>
-      </c>
-      <c r="H56" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I56" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="J56" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K56" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L56" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B57" s="45" t="s">
-        <v>297</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="E57" s="45" t="s">
-        <v>325</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="G57" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="H57" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I57" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="J57" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K57" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L57" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="52.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B58" s="45" t="s">
-        <v>365</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="45" t="s">
-        <v>361</v>
-      </c>
-      <c r="E58" s="45" t="s">
-        <v>362</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>363</v>
-      </c>
-      <c r="G58" s="45" t="s">
-        <v>364</v>
-      </c>
-      <c r="H58" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I58" s="45" t="s">
-        <v>327</v>
-      </c>
-      <c r="J58" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K58" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L58" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="120" x14ac:dyDescent="0.25">
-      <c r="A59" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B59" s="45" t="s">
-        <v>358</v>
-      </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="45" t="s">
-        <v>328</v>
-      </c>
-      <c r="E59" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="F59" s="45" t="s">
-        <v>330</v>
-      </c>
-      <c r="G59" s="45" t="s">
-        <v>331</v>
-      </c>
-      <c r="H59" s="45" t="s">
-        <v>332</v>
-      </c>
-      <c r="I59" s="45" t="s">
-        <v>331</v>
-      </c>
-      <c r="J59" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K59" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L59" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B60" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="45" t="s">
-        <v>333</v>
-      </c>
-      <c r="E60" s="45" t="s">
-        <v>334</v>
-      </c>
-      <c r="F60" s="45" t="s">
-        <v>335</v>
-      </c>
-      <c r="G60" s="45" t="s">
-        <v>336</v>
-      </c>
-      <c r="H60" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I60" s="45" t="s">
-        <v>334</v>
-      </c>
-      <c r="J60" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K60" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L60" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="120" x14ac:dyDescent="0.25">
-      <c r="A61" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B61" s="45" t="s">
-        <v>359</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="E61" s="45" t="s">
-        <v>338</v>
-      </c>
-      <c r="F61" s="45" t="s">
-        <v>339</v>
-      </c>
-      <c r="G61" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="H61" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I61" s="45" t="s">
-        <v>338</v>
-      </c>
-      <c r="J61" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K61" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L61" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A62" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B62" s="45" t="s">
-        <v>360</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="E62" s="45" t="s">
-        <v>341</v>
-      </c>
-      <c r="F62" s="45" t="s">
-        <v>320</v>
-      </c>
-      <c r="G62" s="45" t="s">
-        <v>312</v>
-      </c>
-      <c r="H62" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I62" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K62" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L62" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B63" s="45" t="s">
-        <v>299</v>
-      </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="45" t="s">
-        <v>342</v>
-      </c>
-      <c r="E63" s="45" t="s">
-        <v>343</v>
-      </c>
-      <c r="F63" s="45" t="s">
-        <v>344</v>
-      </c>
-      <c r="G63" s="45" t="s">
-        <v>345</v>
-      </c>
-      <c r="H63" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I63" s="45" t="s">
-        <v>343</v>
-      </c>
-      <c r="J63" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K63" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L63" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" s="45" t="s">
-        <v>300</v>
-      </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="45" t="s">
-        <v>346</v>
-      </c>
-      <c r="E64" s="45" t="s">
-        <v>347</v>
-      </c>
-      <c r="F64" s="45" t="s">
-        <v>348</v>
-      </c>
-      <c r="G64" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="H64" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I64" s="45" t="s">
-        <v>348</v>
-      </c>
-      <c r="J64" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K64" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L64" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B65" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C65" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="J65" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="K65" s="41" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B66" s="47" t="s">
+      <c r="A66" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B66" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="D66" s="45" t="s">
+        <v>385</v>
+      </c>
+      <c r="E66" s="45" t="s">
+        <v>350</v>
+      </c>
+      <c r="F66" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="D66" s="47" t="s">
+      <c r="G66" s="45" t="s">
         <v>352</v>
       </c>
-      <c r="E66" s="47" t="s">
+      <c r="H66" s="45" t="s">
         <v>353</v>
       </c>
-      <c r="F66" s="48" t="s">
+      <c r="I66" s="45" t="s">
+        <v>384</v>
+      </c>
+      <c r="J66" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L66" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A67" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" s="56" t="s">
         <v>354</v>
       </c>
-      <c r="G66" s="48" t="s">
+      <c r="D67" s="45" t="s">
+        <v>386</v>
+      </c>
+      <c r="E67" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="F67" s="45" t="s">
+        <v>388</v>
+      </c>
+      <c r="G67" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="H67" s="45" t="s">
         <v>355</v>
       </c>
-      <c r="H66" s="48" t="s">
+      <c r="I67" s="45" t="s">
+        <v>352</v>
+      </c>
+      <c r="J67" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L67" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A68" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" s="56" t="s">
         <v>356</v>
       </c>
-      <c r="I66" s="47" t="s">
-        <v>353</v>
-      </c>
-      <c r="J66" s="42"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="46">
+      <c r="D68" s="45" t="s">
+        <v>390</v>
+      </c>
+      <c r="E68" s="45" t="s">
+        <v>391</v>
+      </c>
+      <c r="F68" s="45" t="s">
+        <v>392</v>
+      </c>
+      <c r="G68" s="45" t="s">
+        <v>393</v>
+      </c>
+      <c r="H68" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="I68" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="J68" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L68" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="B67" s="47" t="s">
-        <v>369</v>
-      </c>
-      <c r="D67" s="47" t="s">
+    <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="D69" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="E67" s="47" t="s">
+      <c r="E69" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="F67" s="47" t="s">
+      <c r="F69" s="45" t="s">
         <v>396</v>
       </c>
-      <c r="G67" s="47" t="s">
+      <c r="G69" s="45" t="s">
         <v>397</v>
       </c>
-      <c r="H67" s="47" t="s">
+      <c r="H69" s="45" t="s">
         <v>398</v>
       </c>
-      <c r="I67" s="47" t="s">
-        <v>395</v>
-      </c>
-      <c r="J67" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K67" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L67" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="120" x14ac:dyDescent="0.25">
-      <c r="A68" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B68" s="47" t="s">
-        <v>370</v>
-      </c>
-      <c r="D68" s="47" t="s">
-        <v>399</v>
-      </c>
-      <c r="E68" s="47" t="s">
-        <v>400</v>
-      </c>
-      <c r="F68" s="47" t="s">
-        <v>401</v>
-      </c>
-      <c r="G68" s="47" t="s">
-        <v>402</v>
-      </c>
-      <c r="H68" s="47" t="s">
-        <v>371</v>
-      </c>
-      <c r="I68" s="47" t="s">
-        <v>400</v>
-      </c>
-      <c r="J68" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K68" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L68" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A69" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B69" s="47" t="s">
-        <v>403</v>
-      </c>
-      <c r="D69" s="47" t="s">
-        <v>404</v>
-      </c>
-      <c r="E69" s="47" t="s">
-        <v>405</v>
-      </c>
-      <c r="F69" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="G69" s="47" t="s">
-        <v>407</v>
-      </c>
-      <c r="H69" s="47" t="s">
-        <v>372</v>
-      </c>
-      <c r="I69" s="47" t="s">
-        <v>371</v>
-      </c>
-      <c r="J69" s="42" t="s">
-        <v>25</v>
+      <c r="I69" s="45" t="s">
+        <v>392</v>
+      </c>
+      <c r="J69" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L69" s="46">
+        <v>79</v>
+      </c>
+      <c r="L69" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A70" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B70" s="47" t="s">
-        <v>373</v>
-      </c>
-      <c r="D70" s="47" t="s">
+      <c r="A70" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" s="56" t="s">
+        <v>359</v>
+      </c>
+      <c r="D70" s="45" t="s">
+        <v>399</v>
+      </c>
+      <c r="E70" s="45" t="s">
+        <v>422</v>
+      </c>
+      <c r="F70" s="45" t="s">
+        <v>423</v>
+      </c>
+      <c r="G70" s="45" t="s">
+        <v>400</v>
+      </c>
+      <c r="H70" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="I70" s="45" t="s">
+        <v>398</v>
+      </c>
+      <c r="J70" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L70" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B71" s="56" t="s">
+        <v>360</v>
+      </c>
+      <c r="D71" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="E71" s="45" t="s">
+        <v>403</v>
+      </c>
+      <c r="F71" s="45" t="s">
+        <v>404</v>
+      </c>
+      <c r="G71" s="45" t="s">
+        <v>405</v>
+      </c>
+      <c r="H71" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="I71" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="J71" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L71" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>362</v>
+      </c>
+      <c r="D72" s="45" t="s">
+        <v>406</v>
+      </c>
+      <c r="E72" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F72" s="45" t="s">
         <v>408</v>
       </c>
-      <c r="E70" s="47" t="s">
-        <v>446</v>
-      </c>
-      <c r="F70" s="47" t="s">
-        <v>447</v>
-      </c>
-      <c r="G70" s="47" t="s">
+      <c r="G72" s="45" t="s">
         <v>409</v>
       </c>
-      <c r="H70" s="47" t="s">
-        <v>374</v>
-      </c>
-      <c r="I70" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="J70" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K70" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L70" s="46">
+      <c r="H72" s="45" t="s">
+        <v>410</v>
+      </c>
+      <c r="I72" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="J72" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L72" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A71" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B71" s="47" t="s">
-        <v>375</v>
-      </c>
-      <c r="D71" s="47" t="s">
+    <row r="73" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A73" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>363</v>
+      </c>
+      <c r="D73" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="E71" s="47" t="s">
-        <v>376</v>
-      </c>
-      <c r="F71" s="47" t="s">
-        <v>377</v>
-      </c>
-      <c r="G71" s="47" t="s">
-        <v>378</v>
-      </c>
-      <c r="H71" s="47" t="s">
-        <v>379</v>
-      </c>
-      <c r="I71" s="47" t="s">
-        <v>410</v>
-      </c>
-      <c r="J71" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L71" s="46">
+      <c r="E73" s="45" t="s">
+        <v>412</v>
+      </c>
+      <c r="F73" s="45" t="s">
+        <v>413</v>
+      </c>
+      <c r="G73" s="45" t="s">
+        <v>414</v>
+      </c>
+      <c r="H73" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="I73" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="J73" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L73" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A72" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B72" s="47" t="s">
-        <v>380</v>
-      </c>
-      <c r="D72" s="47" t="s">
-        <v>412</v>
-      </c>
-      <c r="E72" s="47" t="s">
+    <row r="74" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A74" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>365</v>
+      </c>
+      <c r="D74" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="E74" s="45" t="s">
+        <v>415</v>
+      </c>
+      <c r="F74" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="G74" s="45" t="s">
+        <v>417</v>
+      </c>
+      <c r="H74" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="I74" s="45" t="s">
         <v>413</v>
       </c>
-      <c r="F72" s="47" t="s">
-        <v>414</v>
-      </c>
-      <c r="G72" s="47" t="s">
-        <v>415</v>
-      </c>
-      <c r="H72" s="47" t="s">
-        <v>381</v>
-      </c>
-      <c r="I72" s="47" t="s">
-        <v>378</v>
-      </c>
-      <c r="J72" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K72" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L72" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A73" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B73" s="47" t="s">
-        <v>382</v>
-      </c>
-      <c r="D73" s="47" t="s">
-        <v>416</v>
-      </c>
-      <c r="E73" s="47" t="s">
-        <v>417</v>
-      </c>
-      <c r="F73" s="47" t="s">
-        <v>418</v>
-      </c>
-      <c r="G73" s="47" t="s">
-        <v>419</v>
-      </c>
-      <c r="H73" s="47" t="s">
-        <v>383</v>
-      </c>
-      <c r="I73" s="47" t="s">
-        <v>413</v>
-      </c>
-      <c r="J73" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K73" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L73" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A74" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B74" s="47" t="s">
-        <v>384</v>
-      </c>
-      <c r="D74" s="47" t="s">
-        <v>420</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>421</v>
-      </c>
-      <c r="F74" s="47" t="s">
-        <v>422</v>
-      </c>
-      <c r="G74" s="47" t="s">
-        <v>423</v>
-      </c>
-      <c r="H74" s="47" t="s">
-        <v>424</v>
-      </c>
-      <c r="I74" s="47" t="s">
-        <v>418</v>
-      </c>
-      <c r="J74" s="42" t="s">
-        <v>25</v>
+      <c r="J74" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K74" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L74" s="46">
+        <v>79</v>
+      </c>
+      <c r="L74" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A75" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B75" s="47" t="s">
-        <v>385</v>
-      </c>
-      <c r="D75" s="47" t="s">
+      <c r="A75" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>427</v>
+      </c>
+      <c r="D75" s="45" t="s">
+        <v>418</v>
+      </c>
+      <c r="E75" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="F75" s="45" t="s">
+        <v>419</v>
+      </c>
+      <c r="G75" s="45" t="s">
+        <v>424</v>
+      </c>
+      <c r="H75" s="45" t="s">
         <v>425</v>
       </c>
-      <c r="E75" s="47" t="s">
+      <c r="I75" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="J75" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L75" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="D76" t="s">
+        <v>436</v>
+      </c>
+      <c r="E76" t="s">
+        <v>437</v>
+      </c>
+      <c r="F76" t="s">
+        <v>438</v>
+      </c>
+      <c r="G76" t="s">
+        <v>439</v>
+      </c>
+      <c r="H76" t="s">
+        <v>440</v>
+      </c>
+      <c r="I76" t="s">
+        <v>438</v>
+      </c>
+      <c r="J76" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L76" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A77" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="56" t="s">
+        <v>431</v>
+      </c>
+      <c r="D77" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" t="s">
+        <v>442</v>
+      </c>
+      <c r="F77" t="s">
+        <v>443</v>
+      </c>
+      <c r="G77" t="s">
+        <v>444</v>
+      </c>
+      <c r="H77" t="s">
+        <v>445</v>
+      </c>
+      <c r="I77" t="s">
+        <v>441</v>
+      </c>
+      <c r="J77" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L77" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" s="56" t="s">
+        <v>432</v>
+      </c>
+      <c r="D78" t="s">
+        <v>446</v>
+      </c>
+      <c r="E78" t="s">
+        <v>447</v>
+      </c>
+      <c r="F78" t="s">
         <v>448</v>
       </c>
-      <c r="F75" s="47" t="s">
+      <c r="G78" t="s">
         <v>449</v>
       </c>
-      <c r="G75" s="47" t="s">
-        <v>426</v>
-      </c>
-      <c r="H75" s="47" t="s">
-        <v>427</v>
-      </c>
-      <c r="I75" s="47" t="s">
-        <v>424</v>
-      </c>
-      <c r="J75" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K75" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L75" s="46">
+      <c r="H78" t="s">
+        <v>450</v>
+      </c>
+      <c r="I78" t="s">
+        <v>449</v>
+      </c>
+      <c r="J78" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L78" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A76" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B76" s="47" t="s">
-        <v>386</v>
-      </c>
-      <c r="D76" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>429</v>
-      </c>
-      <c r="F76" s="47" t="s">
-        <v>430</v>
-      </c>
-      <c r="G76" s="47" t="s">
-        <v>431</v>
-      </c>
-      <c r="H76" s="47" t="s">
-        <v>387</v>
-      </c>
-      <c r="I76" s="47" t="s">
-        <v>427</v>
-      </c>
-      <c r="J76" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K76" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L76" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A77" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B77" s="47" t="s">
-        <v>388</v>
-      </c>
-      <c r="D77" s="47" t="s">
-        <v>432</v>
-      </c>
-      <c r="E77" s="47" t="s">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B79" s="56" t="s">
         <v>433</v>
       </c>
-      <c r="F77" s="47" t="s">
-        <v>434</v>
-      </c>
-      <c r="G77" s="47" t="s">
-        <v>435</v>
-      </c>
-      <c r="H77" s="47" t="s">
-        <v>436</v>
-      </c>
-      <c r="I77" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="J77" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K77" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L77" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A78" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B78" s="47" t="s">
-        <v>389</v>
-      </c>
-      <c r="D78" s="47" t="s">
-        <v>437</v>
-      </c>
-      <c r="E78" s="47" t="s">
-        <v>438</v>
-      </c>
-      <c r="F78" s="47" t="s">
-        <v>439</v>
-      </c>
-      <c r="G78" s="47" t="s">
+      <c r="D79" t="s">
+        <v>451</v>
+      </c>
+      <c r="E79" t="s">
+        <v>452</v>
+      </c>
+      <c r="F79" t="s">
+        <v>453</v>
+      </c>
+      <c r="G79" t="s">
+        <v>454</v>
+      </c>
+      <c r="H79" t="s">
         <v>440</v>
       </c>
-      <c r="H78" s="47" t="s">
-        <v>390</v>
-      </c>
-      <c r="I78" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="J78" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K78" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L78" s="46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A79" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B79" s="47" t="s">
-        <v>391</v>
-      </c>
-      <c r="D79" s="47" t="s">
-        <v>392</v>
-      </c>
-      <c r="E79" s="47" t="s">
-        <v>441</v>
-      </c>
-      <c r="F79" s="47" t="s">
-        <v>442</v>
-      </c>
-      <c r="G79" s="47" t="s">
-        <v>443</v>
-      </c>
-      <c r="H79" s="47" t="s">
-        <v>393</v>
-      </c>
-      <c r="I79" s="47" t="s">
-        <v>439</v>
-      </c>
-      <c r="J79" s="42" t="s">
-        <v>25</v>
+      <c r="I79" t="s">
+        <v>453</v>
+      </c>
+      <c r="J79" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="K79" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L79" s="46">
+        <v>464</v>
+      </c>
+      <c r="L79" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A80" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B80" s="47" t="s">
-        <v>453</v>
-      </c>
-      <c r="D80" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>454</v>
-      </c>
-      <c r="F80" s="47" t="s">
+      <c r="A80" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" s="56" t="s">
+        <v>434</v>
+      </c>
+      <c r="D80" t="s">
+        <v>455</v>
+      </c>
+      <c r="E80" t="s">
+        <v>456</v>
+      </c>
+      <c r="F80" t="s">
+        <v>457</v>
+      </c>
+      <c r="G80" t="s">
+        <v>458</v>
+      </c>
+      <c r="H80" t="s">
+        <v>459</v>
+      </c>
+      <c r="I80" t="s">
+        <v>456</v>
+      </c>
+      <c r="J80" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L80" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A81" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="56" t="s">
+        <v>435</v>
+      </c>
+      <c r="D81" t="s">
+        <v>460</v>
+      </c>
+      <c r="E81" t="s">
+        <v>461</v>
+      </c>
+      <c r="F81" t="s">
+        <v>462</v>
+      </c>
+      <c r="G81" t="s">
+        <v>463</v>
+      </c>
+      <c r="H81" t="s">
         <v>445</v>
       </c>
-      <c r="G80" s="47" t="s">
-        <v>450</v>
-      </c>
-      <c r="H80" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="I80" s="47" t="s">
-        <v>452</v>
-      </c>
-      <c r="J80" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K80" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L80" s="46">
+      <c r="I81" t="s">
+        <v>460</v>
+      </c>
+      <c r="J81" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L81" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A82" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" s="56" t="s">
+        <v>465</v>
+      </c>
+      <c r="D82" t="s">
+        <v>479</v>
+      </c>
+      <c r="E82" t="s">
+        <v>480</v>
+      </c>
+      <c r="F82" t="s">
+        <v>481</v>
+      </c>
+      <c r="G82" t="s">
+        <v>482</v>
+      </c>
+      <c r="H82" t="s">
+        <v>483</v>
+      </c>
+      <c r="I82" t="s">
+        <v>482</v>
+      </c>
+      <c r="J82" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L82" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A83" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>466</v>
+      </c>
+      <c r="D83" t="s">
+        <v>484</v>
+      </c>
+      <c r="E83" t="s">
+        <v>485</v>
+      </c>
+      <c r="F83" t="s">
+        <v>486</v>
+      </c>
+      <c r="G83" t="s">
+        <v>487</v>
+      </c>
+      <c r="H83" t="s">
+        <v>488</v>
+      </c>
+      <c r="I83" t="s">
+        <v>485</v>
+      </c>
+      <c r="J83" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L83" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A84" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>467</v>
+      </c>
+      <c r="D84" t="s">
+        <v>489</v>
+      </c>
+      <c r="E84" t="s">
+        <v>490</v>
+      </c>
+      <c r="F84" t="s">
+        <v>491</v>
+      </c>
+      <c r="G84" t="s">
+        <v>492</v>
+      </c>
+      <c r="H84" t="s">
+        <v>440</v>
+      </c>
+      <c r="I84" t="s">
+        <v>492</v>
+      </c>
+      <c r="J84" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L84" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="56" t="s">
+        <v>468</v>
+      </c>
+      <c r="D85" t="s">
+        <v>489</v>
+      </c>
+      <c r="E85" t="s">
+        <v>493</v>
+      </c>
+      <c r="F85" t="s">
+        <v>494</v>
+      </c>
+      <c r="G85" t="s">
+        <v>495</v>
+      </c>
+      <c r="H85" t="s">
+        <v>496</v>
+      </c>
+      <c r="I85" t="s">
+        <v>493</v>
+      </c>
+      <c r="J85" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L85" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A86" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" s="56" t="s">
+        <v>469</v>
+      </c>
+      <c r="D86" t="s">
+        <v>497</v>
+      </c>
+      <c r="E86" t="s">
+        <v>498</v>
+      </c>
+      <c r="F86" t="s">
+        <v>499</v>
+      </c>
+      <c r="G86" t="s">
+        <v>500</v>
+      </c>
+      <c r="H86" s="45" t="s">
+        <v>501</v>
+      </c>
+      <c r="I86" t="s">
+        <v>497</v>
+      </c>
+      <c r="J86" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L86" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A87" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="56" t="s">
+        <v>470</v>
+      </c>
+      <c r="D87" t="s">
+        <v>502</v>
+      </c>
+      <c r="E87" t="s">
+        <v>503</v>
+      </c>
+      <c r="F87" t="s">
+        <v>504</v>
+      </c>
+      <c r="G87" t="s">
+        <v>505</v>
+      </c>
+      <c r="H87" t="s">
+        <v>440</v>
+      </c>
+      <c r="I87" t="s">
+        <v>505</v>
+      </c>
+      <c r="J87" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K87" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L87" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="195" x14ac:dyDescent="0.25">
+      <c r="A88" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B88" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="D88" t="s">
+        <v>506</v>
+      </c>
+      <c r="E88" t="s">
+        <v>507</v>
+      </c>
+      <c r="F88" t="s">
+        <v>508</v>
+      </c>
+      <c r="G88" t="s">
+        <v>509</v>
+      </c>
+      <c r="H88" t="s">
+        <v>440</v>
+      </c>
+      <c r="I88" t="s">
+        <v>507</v>
+      </c>
+      <c r="J88" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K88" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L88" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A89" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B89" s="56" t="s">
+        <v>472</v>
+      </c>
+      <c r="D89" t="s">
+        <v>510</v>
+      </c>
+      <c r="E89" t="s">
+        <v>511</v>
+      </c>
+      <c r="F89" t="s">
+        <v>512</v>
+      </c>
+      <c r="G89" t="s">
+        <v>513</v>
+      </c>
+      <c r="H89" t="s">
+        <v>440</v>
+      </c>
+      <c r="I89" t="s">
+        <v>511</v>
+      </c>
+      <c r="J89" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K89" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L89" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B90" s="56" t="s">
+        <v>473</v>
+      </c>
+      <c r="D90" t="s">
+        <v>514</v>
+      </c>
+      <c r="E90" t="s">
+        <v>515</v>
+      </c>
+      <c r="F90" t="s">
+        <v>516</v>
+      </c>
+      <c r="G90" t="s">
+        <v>517</v>
+      </c>
+      <c r="H90" t="s">
+        <v>440</v>
+      </c>
+      <c r="I90" t="s">
+        <v>516</v>
+      </c>
+      <c r="J90" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L90" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A91" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B91" s="56" t="s">
+        <v>474</v>
+      </c>
+      <c r="D91" t="s">
+        <v>518</v>
+      </c>
+      <c r="E91" t="s">
+        <v>519</v>
+      </c>
+      <c r="F91" t="s">
+        <v>520</v>
+      </c>
+      <c r="G91" t="s">
+        <v>521</v>
+      </c>
+      <c r="H91" t="s">
+        <v>522</v>
+      </c>
+      <c r="I91" t="s">
+        <v>518</v>
+      </c>
+      <c r="J91" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K91" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L91" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" s="56" t="s">
+        <v>475</v>
+      </c>
+      <c r="D92" t="s">
+        <v>523</v>
+      </c>
+      <c r="E92" t="s">
+        <v>524</v>
+      </c>
+      <c r="F92" t="s">
+        <v>525</v>
+      </c>
+      <c r="G92" t="s">
+        <v>526</v>
+      </c>
+      <c r="H92" t="s">
+        <v>440</v>
+      </c>
+      <c r="I92" t="s">
+        <v>526</v>
+      </c>
+      <c r="J92" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K92" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L92" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A93" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="56" t="s">
+        <v>476</v>
+      </c>
+      <c r="D93" t="s">
+        <v>527</v>
+      </c>
+      <c r="E93" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" t="s">
+        <v>529</v>
+      </c>
+      <c r="G93" t="s">
+        <v>530</v>
+      </c>
+      <c r="H93" t="s">
+        <v>531</v>
+      </c>
+      <c r="I93" t="s">
+        <v>528</v>
+      </c>
+      <c r="J93" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K93" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L93" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A94" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="D94" t="s">
+        <v>532</v>
+      </c>
+      <c r="E94" t="s">
+        <v>533</v>
+      </c>
+      <c r="F94" t="s">
+        <v>534</v>
+      </c>
+      <c r="G94" t="s">
+        <v>535</v>
+      </c>
+      <c r="H94" t="s">
+        <v>440</v>
+      </c>
+      <c r="I94" t="s">
+        <v>532</v>
+      </c>
+      <c r="J94" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K94" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L94" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="165" x14ac:dyDescent="0.25">
+      <c r="A95" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="56" t="s">
+        <v>478</v>
+      </c>
+      <c r="D95" t="s">
+        <v>536</v>
+      </c>
+      <c r="E95" t="s">
+        <v>537</v>
+      </c>
+      <c r="F95" t="s">
+        <v>538</v>
+      </c>
+      <c r="G95" t="s">
+        <v>539</v>
+      </c>
+      <c r="H95" t="s">
+        <v>440</v>
+      </c>
+      <c r="I95" t="s">
+        <v>440</v>
+      </c>
+      <c r="J95" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K95" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="L95" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B96" s="56" t="s">
+        <v>540</v>
+      </c>
+      <c r="D96" s="45" t="s">
+        <v>560</v>
+      </c>
+      <c r="E96" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="F96" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="G96" s="45" t="s">
+        <v>562</v>
+      </c>
+      <c r="H96" s="45" t="s">
+        <v>563</v>
+      </c>
+      <c r="I96" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="J96" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L96" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A97" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="56" t="s">
+        <v>541</v>
+      </c>
+      <c r="D97" s="45" t="s">
+        <v>564</v>
+      </c>
+      <c r="E97" s="45" t="s">
+        <v>565</v>
+      </c>
+      <c r="F97" s="45" t="s">
+        <v>566</v>
+      </c>
+      <c r="G97" s="45" t="s">
+        <v>567</v>
+      </c>
+      <c r="H97" s="45" t="s">
+        <v>568</v>
+      </c>
+      <c r="I97" s="45" t="s">
+        <v>565</v>
+      </c>
+      <c r="J97" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K97" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L97" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A98" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B98" s="56" t="s">
+        <v>542</v>
+      </c>
+      <c r="D98" s="45" t="s">
+        <v>569</v>
+      </c>
+      <c r="E98" s="45" t="s">
+        <v>570</v>
+      </c>
+      <c r="F98" s="45" t="s">
+        <v>571</v>
+      </c>
+      <c r="G98" s="45" t="s">
+        <v>572</v>
+      </c>
+      <c r="H98" s="45" t="s">
+        <v>573</v>
+      </c>
+      <c r="I98" s="45" t="s">
+        <v>572</v>
+      </c>
+      <c r="J98" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K98" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L98" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A99" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B99" s="56" t="s">
+        <v>543</v>
+      </c>
+      <c r="D99" s="45" t="s">
+        <v>574</v>
+      </c>
+      <c r="E99" s="45" t="s">
+        <v>575</v>
+      </c>
+      <c r="F99" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="G99" s="45" t="s">
+        <v>576</v>
+      </c>
+      <c r="H99" s="45" t="s">
+        <v>577</v>
+      </c>
+      <c r="I99" s="45" t="s">
+        <v>577</v>
+      </c>
+      <c r="J99" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K99" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L99" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A100" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" s="56" t="s">
+        <v>544</v>
+      </c>
+      <c r="D100" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="E100" s="45" t="s">
+        <v>578</v>
+      </c>
+      <c r="F100" s="45" t="s">
+        <v>579</v>
+      </c>
+      <c r="G100" s="45" t="s">
+        <v>580</v>
+      </c>
+      <c r="H100" s="45" t="s">
+        <v>581</v>
+      </c>
+      <c r="I100" s="45" t="s">
+        <v>578</v>
+      </c>
+      <c r="J100" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K100" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L100" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B101" s="56" t="s">
+        <v>545</v>
+      </c>
+      <c r="D101" s="45" t="s">
+        <v>582</v>
+      </c>
+      <c r="E101" s="45" t="s">
+        <v>583</v>
+      </c>
+      <c r="F101" s="45" t="s">
+        <v>584</v>
+      </c>
+      <c r="G101" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="H101" s="45" t="s">
+        <v>586</v>
+      </c>
+      <c r="I101" s="45" t="s">
+        <v>586</v>
+      </c>
+      <c r="J101" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K101" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L101" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" s="56" t="s">
+        <v>546</v>
+      </c>
+      <c r="D102" s="45" t="s">
+        <v>587</v>
+      </c>
+      <c r="E102" s="45" t="s">
+        <v>588</v>
+      </c>
+      <c r="F102" s="45" t="s">
+        <v>589</v>
+      </c>
+      <c r="G102" s="45" t="s">
+        <v>590</v>
+      </c>
+      <c r="H102" s="45" t="s">
+        <v>591</v>
+      </c>
+      <c r="I102" s="45" t="s">
+        <v>591</v>
+      </c>
+      <c r="J102" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K102" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L102" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A103" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="D103" s="45" t="s">
+        <v>592</v>
+      </c>
+      <c r="E103" s="45" t="s">
+        <v>593</v>
+      </c>
+      <c r="F103" s="45" t="s">
+        <v>594</v>
+      </c>
+      <c r="G103" s="45" t="s">
+        <v>595</v>
+      </c>
+      <c r="H103" s="45" t="s">
+        <v>596</v>
+      </c>
+      <c r="I103" s="45" t="s">
+        <v>593</v>
+      </c>
+      <c r="J103" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K103" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L103" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A104" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B104" s="56" t="s">
+        <v>548</v>
+      </c>
+      <c r="D104" s="45" t="s">
+        <v>597</v>
+      </c>
+      <c r="E104" s="45" t="s">
+        <v>598</v>
+      </c>
+      <c r="F104" s="45" t="s">
+        <v>599</v>
+      </c>
+      <c r="G104" s="45" t="s">
+        <v>600</v>
+      </c>
+      <c r="H104" s="45" t="s">
+        <v>601</v>
+      </c>
+      <c r="I104" s="45" t="s">
+        <v>600</v>
+      </c>
+      <c r="J104" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K104" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L104" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B105" s="56" t="s">
+        <v>549</v>
+      </c>
+      <c r="D105" s="45" t="s">
+        <v>602</v>
+      </c>
+      <c r="E105" s="45" t="s">
+        <v>603</v>
+      </c>
+      <c r="F105" s="45" t="s">
+        <v>604</v>
+      </c>
+      <c r="G105" s="45" t="s">
+        <v>605</v>
+      </c>
+      <c r="H105" s="45" t="s">
+        <v>606</v>
+      </c>
+      <c r="I105" s="45" t="s">
+        <v>604</v>
+      </c>
+      <c r="J105" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K105" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L105" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A106" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B106" s="56" t="s">
+        <v>550</v>
+      </c>
+      <c r="D106" s="45" t="s">
+        <v>607</v>
+      </c>
+      <c r="E106" s="45" t="s">
+        <v>608</v>
+      </c>
+      <c r="F106" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="G106" s="45" t="s">
+        <v>610</v>
+      </c>
+      <c r="H106" s="45" t="s">
+        <v>611</v>
+      </c>
+      <c r="I106" s="45" t="s">
+        <v>607</v>
+      </c>
+      <c r="J106" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K106" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L106" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A107" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B107" s="56" t="s">
+        <v>551</v>
+      </c>
+      <c r="D107" s="45" t="s">
+        <v>612</v>
+      </c>
+      <c r="E107" s="45" t="s">
+        <v>613</v>
+      </c>
+      <c r="F107" s="45" t="s">
+        <v>614</v>
+      </c>
+      <c r="G107" s="45" t="s">
+        <v>615</v>
+      </c>
+      <c r="H107" s="45" t="s">
+        <v>616</v>
+      </c>
+      <c r="I107" s="45" t="s">
+        <v>614</v>
+      </c>
+      <c r="J107" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K107" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L107" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A108" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B108" s="56" t="s">
+        <v>552</v>
+      </c>
+      <c r="D108" s="45" t="s">
+        <v>617</v>
+      </c>
+      <c r="E108" s="45" t="s">
+        <v>618</v>
+      </c>
+      <c r="F108" s="45" t="s">
+        <v>619</v>
+      </c>
+      <c r="G108" s="45" t="s">
+        <v>620</v>
+      </c>
+      <c r="H108" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="I108" s="45" t="s">
+        <v>619</v>
+      </c>
+      <c r="J108" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K108" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L108" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B109" s="56" t="s">
+        <v>553</v>
+      </c>
+      <c r="D109" s="45" t="s">
+        <v>622</v>
+      </c>
+      <c r="E109" s="45" t="s">
+        <v>623</v>
+      </c>
+      <c r="F109" s="45" t="s">
+        <v>624</v>
+      </c>
+      <c r="G109" s="45" t="s">
+        <v>625</v>
+      </c>
+      <c r="H109" s="45" t="s">
+        <v>626</v>
+      </c>
+      <c r="I109" s="45" t="s">
+        <v>626</v>
+      </c>
+      <c r="J109" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K109" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L109" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A110" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B110" s="56" t="s">
+        <v>554</v>
+      </c>
+      <c r="D110" s="45" t="s">
+        <v>592</v>
+      </c>
+      <c r="E110" s="45" t="s">
+        <v>627</v>
+      </c>
+      <c r="F110" s="45" t="s">
+        <v>628</v>
+      </c>
+      <c r="G110" s="45" t="s">
+        <v>629</v>
+      </c>
+      <c r="H110" s="45" t="s">
+        <v>630</v>
+      </c>
+      <c r="I110" s="45" t="s">
+        <v>592</v>
+      </c>
+      <c r="J110" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K110" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L110" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A111" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="56" t="s">
+        <v>555</v>
+      </c>
+      <c r="D111" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="E111" s="45" t="s">
+        <v>593</v>
+      </c>
+      <c r="F111" s="45" t="s">
+        <v>631</v>
+      </c>
+      <c r="G111" s="45" t="s">
+        <v>632</v>
+      </c>
+      <c r="H111" s="45" t="s">
+        <v>633</v>
+      </c>
+      <c r="I111" s="45" t="s">
+        <v>593</v>
+      </c>
+      <c r="J111" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K111" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L111" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A112" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B112" s="56" t="s">
+        <v>556</v>
+      </c>
+      <c r="D112" s="45" t="s">
+        <v>634</v>
+      </c>
+      <c r="E112" s="45" t="s">
+        <v>635</v>
+      </c>
+      <c r="F112" s="45" t="s">
+        <v>636</v>
+      </c>
+      <c r="G112" s="45" t="s">
+        <v>637</v>
+      </c>
+      <c r="H112" s="45" t="s">
+        <v>638</v>
+      </c>
+      <c r="I112" s="45" t="s">
+        <v>635</v>
+      </c>
+      <c r="J112" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K112" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L112" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A113" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B113" s="56" t="s">
+        <v>557</v>
+      </c>
+      <c r="D113" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="E113" s="45" t="s">
+        <v>578</v>
+      </c>
+      <c r="F113" s="45" t="s">
+        <v>579</v>
+      </c>
+      <c r="G113" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="H113" s="45" t="s">
+        <v>640</v>
+      </c>
+      <c r="I113" s="45" t="s">
+        <v>579</v>
+      </c>
+      <c r="J113" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K113" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L113" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A114" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B114" s="56" t="s">
+        <v>558</v>
+      </c>
+      <c r="D114" s="45" t="s">
+        <v>622</v>
+      </c>
+      <c r="E114" s="45" t="s">
+        <v>623</v>
+      </c>
+      <c r="F114" s="45" t="s">
+        <v>641</v>
+      </c>
+      <c r="G114" s="45" t="s">
+        <v>642</v>
+      </c>
+      <c r="H114" s="45" t="s">
+        <v>643</v>
+      </c>
+      <c r="I114" s="45" t="s">
+        <v>642</v>
+      </c>
+      <c r="J114" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K114" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L114" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A115" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B115" s="56" t="s">
+        <v>559</v>
+      </c>
+      <c r="D115" s="45" t="s">
+        <v>644</v>
+      </c>
+      <c r="E115" s="45" t="s">
+        <v>645</v>
+      </c>
+      <c r="F115" s="45" t="s">
+        <v>646</v>
+      </c>
+      <c r="G115" s="45" t="s">
+        <v>647</v>
+      </c>
+      <c r="H115" s="45" t="s">
+        <v>648</v>
+      </c>
+      <c r="I115" s="45" t="s">
+        <v>644</v>
+      </c>
+      <c r="J115" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K115" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L115" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B116" s="56" t="s">
+        <v>649</v>
+      </c>
+      <c r="D116" s="45" t="s">
+        <v>669</v>
+      </c>
+      <c r="E116" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="F116" s="45" t="s">
+        <v>671</v>
+      </c>
+      <c r="G116" s="45" t="s">
+        <v>672</v>
+      </c>
+      <c r="H116" s="45" t="s">
+        <v>673</v>
+      </c>
+      <c r="I116" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="J116" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K116" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L116" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B117" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="D117" s="45" t="s">
+        <v>674</v>
+      </c>
+      <c r="E117" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="F117" s="45" t="s">
+        <v>676</v>
+      </c>
+      <c r="G117" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="H117" s="45" t="s">
+        <v>678</v>
+      </c>
+      <c r="I117" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="J117" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K117" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L117" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A118" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B118" s="56" t="s">
+        <v>651</v>
+      </c>
+      <c r="D118" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="E118" s="45" t="s">
+        <v>680</v>
+      </c>
+      <c r="F118" s="45" t="s">
+        <v>594</v>
+      </c>
+      <c r="G118" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="H118" s="45" t="s">
+        <v>682</v>
+      </c>
+      <c r="I118" s="45" t="s">
+        <v>594</v>
+      </c>
+      <c r="J118" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K118" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L118" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A119" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B119" s="56" t="s">
+        <v>652</v>
+      </c>
+      <c r="D119" s="45" t="s">
+        <v>683</v>
+      </c>
+      <c r="E119" s="45" t="s">
+        <v>684</v>
+      </c>
+      <c r="F119" s="45" t="s">
+        <v>685</v>
+      </c>
+      <c r="G119" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="H119" s="45" t="s">
+        <v>687</v>
+      </c>
+      <c r="I119" s="45" t="s">
+        <v>687</v>
+      </c>
+      <c r="J119" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K119" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L119" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A120" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B120" s="56" t="s">
+        <v>653</v>
+      </c>
+      <c r="D120" s="45" t="s">
+        <v>688</v>
+      </c>
+      <c r="E120" s="45" t="s">
+        <v>689</v>
+      </c>
+      <c r="F120" s="45" t="s">
+        <v>690</v>
+      </c>
+      <c r="G120" s="45" t="s">
+        <v>691</v>
+      </c>
+      <c r="H120" s="45" t="s">
+        <v>692</v>
+      </c>
+      <c r="I120" s="45" t="s">
+        <v>691</v>
+      </c>
+      <c r="J120" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K120" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L120" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A121" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B121" s="56" t="s">
+        <v>654</v>
+      </c>
+      <c r="D121" s="45" t="s">
+        <v>693</v>
+      </c>
+      <c r="E121" s="45" t="s">
+        <v>694</v>
+      </c>
+      <c r="F121" s="45" t="s">
+        <v>695</v>
+      </c>
+      <c r="G121" s="45" t="s">
+        <v>696</v>
+      </c>
+      <c r="H121" s="45" t="s">
+        <v>697</v>
+      </c>
+      <c r="I121" s="45" t="s">
+        <v>693</v>
+      </c>
+      <c r="J121" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K121" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L121" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B122" s="56" t="s">
+        <v>655</v>
+      </c>
+      <c r="D122" s="45" t="s">
+        <v>698</v>
+      </c>
+      <c r="E122" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="F122" s="45" t="s">
+        <v>700</v>
+      </c>
+      <c r="G122" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="H122" s="45" t="s">
+        <v>702</v>
+      </c>
+      <c r="I122" s="45" t="s">
+        <v>700</v>
+      </c>
+      <c r="J122" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K122" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L122" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A123" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B123" s="56" t="s">
+        <v>656</v>
+      </c>
+      <c r="D123" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="E123" s="45" t="s">
+        <v>704</v>
+      </c>
+      <c r="F123" s="45" t="s">
+        <v>705</v>
+      </c>
+      <c r="G123" s="45" t="s">
+        <v>706</v>
+      </c>
+      <c r="H123" s="45" t="s">
+        <v>707</v>
+      </c>
+      <c r="I123" s="45" t="s">
+        <v>704</v>
+      </c>
+      <c r="J123" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K123" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L123" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A124" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B124" s="56" t="s">
+        <v>657</v>
+      </c>
+      <c r="D124" s="45" t="s">
+        <v>708</v>
+      </c>
+      <c r="E124" s="45" t="s">
+        <v>709</v>
+      </c>
+      <c r="F124" s="45" t="s">
+        <v>710</v>
+      </c>
+      <c r="G124" s="45" t="s">
+        <v>711</v>
+      </c>
+      <c r="H124" s="45" t="s">
+        <v>712</v>
+      </c>
+      <c r="I124" s="45" t="s">
+        <v>709</v>
+      </c>
+      <c r="J124" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K124" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L124" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A125" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B125" s="56" t="s">
+        <v>658</v>
+      </c>
+      <c r="D125" s="45" t="s">
+        <v>713</v>
+      </c>
+      <c r="E125" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="F125" s="45" t="s">
+        <v>594</v>
+      </c>
+      <c r="G125" s="45" t="s">
+        <v>715</v>
+      </c>
+      <c r="H125" s="45" t="s">
+        <v>716</v>
+      </c>
+      <c r="I125" s="45" t="s">
+        <v>713</v>
+      </c>
+      <c r="J125" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K125" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L125" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A126" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B126" s="56" t="s">
+        <v>659</v>
+      </c>
+      <c r="D126" s="45" t="s">
+        <v>717</v>
+      </c>
+      <c r="E126" s="45" t="s">
+        <v>718</v>
+      </c>
+      <c r="F126" s="45" t="s">
+        <v>719</v>
+      </c>
+      <c r="G126" s="45" t="s">
+        <v>720</v>
+      </c>
+      <c r="H126" s="45" t="s">
+        <v>721</v>
+      </c>
+      <c r="I126" s="45" t="s">
+        <v>717</v>
+      </c>
+      <c r="J126" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K126" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L126" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B127" s="56" t="s">
+        <v>660</v>
+      </c>
+      <c r="D127" s="45" t="s">
+        <v>722</v>
+      </c>
+      <c r="E127" s="45" t="s">
+        <v>723</v>
+      </c>
+      <c r="F127" s="45" t="s">
+        <v>724</v>
+      </c>
+      <c r="G127" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="H127" s="45" t="s">
+        <v>726</v>
+      </c>
+      <c r="I127" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="J127" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K127" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L127" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A128" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B128" s="56" t="s">
+        <v>661</v>
+      </c>
+      <c r="D128" s="45" t="s">
+        <v>727</v>
+      </c>
+      <c r="E128" s="45" t="s">
+        <v>728</v>
+      </c>
+      <c r="F128" s="45" t="s">
+        <v>729</v>
+      </c>
+      <c r="G128" s="45" t="s">
+        <v>730</v>
+      </c>
+      <c r="H128" s="45" t="s">
+        <v>731</v>
+      </c>
+      <c r="I128" s="45" t="s">
+        <v>731</v>
+      </c>
+      <c r="J128" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K128" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L128" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A129" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B129" s="56" t="s">
+        <v>662</v>
+      </c>
+      <c r="D129" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="E129" s="45" t="s">
+        <v>732</v>
+      </c>
+      <c r="F129" s="45" t="s">
+        <v>733</v>
+      </c>
+      <c r="G129" s="45" t="s">
+        <v>734</v>
+      </c>
+      <c r="H129" s="45" t="s">
+        <v>735</v>
+      </c>
+      <c r="I129" s="45" t="s">
+        <v>733</v>
+      </c>
+      <c r="J129" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K129" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L129" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A130" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B130" s="56" t="s">
+        <v>663</v>
+      </c>
+      <c r="D130" s="45" t="s">
+        <v>736</v>
+      </c>
+      <c r="E130" s="45" t="s">
+        <v>737</v>
+      </c>
+      <c r="F130" s="45" t="s">
+        <v>738</v>
+      </c>
+      <c r="G130" s="45" t="s">
+        <v>739</v>
+      </c>
+      <c r="H130" s="45" t="s">
+        <v>740</v>
+      </c>
+      <c r="I130" s="45" t="s">
+        <v>737</v>
+      </c>
+      <c r="J130" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K130" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L130" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B131" s="56" t="s">
+        <v>664</v>
+      </c>
+      <c r="D131" s="45" t="s">
+        <v>741</v>
+      </c>
+      <c r="E131" s="45" t="s">
+        <v>742</v>
+      </c>
+      <c r="F131" s="45" t="s">
+        <v>743</v>
+      </c>
+      <c r="G131" s="45" t="s">
+        <v>744</v>
+      </c>
+      <c r="H131" s="45" t="s">
+        <v>745</v>
+      </c>
+      <c r="I131" s="45" t="s">
+        <v>742</v>
+      </c>
+      <c r="J131" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K131" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L131" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A132" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B132" s="56" t="s">
+        <v>665</v>
+      </c>
+      <c r="D132" s="45" t="s">
+        <v>746</v>
+      </c>
+      <c r="E132" s="45" t="s">
+        <v>747</v>
+      </c>
+      <c r="F132" s="45" t="s">
+        <v>748</v>
+      </c>
+      <c r="G132" s="45" t="s">
+        <v>749</v>
+      </c>
+      <c r="H132" s="45" t="s">
+        <v>750</v>
+      </c>
+      <c r="I132" s="45" t="s">
+        <v>747</v>
+      </c>
+      <c r="J132" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K132" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L132" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B133" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="D133" s="45" t="s">
+        <v>751</v>
+      </c>
+      <c r="E133" s="45" t="s">
+        <v>752</v>
+      </c>
+      <c r="F133" s="45" t="s">
+        <v>753</v>
+      </c>
+      <c r="G133" s="45" t="s">
+        <v>754</v>
+      </c>
+      <c r="H133" s="45" t="s">
+        <v>755</v>
+      </c>
+      <c r="I133" s="45" t="s">
+        <v>751</v>
+      </c>
+      <c r="J133" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K133" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L133" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A134" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B134" s="56" t="s">
+        <v>667</v>
+      </c>
+      <c r="D134" s="45" t="s">
+        <v>756</v>
+      </c>
+      <c r="E134" s="45" t="s">
+        <v>757</v>
+      </c>
+      <c r="F134" s="45" t="s">
+        <v>758</v>
+      </c>
+      <c r="G134" s="45" t="s">
+        <v>759</v>
+      </c>
+      <c r="H134" s="45" t="s">
+        <v>760</v>
+      </c>
+      <c r="I134" s="45" t="s">
+        <v>757</v>
+      </c>
+      <c r="J134" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K134" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L134" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A135" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B135" s="56" t="s">
+        <v>668</v>
+      </c>
+      <c r="D135" s="45" t="s">
+        <v>761</v>
+      </c>
+      <c r="E135" s="45" t="s">
+        <v>762</v>
+      </c>
+      <c r="F135" s="45" t="s">
+        <v>763</v>
+      </c>
+      <c r="G135" s="45" t="s">
+        <v>764</v>
+      </c>
+      <c r="H135" s="45" t="s">
+        <v>765</v>
+      </c>
+      <c r="I135" s="45" t="s">
+        <v>763</v>
+      </c>
+      <c r="J135" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K135" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="L135" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="405" x14ac:dyDescent="0.25">
+      <c r="A136" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B136" s="56" t="s">
+        <v>768</v>
+      </c>
+      <c r="C136" t="s">
+        <v>769</v>
+      </c>
+      <c r="J136" s="48" t="s">
+        <v>767</v>
+      </c>
+      <c r="K136" s="48" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A137" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B137" s="57" t="s">
+        <v>770</v>
+      </c>
+      <c r="D137" s="45" t="s">
+        <v>774</v>
+      </c>
+      <c r="E137" s="45" t="s">
+        <v>775</v>
+      </c>
+      <c r="F137" s="45" t="s">
+        <v>776</v>
+      </c>
+      <c r="G137" s="45" t="s">
+        <v>777</v>
+      </c>
+      <c r="H137" s="45" t="s">
+        <v>778</v>
+      </c>
+      <c r="L137" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A138" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B138" s="57" t="s">
+        <v>771</v>
+      </c>
+      <c r="D138" s="45" t="s">
+        <v>779</v>
+      </c>
+      <c r="E138" s="45" t="s">
+        <v>780</v>
+      </c>
+      <c r="F138" s="45" t="s">
+        <v>781</v>
+      </c>
+      <c r="G138" s="45" t="s">
+        <v>782</v>
+      </c>
+      <c r="H138" s="45" t="s">
+        <v>783</v>
+      </c>
+      <c r="L138" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A139" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B139" s="57" t="s">
+        <v>772</v>
+      </c>
+      <c r="D139" s="45" t="s">
+        <v>784</v>
+      </c>
+      <c r="E139" s="45" t="s">
+        <v>785</v>
+      </c>
+      <c r="F139" s="45" t="s">
+        <v>786</v>
+      </c>
+      <c r="G139" s="45" t="s">
+        <v>787</v>
+      </c>
+      <c r="H139" s="45" t="s">
+        <v>788</v>
+      </c>
+      <c r="L139" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A140" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B140" s="56" t="s">
+        <v>773</v>
+      </c>
+      <c r="D140" s="45" t="s">
+        <v>792</v>
+      </c>
+      <c r="E140" s="45" t="s">
+        <v>789</v>
+      </c>
+      <c r="F140" s="45" t="s">
+        <v>793</v>
+      </c>
+      <c r="G140" s="45" t="s">
+        <v>790</v>
+      </c>
+      <c r="H140" s="45" t="s">
+        <v>791</v>
+      </c>
+      <c r="L140" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="195" x14ac:dyDescent="0.25">
+      <c r="A141" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B141" s="56" t="s">
+        <v>794</v>
+      </c>
+      <c r="C141" t="s">
+        <v>769</v>
+      </c>
+      <c r="J141" t="s">
+        <v>767</v>
+      </c>
+      <c r="K141" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A142" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B142" s="56" t="s">
+        <v>795</v>
+      </c>
+      <c r="D142" s="45" t="s">
+        <v>797</v>
+      </c>
+      <c r="E142" s="45" t="s">
+        <v>798</v>
+      </c>
+      <c r="F142" s="45" t="s">
+        <v>799</v>
+      </c>
+      <c r="G142" s="45" t="s">
+        <v>800</v>
+      </c>
+      <c r="H142" s="45" t="s">
+        <v>801</v>
+      </c>
+      <c r="L142" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A143" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B143" s="56" t="s">
+        <v>796</v>
+      </c>
+      <c r="D143" s="45" t="s">
+        <v>802</v>
+      </c>
+      <c r="E143" s="45" t="s">
+        <v>803</v>
+      </c>
+      <c r="F143" s="45" t="s">
+        <v>804</v>
+      </c>
+      <c r="G143" s="45" t="s">
+        <v>805</v>
+      </c>
+      <c r="H143" s="45" t="s">
+        <v>806</v>
+      </c>
+      <c r="L143" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A144" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B144" s="56" t="s">
+        <v>807</v>
+      </c>
+      <c r="C144" t="s">
+        <v>769</v>
+      </c>
+      <c r="J144" t="s">
+        <v>767</v>
+      </c>
+      <c r="K144" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A145" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B145" s="56" t="s">
+        <v>808</v>
+      </c>
+      <c r="D145" t="s">
+        <v>810</v>
+      </c>
+      <c r="E145" t="s">
+        <v>811</v>
+      </c>
+      <c r="F145" t="s">
+        <v>812</v>
+      </c>
+      <c r="G145" t="s">
+        <v>813</v>
+      </c>
+      <c r="H145" t="s">
+        <v>814</v>
+      </c>
+      <c r="L145" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B146" s="56" t="s">
+        <v>809</v>
+      </c>
+      <c r="D146" t="s">
+        <v>815</v>
+      </c>
+      <c r="E146" t="s">
+        <v>816</v>
+      </c>
+      <c r="F146" t="s">
+        <v>817</v>
+      </c>
+      <c r="G146" t="s">
+        <v>818</v>
+      </c>
+      <c r="H146" t="s">
+        <v>819</v>
+      </c>
+      <c r="L146" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="255" x14ac:dyDescent="0.25">
+      <c r="A147" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B147" s="56" t="s">
+        <v>820</v>
+      </c>
+      <c r="J147" t="s">
+        <v>767</v>
+      </c>
+      <c r="K147" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A148" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B148" s="56" t="s">
+        <v>821</v>
+      </c>
+      <c r="D148" s="45" t="s">
+        <v>823</v>
+      </c>
+      <c r="E148" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="F148" s="45" t="s">
+        <v>825</v>
+      </c>
+      <c r="G148" s="45" t="s">
+        <v>826</v>
+      </c>
+      <c r="H148" s="45" t="s">
+        <v>827</v>
+      </c>
+      <c r="L148" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B149" s="56" t="s">
+        <v>822</v>
+      </c>
+      <c r="D149" s="45" t="s">
+        <v>828</v>
+      </c>
+      <c r="E149" s="45" t="s">
+        <v>829</v>
+      </c>
+      <c r="F149" s="45" t="s">
+        <v>830</v>
+      </c>
+      <c r="G149" s="45" t="s">
+        <v>831</v>
+      </c>
+      <c r="H149" s="45" t="s">
+        <v>832</v>
+      </c>
+      <c r="L149" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B150" s="56" t="s">
+        <v>833</v>
+      </c>
+      <c r="J150" t="s">
+        <v>767</v>
+      </c>
+      <c r="K150" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B151" s="45" t="s">
+        <v>834</v>
+      </c>
+      <c r="D151" t="s">
+        <v>836</v>
+      </c>
+      <c r="E151" t="s">
+        <v>837</v>
+      </c>
+      <c r="F151" t="s">
+        <v>838</v>
+      </c>
+      <c r="G151" t="s">
+        <v>839</v>
+      </c>
+      <c r="H151" t="s">
+        <v>840</v>
+      </c>
+      <c r="L151" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A152" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B152" s="45" t="s">
+        <v>835</v>
+      </c>
+      <c r="D152" t="s">
+        <v>841</v>
+      </c>
+      <c r="E152" t="s">
+        <v>842</v>
+      </c>
+      <c r="F152" t="s">
+        <v>843</v>
+      </c>
+      <c r="G152" t="s">
+        <v>844</v>
+      </c>
+      <c r="H152" t="s">
+        <v>845</v>
+      </c>
+      <c r="L152" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="345" x14ac:dyDescent="0.25">
+      <c r="A153" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B153" s="45" t="s">
+        <v>846</v>
+      </c>
+      <c r="J153" t="s">
+        <v>767</v>
+      </c>
+      <c r="K153" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A154" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B154" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="D154" s="45" t="s">
+        <v>850</v>
+      </c>
+      <c r="E154" s="45" t="s">
+        <v>851</v>
+      </c>
+      <c r="F154" s="45" t="s">
+        <v>852</v>
+      </c>
+      <c r="G154" s="45" t="s">
+        <v>853</v>
+      </c>
+      <c r="H154" s="45" t="s">
+        <v>854</v>
+      </c>
+      <c r="L154" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A155" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155" s="45" t="s">
+        <v>848</v>
+      </c>
+      <c r="D155" s="45" t="s">
+        <v>855</v>
+      </c>
+      <c r="E155" s="45" t="s">
+        <v>856</v>
+      </c>
+      <c r="F155" s="45" t="s">
+        <v>857</v>
+      </c>
+      <c r="G155" s="45" t="s">
+        <v>858</v>
+      </c>
+      <c r="H155" s="45" t="s">
+        <v>859</v>
+      </c>
+      <c r="L155" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A156" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B156" s="45" t="s">
+        <v>849</v>
+      </c>
+      <c r="D156" s="45" t="s">
+        <v>860</v>
+      </c>
+      <c r="E156" s="45" t="s">
+        <v>861</v>
+      </c>
+      <c r="F156" s="45" t="s">
+        <v>862</v>
+      </c>
+      <c r="G156" s="45" t="s">
+        <v>863</v>
+      </c>
+      <c r="H156" s="45" t="s">
+        <v>864</v>
+      </c>
+      <c r="L156" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="270" x14ac:dyDescent="0.25">
+      <c r="A157" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="B157" s="45" t="s">
+        <v>895</v>
+      </c>
+      <c r="C157" t="s">
+        <v>896</v>
+      </c>
+      <c r="J157" t="s">
+        <v>767</v>
+      </c>
+      <c r="K157" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A158" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B158" s="45" t="s">
+        <v>865</v>
+      </c>
+      <c r="D158" s="45" t="s">
+        <v>870</v>
+      </c>
+      <c r="E158" s="45" t="s">
+        <v>871</v>
+      </c>
+      <c r="F158" s="45" t="s">
+        <v>872</v>
+      </c>
+      <c r="G158" s="45" t="s">
+        <v>873</v>
+      </c>
+      <c r="H158" s="45" t="s">
+        <v>874</v>
+      </c>
+      <c r="L158" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A159" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B159" s="45" t="s">
+        <v>866</v>
+      </c>
+      <c r="D159" s="45" t="s">
+        <v>875</v>
+      </c>
+      <c r="E159" s="45" t="s">
+        <v>876</v>
+      </c>
+      <c r="F159" s="45" t="s">
+        <v>877</v>
+      </c>
+      <c r="G159" s="45" t="s">
+        <v>878</v>
+      </c>
+      <c r="H159" s="45" t="s">
+        <v>879</v>
+      </c>
+      <c r="L159" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A160" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B160" s="45" t="s">
+        <v>867</v>
+      </c>
+      <c r="D160" s="45" t="s">
+        <v>880</v>
+      </c>
+      <c r="E160" s="45" t="s">
+        <v>881</v>
+      </c>
+      <c r="F160" s="45" t="s">
+        <v>882</v>
+      </c>
+      <c r="G160" s="45" t="s">
+        <v>883</v>
+      </c>
+      <c r="H160" s="45" t="s">
+        <v>884</v>
+      </c>
+      <c r="L160" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B161" s="45" t="s">
+        <v>868</v>
+      </c>
+      <c r="D161" s="45" t="s">
+        <v>885</v>
+      </c>
+      <c r="E161" s="45" t="s">
+        <v>886</v>
+      </c>
+      <c r="F161" s="45" t="s">
+        <v>887</v>
+      </c>
+      <c r="G161" s="45" t="s">
+        <v>888</v>
+      </c>
+      <c r="H161" s="45" t="s">
+        <v>889</v>
+      </c>
+      <c r="L161" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A162" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="B162" s="45" t="s">
+        <v>869</v>
+      </c>
+      <c r="D162" s="45" t="s">
+        <v>890</v>
+      </c>
+      <c r="E162" s="45" t="s">
+        <v>891</v>
+      </c>
+      <c r="F162" s="45" t="s">
+        <v>892</v>
+      </c>
+      <c r="G162" s="45" t="s">
+        <v>893</v>
+      </c>
+      <c r="H162" s="45" t="s">
+        <v>894</v>
+      </c>
+      <c r="L162" s="50">
         <v>1</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1859F96-324A-4BFE-A515-57205A714459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D58AF29-A12B-4F29-8D00-FA9BE7E92095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="897">
   <si>
     <t>Option 1</t>
   </si>
@@ -13853,16 +13853,16 @@
     <t>(C) : &lt;smiles&gt;CC(C)CC(=O)OC(=O)CC(C)C&lt;/smiles&gt;</t>
   </si>
   <si>
-    <t>(D) : &lt;smiles&gt;CCC(C)C(=O)OC(=O)C(C)CC&lt;/smiles&gt;</t>
-  </si>
-  <si>
-    <t>(E) : &lt;smiles&gt;CCCCCOCCCC&lt;/smiles&gt;</t>
-  </si>
-  <si>
     <t>\section*{Méthode de contrôle de l'évolution d'un système chimique : ( $\mathbf{1 0}$ points)} On réalise un mélange équimolaire contenant $n_{0}=0,12 \mathrm{~mol}$ d'un acide ( $A$ ) et $n_{0}=0,12 \mathrm{~mol}$ d'un alcool (B). On ajoute au mélange quelques gouttes d'acide sulfurique concentré et quelques grains de pierre ponce. Le dispositif expérimental utilisée est représenté sur la figure cicontre. À la fin de la transformation on obtient la masse $m(E)=12,64 g$ d'un ester ( $E$ ). \begin{table} \captionsetup{labelformat=empty} \caption{Données : $79 \div 39=2$} \begin{tabular}{|l|l|l|} \hline Composé organique &amp; Formule semi-développée &amp; Masse molaire \\ \hline L'alcool (B) &amp; &lt;smiles&gt;CC(C)CCCO&lt;/smiles&gt; &amp; \\ \hline L'ester (E) &amp; &lt;smiles&gt;CCCC(=O)OCCC(C)C&lt;/smiles&gt; &amp; $M(E)=158 \mathrm{~g} . \mathrm{mol}^{-1}$ \\ \hline \end{tabular} \end{table} \begin{figure} \captionsetup{labelformat=empty} \caption{Données : $79 \div 39=2$} \includegraphics[alt={},max width=\textwidth]</t>
   </si>
   <si>
     <t>CH22F2</t>
+  </si>
+  <si>
+    <t>(E) : $\usepackage{chemfig} \chemfig{CH_3-CH_2-CH_2-CH_2-CH_2-O-CH_2-CH_2-CH_2-CH_3}$</t>
+  </si>
+  <si>
+    <t>(D) : $&lt;smiles&gt;CCC(C)C(=O)OC(=O)C(C)CC&lt;/smiles&gt;$</t>
   </si>
 </sst>
 </file>
@@ -20117,6 +20117,9 @@
       <c r="B147" s="56" t="s">
         <v>820</v>
       </c>
+      <c r="C147" t="s">
+        <v>894</v>
+      </c>
       <c r="J147" t="s">
         <v>767</v>
       </c>
@@ -20183,6 +20186,9 @@
       <c r="B150" s="56" t="s">
         <v>833</v>
       </c>
+      <c r="C150" t="s">
+        <v>894</v>
+      </c>
       <c r="J150" t="s">
         <v>767</v>
       </c>
@@ -20249,6 +20255,9 @@
       <c r="B153" s="45" t="s">
         <v>846</v>
       </c>
+      <c r="C153" t="s">
+        <v>894</v>
+      </c>
       <c r="J153" t="s">
         <v>767</v>
       </c>
@@ -20339,10 +20348,10 @@
         <v>171</v>
       </c>
       <c r="B157" s="45" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C157" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="J157" t="s">
         <v>767</v>
@@ -20472,10 +20481,10 @@
         <v>892</v>
       </c>
       <c r="G162" s="45" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="H162" s="45" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="L162" s="50">
         <v>1</v>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D58AF29-A12B-4F29-8D00-FA9BE7E92095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82A738A-B4A6-403E-8B75-64B5E62E057F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13853,16 +13853,16 @@
     <t>(C) : &lt;smiles&gt;CC(C)CC(=O)OC(=O)CC(C)C&lt;/smiles&gt;</t>
   </si>
   <si>
+    <t>(D) : &lt;smiles&gt;CCC(C)C(=O)OC(=O)C(C)CC&lt;/smiles&gt;</t>
+  </si>
+  <si>
     <t>\section*{Méthode de contrôle de l'évolution d'un système chimique : ( $\mathbf{1 0}$ points)} On réalise un mélange équimolaire contenant $n_{0}=0,12 \mathrm{~mol}$ d'un acide ( $A$ ) et $n_{0}=0,12 \mathrm{~mol}$ d'un alcool (B). On ajoute au mélange quelques gouttes d'acide sulfurique concentré et quelques grains de pierre ponce. Le dispositif expérimental utilisée est représenté sur la figure cicontre. À la fin de la transformation on obtient la masse $m(E)=12,64 g$ d'un ester ( $E$ ). \begin{table} \captionsetup{labelformat=empty} \caption{Données : $79 \div 39=2$} \begin{tabular}{|l|l|l|} \hline Composé organique &amp; Formule semi-développée &amp; Masse molaire \\ \hline L'alcool (B) &amp; &lt;smiles&gt;CC(C)CCCO&lt;/smiles&gt; &amp; \\ \hline L'ester (E) &amp; &lt;smiles&gt;CCCC(=O)OCCC(C)C&lt;/smiles&gt; &amp; $M(E)=158 \mathrm{~g} . \mathrm{mol}^{-1}$ \\ \hline \end{tabular} \end{table} \begin{figure} \captionsetup{labelformat=empty} \caption{Données : $79 \div 39=2$} \includegraphics[alt={},max width=\textwidth]</t>
   </si>
   <si>
     <t>CH22F2</t>
   </si>
   <si>
-    <t>(E) : $\usepackage{chemfig} \chemfig{CH_3-CH_2-CH_2-CH_2-CH_2-O-CH_2-CH_2-CH_2-CH_3}$</t>
-  </si>
-  <si>
-    <t>(D) : $&lt;smiles&gt;CCC(C)C(=O)OC(=O)C(C)CC&lt;/smiles&gt;$</t>
+    <t>(E) :&lt;smiles&gt;CCCCCOCCCC&lt;/smiles&gt;</t>
   </si>
 </sst>
 </file>
@@ -20118,7 +20118,7 @@
         <v>820</v>
       </c>
       <c r="C147" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J147" t="s">
         <v>767</v>
@@ -20187,7 +20187,7 @@
         <v>833</v>
       </c>
       <c r="C150" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J150" t="s">
         <v>767</v>
@@ -20256,7 +20256,7 @@
         <v>846</v>
       </c>
       <c r="C153" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J153" t="s">
         <v>767</v>
@@ -20348,10 +20348,10 @@
         <v>171</v>
       </c>
       <c r="B157" s="45" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C157" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J157" t="s">
         <v>767</v>
@@ -20481,10 +20481,10 @@
         <v>892</v>
       </c>
       <c r="G162" s="45" t="s">
+        <v>893</v>
+      </c>
+      <c r="H162" s="45" t="s">
         <v>896</v>
-      </c>
-      <c r="H162" s="45" t="s">
-        <v>895</v>
       </c>
       <c r="L162" s="50">
         <v>1</v>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82A738A-B4A6-403E-8B75-64B5E62E057F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46A3EBC-4A07-4911-8EB4-9F1500998DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="899">
   <si>
     <t>Option 1</t>
   </si>
@@ -13844,12 +13844,6 @@
     <t>(E) : $68 \%$</t>
   </si>
   <si>
-    <t>(A) : &lt;smiles&gt;CCCC(=O)OC(=O)CCC&lt;/smiles&gt;</t>
-  </si>
-  <si>
-    <t>(B) : &lt;smiles&gt;CCCOC(=O)CCC&lt;/smiles&gt;</t>
-  </si>
-  <si>
     <t>(C) : &lt;smiles&gt;CC(C)CC(=O)OC(=O)CC(C)C&lt;/smiles&gt;</t>
   </si>
   <si>
@@ -13862,7 +13856,19 @@
     <t>CH22F2</t>
   </si>
   <si>
-    <t>(E) :&lt;smiles&gt;CCCCCOCCCC&lt;/smiles&gt;</t>
+    <t>(A) :&lt;smiles&gt;CCCC(=O)OC(=O)CCC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(B) : &lt;smiles&gt;CCCC(=O)OCCC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(E) : &lt;smiles&gt;CCCCOCCCC&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>TESTTEST</t>
+  </si>
+  <si>
+    <t>&lt;smiles&gt;CCO&lt;/smiles&gt;</t>
   </si>
 </sst>
 </file>
@@ -15073,7 +15079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -20118,7 +20124,7 @@
         <v>820</v>
       </c>
       <c r="C147" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J147" t="s">
         <v>767</v>
@@ -20187,7 +20193,7 @@
         <v>833</v>
       </c>
       <c r="C150" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J150" t="s">
         <v>767</v>
@@ -20256,7 +20262,7 @@
         <v>846</v>
       </c>
       <c r="C153" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J153" t="s">
         <v>767</v>
@@ -20348,10 +20354,10 @@
         <v>171</v>
       </c>
       <c r="B157" s="45" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C157" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J157" t="s">
         <v>767</v>
@@ -20472,21 +20478,56 @@
         <v>869</v>
       </c>
       <c r="D162" s="45" t="s">
+        <v>894</v>
+      </c>
+      <c r="E162" s="45" t="s">
+        <v>895</v>
+      </c>
+      <c r="F162" s="45" t="s">
         <v>890</v>
       </c>
-      <c r="E162" s="45" t="s">
+      <c r="G162" s="45" t="s">
         <v>891</v>
-      </c>
-      <c r="F162" s="45" t="s">
-        <v>892</v>
-      </c>
-      <c r="G162" s="45" t="s">
-        <v>893</v>
       </c>
       <c r="H162" s="45" t="s">
         <v>896</v>
       </c>
       <c r="L162" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="45" t="s">
+        <v>897</v>
+      </c>
+      <c r="D163" t="s">
+        <v>898</v>
+      </c>
+      <c r="E163" t="s">
+        <v>898</v>
+      </c>
+      <c r="F163" t="s">
+        <v>898</v>
+      </c>
+      <c r="G163" t="s">
+        <v>898</v>
+      </c>
+      <c r="H163" t="s">
+        <v>898</v>
+      </c>
+      <c r="I163" t="s">
+        <v>898</v>
+      </c>
+      <c r="J163" t="s">
+        <v>767</v>
+      </c>
+      <c r="K163" t="s">
+        <v>78</v>
+      </c>
+      <c r="L163" s="50">
         <v>1</v>
       </c>
     </row>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46A3EBC-4A07-4911-8EB4-9F1500998DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3444935-6853-425A-817B-05CDE5888CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="906">
   <si>
     <t>Option 1</t>
   </si>
@@ -13869,6 +13869,27 @@
   </si>
   <si>
     <t>&lt;smiles&gt;CCO&lt;/smiles&gt;</t>
+  </si>
+  <si>
+    <t>(C) :&lt;img src="/images/M22C1.bmp" alt="C" class="h-24 inline-block" /&gt;</t>
+  </si>
+  <si>
+    <t>TEST-TEST-TEST</t>
+  </si>
+  <si>
+    <t>(B) : Molécule ramifiée &lt;img src="/images/CIRC1.png" alt="B" class="h-24 inline-block" /&gt;</t>
+  </si>
+  <si>
+    <t>(D) :&lt;img src="/images/CIRC1.png" alt="D" class="h-24 inline-block" /&gt;</t>
+  </si>
+  <si>
+    <t>(E) :&lt;img src="/images/CIRC1.png" alt="E" class="h-24 inline-block" /&gt;</t>
+  </si>
+  <si>
+    <t>(A) : Formule linéaire de l'anhydride butyrique &lt;img src="/images/CIRC2.png" alt="A" class="h-20 inline-block my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>(C) :&lt;img src="/images/CIRC2.png" alt="C" class="h-24 inline-block" /&gt;</t>
   </si>
 </sst>
 </file>
@@ -15079,7 +15100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L163"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -20531,6 +20552,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="164" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A164" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" s="45" t="s">
+        <v>900</v>
+      </c>
+      <c r="D164" s="45" t="s">
+        <v>904</v>
+      </c>
+      <c r="E164" s="45" t="s">
+        <v>901</v>
+      </c>
+      <c r="F164" s="45" t="s">
+        <v>905</v>
+      </c>
+      <c r="G164" s="45" t="s">
+        <v>902</v>
+      </c>
+      <c r="H164" s="45" t="s">
+        <v>903</v>
+      </c>
+      <c r="I164" s="45" t="s">
+        <v>899</v>
+      </c>
+      <c r="J164" t="s">
+        <v>767</v>
+      </c>
+      <c r="K164" t="s">
+        <v>78</v>
+      </c>
+      <c r="L164" s="50">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4711ADA-5CF6-4097-810D-1853BC139856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F93223-849B-4530-A519-3433D87E6271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="2444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3884" uniqueCount="2444">
   <si>
     <t>Option 1</t>
   </si>
@@ -9888,9 +9888,6 @@
     <t xml:space="preserve"> - Si $\theta$ est un nombre réel, alors $\cos ^{3} \theta$ est égal à :</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Si $x \in] 0 ; 1$, alors $\lim _{n \rightarrow+\infty}(1-x)^{n}(1+x)^{n}$ est égal à:</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Le domaine de définition de la fonction $f$ définie par $f(x)=\frac{1}{x-1} \ln \left(1+\frac{1}{x}\right)$ est :</t>
   </si>
   <si>
@@ -9900,34 +9897,16 @@
     <t xml:space="preserve"> - Si $z$ est un nombre complexe tel que : $\arg (z-1) \equiv \frac{2 \pi}{3}[2 \pi]$ et $\arg (z+1) \equiv \frac{\pi}{3}[2 \pi]$, alors $z$ est égal à :</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Si $z=1+e^{i \frac{\ell}{z}}$ où $\left.\theta \in\right]-\pi ; \pi[$, alors $|z|$ est égal à :</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - On a $\lim _{n \rightarrow+\infty}\left(\frac{n-1}{n+1}\right)^{2 n}$ est égale à :</t>
   </si>
   <si>
     <t xml:space="preserve"> - Si $(\forall x \in \mathbb{R}) ; f(x)=(x-5)(x-4)(x-3)(x-2)(x-1)$, alors $f^{\prime}(1)$ est égal à :</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Soit $f$ la fonction définie par : $f(x)=\frac{2 \ln x}{x\left(1+(\ln x)^{2}\right)}$. La primitive de $f$ sur $10 ;+\infty[$ qui s'annule en 1 est :</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - L'intégrale $\int_{0}^{1} \frac{2 t+3}{t+2} d t$ est égale à :</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Le plan complexe est rapporté à un repère orthonormé direct ( $O ; \ddot{u} ; \vec{v}$ ). L'ensemble des points $M$ d'affixe $z$ tel que : $z+\frac{1}{z} \in \mathbb{R}$ est : :</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Soit $\left(w_{n}\right)_{n \in N}$ la suite définie par: $w_{0}=\frac{1}{2}$ et $(\forall n \in N) ; w_{n+1}=\left(w_{n}-1\right)^{2}+1$. Si $\left(w_{n}\right)_{n \in N}$ est convergente alors $\lim _{n \rightarrow+\infty} w_{n}$ est égale à :</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Soit $a \in j 0$; $+\infty$ et $f$ la fonction définie par: $f(x)=1+x \ln \left(\sqrt{1+\frac{a}{x}}\right)$, alors $\lim _{x \rightarrow+\infty} f(x)$ est égale à :</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Soit $A B C$ un triangle isocèle en $A$ tel que : $A B=A B=10$. L'aire maximale du triangle $A B C$ est :</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Si $\left(\forall x \in \mathbb{R}_{+}^{\circ}\right) ; f(x)=x^{3}+3 \ln x+1$, alors le nombre dérivé $\left(f^{-1}\right)^{\prime}(2)$ est égal à :</t>
   </si>
   <si>
     <t xml:space="preserve"> - L'intégrale $\int_{0}^{1} \sin (x) e^{x} d x$ est égale à :</t>
@@ -10503,21 +10482,6 @@
     <t>$v_{moy}=3,5.10^{-3}mol.L^{-1}.min^{-1}$</t>
   </si>
   <si>
-    <t>$MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$ et $H_{2}O_{2(l)}/O_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$ et $Mn_{(aq)}^{2+}/MnO_{4(aq)}^{-}$</t>
-  </si>
-  <si>
-    <t>$O_{2(g)}/H_{2}O_{2(l)}$ et $O_{2(g)}/H_{2}O_{2(l)}$</t>
-  </si>
-  <si>
-    <t>$MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$ et $MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O_{(l)}/H_{2}O_{2(l)}$ et $H_{2}O/H_{(aq)}^{+}$</t>
-  </si>
-  <si>
     <t>$t_{1/2}=10~min$</t>
   </si>
   <si>
@@ -10785,25 +10749,12 @@
     <t>Le taux d'avancement final de la réaction est:</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Étude d'un comprimé d'ibuprofène (3 poins)&lt;/b&gt;&lt;/center&gt;
- On titre la solution (S) par hydroxyde de sodium $C_{B}=0,20~mol.L^{-1}$, $V_{B,E}=9,7~mL$, $M=206~g.mol^{-1}$.
- La masse d'ibuprofène contenue dans le comprimé étudié vaut :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Degré d'acidité d'un vinaigre  (5 poins)&lt;/b&gt;&lt;/center&gt;
- masse $m=10g$ ajout d'eau pour volume $V=100~mL$. On dose $V_{A}=20~mL$ par $(S_{B})$ d'hydroxyde de sodium $C_{B}=0,10~mol.L^{-1}$, $V_{B,E}=16,4mL$. </t>
-  </si>
-  <si>
     <t>Le degré d'acidité de ce vinaigre vaut :</t>
   </si>
   <si>
     <t>Les valeurs de l'avancement maximal de la réaction et du pH du milieu réactionnel pour le volume $V_{B}=8,2~mL$ sont :</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Solution aqueuse d'acide benzoïque   (5 poins)&lt;/b&gt;&lt;/center&gt;
- Le pH d'une solution aqueuse (S) d'acide benzoïque de volume $V=1L$ et de concentration $C=0,1mol.L^{-1}$, à $25^{\circ}C$, est $pH=2,6$. </t>
-  </si>
-  <si>
     <t>L'avancement final de la réaction de l'acide benzoïque avec l'eau est:</t>
   </si>
   <si>
@@ -10813,20 +10764,12 @@
     <t>La valeur de la constante d'acidité $K_{A}$ du couple $(C_{6}H_{5}COOH_{(aq)}/C_{6}H_{5}COO_{(aq)}^{-})$ est:</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Solution aqueuse d'ammoniac    (5 poins)&lt;/b&gt;&lt;/center&gt;
- $pH=10,3$, $log\frac{[NH_{3}]}{[NH_{4}^{+}]}=1,1$. </t>
-  </si>
-  <si>
     <t>Le taux d'avancement final de la réaction qui se produit a pour expression:</t>
   </si>
   <si>
     <t>La valeur de $pK_{A}$ du couple $(NH_{4(aq)}^{+}/NH_{3(aq)})$ vaut:</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Réaction d'acide lactique avec l'hydroxyde de sodium     (5 poins)&lt;/b&gt;&lt;/center&gt;
-On ajoute au volume $V_{A}=20mL$ d'acide lactique $C_{A}=3.10^{-2}mol.L^{-1}$, le volume $V_{B}=10mL$ d'hydroxyde de sodium $C_{B}=1,5.10^{-2}mol.L^{-1}$. Le pH du mélange est $pH=3,3$. </t>
-  </si>
-  <si>
     <t>L'avancement final $x_{f}$ de la réaction qui a eu lieu a pour expression:</t>
   </si>
   <si>
@@ -11116,49 +11059,6 @@
   </si>
   <si>
     <t>Un homme porteur d'un allèle lié au chromosome X le transmettra à :</t>
-  </si>
-  <si>
-    <t>Le tableau suivant présente les caractéristiques de trois types de fibres musculaires :
-| Caractéristiques | Type I | Type IIa | Type IIb |
-| Capacité oxydative | Forte | Intermédiaire | Faible |
-| Capacité glycolytique | Faible | Intermédiaire | Forte |
-| Densité des capillaires | Forte | Modérée | Faible |
-| Diamètre de la fibre | Faible | Intermédiaire | Grand |
-| Force produite | Faible | Modérée | Grande |
-Les fibres musculaires les plus adaptées aux efforts de longue durée sont :</t>
-  </si>
-  <si>
-    <t>Un animal se reproduisant sexuellement possède deux gènes non liés, l'un pour la forme de la tête (H) et l'autre pour la longueur de la queue (T). Son génotype est (H//h, T//t).
-Lequel des génotypes suivants est possible dans un gamète de cet organisme ?</t>
-  </si>
-  <si>
-    <t>On croise deux variétés de plantes de pois, l'une à fleurs axiales rouges et l'autre à fleurs terminales blanches. Tous les individus F1 ont des fleurs axiales rouges. Supposant un assortiment indépendant, sur 64 individus de la génération F2, combien d'entre eux devraient avoir des fleurs terminales rouges ?</t>
-  </si>
-  <si>
-    <t>Certaines plantes peuvent résister à des froids extrêmes. Pour expliquer ce phénomène on propose les documents suivants :
-Document 1 : Deux chaînes respiratoires chez certaines plantes. Le cytochrome c oxydase (CCO) et l'oxydase alternative (AOX) sont des accepteurs d'électrons de chaînes respiratoires intervenant dans la réduction du dioxygène en molécule d'eau.
-Document 2 : Couplage énergétique de deux chaînes respiratoires différentes.
-Pour résister au froid extrême :</t>
-  </si>
-  <si>
-    <t>La digestion d'un ADN par une enzyme de restriction a permis d'obtenir 4 fragments A, B, C et D de tailles différentes -voir figure-. (↓ : Site d'action de l'enzyme)
-Le profil attendu lors de la séparation de ces fragments par électrophorèse sur gel d'agarose, est le :</t>
-  </si>
-  <si>
-    <t>Chez les oiseaux, le sexe est déterminé par le couple chromosomique ZW. Les mâles sont ZZ et les femelles sont ZW. Un allèle récessif létal qui provoque la mort de l'embryon est parfois présent sur le chromosome Z chez les pigeons. Quel serait le rapport des sexes dans la progéniture d'un croisement entre un mâle hétérozygote portant l'allèle létal et une femelle normale ?</t>
-  </si>
-  <si>
-    <t>L'emplacement relatif de quatre gènes sur un chromosome peut être cartographié à partir des données suivantes sur les fréquences de crossing-over.
-Fréquence de crossing-over entre les gènes : B et C 5 % ; B et A 30 % ; A et D 15 % ; C et A 25 % ; C et D 40 %.
-Laquelle des propositions suivantes représentent les positions relatives de ces quatre gènes sur le chromosome ?</t>
-  </si>
-  <si>
-    <t>L'arbre généalogique ci-dessous concerne une famille dont certains membres souffrent d'une anomalie de la structure du cuir chevelu appelée « cheveux laineux ». Sachant que l'individu I-1 est homozygote.
-En se basant sur cet arbre généalogique :</t>
-  </si>
-  <si>
-    <t>Dans une population en équilibre de Hardy-Weinberg, la fréquence d'un allèle récessif pour un caractère héréditaire donné est de 0,20.
-Le pourcentage des individus présentant le caractère dominant à la génération suivante est :</t>
   </si>
   <si>
     <t>$x_f=4.10^{-3}$ mol</t>
@@ -13345,30 +13245,144 @@
 &lt;br&gt;&lt;b&gt;Le noyau de Radium ${ }_{88}^{226} R a$ se désintègre en donnant un noyau fils ${ }_{x}^{y} R n$ et une particule $\alpha$.&lt;/b&gt;</t>
   </si>
   <si>
+    <t>&lt;center&gt;&lt;b&gt;Réaction d'acide lactique avec l'hydroxyde de sodium     (5 poins)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;&lt;b&gt;On ajoute au volume $V_{A}=20mL$ d'une solution acqueuse d'acide lactique $(C_{3}H_{6}O_{3})$ de concentration $C_{A}=3.10^{-2}mol.L^{-1}$, le volume $V_{B}=10mL$ d'une solution acqueuse d'hydroxyde de sodium de concentration $C_{B}=1,5.10^{-2}mol.L^{-1}$. Le pH du mélange est $pH=3,3$.&lt;/b&gt;
+&lt;br&gt;&lt;b&gt; Données : $10^{-10,7} = 2 \cdot 10^{-11}$&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Solution aqueuse d'acide benzoïque   (5 poins)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; Le pH d'une solution aqueuse (S) d'acide benzoïque de volume $V=1L$ et de concentration $C=0,1mol.L^{-1}$, à $25^{\circ}C$, est $pH=2,6$.
+&lt;br&gt;&lt;b&gt;Données :&lt;/b&gt; $10^{0,8} = 6,3$; $\quad$; $10^{0,4} = 2,5$; $\quad$ $10^{-1,6} \approx 2,5 \cdot 10^{-2}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Degré d'acidité d'un vinaigre  (5 poins)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On prend la masse $m=10g$ d'un vinaigre commercial, et on y ajoute de l'eau pour obtenir une solution aqueuse $(S_A)$ d'acide éthanoïque $CH_3COOH_{(aq)}$ de volume $V=100~mL$.
+&lt;br&gt;On dose $V_A=20~mL$ de la solution $(S_A)$ par une solution aqueuse $(S_B)$ d'hydroxyde de sodium de concentration $C_B=0,10~mol.L^{-1}$. 
+&lt;br&gt;Le volume versé à l'équivalence est $V_{B,E}=16,4~mL$. 
+&lt;br&gt;&lt;b&gt;Données: &lt;/b&gt;
+&lt;br&gt;&lt;b&gt;Le degré d'acidité d'un vinaigre commercial représente la masse d'acide éthanoïque pur en (g) contenu dans 100 g de vinaigre.&lt;/b&gt;
+&lt;br&gt;&lt;b&gt; $M(CH_3COOH)=60~g.mol^{-1}$. $pK_A(CH_3COOH_{(aq)}/CH_3COO^-_{(aq)})=4,8$.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Étude d'un comprimé d'ibuprofène (3 poins)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On dissout un comprimé d'ibuprofène dans un volume V d'eau pour obtenir une solution aqueuse (S). 
+&lt;br&gt;On titre la solution (S) par une solution aqueuse d'hydroxyde de sodium de concentration $C_B=0,20~mol.L^{-1}$.
+&lt;br&gt; Le volume versé à l'équivalence est $V_{B,E}=9,7~mL$.
+&lt;br&gt;&lt;b&gt;Donnée: $M(ibuprofene)=206~g.mol^{-1}$.&lt;/b&gt;
+&lt;br&gt;&lt;b&gt;La masse d'ibuprofène contenue dans le comprimé étudié vaut :&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Solution aqueuse d'acide éthanoïque (4 poins)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On considère une solution aqueuse (S) d'acide éthanoïque de concentration $C=10^{-2}mol.L^{-1}$. 
+&lt;br&gt;La mesure de la conductivité de la solution (S) a donné $\sigma=1,56.10^{-2}S.m^{-1}$.
+&lt;br&gt;&lt;b&gt;Données :&lt;/b&gt; $\lambda_{H_3O^+}=35~mS.m^2.mol^{-1}$ ; $\quad$ $\lambda_{CH_3COO^-}=4~mS.m^2.mol^{-1}$ ; $\quad$ $\log 2=0,3$. 
+&lt;br&gt;&lt;br&gt;On définit le taux d'avancement final par la relation: $	au=\frac{x_f}{x_{max}}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Evolution temporel d'un système chimique (9 poins)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;&lt;br&gt; À $t_{0}=0$ on ajoute un volume d'eau oxygénée à un volume d'une solution de permanganate de potassium acidifié. 
+&lt;br&gt;&lt;b&gt;L'équation: $5H_{2}O_{2(l)}+2MnO_{4(aq)}^{-}+6H_{(aq)}^{+}\rightarrow5O_{2(g)}+2Mn_{(aq)}^{2+}+8H_{2}O_{(l)}$.&lt;/b&gt;
+&lt;br&gt;&lt;br&gt;À $t_0 = 0$, on ajoute un volume d'eau oxygénée à un volume d'une solution de permanganate de potassium acidifié. L'eau oxygénée $\text{H}_2\text{O}_{2(l)}$ est oxydée par les ions permanganate $\text{MnO}_{4(aq)}^-$ selon l'équation :
+$$5\text{H}_2\text{O}_{2(l)} + 2\text{MnO}_{4(aq)}^- + 6\text{H}_{(aq)}^+ \rightarrow 5\text{O}_{2(g)} + 2\text{Mn}_{(aq)}^{2+} + 8\text{H}_2\text{O}_{(l)}$$
+Le tableau ci-dessous présente l'évolution temporelle de la concentration des ions $\text{Mn}_{(aq)}^{2+}$.
+&lt;br&gt;&lt;b&gt;&lt;img src="/images/CH2020Q44.png" alt="A" class="h-20 inline-block ml-4 my-1" /&gt;&lt;/b&gt;
+&lt;br&gt;&lt;b&gt;Données :&lt;/b&gt;
+&lt;br&gt;&lt;b&gt;Volume molaire : $V_m = 24 \text{ L}\cdot\text{mol}^{-1}$&lt;/b&gt;;  \vspace{0.2cm}   Volume du mélange : $V = 10 \text{ mL}$   ; \vspace{0.2cm}     $\text{H}_2\text{O}_{2(l)}$ : réactif limitant.</t>
+  </si>
+  <si>
+    <t>$MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$ $\quad$ et $\quad$ $H_{2}O_{2(l)}/O_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$ $\quad$ et $\quad$ $Mn_{(aq)}^{2+}/MnO_{4(aq)}^{-}$</t>
+  </si>
+  <si>
+    <t>$O_{2(g)}/H_{2}O_{2(l)}$ $\quad$ et $\quad$ $O_{2(g)}/H_{2}O_{2(l)}$</t>
+  </si>
+  <si>
+    <t>$MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$ $\quad$ et $\quad$ $MnO_{4(aq)}^{-}/Mn_{(aq)}^{2+}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O_{(l)}/H_{2}O_{2(l)}$ $\quad$ et $\quad$ $H_{2}O/H_{(aq)}^{+}$</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt; Suivi temporel d'une transformation chimique (6 points)&lt;/b&gt;&lt;/center&gt;
 On introduit dans un ballon, une quantité de poudre de Zinc, et on y verse à un volume $V=75mL$ d'une solution aqueuse d'acide sulfurique. La réaction qui se produit a pour équation:
 &lt;br&gt;&lt;b&gt; $Zn_{(s)}+2H_{3}O_{(aq)}^{+}\longrightarrow Zn_{(aq)}^{2+}+H_{2(s)}+2H_{2}O_{(l)}$.&lt;/b&gt;
-La courbe ci-contre représente les variations de l'avancement $x$ de la réaction en fonction du temps.
-&lt;img src="/images/CH2020Q1.png" alt="A" class="h-20 inline-block my-1" /&gt;
+&lt;br&gt;&lt;b&gt;La courbe ci-contre représente les variations de l'avancement $x$ de la réaction en fonction du temps.&lt;/b&gt;
+&lt;img src="/images/CH2020Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;&lt;b&gt;Données :&lt;/b&gt;
 La vitesse volumique moyenne d'une réaction a pour expression : $v_{\text{moy}} = \frac{1}{V} \cdot \frac{\Delta x}{\Delta t}$ (avec $V$ le volume total du mélange).
-&lt;br&gt;&lt;b&gt;$75 \times 45 = 3375$&lt;/b&gt;;  $3375} \times 35 approx 1,19 \cdot 10^{5}$
-\end{itemize}</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Solution aqueuse d'acide éthanoïque (4 poins)&lt;/b&gt;&lt;/center&gt;
-On considère une solution acqueuse (S) d'acide éthanoïque de concentration $C=10^{-2}mol.L^{-1}$, conductivité $\sigma=1,56.10^{-2}S.m^{-1}$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Evolution temporel d'un système chimique (9 poins)&lt;/b&gt;&lt;/center&gt;
- À $t_{0}=0$ on ajoute un volume d'eau oxygénée à un volume d'une solution de permanganate de potassium acidifié. 
-&lt;br&gt;&lt;b&gt;L'équation: $5H_{2}O_{2(l)}+2MnO_{4(aq)}^{-}+6H_{(aq)}^{+}\rightarrow5O_{2(g)}+2Mn_{(aq)}^{2+}+8H_{2}O_{(l)}$.&lt;/b&gt;
-&lt;br&gt;&lt;b&gt;À $t_0 = 0$, on ajoute un volume d'eau oxygénée à un volume d'une solution de permanganate de potassium acidifié. L'eau oxygénée $\text{H}_2\text{O}_{2(l)}$ est oxydée par les ions permanganate $\text{MnO}_{4(aq)}^-$ selon l'équation :
-$$5\text{H}_2\text{O}_{2(l)} + 2\text{MnO}_{4(aq)}^- + 6\text{H}_{(aq)}^+ \rightarrow 5\text{O}_{2(g)} + 2\text{Mn}_{(aq)}^{2+} + 8\text{H}_2\text{O}_{(l)}$$
-Le tableau ci-dessous présente l'évolution temporelle de la concentration des ions $\text{Mn}_{(aq)}^{2+}$.
-&lt;br&gt;&lt;b&gt;&lt;img src="/images/CH2020Q44.png" alt="A" class="h-20 inline-block my-1" /&gt;&lt;/b&gt;
-&lt;br&gt;&lt;b&gt;Données :&lt;/b&gt;
-&lt;br&gt;&lt;b&gt;Volume molaire : $V_m = 24 \text{ L}\cdot\text{mol}^{-1}$&lt;/b&gt;   ;   Volume du mélange : $V = 10 \text{ mL}$   ;      $\text{H}_2\text{O}_{2(l)}$ : réactif limitant.</t>
+&lt;br&gt;&lt;b&gt;$75 \times 45 = 3375$ $\quad$ $3375 \times 35 \approx 1,19 \cdot 10^{5}$&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Solution aqueuse d'ammoniac    (5 poins)&lt;/b&gt;&lt;/center&gt;
+La mesure du pH d'une solution acquesue (S) d'ammoniac de concentration C, a donné  $pH=10,3$ $\quad$ $log\frac{[NH_{3}]}{[NH_{4}^{+}]}=1,1$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Si $x \in] 0 ; 1[$, alors $\lim _{n \rightarrow+\infty}(1-x)^{n}(1+x)^{n}$ est égal à:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Si $z = 1 + e^{i\frac{\theta}{2}}$ où $\left.\theta \in\right]-\pi ; \pi[$, alors $|z|$ est égal à :</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Soit $f$ la fonction définie par : $f(x)=\frac{2 \ln x}{x\left(1+(\ln x)^{2}\right)}$. La primitive de $f$ sur $]0 ;+\infty[$ qui s'annule en 1 est :</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Le plan complexe est rapporté à un repère orthonormé direct ( $O ; \vec{u} ; \vec{v}$ ). L'ensemble des points $M$ d'affixe $z$ tel que : $z+\frac{1}{z} \in \mathbb{R}$ est : :</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Soit $a \in ]0$; $+\infty[$ et $f$ la fonction définie par: $f(x)=1+x \ln \left(\sqrt{1+\frac{a}{x}}\right)$, alors $\lim _{x \rightarrow+\infty} f(x)$ est égale à :</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Soit $A B C$ un triangle isocèle en $A$ tel que : $A B=A C=10$. L'aire maximale du triangle $A B C$ est :</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Si $\left(\forall x \in \mathbb{R}_{+}) ; f(x)=x^{3}+3 \ln x+1$, alors le nombre dérivé $\left(f^{-1}\right)^{\prime}(2)$ est égal à :</t>
+  </si>
+  <si>
+    <t>Le tableau suivant présente les caractéristiques de trois types de fibres musculaires :
+&lt;br&gt;&lt;img src="/images/SVT2021Q11.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Les fibres musculaires les plus adaptées aux efforts de longue durée sont :</t>
+  </si>
+  <si>
+    <t>Un animal se reproduisant sexuellement possède deux gènes non liés, l'un pour la forme de la tête (H) et l'autre pour la longueur de la queue (T). Son génotype est (H//h, T//t).
+&lt;br&gt;Lequel des génotypes suivants est possible dans un gamète de cet organisme ?</t>
+  </si>
+  <si>
+    <t>On croise deux variétés de plantes de pois, l'une à fleurs axiales rouges et l'autre à fleurs terminales blanches. Tous les individus F1 ont des fleurs axiales rouges. 
+&lt;br&gt;Supposant un assortiment indépendant, sur 64 individus de la génération F2, combien d'entre eux devraient avoir des fleurs terminales rouges ?</t>
+  </si>
+  <si>
+    <t>Certaines plantes peuvent résister à des froids extrêmes. Pour expliquer ce phénomène on propose les documents suivants :
+&lt;br&gt;Document 1 : Deux chaînes respiratoires chez certaines plantes. Le cytochrome c oxydase (CCO) et l'oxydase alternative (AOX) sont des accepteurs d'électrons de chaînes respiratoires intervenant dans la réduction du dioxygène en molécule d'eau.
+&lt;br&gt;&lt;img src="/images/SVT2021Q15A.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Document 2 : Couplage énergétique de deux chaînes respiratoires différentes.
+&lt;br&gt;&lt;img src="/images/SVT2021Q15B.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Pour résister au froid extrême :</t>
+  </si>
+  <si>
+    <t>La digestion d'un ADN par une enzyme de restriction a permis d'obtenir 4 fragments A, B, C et D de tailles différentes -voir figure-. (↓ : Site d'action de l'enzyme)
+&lt;br&gt;&lt;img src="/images/SVT2021Q16.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Le profil attendu lors de la séparation de ces fragments par électrophorèse sur gel d'agarose, est le :</t>
+  </si>
+  <si>
+    <t>Chez les oiseaux, le sexe est déterminé par le couple chromosomique ZW. Les mâles sont ZZ et les femelles sont ZW. 
+&lt;br&gt;Un allèle récessif létal qui provoque la mort de l'embryon est parfois présent sur le chromosome Z chez les pigeons. 
+&lt;br&gt;Quel serait le rapport des sexes dans la progéniture d'un croisement entre un mâle hétérozygote portant l'allèle létal et une femelle normale ?</t>
+  </si>
+  <si>
+    <t>L'emplacement relatif de quatre gènes sur un chromosome peut être cartographié à partir des données suivantes sur les fréquences de crossing-over.
+&lt;br&gt;Fréquence de crossing-over entre les gènes : B et C 5 % ;$\quad$ B et A 30 % ;$\quad$ A et D 15 % ; $\quad$ C et A 25 % ;$\quad$ C et D 40 %.
+&lt;br&gt;Laquelle des propositions suivantes représentent les positions relatives de ces quatre gènes sur le chromosome ?</t>
+  </si>
+  <si>
+    <t>L'arbre généalogique ci-dessous concerne une famille dont certains membres souffrent d'une anomalie de la structure du cuir chevelu appelée « cheveux laineux ». Sachant que l'individu I-1 est homozygote.
+&lt;br&gt;&lt;img src="/images/SVT2021Q19.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;En se basant sur cet arbre généalogique :</t>
+  </si>
+  <si>
+    <t>Dans une population en équilibre de Hardy-Weinberg, la fréquence d'un allèle récessif pour un caractère héréditaire donné est de 0,20.
+&lt;br&gt;&lt;br&gt;Le pourcentage des individus présentant le caractère dominant à la génération suivante est :</t>
   </si>
 </sst>
 </file>
@@ -14499,25 +14513,27 @@
         <v>98</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="46" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
       <c r="H2" s="46" t="s">
-        <v>1425</v>
-      </c>
-      <c r="I2" s="2"/>
+        <v>1418</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>1418</v>
+      </c>
       <c r="J2" s="18" t="s">
         <v>11</v>
       </c>
@@ -14533,25 +14549,27 @@
         <v>98</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1522</v>
+        <v>1515</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="46" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
       <c r="G3" s="46" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
       <c r="H3" s="46" t="s">
-        <v>1430</v>
-      </c>
-      <c r="I3" s="2"/>
+        <v>1423</v>
+      </c>
+      <c r="I3" s="46" t="s">
+        <v>1421</v>
+      </c>
       <c r="J3" s="18" t="s">
         <v>11</v>
       </c>
@@ -14567,25 +14585,27 @@
         <v>98</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="46" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>1435</v>
-      </c>
-      <c r="I4" s="2"/>
+        <v>1428</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>1425</v>
+      </c>
       <c r="J4" s="18" t="s">
         <v>11</v>
       </c>
@@ -14601,25 +14621,27 @@
         <v>98</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>1524</v>
+        <v>1517</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="46" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>1440</v>
-      </c>
-      <c r="I5" s="2"/>
+        <v>1433</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>1429</v>
+      </c>
       <c r="J5" s="18" t="s">
         <v>11</v>
       </c>
@@ -14630,30 +14652,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="60">
+    <row r="6" spans="1:12" ht="75">
       <c r="A6" s="19" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="46" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>1445</v>
-      </c>
-      <c r="I6" s="2"/>
+        <v>1438</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>1438</v>
+      </c>
       <c r="J6" s="18" t="s">
         <v>11</v>
       </c>
@@ -14669,25 +14693,27 @@
         <v>98</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="46" t="s">
-        <v>1446</v>
+        <v>1439</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>1447</v>
+        <v>1440</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
       <c r="G7" s="46" t="s">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>1450</v>
-      </c>
-      <c r="I7" s="2"/>
+        <v>1443</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>1441</v>
+      </c>
       <c r="J7" s="18" t="s">
         <v>11</v>
       </c>
@@ -14703,25 +14729,27 @@
         <v>98</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="46" t="s">
-        <v>1451</v>
+        <v>1444</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>1452</v>
+        <v>1445</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>1453</v>
+        <v>1446</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>1455</v>
-      </c>
-      <c r="I8" s="2"/>
+        <v>1448</v>
+      </c>
+      <c r="I8" s="46" t="s">
+        <v>1448</v>
+      </c>
       <c r="J8" s="18" t="s">
         <v>11</v>
       </c>
@@ -14737,25 +14765,27 @@
         <v>98</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="46" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I9" s="2"/>
+        <v>1453</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>1453</v>
+      </c>
       <c r="J9" s="18" t="s">
         <v>11</v>
       </c>
@@ -14771,25 +14801,27 @@
         <v>98</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>1529</v>
+        <v>1522</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="46" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>1465</v>
-      </c>
-      <c r="I10" s="2"/>
+        <v>1458</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>1454</v>
+      </c>
       <c r="J10" s="18" t="s">
         <v>11</v>
       </c>
@@ -14805,25 +14837,27 @@
         <v>98</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>1530</v>
+        <v>1523</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="46" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>1470</v>
-      </c>
-      <c r="I11" s="2"/>
+        <v>1463</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>1463</v>
+      </c>
       <c r="J11" s="18" t="s">
         <v>11</v>
       </c>
@@ -14839,25 +14873,27 @@
         <v>98</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>2413</v>
+        <v>2387</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="46" t="s">
-        <v>1471</v>
+        <v>1464</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>1472</v>
+        <v>1465</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>1475</v>
-      </c>
-      <c r="I12" s="2"/>
+        <v>1468</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>1466</v>
+      </c>
       <c r="J12" s="18" t="s">
         <v>11</v>
       </c>
@@ -14873,25 +14909,27 @@
         <v>98</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>2407</v>
+        <v>2381</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="46" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
       <c r="G13" s="46" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>1480</v>
-      </c>
-      <c r="I13" s="2"/>
+        <v>1473</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>1472</v>
+      </c>
       <c r="J13" s="18" t="s">
         <v>11</v>
       </c>
@@ -14907,25 +14945,27 @@
         <v>98</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>2408</v>
+        <v>2382</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="46" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>1482</v>
+        <v>1475</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>1485</v>
-      </c>
-      <c r="I14" s="2"/>
+        <v>1478</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>1474</v>
+      </c>
       <c r="J14" s="18" t="s">
         <v>11</v>
       </c>
@@ -14941,25 +14981,27 @@
         <v>98</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="46" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="G15" s="46" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>1490</v>
-      </c>
-      <c r="I15" s="2"/>
+        <v>1483</v>
+      </c>
+      <c r="I15" s="46" t="s">
+        <v>1482</v>
+      </c>
       <c r="J15" s="18" t="s">
         <v>11</v>
       </c>
@@ -14975,25 +15017,27 @@
         <v>98</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>2409</v>
+        <v>2383</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="46" t="s">
-        <v>1491</v>
+        <v>1484</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
       <c r="G16" s="46" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>1495</v>
-      </c>
-      <c r="I16" s="2"/>
+        <v>1488</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>1484</v>
+      </c>
       <c r="J16" s="18" t="s">
         <v>11</v>
       </c>
@@ -15009,25 +15053,27 @@
         <v>98</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>1532</v>
+        <v>1525</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="46" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
       <c r="G17" s="46" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>1500</v>
-      </c>
-      <c r="I17" s="2"/>
+        <v>1493</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>1493</v>
+      </c>
       <c r="J17" s="18" t="s">
         <v>11</v>
       </c>
@@ -15043,25 +15089,27 @@
         <v>98</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>2410</v>
+        <v>2384</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="46" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>1502</v>
+        <v>1495</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>1503</v>
+        <v>1496</v>
       </c>
       <c r="G18" s="46" t="s">
-        <v>1504</v>
+        <v>1497</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>1505</v>
-      </c>
-      <c r="I18" s="2"/>
+        <v>1498</v>
+      </c>
+      <c r="I18" s="46" t="s">
+        <v>1496</v>
+      </c>
       <c r="J18" s="18" t="s">
         <v>11</v>
       </c>
@@ -15077,25 +15125,27 @@
         <v>98</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>2411</v>
+        <v>2385</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="46" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>1507</v>
+        <v>1500</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="G19" s="46" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>1510</v>
-      </c>
-      <c r="I19" s="2"/>
+        <v>1503</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>1499</v>
+      </c>
       <c r="J19" s="18" t="s">
         <v>11</v>
       </c>
@@ -15111,25 +15161,27 @@
         <v>98</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>2405</v>
+        <v>2379</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="46" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>1513</v>
+        <v>1506</v>
       </c>
       <c r="G20" s="46" t="s">
-        <v>1514</v>
+        <v>1507</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I20" s="2"/>
+        <v>1508</v>
+      </c>
+      <c r="I20" s="46" t="s">
+        <v>1504</v>
+      </c>
       <c r="J20" s="18" t="s">
         <v>11</v>
       </c>
@@ -15145,25 +15197,27 @@
         <v>98</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>2412</v>
+        <v>2386</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="46" t="s">
-        <v>1516</v>
+        <v>1509</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>1517</v>
+        <v>1510</v>
       </c>
       <c r="F21" s="46" t="s">
-        <v>1518</v>
+        <v>1511</v>
       </c>
       <c r="G21" s="46" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
       <c r="H21" s="46" t="s">
-        <v>1520</v>
-      </c>
-      <c r="I21" s="2"/>
+        <v>1513</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>1513</v>
+      </c>
       <c r="J21" s="18" t="s">
         <v>11</v>
       </c>
@@ -15179,7 +15233,7 @@
         <v>99</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>2414</v>
+        <v>2388</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="2"/>
@@ -15201,11 +15255,11 @@
         <v>100</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>2415</v>
+        <v>2389</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="13" t="s">
-        <v>2427</v>
+        <v>2401</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>787</v>
@@ -15219,7 +15273,9 @@
       <c r="H23" s="13" t="s">
         <v>790</v>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="13" t="s">
+        <v>789</v>
+      </c>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="19">
@@ -15249,7 +15305,9 @@
       <c r="H24" s="13" t="s">
         <v>795</v>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="13" t="s">
+        <v>794</v>
+      </c>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="19">
@@ -15279,7 +15337,9 @@
       <c r="H25" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="13" t="s">
+        <v>799</v>
+      </c>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="19">
@@ -15291,7 +15351,7 @@
         <v>99</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2416</v>
+        <v>2390</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -15313,7 +15373,7 @@
         <v>100</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>2417</v>
+        <v>2391</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="13" t="s">
@@ -15331,7 +15391,9 @@
       <c r="H27" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="I27" s="2"/>
+      <c r="I27" s="13" t="s">
+        <v>803</v>
+      </c>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="19">
@@ -15361,7 +15423,9 @@
       <c r="H28" s="13" t="s">
         <v>810</v>
       </c>
-      <c r="I28" s="2"/>
+      <c r="I28" s="13" t="s">
+        <v>807</v>
+      </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="19">
@@ -15373,7 +15437,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2419</v>
+        <v>2393</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -15413,14 +15477,16 @@
       <c r="H30" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="I30" s="2"/>
+      <c r="I30" s="2" t="s">
+        <v>813</v>
+      </c>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" ht="30">
       <c r="A31" s="19" t="s">
         <v>100</v>
       </c>
@@ -15440,10 +15506,12 @@
       <c r="G31" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>2418</v>
-      </c>
-      <c r="I31" s="2"/>
+      <c r="H31" s="13" t="s">
+        <v>2392</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>816</v>
+      </c>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="19">
@@ -15455,7 +15523,7 @@
         <v>100</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2420</v>
+        <v>2394</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
@@ -15473,7 +15541,9 @@
       <c r="H32" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="I32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>820</v>
+      </c>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
       <c r="L32" s="19">
@@ -15485,7 +15555,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2421</v>
+        <v>2395</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -15507,7 +15577,7 @@
         <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2422</v>
+        <v>2396</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -15525,7 +15595,9 @@
       <c r="H34" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="I34" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>827</v>
+      </c>
       <c r="J34" s="18"/>
       <c r="K34" s="18"/>
       <c r="L34" s="19">
@@ -15537,7 +15609,7 @@
         <v>100</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2423</v>
+        <v>2397</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
@@ -15555,7 +15627,9 @@
       <c r="H35" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="I35" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>832</v>
+      </c>
       <c r="J35" s="18"/>
       <c r="K35" s="18"/>
       <c r="L35" s="19">
@@ -15567,7 +15641,7 @@
         <v>99</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>2428</v>
+        <v>2402</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -15589,7 +15663,7 @@
         <v>100</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2424</v>
+        <v>2398</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
@@ -15607,7 +15681,9 @@
       <c r="H37" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="I37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>836</v>
+      </c>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
       <c r="L37" s="19">
@@ -15619,7 +15695,7 @@
         <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2425</v>
+        <v>2399</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
@@ -15637,7 +15713,9 @@
       <c r="H38" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="I38" s="2"/>
+      <c r="I38" s="2" t="s">
+        <v>843</v>
+      </c>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
       <c r="L38" s="19">
@@ -15649,7 +15727,7 @@
         <v>99</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2426</v>
+        <v>2400</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -15671,7 +15749,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>2429</v>
+        <v>2403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="13" t="s">
@@ -15689,7 +15767,9 @@
       <c r="H40" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="I40" s="2"/>
+      <c r="I40" s="13" t="s">
+        <v>848</v>
+      </c>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
       <c r="L40" s="18"/>
@@ -15699,7 +15779,7 @@
         <v>100</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>2430</v>
+        <v>2404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="13" t="s">
@@ -15717,7 +15797,9 @@
       <c r="H41" s="13" t="s">
         <v>854</v>
       </c>
-      <c r="I41" s="2"/>
+      <c r="I41" s="13" t="s">
+        <v>851</v>
+      </c>
       <c r="J41" s="18"/>
       <c r="K41" s="18"/>
       <c r="L41" s="18"/>
@@ -15727,25 +15809,27 @@
         <v>98</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>2431</v>
+        <v>2405</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="13" t="s">
-        <v>2432</v>
+        <v>2406</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>2433</v>
+        <v>2407</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>2434</v>
+        <v>2408</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>2435</v>
+        <v>2409</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>2436</v>
-      </c>
-      <c r="I42" s="2"/>
+        <v>2410</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>2407</v>
+      </c>
       <c r="J42" s="18" t="s">
         <v>9</v>
       </c>
@@ -15761,7 +15845,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>2437</v>
+        <v>2411</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -15783,7 +15867,7 @@
         <v>100</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>2438</v>
+        <v>2412</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
@@ -15801,7 +15885,9 @@
       <c r="H44" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="I44" s="2"/>
+      <c r="I44" s="2" t="s">
+        <v>856</v>
+      </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
       <c r="L44" s="18">
@@ -15813,7 +15899,7 @@
         <v>100</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>2439</v>
+        <v>2413</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
@@ -15831,7 +15917,9 @@
       <c r="H45" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="I45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>862</v>
+      </c>
       <c r="J45" s="18"/>
       <c r="K45" s="18"/>
       <c r="L45" s="18">
@@ -15861,7 +15949,9 @@
       <c r="H46" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="I46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>868</v>
+      </c>
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
       <c r="L46" s="18">
@@ -15873,7 +15963,7 @@
         <v>99</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>2440</v>
+        <v>2414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -15913,7 +16003,9 @@
       <c r="H48" s="13" t="s">
         <v>874</v>
       </c>
-      <c r="I48" s="2"/>
+      <c r="I48" s="13" t="s">
+        <v>873</v>
+      </c>
       <c r="J48" s="18"/>
       <c r="K48" s="18"/>
       <c r="L48" s="18">
@@ -15943,19 +16035,21 @@
       <c r="H49" s="13" t="s">
         <v>879</v>
       </c>
-      <c r="I49" s="2"/>
+      <c r="I49" s="13" t="s">
+        <v>876</v>
+      </c>
       <c r="J49" s="18"/>
       <c r="K49" s="18"/>
       <c r="L49" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="285">
+    <row r="50" spans="1:12" ht="270">
       <c r="A50" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -15977,25 +16071,27 @@
         <v>100</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="46" t="s">
-        <v>1533</v>
+        <v>1526</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>1534</v>
+        <v>1527</v>
       </c>
       <c r="F51" s="46" t="s">
-        <v>1535</v>
+        <v>1528</v>
       </c>
       <c r="G51" s="46" t="s">
-        <v>1536</v>
+        <v>1529</v>
       </c>
       <c r="H51" s="46" t="s">
-        <v>1537</v>
-      </c>
-      <c r="I51" s="2"/>
+        <v>1530</v>
+      </c>
+      <c r="I51" s="46" t="s">
+        <v>1526</v>
+      </c>
       <c r="J51" s="18"/>
       <c r="K51" s="18"/>
       <c r="L51" s="18">
@@ -16007,25 +16103,27 @@
         <v>100</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>1633</v>
+        <v>1621</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="46" t="s">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="G52" s="46" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>1542</v>
-      </c>
-      <c r="I52" s="2"/>
+        <v>1535</v>
+      </c>
+      <c r="I52" s="46" t="s">
+        <v>1532</v>
+      </c>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
       <c r="L52" s="18">
@@ -16037,37 +16135,39 @@
         <v>100</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>1634</v>
+        <v>1622</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="46" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="F53" s="46" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="G53" s="46" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="H53" s="46" t="s">
-        <v>1547</v>
-      </c>
-      <c r="I53" s="2"/>
+        <v>1540</v>
+      </c>
+      <c r="I53" s="46" t="s">
+        <v>1540</v>
+      </c>
       <c r="J53" s="18"/>
       <c r="K53" s="18"/>
       <c r="L53" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="375">
+    <row r="54" spans="1:12" ht="405">
       <c r="A54" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B54" s="46" t="s">
-        <v>2443</v>
+        <v>2420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -16084,30 +16184,32 @@
       </c>
       <c r="L54" s="18"/>
     </row>
-    <row r="55" spans="1:12" ht="60">
+    <row r="55" spans="1:12" ht="75">
       <c r="A55" s="18" t="s">
         <v>100</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>1635</v>
+        <v>1623</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="46" t="s">
-        <v>1548</v>
+        <v>2421</v>
       </c>
       <c r="E55" s="46" t="s">
-        <v>1549</v>
+        <v>2422</v>
       </c>
       <c r="F55" s="46" t="s">
-        <v>1550</v>
+        <v>2423</v>
       </c>
       <c r="G55" s="46" t="s">
-        <v>1551</v>
+        <v>2424</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>1552</v>
-      </c>
-      <c r="I55" s="2"/>
+        <v>2425</v>
+      </c>
+      <c r="I55" s="46" t="s">
+        <v>2422</v>
+      </c>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
       <c r="L55" s="18">
@@ -16119,25 +16221,27 @@
         <v>100</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>1637</v>
+        <v>1625</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="46" t="s">
-        <v>1553</v>
+        <v>1541</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>1554</v>
+        <v>1542</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>1555</v>
+        <v>1543</v>
       </c>
       <c r="G56" s="46" t="s">
-        <v>1556</v>
+        <v>1544</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>1538</v>
-      </c>
-      <c r="I56" s="2"/>
+        <v>1531</v>
+      </c>
+      <c r="I56" s="46" t="s">
+        <v>1542</v>
+      </c>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
       <c r="L56" s="18">
@@ -16149,25 +16253,27 @@
         <v>100</v>
       </c>
       <c r="B57" s="46" t="s">
-        <v>1638</v>
+        <v>1626</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="46" t="s">
-        <v>1557</v>
+        <v>1545</v>
       </c>
       <c r="E57" s="46" t="s">
-        <v>1558</v>
+        <v>1546</v>
       </c>
       <c r="F57" s="46" t="s">
-        <v>1559</v>
+        <v>1547</v>
       </c>
       <c r="G57" s="46" t="s">
-        <v>1560</v>
+        <v>1548</v>
       </c>
       <c r="H57" s="46" t="s">
-        <v>1561</v>
-      </c>
-      <c r="I57" s="2"/>
+        <v>1549</v>
+      </c>
+      <c r="I57" s="46" t="s">
+        <v>1549</v>
+      </c>
       <c r="J57" s="18"/>
       <c r="K57" s="18"/>
       <c r="L57" s="18">
@@ -16179,37 +16285,39 @@
         <v>100</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>1636</v>
+        <v>1624</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="46" t="s">
-        <v>1562</v>
+        <v>1550</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>1563</v>
+        <v>1551</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>1564</v>
+        <v>1552</v>
       </c>
       <c r="G58" s="46" t="s">
-        <v>1565</v>
+        <v>1553</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>1566</v>
-      </c>
-      <c r="I58" s="2"/>
+        <v>1554</v>
+      </c>
+      <c r="I58" s="46" t="s">
+        <v>1552</v>
+      </c>
       <c r="J58" s="18"/>
       <c r="K58" s="18"/>
       <c r="L58" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="75">
+    <row r="59" spans="1:12" ht="165">
       <c r="A59" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>2442</v>
+        <v>2419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -16231,25 +16339,27 @@
         <v>100</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>1639</v>
+        <v>1627</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="46" t="s">
-        <v>1567</v>
+        <v>1555</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>1568</v>
+        <v>1556</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>1569</v>
+        <v>1557</v>
       </c>
       <c r="G60" s="46" t="s">
-        <v>1570</v>
+        <v>1558</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>1571</v>
-      </c>
-      <c r="I60" s="2"/>
+        <v>1559</v>
+      </c>
+      <c r="I60" s="46" t="s">
+        <v>1556</v>
+      </c>
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
       <c r="L60" s="18">
@@ -16261,25 +16371,27 @@
         <v>100</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>1640</v>
+        <v>1628</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="46" t="s">
-        <v>1572</v>
+        <v>1560</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>1573</v>
+        <v>1561</v>
       </c>
       <c r="F61" s="46" t="s">
-        <v>1574</v>
+        <v>1562</v>
       </c>
       <c r="G61" s="46" t="s">
-        <v>1575</v>
+        <v>1563</v>
       </c>
       <c r="H61" s="46" t="s">
-        <v>1576</v>
-      </c>
-      <c r="I61" s="2"/>
+        <v>1564</v>
+      </c>
+      <c r="I61" s="46" t="s">
+        <v>1561</v>
+      </c>
       <c r="J61" s="18"/>
       <c r="K61" s="18"/>
       <c r="L61" s="18">
@@ -16291,55 +16403,59 @@
         <v>100</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>1641</v>
+        <v>1629</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="46" t="s">
-        <v>1577</v>
+        <v>1565</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>1578</v>
+        <v>1566</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>1579</v>
+        <v>1567</v>
       </c>
       <c r="G62" s="46" t="s">
-        <v>1580</v>
+        <v>1568</v>
       </c>
       <c r="H62" s="46" t="s">
-        <v>1581</v>
-      </c>
-      <c r="I62" s="2"/>
+        <v>1569</v>
+      </c>
+      <c r="I62" s="46" t="s">
+        <v>1565</v>
+      </c>
       <c r="J62" s="18"/>
       <c r="K62" s="18"/>
       <c r="L62" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="105">
+    <row r="63" spans="1:12" ht="165">
       <c r="A63" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>1642</v>
+        <v>2418</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="46" t="s">
-        <v>1582</v>
+        <v>1570</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F63" s="46" t="s">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="G63" s="46" t="s">
-        <v>1585</v>
+        <v>1573</v>
       </c>
       <c r="H63" s="46" t="s">
-        <v>1586</v>
-      </c>
-      <c r="I63" s="2"/>
+        <v>1574</v>
+      </c>
+      <c r="I63" s="46" t="s">
+        <v>1573</v>
+      </c>
       <c r="J63" s="18" t="s">
         <v>659</v>
       </c>
@@ -16350,12 +16466,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="75">
+    <row r="64" spans="1:12" ht="255">
       <c r="A64" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>1643</v>
+        <v>2417</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -16377,25 +16493,27 @@
         <v>100</v>
       </c>
       <c r="B65" s="46" t="s">
-        <v>1644</v>
+        <v>1630</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="46" t="s">
-        <v>1587</v>
+        <v>1575</v>
       </c>
       <c r="E65" s="46" t="s">
-        <v>1588</v>
+        <v>1576</v>
       </c>
       <c r="F65" s="46" t="s">
-        <v>1589</v>
+        <v>1577</v>
       </c>
       <c r="G65" s="46" t="s">
-        <v>1590</v>
+        <v>1578</v>
       </c>
       <c r="H65" s="46" t="s">
-        <v>1591</v>
-      </c>
-      <c r="I65" s="2"/>
+        <v>1579</v>
+      </c>
+      <c r="I65" s="46" t="s">
+        <v>1576</v>
+      </c>
       <c r="J65" s="18"/>
       <c r="K65" s="18"/>
       <c r="L65" s="18">
@@ -16407,37 +16525,39 @@
         <v>100</v>
       </c>
       <c r="B66" s="46" t="s">
-        <v>1645</v>
+        <v>1631</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="46" t="s">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>1593</v>
+        <v>1581</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>1594</v>
+        <v>1582</v>
       </c>
       <c r="G66" s="46" t="s">
-        <v>1595</v>
+        <v>1583</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>1596</v>
-      </c>
-      <c r="I66" s="2"/>
+        <v>1584</v>
+      </c>
+      <c r="I66" s="46" t="s">
+        <v>1584</v>
+      </c>
       <c r="J66" s="18"/>
       <c r="K66" s="18"/>
       <c r="L66" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="75">
+    <row r="67" spans="1:12" ht="105">
       <c r="A67" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>1646</v>
+        <v>2416</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -16459,25 +16579,27 @@
         <v>100</v>
       </c>
       <c r="B68" s="46" t="s">
-        <v>1647</v>
+        <v>1632</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="46" t="s">
-        <v>1597</v>
+        <v>1585</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="G68" s="46" t="s">
-        <v>1600</v>
+        <v>1588</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>1601</v>
-      </c>
-      <c r="I68" s="2"/>
+        <v>1589</v>
+      </c>
+      <c r="I68" s="46" t="s">
+        <v>1585</v>
+      </c>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
       <c r="L68" s="18">
@@ -16489,25 +16611,27 @@
         <v>100</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>1648</v>
+        <v>1633</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="46" t="s">
-        <v>1602</v>
+        <v>1590</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="F69" s="46" t="s">
-        <v>1604</v>
+        <v>1592</v>
       </c>
       <c r="G69" s="46" t="s">
-        <v>1605</v>
+        <v>1593</v>
       </c>
       <c r="H69" s="46" t="s">
-        <v>1606</v>
-      </c>
-      <c r="I69" s="2"/>
+        <v>1594</v>
+      </c>
+      <c r="I69" s="46" t="s">
+        <v>1592</v>
+      </c>
       <c r="J69" s="18"/>
       <c r="K69" s="18"/>
       <c r="L69" s="18">
@@ -16519,37 +16643,39 @@
         <v>100</v>
       </c>
       <c r="B70" s="46" t="s">
-        <v>1649</v>
+        <v>1634</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="46" t="s">
-        <v>1607</v>
+        <v>1595</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>1608</v>
+        <v>1596</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>1609</v>
+        <v>1597</v>
       </c>
       <c r="G70" s="46" t="s">
-        <v>1610</v>
+        <v>1598</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>1611</v>
-      </c>
-      <c r="I70" s="2"/>
+        <v>1599</v>
+      </c>
+      <c r="I70" s="46" t="s">
+        <v>1596</v>
+      </c>
       <c r="J70" s="18"/>
       <c r="K70" s="18"/>
       <c r="L70" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="45">
+    <row r="71" spans="1:12" ht="75">
       <c r="A71" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>1650</v>
+        <v>2427</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -16571,25 +16697,27 @@
         <v>100</v>
       </c>
       <c r="B72" s="46" t="s">
-        <v>1651</v>
+        <v>1635</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="46" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>1613</v>
+        <v>1601</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>1614</v>
+        <v>1602</v>
       </c>
       <c r="G72" s="46" t="s">
-        <v>1615</v>
+        <v>1603</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>1616</v>
-      </c>
-      <c r="I72" s="2"/>
+        <v>1604</v>
+      </c>
+      <c r="I72" s="46" t="s">
+        <v>1603</v>
+      </c>
       <c r="J72" s="18"/>
       <c r="K72" s="18"/>
       <c r="L72" s="18">
@@ -16601,37 +16729,39 @@
         <v>100</v>
       </c>
       <c r="B73" s="46" t="s">
-        <v>1652</v>
+        <v>1636</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="46" t="s">
-        <v>1617</v>
+        <v>1605</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>1618</v>
+        <v>1606</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>1619</v>
+        <v>1607</v>
       </c>
       <c r="G73" s="46" t="s">
-        <v>1620</v>
+        <v>1608</v>
       </c>
       <c r="H73" s="46" t="s">
-        <v>1621</v>
-      </c>
-      <c r="I73" s="2"/>
+        <v>1609</v>
+      </c>
+      <c r="I73" s="46" t="s">
+        <v>1609</v>
+      </c>
       <c r="J73" s="18"/>
       <c r="K73" s="18"/>
       <c r="L73" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="90">
+    <row r="74" spans="1:12" ht="135">
       <c r="A74" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B74" s="46" t="s">
-        <v>1653</v>
+        <v>2415</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -16653,25 +16783,27 @@
         <v>100</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>1654</v>
+        <v>1637</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="46" t="s">
-        <v>1622</v>
+        <v>1610</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>1623</v>
+        <v>1611</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>1624</v>
+        <v>1612</v>
       </c>
       <c r="G75" s="46" t="s">
-        <v>1625</v>
+        <v>1613</v>
       </c>
       <c r="H75" s="46" t="s">
-        <v>1626</v>
-      </c>
-      <c r="I75" s="2"/>
+        <v>1614</v>
+      </c>
+      <c r="I75" s="46" t="s">
+        <v>1610</v>
+      </c>
       <c r="J75" s="18"/>
       <c r="K75" s="18"/>
       <c r="L75" s="18">
@@ -16683,25 +16815,27 @@
         <v>100</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>1655</v>
+        <v>1638</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="46" t="s">
-        <v>1627</v>
+        <v>1615</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>1628</v>
+        <v>1616</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>1629</v>
+        <v>1617</v>
       </c>
       <c r="G76" s="46" t="s">
-        <v>1630</v>
+        <v>1618</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>1631</v>
-      </c>
-      <c r="I76" s="2"/>
+        <v>1619</v>
+      </c>
+      <c r="I76" s="46" t="s">
+        <v>1618</v>
+      </c>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
       <c r="L76" s="18">
@@ -16768,7 +16902,7 @@
         <v>570</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J78" s="25" t="s">
         <v>10</v>
@@ -16785,7 +16919,7 @@
         <v>98</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1347</v>
+        <v>2428</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="13" t="s">
@@ -16821,7 +16955,7 @@
         <v>98</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="13" t="s">
@@ -16840,7 +16974,7 @@
         <v>579</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J80" s="25" t="s">
         <v>10</v>
@@ -16857,7 +16991,7 @@
         <v>98</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="13" t="s">
@@ -16893,7 +17027,7 @@
         <v>98</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="13" t="s">
@@ -16929,7 +17063,7 @@
         <v>98</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>1351</v>
+        <v>2429</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="13" t="s">
@@ -16965,7 +17099,7 @@
         <v>98</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="13" t="s">
@@ -17001,7 +17135,7 @@
         <v>98</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>2404</v>
+        <v>2378</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="13" t="s">
@@ -17037,7 +17171,7 @@
         <v>98</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="13" t="s">
@@ -17073,7 +17207,7 @@
         <v>98</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>1354</v>
+        <v>2430</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="13" t="s">
@@ -17109,7 +17243,7 @@
         <v>98</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="13" t="s">
@@ -17145,7 +17279,7 @@
         <v>98</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>1356</v>
+        <v>2431</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="13" t="s">
@@ -17181,7 +17315,7 @@
         <v>98</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="13" t="s">
@@ -17217,7 +17351,7 @@
         <v>98</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>1358</v>
+        <v>2432</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="13" t="s">
@@ -17253,7 +17387,7 @@
         <v>98</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>1359</v>
+        <v>2433</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="13" t="s">
@@ -17289,7 +17423,7 @@
         <v>98</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>1360</v>
+        <v>2434</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="13" t="s">
@@ -17325,7 +17459,7 @@
         <v>98</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="13" t="s">
@@ -17361,7 +17495,7 @@
         <v>98</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="13" t="s">
@@ -17397,7 +17531,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="13" t="s">
@@ -17433,23 +17567,23 @@
         <v>98</v>
       </c>
       <c r="B97" s="37" t="s">
-        <v>1745</v>
+        <v>1728</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="47" t="s">
-        <v>1656</v>
+        <v>1639</v>
       </c>
       <c r="E97" s="47" t="s">
-        <v>1657</v>
+        <v>1640</v>
       </c>
       <c r="F97" s="47" t="s">
-        <v>1658</v>
+        <v>1641</v>
       </c>
       <c r="G97" s="47" t="s">
-        <v>1659</v>
+        <v>1642</v>
       </c>
       <c r="H97" s="47" t="s">
-        <v>1660</v>
+        <v>1643</v>
       </c>
       <c r="I97" s="2"/>
       <c r="J97" s="18" t="s">
@@ -17471,19 +17605,19 @@
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="48" t="s">
-        <v>1661</v>
+        <v>1644</v>
       </c>
       <c r="E98" s="48" t="s">
-        <v>1662</v>
+        <v>1645</v>
       </c>
       <c r="F98" s="48" t="s">
-        <v>1663</v>
+        <v>1646</v>
       </c>
       <c r="G98" s="48" t="s">
-        <v>1664</v>
+        <v>1647</v>
       </c>
       <c r="H98" s="48" t="s">
-        <v>1665</v>
+        <v>1648</v>
       </c>
       <c r="I98" s="2"/>
       <c r="J98" s="18" t="s">
@@ -17505,19 +17639,19 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="47" t="s">
-        <v>1666</v>
+        <v>1649</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>1667</v>
+        <v>1650</v>
       </c>
       <c r="F99" s="47" t="s">
-        <v>1668</v>
+        <v>1651</v>
       </c>
       <c r="G99" s="47" t="s">
-        <v>1669</v>
+        <v>1652</v>
       </c>
       <c r="H99" s="47" t="s">
-        <v>1670</v>
+        <v>1653</v>
       </c>
       <c r="I99" s="2"/>
       <c r="J99" s="18" t="s">
@@ -17535,23 +17669,23 @@
         <v>98</v>
       </c>
       <c r="B100" s="40" t="s">
-        <v>1746</v>
+        <v>1729</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="48" t="s">
-        <v>1671</v>
+        <v>1654</v>
       </c>
       <c r="E100" s="48" t="s">
-        <v>1672</v>
+        <v>1655</v>
       </c>
       <c r="F100" s="48" t="s">
-        <v>1673</v>
+        <v>1656</v>
       </c>
       <c r="G100" s="48" t="s">
-        <v>1674</v>
+        <v>1657</v>
       </c>
       <c r="H100" s="48" t="s">
-        <v>1675</v>
+        <v>1658</v>
       </c>
       <c r="I100" s="2"/>
       <c r="J100" s="18" t="s">
@@ -17569,23 +17703,23 @@
         <v>98</v>
       </c>
       <c r="B101" s="37" t="s">
-        <v>1747</v>
+        <v>1730</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="47" t="s">
-        <v>1676</v>
+        <v>1659</v>
       </c>
       <c r="E101" s="47" t="s">
-        <v>1677</v>
+        <v>1660</v>
       </c>
       <c r="F101" s="47" t="s">
-        <v>1678</v>
+        <v>1661</v>
       </c>
       <c r="G101" s="47" t="s">
-        <v>1679</v>
+        <v>1662</v>
       </c>
       <c r="H101" s="47" t="s">
-        <v>1680</v>
+        <v>1663</v>
       </c>
       <c r="I101" s="2"/>
       <c r="J101" s="18" t="s">
@@ -17607,19 +17741,19 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="48" t="s">
-        <v>1681</v>
+        <v>1664</v>
       </c>
       <c r="E102" s="48" t="s">
-        <v>1682</v>
+        <v>1665</v>
       </c>
       <c r="F102" s="48" t="s">
-        <v>1683</v>
+        <v>1666</v>
       </c>
       <c r="G102" s="48" t="s">
-        <v>1684</v>
+        <v>1667</v>
       </c>
       <c r="H102" s="48" t="s">
-        <v>1685</v>
+        <v>1668</v>
       </c>
       <c r="I102" s="2"/>
       <c r="J102" s="18" t="s">
@@ -17637,23 +17771,23 @@
         <v>98</v>
       </c>
       <c r="B103" s="37" t="s">
-        <v>1748</v>
+        <v>1731</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="47" t="s">
-        <v>1686</v>
+        <v>1669</v>
       </c>
       <c r="E103" s="47" t="s">
-        <v>1687</v>
+        <v>1670</v>
       </c>
       <c r="F103" s="47" t="s">
-        <v>1688</v>
+        <v>1671</v>
       </c>
       <c r="G103" s="47" t="s">
-        <v>1689</v>
+        <v>1672</v>
       </c>
       <c r="H103" s="47" t="s">
-        <v>1690</v>
+        <v>1673</v>
       </c>
       <c r="I103" s="2"/>
       <c r="J103" s="18" t="s">
@@ -17671,23 +17805,23 @@
         <v>98</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>1749</v>
+        <v>1732</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="48" t="s">
-        <v>1691</v>
+        <v>1674</v>
       </c>
       <c r="E104" s="48" t="s">
-        <v>1692</v>
+        <v>1675</v>
       </c>
       <c r="F104" s="48" t="s">
-        <v>1693</v>
+        <v>1676</v>
       </c>
       <c r="G104" s="48" t="s">
-        <v>1694</v>
+        <v>1677</v>
       </c>
       <c r="H104" s="48" t="s">
-        <v>1695</v>
+        <v>1678</v>
       </c>
       <c r="I104" s="2"/>
       <c r="J104" s="18" t="s">
@@ -17705,20 +17839,20 @@
         <v>98</v>
       </c>
       <c r="B105" s="37" t="s">
-        <v>1750</v>
+        <v>1733</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="47" t="s">
-        <v>1696</v>
+        <v>1679</v>
       </c>
       <c r="E105" s="47" t="s">
-        <v>1697</v>
+        <v>1680</v>
       </c>
       <c r="F105" s="47" t="s">
-        <v>1698</v>
+        <v>1681</v>
       </c>
       <c r="G105" s="47" t="s">
-        <v>1699</v>
+        <v>1682</v>
       </c>
       <c r="H105" s="47" t="s">
         <v>82</v>
@@ -17743,19 +17877,19 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="48" t="s">
-        <v>1700</v>
+        <v>1683</v>
       </c>
       <c r="E106" s="48" t="s">
-        <v>1701</v>
+        <v>1684</v>
       </c>
       <c r="F106" s="48" t="s">
-        <v>1702</v>
+        <v>1685</v>
       </c>
       <c r="G106" s="48" t="s">
-        <v>1703</v>
+        <v>1686</v>
       </c>
       <c r="H106" s="48" t="s">
-        <v>1704</v>
+        <v>1687</v>
       </c>
       <c r="I106" s="2"/>
       <c r="J106" s="18" t="s">
@@ -17768,28 +17902,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="142.5">
+    <row r="107" spans="1:12" ht="85.5">
       <c r="A107" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B107" s="37" t="s">
-        <v>1751</v>
+        <v>2435</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="47" t="s">
         <v>83</v>
       </c>
       <c r="E107" s="47" t="s">
-        <v>1705</v>
+        <v>1688</v>
       </c>
       <c r="F107" s="47" t="s">
-        <v>1706</v>
+        <v>1689</v>
       </c>
       <c r="G107" s="47" t="s">
-        <v>1707</v>
+        <v>1690</v>
       </c>
       <c r="H107" s="47" t="s">
-        <v>1708</v>
+        <v>1691</v>
       </c>
       <c r="I107" s="2"/>
       <c r="J107" s="18" t="s">
@@ -17814,16 +17948,16 @@
         <v>84</v>
       </c>
       <c r="E108" s="48" t="s">
-        <v>1709</v>
+        <v>1692</v>
       </c>
       <c r="F108" s="48" t="s">
-        <v>1710</v>
+        <v>1693</v>
       </c>
       <c r="G108" s="48" t="s">
         <v>85</v>
       </c>
       <c r="H108" s="48" t="s">
-        <v>1711</v>
+        <v>1694</v>
       </c>
       <c r="I108" s="2"/>
       <c r="J108" s="18" t="s">
@@ -17841,23 +17975,23 @@
         <v>98</v>
       </c>
       <c r="B109" s="37" t="s">
-        <v>1752</v>
+        <v>2436</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="47" t="s">
-        <v>1712</v>
+        <v>1695</v>
       </c>
       <c r="E109" s="47" t="s">
-        <v>1713</v>
+        <v>1696</v>
       </c>
       <c r="F109" s="47" t="s">
-        <v>1714</v>
+        <v>1697</v>
       </c>
       <c r="G109" s="47" t="s">
-        <v>1715</v>
+        <v>1698</v>
       </c>
       <c r="H109" s="47" t="s">
-        <v>1716</v>
+        <v>1699</v>
       </c>
       <c r="I109" s="2"/>
       <c r="J109" s="18" t="s">
@@ -17875,7 +18009,7 @@
         <v>98</v>
       </c>
       <c r="B110" s="40" t="s">
-        <v>1753</v>
+        <v>2437</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="48" t="s">
@@ -17885,13 +18019,13 @@
         <v>1139</v>
       </c>
       <c r="F110" s="48" t="s">
-        <v>1717</v>
+        <v>1700</v>
       </c>
       <c r="G110" s="48" t="s">
-        <v>1718</v>
+        <v>1701</v>
       </c>
       <c r="H110" s="48" t="s">
-        <v>1719</v>
+        <v>1702</v>
       </c>
       <c r="I110" s="2"/>
       <c r="J110" s="18" t="s">
@@ -17904,28 +18038,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="156.75">
+    <row r="111" spans="1:12" ht="199.5">
       <c r="A111" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B111" s="37" t="s">
-        <v>1754</v>
+        <v>2438</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="47" t="s">
-        <v>1720</v>
+        <v>1703</v>
       </c>
       <c r="E111" s="47" t="s">
-        <v>1721</v>
+        <v>1704</v>
       </c>
       <c r="F111" s="47" t="s">
-        <v>1722</v>
+        <v>1705</v>
       </c>
       <c r="G111" s="47" t="s">
-        <v>1723</v>
+        <v>1706</v>
       </c>
       <c r="H111" s="47" t="s">
-        <v>1724</v>
+        <v>1707</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="18" t="s">
@@ -17938,28 +18072,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="85.5">
+    <row r="112" spans="1:12" ht="114">
       <c r="A112" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B112" s="40" t="s">
-        <v>1755</v>
+        <v>2439</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="48" t="s">
-        <v>1725</v>
+        <v>1708</v>
       </c>
       <c r="E112" s="48" t="s">
-        <v>1726</v>
+        <v>1709</v>
       </c>
       <c r="F112" s="48" t="s">
-        <v>1727</v>
+        <v>1710</v>
       </c>
       <c r="G112" s="48" t="s">
-        <v>1728</v>
+        <v>1711</v>
       </c>
       <c r="H112" s="48" t="s">
-        <v>1729</v>
+        <v>1712</v>
       </c>
       <c r="I112" s="2"/>
       <c r="J112" s="18" t="s">
@@ -17972,28 +18106,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="99.75">
+    <row r="113" spans="1:12" ht="128.25">
       <c r="A113" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B113" s="37" t="s">
-        <v>1756</v>
+        <v>2440</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="47" t="s">
-        <v>1730</v>
+        <v>1713</v>
       </c>
       <c r="E113" s="47" t="s">
-        <v>1731</v>
+        <v>1714</v>
       </c>
       <c r="F113" s="47" t="s">
-        <v>1732</v>
+        <v>1715</v>
       </c>
       <c r="G113" s="47" t="s">
-        <v>1733</v>
+        <v>1716</v>
       </c>
       <c r="H113" s="47" t="s">
-        <v>1734</v>
+        <v>1717</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="18" t="s">
@@ -18006,12 +18140,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="114">
+    <row r="114" spans="1:12" ht="128.25">
       <c r="A114" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>1757</v>
+        <v>2441</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="48" t="s">
@@ -18040,28 +18174,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="85.5">
+    <row r="115" spans="1:12" ht="114">
       <c r="A115" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B115" s="37" t="s">
-        <v>1758</v>
+        <v>2442</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="47" t="s">
-        <v>1735</v>
+        <v>1718</v>
       </c>
       <c r="E115" s="47" t="s">
-        <v>1736</v>
+        <v>1719</v>
       </c>
       <c r="F115" s="47" t="s">
-        <v>1737</v>
+        <v>1720</v>
       </c>
       <c r="G115" s="47" t="s">
-        <v>1738</v>
+        <v>1721</v>
       </c>
       <c r="H115" s="47" t="s">
-        <v>1739</v>
+        <v>1722</v>
       </c>
       <c r="I115" s="2"/>
       <c r="J115" s="18" t="s">
@@ -18079,23 +18213,23 @@
         <v>98</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>1759</v>
+        <v>2443</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="48" t="s">
-        <v>1740</v>
+        <v>1723</v>
       </c>
       <c r="E116" s="48" t="s">
-        <v>1741</v>
+        <v>1724</v>
       </c>
       <c r="F116" s="48" t="s">
-        <v>1742</v>
+        <v>1725</v>
       </c>
       <c r="G116" s="48" t="s">
-        <v>1743</v>
+        <v>1726</v>
       </c>
       <c r="H116" s="48" t="s">
-        <v>1744</v>
+        <v>1727</v>
       </c>
       <c r="I116" s="2"/>
       <c r="J116" s="18" t="s">
@@ -18883,7 +19017,7 @@
         <v>99</v>
       </c>
       <c r="B144" s="46" t="s">
-        <v>1857</v>
+        <v>1831</v>
       </c>
       <c r="C144" s="46"/>
       <c r="D144" s="46"/>
@@ -18905,23 +19039,23 @@
         <v>100</v>
       </c>
       <c r="B145" s="46" t="s">
-        <v>1858</v>
+        <v>1832</v>
       </c>
       <c r="C145" s="46"/>
       <c r="D145" s="46" t="s">
-        <v>1760</v>
+        <v>1734</v>
       </c>
       <c r="E145" s="46" t="s">
-        <v>1761</v>
+        <v>1735</v>
       </c>
       <c r="F145" s="46" t="s">
-        <v>1762</v>
+        <v>1736</v>
       </c>
       <c r="G145" s="46" t="s">
-        <v>1763</v>
+        <v>1737</v>
       </c>
       <c r="H145" s="46" t="s">
-        <v>1764</v>
+        <v>1738</v>
       </c>
       <c r="I145" s="2"/>
       <c r="J145" s="18"/>
@@ -18935,23 +19069,23 @@
         <v>100</v>
       </c>
       <c r="B146" s="46" t="s">
-        <v>1637</v>
+        <v>1625</v>
       </c>
       <c r="C146" s="46"/>
       <c r="D146" s="46" t="s">
-        <v>1765</v>
+        <v>1739</v>
       </c>
       <c r="E146" s="46" t="s">
-        <v>1766</v>
+        <v>1740</v>
       </c>
       <c r="F146" s="46" t="s">
-        <v>1767</v>
+        <v>1741</v>
       </c>
       <c r="G146" s="46" t="s">
-        <v>1768</v>
+        <v>1742</v>
       </c>
       <c r="H146" s="46" t="s">
-        <v>1553</v>
+        <v>1541</v>
       </c>
       <c r="I146" s="2"/>
       <c r="J146" s="18"/>
@@ -18965,23 +19099,23 @@
         <v>100</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1859</v>
+        <v>1833</v>
       </c>
       <c r="C147" s="46"/>
       <c r="D147" s="46" t="s">
-        <v>1769</v>
+        <v>1743</v>
       </c>
       <c r="E147" s="46" t="s">
-        <v>1770</v>
+        <v>1744</v>
       </c>
       <c r="F147" s="46" t="s">
-        <v>1771</v>
+        <v>1745</v>
       </c>
       <c r="G147" s="46" t="s">
-        <v>1772</v>
+        <v>1746</v>
       </c>
       <c r="H147" s="46" t="s">
-        <v>1773</v>
+        <v>1747</v>
       </c>
       <c r="I147" s="2"/>
       <c r="J147" s="18"/>
@@ -18995,7 +19129,7 @@
         <v>99</v>
       </c>
       <c r="B148" s="46" t="s">
-        <v>1860</v>
+        <v>1834</v>
       </c>
       <c r="C148" s="46"/>
       <c r="D148" s="46"/>
@@ -19017,23 +19151,23 @@
         <v>100</v>
       </c>
       <c r="B149" s="46" t="s">
-        <v>1858</v>
+        <v>1832</v>
       </c>
       <c r="C149" s="46"/>
       <c r="D149" s="46" t="s">
-        <v>1774</v>
+        <v>1748</v>
       </c>
       <c r="E149" s="46" t="s">
-        <v>1775</v>
+        <v>1749</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>1776</v>
+        <v>1750</v>
       </c>
       <c r="G149" s="46" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
       <c r="H149" s="46" t="s">
-        <v>1778</v>
+        <v>1752</v>
       </c>
       <c r="I149" s="2"/>
       <c r="J149" s="18"/>
@@ -19047,23 +19181,23 @@
         <v>100</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1861</v>
+        <v>1835</v>
       </c>
       <c r="C150" s="46"/>
       <c r="D150" s="46" t="s">
-        <v>1779</v>
+        <v>1753</v>
       </c>
       <c r="E150" s="46" t="s">
-        <v>1780</v>
+        <v>1754</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>1781</v>
+        <v>1755</v>
       </c>
       <c r="G150" s="46" t="s">
-        <v>1782</v>
+        <v>1756</v>
       </c>
       <c r="H150" s="46" t="s">
-        <v>1783</v>
+        <v>1757</v>
       </c>
       <c r="I150" s="2"/>
       <c r="J150" s="18"/>
@@ -19077,23 +19211,23 @@
         <v>100</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1862</v>
+        <v>1836</v>
       </c>
       <c r="C151" s="46"/>
       <c r="D151" s="46" t="s">
-        <v>1784</v>
+        <v>1758</v>
       </c>
       <c r="E151" s="46" t="s">
-        <v>1785</v>
+        <v>1759</v>
       </c>
       <c r="F151" s="46" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="G151" s="46" t="s">
-        <v>1787</v>
+        <v>1761</v>
       </c>
       <c r="H151" s="46" t="s">
-        <v>1788</v>
+        <v>1762</v>
       </c>
       <c r="I151" s="2"/>
       <c r="J151" s="18"/>
@@ -19107,7 +19241,7 @@
         <v>99</v>
       </c>
       <c r="B152" s="46" t="s">
-        <v>1863</v>
+        <v>1837</v>
       </c>
       <c r="C152" s="46"/>
       <c r="D152" s="46"/>
@@ -19129,23 +19263,23 @@
         <v>100</v>
       </c>
       <c r="B153" s="46" t="s">
-        <v>1864</v>
+        <v>1838</v>
       </c>
       <c r="C153" s="46"/>
       <c r="D153" s="46" t="s">
-        <v>1789</v>
+        <v>1763</v>
       </c>
       <c r="E153" s="46" t="s">
-        <v>1790</v>
+        <v>1764</v>
       </c>
       <c r="F153" s="46" t="s">
-        <v>1791</v>
+        <v>1765</v>
       </c>
       <c r="G153" s="46" t="s">
-        <v>1792</v>
+        <v>1766</v>
       </c>
       <c r="H153" s="46" t="s">
-        <v>1793</v>
+        <v>1767</v>
       </c>
       <c r="I153" s="2"/>
       <c r="J153" s="18"/>
@@ -19159,23 +19293,23 @@
         <v>100</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1865</v>
+        <v>1839</v>
       </c>
       <c r="C154" s="46"/>
       <c r="D154" s="46" t="s">
-        <v>1794</v>
+        <v>1768</v>
       </c>
       <c r="E154" s="46" t="s">
-        <v>1795</v>
+        <v>1769</v>
       </c>
       <c r="F154" s="46" t="s">
-        <v>1796</v>
+        <v>1770</v>
       </c>
       <c r="G154" s="46" t="s">
-        <v>1797</v>
+        <v>1771</v>
       </c>
       <c r="H154" s="46" t="s">
-        <v>1798</v>
+        <v>1772</v>
       </c>
       <c r="I154" s="2"/>
       <c r="J154" s="18"/>
@@ -19189,23 +19323,23 @@
         <v>100</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1866</v>
+        <v>1840</v>
       </c>
       <c r="C155" s="46"/>
       <c r="D155" s="46" t="s">
-        <v>1799</v>
+        <v>1773</v>
       </c>
       <c r="E155" s="46" t="s">
-        <v>1800</v>
+        <v>1774</v>
       </c>
       <c r="F155" s="46" t="s">
-        <v>1801</v>
+        <v>1775</v>
       </c>
       <c r="G155" s="46" t="s">
-        <v>1802</v>
+        <v>1776</v>
       </c>
       <c r="H155" s="46" t="s">
-        <v>1803</v>
+        <v>1777</v>
       </c>
       <c r="I155" s="2"/>
       <c r="J155" s="18"/>
@@ -19219,23 +19353,23 @@
         <v>100</v>
       </c>
       <c r="B156" s="46" t="s">
-        <v>1867</v>
+        <v>1841</v>
       </c>
       <c r="C156" s="46"/>
       <c r="D156" s="46" t="s">
-        <v>1804</v>
+        <v>1778</v>
       </c>
       <c r="E156" s="46" t="s">
-        <v>1608</v>
+        <v>1596</v>
       </c>
       <c r="F156" s="46" t="s">
-        <v>1805</v>
+        <v>1779</v>
       </c>
       <c r="G156" s="46" t="s">
-        <v>1806</v>
+        <v>1780</v>
       </c>
       <c r="H156" s="46" t="s">
-        <v>1807</v>
+        <v>1781</v>
       </c>
       <c r="I156" s="2"/>
       <c r="J156" s="18"/>
@@ -19249,7 +19383,7 @@
         <v>99</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1874</v>
+        <v>1848</v>
       </c>
       <c r="C157" s="46"/>
       <c r="D157" s="2"/>
@@ -19271,23 +19405,23 @@
         <v>100</v>
       </c>
       <c r="B158" s="46" t="s">
-        <v>1868</v>
+        <v>1842</v>
       </c>
       <c r="C158" s="46"/>
       <c r="D158" s="46" t="s">
-        <v>1808</v>
+        <v>1782</v>
       </c>
       <c r="E158" s="46" t="s">
-        <v>1809</v>
+        <v>1783</v>
       </c>
       <c r="F158" s="46" t="s">
-        <v>1810</v>
+        <v>1784</v>
       </c>
       <c r="G158" s="46" t="s">
-        <v>1811</v>
+        <v>1785</v>
       </c>
       <c r="H158" s="46" t="s">
-        <v>1812</v>
+        <v>1786</v>
       </c>
       <c r="I158" s="2"/>
       <c r="J158" s="18"/>
@@ -19301,23 +19435,23 @@
         <v>100</v>
       </c>
       <c r="B159" s="46" t="s">
-        <v>1869</v>
+        <v>1843</v>
       </c>
       <c r="C159" s="46"/>
       <c r="D159" s="46" t="s">
-        <v>1813</v>
+        <v>1787</v>
       </c>
       <c r="E159" s="46" t="s">
-        <v>1814</v>
+        <v>1788</v>
       </c>
       <c r="F159" s="46" t="s">
-        <v>1815</v>
+        <v>1789</v>
       </c>
       <c r="G159" s="46" t="s">
-        <v>1816</v>
+        <v>1790</v>
       </c>
       <c r="H159" s="46" t="s">
-        <v>1817</v>
+        <v>1791</v>
       </c>
       <c r="I159" s="2"/>
       <c r="J159" s="18"/>
@@ -19331,7 +19465,7 @@
         <v>99</v>
       </c>
       <c r="B160" s="46" t="s">
-        <v>1870</v>
+        <v>1844</v>
       </c>
       <c r="C160" s="46"/>
       <c r="D160" s="46"/>
@@ -19353,23 +19487,23 @@
         <v>100</v>
       </c>
       <c r="B161" s="46" t="s">
-        <v>1871</v>
+        <v>1845</v>
       </c>
       <c r="C161" s="46"/>
       <c r="D161" s="46" t="s">
-        <v>1818</v>
+        <v>1792</v>
       </c>
       <c r="E161" s="46" t="s">
-        <v>1819</v>
+        <v>1793</v>
       </c>
       <c r="F161" s="46" t="s">
-        <v>1820</v>
+        <v>1794</v>
       </c>
       <c r="G161" s="46" t="s">
-        <v>1821</v>
+        <v>1795</v>
       </c>
       <c r="H161" s="46" t="s">
-        <v>1822</v>
+        <v>1796</v>
       </c>
       <c r="I161" s="2"/>
       <c r="J161" s="18"/>
@@ -19383,23 +19517,23 @@
         <v>100</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1872</v>
+        <v>1846</v>
       </c>
       <c r="C162" s="46"/>
       <c r="D162" s="46" t="s">
-        <v>1823</v>
+        <v>1797</v>
       </c>
       <c r="E162" s="46" t="s">
-        <v>1824</v>
+        <v>1798</v>
       </c>
       <c r="F162" s="46" t="s">
-        <v>1825</v>
+        <v>1799</v>
       </c>
       <c r="G162" s="46" t="s">
-        <v>1826</v>
+        <v>1800</v>
       </c>
       <c r="H162" s="46" t="s">
-        <v>1827</v>
+        <v>1801</v>
       </c>
       <c r="I162" s="2"/>
       <c r="J162" s="18"/>
@@ -19413,23 +19547,23 @@
         <v>100</v>
       </c>
       <c r="B163" s="46" t="s">
-        <v>1873</v>
+        <v>1847</v>
       </c>
       <c r="C163" s="46"/>
       <c r="D163" s="46" t="s">
-        <v>1828</v>
+        <v>1802</v>
       </c>
       <c r="E163" s="46" t="s">
-        <v>1829</v>
+        <v>1803</v>
       </c>
       <c r="F163" s="46" t="s">
-        <v>1830</v>
+        <v>1804</v>
       </c>
       <c r="G163" s="46" t="s">
-        <v>1831</v>
+        <v>1805</v>
       </c>
       <c r="H163" s="46" t="s">
-        <v>1832</v>
+        <v>1806</v>
       </c>
       <c r="I163" s="2"/>
       <c r="J163" s="18"/>
@@ -19443,7 +19577,7 @@
         <v>99</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1875</v>
+        <v>1849</v>
       </c>
       <c r="C164" s="46"/>
       <c r="D164" s="46"/>
@@ -19465,23 +19599,23 @@
         <v>100</v>
       </c>
       <c r="B165" s="46" t="s">
-        <v>1876</v>
+        <v>1850</v>
       </c>
       <c r="C165" s="46"/>
       <c r="D165" s="46" t="s">
-        <v>1833</v>
+        <v>1807</v>
       </c>
       <c r="E165" s="46" t="s">
-        <v>1834</v>
+        <v>1808</v>
       </c>
       <c r="F165" s="46" t="s">
-        <v>1835</v>
+        <v>1809</v>
       </c>
       <c r="G165" s="46" t="s">
-        <v>1836</v>
+        <v>1810</v>
       </c>
       <c r="H165" s="46" t="s">
-        <v>1837</v>
+        <v>1811</v>
       </c>
       <c r="I165" s="2"/>
       <c r="J165" s="18"/>
@@ -19495,23 +19629,23 @@
         <v>100</v>
       </c>
       <c r="B166" s="46" t="s">
-        <v>1877</v>
+        <v>1851</v>
       </c>
       <c r="C166" s="46"/>
       <c r="D166" s="46" t="s">
-        <v>1838</v>
+        <v>1812</v>
       </c>
       <c r="E166" s="46" t="s">
-        <v>1839</v>
+        <v>1813</v>
       </c>
       <c r="F166" s="46" t="s">
-        <v>1840</v>
+        <v>1814</v>
       </c>
       <c r="G166" s="46" t="s">
-        <v>1841</v>
+        <v>1815</v>
       </c>
       <c r="H166" s="46" t="s">
-        <v>1842</v>
+        <v>1816</v>
       </c>
       <c r="I166" s="2"/>
       <c r="J166" s="18"/>
@@ -19525,23 +19659,23 @@
         <v>100</v>
       </c>
       <c r="B167" s="46" t="s">
-        <v>1878</v>
+        <v>1852</v>
       </c>
       <c r="C167" s="46"/>
       <c r="D167" s="46" t="s">
-        <v>1843</v>
+        <v>1817</v>
       </c>
       <c r="E167" s="46" t="s">
-        <v>1844</v>
+        <v>1818</v>
       </c>
       <c r="F167" s="46" t="s">
-        <v>1845</v>
+        <v>1819</v>
       </c>
       <c r="G167" s="46" t="s">
-        <v>1846</v>
+        <v>1820</v>
       </c>
       <c r="H167" s="46" t="s">
-        <v>1823</v>
+        <v>1797</v>
       </c>
       <c r="I167" s="2"/>
       <c r="J167" s="18"/>
@@ -19555,23 +19689,23 @@
         <v>100</v>
       </c>
       <c r="B168" s="46" t="s">
-        <v>1879</v>
+        <v>1853</v>
       </c>
       <c r="C168" s="46"/>
       <c r="D168" s="46" t="s">
-        <v>1847</v>
+        <v>1821</v>
       </c>
       <c r="E168" s="46" t="s">
-        <v>1848</v>
+        <v>1822</v>
       </c>
       <c r="F168" s="46" t="s">
-        <v>1849</v>
+        <v>1823</v>
       </c>
       <c r="G168" s="46" t="s">
-        <v>1850</v>
+        <v>1824</v>
       </c>
       <c r="H168" s="46" t="s">
-        <v>1851</v>
+        <v>1825</v>
       </c>
       <c r="I168" s="2"/>
       <c r="J168" s="18"/>
@@ -19585,23 +19719,23 @@
         <v>100</v>
       </c>
       <c r="B169" s="46" t="s">
-        <v>1880</v>
+        <v>1854</v>
       </c>
       <c r="C169" s="46"/>
       <c r="D169" s="46" t="s">
-        <v>1852</v>
+        <v>1826</v>
       </c>
       <c r="E169" s="46" t="s">
-        <v>1853</v>
+        <v>1827</v>
       </c>
       <c r="F169" s="46" t="s">
-        <v>1854</v>
+        <v>1828</v>
       </c>
       <c r="G169" s="46" t="s">
-        <v>1855</v>
+        <v>1829</v>
       </c>
       <c r="H169" s="46" t="s">
-        <v>1856</v>
+        <v>1830</v>
       </c>
       <c r="I169" s="2"/>
       <c r="J169" s="18"/>
@@ -20335,23 +20469,23 @@
         <v>98</v>
       </c>
       <c r="B190" s="61" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="44" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="E190" s="44" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="F190" s="44" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="G190" s="44" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="H190" s="44" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
       <c r="I190" s="2"/>
       <c r="J190" s="18" t="s">
@@ -20369,23 +20503,23 @@
         <v>98</v>
       </c>
       <c r="B191" s="45" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="45" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="E191" s="45" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="F191" s="45" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="G191" s="45" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
       <c r="H191" s="45" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="I191" s="2"/>
       <c r="J191" s="18" t="s">
@@ -20403,23 +20537,23 @@
         <v>98</v>
       </c>
       <c r="B192" s="44" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="44" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="E192" s="44" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F192" s="44" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="G192" s="44" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
       <c r="H192" s="44" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="I192" s="2"/>
       <c r="J192" s="18" t="s">
@@ -20437,23 +20571,23 @@
         <v>98</v>
       </c>
       <c r="B193" s="45" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="45" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="E193" s="45" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F193" s="45" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="G193" s="45" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
       <c r="H193" s="45" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="I193" s="2"/>
       <c r="J193" s="18" t="s">
@@ -20471,23 +20605,23 @@
         <v>98</v>
       </c>
       <c r="B194" s="44" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="44" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="E194" s="44" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
       <c r="F194" s="44" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
       <c r="G194" s="44" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="H194" s="44" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="I194" s="2"/>
       <c r="J194" s="18" t="s">
@@ -20505,23 +20639,23 @@
         <v>98</v>
       </c>
       <c r="B195" s="45" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="45" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="E195" s="45" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="F195" s="45" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="G195" s="45" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="H195" s="45" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="I195" s="2"/>
       <c r="J195" s="18" t="s">
@@ -20539,23 +20673,23 @@
         <v>98</v>
       </c>
       <c r="B196" s="44" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="44" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="E196" s="44" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="F196" s="44" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="G196" s="44" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="H196" s="44" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="I196" s="2"/>
       <c r="J196" s="18" t="s">
@@ -20573,23 +20707,23 @@
         <v>98</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="45" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="E197" s="45" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="F197" s="45" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
       <c r="G197" s="45" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="H197" s="45" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="I197" s="2"/>
       <c r="J197" s="18" t="s">
@@ -20607,23 +20741,23 @@
         <v>98</v>
       </c>
       <c r="B198" s="44" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="44" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="E198" s="44" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="F198" s="44" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="G198" s="44" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="H198" s="44" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="I198" s="2"/>
       <c r="J198" s="18" t="s">
@@ -20641,23 +20775,23 @@
         <v>98</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="45" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="E199" s="45" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="F199" s="45" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="G199" s="45" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="H199" s="45" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="I199" s="2"/>
       <c r="J199" s="18" t="s">
@@ -20957,7 +21091,7 @@
         <v>99</v>
       </c>
       <c r="B210" s="29" t="s">
-        <v>2386</v>
+        <v>2360</v>
       </c>
       <c r="C210" s="58"/>
       <c r="D210" s="2"/>
@@ -20979,23 +21113,23 @@
         <v>100</v>
       </c>
       <c r="B211" s="29" t="s">
-        <v>2387</v>
+        <v>2361</v>
       </c>
       <c r="C211" s="58"/>
       <c r="D211" s="30" t="s">
-        <v>2318</v>
+        <v>2292</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>2319</v>
+        <v>2293</v>
       </c>
       <c r="F211" s="30" t="s">
-        <v>2320</v>
+        <v>2294</v>
       </c>
       <c r="G211" s="30" t="s">
-        <v>2321</v>
+        <v>2295</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>2322</v>
+        <v>2296</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
@@ -21009,23 +21143,23 @@
         <v>100</v>
       </c>
       <c r="B212" s="59" t="s">
-        <v>2388</v>
+        <v>2362</v>
       </c>
       <c r="C212" s="60"/>
       <c r="D212" s="31" t="s">
-        <v>2323</v>
+        <v>2297</v>
       </c>
       <c r="E212" s="31" t="s">
-        <v>2324</v>
+        <v>2298</v>
       </c>
       <c r="F212" s="31" t="s">
-        <v>2325</v>
+        <v>2299</v>
       </c>
       <c r="G212" s="31" t="s">
-        <v>2326</v>
+        <v>2300</v>
       </c>
       <c r="H212" s="31" t="s">
-        <v>2327</v>
+        <v>2301</v>
       </c>
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
@@ -21039,23 +21173,23 @@
         <v>100</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>2390</v>
+        <v>2364</v>
       </c>
       <c r="C213" s="58"/>
       <c r="D213" s="30" t="s">
-        <v>2328</v>
+        <v>2302</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>2329</v>
+        <v>2303</v>
       </c>
       <c r="F213" s="30" t="s">
-        <v>2330</v>
+        <v>2304</v>
       </c>
       <c r="G213" s="30" t="s">
-        <v>2331</v>
+        <v>2305</v>
       </c>
       <c r="H213" s="30" t="s">
-        <v>2332</v>
+        <v>2306</v>
       </c>
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
@@ -21069,23 +21203,23 @@
         <v>100</v>
       </c>
       <c r="B214" s="59" t="s">
-        <v>2389</v>
+        <v>2363</v>
       </c>
       <c r="C214" s="60"/>
       <c r="D214" s="31" t="s">
-        <v>2333</v>
+        <v>2307</v>
       </c>
       <c r="E214" s="31" t="s">
-        <v>2334</v>
+        <v>2308</v>
       </c>
       <c r="F214" s="31" t="s">
-        <v>2335</v>
+        <v>2309</v>
       </c>
       <c r="G214" s="31" t="s">
-        <v>2336</v>
+        <v>2310</v>
       </c>
       <c r="H214" s="31" t="s">
-        <v>2337</v>
+        <v>2311</v>
       </c>
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
@@ -21099,10 +21233,10 @@
         <v>99</v>
       </c>
       <c r="B215" s="29" t="s">
-        <v>2391</v>
+        <v>2365</v>
       </c>
       <c r="C215" s="58" t="s">
-        <v>2338</v>
+        <v>2312</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -21123,23 +21257,23 @@
         <v>100</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>2392</v>
+        <v>2366</v>
       </c>
       <c r="C216" s="58"/>
       <c r="D216" s="30" t="s">
-        <v>2339</v>
+        <v>2313</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>2340</v>
+        <v>2314</v>
       </c>
       <c r="F216" s="30" t="s">
-        <v>2341</v>
+        <v>2315</v>
       </c>
       <c r="G216" s="30" t="s">
-        <v>2342</v>
+        <v>2316</v>
       </c>
       <c r="H216" s="30" t="s">
-        <v>2343</v>
+        <v>2317</v>
       </c>
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
@@ -21153,23 +21287,23 @@
         <v>100</v>
       </c>
       <c r="B217" s="59" t="s">
-        <v>2393</v>
+        <v>2367</v>
       </c>
       <c r="C217" s="60"/>
       <c r="D217" s="31" t="s">
-        <v>2344</v>
+        <v>2318</v>
       </c>
       <c r="E217" s="31" t="s">
-        <v>2345</v>
+        <v>2319</v>
       </c>
       <c r="F217" s="31" t="s">
-        <v>2346</v>
+        <v>2320</v>
       </c>
       <c r="G217" s="31" t="s">
-        <v>2347</v>
+        <v>2321</v>
       </c>
       <c r="H217" s="31" t="s">
-        <v>2348</v>
+        <v>2322</v>
       </c>
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
@@ -21183,23 +21317,23 @@
         <v>100</v>
       </c>
       <c r="B218" s="29" t="s">
-        <v>2394</v>
+        <v>2368</v>
       </c>
       <c r="C218" s="58"/>
       <c r="D218" s="30" t="s">
-        <v>2349</v>
+        <v>2323</v>
       </c>
       <c r="E218" s="30" t="s">
-        <v>2350</v>
+        <v>2324</v>
       </c>
       <c r="F218" s="30" t="s">
-        <v>2351</v>
+        <v>2325</v>
       </c>
       <c r="G218" s="30" t="s">
-        <v>2352</v>
+        <v>2326</v>
       </c>
       <c r="H218" s="30" t="s">
-        <v>2353</v>
+        <v>2327</v>
       </c>
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
@@ -21213,10 +21347,10 @@
         <v>99</v>
       </c>
       <c r="B219" s="59" t="s">
-        <v>2401</v>
+        <v>2375</v>
       </c>
       <c r="C219" s="60" t="s">
-        <v>2354</v>
+        <v>2328</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -21237,23 +21371,23 @@
         <v>100</v>
       </c>
       <c r="B220" s="59" t="s">
-        <v>2395</v>
+        <v>2369</v>
       </c>
       <c r="C220" s="60"/>
       <c r="D220" s="31" t="s">
-        <v>2355</v>
+        <v>2329</v>
       </c>
       <c r="E220" s="31" t="s">
-        <v>2356</v>
+        <v>2330</v>
       </c>
       <c r="F220" s="31" t="s">
-        <v>2357</v>
+        <v>2331</v>
       </c>
       <c r="G220" s="31" t="s">
-        <v>2358</v>
+        <v>2332</v>
       </c>
       <c r="H220" s="31" t="s">
-        <v>2359</v>
+        <v>2333</v>
       </c>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
@@ -21267,23 +21401,23 @@
         <v>100</v>
       </c>
       <c r="B221" s="59" t="s">
-        <v>2402</v>
+        <v>2376</v>
       </c>
       <c r="C221" s="60"/>
       <c r="D221" s="30" t="s">
-        <v>2360</v>
+        <v>2334</v>
       </c>
       <c r="E221" s="30" t="s">
-        <v>2361</v>
+        <v>2335</v>
       </c>
       <c r="F221" s="30" t="s">
-        <v>2362</v>
+        <v>2336</v>
       </c>
       <c r="G221" s="30" t="s">
-        <v>2363</v>
+        <v>2337</v>
       </c>
       <c r="H221" s="30" t="s">
-        <v>2364</v>
+        <v>2338</v>
       </c>
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
@@ -21297,23 +21431,23 @@
         <v>100</v>
       </c>
       <c r="B222" s="59" t="s">
-        <v>2396</v>
+        <v>2370</v>
       </c>
       <c r="C222" s="60"/>
       <c r="D222" s="31" t="s">
-        <v>2365</v>
+        <v>2339</v>
       </c>
       <c r="E222" s="31" t="s">
-        <v>2366</v>
+        <v>2340</v>
       </c>
       <c r="F222" s="31" t="s">
-        <v>2367</v>
+        <v>2341</v>
       </c>
       <c r="G222" s="31" t="s">
-        <v>2368</v>
+        <v>2342</v>
       </c>
       <c r="H222" s="31" t="s">
-        <v>2369</v>
+        <v>2343</v>
       </c>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
@@ -21327,10 +21461,10 @@
         <v>99</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>2397</v>
+        <v>2371</v>
       </c>
       <c r="C223" s="58" t="s">
-        <v>2370</v>
+        <v>2344</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
@@ -21351,23 +21485,23 @@
         <v>100</v>
       </c>
       <c r="B224" s="29" t="s">
-        <v>2398</v>
+        <v>2372</v>
       </c>
       <c r="C224" s="58"/>
       <c r="D224" s="30" t="s">
-        <v>2371</v>
+        <v>2345</v>
       </c>
       <c r="E224" s="30" t="s">
-        <v>2372</v>
+        <v>2346</v>
       </c>
       <c r="F224" s="30" t="s">
-        <v>2373</v>
+        <v>2347</v>
       </c>
       <c r="G224" s="30" t="s">
-        <v>2374</v>
+        <v>2348</v>
       </c>
       <c r="H224" s="30" t="s">
-        <v>2375</v>
+        <v>2349</v>
       </c>
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
@@ -21381,23 +21515,23 @@
         <v>100</v>
       </c>
       <c r="B225" s="59" t="s">
-        <v>2399</v>
+        <v>2373</v>
       </c>
       <c r="C225" s="60"/>
       <c r="D225" s="31" t="s">
-        <v>2376</v>
+        <v>2350</v>
       </c>
       <c r="E225" s="31" t="s">
-        <v>2377</v>
+        <v>2351</v>
       </c>
       <c r="F225" s="31" t="s">
-        <v>2378</v>
+        <v>2352</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>2379</v>
+        <v>2353</v>
       </c>
       <c r="H225" s="31" t="s">
-        <v>2380</v>
+        <v>2354</v>
       </c>
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
@@ -21411,23 +21545,23 @@
         <v>100</v>
       </c>
       <c r="B226" s="29" t="s">
-        <v>2400</v>
+        <v>2374</v>
       </c>
       <c r="C226" s="58"/>
       <c r="D226" s="30" t="s">
-        <v>2381</v>
+        <v>2355</v>
       </c>
       <c r="E226" s="30" t="s">
-        <v>2382</v>
+        <v>2356</v>
       </c>
       <c r="F226" s="30" t="s">
-        <v>2383</v>
+        <v>2357</v>
       </c>
       <c r="G226" s="30" t="s">
-        <v>2384</v>
+        <v>2358</v>
       </c>
       <c r="H226" s="30" t="s">
-        <v>2385</v>
+        <v>2359</v>
       </c>
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
@@ -22195,7 +22329,7 @@
         <v>781</v>
       </c>
       <c r="H253" s="13" t="s">
-        <v>2406</v>
+        <v>2380</v>
       </c>
       <c r="I253" s="2"/>
       <c r="J253" s="18"/>
@@ -22929,23 +23063,23 @@
         <v>98</v>
       </c>
       <c r="B274" s="40" t="s">
-        <v>1881</v>
+        <v>1855</v>
       </c>
       <c r="C274" s="41"/>
       <c r="D274" s="42" t="s">
-        <v>1882</v>
+        <v>1856</v>
       </c>
       <c r="E274" s="42" t="s">
-        <v>1883</v>
+        <v>1857</v>
       </c>
       <c r="F274" s="42" t="s">
-        <v>1884</v>
+        <v>1858</v>
       </c>
       <c r="G274" s="42" t="s">
-        <v>1885</v>
+        <v>1859</v>
       </c>
       <c r="H274" s="42" t="s">
-        <v>1886</v>
+        <v>1860</v>
       </c>
       <c r="I274" s="2"/>
       <c r="J274" s="18" t="s">
@@ -22963,23 +23097,23 @@
         <v>98</v>
       </c>
       <c r="B275" s="37" t="s">
-        <v>1887</v>
+        <v>1861</v>
       </c>
       <c r="C275" s="38"/>
       <c r="D275" s="39" t="s">
-        <v>1888</v>
+        <v>1862</v>
       </c>
       <c r="E275" s="39" t="s">
-        <v>1889</v>
+        <v>1863</v>
       </c>
       <c r="F275" s="39" t="s">
-        <v>1890</v>
+        <v>1864</v>
       </c>
       <c r="G275" s="39" t="s">
-        <v>1891</v>
+        <v>1865</v>
       </c>
       <c r="H275" s="39" t="s">
-        <v>1892</v>
+        <v>1866</v>
       </c>
       <c r="I275" s="2"/>
       <c r="J275" s="18" t="s">
@@ -22997,23 +23131,23 @@
         <v>98</v>
       </c>
       <c r="B276" s="40" t="s">
-        <v>1893</v>
+        <v>1867</v>
       </c>
       <c r="C276" s="41"/>
       <c r="D276" s="42" t="s">
-        <v>1894</v>
+        <v>1868</v>
       </c>
       <c r="E276" s="42" t="s">
-        <v>1895</v>
+        <v>1869</v>
       </c>
       <c r="F276" s="42" t="s">
-        <v>1896</v>
+        <v>1870</v>
       </c>
       <c r="G276" s="42" t="s">
-        <v>1897</v>
+        <v>1871</v>
       </c>
       <c r="H276" s="42" t="s">
-        <v>1898</v>
+        <v>1872</v>
       </c>
       <c r="I276" s="2"/>
       <c r="J276" s="18" t="s">
@@ -23031,23 +23165,23 @@
         <v>98</v>
       </c>
       <c r="B277" s="37" t="s">
-        <v>1899</v>
+        <v>1873</v>
       </c>
       <c r="C277" s="38"/>
       <c r="D277" s="39" t="s">
-        <v>1900</v>
+        <v>1874</v>
       </c>
       <c r="E277" s="39" t="s">
-        <v>1901</v>
+        <v>1875</v>
       </c>
       <c r="F277" s="39" t="s">
-        <v>1902</v>
+        <v>1876</v>
       </c>
       <c r="G277" s="39" t="s">
-        <v>1903</v>
+        <v>1877</v>
       </c>
       <c r="H277" s="39" t="s">
-        <v>1904</v>
+        <v>1878</v>
       </c>
       <c r="I277" s="2"/>
       <c r="J277" s="18" t="s">
@@ -23065,23 +23199,23 @@
         <v>98</v>
       </c>
       <c r="B278" s="40" t="s">
-        <v>1905</v>
+        <v>1879</v>
       </c>
       <c r="C278" s="41"/>
       <c r="D278" s="42" t="s">
-        <v>1906</v>
+        <v>1880</v>
       </c>
       <c r="E278" s="42" t="s">
-        <v>1907</v>
+        <v>1881</v>
       </c>
       <c r="F278" s="42" t="s">
-        <v>1908</v>
+        <v>1882</v>
       </c>
       <c r="G278" s="42" t="s">
-        <v>1909</v>
+        <v>1883</v>
       </c>
       <c r="H278" s="42" t="s">
-        <v>1910</v>
+        <v>1884</v>
       </c>
       <c r="I278" s="2"/>
       <c r="J278" s="18" t="s">
@@ -23099,23 +23233,23 @@
         <v>98</v>
       </c>
       <c r="B279" s="37" t="s">
-        <v>1911</v>
+        <v>1885</v>
       </c>
       <c r="C279" s="38"/>
       <c r="D279" s="39" t="s">
-        <v>1912</v>
+        <v>1886</v>
       </c>
       <c r="E279" s="39" t="s">
-        <v>1913</v>
+        <v>1887</v>
       </c>
       <c r="F279" s="39" t="s">
-        <v>1914</v>
+        <v>1888</v>
       </c>
       <c r="G279" s="39" t="s">
-        <v>1915</v>
+        <v>1889</v>
       </c>
       <c r="H279" s="39" t="s">
-        <v>1916</v>
+        <v>1890</v>
       </c>
       <c r="I279" s="2"/>
       <c r="J279" s="18" t="s">
@@ -23133,23 +23267,23 @@
         <v>98</v>
       </c>
       <c r="B280" s="40" t="s">
-        <v>1917</v>
+        <v>1891</v>
       </c>
       <c r="C280" s="41"/>
       <c r="D280" s="42" t="s">
-        <v>1918</v>
+        <v>1892</v>
       </c>
       <c r="E280" s="42" t="s">
-        <v>1919</v>
+        <v>1893</v>
       </c>
       <c r="F280" s="42" t="s">
-        <v>1920</v>
+        <v>1894</v>
       </c>
       <c r="G280" s="42" t="s">
-        <v>1921</v>
+        <v>1895</v>
       </c>
       <c r="H280" s="42" t="s">
-        <v>1922</v>
+        <v>1896</v>
       </c>
       <c r="I280" s="2"/>
       <c r="J280" s="18" t="s">
@@ -23167,7 +23301,7 @@
         <v>99</v>
       </c>
       <c r="B281" s="49" t="s">
-        <v>2039</v>
+        <v>2013</v>
       </c>
       <c r="C281" s="50"/>
       <c r="D281" s="50"/>
@@ -23189,23 +23323,23 @@
         <v>100</v>
       </c>
       <c r="B282" s="37" t="s">
-        <v>1923</v>
+        <v>1897</v>
       </c>
       <c r="C282" s="51"/>
       <c r="D282" s="39" t="s">
-        <v>1924</v>
+        <v>1898</v>
       </c>
       <c r="E282" s="39" t="s">
-        <v>1925</v>
+        <v>1899</v>
       </c>
       <c r="F282" s="39" t="s">
-        <v>1926</v>
+        <v>1900</v>
       </c>
       <c r="G282" s="39" t="s">
-        <v>1927</v>
+        <v>1901</v>
       </c>
       <c r="H282" s="39" t="s">
-        <v>1928</v>
+        <v>1902</v>
       </c>
       <c r="I282" s="2"/>
       <c r="J282" s="18"/>
@@ -23219,23 +23353,23 @@
         <v>98</v>
       </c>
       <c r="B283" s="40" t="s">
-        <v>1929</v>
+        <v>1903</v>
       </c>
       <c r="C283" s="41"/>
       <c r="D283" s="42" t="s">
-        <v>1930</v>
+        <v>1904</v>
       </c>
       <c r="E283" s="42" t="s">
-        <v>1931</v>
+        <v>1905</v>
       </c>
       <c r="F283" s="42" t="s">
-        <v>1932</v>
+        <v>1906</v>
       </c>
       <c r="G283" s="42" t="s">
-        <v>1933</v>
+        <v>1907</v>
       </c>
       <c r="H283" s="42" t="s">
-        <v>1934</v>
+        <v>1908</v>
       </c>
       <c r="I283" s="2"/>
       <c r="J283" s="18" t="s">
@@ -23253,23 +23387,23 @@
         <v>98</v>
       </c>
       <c r="B284" s="37" t="s">
-        <v>1935</v>
+        <v>1909</v>
       </c>
       <c r="C284" s="38"/>
       <c r="D284" s="39" t="s">
-        <v>1936</v>
+        <v>1910</v>
       </c>
       <c r="E284" s="39" t="s">
-        <v>1937</v>
+        <v>1911</v>
       </c>
       <c r="F284" s="39" t="s">
-        <v>1938</v>
+        <v>1912</v>
       </c>
       <c r="G284" s="39" t="s">
-        <v>1939</v>
+        <v>1913</v>
       </c>
       <c r="H284" s="39" t="s">
-        <v>1940</v>
+        <v>1914</v>
       </c>
       <c r="I284" s="2"/>
       <c r="J284" s="18" t="s">
@@ -23287,23 +23421,23 @@
         <v>98</v>
       </c>
       <c r="B285" s="40" t="s">
-        <v>1941</v>
+        <v>1915</v>
       </c>
       <c r="C285" s="41"/>
       <c r="D285" s="42" t="s">
-        <v>1942</v>
+        <v>1916</v>
       </c>
       <c r="E285" s="42" t="s">
-        <v>1943</v>
+        <v>1917</v>
       </c>
       <c r="F285" s="42" t="s">
-        <v>1944</v>
+        <v>1918</v>
       </c>
       <c r="G285" s="42" t="s">
-        <v>1945</v>
+        <v>1919</v>
       </c>
       <c r="H285" s="42" t="s">
-        <v>1946</v>
+        <v>1920</v>
       </c>
       <c r="I285" s="2"/>
       <c r="J285" s="18" t="s">
@@ -23321,23 +23455,23 @@
         <v>98</v>
       </c>
       <c r="B286" s="37" t="s">
-        <v>1947</v>
+        <v>1921</v>
       </c>
       <c r="C286" s="38"/>
       <c r="D286" s="39" t="s">
-        <v>1948</v>
+        <v>1922</v>
       </c>
       <c r="E286" s="39" t="s">
-        <v>1949</v>
+        <v>1923</v>
       </c>
       <c r="F286" s="39" t="s">
-        <v>1950</v>
+        <v>1924</v>
       </c>
       <c r="G286" s="39" t="s">
-        <v>1951</v>
+        <v>1925</v>
       </c>
       <c r="H286" s="39" t="s">
-        <v>1952</v>
+        <v>1926</v>
       </c>
       <c r="I286" s="2"/>
       <c r="J286" s="18" t="s">
@@ -23355,23 +23489,23 @@
         <v>98</v>
       </c>
       <c r="B287" s="40" t="s">
-        <v>1953</v>
+        <v>1927</v>
       </c>
       <c r="C287" s="41"/>
       <c r="D287" s="42" t="s">
-        <v>1954</v>
+        <v>1928</v>
       </c>
       <c r="E287" s="42" t="s">
-        <v>1955</v>
+        <v>1929</v>
       </c>
       <c r="F287" s="42" t="s">
-        <v>1956</v>
+        <v>1930</v>
       </c>
       <c r="G287" s="42" t="s">
-        <v>1957</v>
+        <v>1931</v>
       </c>
       <c r="H287" s="42" t="s">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="I287" s="2"/>
       <c r="J287" s="18" t="s">
@@ -23389,23 +23523,23 @@
         <v>98</v>
       </c>
       <c r="B288" s="37" t="s">
-        <v>1959</v>
+        <v>1933</v>
       </c>
       <c r="C288" s="38"/>
       <c r="D288" s="39" t="s">
-        <v>1960</v>
+        <v>1934</v>
       </c>
       <c r="E288" s="39" t="s">
-        <v>1961</v>
+        <v>1935</v>
       </c>
       <c r="F288" s="39" t="s">
-        <v>1962</v>
+        <v>1936</v>
       </c>
       <c r="G288" s="39" t="s">
-        <v>1963</v>
+        <v>1937</v>
       </c>
       <c r="H288" s="39" t="s">
-        <v>1964</v>
+        <v>1938</v>
       </c>
       <c r="I288" s="2"/>
       <c r="J288" s="18" t="s">
@@ -24041,23 +24175,23 @@
         <v>98</v>
       </c>
       <c r="B312" s="40" t="s">
-        <v>1965</v>
+        <v>1939</v>
       </c>
       <c r="C312" s="41"/>
       <c r="D312" s="42" t="s">
-        <v>1966</v>
+        <v>1940</v>
       </c>
       <c r="E312" s="42" t="s">
-        <v>1967</v>
+        <v>1941</v>
       </c>
       <c r="F312" s="42" t="s">
-        <v>1968</v>
+        <v>1942</v>
       </c>
       <c r="G312" s="42" t="s">
-        <v>1969</v>
+        <v>1943</v>
       </c>
       <c r="H312" s="42" t="s">
-        <v>1970</v>
+        <v>1944</v>
       </c>
       <c r="I312" s="2"/>
       <c r="J312" s="18" t="s">
@@ -24075,23 +24209,23 @@
         <v>98</v>
       </c>
       <c r="B313" s="37" t="s">
-        <v>1971</v>
+        <v>1945</v>
       </c>
       <c r="C313" s="38"/>
       <c r="D313" s="39" t="s">
-        <v>1972</v>
+        <v>1946</v>
       </c>
       <c r="E313" s="39" t="s">
-        <v>1973</v>
+        <v>1947</v>
       </c>
       <c r="F313" s="39" t="s">
-        <v>1974</v>
+        <v>1948</v>
       </c>
       <c r="G313" s="39" t="s">
-        <v>1975</v>
+        <v>1949</v>
       </c>
       <c r="H313" s="39" t="s">
-        <v>1976</v>
+        <v>1950</v>
       </c>
       <c r="I313" s="2"/>
       <c r="J313" s="18" t="s">
@@ -24109,23 +24243,23 @@
         <v>98</v>
       </c>
       <c r="B314" s="40" t="s">
-        <v>1977</v>
+        <v>1951</v>
       </c>
       <c r="C314" s="41"/>
       <c r="D314" s="42" t="s">
-        <v>1978</v>
+        <v>1952</v>
       </c>
       <c r="E314" s="42" t="s">
-        <v>1979</v>
+        <v>1953</v>
       </c>
       <c r="F314" s="42" t="s">
-        <v>1980</v>
+        <v>1954</v>
       </c>
       <c r="G314" s="42" t="s">
-        <v>1981</v>
+        <v>1955</v>
       </c>
       <c r="H314" s="42" t="s">
-        <v>1982</v>
+        <v>1956</v>
       </c>
       <c r="I314" s="2"/>
       <c r="J314" s="18" t="s">
@@ -24143,23 +24277,23 @@
         <v>98</v>
       </c>
       <c r="B315" s="37" t="s">
-        <v>1983</v>
+        <v>1957</v>
       </c>
       <c r="C315" s="38"/>
       <c r="D315" s="39" t="s">
-        <v>1984</v>
+        <v>1958</v>
       </c>
       <c r="E315" s="39" t="s">
-        <v>1985</v>
+        <v>1959</v>
       </c>
       <c r="F315" s="39" t="s">
-        <v>1986</v>
+        <v>1960</v>
       </c>
       <c r="G315" s="39" t="s">
-        <v>1987</v>
+        <v>1961</v>
       </c>
       <c r="H315" s="39" t="s">
-        <v>1988</v>
+        <v>1962</v>
       </c>
       <c r="I315" s="2"/>
       <c r="J315" s="18" t="s">
@@ -24177,7 +24311,7 @@
         <v>99</v>
       </c>
       <c r="B316" s="49" t="s">
-        <v>2040</v>
+        <v>2014</v>
       </c>
       <c r="C316" s="50"/>
       <c r="D316" s="50"/>
@@ -24199,23 +24333,23 @@
         <v>100</v>
       </c>
       <c r="B317" s="40" t="s">
-        <v>1989</v>
+        <v>1963</v>
       </c>
       <c r="C317" s="41"/>
       <c r="D317" s="42" t="s">
-        <v>1990</v>
+        <v>1964</v>
       </c>
       <c r="E317" s="42" t="s">
-        <v>1991</v>
+        <v>1965</v>
       </c>
       <c r="F317" s="42" t="s">
-        <v>1992</v>
+        <v>1966</v>
       </c>
       <c r="G317" s="42" t="s">
-        <v>1993</v>
+        <v>1967</v>
       </c>
       <c r="H317" s="42" t="s">
-        <v>1994</v>
+        <v>1968</v>
       </c>
       <c r="I317" s="2"/>
       <c r="J317" s="18"/>
@@ -24229,23 +24363,23 @@
         <v>100</v>
       </c>
       <c r="B318" s="37" t="s">
-        <v>1995</v>
+        <v>1969</v>
       </c>
       <c r="C318" s="38"/>
       <c r="D318" s="39" t="s">
-        <v>1996</v>
+        <v>1970</v>
       </c>
       <c r="E318" s="39" t="s">
-        <v>1997</v>
+        <v>1971</v>
       </c>
       <c r="F318" s="39" t="s">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="G318" s="39" t="s">
-        <v>1999</v>
+        <v>1973</v>
       </c>
       <c r="H318" s="39" t="s">
-        <v>2000</v>
+        <v>1974</v>
       </c>
       <c r="I318" s="2"/>
       <c r="J318" s="18"/>
@@ -24259,23 +24393,23 @@
         <v>100</v>
       </c>
       <c r="B319" s="40" t="s">
-        <v>2001</v>
+        <v>1975</v>
       </c>
       <c r="C319" s="41"/>
       <c r="D319" s="42" t="s">
-        <v>2002</v>
+        <v>1976</v>
       </c>
       <c r="E319" s="42" t="s">
-        <v>2003</v>
+        <v>1977</v>
       </c>
       <c r="F319" s="42" t="s">
-        <v>2004</v>
+        <v>1978</v>
       </c>
       <c r="G319" s="42" t="s">
-        <v>2005</v>
+        <v>1979</v>
       </c>
       <c r="H319" s="42" t="s">
-        <v>2006</v>
+        <v>1980</v>
       </c>
       <c r="I319" s="2"/>
       <c r="J319" s="18"/>
@@ -24289,7 +24423,7 @@
         <v>99</v>
       </c>
       <c r="B320" s="49" t="s">
-        <v>2041</v>
+        <v>2015</v>
       </c>
       <c r="C320" s="50"/>
       <c r="D320" s="50"/>
@@ -24311,23 +24445,23 @@
         <v>100</v>
       </c>
       <c r="B321" s="37" t="s">
-        <v>2007</v>
+        <v>1981</v>
       </c>
       <c r="C321" s="38"/>
       <c r="D321" s="39" t="s">
-        <v>2008</v>
+        <v>1982</v>
       </c>
       <c r="E321" s="39" t="s">
-        <v>2009</v>
+        <v>1983</v>
       </c>
       <c r="F321" s="39" t="s">
-        <v>2010</v>
+        <v>1984</v>
       </c>
       <c r="G321" s="39" t="s">
-        <v>2011</v>
+        <v>1985</v>
       </c>
       <c r="H321" s="39" t="s">
-        <v>2012</v>
+        <v>1986</v>
       </c>
       <c r="I321" s="2"/>
       <c r="J321" s="18"/>
@@ -24341,23 +24475,23 @@
         <v>100</v>
       </c>
       <c r="B322" s="40" t="s">
-        <v>2013</v>
+        <v>1987</v>
       </c>
       <c r="C322" s="41"/>
       <c r="D322" s="42" t="s">
-        <v>2014</v>
+        <v>1988</v>
       </c>
       <c r="E322" s="42" t="s">
-        <v>2015</v>
+        <v>1989</v>
       </c>
       <c r="F322" s="42" t="s">
-        <v>2016</v>
+        <v>1990</v>
       </c>
       <c r="G322" s="42" t="s">
-        <v>2017</v>
+        <v>1991</v>
       </c>
       <c r="H322" s="42" t="s">
-        <v>2018</v>
+        <v>1992</v>
       </c>
       <c r="I322" s="2"/>
       <c r="J322" s="18"/>
@@ -24371,7 +24505,7 @@
         <v>99</v>
       </c>
       <c r="B323" s="49" t="s">
-        <v>2042</v>
+        <v>2016</v>
       </c>
       <c r="C323" s="50"/>
       <c r="D323" s="50"/>
@@ -24393,23 +24527,23 @@
         <v>100</v>
       </c>
       <c r="B324" s="37" t="s">
-        <v>2019</v>
+        <v>1993</v>
       </c>
       <c r="C324" s="51"/>
       <c r="D324" s="39" t="s">
-        <v>2020</v>
+        <v>1994</v>
       </c>
       <c r="E324" s="39" t="s">
-        <v>2021</v>
+        <v>1995</v>
       </c>
       <c r="F324" s="39" t="s">
-        <v>2022</v>
+        <v>1996</v>
       </c>
       <c r="G324" s="39" t="s">
-        <v>2023</v>
+        <v>1997</v>
       </c>
       <c r="H324" s="39" t="s">
-        <v>2024</v>
+        <v>1998</v>
       </c>
       <c r="I324" s="2"/>
       <c r="J324" s="18"/>
@@ -24423,23 +24557,23 @@
         <v>100</v>
       </c>
       <c r="B325" s="40" t="s">
-        <v>2025</v>
+        <v>1999</v>
       </c>
       <c r="C325" s="43"/>
       <c r="D325" s="42" t="s">
-        <v>2020</v>
+        <v>1994</v>
       </c>
       <c r="E325" s="42" t="s">
-        <v>2021</v>
+        <v>1995</v>
       </c>
       <c r="F325" s="42" t="s">
-        <v>2022</v>
+        <v>1996</v>
       </c>
       <c r="G325" s="42" t="s">
-        <v>2023</v>
+        <v>1997</v>
       </c>
       <c r="H325" s="42" t="s">
-        <v>2024</v>
+        <v>1998</v>
       </c>
       <c r="I325" s="2"/>
       <c r="J325" s="18"/>
@@ -24453,23 +24587,23 @@
         <v>100</v>
       </c>
       <c r="B326" s="37" t="s">
-        <v>2026</v>
+        <v>2000</v>
       </c>
       <c r="C326" s="51"/>
       <c r="D326" s="39" t="s">
-        <v>2020</v>
+        <v>1994</v>
       </c>
       <c r="E326" s="39" t="s">
-        <v>2021</v>
+        <v>1995</v>
       </c>
       <c r="F326" s="39" t="s">
-        <v>2022</v>
+        <v>1996</v>
       </c>
       <c r="G326" s="39" t="s">
-        <v>2023</v>
+        <v>1997</v>
       </c>
       <c r="H326" s="39" t="s">
-        <v>2024</v>
+        <v>1998</v>
       </c>
       <c r="I326" s="2"/>
       <c r="J326" s="18"/>
@@ -24483,23 +24617,23 @@
         <v>100</v>
       </c>
       <c r="B327" s="40" t="s">
-        <v>2027</v>
+        <v>2001</v>
       </c>
       <c r="C327" s="41"/>
       <c r="D327" s="42" t="s">
-        <v>2028</v>
+        <v>2002</v>
       </c>
       <c r="E327" s="42" t="s">
-        <v>2029</v>
+        <v>2003</v>
       </c>
       <c r="F327" s="42" t="s">
-        <v>2030</v>
+        <v>2004</v>
       </c>
       <c r="G327" s="42" t="s">
-        <v>2031</v>
+        <v>2005</v>
       </c>
       <c r="H327" s="42" t="s">
-        <v>2032</v>
+        <v>2006</v>
       </c>
       <c r="I327" s="2"/>
       <c r="J327" s="18"/>
@@ -24513,23 +24647,23 @@
         <v>100</v>
       </c>
       <c r="B328" s="37" t="s">
-        <v>2033</v>
+        <v>2007</v>
       </c>
       <c r="C328" s="38"/>
       <c r="D328" s="39" t="s">
-        <v>2034</v>
+        <v>2008</v>
       </c>
       <c r="E328" s="39" t="s">
-        <v>2035</v>
+        <v>2009</v>
       </c>
       <c r="F328" s="39" t="s">
-        <v>2036</v>
+        <v>2010</v>
       </c>
       <c r="G328" s="39" t="s">
-        <v>2037</v>
+        <v>2011</v>
       </c>
       <c r="H328" s="39" t="s">
-        <v>2038</v>
+        <v>2012</v>
       </c>
       <c r="I328" s="2"/>
       <c r="J328" s="18"/>
@@ -26127,23 +26261,23 @@
         <v>98</v>
       </c>
       <c r="B379" s="52" t="s">
-        <v>2105</v>
+        <v>2079</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" s="52" t="s">
-        <v>2119</v>
+        <v>2093</v>
       </c>
       <c r="E379" s="52" t="s">
-        <v>2120</v>
+        <v>2094</v>
       </c>
       <c r="F379" s="52" t="s">
-        <v>2121</v>
+        <v>2095</v>
       </c>
       <c r="G379" s="52" t="s">
-        <v>2122</v>
+        <v>2096</v>
       </c>
       <c r="H379" s="52" t="s">
-        <v>2123</v>
+        <v>2097</v>
       </c>
       <c r="I379" s="2"/>
       <c r="J379" s="18" t="s">
@@ -26161,23 +26295,23 @@
         <v>98</v>
       </c>
       <c r="B380" s="53" t="s">
-        <v>2106</v>
+        <v>2080</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="53" t="s">
-        <v>2124</v>
+        <v>2098</v>
       </c>
       <c r="E380" s="53" t="s">
-        <v>2125</v>
+        <v>2099</v>
       </c>
       <c r="F380" s="53" t="s">
-        <v>2126</v>
+        <v>2100</v>
       </c>
       <c r="G380" s="53" t="s">
-        <v>2127</v>
+        <v>2101</v>
       </c>
       <c r="H380" s="53" t="s">
-        <v>2128</v>
+        <v>2102</v>
       </c>
       <c r="I380" s="2"/>
       <c r="J380" s="18" t="s">
@@ -26195,23 +26329,23 @@
         <v>98</v>
       </c>
       <c r="B381" s="52" t="s">
-        <v>2107</v>
+        <v>2081</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" s="52" t="s">
-        <v>2124</v>
+        <v>2098</v>
       </c>
       <c r="E381" s="52" t="s">
-        <v>2125</v>
+        <v>2099</v>
       </c>
       <c r="F381" s="52" t="s">
-        <v>2126</v>
+        <v>2100</v>
       </c>
       <c r="G381" s="52" t="s">
-        <v>2127</v>
+        <v>2101</v>
       </c>
       <c r="H381" s="52" t="s">
-        <v>2128</v>
+        <v>2102</v>
       </c>
       <c r="I381" s="2"/>
       <c r="J381" s="18" t="s">
@@ -26229,23 +26363,23 @@
         <v>98</v>
       </c>
       <c r="B382" s="53" t="s">
-        <v>2108</v>
+        <v>2082</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" s="53" t="s">
-        <v>2129</v>
+        <v>2103</v>
       </c>
       <c r="E382" s="53" t="s">
-        <v>2130</v>
+        <v>2104</v>
       </c>
       <c r="F382" s="53" t="s">
-        <v>2131</v>
+        <v>2105</v>
       </c>
       <c r="G382" s="53" t="s">
-        <v>2132</v>
+        <v>2106</v>
       </c>
       <c r="H382" s="53" t="s">
-        <v>2133</v>
+        <v>2107</v>
       </c>
       <c r="I382" s="2"/>
       <c r="J382" s="18" t="s">
@@ -26263,23 +26397,23 @@
         <v>98</v>
       </c>
       <c r="B383" s="52" t="s">
-        <v>2109</v>
+        <v>2083</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" s="52" t="s">
-        <v>2134</v>
+        <v>2108</v>
       </c>
       <c r="E383" s="52" t="s">
-        <v>2135</v>
+        <v>2109</v>
       </c>
       <c r="F383" s="52" t="s">
-        <v>2136</v>
+        <v>2110</v>
       </c>
       <c r="G383" s="52" t="s">
-        <v>2137</v>
+        <v>2111</v>
       </c>
       <c r="H383" s="52" t="s">
-        <v>2128</v>
+        <v>2102</v>
       </c>
       <c r="I383" s="2"/>
       <c r="J383" s="18" t="s">
@@ -26297,23 +26431,23 @@
         <v>98</v>
       </c>
       <c r="B384" s="53" t="s">
-        <v>2110</v>
+        <v>2084</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" s="53" t="s">
-        <v>2138</v>
+        <v>2112</v>
       </c>
       <c r="E384" s="53" t="s">
-        <v>2139</v>
+        <v>2113</v>
       </c>
       <c r="F384" s="53" t="s">
-        <v>2140</v>
+        <v>2114</v>
       </c>
       <c r="G384" s="53" t="s">
-        <v>2141</v>
+        <v>2115</v>
       </c>
       <c r="H384" s="53" t="s">
-        <v>2128</v>
+        <v>2102</v>
       </c>
       <c r="I384" s="2"/>
       <c r="J384" s="18" t="s">
@@ -26331,23 +26465,23 @@
         <v>98</v>
       </c>
       <c r="B385" s="52" t="s">
-        <v>2111</v>
+        <v>2085</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" s="52" t="s">
-        <v>2142</v>
+        <v>2116</v>
       </c>
       <c r="E385" s="52" t="s">
-        <v>2143</v>
+        <v>2117</v>
       </c>
       <c r="F385" s="52" t="s">
-        <v>2144</v>
+        <v>2118</v>
       </c>
       <c r="G385" s="52" t="s">
-        <v>2145</v>
+        <v>2119</v>
       </c>
       <c r="H385" s="52" t="s">
-        <v>2123</v>
+        <v>2097</v>
       </c>
       <c r="I385" s="2"/>
       <c r="J385" s="18" t="s">
@@ -26365,23 +26499,23 @@
         <v>98</v>
       </c>
       <c r="B386" s="53" t="s">
-        <v>2112</v>
+        <v>2086</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" s="53" t="s">
-        <v>2146</v>
+        <v>2120</v>
       </c>
       <c r="E386" s="53" t="s">
-        <v>2147</v>
+        <v>2121</v>
       </c>
       <c r="F386" s="53" t="s">
-        <v>2148</v>
+        <v>2122</v>
       </c>
       <c r="G386" s="53" t="s">
-        <v>2149</v>
+        <v>2123</v>
       </c>
       <c r="H386" s="53" t="s">
-        <v>2150</v>
+        <v>2124</v>
       </c>
       <c r="I386" s="2"/>
       <c r="J386" s="18" t="s">
@@ -26399,23 +26533,23 @@
         <v>98</v>
       </c>
       <c r="B387" s="52" t="s">
-        <v>2113</v>
+        <v>2087</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" s="52" t="s">
-        <v>2151</v>
+        <v>2125</v>
       </c>
       <c r="E387" s="52" t="s">
-        <v>2152</v>
+        <v>2126</v>
       </c>
       <c r="F387" s="52" t="s">
-        <v>2153</v>
+        <v>2127</v>
       </c>
       <c r="G387" s="52" t="s">
-        <v>2154</v>
+        <v>2128</v>
       </c>
       <c r="H387" s="52" t="s">
-        <v>2128</v>
+        <v>2102</v>
       </c>
       <c r="I387" s="2"/>
       <c r="J387" s="18" t="s">
@@ -26433,23 +26567,23 @@
         <v>98</v>
       </c>
       <c r="B388" s="53" t="s">
-        <v>2114</v>
+        <v>2088</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" s="53" t="s">
-        <v>2151</v>
+        <v>2125</v>
       </c>
       <c r="E388" s="53" t="s">
-        <v>2152</v>
+        <v>2126</v>
       </c>
       <c r="F388" s="53" t="s">
-        <v>2153</v>
+        <v>2127</v>
       </c>
       <c r="G388" s="53" t="s">
-        <v>2154</v>
+        <v>2128</v>
       </c>
       <c r="H388" s="53" t="s">
-        <v>2128</v>
+        <v>2102</v>
       </c>
       <c r="I388" s="2"/>
       <c r="J388" s="18" t="s">
@@ -26467,23 +26601,23 @@
         <v>98</v>
       </c>
       <c r="B389" s="52" t="s">
-        <v>2115</v>
+        <v>2089</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" s="52" t="s">
-        <v>2155</v>
+        <v>2129</v>
       </c>
       <c r="E389" s="52" t="s">
-        <v>2156</v>
+        <v>2130</v>
       </c>
       <c r="F389" s="52" t="s">
-        <v>2157</v>
+        <v>2131</v>
       </c>
       <c r="G389" s="52" t="s">
-        <v>2158</v>
+        <v>2132</v>
       </c>
       <c r="H389" s="52" t="s">
-        <v>2159</v>
+        <v>2133</v>
       </c>
       <c r="I389" s="2"/>
       <c r="J389" s="18" t="s">
@@ -26501,23 +26635,23 @@
         <v>98</v>
       </c>
       <c r="B390" s="53" t="s">
-        <v>2116</v>
+        <v>2090</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" s="53" t="s">
-        <v>2160</v>
+        <v>2134</v>
       </c>
       <c r="E390" s="53" t="s">
-        <v>2161</v>
+        <v>2135</v>
       </c>
       <c r="F390" s="53" t="s">
-        <v>2162</v>
+        <v>2136</v>
       </c>
       <c r="G390" s="53" t="s">
-        <v>2163</v>
+        <v>2137</v>
       </c>
       <c r="H390" s="53" t="s">
-        <v>2164</v>
+        <v>2138</v>
       </c>
       <c r="I390" s="2"/>
       <c r="J390" s="18" t="s">
@@ -26535,23 +26669,23 @@
         <v>98</v>
       </c>
       <c r="B391" s="52" t="s">
-        <v>2117</v>
+        <v>2091</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" s="52" t="s">
-        <v>2165</v>
+        <v>2139</v>
       </c>
       <c r="E391" s="52" t="s">
-        <v>2166</v>
+        <v>2140</v>
       </c>
       <c r="F391" s="52" t="s">
-        <v>2167</v>
+        <v>2141</v>
       </c>
       <c r="G391" s="52" t="s">
-        <v>2168</v>
+        <v>2142</v>
       </c>
       <c r="H391" s="52" t="s">
-        <v>2164</v>
+        <v>2138</v>
       </c>
       <c r="I391" s="2"/>
       <c r="J391" s="18" t="s">
@@ -26569,23 +26703,23 @@
         <v>98</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2118</v>
+        <v>2092</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" s="53" t="s">
-        <v>2169</v>
+        <v>2143</v>
       </c>
       <c r="E392" s="53" t="s">
-        <v>2170</v>
+        <v>2144</v>
       </c>
       <c r="F392" s="53" t="s">
-        <v>2171</v>
+        <v>2145</v>
       </c>
       <c r="G392" s="53" t="s">
-        <v>2172</v>
+        <v>2146</v>
       </c>
       <c r="H392" s="53" t="s">
-        <v>2159</v>
+        <v>2133</v>
       </c>
       <c r="I392" s="2"/>
       <c r="J392" s="18" t="s">
@@ -27525,7 +27659,7 @@
         <v>99</v>
       </c>
       <c r="B419" s="54" t="s">
-        <v>2286</v>
+        <v>2260</v>
       </c>
       <c r="C419" s="54"/>
       <c r="D419" s="54"/>
@@ -27547,23 +27681,23 @@
         <v>100</v>
       </c>
       <c r="B420" s="54" t="s">
-        <v>2287</v>
+        <v>2261</v>
       </c>
       <c r="C420" s="54"/>
       <c r="D420" s="54" t="s">
-        <v>2173</v>
+        <v>2147</v>
       </c>
       <c r="E420" s="54" t="s">
-        <v>2174</v>
+        <v>2148</v>
       </c>
       <c r="F420" s="54" t="s">
-        <v>2175</v>
+        <v>2149</v>
       </c>
       <c r="G420" s="54" t="s">
-        <v>2176</v>
+        <v>2150</v>
       </c>
       <c r="H420" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I420" s="2"/>
       <c r="J420" s="18"/>
@@ -27577,23 +27711,23 @@
         <v>100</v>
       </c>
       <c r="B421" s="54" t="s">
-        <v>2288</v>
+        <v>2262</v>
       </c>
       <c r="C421" s="54"/>
       <c r="D421" s="54" t="s">
-        <v>2178</v>
+        <v>2152</v>
       </c>
       <c r="E421" s="54" t="s">
-        <v>2179</v>
+        <v>2153</v>
       </c>
       <c r="F421" s="54" t="s">
-        <v>2180</v>
+        <v>2154</v>
       </c>
       <c r="G421" s="54" t="s">
-        <v>2181</v>
+        <v>2155</v>
       </c>
       <c r="H421" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I421" s="2"/>
       <c r="J421" s="18"/>
@@ -27607,23 +27741,23 @@
         <v>100</v>
       </c>
       <c r="B422" s="54" t="s">
-        <v>2289</v>
+        <v>2263</v>
       </c>
       <c r="C422" s="54"/>
       <c r="D422" s="54" t="s">
-        <v>2182</v>
+        <v>2156</v>
       </c>
       <c r="E422" s="54" t="s">
-        <v>2183</v>
+        <v>2157</v>
       </c>
       <c r="F422" s="54" t="s">
-        <v>2184</v>
+        <v>2158</v>
       </c>
       <c r="G422" s="54" t="s">
-        <v>2185</v>
+        <v>2159</v>
       </c>
       <c r="H422" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I422" s="2"/>
       <c r="J422" s="18"/>
@@ -27637,23 +27771,23 @@
         <v>100</v>
       </c>
       <c r="B423" s="54" t="s">
-        <v>2290</v>
+        <v>2264</v>
       </c>
       <c r="C423" s="54"/>
       <c r="D423" s="54" t="s">
-        <v>2186</v>
+        <v>2160</v>
       </c>
       <c r="E423" s="54" t="s">
-        <v>2187</v>
+        <v>2161</v>
       </c>
       <c r="F423" s="54" t="s">
-        <v>2188</v>
+        <v>2162</v>
       </c>
       <c r="G423" s="54" t="s">
-        <v>2189</v>
+        <v>2163</v>
       </c>
       <c r="H423" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I423" s="2"/>
       <c r="J423" s="18"/>
@@ -27667,7 +27801,7 @@
         <v>99</v>
       </c>
       <c r="B424" s="54" t="s">
-        <v>2291</v>
+        <v>2265</v>
       </c>
       <c r="C424" s="54"/>
       <c r="D424" s="54"/>
@@ -27689,23 +27823,23 @@
         <v>100</v>
       </c>
       <c r="B425" s="54" t="s">
-        <v>2292</v>
+        <v>2266</v>
       </c>
       <c r="C425" s="54"/>
       <c r="D425" s="54" t="s">
-        <v>2190</v>
+        <v>2164</v>
       </c>
       <c r="E425" s="54" t="s">
-        <v>2191</v>
+        <v>2165</v>
       </c>
       <c r="F425" s="54" t="s">
-        <v>2192</v>
+        <v>2166</v>
       </c>
       <c r="G425" s="54" t="s">
-        <v>2193</v>
+        <v>2167</v>
       </c>
       <c r="H425" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I425" s="2"/>
       <c r="J425" s="18"/>
@@ -27719,23 +27853,23 @@
         <v>100</v>
       </c>
       <c r="B426" s="54" t="s">
-        <v>2293</v>
+        <v>2267</v>
       </c>
       <c r="C426" s="54"/>
       <c r="D426" s="54" t="s">
-        <v>2194</v>
+        <v>2168</v>
       </c>
       <c r="E426" s="54" t="s">
-        <v>2195</v>
+        <v>2169</v>
       </c>
       <c r="F426" s="54" t="s">
-        <v>2196</v>
+        <v>2170</v>
       </c>
       <c r="G426" s="54" t="s">
-        <v>2197</v>
+        <v>2171</v>
       </c>
       <c r="H426" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I426" s="2"/>
       <c r="J426" s="18"/>
@@ -27749,23 +27883,23 @@
         <v>100</v>
       </c>
       <c r="B427" s="54" t="s">
-        <v>2294</v>
+        <v>2268</v>
       </c>
       <c r="C427" s="54"/>
       <c r="D427" s="54" t="s">
-        <v>2198</v>
+        <v>2172</v>
       </c>
       <c r="E427" s="54" t="s">
-        <v>2199</v>
+        <v>2173</v>
       </c>
       <c r="F427" s="54" t="s">
-        <v>2200</v>
+        <v>2174</v>
       </c>
       <c r="G427" s="54" t="s">
-        <v>2201</v>
+        <v>2175</v>
       </c>
       <c r="H427" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I427" s="2"/>
       <c r="J427" s="18"/>
@@ -27779,23 +27913,23 @@
         <v>100</v>
       </c>
       <c r="B428" s="54" t="s">
-        <v>2295</v>
+        <v>2269</v>
       </c>
       <c r="C428" s="54"/>
       <c r="D428" s="54" t="s">
-        <v>2202</v>
+        <v>2176</v>
       </c>
       <c r="E428" s="54" t="s">
-        <v>2203</v>
+        <v>2177</v>
       </c>
       <c r="F428" s="54" t="s">
-        <v>2204</v>
+        <v>2178</v>
       </c>
       <c r="G428" s="54" t="s">
-        <v>2205</v>
+        <v>2179</v>
       </c>
       <c r="H428" s="55" t="s">
-        <v>2177</v>
+        <v>2151</v>
       </c>
       <c r="I428" s="2"/>
       <c r="J428" s="18"/>
@@ -27809,7 +27943,7 @@
         <v>99</v>
       </c>
       <c r="B429" s="54" t="s">
-        <v>2296</v>
+        <v>2270</v>
       </c>
       <c r="C429" s="54"/>
       <c r="D429" s="54"/>
@@ -27831,23 +27965,23 @@
         <v>100</v>
       </c>
       <c r="B430" s="54" t="s">
-        <v>2297</v>
+        <v>2271</v>
       </c>
       <c r="C430" s="54"/>
       <c r="D430" s="54" t="s">
-        <v>2206</v>
+        <v>2180</v>
       </c>
       <c r="E430" s="54" t="s">
-        <v>2207</v>
+        <v>2181</v>
       </c>
       <c r="F430" s="54" t="s">
-        <v>2208</v>
+        <v>2182</v>
       </c>
       <c r="G430" s="54" t="s">
-        <v>2209</v>
+        <v>2183</v>
       </c>
       <c r="H430" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I430" s="2"/>
       <c r="J430" s="18"/>
@@ -27861,11 +27995,11 @@
         <v>100</v>
       </c>
       <c r="B431" s="54" t="s">
-        <v>2298</v>
+        <v>2272</v>
       </c>
       <c r="C431" s="54"/>
       <c r="D431" s="56" t="s">
-        <v>2211</v>
+        <v>2185</v>
       </c>
       <c r="E431" s="56">
         <v>37</v>
@@ -27877,7 +28011,7 @@
         <v>13516</v>
       </c>
       <c r="H431" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I431" s="2"/>
       <c r="J431" s="18"/>
@@ -27891,23 +28025,23 @@
         <v>100</v>
       </c>
       <c r="B432" s="54" t="s">
-        <v>2299</v>
+        <v>2273</v>
       </c>
       <c r="C432" s="54"/>
       <c r="D432" s="54" t="s">
-        <v>2212</v>
+        <v>2186</v>
       </c>
       <c r="E432" s="54" t="s">
-        <v>2213</v>
+        <v>2187</v>
       </c>
       <c r="F432" s="54" t="s">
-        <v>2214</v>
+        <v>2188</v>
       </c>
       <c r="G432" s="54" t="s">
-        <v>2215</v>
+        <v>2189</v>
       </c>
       <c r="H432" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I432" s="2"/>
       <c r="J432" s="18"/>
@@ -27921,7 +28055,7 @@
         <v>100</v>
       </c>
       <c r="B433" s="54" t="s">
-        <v>2300</v>
+        <v>2274</v>
       </c>
       <c r="C433" s="54"/>
       <c r="D433" s="56">
@@ -27934,10 +28068,10 @@
         <v>43</v>
       </c>
       <c r="G433" s="56" t="s">
-        <v>2216</v>
+        <v>2190</v>
       </c>
       <c r="H433" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I433" s="2"/>
       <c r="J433" s="18"/>
@@ -27951,7 +28085,7 @@
         <v>99</v>
       </c>
       <c r="B434" s="54" t="s">
-        <v>2301</v>
+        <v>2275</v>
       </c>
       <c r="C434" s="54"/>
       <c r="D434" s="54"/>
@@ -27973,23 +28107,23 @@
         <v>100</v>
       </c>
       <c r="B435" s="54" t="s">
-        <v>2302</v>
+        <v>2276</v>
       </c>
       <c r="C435" s="54"/>
       <c r="D435" s="54" t="s">
-        <v>2217</v>
+        <v>2191</v>
       </c>
       <c r="E435" s="54" t="s">
-        <v>2218</v>
+        <v>2192</v>
       </c>
       <c r="F435" s="54" t="s">
-        <v>2219</v>
+        <v>2193</v>
       </c>
       <c r="G435" s="54" t="s">
-        <v>2220</v>
+        <v>2194</v>
       </c>
       <c r="H435" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I435" s="2"/>
       <c r="J435" s="18"/>
@@ -28003,23 +28137,23 @@
         <v>100</v>
       </c>
       <c r="B436" s="54" t="s">
-        <v>2303</v>
+        <v>2277</v>
       </c>
       <c r="C436" s="54"/>
       <c r="D436" s="56" t="s">
-        <v>2036</v>
+        <v>2010</v>
       </c>
       <c r="E436" s="56">
         <v>1</v>
       </c>
       <c r="F436" s="56" t="s">
-        <v>2221</v>
+        <v>2195</v>
       </c>
       <c r="G436" s="56" t="s">
-        <v>2222</v>
+        <v>2196</v>
       </c>
       <c r="H436" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I436" s="2"/>
       <c r="J436" s="18"/>
@@ -28033,23 +28167,23 @@
         <v>98</v>
       </c>
       <c r="B437" s="54" t="s">
-        <v>2304</v>
+        <v>2278</v>
       </c>
       <c r="C437" s="54"/>
       <c r="D437" s="54" t="s">
-        <v>2223</v>
+        <v>2197</v>
       </c>
       <c r="E437" s="54" t="s">
-        <v>2224</v>
+        <v>2198</v>
       </c>
       <c r="F437" s="54" t="s">
-        <v>2225</v>
+        <v>2199</v>
       </c>
       <c r="G437" s="54" t="s">
-        <v>2226</v>
+        <v>2200</v>
       </c>
       <c r="H437" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I437" s="2"/>
       <c r="J437" s="18" t="s">
@@ -28067,23 +28201,23 @@
         <v>98</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2305</v>
+        <v>2279</v>
       </c>
       <c r="C438" s="54"/>
       <c r="D438" s="54" t="s">
-        <v>2228</v>
+        <v>2202</v>
       </c>
       <c r="E438" s="54" t="s">
-        <v>2229</v>
+        <v>2203</v>
       </c>
       <c r="F438" s="54" t="s">
-        <v>2230</v>
+        <v>2204</v>
       </c>
       <c r="G438" s="54" t="s">
-        <v>2231</v>
+        <v>2205</v>
       </c>
       <c r="H438" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I438" s="2"/>
       <c r="J438" s="18" t="s">
@@ -28101,23 +28235,23 @@
         <v>98</v>
       </c>
       <c r="B439" s="54" t="s">
-        <v>2306</v>
+        <v>2280</v>
       </c>
       <c r="C439" s="54"/>
       <c r="D439" s="54" t="s">
-        <v>2232</v>
+        <v>2206</v>
       </c>
       <c r="E439" s="54" t="s">
-        <v>2233</v>
+        <v>2207</v>
       </c>
       <c r="F439" s="54" t="s">
-        <v>2234</v>
+        <v>2208</v>
       </c>
       <c r="G439" s="54" t="s">
-        <v>2235</v>
+        <v>2209</v>
       </c>
       <c r="H439" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I439" s="2"/>
       <c r="J439" s="18" t="s">
@@ -28135,23 +28269,23 @@
         <v>98</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2307</v>
+        <v>2281</v>
       </c>
       <c r="C440" s="54"/>
       <c r="D440" s="54" t="s">
-        <v>2236</v>
+        <v>2210</v>
       </c>
       <c r="E440" s="54" t="s">
-        <v>2237</v>
+        <v>2211</v>
       </c>
       <c r="F440" s="54" t="s">
-        <v>2238</v>
+        <v>2212</v>
       </c>
       <c r="G440" s="54" t="s">
-        <v>2239</v>
+        <v>2213</v>
       </c>
       <c r="H440" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I440" s="2"/>
       <c r="J440" s="18" t="s">
@@ -28169,23 +28303,23 @@
         <v>98</v>
       </c>
       <c r="B441" s="54" t="s">
-        <v>2308</v>
+        <v>2282</v>
       </c>
       <c r="C441" s="54"/>
       <c r="D441" s="54" t="s">
-        <v>2240</v>
+        <v>2214</v>
       </c>
       <c r="E441" s="54" t="s">
-        <v>2241</v>
+        <v>2215</v>
       </c>
       <c r="F441" s="54" t="s">
-        <v>2242</v>
+        <v>2216</v>
       </c>
       <c r="G441" s="54" t="s">
-        <v>2243</v>
+        <v>2217</v>
       </c>
       <c r="H441" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I441" s="2"/>
       <c r="J441" s="18" t="s">
@@ -28203,23 +28337,23 @@
         <v>98</v>
       </c>
       <c r="B442" s="54" t="s">
-        <v>2309</v>
+        <v>2283</v>
       </c>
       <c r="C442" s="54"/>
       <c r="D442" s="54" t="s">
-        <v>2244</v>
+        <v>2218</v>
       </c>
       <c r="E442" s="54" t="s">
-        <v>2245</v>
+        <v>2219</v>
       </c>
       <c r="F442" s="54" t="s">
-        <v>2246</v>
+        <v>2220</v>
       </c>
       <c r="G442" s="54" t="s">
-        <v>2247</v>
+        <v>2221</v>
       </c>
       <c r="H442" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I442" s="2"/>
       <c r="J442" s="18" t="s">
@@ -28237,23 +28371,23 @@
         <v>98</v>
       </c>
       <c r="B443" s="54" t="s">
-        <v>2310</v>
+        <v>2284</v>
       </c>
       <c r="C443" s="54"/>
       <c r="D443" s="54" t="s">
-        <v>2248</v>
+        <v>2222</v>
       </c>
       <c r="E443" s="54" t="s">
-        <v>2249</v>
+        <v>2223</v>
       </c>
       <c r="F443" s="54" t="s">
-        <v>2250</v>
+        <v>2224</v>
       </c>
       <c r="G443" s="54" t="s">
-        <v>2251</v>
+        <v>2225</v>
       </c>
       <c r="H443" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I443" s="2"/>
       <c r="J443" s="18" t="s">
@@ -28271,23 +28405,23 @@
         <v>98</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2311</v>
+        <v>2285</v>
       </c>
       <c r="C444" s="54"/>
       <c r="D444" s="54" t="s">
-        <v>2252</v>
+        <v>2226</v>
       </c>
       <c r="E444" s="54" t="s">
-        <v>2253</v>
+        <v>2227</v>
       </c>
       <c r="F444" s="54" t="s">
-        <v>2254</v>
+        <v>2228</v>
       </c>
       <c r="G444" s="54" t="s">
-        <v>2255</v>
+        <v>2229</v>
       </c>
       <c r="H444" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I444" s="2"/>
       <c r="J444" s="18" t="s">
@@ -28305,7 +28439,7 @@
         <v>99</v>
       </c>
       <c r="B445" s="54" t="s">
-        <v>2256</v>
+        <v>2230</v>
       </c>
       <c r="C445" s="54"/>
       <c r="D445" s="54"/>
@@ -28327,23 +28461,23 @@
         <v>100</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2312</v>
+        <v>2286</v>
       </c>
       <c r="C446" s="54"/>
       <c r="D446" s="54" t="s">
-        <v>2257</v>
+        <v>2231</v>
       </c>
       <c r="E446" s="54" t="s">
-        <v>2258</v>
+        <v>2232</v>
       </c>
       <c r="F446" s="54" t="s">
-        <v>2259</v>
+        <v>2233</v>
       </c>
       <c r="G446" s="54" t="s">
-        <v>2260</v>
+        <v>2234</v>
       </c>
       <c r="H446" s="55" t="s">
-        <v>2261</v>
+        <v>2235</v>
       </c>
       <c r="I446" s="2"/>
       <c r="J446" s="18"/>
@@ -28357,23 +28491,23 @@
         <v>100</v>
       </c>
       <c r="B447" s="54" t="s">
-        <v>2313</v>
+        <v>2287</v>
       </c>
       <c r="C447" s="54"/>
       <c r="D447" s="54" t="s">
-        <v>2262</v>
+        <v>2236</v>
       </c>
       <c r="E447" s="54" t="s">
-        <v>2263</v>
+        <v>2237</v>
       </c>
       <c r="F447" s="54" t="s">
-        <v>2264</v>
+        <v>2238</v>
       </c>
       <c r="G447" s="54" t="s">
-        <v>2265</v>
+        <v>2239</v>
       </c>
       <c r="H447" s="54" t="s">
-        <v>2266</v>
+        <v>2240</v>
       </c>
       <c r="I447" s="2"/>
       <c r="J447" s="18"/>
@@ -28387,23 +28521,23 @@
         <v>100</v>
       </c>
       <c r="B448" s="54" t="s">
-        <v>2314</v>
+        <v>2288</v>
       </c>
       <c r="C448" s="54"/>
       <c r="D448" s="54" t="s">
-        <v>2267</v>
+        <v>2241</v>
       </c>
       <c r="E448" s="54" t="s">
-        <v>2268</v>
+        <v>2242</v>
       </c>
       <c r="F448" s="54" t="s">
-        <v>2269</v>
+        <v>2243</v>
       </c>
       <c r="G448" s="54" t="s">
-        <v>2270</v>
+        <v>2244</v>
       </c>
       <c r="H448" s="55" t="s">
-        <v>2227</v>
+        <v>2201</v>
       </c>
       <c r="I448" s="2"/>
       <c r="J448" s="18"/>
@@ -28417,7 +28551,7 @@
         <v>99</v>
       </c>
       <c r="B449" s="54" t="s">
-        <v>2271</v>
+        <v>2245</v>
       </c>
       <c r="C449" s="54"/>
       <c r="D449" s="54"/>
@@ -28439,23 +28573,23 @@
         <v>100</v>
       </c>
       <c r="B450" s="54" t="s">
-        <v>2315</v>
+        <v>2289</v>
       </c>
       <c r="C450" s="54"/>
       <c r="D450" s="54" t="s">
-        <v>2272</v>
+        <v>2246</v>
       </c>
       <c r="E450" s="54" t="s">
-        <v>2273</v>
+        <v>2247</v>
       </c>
       <c r="F450" s="54" t="s">
-        <v>2274</v>
+        <v>2248</v>
       </c>
       <c r="G450" s="54" t="s">
-        <v>2275</v>
+        <v>2249</v>
       </c>
       <c r="H450" s="55" t="s">
-        <v>2276</v>
+        <v>2250</v>
       </c>
       <c r="I450" s="2"/>
       <c r="J450" s="18"/>
@@ -28469,23 +28603,23 @@
         <v>100</v>
       </c>
       <c r="B451" s="54" t="s">
-        <v>2316</v>
+        <v>2290</v>
       </c>
       <c r="C451" s="54"/>
       <c r="D451" s="54" t="s">
-        <v>2277</v>
+        <v>2251</v>
       </c>
       <c r="E451" s="54" t="s">
-        <v>2278</v>
+        <v>2252</v>
       </c>
       <c r="F451" s="54" t="s">
-        <v>2279</v>
+        <v>2253</v>
       </c>
       <c r="G451" s="54" t="s">
-        <v>2280</v>
+        <v>2254</v>
       </c>
       <c r="H451" s="55" t="s">
-        <v>2210</v>
+        <v>2184</v>
       </c>
       <c r="I451" s="2"/>
       <c r="J451" s="18"/>
@@ -28499,23 +28633,23 @@
         <v>100</v>
       </c>
       <c r="B452" s="54" t="s">
-        <v>2317</v>
+        <v>2291</v>
       </c>
       <c r="C452" s="54"/>
       <c r="D452" s="54" t="s">
-        <v>2281</v>
+        <v>2255</v>
       </c>
       <c r="E452" s="54" t="s">
-        <v>2282</v>
+        <v>2256</v>
       </c>
       <c r="F452" s="54" t="s">
-        <v>2283</v>
+        <v>2257</v>
       </c>
       <c r="G452" s="54" t="s">
-        <v>2284</v>
+        <v>2258</v>
       </c>
       <c r="H452" s="54" t="s">
-        <v>2285</v>
+        <v>2259</v>
       </c>
       <c r="I452" s="2"/>
       <c r="J452" s="18"/>
@@ -29065,30 +29199,30 @@
         <v>98</v>
       </c>
       <c r="B468" s="44" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="C468" s="2"/>
       <c r="D468" s="44" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="E468" s="44" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="F468" s="44" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="G468" s="44" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="H468" s="44" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
       <c r="I468" s="2"/>
       <c r="J468" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K468" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L468" s="18">
         <v>1</v>
@@ -29099,30 +29233,30 @@
         <v>98</v>
       </c>
       <c r="B469" s="45" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="C469" s="2"/>
       <c r="D469" s="45" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="E469" s="45" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="F469" s="45" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="G469" s="45" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
       <c r="H469" s="45" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="I469" s="2"/>
       <c r="J469" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K469" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L469" s="18">
         <v>1</v>
@@ -29133,30 +29267,30 @@
         <v>98</v>
       </c>
       <c r="B470" s="44" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="C470" s="2"/>
       <c r="D470" s="44" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="E470" s="44" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F470" s="44" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="G470" s="44" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
       <c r="H470" s="44" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="I470" s="2"/>
       <c r="J470" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K470" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L470" s="18">
         <v>1</v>
@@ -29167,30 +29301,30 @@
         <v>98</v>
       </c>
       <c r="B471" s="45" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="C471" s="2"/>
       <c r="D471" s="45" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="E471" s="45" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F471" s="45" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="G471" s="45" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
       <c r="H471" s="45" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="I471" s="2"/>
       <c r="J471" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K471" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L471" s="18">
         <v>1</v>
@@ -29201,30 +29335,30 @@
         <v>98</v>
       </c>
       <c r="B472" s="44" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="C472" s="2"/>
       <c r="D472" s="44" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="E472" s="44" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
       <c r="F472" s="44" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
       <c r="G472" s="44" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="H472" s="44" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="I472" s="2"/>
       <c r="J472" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K472" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L472" s="18">
         <v>1</v>
@@ -29235,30 +29369,30 @@
         <v>98</v>
       </c>
       <c r="B473" s="45" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="C473" s="2"/>
       <c r="D473" s="45" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="E473" s="45" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="F473" s="45" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="G473" s="45" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="H473" s="45" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="I473" s="2"/>
       <c r="J473" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K473" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L473" s="18">
         <v>1</v>
@@ -29269,30 +29403,30 @@
         <v>98</v>
       </c>
       <c r="B474" s="44" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="C474" s="2"/>
       <c r="D474" s="44" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="E474" s="44" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="F474" s="44" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="G474" s="44" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="H474" s="44" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="I474" s="2"/>
       <c r="J474" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K474" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L474" s="18">
         <v>1</v>
@@ -29303,30 +29437,30 @@
         <v>98</v>
       </c>
       <c r="B475" s="45" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="C475" s="2"/>
       <c r="D475" s="45" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="E475" s="45" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="F475" s="45" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
       <c r="G475" s="45" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="H475" s="45" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="I475" s="2"/>
       <c r="J475" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K475" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L475" s="18">
         <v>1</v>
@@ -29337,30 +29471,30 @@
         <v>98</v>
       </c>
       <c r="B476" s="44" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="C476" s="2"/>
       <c r="D476" s="44" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="E476" s="44" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="F476" s="44" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="G476" s="44" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="H476" s="44" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="I476" s="2"/>
       <c r="J476" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K476" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L476" s="18">
         <v>1</v>
@@ -29371,30 +29505,30 @@
         <v>98</v>
       </c>
       <c r="B477" s="45" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="C477" s="2"/>
       <c r="D477" s="45" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="E477" s="45" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="F477" s="45" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="G477" s="45" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="H477" s="45" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="I477" s="2"/>
       <c r="J477" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K477" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L477" s="18">
         <v>1</v>
@@ -29405,7 +29539,7 @@
         <v>99</v>
       </c>
       <c r="B478" s="44" t="s">
-        <v>2043</v>
+        <v>2017</v>
       </c>
       <c r="C478" s="2"/>
       <c r="D478" s="2"/>
@@ -29418,7 +29552,7 @@
         <v>11</v>
       </c>
       <c r="K478" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L478" s="18"/>
     </row>
@@ -29427,23 +29561,23 @@
         <v>100</v>
       </c>
       <c r="B479" s="44" t="s">
-        <v>2044</v>
+        <v>2018</v>
       </c>
       <c r="C479" s="2"/>
       <c r="D479" s="44" t="s">
-        <v>2045</v>
+        <v>2019</v>
       </c>
       <c r="E479" s="44" t="s">
-        <v>2046</v>
+        <v>2020</v>
       </c>
       <c r="F479" s="44" t="s">
-        <v>2047</v>
+        <v>2021</v>
       </c>
       <c r="G479" s="44" t="s">
-        <v>2048</v>
+        <v>2022</v>
       </c>
       <c r="H479" s="44" t="s">
-        <v>2049</v>
+        <v>2023</v>
       </c>
       <c r="I479" s="2"/>
       <c r="J479" s="18"/>
@@ -29457,7 +29591,7 @@
         <v>99</v>
       </c>
       <c r="B480" s="45" t="s">
-        <v>2052</v>
+        <v>2026</v>
       </c>
       <c r="C480" s="2"/>
       <c r="D480" s="2"/>
@@ -29470,7 +29604,7 @@
         <v>11</v>
       </c>
       <c r="K480" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L480" s="18"/>
     </row>
@@ -29479,23 +29613,23 @@
         <v>100</v>
       </c>
       <c r="B481" s="45" t="s">
-        <v>2050</v>
+        <v>2024</v>
       </c>
       <c r="C481" s="2"/>
       <c r="D481" s="45" t="s">
-        <v>2051</v>
+        <v>2025</v>
       </c>
       <c r="E481" s="45" t="s">
-        <v>2053</v>
+        <v>2027</v>
       </c>
       <c r="F481" s="45" t="s">
-        <v>2054</v>
+        <v>2028</v>
       </c>
       <c r="G481" s="45" t="s">
-        <v>2055</v>
+        <v>2029</v>
       </c>
       <c r="H481" s="45" t="s">
-        <v>2056</v>
+        <v>2030</v>
       </c>
       <c r="I481" s="2"/>
       <c r="J481" s="18"/>
@@ -29509,30 +29643,30 @@
         <v>98</v>
       </c>
       <c r="B482" s="44" t="s">
-        <v>2057</v>
+        <v>2031</v>
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="44" t="s">
-        <v>2058</v>
+        <v>2032</v>
       </c>
       <c r="E482" s="44" t="s">
-        <v>2059</v>
+        <v>2033</v>
       </c>
       <c r="F482" s="44" t="s">
-        <v>2060</v>
+        <v>2034</v>
       </c>
       <c r="G482" s="44" t="s">
-        <v>2061</v>
+        <v>2035</v>
       </c>
       <c r="H482" s="44" t="s">
-        <v>2062</v>
+        <v>2036</v>
       </c>
       <c r="I482" s="2"/>
       <c r="J482" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K482" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L482" s="18">
         <v>1</v>
@@ -29543,7 +29677,7 @@
         <v>99</v>
       </c>
       <c r="B483" s="45" t="s">
-        <v>2063</v>
+        <v>2037</v>
       </c>
       <c r="C483" s="2"/>
       <c r="D483" s="2"/>
@@ -29556,7 +29690,7 @@
         <v>11</v>
       </c>
       <c r="K483" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L483" s="18"/>
     </row>
@@ -29565,23 +29699,23 @@
         <v>100</v>
       </c>
       <c r="B484" s="45" t="s">
-        <v>2064</v>
+        <v>2038</v>
       </c>
       <c r="C484" s="2"/>
       <c r="D484" s="45" t="s">
-        <v>2080</v>
+        <v>2054</v>
       </c>
       <c r="E484" s="45" t="s">
-        <v>2076</v>
+        <v>2050</v>
       </c>
       <c r="F484" s="45" t="s">
-        <v>2077</v>
+        <v>2051</v>
       </c>
       <c r="G484" s="45" t="s">
-        <v>2078</v>
+        <v>2052</v>
       </c>
       <c r="H484" s="45" t="s">
-        <v>2079</v>
+        <v>2053</v>
       </c>
       <c r="I484" s="2"/>
       <c r="J484" s="18"/>
@@ -29595,30 +29729,30 @@
         <v>98</v>
       </c>
       <c r="B485" s="44" t="s">
-        <v>2065</v>
+        <v>2039</v>
       </c>
       <c r="C485" s="2"/>
       <c r="D485" s="44" t="s">
-        <v>2081</v>
+        <v>2055</v>
       </c>
       <c r="E485" s="44" t="s">
-        <v>2082</v>
+        <v>2056</v>
       </c>
       <c r="F485" s="44" t="s">
-        <v>2083</v>
+        <v>2057</v>
       </c>
       <c r="G485" s="44" t="s">
-        <v>2084</v>
+        <v>2058</v>
       </c>
       <c r="H485" s="44" t="s">
-        <v>2085</v>
+        <v>2059</v>
       </c>
       <c r="I485" s="2"/>
       <c r="J485" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K485" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L485" s="18">
         <v>1</v>
@@ -29629,20 +29763,20 @@
         <v>98</v>
       </c>
       <c r="B486" s="45" t="s">
-        <v>2066</v>
+        <v>2040</v>
       </c>
       <c r="C486" s="2"/>
       <c r="D486" s="45" t="s">
-        <v>2086</v>
+        <v>2060</v>
       </c>
       <c r="E486" s="45" t="s">
-        <v>2087</v>
+        <v>2061</v>
       </c>
       <c r="F486" s="45" t="s">
-        <v>2088</v>
+        <v>2062</v>
       </c>
       <c r="G486" s="45" t="s">
-        <v>2089</v>
+        <v>2063</v>
       </c>
       <c r="H486" s="45" t="s">
         <v>1129</v>
@@ -29652,7 +29786,7 @@
         <v>11</v>
       </c>
       <c r="K486" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L486" s="18">
         <v>1</v>
@@ -29663,7 +29797,7 @@
         <v>99</v>
       </c>
       <c r="B487" s="44" t="s">
-        <v>2067</v>
+        <v>2041</v>
       </c>
       <c r="C487" s="2"/>
       <c r="D487" s="2"/>
@@ -29676,7 +29810,7 @@
         <v>11</v>
       </c>
       <c r="K487" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L487" s="18"/>
     </row>
@@ -29685,23 +29819,23 @@
         <v>100</v>
       </c>
       <c r="B488" s="44" t="s">
-        <v>2068</v>
+        <v>2042</v>
       </c>
       <c r="C488" s="2"/>
       <c r="D488" s="44" t="s">
-        <v>2090</v>
+        <v>2064</v>
       </c>
       <c r="E488" s="44" t="s">
-        <v>2091</v>
+        <v>2065</v>
       </c>
       <c r="F488" s="44" t="s">
-        <v>2092</v>
+        <v>2066</v>
       </c>
       <c r="G488" s="44" t="s">
-        <v>2093</v>
+        <v>2067</v>
       </c>
       <c r="H488" s="44" t="s">
-        <v>2094</v>
+        <v>2068</v>
       </c>
       <c r="I488" s="2"/>
       <c r="J488" s="18"/>
@@ -29715,30 +29849,30 @@
         <v>98</v>
       </c>
       <c r="B489" s="45" t="s">
-        <v>2069</v>
+        <v>2043</v>
       </c>
       <c r="C489" s="2"/>
       <c r="D489" s="45" t="s">
-        <v>2095</v>
+        <v>2069</v>
       </c>
       <c r="E489" s="45" t="s">
-        <v>2096</v>
+        <v>2070</v>
       </c>
       <c r="F489" s="45" t="s">
-        <v>2097</v>
+        <v>2071</v>
       </c>
       <c r="G489" s="45" t="s">
-        <v>2098</v>
+        <v>2072</v>
       </c>
       <c r="H489" s="45" t="s">
-        <v>2099</v>
+        <v>2073</v>
       </c>
       <c r="I489" s="2"/>
       <c r="J489" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K489" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L489" s="18">
         <v>1</v>
@@ -29749,7 +29883,7 @@
         <v>99</v>
       </c>
       <c r="B490" s="44" t="s">
-        <v>2070</v>
+        <v>2044</v>
       </c>
       <c r="C490" s="2"/>
       <c r="D490" s="2"/>
@@ -29762,7 +29896,7 @@
         <v>11</v>
       </c>
       <c r="K490" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L490" s="18"/>
     </row>
@@ -29771,23 +29905,23 @@
         <v>100</v>
       </c>
       <c r="B491" s="44" t="s">
-        <v>2071</v>
+        <v>2045</v>
       </c>
       <c r="C491" s="2"/>
       <c r="D491" s="44" t="s">
-        <v>2100</v>
+        <v>2074</v>
       </c>
       <c r="E491" s="44" t="s">
-        <v>2101</v>
+        <v>2075</v>
       </c>
       <c r="F491" s="44" t="s">
-        <v>2102</v>
+        <v>2076</v>
       </c>
       <c r="G491" s="44" t="s">
-        <v>2103</v>
+        <v>2077</v>
       </c>
       <c r="H491" s="44" t="s">
-        <v>2104</v>
+        <v>2078</v>
       </c>
       <c r="I491" s="2"/>
       <c r="J491" s="18"/>
@@ -29801,7 +29935,7 @@
         <v>99</v>
       </c>
       <c r="B492" s="45" t="s">
-        <v>2072</v>
+        <v>2046</v>
       </c>
       <c r="C492" s="2"/>
       <c r="D492" s="2"/>
@@ -29814,7 +29948,7 @@
         <v>11</v>
       </c>
       <c r="K492" s="18" t="s">
-        <v>2403</v>
+        <v>2377</v>
       </c>
       <c r="L492" s="18"/>
     </row>
@@ -29823,23 +29957,23 @@
         <v>100</v>
       </c>
       <c r="B493" s="45" t="s">
-        <v>2073</v>
+        <v>2047</v>
       </c>
       <c r="C493" s="2"/>
       <c r="D493" s="45" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="E493" s="45" t="s">
-        <v>2074</v>
+        <v>2048</v>
       </c>
       <c r="F493" s="45" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="G493" s="45" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="H493" s="45" t="s">
-        <v>2075</v>
+        <v>2049</v>
       </c>
       <c r="I493" s="2"/>
       <c r="J493" s="18"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F93223-849B-4530-A519-3433D87E6271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346D59CD-E175-4AE1-9B54-35E93DB379C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3884" uniqueCount="2444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3877" uniqueCount="2438">
   <si>
     <t>Option 1</t>
   </si>
@@ -8453,24 +8453,6 @@
     <t>(E) : $\mathbf{8 8}$ protons $\mathbf{1 3 8}$ neutrons</t>
   </si>
   <si>
-    <t>M21F1 ; M21F2</t>
-  </si>
-  <si>
-    <t>(A) : $\lambda=0,40 \mathrm{~m}$ &amp; $v=0,25 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
-  </si>
-  <si>
-    <t>(B) : $\lambda=0,08 \mathrm{~m}$ &amp; $v=0,8 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
-  </si>
-  <si>
-    <t>(C) : $\lambda=0,40 \mathrm{~m}$ &amp; $v=2,5 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
-  </si>
-  <si>
-    <t>(D) : $\lambda=0,40 \mathrm{~m}$ &amp; $v=5,0 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
-  </si>
-  <si>
-    <t>(E) : $\lambda=0,80 \mathrm{~m}$ &amp; $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
-  </si>
-  <si>
     <t>(A) : $d=0,20 \mathrm{~m}$</t>
   </si>
   <si>
@@ -8501,9 +8483,6 @@
     <t>(E) : $y_{M}(t)=y_{S}(t-0,4)$</t>
   </si>
   <si>
-    <t>M21F3; M21F4</t>
-  </si>
-  <si>
     <t>(A) : $\Delta t=d \cdot\left(\frac{1}{V_{a}}-\frac{1}{V_{e}}\right)$</t>
   </si>
   <si>
@@ -8624,12 +8603,6 @@
     <t>(E) : $\boldsymbol{x} \quad 2,8.10^{9} s$</t>
   </si>
   <si>
-    <t>M21F5</t>
-  </si>
-  <si>
-    <t>M21F6</t>
-  </si>
-  <si>
     <t>(A) : $N=\frac{2 \cdot a_{0} \cdot t_{1 / 2}}{\ln 2}$</t>
   </si>
   <si>
@@ -8660,15 +8633,6 @@
     <t>(E) : $a=2,1 B q$</t>
   </si>
   <si>
-    <t>M21F7; M21F8</t>
-  </si>
-  <si>
-    <t>Lorsque le condensateur devient chargé, on place $K$ en position (2), à un instant pris comme nouvelle origine des dates ( $t_{0}=0$ ). La courbe de la figure (3) représente l'évolution de $u_{C}(t)$. La tension aux bornes du condensateur s'écrit : $\boldsymbol{u}_{C}(\boldsymbol{t})=\boldsymbol{A} \cdot \boldsymbol{e}^{-\frac{\boldsymbol{t}}{R C}}$ avec $A$ constante.\\ Q35. Les valeurs de $A$ et $R$ sont :</t>
-  </si>
-  <si>
-    <t>(A) : $\C=5 \mu \mathrm{~F}$</t>
-  </si>
-  <si>
     <t>(B) : $C=20 \mu \mathrm{~F}$</t>
   </si>
   <si>
@@ -8681,21 +8645,6 @@
     <t>(E) : $C=500 \mu \mathrm{~F}$</t>
   </si>
   <si>
-    <t>(A) : $A=6 \mathrm{~V}$ \\ $R=50 \Omega$</t>
-  </si>
-  <si>
-    <t>(B) : $A=10 \mathrm{~V}$ \\ $R=100 \Omega$</t>
-  </si>
-  <si>
-    <t>(C) : $A=10 \mathrm{~V}$ \\ $R=200 \Omega$</t>
-  </si>
-  <si>
-    <t>(D) : $A=5 \mathrm{~V}$ \\ $R=0,5 \Omega$</t>
-  </si>
-  <si>
-    <t>(E) : $A=10 \mathrm{~V}$ \\ $R=1 \Omega$</t>
-  </si>
-  <si>
     <t>(A) : $i_{0}=320 \mathrm{~mA}$</t>
   </si>
   <si>
@@ -8726,27 +8675,9 @@
     <t>(E) : $\mathscr{E}_{e}=9,0 \mathrm{~mJ}$</t>
   </si>
   <si>
-    <t>(A) : $\tau_{1}=0,3 \mathrm{~s}$ \\ $\tau_{2}=1,2 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(B) : $\tau_{1}=0,3 \mathrm{~s}$ \\ $\tau_{2}=0,6 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(C) : $\tau_{1}=0,3 \mathrm{~s}$ \\ $\tau_{2}=1,5 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(D) : $\tau_{1}=0,6 \mathrm{~s}$ \\ $\tau_{2}=1,5 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(E) : $\tau_{1}=0,9 \mathrm{~s}$ \\ $\tau_{2}=1,5 \mathrm{~s}$</t>
-  </si>
-  <si>
     <t>(A) : $C_{2}=5 . C_{1}$</t>
   </si>
   <si>
-    <t>(B) : $\C_{2}=0,2 . C_{1}$</t>
-  </si>
-  <si>
     <t>(C) : $C_{2}=0,5 . C_{1}$</t>
   </si>
   <si>
@@ -8754,24 +8685,6 @@
   </si>
   <si>
     <t>(E) : $C_{2}=2,3 . C_{1}$</t>
-  </si>
-  <si>
-    <t>(A) : $u_{C_{2}}=37 \% . E$</t>
-  </si>
-  <si>
-    <t>(B) : $\chi^{u_{C_{2}}}=63 \% . E$</t>
-  </si>
-  <si>
-    <t>(C) : $u_{C_{2}}=67 \% . E$</t>
-  </si>
-  <si>
-    <t>(D) : $u_{C_{2}}=33 \% . E$</t>
-  </si>
-  <si>
-    <t>(E) : $u_{C_{2}}=57 \% E$</t>
-  </si>
-  <si>
-    <t>M21F9</t>
   </si>
   <si>
     <t>M21F10 ; M21F11</t>
@@ -9607,10 +9520,6 @@
     <t>Dans le muscle strié squelettique, la troponine :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Propagation d'une onde le long d'une corde (5 points)&lt;/b&gt;&lt;/center&gt;
-Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $v$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 s$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.</t>
-  </si>
-  <si>
     <t>La composition du noyau fils ${ }_{x}^{y} R n$ est:</t>
   </si>
   <si>
@@ -9651,24 +9560,13 @@
  Lors d'une scintigraphie thyroïdienne, on injecte à $t_{0}=0$, à un patient un échantillon d'iode 123 d'activité 7 MBq . L'iode 123 se répartie à $30 \%$ dans la thyroïde et $70 \%$ dans le reste de l'organisme. On néglige le temps de fixation des noyaux dans la thyroïde. Soit $a_{0}$ l'activité dans la thyroïde à $t_{0}=0$. Données : $\ln 2=0,69 \quad ; \quad e^{-13,8}=2^{-20}=10^{-6}$</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;La radioactivité du plutonium : (8 points)&lt;/b&gt;&lt;/center&gt;
- Le plutonium ${ }_{94}^{238} \mathrm{Pu}$ est radioactif $\alpha$. Un échantillon de plutonium contient à $t_{0}=0, N_{0}$ noyaux de plutonium ${ }_{94}^{238} \mathrm{Pu}$. On note $N_{d}$ le nombre de noyaux de ${ }_{94}^{238} \mathrm{Pu}$ désintégrés à l'instant $t$. La courbe cicontre représente les variations de $\left(\frac{d N_{d}}{d t}\right)$ en fonction de $N_{d}$. Donnée: $\ln 2 \approx 0,7$</t>
-  </si>
-  <si>
     <t>L'expression du nombre de noyaux d'iode 123 présent dans la thyroïde à l'instant $\boldsymbol{t}=\boldsymbol{t}_{1 / 2}$ est:</t>
   </si>
   <si>
-    <t>On considère que l'activité d'un échantillon radioactif devient négligeable (échantillon inactif) après une durée de 20 demi-vie. \section*{Après l'injection, la valeur de l'activité de l'échantillon lorsqu'il devient inactif est :}</t>
-  </si>
-  <si>
     <t>L'intensité du courant électrique à l'instant $t_{0}=0$ est :</t>
   </si>
   <si>
     <t>L'énergie électrique emmagasinée dans le condensateur à un instant $t$ s'exprime par la relation $\mathscr{E}_{e}=\frac{1}{2} \cdot C \cdot u_{C}^{2}$. La valeur de $\mathscr{E}_{e}$ à l'instant $t=0,25 s$ est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Réponse de dipôles à un échelon de tension (6 points)&lt;/b&gt;&lt;/center&gt;
- Le montage de la figure (1) permet de charger en même temps deux condensateurs de capacité $C_{1}$ et $C_{2}$ tel que $C_{1}&lt;C_{2}$. Les deux conducteurs ohmiques ont la même résistance $R_{1}=R_{2}=R$. À l'instant $t_{0}=0$, on ferme l'interrupteur $K$. Un système d'acquisition permet d'enregistrer l'évolution des tensions $u_{C_{1}}(t)$ et $u_{C_{2}}(t)$ (figure 2).</t>
   </si>
   <si>
     <t>Les valeurs des constantes de temps $\tau_{1}$ et $\tau_{2}$ des dipôles $R_{1} C_{1}$ et $R_{2} C_{2}$ sont :</t>
@@ -9844,18 +9742,6 @@
   </si>
   <si>
     <t>La valeur de la capacité est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Charge et décharge d'un condensateur : (9 points)&lt;/b&gt;&lt;/center&gt;
- On considère le montage de la figure (1). À l'instant $t_{0}=0$, on place l'interrupteur $K$ en position (1). La courbe de la figure (2) représente l'évolution de la tension $u_{C}(t)$ aux bornes du condensateur. Donnée : $I_{0}=0,5 \mathrm{~mA}$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Diffraction de la lumiére par une fente : (4 points)&lt;/b&gt;&lt;/center&gt;
- On éclaire une fente de largeur $a$ par une lumière monochromatique de fréquence $N$ émise par un laser. La figure de diffraction est observée sur un écran placé à une distance $D$ de la fente. La largeur de la tache centrale est notée $L$. - Avec un laser émettant une lumière verte de fréquence $N_{v}=5,36.10^{14} \mathrm{~Hz}$, on obtient une tache centrale de largeur $L_{v}=8,6 \mathrm{~mm}$. - Avec un laser émettant une lumière rouge de fréquence $N_{r}=4,74.10^{14} \mathrm{~Hz}$, on obtient une tache centrale de largeur $L_{r}$. Données : $\tan \theta \approx \theta(\mathrm{rad}) ; \frac{268}{237}=1,13$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Comportement des ondes ultrasonores dans deux milieux différents : ( 5 points)&lt;/b&gt;&lt;/center&gt;
- Deux sondes $E_{1}$ et $E_{2}$ émettent, au même instant, des ondes ultrasonores de même fréquence respectivement dans l'air et dans l'eau de mer (figure 1). Le capteur $R_{1}$ capte les ondes se propageant dans l'air et le capteur $R_{2}$ capte les ondes se propageant dans l'eau de mer. Soit $\Delta t$ le retard temporel des ondes reçues par $R_{1}$ par rapport à celles reçues par $R_{2}$, pour une valeur de $d$. La courbe de la figure (2) représente les variations de $\Delta t$ en fonction de $d$. On note $V_{a}$ la vitesse de propagation des ultrasons dans l'air et $V_{e}$ celle des ultrasons dans l'eau de mer. Données : $V_{a}=340 m \cdot .^{-1} \quad ; \quad \frac{1}{34}=2,94 \cdot 10^{-2} \quad ; 11 \times 2,27=25 \quad ; 14,92 \times 67=10^{3}$</t>
   </si>
   <si>
     <t xml:space="preserve"> Les valeurs de $\mathbf{x}$ et $\mathbf{y}$ sont :</t>
@@ -13383,6 +13269,129 @@
   <si>
     <t>Dans une population en équilibre de Hardy-Weinberg, la fréquence d'un allèle récessif pour un caractère héréditaire donné est de 0,20.
 &lt;br&gt;&lt;br&gt;Le pourcentage des individus présentant le caractère dominant à la génération suivante est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Propagation d'une onde le long d'une corde (5 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $v$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 s$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.
+&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
+    &lt;img src="/images/M21F1.png" alt="A" class="h-20" /&gt;
+    &lt;img src="/images/M21F2.png" alt="B" class="h-20" /&gt;
+&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>(A) : $\lambda=0,40 \mathrm{~m}$ $\quad$ $v=0,25 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>(B) : $\lambda=0,08 \mathrm{~m}$ $\quad$ $v=0,8 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>(C) : $\lambda=0,40 \mathrm{~m}$ $\quad$ $v=2,5 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>(D) : $\lambda=0,40 \mathrm{~m}$ $\quad$ $v=5,0 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>(E) : $\lambda=0,80 \mathrm{~m}$ $\quad$ $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Comportement des ondes ultrasonores dans deux milieux différents : ( 5 points)&lt;/b&gt;&lt;/center&gt;
+ Deux sondes $E_{1}$ et $E_{2}$ émettent, au même instant, des ondes ultrasonores de même fréquence respectivement dans l'air et dans l'eau de mer (figure 1). Le capteur $R_{1}$ capte les ondes se propageant dans l'air et le capteur $R_{2}$ capte les ondes se propageant dans l'eau de mer. Soit $\Delta t$ le retard temporel des ondes reçues par $R_{1}$ par rapport à celles reçues par $R_{2}$, pour une valeur de $d$. La courbe de la figure (2) représente les variations de $\Delta t$ en fonction de $d$. On note $V_{a}$ la vitesse de propagation des ultrasons dans l'air et $V_{e}$ celle des ultrasons dans l'eau de mer. 
+&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
+    &lt;img src="/images/M21F3.png" alt="A" class="h-20" /&gt;
+    &lt;img src="/images/M21F4.png" alt="B" class="h-20" /&gt;
+&lt;/div&gt;
+&lt;br&gt;Données : $V_{a}=340 m \cdot .s^{-1} \quad ; \quad \frac{1}{34}=2,94 \cdot 10^{-2} \quad ; 11 \times 2,27=25 \quad ; 14,92 \times 67=10^{3}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Diffraction de la lumiére par une fente : (4 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; On éclaire une fente de largeur $a$ par une lumière monochromatique de fréquence $N$ émise par un laser. La figure de diffraction est observée sur un écran placé à une distance $D$ de la fente. 
+La largeur de la tache centrale est notée $L$. &lt;br&gt;- Avec un laser émettant une lumière verte de fréquence $N_{v}=5,36.10^{14} \mathrm{~Hz}$, on obtient une tache centrale de largeur $L_{v}=8,6 \mathrm{~mm}$. &lt;br&gt;- Avec un laser émettant une lumière rouge de fréquence $N_{r}=4,74.10^{14} \mathrm{~Hz}$, on obtient une tache centrale de largeur $L_{r}$. 
+&lt;br&gt;&lt;img src="/images/M21F5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Données : $\tan \theta \approx \theta(\mathrm{rad}) ; \frac{268}{237}=1,13$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La radioactivité du plutonium : (8 points)&lt;/b&gt;&lt;/center&gt;
+ Le plutonium ${ }_{94}^{238} \mathrm{Pu}$ est radioactif $\alpha$. Un échantillon de plutonium contient à $t_{0}=0, N_{0}$ noyaux de plutonium ${ }_{94}^{238} \mathrm{Pu}$. On note $N_{d}$ le nombre de noyaux de ${ }_{94}^{238} \mathrm{Pu}$ désintégrés à l'instant $t$. La courbe cicontre représente les variations de $\left(\frac{d N_{d}}{d t}\right)$ en fonction de $N_{d}$. 
+&lt;br&gt;&lt;img src="/images/M21F6.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Donnée: $\ln 2 \approx 0,7$</t>
+  </si>
+  <si>
+    <t>On considère que l'activité d'un échantillon radioactif devient négligeable (échantillon inactif) après une durée de 20 demi-vie. 
+&lt;br&gt;Après l'injection, la valeur de l'activité de l'échantillon lorsqu'il devient inactif est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Charge et décharge d'un condensateur : (9 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; On considère le montage de la figure (1). À l'instant $t_{0}=0$, on place l'interrupteur $K$ en position (1). La courbe de la figure (2) représente l'évolution de la tension $u_{C}(t)$ aux bornes du condensateur. 
+Donnée : $I_{0}=0,5 \mathrm{~mA}$
+&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
+    &lt;img src="/images/M21F7.png" alt="A" class="h-20" /&gt;
+    &lt;img src="/images/M21F8.png" alt="B" class="h-20" /&gt;
+&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>(A) : $C=5 \mu \mathrm{~F}$</t>
+  </si>
+  <si>
+    <t>Lorsque le condensateur devient chargé, on place $K$ en position (2), à un instant pris comme nouvelle origine des dates ( $t_{0}=0$ ). La courbe de la figure (3) représente l'évolution de $u_{C}(t)$. 
+&lt;br&gt;&lt;img src="/images/M21F9.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;La tension aux bornes du condensateur s'écrit : $\boldsymbol{u}_{C}(\boldsymbol{t})=\boldsymbol{A} \cdot \boldsymbol{e}^{-\frac{\boldsymbol{t}}{R C}}$ avec $A$ constante.
+&lt;br&gt; Les valeurs de $A$ et $R$ sont :</t>
+  </si>
+  <si>
+    <t>(A) : $A=6 \mathrm{~V}$ $\qquad$ $R=50 \Omega$</t>
+  </si>
+  <si>
+    <t>(B) : $A=10 \mathrm{~V}$ $\qquad$ $R=100 \Omega$</t>
+  </si>
+  <si>
+    <t>(C) : $A=10 \mathrm{~V}$ $\qquad$ $R=200 \Omega$</t>
+  </si>
+  <si>
+    <t>(D) : $A=5 \mathrm{~V}$ $\qquad$ $R=0,5 \Omega$</t>
+  </si>
+  <si>
+    <t>(E) : $A=10 \mathrm{~V}$ $\qquad$ $R=1 \Omega$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Réponse de dipôles à un échelon de tension (6 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; Le montage de la figure (1) permet de charger en même temps deux condensateurs de capacité $C_{1}$ et $C_{2}$ tel que $C_{1}&lt;C_{2}$. Les deux conducteurs ohmiques ont la même résistance $R_{1}=R_{2}=R$. À l'instant $t_{0}=0$, on ferme l'interrupteur $K$. Un système d'acquisition permet d'enregistrer l'évolution des tensions $u_{C_{1}}(t)$ et $u_{C_{2}}(t)$ (figure 2).
+&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
+    &lt;img src="/images/M21F10.png" alt="A" class="h-20" /&gt;
+    &lt;img src="/images/M21F11.png" alt="B" class="h-20" /&gt;
+&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>(A) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,2 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(B) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=0,6 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(C) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(D) : $\tau_{1}=0,6 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(E) : $\tau_{1}=0,9 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(B) : $C_{2}=0,2 . C_{1}$</t>
+  </si>
+  <si>
+    <t>(A) : $U_{C_{2}}=37 \% . E$</t>
+  </si>
+  <si>
+    <t>(B) : $U_{C_{2}}=63 \% . E$</t>
+  </si>
+  <si>
+    <t>(C) : $U_{C_{2}}=67 \% . E$</t>
+  </si>
+  <si>
+    <t>(D) : $U_{C_{2}}=33 \% . E$</t>
+  </si>
+  <si>
+    <t>(E) : $U_{C_{2}}=57 \% E$</t>
   </si>
 </sst>
 </file>
@@ -14513,26 +14522,26 @@
         <v>98</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>1514</v>
+        <v>1478</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="46" t="s">
-        <v>1414</v>
+        <v>1378</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>1415</v>
+        <v>1379</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>1416</v>
+        <v>1380</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>1417</v>
+        <v>1381</v>
       </c>
       <c r="H2" s="46" t="s">
-        <v>1418</v>
+        <v>1382</v>
       </c>
       <c r="I2" s="46" t="s">
-        <v>1418</v>
+        <v>1382</v>
       </c>
       <c r="J2" s="18" t="s">
         <v>11</v>
@@ -14549,26 +14558,26 @@
         <v>98</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1515</v>
+        <v>1479</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="46" t="s">
-        <v>1419</v>
+        <v>1383</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>1420</v>
+        <v>1384</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>1421</v>
+        <v>1385</v>
       </c>
       <c r="G3" s="46" t="s">
-        <v>1422</v>
+        <v>1386</v>
       </c>
       <c r="H3" s="46" t="s">
-        <v>1423</v>
+        <v>1387</v>
       </c>
       <c r="I3" s="46" t="s">
-        <v>1421</v>
+        <v>1385</v>
       </c>
       <c r="J3" s="18" t="s">
         <v>11</v>
@@ -14585,26 +14594,26 @@
         <v>98</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>1516</v>
+        <v>1480</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="46" t="s">
-        <v>1424</v>
+        <v>1388</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>1425</v>
+        <v>1389</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>1426</v>
+        <v>1390</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>1427</v>
+        <v>1391</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>1428</v>
+        <v>1392</v>
       </c>
       <c r="I4" s="46" t="s">
-        <v>1425</v>
+        <v>1389</v>
       </c>
       <c r="J4" s="18" t="s">
         <v>11</v>
@@ -14621,26 +14630,26 @@
         <v>98</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>1517</v>
+        <v>1481</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="46" t="s">
-        <v>1429</v>
+        <v>1393</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>1430</v>
+        <v>1394</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>1431</v>
+        <v>1395</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>1432</v>
+        <v>1396</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>1433</v>
+        <v>1397</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>1429</v>
+        <v>1393</v>
       </c>
       <c r="J5" s="18" t="s">
         <v>11</v>
@@ -14657,26 +14666,26 @@
         <v>98</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>1518</v>
+        <v>1482</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="46" t="s">
-        <v>1434</v>
+        <v>1398</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>1435</v>
+        <v>1399</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>1436</v>
+        <v>1400</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>1437</v>
+        <v>1401</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>1438</v>
+        <v>1402</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>1438</v>
+        <v>1402</v>
       </c>
       <c r="J6" s="18" t="s">
         <v>11</v>
@@ -14693,26 +14702,26 @@
         <v>98</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>1519</v>
+        <v>1483</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="46" t="s">
-        <v>1439</v>
+        <v>1403</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>1440</v>
+        <v>1404</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>1441</v>
+        <v>1405</v>
       </c>
       <c r="G7" s="46" t="s">
-        <v>1442</v>
+        <v>1406</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>1443</v>
+        <v>1407</v>
       </c>
       <c r="I7" s="46" t="s">
-        <v>1441</v>
+        <v>1405</v>
       </c>
       <c r="J7" s="18" t="s">
         <v>11</v>
@@ -14729,26 +14738,26 @@
         <v>98</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>1520</v>
+        <v>1484</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="46" t="s">
-        <v>1444</v>
+        <v>1408</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>1445</v>
+        <v>1409</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>1446</v>
+        <v>1410</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>1447</v>
+        <v>1411</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>1448</v>
+        <v>1412</v>
       </c>
       <c r="I8" s="46" t="s">
-        <v>1448</v>
+        <v>1412</v>
       </c>
       <c r="J8" s="18" t="s">
         <v>11</v>
@@ -14765,26 +14774,26 @@
         <v>98</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>1521</v>
+        <v>1485</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="46" t="s">
-        <v>1449</v>
+        <v>1413</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>1450</v>
+        <v>1414</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>1451</v>
+        <v>1415</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>1452</v>
+        <v>1416</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>1453</v>
+        <v>1417</v>
       </c>
       <c r="I9" s="46" t="s">
-        <v>1453</v>
+        <v>1417</v>
       </c>
       <c r="J9" s="18" t="s">
         <v>11</v>
@@ -14801,26 +14810,26 @@
         <v>98</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>1522</v>
+        <v>1486</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="46" t="s">
-        <v>1454</v>
+        <v>1418</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>1455</v>
+        <v>1419</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>1456</v>
+        <v>1420</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>1457</v>
+        <v>1421</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>1458</v>
+        <v>1422</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>1454</v>
+        <v>1418</v>
       </c>
       <c r="J10" s="18" t="s">
         <v>11</v>
@@ -14837,26 +14846,26 @@
         <v>98</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>1523</v>
+        <v>1487</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="46" t="s">
-        <v>1459</v>
+        <v>1423</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>1460</v>
+        <v>1424</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>1461</v>
+        <v>1425</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>1462</v>
+        <v>1426</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>1463</v>
+        <v>1427</v>
       </c>
       <c r="I11" s="46" t="s">
-        <v>1463</v>
+        <v>1427</v>
       </c>
       <c r="J11" s="18" t="s">
         <v>11</v>
@@ -14873,26 +14882,26 @@
         <v>98</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>2387</v>
+        <v>2351</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="46" t="s">
-        <v>1464</v>
+        <v>1428</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>1465</v>
+        <v>1429</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>1466</v>
+        <v>1430</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>1467</v>
+        <v>1431</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>1468</v>
+        <v>1432</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>1466</v>
+        <v>1430</v>
       </c>
       <c r="J12" s="18" t="s">
         <v>11</v>
@@ -14909,26 +14918,26 @@
         <v>98</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>2381</v>
+        <v>2345</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="46" t="s">
-        <v>1469</v>
+        <v>1433</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>1470</v>
+        <v>1434</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>1471</v>
+        <v>1435</v>
       </c>
       <c r="G13" s="46" t="s">
-        <v>1472</v>
+        <v>1436</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>1473</v>
+        <v>1437</v>
       </c>
       <c r="I13" s="46" t="s">
-        <v>1472</v>
+        <v>1436</v>
       </c>
       <c r="J13" s="18" t="s">
         <v>11</v>
@@ -14945,26 +14954,26 @@
         <v>98</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>2382</v>
+        <v>2346</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="46" t="s">
-        <v>1474</v>
+        <v>1438</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>1475</v>
+        <v>1439</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>1476</v>
+        <v>1440</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>1477</v>
+        <v>1441</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>1478</v>
+        <v>1442</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>1474</v>
+        <v>1438</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>11</v>
@@ -14981,26 +14990,26 @@
         <v>98</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>1524</v>
+        <v>1488</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="46" t="s">
-        <v>1479</v>
+        <v>1443</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>1480</v>
+        <v>1444</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>1481</v>
+        <v>1445</v>
       </c>
       <c r="G15" s="46" t="s">
-        <v>1482</v>
+        <v>1446</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>1483</v>
+        <v>1447</v>
       </c>
       <c r="I15" s="46" t="s">
-        <v>1482</v>
+        <v>1446</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>11</v>
@@ -15017,26 +15026,26 @@
         <v>98</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>2383</v>
+        <v>2347</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="46" t="s">
-        <v>1484</v>
+        <v>1448</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>1485</v>
+        <v>1449</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>1486</v>
+        <v>1450</v>
       </c>
       <c r="G16" s="46" t="s">
-        <v>1487</v>
+        <v>1451</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>1488</v>
+        <v>1452</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>1484</v>
+        <v>1448</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>11</v>
@@ -15053,26 +15062,26 @@
         <v>98</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>1525</v>
+        <v>1489</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="46" t="s">
-        <v>1489</v>
+        <v>1453</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>1490</v>
+        <v>1454</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>1491</v>
+        <v>1455</v>
       </c>
       <c r="G17" s="46" t="s">
-        <v>1492</v>
+        <v>1456</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>1493</v>
+        <v>1457</v>
       </c>
       <c r="I17" s="46" t="s">
-        <v>1493</v>
+        <v>1457</v>
       </c>
       <c r="J17" s="18" t="s">
         <v>11</v>
@@ -15089,26 +15098,26 @@
         <v>98</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>2384</v>
+        <v>2348</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="46" t="s">
-        <v>1494</v>
+        <v>1458</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>1495</v>
+        <v>1459</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>1496</v>
+        <v>1460</v>
       </c>
       <c r="G18" s="46" t="s">
-        <v>1497</v>
+        <v>1461</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>1498</v>
+        <v>1462</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>1496</v>
+        <v>1460</v>
       </c>
       <c r="J18" s="18" t="s">
         <v>11</v>
@@ -15125,26 +15134,26 @@
         <v>98</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>2385</v>
+        <v>2349</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="46" t="s">
-        <v>1499</v>
+        <v>1463</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>1500</v>
+        <v>1464</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>1501</v>
+        <v>1465</v>
       </c>
       <c r="G19" s="46" t="s">
-        <v>1502</v>
+        <v>1466</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>1503</v>
+        <v>1467</v>
       </c>
       <c r="I19" s="46" t="s">
-        <v>1499</v>
+        <v>1463</v>
       </c>
       <c r="J19" s="18" t="s">
         <v>11</v>
@@ -15161,26 +15170,26 @@
         <v>98</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>2379</v>
+        <v>2343</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="46" t="s">
-        <v>1504</v>
+        <v>1468</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>1505</v>
+        <v>1469</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>1506</v>
+        <v>1470</v>
       </c>
       <c r="G20" s="46" t="s">
-        <v>1507</v>
+        <v>1471</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>1508</v>
+        <v>1472</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>1504</v>
+        <v>1468</v>
       </c>
       <c r="J20" s="18" t="s">
         <v>11</v>
@@ -15197,26 +15206,26 @@
         <v>98</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>2386</v>
+        <v>2350</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="46" t="s">
-        <v>1509</v>
+        <v>1473</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>1510</v>
+        <v>1474</v>
       </c>
       <c r="F21" s="46" t="s">
-        <v>1511</v>
+        <v>1475</v>
       </c>
       <c r="G21" s="46" t="s">
-        <v>1512</v>
+        <v>1476</v>
       </c>
       <c r="H21" s="46" t="s">
-        <v>1513</v>
+        <v>1477</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>1513</v>
+        <v>1477</v>
       </c>
       <c r="J21" s="18" t="s">
         <v>11</v>
@@ -15233,7 +15242,7 @@
         <v>99</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>2388</v>
+        <v>2352</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="2"/>
@@ -15255,11 +15264,11 @@
         <v>100</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>2389</v>
+        <v>2353</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="13" t="s">
-        <v>2401</v>
+        <v>2365</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>787</v>
@@ -15287,7 +15296,7 @@
         <v>100</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1339</v>
+        <v>1303</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="13" t="s">
@@ -15319,7 +15328,7 @@
         <v>100</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1340</v>
+        <v>1304</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="13" t="s">
@@ -15351,7 +15360,7 @@
         <v>99</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2390</v>
+        <v>2354</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -15373,7 +15382,7 @@
         <v>100</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>2391</v>
+        <v>2355</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="13" t="s">
@@ -15405,7 +15414,7 @@
         <v>100</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1341</v>
+        <v>1305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="13" t="s">
@@ -15437,7 +15446,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2393</v>
+        <v>2357</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -15459,7 +15468,7 @@
         <v>100</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1342</v>
+        <v>1306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
@@ -15491,7 +15500,7 @@
         <v>100</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1343</v>
+        <v>1307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
@@ -15507,7 +15516,7 @@
         <v>819</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>2392</v>
+        <v>2356</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>816</v>
@@ -15523,7 +15532,7 @@
         <v>100</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2394</v>
+        <v>2358</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
@@ -15555,7 +15564,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2395</v>
+        <v>2359</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -15577,7 +15586,7 @@
         <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2396</v>
+        <v>2360</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -15609,7 +15618,7 @@
         <v>100</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2397</v>
+        <v>2361</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
@@ -15641,7 +15650,7 @@
         <v>99</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>2402</v>
+        <v>2366</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -15663,7 +15672,7 @@
         <v>100</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2398</v>
+        <v>2362</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
@@ -15695,7 +15704,7 @@
         <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2399</v>
+        <v>2363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
@@ -15727,7 +15736,7 @@
         <v>99</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2400</v>
+        <v>2364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -15749,7 +15758,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>2403</v>
+        <v>2367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="13" t="s">
@@ -15779,7 +15788,7 @@
         <v>100</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>2404</v>
+        <v>2368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="13" t="s">
@@ -15809,26 +15818,26 @@
         <v>98</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>2405</v>
+        <v>2369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="13" t="s">
-        <v>2406</v>
+        <v>2370</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>2407</v>
+        <v>2371</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>2408</v>
+        <v>2372</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>2409</v>
+        <v>2373</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>2410</v>
+        <v>2374</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>2407</v>
+        <v>2371</v>
       </c>
       <c r="J42" s="18" t="s">
         <v>9</v>
@@ -15845,7 +15854,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>2411</v>
+        <v>2375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -15867,7 +15876,7 @@
         <v>100</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>2412</v>
+        <v>2376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
@@ -15899,7 +15908,7 @@
         <v>100</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>2413</v>
+        <v>2377</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
@@ -15931,7 +15940,7 @@
         <v>100</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>1338</v>
+        <v>1302</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
@@ -15963,7 +15972,7 @@
         <v>99</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>2414</v>
+        <v>2378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -15985,7 +15994,7 @@
         <v>100</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1337</v>
+        <v>1301</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="13" t="s">
@@ -16017,7 +16026,7 @@
         <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1265</v>
+        <v>1235</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="13" t="s">
@@ -16049,7 +16058,7 @@
         <v>99</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>2426</v>
+        <v>2390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -16071,26 +16080,26 @@
         <v>100</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>1620</v>
+        <v>1584</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="46" t="s">
-        <v>1526</v>
+        <v>1490</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>1527</v>
+        <v>1491</v>
       </c>
       <c r="F51" s="46" t="s">
-        <v>1528</v>
+        <v>1492</v>
       </c>
       <c r="G51" s="46" t="s">
-        <v>1529</v>
+        <v>1493</v>
       </c>
       <c r="H51" s="46" t="s">
-        <v>1530</v>
+        <v>1494</v>
       </c>
       <c r="I51" s="46" t="s">
-        <v>1526</v>
+        <v>1490</v>
       </c>
       <c r="J51" s="18"/>
       <c r="K51" s="18"/>
@@ -16103,26 +16112,26 @@
         <v>100</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>1621</v>
+        <v>1585</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="46" t="s">
-        <v>1531</v>
+        <v>1495</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>1532</v>
+        <v>1496</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>1533</v>
+        <v>1497</v>
       </c>
       <c r="G52" s="46" t="s">
-        <v>1534</v>
+        <v>1498</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>1535</v>
+        <v>1499</v>
       </c>
       <c r="I52" s="46" t="s">
-        <v>1532</v>
+        <v>1496</v>
       </c>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
@@ -16135,26 +16144,26 @@
         <v>100</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>1622</v>
+        <v>1586</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="46" t="s">
-        <v>1536</v>
+        <v>1500</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>1537</v>
+        <v>1501</v>
       </c>
       <c r="F53" s="46" t="s">
-        <v>1538</v>
+        <v>1502</v>
       </c>
       <c r="G53" s="46" t="s">
-        <v>1539</v>
+        <v>1503</v>
       </c>
       <c r="H53" s="46" t="s">
-        <v>1540</v>
+        <v>1504</v>
       </c>
       <c r="I53" s="46" t="s">
-        <v>1540</v>
+        <v>1504</v>
       </c>
       <c r="J53" s="18"/>
       <c r="K53" s="18"/>
@@ -16167,7 +16176,7 @@
         <v>99</v>
       </c>
       <c r="B54" s="46" t="s">
-        <v>2420</v>
+        <v>2384</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -16189,26 +16198,26 @@
         <v>100</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>1623</v>
+        <v>1587</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="46" t="s">
-        <v>2421</v>
+        <v>2385</v>
       </c>
       <c r="E55" s="46" t="s">
-        <v>2422</v>
+        <v>2386</v>
       </c>
       <c r="F55" s="46" t="s">
-        <v>2423</v>
+        <v>2387</v>
       </c>
       <c r="G55" s="46" t="s">
-        <v>2424</v>
+        <v>2388</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>2425</v>
+        <v>2389</v>
       </c>
       <c r="I55" s="46" t="s">
-        <v>2422</v>
+        <v>2386</v>
       </c>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
@@ -16221,26 +16230,26 @@
         <v>100</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>1625</v>
+        <v>1589</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="46" t="s">
-        <v>1541</v>
+        <v>1505</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>1542</v>
+        <v>1506</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>1543</v>
+        <v>1507</v>
       </c>
       <c r="G56" s="46" t="s">
-        <v>1544</v>
+        <v>1508</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>1531</v>
+        <v>1495</v>
       </c>
       <c r="I56" s="46" t="s">
-        <v>1542</v>
+        <v>1506</v>
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
@@ -16253,26 +16262,26 @@
         <v>100</v>
       </c>
       <c r="B57" s="46" t="s">
-        <v>1626</v>
+        <v>1590</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="46" t="s">
-        <v>1545</v>
+        <v>1509</v>
       </c>
       <c r="E57" s="46" t="s">
-        <v>1546</v>
+        <v>1510</v>
       </c>
       <c r="F57" s="46" t="s">
-        <v>1547</v>
+        <v>1511</v>
       </c>
       <c r="G57" s="46" t="s">
-        <v>1548</v>
+        <v>1512</v>
       </c>
       <c r="H57" s="46" t="s">
-        <v>1549</v>
+        <v>1513</v>
       </c>
       <c r="I57" s="46" t="s">
-        <v>1549</v>
+        <v>1513</v>
       </c>
       <c r="J57" s="18"/>
       <c r="K57" s="18"/>
@@ -16285,26 +16294,26 @@
         <v>100</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>1624</v>
+        <v>1588</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="46" t="s">
-        <v>1550</v>
+        <v>1514</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>1551</v>
+        <v>1515</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>1552</v>
+        <v>1516</v>
       </c>
       <c r="G58" s="46" t="s">
-        <v>1553</v>
+        <v>1517</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>1554</v>
+        <v>1518</v>
       </c>
       <c r="I58" s="46" t="s">
-        <v>1552</v>
+        <v>1516</v>
       </c>
       <c r="J58" s="18"/>
       <c r="K58" s="18"/>
@@ -16317,7 +16326,7 @@
         <v>99</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>2419</v>
+        <v>2383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -16339,26 +16348,26 @@
         <v>100</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>1627</v>
+        <v>1591</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="46" t="s">
-        <v>1555</v>
+        <v>1519</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>1556</v>
+        <v>1520</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>1557</v>
+        <v>1521</v>
       </c>
       <c r="G60" s="46" t="s">
-        <v>1558</v>
+        <v>1522</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>1559</v>
+        <v>1523</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>1556</v>
+        <v>1520</v>
       </c>
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
@@ -16371,26 +16380,26 @@
         <v>100</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>1628</v>
+        <v>1592</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="46" t="s">
-        <v>1560</v>
+        <v>1524</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>1561</v>
+        <v>1525</v>
       </c>
       <c r="F61" s="46" t="s">
-        <v>1562</v>
+        <v>1526</v>
       </c>
       <c r="G61" s="46" t="s">
-        <v>1563</v>
+        <v>1527</v>
       </c>
       <c r="H61" s="46" t="s">
-        <v>1564</v>
+        <v>1528</v>
       </c>
       <c r="I61" s="46" t="s">
-        <v>1561</v>
+        <v>1525</v>
       </c>
       <c r="J61" s="18"/>
       <c r="K61" s="18"/>
@@ -16403,26 +16412,26 @@
         <v>100</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>1629</v>
+        <v>1593</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="46" t="s">
-        <v>1565</v>
+        <v>1529</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>1567</v>
+        <v>1531</v>
       </c>
       <c r="G62" s="46" t="s">
-        <v>1568</v>
+        <v>1532</v>
       </c>
       <c r="H62" s="46" t="s">
-        <v>1569</v>
+        <v>1533</v>
       </c>
       <c r="I62" s="46" t="s">
-        <v>1565</v>
+        <v>1529</v>
       </c>
       <c r="J62" s="18"/>
       <c r="K62" s="18"/>
@@ -16435,26 +16444,26 @@
         <v>98</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>2418</v>
+        <v>2382</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="46" t="s">
-        <v>1570</v>
+        <v>1534</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>1571</v>
+        <v>1535</v>
       </c>
       <c r="F63" s="46" t="s">
-        <v>1572</v>
+        <v>1536</v>
       </c>
       <c r="G63" s="46" t="s">
-        <v>1573</v>
+        <v>1537</v>
       </c>
       <c r="H63" s="46" t="s">
-        <v>1574</v>
+        <v>1538</v>
       </c>
       <c r="I63" s="46" t="s">
-        <v>1573</v>
+        <v>1537</v>
       </c>
       <c r="J63" s="18" t="s">
         <v>659</v>
@@ -16471,7 +16480,7 @@
         <v>99</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>2417</v>
+        <v>2381</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -16493,26 +16502,26 @@
         <v>100</v>
       </c>
       <c r="B65" s="46" t="s">
-        <v>1630</v>
+        <v>1594</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="46" t="s">
-        <v>1575</v>
+        <v>1539</v>
       </c>
       <c r="E65" s="46" t="s">
-        <v>1576</v>
+        <v>1540</v>
       </c>
       <c r="F65" s="46" t="s">
-        <v>1577</v>
+        <v>1541</v>
       </c>
       <c r="G65" s="46" t="s">
-        <v>1578</v>
+        <v>1542</v>
       </c>
       <c r="H65" s="46" t="s">
-        <v>1579</v>
+        <v>1543</v>
       </c>
       <c r="I65" s="46" t="s">
-        <v>1576</v>
+        <v>1540</v>
       </c>
       <c r="J65" s="18"/>
       <c r="K65" s="18"/>
@@ -16525,26 +16534,26 @@
         <v>100</v>
       </c>
       <c r="B66" s="46" t="s">
-        <v>1631</v>
+        <v>1595</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="46" t="s">
-        <v>1580</v>
+        <v>1544</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>1581</v>
+        <v>1545</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>1582</v>
+        <v>1546</v>
       </c>
       <c r="G66" s="46" t="s">
-        <v>1583</v>
+        <v>1547</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>1584</v>
+        <v>1548</v>
       </c>
       <c r="I66" s="46" t="s">
-        <v>1584</v>
+        <v>1548</v>
       </c>
       <c r="J66" s="18"/>
       <c r="K66" s="18"/>
@@ -16557,7 +16566,7 @@
         <v>99</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>2416</v>
+        <v>2380</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -16579,26 +16588,26 @@
         <v>100</v>
       </c>
       <c r="B68" s="46" t="s">
-        <v>1632</v>
+        <v>1596</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="46" t="s">
-        <v>1585</v>
+        <v>1549</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>1586</v>
+        <v>1550</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>1587</v>
+        <v>1551</v>
       </c>
       <c r="G68" s="46" t="s">
-        <v>1588</v>
+        <v>1552</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>1589</v>
+        <v>1553</v>
       </c>
       <c r="I68" s="46" t="s">
-        <v>1585</v>
+        <v>1549</v>
       </c>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
@@ -16611,26 +16620,26 @@
         <v>100</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>1633</v>
+        <v>1597</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="46" t="s">
-        <v>1590</v>
+        <v>1554</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>1591</v>
+        <v>1555</v>
       </c>
       <c r="F69" s="46" t="s">
-        <v>1592</v>
+        <v>1556</v>
       </c>
       <c r="G69" s="46" t="s">
-        <v>1593</v>
+        <v>1557</v>
       </c>
       <c r="H69" s="46" t="s">
-        <v>1594</v>
+        <v>1558</v>
       </c>
       <c r="I69" s="46" t="s">
-        <v>1592</v>
+        <v>1556</v>
       </c>
       <c r="J69" s="18"/>
       <c r="K69" s="18"/>
@@ -16643,26 +16652,26 @@
         <v>100</v>
       </c>
       <c r="B70" s="46" t="s">
-        <v>1634</v>
+        <v>1598</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="46" t="s">
-        <v>1595</v>
+        <v>1559</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>1596</v>
+        <v>1560</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>1597</v>
+        <v>1561</v>
       </c>
       <c r="G70" s="46" t="s">
-        <v>1598</v>
+        <v>1562</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>1599</v>
+        <v>1563</v>
       </c>
       <c r="I70" s="46" t="s">
-        <v>1596</v>
+        <v>1560</v>
       </c>
       <c r="J70" s="18"/>
       <c r="K70" s="18"/>
@@ -16675,7 +16684,7 @@
         <v>99</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>2427</v>
+        <v>2391</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -16697,26 +16706,26 @@
         <v>100</v>
       </c>
       <c r="B72" s="46" t="s">
-        <v>1635</v>
+        <v>1599</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="46" t="s">
-        <v>1600</v>
+        <v>1564</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>1601</v>
+        <v>1565</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>1602</v>
+        <v>1566</v>
       </c>
       <c r="G72" s="46" t="s">
-        <v>1603</v>
+        <v>1567</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>1604</v>
+        <v>1568</v>
       </c>
       <c r="I72" s="46" t="s">
-        <v>1603</v>
+        <v>1567</v>
       </c>
       <c r="J72" s="18"/>
       <c r="K72" s="18"/>
@@ -16729,26 +16738,26 @@
         <v>100</v>
       </c>
       <c r="B73" s="46" t="s">
-        <v>1636</v>
+        <v>1600</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="46" t="s">
-        <v>1605</v>
+        <v>1569</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>1606</v>
+        <v>1570</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>1607</v>
+        <v>1571</v>
       </c>
       <c r="G73" s="46" t="s">
-        <v>1608</v>
+        <v>1572</v>
       </c>
       <c r="H73" s="46" t="s">
-        <v>1609</v>
+        <v>1573</v>
       </c>
       <c r="I73" s="46" t="s">
-        <v>1609</v>
+        <v>1573</v>
       </c>
       <c r="J73" s="18"/>
       <c r="K73" s="18"/>
@@ -16761,7 +16770,7 @@
         <v>99</v>
       </c>
       <c r="B74" s="46" t="s">
-        <v>2415</v>
+        <v>2379</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -16783,26 +16792,26 @@
         <v>100</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>1637</v>
+        <v>1601</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="46" t="s">
-        <v>1610</v>
+        <v>1574</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>1611</v>
+        <v>1575</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>1612</v>
+        <v>1576</v>
       </c>
       <c r="G75" s="46" t="s">
-        <v>1613</v>
+        <v>1577</v>
       </c>
       <c r="H75" s="46" t="s">
-        <v>1614</v>
+        <v>1578</v>
       </c>
       <c r="I75" s="46" t="s">
-        <v>1610</v>
+        <v>1574</v>
       </c>
       <c r="J75" s="18"/>
       <c r="K75" s="18"/>
@@ -16815,26 +16824,26 @@
         <v>100</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>1638</v>
+        <v>1602</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="46" t="s">
-        <v>1615</v>
+        <v>1579</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>1616</v>
+        <v>1580</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>1617</v>
+        <v>1581</v>
       </c>
       <c r="G76" s="46" t="s">
-        <v>1618</v>
+        <v>1582</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>1619</v>
+        <v>1583</v>
       </c>
       <c r="I76" s="46" t="s">
-        <v>1618</v>
+        <v>1582</v>
       </c>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
@@ -16847,7 +16856,7 @@
         <v>98</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>1345</v>
+        <v>1309</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="13" t="s">
@@ -16883,7 +16892,7 @@
         <v>98</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>1346</v>
+        <v>1310</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="13" t="s">
@@ -16919,7 +16928,7 @@
         <v>98</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>2428</v>
+        <v>2392</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="13" t="s">
@@ -16955,7 +16964,7 @@
         <v>98</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>1347</v>
+        <v>1311</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="13" t="s">
@@ -16991,7 +17000,7 @@
         <v>98</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>1348</v>
+        <v>1312</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="13" t="s">
@@ -17027,7 +17036,7 @@
         <v>98</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1349</v>
+        <v>1313</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="13" t="s">
@@ -17063,7 +17072,7 @@
         <v>98</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>2429</v>
+        <v>2393</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="13" t="s">
@@ -17099,7 +17108,7 @@
         <v>98</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>1350</v>
+        <v>1314</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="13" t="s">
@@ -17135,7 +17144,7 @@
         <v>98</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>2378</v>
+        <v>2342</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="13" t="s">
@@ -17171,7 +17180,7 @@
         <v>98</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>1351</v>
+        <v>1315</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="13" t="s">
@@ -17207,7 +17216,7 @@
         <v>98</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>2430</v>
+        <v>2394</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="13" t="s">
@@ -17243,7 +17252,7 @@
         <v>98</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>1352</v>
+        <v>1316</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="13" t="s">
@@ -17279,7 +17288,7 @@
         <v>98</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>2431</v>
+        <v>2395</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="13" t="s">
@@ -17315,7 +17324,7 @@
         <v>98</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>1353</v>
+        <v>1317</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="13" t="s">
@@ -17351,7 +17360,7 @@
         <v>98</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>2432</v>
+        <v>2396</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="13" t="s">
@@ -17387,7 +17396,7 @@
         <v>98</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>2433</v>
+        <v>2397</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="13" t="s">
@@ -17423,7 +17432,7 @@
         <v>98</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>2434</v>
+        <v>2398</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="13" t="s">
@@ -17459,7 +17468,7 @@
         <v>98</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>1354</v>
+        <v>1318</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="13" t="s">
@@ -17495,7 +17504,7 @@
         <v>98</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>1355</v>
+        <v>1319</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="13" t="s">
@@ -17531,7 +17540,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>1356</v>
+        <v>1320</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="13" t="s">
@@ -17567,23 +17576,23 @@
         <v>98</v>
       </c>
       <c r="B97" s="37" t="s">
-        <v>1728</v>
+        <v>1692</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="47" t="s">
-        <v>1639</v>
+        <v>1603</v>
       </c>
       <c r="E97" s="47" t="s">
-        <v>1640</v>
+        <v>1604</v>
       </c>
       <c r="F97" s="47" t="s">
-        <v>1641</v>
+        <v>1605</v>
       </c>
       <c r="G97" s="47" t="s">
-        <v>1642</v>
+        <v>1606</v>
       </c>
       <c r="H97" s="47" t="s">
-        <v>1643</v>
+        <v>1607</v>
       </c>
       <c r="I97" s="2"/>
       <c r="J97" s="18" t="s">
@@ -17601,23 +17610,23 @@
         <v>98</v>
       </c>
       <c r="B98" s="40" t="s">
-        <v>1263</v>
+        <v>1234</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="48" t="s">
-        <v>1644</v>
+        <v>1608</v>
       </c>
       <c r="E98" s="48" t="s">
-        <v>1645</v>
+        <v>1609</v>
       </c>
       <c r="F98" s="48" t="s">
-        <v>1646</v>
+        <v>1610</v>
       </c>
       <c r="G98" s="48" t="s">
-        <v>1647</v>
+        <v>1611</v>
       </c>
       <c r="H98" s="48" t="s">
-        <v>1648</v>
+        <v>1612</v>
       </c>
       <c r="I98" s="2"/>
       <c r="J98" s="18" t="s">
@@ -17639,19 +17648,19 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="47" t="s">
-        <v>1649</v>
+        <v>1613</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>1650</v>
+        <v>1614</v>
       </c>
       <c r="F99" s="47" t="s">
-        <v>1651</v>
+        <v>1615</v>
       </c>
       <c r="G99" s="47" t="s">
-        <v>1652</v>
+        <v>1616</v>
       </c>
       <c r="H99" s="47" t="s">
-        <v>1653</v>
+        <v>1617</v>
       </c>
       <c r="I99" s="2"/>
       <c r="J99" s="18" t="s">
@@ -17669,23 +17678,23 @@
         <v>98</v>
       </c>
       <c r="B100" s="40" t="s">
-        <v>1729</v>
+        <v>1693</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="48" t="s">
-        <v>1654</v>
+        <v>1618</v>
       </c>
       <c r="E100" s="48" t="s">
-        <v>1655</v>
+        <v>1619</v>
       </c>
       <c r="F100" s="48" t="s">
-        <v>1656</v>
+        <v>1620</v>
       </c>
       <c r="G100" s="48" t="s">
-        <v>1657</v>
+        <v>1621</v>
       </c>
       <c r="H100" s="48" t="s">
-        <v>1658</v>
+        <v>1622</v>
       </c>
       <c r="I100" s="2"/>
       <c r="J100" s="18" t="s">
@@ -17703,23 +17712,23 @@
         <v>98</v>
       </c>
       <c r="B101" s="37" t="s">
-        <v>1730</v>
+        <v>1694</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="47" t="s">
-        <v>1659</v>
+        <v>1623</v>
       </c>
       <c r="E101" s="47" t="s">
-        <v>1660</v>
+        <v>1624</v>
       </c>
       <c r="F101" s="47" t="s">
-        <v>1661</v>
+        <v>1625</v>
       </c>
       <c r="G101" s="47" t="s">
-        <v>1662</v>
+        <v>1626</v>
       </c>
       <c r="H101" s="47" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="I101" s="2"/>
       <c r="J101" s="18" t="s">
@@ -17741,19 +17750,19 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="48" t="s">
-        <v>1664</v>
+        <v>1628</v>
       </c>
       <c r="E102" s="48" t="s">
-        <v>1665</v>
+        <v>1629</v>
       </c>
       <c r="F102" s="48" t="s">
-        <v>1666</v>
+        <v>1630</v>
       </c>
       <c r="G102" s="48" t="s">
-        <v>1667</v>
+        <v>1631</v>
       </c>
       <c r="H102" s="48" t="s">
-        <v>1668</v>
+        <v>1632</v>
       </c>
       <c r="I102" s="2"/>
       <c r="J102" s="18" t="s">
@@ -17771,23 +17780,23 @@
         <v>98</v>
       </c>
       <c r="B103" s="37" t="s">
-        <v>1731</v>
+        <v>1695</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="47" t="s">
-        <v>1669</v>
+        <v>1633</v>
       </c>
       <c r="E103" s="47" t="s">
-        <v>1670</v>
+        <v>1634</v>
       </c>
       <c r="F103" s="47" t="s">
-        <v>1671</v>
+        <v>1635</v>
       </c>
       <c r="G103" s="47" t="s">
-        <v>1672</v>
+        <v>1636</v>
       </c>
       <c r="H103" s="47" t="s">
-        <v>1673</v>
+        <v>1637</v>
       </c>
       <c r="I103" s="2"/>
       <c r="J103" s="18" t="s">
@@ -17805,23 +17814,23 @@
         <v>98</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>1732</v>
+        <v>1696</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="48" t="s">
-        <v>1674</v>
+        <v>1638</v>
       </c>
       <c r="E104" s="48" t="s">
-        <v>1675</v>
+        <v>1639</v>
       </c>
       <c r="F104" s="48" t="s">
-        <v>1676</v>
+        <v>1640</v>
       </c>
       <c r="G104" s="48" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="H104" s="48" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="I104" s="2"/>
       <c r="J104" s="18" t="s">
@@ -17839,20 +17848,20 @@
         <v>98</v>
       </c>
       <c r="B105" s="37" t="s">
-        <v>1733</v>
+        <v>1697</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="47" t="s">
-        <v>1679</v>
+        <v>1643</v>
       </c>
       <c r="E105" s="47" t="s">
-        <v>1680</v>
+        <v>1644</v>
       </c>
       <c r="F105" s="47" t="s">
-        <v>1681</v>
+        <v>1645</v>
       </c>
       <c r="G105" s="47" t="s">
-        <v>1682</v>
+        <v>1646</v>
       </c>
       <c r="H105" s="47" t="s">
         <v>82</v>
@@ -17877,19 +17886,19 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="48" t="s">
-        <v>1683</v>
+        <v>1647</v>
       </c>
       <c r="E106" s="48" t="s">
-        <v>1684</v>
+        <v>1648</v>
       </c>
       <c r="F106" s="48" t="s">
-        <v>1685</v>
+        <v>1649</v>
       </c>
       <c r="G106" s="48" t="s">
-        <v>1686</v>
+        <v>1650</v>
       </c>
       <c r="H106" s="48" t="s">
-        <v>1687</v>
+        <v>1651</v>
       </c>
       <c r="I106" s="2"/>
       <c r="J106" s="18" t="s">
@@ -17907,23 +17916,23 @@
         <v>98</v>
       </c>
       <c r="B107" s="37" t="s">
-        <v>2435</v>
+        <v>2399</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="47" t="s">
         <v>83</v>
       </c>
       <c r="E107" s="47" t="s">
-        <v>1688</v>
+        <v>1652</v>
       </c>
       <c r="F107" s="47" t="s">
-        <v>1689</v>
+        <v>1653</v>
       </c>
       <c r="G107" s="47" t="s">
-        <v>1690</v>
+        <v>1654</v>
       </c>
       <c r="H107" s="47" t="s">
-        <v>1691</v>
+        <v>1655</v>
       </c>
       <c r="I107" s="2"/>
       <c r="J107" s="18" t="s">
@@ -17948,16 +17957,16 @@
         <v>84</v>
       </c>
       <c r="E108" s="48" t="s">
-        <v>1692</v>
+        <v>1656</v>
       </c>
       <c r="F108" s="48" t="s">
-        <v>1693</v>
+        <v>1657</v>
       </c>
       <c r="G108" s="48" t="s">
         <v>85</v>
       </c>
       <c r="H108" s="48" t="s">
-        <v>1694</v>
+        <v>1658</v>
       </c>
       <c r="I108" s="2"/>
       <c r="J108" s="18" t="s">
@@ -17975,23 +17984,23 @@
         <v>98</v>
       </c>
       <c r="B109" s="37" t="s">
-        <v>2436</v>
+        <v>2400</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="47" t="s">
-        <v>1695</v>
+        <v>1659</v>
       </c>
       <c r="E109" s="47" t="s">
-        <v>1696</v>
+        <v>1660</v>
       </c>
       <c r="F109" s="47" t="s">
-        <v>1697</v>
+        <v>1661</v>
       </c>
       <c r="G109" s="47" t="s">
-        <v>1698</v>
+        <v>1662</v>
       </c>
       <c r="H109" s="47" t="s">
-        <v>1699</v>
+        <v>1663</v>
       </c>
       <c r="I109" s="2"/>
       <c r="J109" s="18" t="s">
@@ -18009,23 +18018,23 @@
         <v>98</v>
       </c>
       <c r="B110" s="40" t="s">
-        <v>2437</v>
+        <v>2401</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="48" t="s">
-        <v>1138</v>
+        <v>1109</v>
       </c>
       <c r="E110" s="48" t="s">
-        <v>1139</v>
+        <v>1110</v>
       </c>
       <c r="F110" s="48" t="s">
-        <v>1700</v>
+        <v>1664</v>
       </c>
       <c r="G110" s="48" t="s">
-        <v>1701</v>
+        <v>1665</v>
       </c>
       <c r="H110" s="48" t="s">
-        <v>1702</v>
+        <v>1666</v>
       </c>
       <c r="I110" s="2"/>
       <c r="J110" s="18" t="s">
@@ -18043,23 +18052,23 @@
         <v>98</v>
       </c>
       <c r="B111" s="37" t="s">
-        <v>2438</v>
+        <v>2402</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="47" t="s">
-        <v>1703</v>
+        <v>1667</v>
       </c>
       <c r="E111" s="47" t="s">
-        <v>1704</v>
+        <v>1668</v>
       </c>
       <c r="F111" s="47" t="s">
-        <v>1705</v>
+        <v>1669</v>
       </c>
       <c r="G111" s="47" t="s">
-        <v>1706</v>
+        <v>1670</v>
       </c>
       <c r="H111" s="47" t="s">
-        <v>1707</v>
+        <v>1671</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="18" t="s">
@@ -18077,23 +18086,23 @@
         <v>98</v>
       </c>
       <c r="B112" s="40" t="s">
-        <v>2439</v>
+        <v>2403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="48" t="s">
-        <v>1708</v>
+        <v>1672</v>
       </c>
       <c r="E112" s="48" t="s">
-        <v>1709</v>
+        <v>1673</v>
       </c>
       <c r="F112" s="48" t="s">
-        <v>1710</v>
+        <v>1674</v>
       </c>
       <c r="G112" s="48" t="s">
-        <v>1711</v>
+        <v>1675</v>
       </c>
       <c r="H112" s="48" t="s">
-        <v>1712</v>
+        <v>1676</v>
       </c>
       <c r="I112" s="2"/>
       <c r="J112" s="18" t="s">
@@ -18111,23 +18120,23 @@
         <v>98</v>
       </c>
       <c r="B113" s="37" t="s">
-        <v>2440</v>
+        <v>2404</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="47" t="s">
-        <v>1713</v>
+        <v>1677</v>
       </c>
       <c r="E113" s="47" t="s">
-        <v>1714</v>
+        <v>1678</v>
       </c>
       <c r="F113" s="47" t="s">
-        <v>1715</v>
+        <v>1679</v>
       </c>
       <c r="G113" s="47" t="s">
-        <v>1716</v>
+        <v>1680</v>
       </c>
       <c r="H113" s="47" t="s">
-        <v>1717</v>
+        <v>1681</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="18" t="s">
@@ -18145,7 +18154,7 @@
         <v>98</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>2441</v>
+        <v>2405</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="48" t="s">
@@ -18179,23 +18188,23 @@
         <v>98</v>
       </c>
       <c r="B115" s="37" t="s">
-        <v>2442</v>
+        <v>2406</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="47" t="s">
-        <v>1718</v>
+        <v>1682</v>
       </c>
       <c r="E115" s="47" t="s">
-        <v>1719</v>
+        <v>1683</v>
       </c>
       <c r="F115" s="47" t="s">
-        <v>1720</v>
+        <v>1684</v>
       </c>
       <c r="G115" s="47" t="s">
-        <v>1721</v>
+        <v>1685</v>
       </c>
       <c r="H115" s="47" t="s">
-        <v>1722</v>
+        <v>1686</v>
       </c>
       <c r="I115" s="2"/>
       <c r="J115" s="18" t="s">
@@ -18213,23 +18222,23 @@
         <v>98</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>2443</v>
+        <v>2407</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="48" t="s">
-        <v>1723</v>
+        <v>1687</v>
       </c>
       <c r="E116" s="48" t="s">
-        <v>1724</v>
+        <v>1688</v>
       </c>
       <c r="F116" s="48" t="s">
-        <v>1725</v>
+        <v>1689</v>
       </c>
       <c r="G116" s="48" t="s">
-        <v>1726</v>
+        <v>1690</v>
       </c>
       <c r="H116" s="48" t="s">
-        <v>1727</v>
+        <v>1691</v>
       </c>
       <c r="I116" s="2"/>
       <c r="J116" s="18" t="s">
@@ -18242,16 +18251,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="150">
+    <row r="117" spans="1:12" ht="225">
       <c r="A117" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>880</v>
-      </c>
+        <v>2408</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
@@ -18271,23 +18278,23 @@
         <v>100</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>1266</v>
+        <v>1236</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="13" t="s">
-        <v>881</v>
+        <v>2409</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>882</v>
+        <v>2410</v>
       </c>
       <c r="F118" s="13" t="s">
-        <v>883</v>
+        <v>2411</v>
       </c>
       <c r="G118" s="13" t="s">
-        <v>884</v>
+        <v>2412</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>885</v>
+        <v>2413</v>
       </c>
       <c r="I118" s="2"/>
       <c r="J118" s="18"/>
@@ -18301,23 +18308,23 @@
         <v>100</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>1267</v>
+        <v>1237</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="13" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="F119" s="13" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="I119" s="2"/>
       <c r="J119" s="18"/>
@@ -18331,23 +18338,23 @@
         <v>100</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>1268</v>
+        <v>1238</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="13" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="F120" s="13" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="I120" s="2"/>
       <c r="J120" s="18"/>
@@ -18356,16 +18363,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="225">
+    <row r="121" spans="1:12" ht="300">
       <c r="A121" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>896</v>
-      </c>
+        <v>2414</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
@@ -18385,23 +18390,23 @@
         <v>100</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>1269</v>
+        <v>1239</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="13" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="F122" s="13" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="I122" s="2"/>
       <c r="J122" s="18"/>
@@ -18415,23 +18420,23 @@
         <v>100</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>1270</v>
+        <v>1240</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="13" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="F123" s="13" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="H123" s="13" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="I123" s="2"/>
       <c r="J123" s="18"/>
@@ -18440,16 +18445,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="195">
+    <row r="124" spans="1:12" ht="255">
       <c r="A124" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>937</v>
-      </c>
+        <v>2415</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
@@ -18469,23 +18472,23 @@
         <v>100</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>1271</v>
+        <v>1241</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="13" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="F125" s="13" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="I125" s="2"/>
       <c r="J125" s="18"/>
@@ -18499,23 +18502,23 @@
         <v>100</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>1272</v>
+        <v>1242</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="13" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="I126" s="2"/>
       <c r="J126" s="18"/>
@@ -18524,16 +18527,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="135">
+    <row r="127" spans="1:12" ht="180">
       <c r="A127" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>938</v>
-      </c>
+        <v>2416</v>
+      </c>
+      <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
@@ -18553,23 +18554,23 @@
         <v>100</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>1273</v>
+        <v>1243</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="13" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="F128" s="13" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="H128" s="13" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="I128" s="2"/>
       <c r="J128" s="18"/>
@@ -18583,23 +18584,23 @@
         <v>100</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>1274</v>
+        <v>1244</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="13" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="F129" s="13" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="H129" s="13" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="I129" s="2"/>
       <c r="J129" s="18"/>
@@ -18613,23 +18614,23 @@
         <v>100</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>1275</v>
+        <v>1245</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="13" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="I130" s="2"/>
       <c r="J130" s="18"/>
@@ -18643,23 +18644,23 @@
         <v>100</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>1276</v>
+        <v>1246</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="13" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="F131" s="13" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="G131" s="13" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="I131" s="2"/>
       <c r="J131" s="18"/>
@@ -18673,11 +18674,9 @@
         <v>99</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>786</v>
-      </c>
+        <v>1247</v>
+      </c>
+      <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
@@ -18697,23 +18696,23 @@
         <v>100</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>1279</v>
+        <v>1248</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="I133" s="2"/>
       <c r="J133" s="18"/>
@@ -18722,28 +18721,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="60">
+    <row r="134" spans="1:12" ht="75">
       <c r="A134" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>1280</v>
+        <v>2417</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="I134" s="2"/>
       <c r="J134" s="18"/>
@@ -18752,16 +18751,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="90">
+    <row r="135" spans="1:12" ht="165">
       <c r="A135" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>949</v>
-      </c>
+        <v>2418</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
@@ -18781,23 +18778,23 @@
         <v>100</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>1333</v>
+        <v>1300</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="13" t="s">
-        <v>951</v>
+        <v>2419</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="F136" s="13" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="I136" s="2"/>
       <c r="J136" s="18"/>
@@ -18806,30 +18803,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="120">
+    <row r="137" spans="1:12" ht="180">
       <c r="A137" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>950</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>986</v>
-      </c>
+        <v>2420</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" s="13" t="s">
-        <v>956</v>
+        <v>2421</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>957</v>
+        <v>2422</v>
       </c>
       <c r="F137" s="13" t="s">
-        <v>958</v>
+        <v>2423</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>959</v>
+        <v>2424</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>960</v>
+        <v>2425</v>
       </c>
       <c r="I137" s="2"/>
       <c r="J137" s="18"/>
@@ -18843,23 +18838,23 @@
         <v>100</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>1281</v>
+        <v>1249</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="13" t="s">
-        <v>961</v>
+        <v>944</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>962</v>
+        <v>945</v>
       </c>
       <c r="F138" s="13" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>964</v>
+        <v>947</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="I138" s="2"/>
       <c r="J138" s="18"/>
@@ -18873,23 +18868,23 @@
         <v>100</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>1282</v>
+        <v>1250</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="13" t="s">
-        <v>966</v>
+        <v>949</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>967</v>
+        <v>950</v>
       </c>
       <c r="F139" s="13" t="s">
-        <v>968</v>
+        <v>951</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>969</v>
+        <v>952</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
       <c r="I139" s="2"/>
       <c r="J139" s="18"/>
@@ -18898,15 +18893,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="135">
+    <row r="140" spans="1:12" ht="195">
       <c r="A140" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>1283</v>
+        <v>2426</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>987</v>
+        <v>958</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
@@ -18927,23 +18922,23 @@
         <v>100</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>1284</v>
+        <v>1251</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="13" t="s">
-        <v>971</v>
+        <v>2427</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>972</v>
+        <v>2428</v>
       </c>
       <c r="F141" s="13" t="s">
-        <v>973</v>
+        <v>2429</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>974</v>
+        <v>2430</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>975</v>
+        <v>2431</v>
       </c>
       <c r="I141" s="2"/>
       <c r="J141" s="18"/>
@@ -18957,23 +18952,23 @@
         <v>100</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>1285</v>
+        <v>1252</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="13" t="s">
-        <v>976</v>
+        <v>954</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>977</v>
+        <v>2432</v>
       </c>
       <c r="F142" s="13" t="s">
-        <v>978</v>
+        <v>955</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>979</v>
+        <v>956</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>980</v>
+        <v>957</v>
       </c>
       <c r="I142" s="2"/>
       <c r="J142" s="18"/>
@@ -18987,23 +18982,23 @@
         <v>100</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>1286</v>
+        <v>1253</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="13" t="s">
-        <v>981</v>
+        <v>2433</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>982</v>
+        <v>2434</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>983</v>
+        <v>2435</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>984</v>
+        <v>2436</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>985</v>
+        <v>2437</v>
       </c>
       <c r="I143" s="2"/>
       <c r="J143" s="18"/>
@@ -19017,7 +19012,7 @@
         <v>99</v>
       </c>
       <c r="B144" s="46" t="s">
-        <v>1831</v>
+        <v>1795</v>
       </c>
       <c r="C144" s="46"/>
       <c r="D144" s="46"/>
@@ -19039,23 +19034,23 @@
         <v>100</v>
       </c>
       <c r="B145" s="46" t="s">
-        <v>1832</v>
+        <v>1796</v>
       </c>
       <c r="C145" s="46"/>
       <c r="D145" s="46" t="s">
-        <v>1734</v>
+        <v>1698</v>
       </c>
       <c r="E145" s="46" t="s">
-        <v>1735</v>
+        <v>1699</v>
       </c>
       <c r="F145" s="46" t="s">
-        <v>1736</v>
+        <v>1700</v>
       </c>
       <c r="G145" s="46" t="s">
-        <v>1737</v>
+        <v>1701</v>
       </c>
       <c r="H145" s="46" t="s">
-        <v>1738</v>
+        <v>1702</v>
       </c>
       <c r="I145" s="2"/>
       <c r="J145" s="18"/>
@@ -19069,23 +19064,23 @@
         <v>100</v>
       </c>
       <c r="B146" s="46" t="s">
-        <v>1625</v>
+        <v>1589</v>
       </c>
       <c r="C146" s="46"/>
       <c r="D146" s="46" t="s">
-        <v>1739</v>
+        <v>1703</v>
       </c>
       <c r="E146" s="46" t="s">
-        <v>1740</v>
+        <v>1704</v>
       </c>
       <c r="F146" s="46" t="s">
-        <v>1741</v>
+        <v>1705</v>
       </c>
       <c r="G146" s="46" t="s">
-        <v>1742</v>
+        <v>1706</v>
       </c>
       <c r="H146" s="46" t="s">
-        <v>1541</v>
+        <v>1505</v>
       </c>
       <c r="I146" s="2"/>
       <c r="J146" s="18"/>
@@ -19099,23 +19094,23 @@
         <v>100</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1833</v>
+        <v>1797</v>
       </c>
       <c r="C147" s="46"/>
       <c r="D147" s="46" t="s">
-        <v>1743</v>
+        <v>1707</v>
       </c>
       <c r="E147" s="46" t="s">
-        <v>1744</v>
+        <v>1708</v>
       </c>
       <c r="F147" s="46" t="s">
-        <v>1745</v>
+        <v>1709</v>
       </c>
       <c r="G147" s="46" t="s">
-        <v>1746</v>
+        <v>1710</v>
       </c>
       <c r="H147" s="46" t="s">
-        <v>1747</v>
+        <v>1711</v>
       </c>
       <c r="I147" s="2"/>
       <c r="J147" s="18"/>
@@ -19129,7 +19124,7 @@
         <v>99</v>
       </c>
       <c r="B148" s="46" t="s">
-        <v>1834</v>
+        <v>1798</v>
       </c>
       <c r="C148" s="46"/>
       <c r="D148" s="46"/>
@@ -19151,23 +19146,23 @@
         <v>100</v>
       </c>
       <c r="B149" s="46" t="s">
-        <v>1832</v>
+        <v>1796</v>
       </c>
       <c r="C149" s="46"/>
       <c r="D149" s="46" t="s">
-        <v>1748</v>
+        <v>1712</v>
       </c>
       <c r="E149" s="46" t="s">
-        <v>1749</v>
+        <v>1713</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>1750</v>
+        <v>1714</v>
       </c>
       <c r="G149" s="46" t="s">
-        <v>1751</v>
+        <v>1715</v>
       </c>
       <c r="H149" s="46" t="s">
-        <v>1752</v>
+        <v>1716</v>
       </c>
       <c r="I149" s="2"/>
       <c r="J149" s="18"/>
@@ -19181,23 +19176,23 @@
         <v>100</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1835</v>
+        <v>1799</v>
       </c>
       <c r="C150" s="46"/>
       <c r="D150" s="46" t="s">
-        <v>1753</v>
+        <v>1717</v>
       </c>
       <c r="E150" s="46" t="s">
-        <v>1754</v>
+        <v>1718</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>1755</v>
+        <v>1719</v>
       </c>
       <c r="G150" s="46" t="s">
-        <v>1756</v>
+        <v>1720</v>
       </c>
       <c r="H150" s="46" t="s">
-        <v>1757</v>
+        <v>1721</v>
       </c>
       <c r="I150" s="2"/>
       <c r="J150" s="18"/>
@@ -19211,23 +19206,23 @@
         <v>100</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1836</v>
+        <v>1800</v>
       </c>
       <c r="C151" s="46"/>
       <c r="D151" s="46" t="s">
-        <v>1758</v>
+        <v>1722</v>
       </c>
       <c r="E151" s="46" t="s">
-        <v>1759</v>
+        <v>1723</v>
       </c>
       <c r="F151" s="46" t="s">
-        <v>1760</v>
+        <v>1724</v>
       </c>
       <c r="G151" s="46" t="s">
-        <v>1761</v>
+        <v>1725</v>
       </c>
       <c r="H151" s="46" t="s">
-        <v>1762</v>
+        <v>1726</v>
       </c>
       <c r="I151" s="2"/>
       <c r="J151" s="18"/>
@@ -19241,7 +19236,7 @@
         <v>99</v>
       </c>
       <c r="B152" s="46" t="s">
-        <v>1837</v>
+        <v>1801</v>
       </c>
       <c r="C152" s="46"/>
       <c r="D152" s="46"/>
@@ -19263,23 +19258,23 @@
         <v>100</v>
       </c>
       <c r="B153" s="46" t="s">
-        <v>1838</v>
+        <v>1802</v>
       </c>
       <c r="C153" s="46"/>
       <c r="D153" s="46" t="s">
-        <v>1763</v>
+        <v>1727</v>
       </c>
       <c r="E153" s="46" t="s">
-        <v>1764</v>
+        <v>1728</v>
       </c>
       <c r="F153" s="46" t="s">
-        <v>1765</v>
+        <v>1729</v>
       </c>
       <c r="G153" s="46" t="s">
-        <v>1766</v>
+        <v>1730</v>
       </c>
       <c r="H153" s="46" t="s">
-        <v>1767</v>
+        <v>1731</v>
       </c>
       <c r="I153" s="2"/>
       <c r="J153" s="18"/>
@@ -19293,23 +19288,23 @@
         <v>100</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1839</v>
+        <v>1803</v>
       </c>
       <c r="C154" s="46"/>
       <c r="D154" s="46" t="s">
-        <v>1768</v>
+        <v>1732</v>
       </c>
       <c r="E154" s="46" t="s">
-        <v>1769</v>
+        <v>1733</v>
       </c>
       <c r="F154" s="46" t="s">
-        <v>1770</v>
+        <v>1734</v>
       </c>
       <c r="G154" s="46" t="s">
-        <v>1771</v>
+        <v>1735</v>
       </c>
       <c r="H154" s="46" t="s">
-        <v>1772</v>
+        <v>1736</v>
       </c>
       <c r="I154" s="2"/>
       <c r="J154" s="18"/>
@@ -19323,23 +19318,23 @@
         <v>100</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1840</v>
+        <v>1804</v>
       </c>
       <c r="C155" s="46"/>
       <c r="D155" s="46" t="s">
-        <v>1773</v>
+        <v>1737</v>
       </c>
       <c r="E155" s="46" t="s">
-        <v>1774</v>
+        <v>1738</v>
       </c>
       <c r="F155" s="46" t="s">
-        <v>1775</v>
+        <v>1739</v>
       </c>
       <c r="G155" s="46" t="s">
-        <v>1776</v>
+        <v>1740</v>
       </c>
       <c r="H155" s="46" t="s">
-        <v>1777</v>
+        <v>1741</v>
       </c>
       <c r="I155" s="2"/>
       <c r="J155" s="18"/>
@@ -19353,23 +19348,23 @@
         <v>100</v>
       </c>
       <c r="B156" s="46" t="s">
-        <v>1841</v>
+        <v>1805</v>
       </c>
       <c r="C156" s="46"/>
       <c r="D156" s="46" t="s">
-        <v>1778</v>
+        <v>1742</v>
       </c>
       <c r="E156" s="46" t="s">
-        <v>1596</v>
+        <v>1560</v>
       </c>
       <c r="F156" s="46" t="s">
-        <v>1779</v>
+        <v>1743</v>
       </c>
       <c r="G156" s="46" t="s">
-        <v>1780</v>
+        <v>1744</v>
       </c>
       <c r="H156" s="46" t="s">
-        <v>1781</v>
+        <v>1745</v>
       </c>
       <c r="I156" s="2"/>
       <c r="J156" s="18"/>
@@ -19383,7 +19378,7 @@
         <v>99</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1848</v>
+        <v>1812</v>
       </c>
       <c r="C157" s="46"/>
       <c r="D157" s="2"/>
@@ -19405,23 +19400,23 @@
         <v>100</v>
       </c>
       <c r="B158" s="46" t="s">
-        <v>1842</v>
+        <v>1806</v>
       </c>
       <c r="C158" s="46"/>
       <c r="D158" s="46" t="s">
-        <v>1782</v>
+        <v>1746</v>
       </c>
       <c r="E158" s="46" t="s">
-        <v>1783</v>
+        <v>1747</v>
       </c>
       <c r="F158" s="46" t="s">
-        <v>1784</v>
+        <v>1748</v>
       </c>
       <c r="G158" s="46" t="s">
-        <v>1785</v>
+        <v>1749</v>
       </c>
       <c r="H158" s="46" t="s">
-        <v>1786</v>
+        <v>1750</v>
       </c>
       <c r="I158" s="2"/>
       <c r="J158" s="18"/>
@@ -19435,23 +19430,23 @@
         <v>100</v>
       </c>
       <c r="B159" s="46" t="s">
-        <v>1843</v>
+        <v>1807</v>
       </c>
       <c r="C159" s="46"/>
       <c r="D159" s="46" t="s">
-        <v>1787</v>
+        <v>1751</v>
       </c>
       <c r="E159" s="46" t="s">
-        <v>1788</v>
+        <v>1752</v>
       </c>
       <c r="F159" s="46" t="s">
-        <v>1789</v>
+        <v>1753</v>
       </c>
       <c r="G159" s="46" t="s">
-        <v>1790</v>
+        <v>1754</v>
       </c>
       <c r="H159" s="46" t="s">
-        <v>1791</v>
+        <v>1755</v>
       </c>
       <c r="I159" s="2"/>
       <c r="J159" s="18"/>
@@ -19465,7 +19460,7 @@
         <v>99</v>
       </c>
       <c r="B160" s="46" t="s">
-        <v>1844</v>
+        <v>1808</v>
       </c>
       <c r="C160" s="46"/>
       <c r="D160" s="46"/>
@@ -19487,23 +19482,23 @@
         <v>100</v>
       </c>
       <c r="B161" s="46" t="s">
-        <v>1845</v>
+        <v>1809</v>
       </c>
       <c r="C161" s="46"/>
       <c r="D161" s="46" t="s">
-        <v>1792</v>
+        <v>1756</v>
       </c>
       <c r="E161" s="46" t="s">
-        <v>1793</v>
+        <v>1757</v>
       </c>
       <c r="F161" s="46" t="s">
-        <v>1794</v>
+        <v>1758</v>
       </c>
       <c r="G161" s="46" t="s">
-        <v>1795</v>
+        <v>1759</v>
       </c>
       <c r="H161" s="46" t="s">
-        <v>1796</v>
+        <v>1760</v>
       </c>
       <c r="I161" s="2"/>
       <c r="J161" s="18"/>
@@ -19517,23 +19512,23 @@
         <v>100</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1846</v>
+        <v>1810</v>
       </c>
       <c r="C162" s="46"/>
       <c r="D162" s="46" t="s">
-        <v>1797</v>
+        <v>1761</v>
       </c>
       <c r="E162" s="46" t="s">
-        <v>1798</v>
+        <v>1762</v>
       </c>
       <c r="F162" s="46" t="s">
-        <v>1799</v>
+        <v>1763</v>
       </c>
       <c r="G162" s="46" t="s">
-        <v>1800</v>
+        <v>1764</v>
       </c>
       <c r="H162" s="46" t="s">
-        <v>1801</v>
+        <v>1765</v>
       </c>
       <c r="I162" s="2"/>
       <c r="J162" s="18"/>
@@ -19547,23 +19542,23 @@
         <v>100</v>
       </c>
       <c r="B163" s="46" t="s">
-        <v>1847</v>
+        <v>1811</v>
       </c>
       <c r="C163" s="46"/>
       <c r="D163" s="46" t="s">
-        <v>1802</v>
+        <v>1766</v>
       </c>
       <c r="E163" s="46" t="s">
-        <v>1803</v>
+        <v>1767</v>
       </c>
       <c r="F163" s="46" t="s">
-        <v>1804</v>
+        <v>1768</v>
       </c>
       <c r="G163" s="46" t="s">
-        <v>1805</v>
+        <v>1769</v>
       </c>
       <c r="H163" s="46" t="s">
-        <v>1806</v>
+        <v>1770</v>
       </c>
       <c r="I163" s="2"/>
       <c r="J163" s="18"/>
@@ -19577,7 +19572,7 @@
         <v>99</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1849</v>
+        <v>1813</v>
       </c>
       <c r="C164" s="46"/>
       <c r="D164" s="46"/>
@@ -19599,23 +19594,23 @@
         <v>100</v>
       </c>
       <c r="B165" s="46" t="s">
-        <v>1850</v>
+        <v>1814</v>
       </c>
       <c r="C165" s="46"/>
       <c r="D165" s="46" t="s">
-        <v>1807</v>
+        <v>1771</v>
       </c>
       <c r="E165" s="46" t="s">
-        <v>1808</v>
+        <v>1772</v>
       </c>
       <c r="F165" s="46" t="s">
-        <v>1809</v>
+        <v>1773</v>
       </c>
       <c r="G165" s="46" t="s">
-        <v>1810</v>
+        <v>1774</v>
       </c>
       <c r="H165" s="46" t="s">
-        <v>1811</v>
+        <v>1775</v>
       </c>
       <c r="I165" s="2"/>
       <c r="J165" s="18"/>
@@ -19629,23 +19624,23 @@
         <v>100</v>
       </c>
       <c r="B166" s="46" t="s">
-        <v>1851</v>
+        <v>1815</v>
       </c>
       <c r="C166" s="46"/>
       <c r="D166" s="46" t="s">
-        <v>1812</v>
+        <v>1776</v>
       </c>
       <c r="E166" s="46" t="s">
-        <v>1813</v>
+        <v>1777</v>
       </c>
       <c r="F166" s="46" t="s">
-        <v>1814</v>
+        <v>1778</v>
       </c>
       <c r="G166" s="46" t="s">
-        <v>1815</v>
+        <v>1779</v>
       </c>
       <c r="H166" s="46" t="s">
-        <v>1816</v>
+        <v>1780</v>
       </c>
       <c r="I166" s="2"/>
       <c r="J166" s="18"/>
@@ -19659,23 +19654,23 @@
         <v>100</v>
       </c>
       <c r="B167" s="46" t="s">
-        <v>1852</v>
+        <v>1816</v>
       </c>
       <c r="C167" s="46"/>
       <c r="D167" s="46" t="s">
-        <v>1817</v>
+        <v>1781</v>
       </c>
       <c r="E167" s="46" t="s">
-        <v>1818</v>
+        <v>1782</v>
       </c>
       <c r="F167" s="46" t="s">
-        <v>1819</v>
+        <v>1783</v>
       </c>
       <c r="G167" s="46" t="s">
-        <v>1820</v>
+        <v>1784</v>
       </c>
       <c r="H167" s="46" t="s">
-        <v>1797</v>
+        <v>1761</v>
       </c>
       <c r="I167" s="2"/>
       <c r="J167" s="18"/>
@@ -19689,23 +19684,23 @@
         <v>100</v>
       </c>
       <c r="B168" s="46" t="s">
-        <v>1853</v>
+        <v>1817</v>
       </c>
       <c r="C168" s="46"/>
       <c r="D168" s="46" t="s">
-        <v>1821</v>
+        <v>1785</v>
       </c>
       <c r="E168" s="46" t="s">
-        <v>1822</v>
+        <v>1786</v>
       </c>
       <c r="F168" s="46" t="s">
-        <v>1823</v>
+        <v>1787</v>
       </c>
       <c r="G168" s="46" t="s">
-        <v>1824</v>
+        <v>1788</v>
       </c>
       <c r="H168" s="46" t="s">
-        <v>1825</v>
+        <v>1789</v>
       </c>
       <c r="I168" s="2"/>
       <c r="J168" s="18"/>
@@ -19719,23 +19714,23 @@
         <v>100</v>
       </c>
       <c r="B169" s="46" t="s">
-        <v>1854</v>
+        <v>1818</v>
       </c>
       <c r="C169" s="46"/>
       <c r="D169" s="46" t="s">
-        <v>1826</v>
+        <v>1790</v>
       </c>
       <c r="E169" s="46" t="s">
-        <v>1827</v>
+        <v>1791</v>
       </c>
       <c r="F169" s="46" t="s">
-        <v>1828</v>
+        <v>1792</v>
       </c>
       <c r="G169" s="46" t="s">
-        <v>1829</v>
+        <v>1793</v>
       </c>
       <c r="H169" s="46" t="s">
-        <v>1830</v>
+        <v>1794</v>
       </c>
       <c r="I169" s="2"/>
       <c r="J169" s="18"/>
@@ -20469,23 +20464,23 @@
         <v>98</v>
       </c>
       <c r="B190" s="61" t="s">
-        <v>1357</v>
+        <v>1321</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="44" t="s">
-        <v>1367</v>
+        <v>1331</v>
       </c>
       <c r="E190" s="44" t="s">
-        <v>1368</v>
+        <v>1332</v>
       </c>
       <c r="F190" s="44" t="s">
-        <v>1369</v>
+        <v>1333</v>
       </c>
       <c r="G190" s="44" t="s">
-        <v>1370</v>
+        <v>1334</v>
       </c>
       <c r="H190" s="44" t="s">
-        <v>1371</v>
+        <v>1335</v>
       </c>
       <c r="I190" s="2"/>
       <c r="J190" s="18" t="s">
@@ -20503,23 +20498,23 @@
         <v>98</v>
       </c>
       <c r="B191" s="45" t="s">
-        <v>1358</v>
+        <v>1322</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="45" t="s">
-        <v>1372</v>
+        <v>1336</v>
       </c>
       <c r="E191" s="45" t="s">
-        <v>1373</v>
+        <v>1337</v>
       </c>
       <c r="F191" s="45" t="s">
-        <v>1374</v>
+        <v>1338</v>
       </c>
       <c r="G191" s="45" t="s">
-        <v>1375</v>
+        <v>1339</v>
       </c>
       <c r="H191" s="45" t="s">
-        <v>1376</v>
+        <v>1340</v>
       </c>
       <c r="I191" s="2"/>
       <c r="J191" s="18" t="s">
@@ -20537,23 +20532,23 @@
         <v>98</v>
       </c>
       <c r="B192" s="44" t="s">
-        <v>1359</v>
+        <v>1323</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="44" t="s">
-        <v>1377</v>
+        <v>1341</v>
       </c>
       <c r="E192" s="44" t="s">
-        <v>1378</v>
+        <v>1342</v>
       </c>
       <c r="F192" s="44" t="s">
-        <v>1379</v>
+        <v>1343</v>
       </c>
       <c r="G192" s="44" t="s">
-        <v>1380</v>
+        <v>1344</v>
       </c>
       <c r="H192" s="44" t="s">
-        <v>1381</v>
+        <v>1345</v>
       </c>
       <c r="I192" s="2"/>
       <c r="J192" s="18" t="s">
@@ -20571,23 +20566,23 @@
         <v>98</v>
       </c>
       <c r="B193" s="45" t="s">
-        <v>1360</v>
+        <v>1324</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="45" t="s">
-        <v>1382</v>
+        <v>1346</v>
       </c>
       <c r="E193" s="45" t="s">
-        <v>1383</v>
+        <v>1347</v>
       </c>
       <c r="F193" s="45" t="s">
-        <v>1384</v>
+        <v>1348</v>
       </c>
       <c r="G193" s="45" t="s">
-        <v>1385</v>
+        <v>1349</v>
       </c>
       <c r="H193" s="45" t="s">
-        <v>1386</v>
+        <v>1350</v>
       </c>
       <c r="I193" s="2"/>
       <c r="J193" s="18" t="s">
@@ -20605,23 +20600,23 @@
         <v>98</v>
       </c>
       <c r="B194" s="44" t="s">
-        <v>1361</v>
+        <v>1325</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="44" t="s">
-        <v>1387</v>
+        <v>1351</v>
       </c>
       <c r="E194" s="44" t="s">
-        <v>1388</v>
+        <v>1352</v>
       </c>
       <c r="F194" s="44" t="s">
-        <v>1389</v>
+        <v>1353</v>
       </c>
       <c r="G194" s="44" t="s">
-        <v>1390</v>
+        <v>1354</v>
       </c>
       <c r="H194" s="44" t="s">
-        <v>1391</v>
+        <v>1355</v>
       </c>
       <c r="I194" s="2"/>
       <c r="J194" s="18" t="s">
@@ -20639,23 +20634,23 @@
         <v>98</v>
       </c>
       <c r="B195" s="45" t="s">
-        <v>1362</v>
+        <v>1326</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="45" t="s">
-        <v>1392</v>
+        <v>1356</v>
       </c>
       <c r="E195" s="45" t="s">
-        <v>1393</v>
+        <v>1357</v>
       </c>
       <c r="F195" s="45" t="s">
-        <v>1394</v>
+        <v>1358</v>
       </c>
       <c r="G195" s="45" t="s">
-        <v>1395</v>
+        <v>1359</v>
       </c>
       <c r="H195" s="45" t="s">
-        <v>1396</v>
+        <v>1360</v>
       </c>
       <c r="I195" s="2"/>
       <c r="J195" s="18" t="s">
@@ -20673,23 +20668,23 @@
         <v>98</v>
       </c>
       <c r="B196" s="44" t="s">
-        <v>1363</v>
+        <v>1327</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="44" t="s">
-        <v>1397</v>
+        <v>1361</v>
       </c>
       <c r="E196" s="44" t="s">
-        <v>1398</v>
+        <v>1362</v>
       </c>
       <c r="F196" s="44" t="s">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="G196" s="44" t="s">
-        <v>1400</v>
+        <v>1364</v>
       </c>
       <c r="H196" s="44" t="s">
-        <v>1401</v>
+        <v>1365</v>
       </c>
       <c r="I196" s="2"/>
       <c r="J196" s="18" t="s">
@@ -20707,23 +20702,23 @@
         <v>98</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>1364</v>
+        <v>1328</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="45" t="s">
-        <v>1402</v>
+        <v>1366</v>
       </c>
       <c r="E197" s="45" t="s">
-        <v>1403</v>
+        <v>1367</v>
       </c>
       <c r="F197" s="45" t="s">
-        <v>1404</v>
+        <v>1368</v>
       </c>
       <c r="G197" s="45" t="s">
-        <v>1405</v>
+        <v>1369</v>
       </c>
       <c r="H197" s="45" t="s">
-        <v>1406</v>
+        <v>1370</v>
       </c>
       <c r="I197" s="2"/>
       <c r="J197" s="18" t="s">
@@ -20741,23 +20736,23 @@
         <v>98</v>
       </c>
       <c r="B198" s="44" t="s">
-        <v>1365</v>
+        <v>1329</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="44" t="s">
-        <v>1407</v>
+        <v>1371</v>
       </c>
       <c r="E198" s="44" t="s">
-        <v>1374</v>
+        <v>1338</v>
       </c>
       <c r="F198" s="44" t="s">
-        <v>1376</v>
+        <v>1340</v>
       </c>
       <c r="G198" s="44" t="s">
-        <v>1408</v>
+        <v>1372</v>
       </c>
       <c r="H198" s="44" t="s">
-        <v>1373</v>
+        <v>1337</v>
       </c>
       <c r="I198" s="2"/>
       <c r="J198" s="18" t="s">
@@ -20775,23 +20770,23 @@
         <v>98</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>1366</v>
+        <v>1330</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="45" t="s">
-        <v>1409</v>
+        <v>1373</v>
       </c>
       <c r="E199" s="45" t="s">
-        <v>1410</v>
+        <v>1374</v>
       </c>
       <c r="F199" s="45" t="s">
-        <v>1411</v>
+        <v>1375</v>
       </c>
       <c r="G199" s="45" t="s">
-        <v>1412</v>
+        <v>1376</v>
       </c>
       <c r="H199" s="45" t="s">
-        <v>1413</v>
+        <v>1377</v>
       </c>
       <c r="I199" s="2"/>
       <c r="J199" s="18" t="s">
@@ -20809,7 +20804,7 @@
         <v>99</v>
       </c>
       <c r="B200" s="29" t="s">
-        <v>1287</v>
+        <v>1254</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>786</v>
@@ -20833,23 +20828,23 @@
         <v>100</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1288</v>
+        <v>1255</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="30" t="s">
-        <v>988</v>
+        <v>959</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>989</v>
+        <v>960</v>
       </c>
       <c r="F201" s="30" t="s">
-        <v>990</v>
+        <v>961</v>
       </c>
       <c r="G201" s="30" t="s">
-        <v>991</v>
+        <v>962</v>
       </c>
       <c r="H201" s="30" t="s">
-        <v>992</v>
+        <v>963</v>
       </c>
       <c r="I201" s="2"/>
       <c r="J201" s="18"/>
@@ -20863,23 +20858,23 @@
         <v>100</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>1289</v>
+        <v>1256</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="31" t="s">
-        <v>993</v>
+        <v>964</v>
       </c>
       <c r="E202" s="31" t="s">
-        <v>994</v>
+        <v>965</v>
       </c>
       <c r="F202" s="31" t="s">
-        <v>995</v>
+        <v>966</v>
       </c>
       <c r="G202" s="31" t="s">
-        <v>996</v>
+        <v>967</v>
       </c>
       <c r="H202" s="31" t="s">
-        <v>997</v>
+        <v>968</v>
       </c>
       <c r="I202" s="2"/>
       <c r="J202" s="18"/>
@@ -20893,7 +20888,7 @@
         <v>99</v>
       </c>
       <c r="B203" s="29" t="s">
-        <v>1290</v>
+        <v>1257</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>786</v>
@@ -20917,23 +20912,23 @@
         <v>100</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1291</v>
+        <v>1258</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="30" t="s">
-        <v>998</v>
+        <v>969</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>999</v>
+        <v>970</v>
       </c>
       <c r="F204" s="30" t="s">
-        <v>1000</v>
+        <v>971</v>
       </c>
       <c r="G204" s="30" t="s">
-        <v>1001</v>
+        <v>972</v>
       </c>
       <c r="H204" s="30" t="s">
-        <v>1002</v>
+        <v>973</v>
       </c>
       <c r="I204" s="2"/>
       <c r="J204" s="18"/>
@@ -20947,23 +20942,23 @@
         <v>100</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1292</v>
+        <v>1259</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="31" t="s">
-        <v>1003</v>
+        <v>974</v>
       </c>
       <c r="E205" s="31" t="s">
-        <v>1004</v>
+        <v>975</v>
       </c>
       <c r="F205" s="31" t="s">
-        <v>1005</v>
+        <v>976</v>
       </c>
       <c r="G205" s="31" t="s">
-        <v>1006</v>
+        <v>977</v>
       </c>
       <c r="H205" s="31" t="s">
-        <v>1007</v>
+        <v>978</v>
       </c>
       <c r="I205" s="2"/>
       <c r="J205" s="18"/>
@@ -20977,7 +20972,7 @@
         <v>99</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>1293</v>
+        <v>1260</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>786</v>
@@ -21001,23 +20996,23 @@
         <v>100</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1294</v>
+        <v>1261</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="30" t="s">
-        <v>1008</v>
+        <v>979</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>1009</v>
+        <v>980</v>
       </c>
       <c r="F207" s="30" t="s">
-        <v>1010</v>
+        <v>981</v>
       </c>
       <c r="G207" s="30" t="s">
-        <v>1011</v>
+        <v>982</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>1012</v>
+        <v>983</v>
       </c>
       <c r="I207" s="2"/>
       <c r="J207" s="18"/>
@@ -21031,23 +21026,23 @@
         <v>100</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1295</v>
+        <v>1262</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="31" t="s">
-        <v>1013</v>
+        <v>984</v>
       </c>
       <c r="E208" s="31" t="s">
-        <v>1014</v>
+        <v>985</v>
       </c>
       <c r="F208" s="31" t="s">
-        <v>1015</v>
+        <v>986</v>
       </c>
       <c r="G208" s="31" t="s">
-        <v>1016</v>
+        <v>987</v>
       </c>
       <c r="H208" s="31" t="s">
-        <v>1017</v>
+        <v>988</v>
       </c>
       <c r="I208" s="2"/>
       <c r="J208" s="18"/>
@@ -21061,23 +21056,23 @@
         <v>100</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1296</v>
+        <v>1263</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="30" t="s">
-        <v>1018</v>
+        <v>989</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>1019</v>
+        <v>990</v>
       </c>
       <c r="F209" s="30" t="s">
-        <v>1020</v>
+        <v>991</v>
       </c>
       <c r="G209" s="30" t="s">
-        <v>1021</v>
+        <v>992</v>
       </c>
       <c r="H209" s="30" t="s">
-        <v>1022</v>
+        <v>993</v>
       </c>
       <c r="I209" s="2"/>
       <c r="J209" s="18"/>
@@ -21091,7 +21086,7 @@
         <v>99</v>
       </c>
       <c r="B210" s="29" t="s">
-        <v>2360</v>
+        <v>2324</v>
       </c>
       <c r="C210" s="58"/>
       <c r="D210" s="2"/>
@@ -21113,23 +21108,23 @@
         <v>100</v>
       </c>
       <c r="B211" s="29" t="s">
-        <v>2361</v>
+        <v>2325</v>
       </c>
       <c r="C211" s="58"/>
       <c r="D211" s="30" t="s">
-        <v>2292</v>
+        <v>2256</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>2293</v>
+        <v>2257</v>
       </c>
       <c r="F211" s="30" t="s">
-        <v>2294</v>
+        <v>2258</v>
       </c>
       <c r="G211" s="30" t="s">
-        <v>2295</v>
+        <v>2259</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>2296</v>
+        <v>2260</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
@@ -21143,23 +21138,23 @@
         <v>100</v>
       </c>
       <c r="B212" s="59" t="s">
-        <v>2362</v>
+        <v>2326</v>
       </c>
       <c r="C212" s="60"/>
       <c r="D212" s="31" t="s">
-        <v>2297</v>
+        <v>2261</v>
       </c>
       <c r="E212" s="31" t="s">
-        <v>2298</v>
+        <v>2262</v>
       </c>
       <c r="F212" s="31" t="s">
-        <v>2299</v>
+        <v>2263</v>
       </c>
       <c r="G212" s="31" t="s">
-        <v>2300</v>
+        <v>2264</v>
       </c>
       <c r="H212" s="31" t="s">
-        <v>2301</v>
+        <v>2265</v>
       </c>
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
@@ -21173,23 +21168,23 @@
         <v>100</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>2364</v>
+        <v>2328</v>
       </c>
       <c r="C213" s="58"/>
       <c r="D213" s="30" t="s">
-        <v>2302</v>
+        <v>2266</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>2303</v>
+        <v>2267</v>
       </c>
       <c r="F213" s="30" t="s">
-        <v>2304</v>
+        <v>2268</v>
       </c>
       <c r="G213" s="30" t="s">
-        <v>2305</v>
+        <v>2269</v>
       </c>
       <c r="H213" s="30" t="s">
-        <v>2306</v>
+        <v>2270</v>
       </c>
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
@@ -21203,23 +21198,23 @@
         <v>100</v>
       </c>
       <c r="B214" s="59" t="s">
-        <v>2363</v>
+        <v>2327</v>
       </c>
       <c r="C214" s="60"/>
       <c r="D214" s="31" t="s">
-        <v>2307</v>
+        <v>2271</v>
       </c>
       <c r="E214" s="31" t="s">
-        <v>2308</v>
+        <v>2272</v>
       </c>
       <c r="F214" s="31" t="s">
-        <v>2309</v>
+        <v>2273</v>
       </c>
       <c r="G214" s="31" t="s">
-        <v>2310</v>
+        <v>2274</v>
       </c>
       <c r="H214" s="31" t="s">
-        <v>2311</v>
+        <v>2275</v>
       </c>
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
@@ -21233,10 +21228,10 @@
         <v>99</v>
       </c>
       <c r="B215" s="29" t="s">
-        <v>2365</v>
+        <v>2329</v>
       </c>
       <c r="C215" s="58" t="s">
-        <v>2312</v>
+        <v>2276</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -21257,23 +21252,23 @@
         <v>100</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>2366</v>
+        <v>2330</v>
       </c>
       <c r="C216" s="58"/>
       <c r="D216" s="30" t="s">
-        <v>2313</v>
+        <v>2277</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>2314</v>
+        <v>2278</v>
       </c>
       <c r="F216" s="30" t="s">
-        <v>2315</v>
+        <v>2279</v>
       </c>
       <c r="G216" s="30" t="s">
-        <v>2316</v>
+        <v>2280</v>
       </c>
       <c r="H216" s="30" t="s">
-        <v>2317</v>
+        <v>2281</v>
       </c>
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
@@ -21287,23 +21282,23 @@
         <v>100</v>
       </c>
       <c r="B217" s="59" t="s">
-        <v>2367</v>
+        <v>2331</v>
       </c>
       <c r="C217" s="60"/>
       <c r="D217" s="31" t="s">
-        <v>2318</v>
+        <v>2282</v>
       </c>
       <c r="E217" s="31" t="s">
-        <v>2319</v>
+        <v>2283</v>
       </c>
       <c r="F217" s="31" t="s">
-        <v>2320</v>
+        <v>2284</v>
       </c>
       <c r="G217" s="31" t="s">
-        <v>2321</v>
+        <v>2285</v>
       </c>
       <c r="H217" s="31" t="s">
-        <v>2322</v>
+        <v>2286</v>
       </c>
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
@@ -21317,23 +21312,23 @@
         <v>100</v>
       </c>
       <c r="B218" s="29" t="s">
-        <v>2368</v>
+        <v>2332</v>
       </c>
       <c r="C218" s="58"/>
       <c r="D218" s="30" t="s">
-        <v>2323</v>
+        <v>2287</v>
       </c>
       <c r="E218" s="30" t="s">
-        <v>2324</v>
+        <v>2288</v>
       </c>
       <c r="F218" s="30" t="s">
-        <v>2325</v>
+        <v>2289</v>
       </c>
       <c r="G218" s="30" t="s">
-        <v>2326</v>
+        <v>2290</v>
       </c>
       <c r="H218" s="30" t="s">
-        <v>2327</v>
+        <v>2291</v>
       </c>
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
@@ -21347,10 +21342,10 @@
         <v>99</v>
       </c>
       <c r="B219" s="59" t="s">
-        <v>2375</v>
+        <v>2339</v>
       </c>
       <c r="C219" s="60" t="s">
-        <v>2328</v>
+        <v>2292</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -21371,23 +21366,23 @@
         <v>100</v>
       </c>
       <c r="B220" s="59" t="s">
-        <v>2369</v>
+        <v>2333</v>
       </c>
       <c r="C220" s="60"/>
       <c r="D220" s="31" t="s">
-        <v>2329</v>
+        <v>2293</v>
       </c>
       <c r="E220" s="31" t="s">
-        <v>2330</v>
+        <v>2294</v>
       </c>
       <c r="F220" s="31" t="s">
-        <v>2331</v>
+        <v>2295</v>
       </c>
       <c r="G220" s="31" t="s">
-        <v>2332</v>
+        <v>2296</v>
       </c>
       <c r="H220" s="31" t="s">
-        <v>2333</v>
+        <v>2297</v>
       </c>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
@@ -21401,23 +21396,23 @@
         <v>100</v>
       </c>
       <c r="B221" s="59" t="s">
-        <v>2376</v>
+        <v>2340</v>
       </c>
       <c r="C221" s="60"/>
       <c r="D221" s="30" t="s">
-        <v>2334</v>
+        <v>2298</v>
       </c>
       <c r="E221" s="30" t="s">
-        <v>2335</v>
+        <v>2299</v>
       </c>
       <c r="F221" s="30" t="s">
-        <v>2336</v>
+        <v>2300</v>
       </c>
       <c r="G221" s="30" t="s">
-        <v>2337</v>
+        <v>2301</v>
       </c>
       <c r="H221" s="30" t="s">
-        <v>2338</v>
+        <v>2302</v>
       </c>
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
@@ -21431,23 +21426,23 @@
         <v>100</v>
       </c>
       <c r="B222" s="59" t="s">
-        <v>2370</v>
+        <v>2334</v>
       </c>
       <c r="C222" s="60"/>
       <c r="D222" s="31" t="s">
-        <v>2339</v>
+        <v>2303</v>
       </c>
       <c r="E222" s="31" t="s">
-        <v>2340</v>
+        <v>2304</v>
       </c>
       <c r="F222" s="31" t="s">
-        <v>2341</v>
+        <v>2305</v>
       </c>
       <c r="G222" s="31" t="s">
-        <v>2342</v>
+        <v>2306</v>
       </c>
       <c r="H222" s="31" t="s">
-        <v>2343</v>
+        <v>2307</v>
       </c>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
@@ -21461,10 +21456,10 @@
         <v>99</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>2371</v>
+        <v>2335</v>
       </c>
       <c r="C223" s="58" t="s">
-        <v>2344</v>
+        <v>2308</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
@@ -21485,23 +21480,23 @@
         <v>100</v>
       </c>
       <c r="B224" s="29" t="s">
-        <v>2372</v>
+        <v>2336</v>
       </c>
       <c r="C224" s="58"/>
       <c r="D224" s="30" t="s">
-        <v>2345</v>
+        <v>2309</v>
       </c>
       <c r="E224" s="30" t="s">
-        <v>2346</v>
+        <v>2310</v>
       </c>
       <c r="F224" s="30" t="s">
-        <v>2347</v>
+        <v>2311</v>
       </c>
       <c r="G224" s="30" t="s">
-        <v>2348</v>
+        <v>2312</v>
       </c>
       <c r="H224" s="30" t="s">
-        <v>2349</v>
+        <v>2313</v>
       </c>
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
@@ -21515,23 +21510,23 @@
         <v>100</v>
       </c>
       <c r="B225" s="59" t="s">
-        <v>2373</v>
+        <v>2337</v>
       </c>
       <c r="C225" s="60"/>
       <c r="D225" s="31" t="s">
-        <v>2350</v>
+        <v>2314</v>
       </c>
       <c r="E225" s="31" t="s">
-        <v>2351</v>
+        <v>2315</v>
       </c>
       <c r="F225" s="31" t="s">
-        <v>2352</v>
+        <v>2316</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>2353</v>
+        <v>2317</v>
       </c>
       <c r="H225" s="31" t="s">
-        <v>2354</v>
+        <v>2318</v>
       </c>
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
@@ -21545,23 +21540,23 @@
         <v>100</v>
       </c>
       <c r="B226" s="29" t="s">
-        <v>2374</v>
+        <v>2338</v>
       </c>
       <c r="C226" s="58"/>
       <c r="D226" s="30" t="s">
-        <v>2355</v>
+        <v>2319</v>
       </c>
       <c r="E226" s="30" t="s">
-        <v>2356</v>
+        <v>2320</v>
       </c>
       <c r="F226" s="30" t="s">
-        <v>2357</v>
+        <v>2321</v>
       </c>
       <c r="G226" s="30" t="s">
-        <v>2358</v>
+        <v>2322</v>
       </c>
       <c r="H226" s="30" t="s">
-        <v>2359</v>
+        <v>2323</v>
       </c>
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
@@ -21693,13 +21688,13 @@
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="13" t="s">
-        <v>1025</v>
+        <v>996</v>
       </c>
       <c r="E231" s="13" t="s">
         <v>681</v>
       </c>
       <c r="F231" s="13" t="s">
-        <v>1026</v>
+        <v>997</v>
       </c>
       <c r="G231" s="13" t="s">
         <v>682</v>
@@ -22329,7 +22324,7 @@
         <v>781</v>
       </c>
       <c r="H253" s="13" t="s">
-        <v>2380</v>
+        <v>2344</v>
       </c>
       <c r="I253" s="2"/>
       <c r="J253" s="18"/>
@@ -22775,7 +22770,7 @@
         <v>98</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>1023</v>
+        <v>994</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2" t="s">
@@ -23027,7 +23022,7 @@
         <v>98</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>1024</v>
+        <v>995</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2" t="s">
@@ -23063,23 +23058,23 @@
         <v>98</v>
       </c>
       <c r="B274" s="40" t="s">
-        <v>1855</v>
+        <v>1819</v>
       </c>
       <c r="C274" s="41"/>
       <c r="D274" s="42" t="s">
-        <v>1856</v>
+        <v>1820</v>
       </c>
       <c r="E274" s="42" t="s">
-        <v>1857</v>
+        <v>1821</v>
       </c>
       <c r="F274" s="42" t="s">
-        <v>1858</v>
+        <v>1822</v>
       </c>
       <c r="G274" s="42" t="s">
-        <v>1859</v>
+        <v>1823</v>
       </c>
       <c r="H274" s="42" t="s">
-        <v>1860</v>
+        <v>1824</v>
       </c>
       <c r="I274" s="2"/>
       <c r="J274" s="18" t="s">
@@ -23097,23 +23092,23 @@
         <v>98</v>
       </c>
       <c r="B275" s="37" t="s">
-        <v>1861</v>
+        <v>1825</v>
       </c>
       <c r="C275" s="38"/>
       <c r="D275" s="39" t="s">
-        <v>1862</v>
+        <v>1826</v>
       </c>
       <c r="E275" s="39" t="s">
-        <v>1863</v>
+        <v>1827</v>
       </c>
       <c r="F275" s="39" t="s">
-        <v>1864</v>
+        <v>1828</v>
       </c>
       <c r="G275" s="39" t="s">
-        <v>1865</v>
+        <v>1829</v>
       </c>
       <c r="H275" s="39" t="s">
-        <v>1866</v>
+        <v>1830</v>
       </c>
       <c r="I275" s="2"/>
       <c r="J275" s="18" t="s">
@@ -23131,23 +23126,23 @@
         <v>98</v>
       </c>
       <c r="B276" s="40" t="s">
-        <v>1867</v>
+        <v>1831</v>
       </c>
       <c r="C276" s="41"/>
       <c r="D276" s="42" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="E276" s="42" t="s">
-        <v>1869</v>
+        <v>1833</v>
       </c>
       <c r="F276" s="42" t="s">
-        <v>1870</v>
+        <v>1834</v>
       </c>
       <c r="G276" s="42" t="s">
-        <v>1871</v>
+        <v>1835</v>
       </c>
       <c r="H276" s="42" t="s">
-        <v>1872</v>
+        <v>1836</v>
       </c>
       <c r="I276" s="2"/>
       <c r="J276" s="18" t="s">
@@ -23165,23 +23160,23 @@
         <v>98</v>
       </c>
       <c r="B277" s="37" t="s">
-        <v>1873</v>
+        <v>1837</v>
       </c>
       <c r="C277" s="38"/>
       <c r="D277" s="39" t="s">
-        <v>1874</v>
+        <v>1838</v>
       </c>
       <c r="E277" s="39" t="s">
-        <v>1875</v>
+        <v>1839</v>
       </c>
       <c r="F277" s="39" t="s">
-        <v>1876</v>
+        <v>1840</v>
       </c>
       <c r="G277" s="39" t="s">
-        <v>1877</v>
+        <v>1841</v>
       </c>
       <c r="H277" s="39" t="s">
-        <v>1878</v>
+        <v>1842</v>
       </c>
       <c r="I277" s="2"/>
       <c r="J277" s="18" t="s">
@@ -23199,23 +23194,23 @@
         <v>98</v>
       </c>
       <c r="B278" s="40" t="s">
-        <v>1879</v>
+        <v>1843</v>
       </c>
       <c r="C278" s="41"/>
       <c r="D278" s="42" t="s">
-        <v>1880</v>
+        <v>1844</v>
       </c>
       <c r="E278" s="42" t="s">
-        <v>1881</v>
+        <v>1845</v>
       </c>
       <c r="F278" s="42" t="s">
-        <v>1882</v>
+        <v>1846</v>
       </c>
       <c r="G278" s="42" t="s">
-        <v>1883</v>
+        <v>1847</v>
       </c>
       <c r="H278" s="42" t="s">
-        <v>1884</v>
+        <v>1848</v>
       </c>
       <c r="I278" s="2"/>
       <c r="J278" s="18" t="s">
@@ -23233,23 +23228,23 @@
         <v>98</v>
       </c>
       <c r="B279" s="37" t="s">
-        <v>1885</v>
+        <v>1849</v>
       </c>
       <c r="C279" s="38"/>
       <c r="D279" s="39" t="s">
-        <v>1886</v>
+        <v>1850</v>
       </c>
       <c r="E279" s="39" t="s">
-        <v>1887</v>
+        <v>1851</v>
       </c>
       <c r="F279" s="39" t="s">
-        <v>1888</v>
+        <v>1852</v>
       </c>
       <c r="G279" s="39" t="s">
-        <v>1889</v>
+        <v>1853</v>
       </c>
       <c r="H279" s="39" t="s">
-        <v>1890</v>
+        <v>1854</v>
       </c>
       <c r="I279" s="2"/>
       <c r="J279" s="18" t="s">
@@ -23267,23 +23262,23 @@
         <v>98</v>
       </c>
       <c r="B280" s="40" t="s">
-        <v>1891</v>
+        <v>1855</v>
       </c>
       <c r="C280" s="41"/>
       <c r="D280" s="42" t="s">
-        <v>1892</v>
+        <v>1856</v>
       </c>
       <c r="E280" s="42" t="s">
-        <v>1893</v>
+        <v>1857</v>
       </c>
       <c r="F280" s="42" t="s">
-        <v>1894</v>
+        <v>1858</v>
       </c>
       <c r="G280" s="42" t="s">
-        <v>1895</v>
+        <v>1859</v>
       </c>
       <c r="H280" s="42" t="s">
-        <v>1896</v>
+        <v>1860</v>
       </c>
       <c r="I280" s="2"/>
       <c r="J280" s="18" t="s">
@@ -23301,7 +23296,7 @@
         <v>99</v>
       </c>
       <c r="B281" s="49" t="s">
-        <v>2013</v>
+        <v>1977</v>
       </c>
       <c r="C281" s="50"/>
       <c r="D281" s="50"/>
@@ -23323,23 +23318,23 @@
         <v>100</v>
       </c>
       <c r="B282" s="37" t="s">
-        <v>1897</v>
+        <v>1861</v>
       </c>
       <c r="C282" s="51"/>
       <c r="D282" s="39" t="s">
-        <v>1898</v>
+        <v>1862</v>
       </c>
       <c r="E282" s="39" t="s">
-        <v>1899</v>
+        <v>1863</v>
       </c>
       <c r="F282" s="39" t="s">
-        <v>1900</v>
+        <v>1864</v>
       </c>
       <c r="G282" s="39" t="s">
-        <v>1901</v>
+        <v>1865</v>
       </c>
       <c r="H282" s="39" t="s">
-        <v>1902</v>
+        <v>1866</v>
       </c>
       <c r="I282" s="2"/>
       <c r="J282" s="18"/>
@@ -23353,23 +23348,23 @@
         <v>98</v>
       </c>
       <c r="B283" s="40" t="s">
-        <v>1903</v>
+        <v>1867</v>
       </c>
       <c r="C283" s="41"/>
       <c r="D283" s="42" t="s">
-        <v>1904</v>
+        <v>1868</v>
       </c>
       <c r="E283" s="42" t="s">
-        <v>1905</v>
+        <v>1869</v>
       </c>
       <c r="F283" s="42" t="s">
-        <v>1906</v>
+        <v>1870</v>
       </c>
       <c r="G283" s="42" t="s">
-        <v>1907</v>
+        <v>1871</v>
       </c>
       <c r="H283" s="42" t="s">
-        <v>1908</v>
+        <v>1872</v>
       </c>
       <c r="I283" s="2"/>
       <c r="J283" s="18" t="s">
@@ -23387,23 +23382,23 @@
         <v>98</v>
       </c>
       <c r="B284" s="37" t="s">
-        <v>1909</v>
+        <v>1873</v>
       </c>
       <c r="C284" s="38"/>
       <c r="D284" s="39" t="s">
-        <v>1910</v>
+        <v>1874</v>
       </c>
       <c r="E284" s="39" t="s">
-        <v>1911</v>
+        <v>1875</v>
       </c>
       <c r="F284" s="39" t="s">
-        <v>1912</v>
+        <v>1876</v>
       </c>
       <c r="G284" s="39" t="s">
-        <v>1913</v>
+        <v>1877</v>
       </c>
       <c r="H284" s="39" t="s">
-        <v>1914</v>
+        <v>1878</v>
       </c>
       <c r="I284" s="2"/>
       <c r="J284" s="18" t="s">
@@ -23421,23 +23416,23 @@
         <v>98</v>
       </c>
       <c r="B285" s="40" t="s">
-        <v>1915</v>
+        <v>1879</v>
       </c>
       <c r="C285" s="41"/>
       <c r="D285" s="42" t="s">
-        <v>1916</v>
+        <v>1880</v>
       </c>
       <c r="E285" s="42" t="s">
-        <v>1917</v>
+        <v>1881</v>
       </c>
       <c r="F285" s="42" t="s">
-        <v>1918</v>
+        <v>1882</v>
       </c>
       <c r="G285" s="42" t="s">
-        <v>1919</v>
+        <v>1883</v>
       </c>
       <c r="H285" s="42" t="s">
-        <v>1920</v>
+        <v>1884</v>
       </c>
       <c r="I285" s="2"/>
       <c r="J285" s="18" t="s">
@@ -23455,23 +23450,23 @@
         <v>98</v>
       </c>
       <c r="B286" s="37" t="s">
-        <v>1921</v>
+        <v>1885</v>
       </c>
       <c r="C286" s="38"/>
       <c r="D286" s="39" t="s">
-        <v>1922</v>
+        <v>1886</v>
       </c>
       <c r="E286" s="39" t="s">
-        <v>1923</v>
+        <v>1887</v>
       </c>
       <c r="F286" s="39" t="s">
-        <v>1924</v>
+        <v>1888</v>
       </c>
       <c r="G286" s="39" t="s">
-        <v>1925</v>
+        <v>1889</v>
       </c>
       <c r="H286" s="39" t="s">
-        <v>1926</v>
+        <v>1890</v>
       </c>
       <c r="I286" s="2"/>
       <c r="J286" s="18" t="s">
@@ -23489,23 +23484,23 @@
         <v>98</v>
       </c>
       <c r="B287" s="40" t="s">
-        <v>1927</v>
+        <v>1891</v>
       </c>
       <c r="C287" s="41"/>
       <c r="D287" s="42" t="s">
-        <v>1928</v>
+        <v>1892</v>
       </c>
       <c r="E287" s="42" t="s">
-        <v>1929</v>
+        <v>1893</v>
       </c>
       <c r="F287" s="42" t="s">
-        <v>1930</v>
+        <v>1894</v>
       </c>
       <c r="G287" s="42" t="s">
-        <v>1931</v>
+        <v>1895</v>
       </c>
       <c r="H287" s="42" t="s">
-        <v>1932</v>
+        <v>1896</v>
       </c>
       <c r="I287" s="2"/>
       <c r="J287" s="18" t="s">
@@ -23523,23 +23518,23 @@
         <v>98</v>
       </c>
       <c r="B288" s="37" t="s">
-        <v>1933</v>
+        <v>1897</v>
       </c>
       <c r="C288" s="38"/>
       <c r="D288" s="39" t="s">
-        <v>1934</v>
+        <v>1898</v>
       </c>
       <c r="E288" s="39" t="s">
-        <v>1935</v>
+        <v>1899</v>
       </c>
       <c r="F288" s="39" t="s">
-        <v>1936</v>
+        <v>1900</v>
       </c>
       <c r="G288" s="39" t="s">
-        <v>1937</v>
+        <v>1901</v>
       </c>
       <c r="H288" s="39" t="s">
-        <v>1938</v>
+        <v>1902</v>
       </c>
       <c r="I288" s="2"/>
       <c r="J288" s="18" t="s">
@@ -23557,7 +23552,7 @@
         <v>99</v>
       </c>
       <c r="B289" s="32" t="s">
-        <v>1315</v>
+        <v>1282</v>
       </c>
       <c r="C289" s="33"/>
       <c r="D289" s="33"/>
@@ -23579,23 +23574,23 @@
         <v>100</v>
       </c>
       <c r="B290" s="34" t="s">
-        <v>1250</v>
+        <v>1221</v>
       </c>
       <c r="C290" s="35"/>
       <c r="D290" s="36" t="s">
-        <v>1104</v>
+        <v>1075</v>
       </c>
       <c r="E290" s="36" t="s">
-        <v>1105</v>
+        <v>1076</v>
       </c>
       <c r="F290" s="36" t="s">
-        <v>1106</v>
+        <v>1077</v>
       </c>
       <c r="G290" s="36" t="s">
-        <v>1107</v>
+        <v>1078</v>
       </c>
       <c r="H290" s="36" t="s">
-        <v>1108</v>
+        <v>1079</v>
       </c>
       <c r="I290" s="2"/>
       <c r="J290" s="18"/>
@@ -23609,23 +23604,23 @@
         <v>100</v>
       </c>
       <c r="B291" s="37" t="s">
-        <v>1249</v>
+        <v>1220</v>
       </c>
       <c r="C291" s="38"/>
       <c r="D291" s="39" t="s">
-        <v>1109</v>
+        <v>1080</v>
       </c>
       <c r="E291" s="39" t="s">
-        <v>1110</v>
+        <v>1081</v>
       </c>
       <c r="F291" s="39" t="s">
-        <v>1111</v>
+        <v>1082</v>
       </c>
       <c r="G291" s="39" t="s">
-        <v>1112</v>
+        <v>1083</v>
       </c>
       <c r="H291" s="39" t="s">
-        <v>1113</v>
+        <v>1084</v>
       </c>
       <c r="I291" s="2"/>
       <c r="J291" s="18"/>
@@ -23639,23 +23634,23 @@
         <v>100</v>
       </c>
       <c r="B292" s="34" t="s">
-        <v>1251</v>
+        <v>1222</v>
       </c>
       <c r="C292" s="35"/>
       <c r="D292" s="36" t="s">
-        <v>1114</v>
+        <v>1085</v>
       </c>
       <c r="E292" s="36" t="s">
-        <v>1115</v>
+        <v>1086</v>
       </c>
       <c r="F292" s="36" t="s">
-        <v>1116</v>
+        <v>1087</v>
       </c>
       <c r="G292" s="36" t="s">
-        <v>1117</v>
+        <v>1088</v>
       </c>
       <c r="H292" s="36" t="s">
-        <v>1118</v>
+        <v>1089</v>
       </c>
       <c r="I292" s="2"/>
       <c r="J292" s="18"/>
@@ -23669,7 +23664,7 @@
         <v>99</v>
       </c>
       <c r="B293" s="32" t="s">
-        <v>1316</v>
+        <v>1283</v>
       </c>
       <c r="C293" s="33"/>
       <c r="D293" s="33"/>
@@ -23691,23 +23686,23 @@
         <v>100</v>
       </c>
       <c r="B294" s="37" t="s">
-        <v>1252</v>
+        <v>1223</v>
       </c>
       <c r="C294" s="38"/>
       <c r="D294" s="39" t="s">
-        <v>1119</v>
+        <v>1090</v>
       </c>
       <c r="E294" s="39" t="s">
-        <v>1120</v>
+        <v>1091</v>
       </c>
       <c r="F294" s="39" t="s">
-        <v>1121</v>
+        <v>1092</v>
       </c>
       <c r="G294" s="39" t="s">
-        <v>1122</v>
+        <v>1093</v>
       </c>
       <c r="H294" s="39" t="s">
-        <v>1123</v>
+        <v>1094</v>
       </c>
       <c r="I294" s="2"/>
       <c r="J294" s="18"/>
@@ -23721,7 +23716,7 @@
         <v>99</v>
       </c>
       <c r="B295" s="32" t="s">
-        <v>1124</v>
+        <v>1095</v>
       </c>
       <c r="C295" s="33"/>
       <c r="D295" s="33"/>
@@ -23743,23 +23738,23 @@
         <v>100</v>
       </c>
       <c r="B296" s="34" t="s">
-        <v>1253</v>
+        <v>1224</v>
       </c>
       <c r="C296" s="35"/>
       <c r="D296" s="36" t="s">
-        <v>1125</v>
+        <v>1096</v>
       </c>
       <c r="E296" s="36" t="s">
-        <v>1126</v>
+        <v>1097</v>
       </c>
       <c r="F296" s="36" t="s">
-        <v>1127</v>
+        <v>1098</v>
       </c>
       <c r="G296" s="36" t="s">
-        <v>1128</v>
+        <v>1099</v>
       </c>
       <c r="H296" s="36" t="s">
-        <v>1129</v>
+        <v>1100</v>
       </c>
       <c r="I296" s="2"/>
       <c r="J296" s="18"/>
@@ -23773,7 +23768,7 @@
         <v>99</v>
       </c>
       <c r="B297" s="32" t="s">
-        <v>1130</v>
+        <v>1101</v>
       </c>
       <c r="C297" s="33"/>
       <c r="D297" s="33"/>
@@ -23795,23 +23790,23 @@
         <v>100</v>
       </c>
       <c r="B298" s="37" t="s">
-        <v>1254</v>
+        <v>1225</v>
       </c>
       <c r="C298" s="38"/>
       <c r="D298" s="39" t="s">
-        <v>1131</v>
+        <v>1102</v>
       </c>
       <c r="E298" s="39" t="s">
-        <v>1132</v>
+        <v>1103</v>
       </c>
       <c r="F298" s="39" t="s">
-        <v>1133</v>
+        <v>1104</v>
       </c>
       <c r="G298" s="39" t="s">
-        <v>1134</v>
+        <v>1105</v>
       </c>
       <c r="H298" s="39" t="s">
-        <v>1135</v>
+        <v>1106</v>
       </c>
       <c r="I298" s="2"/>
       <c r="J298" s="18"/>
@@ -23825,7 +23820,7 @@
         <v>99</v>
       </c>
       <c r="B299" s="32" t="s">
-        <v>1136</v>
+        <v>1107</v>
       </c>
       <c r="C299" s="33"/>
       <c r="D299" s="33"/>
@@ -23847,23 +23842,23 @@
         <v>100</v>
       </c>
       <c r="B300" s="34" t="s">
-        <v>1255</v>
+        <v>1226</v>
       </c>
       <c r="C300" s="35"/>
       <c r="D300" s="36" t="s">
-        <v>1137</v>
+        <v>1108</v>
       </c>
       <c r="E300" s="36" t="s">
-        <v>1138</v>
+        <v>1109</v>
       </c>
       <c r="F300" s="36" t="s">
-        <v>1139</v>
+        <v>1110</v>
       </c>
       <c r="G300" s="36" t="s">
-        <v>1140</v>
+        <v>1111</v>
       </c>
       <c r="H300" s="36" t="s">
-        <v>1141</v>
+        <v>1112</v>
       </c>
       <c r="I300" s="2"/>
       <c r="J300" s="18"/>
@@ -23877,7 +23872,7 @@
         <v>99</v>
       </c>
       <c r="B301" s="32" t="s">
-        <v>1142</v>
+        <v>1113</v>
       </c>
       <c r="C301" s="33"/>
       <c r="D301" s="33"/>
@@ -23899,23 +23894,23 @@
         <v>100</v>
       </c>
       <c r="B302" s="37" t="s">
-        <v>1256</v>
+        <v>1227</v>
       </c>
       <c r="C302" s="38"/>
       <c r="D302" s="39" t="s">
-        <v>1143</v>
+        <v>1114</v>
       </c>
       <c r="E302" s="39" t="s">
-        <v>1144</v>
+        <v>1115</v>
       </c>
       <c r="F302" s="39" t="s">
-        <v>1145</v>
+        <v>1116</v>
       </c>
       <c r="G302" s="39" t="s">
-        <v>1146</v>
+        <v>1117</v>
       </c>
       <c r="H302" s="39" t="s">
-        <v>1147</v>
+        <v>1118</v>
       </c>
       <c r="I302" s="2"/>
       <c r="J302" s="18"/>
@@ -23929,7 +23924,7 @@
         <v>99</v>
       </c>
       <c r="B303" s="32" t="s">
-        <v>1317</v>
+        <v>1284</v>
       </c>
       <c r="C303" s="33"/>
       <c r="D303" s="33"/>
@@ -23951,23 +23946,23 @@
         <v>100</v>
       </c>
       <c r="B304" s="34" t="s">
-        <v>1257</v>
+        <v>1228</v>
       </c>
       <c r="C304" s="35"/>
       <c r="D304" s="36" t="s">
-        <v>1129</v>
+        <v>1100</v>
       </c>
       <c r="E304" s="36" t="s">
-        <v>1148</v>
+        <v>1119</v>
       </c>
       <c r="F304" s="36" t="s">
-        <v>1149</v>
+        <v>1120</v>
       </c>
       <c r="G304" s="36" t="s">
-        <v>1150</v>
+        <v>1121</v>
       </c>
       <c r="H304" s="36" t="s">
-        <v>1151</v>
+        <v>1122</v>
       </c>
       <c r="I304" s="2"/>
       <c r="J304" s="18"/>
@@ -23981,23 +23976,23 @@
         <v>100</v>
       </c>
       <c r="B305" s="37" t="s">
-        <v>1258</v>
+        <v>1229</v>
       </c>
       <c r="C305" s="38"/>
       <c r="D305" s="39" t="s">
-        <v>1152</v>
+        <v>1123</v>
       </c>
       <c r="E305" s="39" t="s">
-        <v>1153</v>
+        <v>1124</v>
       </c>
       <c r="F305" s="39" t="s">
-        <v>1154</v>
+        <v>1125</v>
       </c>
       <c r="G305" s="39" t="s">
-        <v>1155</v>
+        <v>1126</v>
       </c>
       <c r="H305" s="39" t="s">
-        <v>1156</v>
+        <v>1127</v>
       </c>
       <c r="I305" s="2"/>
       <c r="J305" s="18"/>
@@ -24011,7 +24006,7 @@
         <v>99</v>
       </c>
       <c r="B306" s="32" t="s">
-        <v>1157</v>
+        <v>1128</v>
       </c>
       <c r="C306" s="33"/>
       <c r="D306" s="33"/>
@@ -24033,23 +24028,23 @@
         <v>100</v>
       </c>
       <c r="B307" s="34" t="s">
-        <v>1259</v>
+        <v>1230</v>
       </c>
       <c r="C307" s="35"/>
       <c r="D307" s="36" t="s">
-        <v>1158</v>
+        <v>1129</v>
       </c>
       <c r="E307" s="36" t="s">
-        <v>1159</v>
+        <v>1130</v>
       </c>
       <c r="F307" s="36" t="s">
-        <v>1160</v>
+        <v>1131</v>
       </c>
       <c r="G307" s="36" t="s">
-        <v>1161</v>
+        <v>1132</v>
       </c>
       <c r="H307" s="36" t="s">
-        <v>1162</v>
+        <v>1133</v>
       </c>
       <c r="I307" s="2"/>
       <c r="J307" s="18"/>
@@ -24063,7 +24058,7 @@
         <v>99</v>
       </c>
       <c r="B308" s="32" t="s">
-        <v>1318</v>
+        <v>1285</v>
       </c>
       <c r="C308" s="33"/>
       <c r="D308" s="33"/>
@@ -24085,23 +24080,23 @@
         <v>100</v>
       </c>
       <c r="B309" s="37" t="s">
-        <v>1260</v>
+        <v>1231</v>
       </c>
       <c r="C309" s="38"/>
       <c r="D309" s="39" t="s">
-        <v>1163</v>
+        <v>1134</v>
       </c>
       <c r="E309" s="39" t="s">
-        <v>1164</v>
+        <v>1135</v>
       </c>
       <c r="F309" s="39" t="s">
-        <v>1165</v>
+        <v>1136</v>
       </c>
       <c r="G309" s="39" t="s">
-        <v>1166</v>
+        <v>1137</v>
       </c>
       <c r="H309" s="39" t="s">
-        <v>1167</v>
+        <v>1138</v>
       </c>
       <c r="I309" s="2"/>
       <c r="J309" s="18"/>
@@ -24115,23 +24110,23 @@
         <v>100</v>
       </c>
       <c r="B310" s="34" t="s">
-        <v>1261</v>
+        <v>1232</v>
       </c>
       <c r="C310" s="35"/>
       <c r="D310" s="36" t="s">
-        <v>1168</v>
+        <v>1139</v>
       </c>
       <c r="E310" s="36" t="s">
-        <v>1169</v>
+        <v>1140</v>
       </c>
       <c r="F310" s="36" t="s">
-        <v>1170</v>
+        <v>1141</v>
       </c>
       <c r="G310" s="36" t="s">
-        <v>1171</v>
+        <v>1142</v>
       </c>
       <c r="H310" s="36" t="s">
-        <v>1172</v>
+        <v>1143</v>
       </c>
       <c r="I310" s="2"/>
       <c r="J310" s="18"/>
@@ -24145,23 +24140,23 @@
         <v>100</v>
       </c>
       <c r="B311" s="37" t="s">
-        <v>1262</v>
+        <v>1233</v>
       </c>
       <c r="C311" s="38"/>
       <c r="D311" s="39" t="s">
-        <v>1173</v>
+        <v>1144</v>
       </c>
       <c r="E311" s="39" t="s">
-        <v>1174</v>
+        <v>1145</v>
       </c>
       <c r="F311" s="39" t="s">
-        <v>1175</v>
+        <v>1146</v>
       </c>
       <c r="G311" s="39" t="s">
-        <v>1176</v>
+        <v>1147</v>
       </c>
       <c r="H311" s="39" t="s">
-        <v>1177</v>
+        <v>1148</v>
       </c>
       <c r="I311" s="2"/>
       <c r="J311" s="18"/>
@@ -24175,23 +24170,23 @@
         <v>98</v>
       </c>
       <c r="B312" s="40" t="s">
-        <v>1939</v>
+        <v>1903</v>
       </c>
       <c r="C312" s="41"/>
       <c r="D312" s="42" t="s">
-        <v>1940</v>
+        <v>1904</v>
       </c>
       <c r="E312" s="42" t="s">
-        <v>1941</v>
+        <v>1905</v>
       </c>
       <c r="F312" s="42" t="s">
-        <v>1942</v>
+        <v>1906</v>
       </c>
       <c r="G312" s="42" t="s">
-        <v>1943</v>
+        <v>1907</v>
       </c>
       <c r="H312" s="42" t="s">
-        <v>1944</v>
+        <v>1908</v>
       </c>
       <c r="I312" s="2"/>
       <c r="J312" s="18" t="s">
@@ -24209,23 +24204,23 @@
         <v>98</v>
       </c>
       <c r="B313" s="37" t="s">
-        <v>1945</v>
+        <v>1909</v>
       </c>
       <c r="C313" s="38"/>
       <c r="D313" s="39" t="s">
-        <v>1946</v>
+        <v>1910</v>
       </c>
       <c r="E313" s="39" t="s">
-        <v>1947</v>
+        <v>1911</v>
       </c>
       <c r="F313" s="39" t="s">
-        <v>1948</v>
+        <v>1912</v>
       </c>
       <c r="G313" s="39" t="s">
-        <v>1949</v>
+        <v>1913</v>
       </c>
       <c r="H313" s="39" t="s">
-        <v>1950</v>
+        <v>1914</v>
       </c>
       <c r="I313" s="2"/>
       <c r="J313" s="18" t="s">
@@ -24243,23 +24238,23 @@
         <v>98</v>
       </c>
       <c r="B314" s="40" t="s">
-        <v>1951</v>
+        <v>1915</v>
       </c>
       <c r="C314" s="41"/>
       <c r="D314" s="42" t="s">
-        <v>1952</v>
+        <v>1916</v>
       </c>
       <c r="E314" s="42" t="s">
-        <v>1953</v>
+        <v>1917</v>
       </c>
       <c r="F314" s="42" t="s">
-        <v>1954</v>
+        <v>1918</v>
       </c>
       <c r="G314" s="42" t="s">
-        <v>1955</v>
+        <v>1919</v>
       </c>
       <c r="H314" s="42" t="s">
-        <v>1956</v>
+        <v>1920</v>
       </c>
       <c r="I314" s="2"/>
       <c r="J314" s="18" t="s">
@@ -24277,23 +24272,23 @@
         <v>98</v>
       </c>
       <c r="B315" s="37" t="s">
-        <v>1957</v>
+        <v>1921</v>
       </c>
       <c r="C315" s="38"/>
       <c r="D315" s="39" t="s">
-        <v>1958</v>
+        <v>1922</v>
       </c>
       <c r="E315" s="39" t="s">
-        <v>1959</v>
+        <v>1923</v>
       </c>
       <c r="F315" s="39" t="s">
-        <v>1960</v>
+        <v>1924</v>
       </c>
       <c r="G315" s="39" t="s">
-        <v>1961</v>
+        <v>1925</v>
       </c>
       <c r="H315" s="39" t="s">
-        <v>1962</v>
+        <v>1926</v>
       </c>
       <c r="I315" s="2"/>
       <c r="J315" s="18" t="s">
@@ -24311,7 +24306,7 @@
         <v>99</v>
       </c>
       <c r="B316" s="49" t="s">
-        <v>2014</v>
+        <v>1978</v>
       </c>
       <c r="C316" s="50"/>
       <c r="D316" s="50"/>
@@ -24333,23 +24328,23 @@
         <v>100</v>
       </c>
       <c r="B317" s="40" t="s">
-        <v>1963</v>
+        <v>1927</v>
       </c>
       <c r="C317" s="41"/>
       <c r="D317" s="42" t="s">
-        <v>1964</v>
+        <v>1928</v>
       </c>
       <c r="E317" s="42" t="s">
-        <v>1965</v>
+        <v>1929</v>
       </c>
       <c r="F317" s="42" t="s">
-        <v>1966</v>
+        <v>1930</v>
       </c>
       <c r="G317" s="42" t="s">
-        <v>1967</v>
+        <v>1931</v>
       </c>
       <c r="H317" s="42" t="s">
-        <v>1968</v>
+        <v>1932</v>
       </c>
       <c r="I317" s="2"/>
       <c r="J317" s="18"/>
@@ -24363,23 +24358,23 @@
         <v>100</v>
       </c>
       <c r="B318" s="37" t="s">
-        <v>1969</v>
+        <v>1933</v>
       </c>
       <c r="C318" s="38"/>
       <c r="D318" s="39" t="s">
-        <v>1970</v>
+        <v>1934</v>
       </c>
       <c r="E318" s="39" t="s">
-        <v>1971</v>
+        <v>1935</v>
       </c>
       <c r="F318" s="39" t="s">
-        <v>1972</v>
+        <v>1936</v>
       </c>
       <c r="G318" s="39" t="s">
-        <v>1973</v>
+        <v>1937</v>
       </c>
       <c r="H318" s="39" t="s">
-        <v>1974</v>
+        <v>1938</v>
       </c>
       <c r="I318" s="2"/>
       <c r="J318" s="18"/>
@@ -24393,23 +24388,23 @@
         <v>100</v>
       </c>
       <c r="B319" s="40" t="s">
-        <v>1975</v>
+        <v>1939</v>
       </c>
       <c r="C319" s="41"/>
       <c r="D319" s="42" t="s">
-        <v>1976</v>
+        <v>1940</v>
       </c>
       <c r="E319" s="42" t="s">
-        <v>1977</v>
+        <v>1941</v>
       </c>
       <c r="F319" s="42" t="s">
-        <v>1978</v>
+        <v>1942</v>
       </c>
       <c r="G319" s="42" t="s">
-        <v>1979</v>
+        <v>1943</v>
       </c>
       <c r="H319" s="42" t="s">
-        <v>1980</v>
+        <v>1944</v>
       </c>
       <c r="I319" s="2"/>
       <c r="J319" s="18"/>
@@ -24423,7 +24418,7 @@
         <v>99</v>
       </c>
       <c r="B320" s="49" t="s">
-        <v>2015</v>
+        <v>1979</v>
       </c>
       <c r="C320" s="50"/>
       <c r="D320" s="50"/>
@@ -24445,23 +24440,23 @@
         <v>100</v>
       </c>
       <c r="B321" s="37" t="s">
-        <v>1981</v>
+        <v>1945</v>
       </c>
       <c r="C321" s="38"/>
       <c r="D321" s="39" t="s">
-        <v>1982</v>
+        <v>1946</v>
       </c>
       <c r="E321" s="39" t="s">
-        <v>1983</v>
+        <v>1947</v>
       </c>
       <c r="F321" s="39" t="s">
-        <v>1984</v>
+        <v>1948</v>
       </c>
       <c r="G321" s="39" t="s">
-        <v>1985</v>
+        <v>1949</v>
       </c>
       <c r="H321" s="39" t="s">
-        <v>1986</v>
+        <v>1950</v>
       </c>
       <c r="I321" s="2"/>
       <c r="J321" s="18"/>
@@ -24475,23 +24470,23 @@
         <v>100</v>
       </c>
       <c r="B322" s="40" t="s">
-        <v>1987</v>
+        <v>1951</v>
       </c>
       <c r="C322" s="41"/>
       <c r="D322" s="42" t="s">
-        <v>1988</v>
+        <v>1952</v>
       </c>
       <c r="E322" s="42" t="s">
-        <v>1989</v>
+        <v>1953</v>
       </c>
       <c r="F322" s="42" t="s">
-        <v>1990</v>
+        <v>1954</v>
       </c>
       <c r="G322" s="42" t="s">
-        <v>1991</v>
+        <v>1955</v>
       </c>
       <c r="H322" s="42" t="s">
-        <v>1992</v>
+        <v>1956</v>
       </c>
       <c r="I322" s="2"/>
       <c r="J322" s="18"/>
@@ -24505,7 +24500,7 @@
         <v>99</v>
       </c>
       <c r="B323" s="49" t="s">
-        <v>2016</v>
+        <v>1980</v>
       </c>
       <c r="C323" s="50"/>
       <c r="D323" s="50"/>
@@ -24527,23 +24522,23 @@
         <v>100</v>
       </c>
       <c r="B324" s="37" t="s">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="C324" s="51"/>
       <c r="D324" s="39" t="s">
-        <v>1994</v>
+        <v>1958</v>
       </c>
       <c r="E324" s="39" t="s">
-        <v>1995</v>
+        <v>1959</v>
       </c>
       <c r="F324" s="39" t="s">
-        <v>1996</v>
+        <v>1960</v>
       </c>
       <c r="G324" s="39" t="s">
-        <v>1997</v>
+        <v>1961</v>
       </c>
       <c r="H324" s="39" t="s">
-        <v>1998</v>
+        <v>1962</v>
       </c>
       <c r="I324" s="2"/>
       <c r="J324" s="18"/>
@@ -24557,23 +24552,23 @@
         <v>100</v>
       </c>
       <c r="B325" s="40" t="s">
-        <v>1999</v>
+        <v>1963</v>
       </c>
       <c r="C325" s="43"/>
       <c r="D325" s="42" t="s">
-        <v>1994</v>
+        <v>1958</v>
       </c>
       <c r="E325" s="42" t="s">
-        <v>1995</v>
+        <v>1959</v>
       </c>
       <c r="F325" s="42" t="s">
-        <v>1996</v>
+        <v>1960</v>
       </c>
       <c r="G325" s="42" t="s">
-        <v>1997</v>
+        <v>1961</v>
       </c>
       <c r="H325" s="42" t="s">
-        <v>1998</v>
+        <v>1962</v>
       </c>
       <c r="I325" s="2"/>
       <c r="J325" s="18"/>
@@ -24587,23 +24582,23 @@
         <v>100</v>
       </c>
       <c r="B326" s="37" t="s">
-        <v>2000</v>
+        <v>1964</v>
       </c>
       <c r="C326" s="51"/>
       <c r="D326" s="39" t="s">
-        <v>1994</v>
+        <v>1958</v>
       </c>
       <c r="E326" s="39" t="s">
-        <v>1995</v>
+        <v>1959</v>
       </c>
       <c r="F326" s="39" t="s">
-        <v>1996</v>
+        <v>1960</v>
       </c>
       <c r="G326" s="39" t="s">
-        <v>1997</v>
+        <v>1961</v>
       </c>
       <c r="H326" s="39" t="s">
-        <v>1998</v>
+        <v>1962</v>
       </c>
       <c r="I326" s="2"/>
       <c r="J326" s="18"/>
@@ -24617,23 +24612,23 @@
         <v>100</v>
       </c>
       <c r="B327" s="40" t="s">
-        <v>2001</v>
+        <v>1965</v>
       </c>
       <c r="C327" s="41"/>
       <c r="D327" s="42" t="s">
-        <v>2002</v>
+        <v>1966</v>
       </c>
       <c r="E327" s="42" t="s">
-        <v>2003</v>
+        <v>1967</v>
       </c>
       <c r="F327" s="42" t="s">
-        <v>2004</v>
+        <v>1968</v>
       </c>
       <c r="G327" s="42" t="s">
-        <v>2005</v>
+        <v>1969</v>
       </c>
       <c r="H327" s="42" t="s">
-        <v>2006</v>
+        <v>1970</v>
       </c>
       <c r="I327" s="2"/>
       <c r="J327" s="18"/>
@@ -24647,23 +24642,23 @@
         <v>100</v>
       </c>
       <c r="B328" s="37" t="s">
-        <v>2007</v>
+        <v>1971</v>
       </c>
       <c r="C328" s="38"/>
       <c r="D328" s="39" t="s">
-        <v>2008</v>
+        <v>1972</v>
       </c>
       <c r="E328" s="39" t="s">
-        <v>2009</v>
+        <v>1973</v>
       </c>
       <c r="F328" s="39" t="s">
-        <v>2010</v>
+        <v>1974</v>
       </c>
       <c r="G328" s="39" t="s">
-        <v>2011</v>
+        <v>1975</v>
       </c>
       <c r="H328" s="39" t="s">
-        <v>2012</v>
+        <v>1976</v>
       </c>
       <c r="I328" s="2"/>
       <c r="J328" s="18"/>
@@ -25181,23 +25176,23 @@
         <v>98</v>
       </c>
       <c r="B343" s="40" t="s">
-        <v>1319</v>
+        <v>1286</v>
       </c>
       <c r="C343" s="41"/>
       <c r="D343" s="42" t="s">
-        <v>1178</v>
+        <v>1149</v>
       </c>
       <c r="E343" s="42" t="s">
-        <v>1179</v>
+        <v>1150</v>
       </c>
       <c r="F343" s="42" t="s">
-        <v>1180</v>
+        <v>1151</v>
       </c>
       <c r="G343" s="42" t="s">
-        <v>1181</v>
+        <v>1152</v>
       </c>
       <c r="H343" s="42" t="s">
-        <v>1182</v>
+        <v>1153</v>
       </c>
       <c r="I343" s="2"/>
       <c r="J343" s="18" t="s">
@@ -25215,23 +25210,23 @@
         <v>98</v>
       </c>
       <c r="B344" s="37" t="s">
-        <v>1320</v>
+        <v>1287</v>
       </c>
       <c r="C344" s="38"/>
       <c r="D344" s="39" t="s">
-        <v>1183</v>
+        <v>1154</v>
       </c>
       <c r="E344" s="39" t="s">
-        <v>1184</v>
+        <v>1155</v>
       </c>
       <c r="F344" s="39" t="s">
-        <v>1185</v>
+        <v>1156</v>
       </c>
       <c r="G344" s="39" t="s">
-        <v>1186</v>
+        <v>1157</v>
       </c>
       <c r="H344" s="39" t="s">
-        <v>1187</v>
+        <v>1158</v>
       </c>
       <c r="I344" s="2"/>
       <c r="J344" s="18" t="s">
@@ -25249,23 +25244,23 @@
         <v>98</v>
       </c>
       <c r="B345" s="40" t="s">
-        <v>1321</v>
+        <v>1288</v>
       </c>
       <c r="C345" s="41"/>
       <c r="D345" s="42" t="s">
-        <v>1188</v>
+        <v>1159</v>
       </c>
       <c r="E345" s="42" t="s">
-        <v>1189</v>
+        <v>1160</v>
       </c>
       <c r="F345" s="42" t="s">
-        <v>1190</v>
+        <v>1161</v>
       </c>
       <c r="G345" s="42" t="s">
-        <v>1191</v>
+        <v>1162</v>
       </c>
       <c r="H345" s="42" t="s">
-        <v>1192</v>
+        <v>1163</v>
       </c>
       <c r="I345" s="2"/>
       <c r="J345" s="18" t="s">
@@ -25283,23 +25278,23 @@
         <v>98</v>
       </c>
       <c r="B346" s="37" t="s">
-        <v>1322</v>
+        <v>1289</v>
       </c>
       <c r="C346" s="38"/>
       <c r="D346" s="39" t="s">
-        <v>1193</v>
+        <v>1164</v>
       </c>
       <c r="E346" s="39" t="s">
-        <v>1194</v>
+        <v>1165</v>
       </c>
       <c r="F346" s="39" t="s">
-        <v>1195</v>
+        <v>1166</v>
       </c>
       <c r="G346" s="39" t="s">
-        <v>1196</v>
+        <v>1167</v>
       </c>
       <c r="H346" s="39" t="s">
-        <v>1197</v>
+        <v>1168</v>
       </c>
       <c r="I346" s="2"/>
       <c r="J346" s="18" t="s">
@@ -25317,23 +25312,23 @@
         <v>98</v>
       </c>
       <c r="B347" s="40" t="s">
-        <v>1323</v>
+        <v>1290</v>
       </c>
       <c r="C347" s="41"/>
       <c r="D347" s="42" t="s">
-        <v>1198</v>
+        <v>1169</v>
       </c>
       <c r="E347" s="42" t="s">
-        <v>1199</v>
+        <v>1170</v>
       </c>
       <c r="F347" s="42" t="s">
-        <v>1200</v>
+        <v>1171</v>
       </c>
       <c r="G347" s="42" t="s">
-        <v>1201</v>
+        <v>1172</v>
       </c>
       <c r="H347" s="42" t="s">
-        <v>1202</v>
+        <v>1173</v>
       </c>
       <c r="I347" s="2"/>
       <c r="J347" s="18" t="s">
@@ -25351,23 +25346,23 @@
         <v>98</v>
       </c>
       <c r="B348" s="37" t="s">
-        <v>1324</v>
+        <v>1291</v>
       </c>
       <c r="C348" s="38"/>
       <c r="D348" s="39" t="s">
-        <v>1203</v>
+        <v>1174</v>
       </c>
       <c r="E348" s="39" t="s">
-        <v>1204</v>
+        <v>1175</v>
       </c>
       <c r="F348" s="39" t="s">
-        <v>1205</v>
+        <v>1176</v>
       </c>
       <c r="G348" s="39" t="s">
-        <v>1206</v>
+        <v>1177</v>
       </c>
       <c r="H348" s="39" t="s">
-        <v>1207</v>
+        <v>1178</v>
       </c>
       <c r="I348" s="2"/>
       <c r="J348" s="18" t="s">
@@ -25385,23 +25380,23 @@
         <v>98</v>
       </c>
       <c r="B349" s="40" t="s">
-        <v>1325</v>
+        <v>1292</v>
       </c>
       <c r="C349" s="41"/>
       <c r="D349" s="42" t="s">
-        <v>1208</v>
+        <v>1179</v>
       </c>
       <c r="E349" s="42" t="s">
-        <v>1209</v>
+        <v>1180</v>
       </c>
       <c r="F349" s="42" t="s">
-        <v>1210</v>
+        <v>1181</v>
       </c>
       <c r="G349" s="42" t="s">
-        <v>1211</v>
+        <v>1182</v>
       </c>
       <c r="H349" s="42" t="s">
-        <v>1212</v>
+        <v>1183</v>
       </c>
       <c r="I349" s="2"/>
       <c r="J349" s="18" t="s">
@@ -25419,23 +25414,23 @@
         <v>98</v>
       </c>
       <c r="B350" s="37" t="s">
-        <v>1326</v>
+        <v>1293</v>
       </c>
       <c r="C350" s="38"/>
       <c r="D350" s="39" t="s">
-        <v>1213</v>
+        <v>1184</v>
       </c>
       <c r="E350" s="39" t="s">
-        <v>1214</v>
+        <v>1185</v>
       </c>
       <c r="F350" s="39" t="s">
-        <v>1215</v>
+        <v>1186</v>
       </c>
       <c r="G350" s="39" t="s">
-        <v>1216</v>
+        <v>1187</v>
       </c>
       <c r="H350" s="39" t="s">
-        <v>1217</v>
+        <v>1188</v>
       </c>
       <c r="I350" s="2"/>
       <c r="J350" s="18" t="s">
@@ -25453,25 +25448,25 @@
         <v>98</v>
       </c>
       <c r="B351" s="40" t="s">
-        <v>1327</v>
+        <v>1294</v>
       </c>
       <c r="C351" s="43" t="s">
-        <v>1248</v>
+        <v>1219</v>
       </c>
       <c r="D351" s="42" t="s">
-        <v>1218</v>
+        <v>1189</v>
       </c>
       <c r="E351" s="42" t="s">
-        <v>1219</v>
+        <v>1190</v>
       </c>
       <c r="F351" s="42" t="s">
-        <v>1220</v>
+        <v>1191</v>
       </c>
       <c r="G351" s="42" t="s">
-        <v>1221</v>
+        <v>1192</v>
       </c>
       <c r="H351" s="42" t="s">
-        <v>1222</v>
+        <v>1193</v>
       </c>
       <c r="I351" s="2"/>
       <c r="J351" s="18" t="s">
@@ -25489,23 +25484,23 @@
         <v>98</v>
       </c>
       <c r="B352" s="37" t="s">
-        <v>1328</v>
+        <v>1295</v>
       </c>
       <c r="C352" s="38"/>
       <c r="D352" s="39" t="s">
-        <v>1223</v>
+        <v>1194</v>
       </c>
       <c r="E352" s="39" t="s">
-        <v>1224</v>
+        <v>1195</v>
       </c>
       <c r="F352" s="39" t="s">
-        <v>1225</v>
+        <v>1196</v>
       </c>
       <c r="G352" s="39" t="s">
-        <v>1226</v>
+        <v>1197</v>
       </c>
       <c r="H352" s="39" t="s">
-        <v>1227</v>
+        <v>1198</v>
       </c>
       <c r="I352" s="2"/>
       <c r="J352" s="18" t="s">
@@ -25523,23 +25518,23 @@
         <v>98</v>
       </c>
       <c r="B353" s="40" t="s">
-        <v>1329</v>
+        <v>1296</v>
       </c>
       <c r="C353" s="41"/>
       <c r="D353" s="42" t="s">
-        <v>1228</v>
+        <v>1199</v>
       </c>
       <c r="E353" s="42" t="s">
-        <v>1229</v>
+        <v>1200</v>
       </c>
       <c r="F353" s="42" t="s">
-        <v>1230</v>
+        <v>1201</v>
       </c>
       <c r="G353" s="42" t="s">
-        <v>1231</v>
+        <v>1202</v>
       </c>
       <c r="H353" s="42" t="s">
-        <v>1232</v>
+        <v>1203</v>
       </c>
       <c r="I353" s="2"/>
       <c r="J353" s="18" t="s">
@@ -25557,23 +25552,23 @@
         <v>98</v>
       </c>
       <c r="B354" s="37" t="s">
-        <v>1330</v>
+        <v>1297</v>
       </c>
       <c r="C354" s="38"/>
       <c r="D354" s="39" t="s">
-        <v>1233</v>
+        <v>1204</v>
       </c>
       <c r="E354" s="39" t="s">
-        <v>1234</v>
+        <v>1205</v>
       </c>
       <c r="F354" s="39" t="s">
-        <v>1235</v>
+        <v>1206</v>
       </c>
       <c r="G354" s="39" t="s">
-        <v>1236</v>
+        <v>1207</v>
       </c>
       <c r="H354" s="39" t="s">
-        <v>1237</v>
+        <v>1208</v>
       </c>
       <c r="I354" s="2"/>
       <c r="J354" s="18" t="s">
@@ -25591,23 +25586,23 @@
         <v>98</v>
       </c>
       <c r="B355" s="40" t="s">
-        <v>1331</v>
+        <v>1298</v>
       </c>
       <c r="C355" s="41"/>
       <c r="D355" s="42" t="s">
-        <v>1238</v>
+        <v>1209</v>
       </c>
       <c r="E355" s="42" t="s">
-        <v>1239</v>
+        <v>1210</v>
       </c>
       <c r="F355" s="42" t="s">
-        <v>1240</v>
+        <v>1211</v>
       </c>
       <c r="G355" s="42" t="s">
-        <v>1241</v>
+        <v>1212</v>
       </c>
       <c r="H355" s="42" t="s">
-        <v>1242</v>
+        <v>1213</v>
       </c>
       <c r="I355" s="2"/>
       <c r="J355" s="18" t="s">
@@ -25625,23 +25620,23 @@
         <v>98</v>
       </c>
       <c r="B356" s="37" t="s">
-        <v>1332</v>
+        <v>1299</v>
       </c>
       <c r="C356" s="38"/>
       <c r="D356" s="39" t="s">
-        <v>1243</v>
+        <v>1214</v>
       </c>
       <c r="E356" s="39" t="s">
-        <v>1244</v>
+        <v>1215</v>
       </c>
       <c r="F356" s="39" t="s">
-        <v>1245</v>
+        <v>1216</v>
       </c>
       <c r="G356" s="39" t="s">
-        <v>1246</v>
+        <v>1217</v>
       </c>
       <c r="H356" s="39" t="s">
-        <v>1247</v>
+        <v>1218</v>
       </c>
       <c r="I356" s="2"/>
       <c r="J356" s="18" t="s">
@@ -25659,7 +25654,7 @@
         <v>99</v>
       </c>
       <c r="B357" s="32" t="s">
-        <v>1297</v>
+        <v>1264</v>
       </c>
       <c r="C357" s="33"/>
       <c r="D357" s="33"/>
@@ -25681,23 +25676,23 @@
         <v>100</v>
       </c>
       <c r="B358" s="34" t="s">
-        <v>1298</v>
+        <v>1265</v>
       </c>
       <c r="C358" s="35"/>
       <c r="D358" s="36" t="s">
-        <v>1027</v>
+        <v>998</v>
       </c>
       <c r="E358" s="36" t="s">
-        <v>1028</v>
+        <v>999</v>
       </c>
       <c r="F358" s="36" t="s">
-        <v>1029</v>
+        <v>1000</v>
       </c>
       <c r="G358" s="36" t="s">
-        <v>1030</v>
+        <v>1001</v>
       </c>
       <c r="H358" s="36" t="s">
-        <v>1031</v>
+        <v>1002</v>
       </c>
       <c r="I358" s="2"/>
       <c r="J358" s="18"/>
@@ -25711,7 +25706,7 @@
         <v>99</v>
       </c>
       <c r="B359" s="32" t="s">
-        <v>1032</v>
+        <v>1003</v>
       </c>
       <c r="C359" s="33"/>
       <c r="D359" s="33"/>
@@ -25733,23 +25728,23 @@
         <v>100</v>
       </c>
       <c r="B360" s="37" t="s">
-        <v>1299</v>
+        <v>1266</v>
       </c>
       <c r="C360" s="38"/>
       <c r="D360" s="39" t="s">
-        <v>1033</v>
+        <v>1004</v>
       </c>
       <c r="E360" s="39" t="s">
-        <v>1034</v>
+        <v>1005</v>
       </c>
       <c r="F360" s="39" t="s">
-        <v>1035</v>
+        <v>1006</v>
       </c>
       <c r="G360" s="39" t="s">
-        <v>1036</v>
+        <v>1007</v>
       </c>
       <c r="H360" s="39" t="s">
-        <v>1037</v>
+        <v>1008</v>
       </c>
       <c r="I360" s="2"/>
       <c r="J360" s="18"/>
@@ -25763,7 +25758,7 @@
         <v>99</v>
       </c>
       <c r="B361" s="32" t="s">
-        <v>1038</v>
+        <v>1009</v>
       </c>
       <c r="C361" s="33"/>
       <c r="D361" s="33"/>
@@ -25785,23 +25780,23 @@
         <v>100</v>
       </c>
       <c r="B362" s="34" t="s">
-        <v>1300</v>
+        <v>1267</v>
       </c>
       <c r="C362" s="35"/>
       <c r="D362" s="36" t="s">
-        <v>1039</v>
+        <v>1010</v>
       </c>
       <c r="E362" s="36" t="s">
-        <v>1040</v>
+        <v>1011</v>
       </c>
       <c r="F362" s="36" t="s">
-        <v>1041</v>
+        <v>1012</v>
       </c>
       <c r="G362" s="36" t="s">
-        <v>1042</v>
+        <v>1013</v>
       </c>
       <c r="H362" s="36" t="s">
-        <v>1043</v>
+        <v>1014</v>
       </c>
       <c r="I362" s="2"/>
       <c r="J362" s="18"/>
@@ -25815,7 +25810,7 @@
         <v>99</v>
       </c>
       <c r="B363" s="32" t="s">
-        <v>1301</v>
+        <v>1268</v>
       </c>
       <c r="C363" s="33"/>
       <c r="D363" s="33"/>
@@ -25837,23 +25832,23 @@
         <v>100</v>
       </c>
       <c r="B364" s="37" t="s">
-        <v>1302</v>
+        <v>1269</v>
       </c>
       <c r="C364" s="38"/>
       <c r="D364" s="39" t="s">
-        <v>1044</v>
+        <v>1015</v>
       </c>
       <c r="E364" s="39" t="s">
-        <v>1045</v>
+        <v>1016</v>
       </c>
       <c r="F364" s="39" t="s">
-        <v>1046</v>
+        <v>1017</v>
       </c>
       <c r="G364" s="39" t="s">
-        <v>1047</v>
+        <v>1018</v>
       </c>
       <c r="H364" s="39" t="s">
-        <v>1048</v>
+        <v>1019</v>
       </c>
       <c r="I364" s="2"/>
       <c r="J364" s="18"/>
@@ -25867,23 +25862,23 @@
         <v>100</v>
       </c>
       <c r="B365" s="34" t="s">
-        <v>1303</v>
+        <v>1270</v>
       </c>
       <c r="C365" s="35"/>
       <c r="D365" s="36" t="s">
-        <v>1049</v>
+        <v>1020</v>
       </c>
       <c r="E365" s="36" t="s">
-        <v>1050</v>
+        <v>1021</v>
       </c>
       <c r="F365" s="36" t="s">
-        <v>1051</v>
+        <v>1022</v>
       </c>
       <c r="G365" s="36" t="s">
-        <v>1052</v>
+        <v>1023</v>
       </c>
       <c r="H365" s="36" t="s">
-        <v>1053</v>
+        <v>1024</v>
       </c>
       <c r="I365" s="2"/>
       <c r="J365" s="18"/>
@@ -25897,7 +25892,7 @@
         <v>99</v>
       </c>
       <c r="B366" s="32" t="s">
-        <v>1054</v>
+        <v>1025</v>
       </c>
       <c r="C366" s="33"/>
       <c r="D366" s="33"/>
@@ -25919,23 +25914,23 @@
         <v>100</v>
       </c>
       <c r="B367" s="37" t="s">
-        <v>1304</v>
+        <v>1271</v>
       </c>
       <c r="C367" s="38"/>
       <c r="D367" s="39" t="s">
-        <v>1055</v>
+        <v>1026</v>
       </c>
       <c r="E367" s="39" t="s">
-        <v>1056</v>
+        <v>1027</v>
       </c>
       <c r="F367" s="39" t="s">
-        <v>1057</v>
+        <v>1028</v>
       </c>
       <c r="G367" s="39" t="s">
-        <v>1058</v>
+        <v>1029</v>
       </c>
       <c r="H367" s="39" t="s">
-        <v>1059</v>
+        <v>1030</v>
       </c>
       <c r="I367" s="2"/>
       <c r="J367" s="18"/>
@@ -25949,23 +25944,23 @@
         <v>100</v>
       </c>
       <c r="B368" s="34" t="s">
-        <v>1305</v>
+        <v>1272</v>
       </c>
       <c r="C368" s="35"/>
       <c r="D368" s="36" t="s">
-        <v>1060</v>
+        <v>1031</v>
       </c>
       <c r="E368" s="36" t="s">
-        <v>1061</v>
+        <v>1032</v>
       </c>
       <c r="F368" s="36" t="s">
-        <v>1062</v>
+        <v>1033</v>
       </c>
       <c r="G368" s="36" t="s">
-        <v>1063</v>
+        <v>1034</v>
       </c>
       <c r="H368" s="36" t="s">
-        <v>1064</v>
+        <v>1035</v>
       </c>
       <c r="I368" s="2"/>
       <c r="J368" s="18"/>
@@ -25979,10 +25974,10 @@
         <v>99</v>
       </c>
       <c r="B369" s="32" t="s">
-        <v>1065</v>
+        <v>1036</v>
       </c>
       <c r="C369" s="33" t="s">
-        <v>1101</v>
+        <v>1072</v>
       </c>
       <c r="D369" s="33"/>
       <c r="E369" s="33"/>
@@ -26003,23 +25998,23 @@
         <v>100</v>
       </c>
       <c r="B370" s="37" t="s">
-        <v>1306</v>
+        <v>1273</v>
       </c>
       <c r="C370" s="38"/>
       <c r="D370" s="39" t="s">
-        <v>1066</v>
+        <v>1037</v>
       </c>
       <c r="E370" s="39" t="s">
-        <v>1067</v>
+        <v>1038</v>
       </c>
       <c r="F370" s="39" t="s">
-        <v>1068</v>
+        <v>1039</v>
       </c>
       <c r="G370" s="39" t="s">
-        <v>1069</v>
+        <v>1040</v>
       </c>
       <c r="H370" s="39" t="s">
-        <v>1070</v>
+        <v>1041</v>
       </c>
       <c r="I370" s="2"/>
       <c r="J370" s="18"/>
@@ -26033,10 +26028,10 @@
         <v>99</v>
       </c>
       <c r="B371" s="32" t="s">
-        <v>1307</v>
+        <v>1274</v>
       </c>
       <c r="C371" s="33" t="s">
-        <v>1102</v>
+        <v>1073</v>
       </c>
       <c r="D371" s="33"/>
       <c r="E371" s="33"/>
@@ -26057,23 +26052,23 @@
         <v>100</v>
       </c>
       <c r="B372" s="34" t="s">
-        <v>1308</v>
+        <v>1275</v>
       </c>
       <c r="C372" s="35"/>
       <c r="D372" s="36" t="s">
-        <v>1071</v>
+        <v>1042</v>
       </c>
       <c r="E372" s="36" t="s">
-        <v>1072</v>
+        <v>1043</v>
       </c>
       <c r="F372" s="36" t="s">
-        <v>1073</v>
+        <v>1044</v>
       </c>
       <c r="G372" s="36" t="s">
-        <v>1074</v>
+        <v>1045</v>
       </c>
       <c r="H372" s="36" t="s">
-        <v>1075</v>
+        <v>1046</v>
       </c>
       <c r="I372" s="2"/>
       <c r="J372" s="18"/>
@@ -26087,23 +26082,23 @@
         <v>100</v>
       </c>
       <c r="B373" s="37" t="s">
-        <v>1309</v>
+        <v>1276</v>
       </c>
       <c r="C373" s="38"/>
       <c r="D373" s="39" t="s">
-        <v>1076</v>
+        <v>1047</v>
       </c>
       <c r="E373" s="39" t="s">
-        <v>1077</v>
+        <v>1048</v>
       </c>
       <c r="F373" s="39" t="s">
-        <v>1078</v>
+        <v>1049</v>
       </c>
       <c r="G373" s="39" t="s">
-        <v>1079</v>
+        <v>1050</v>
       </c>
       <c r="H373" s="39" t="s">
-        <v>1080</v>
+        <v>1051</v>
       </c>
       <c r="I373" s="2"/>
       <c r="J373" s="18"/>
@@ -26117,23 +26112,23 @@
         <v>100</v>
       </c>
       <c r="B374" s="34" t="s">
-        <v>1310</v>
+        <v>1277</v>
       </c>
       <c r="C374" s="35"/>
       <c r="D374" s="36" t="s">
-        <v>1081</v>
+        <v>1052</v>
       </c>
       <c r="E374" s="36" t="s">
-        <v>1082</v>
+        <v>1053</v>
       </c>
       <c r="F374" s="36" t="s">
-        <v>1083</v>
+        <v>1054</v>
       </c>
       <c r="G374" s="36" t="s">
-        <v>1084</v>
+        <v>1055</v>
       </c>
       <c r="H374" s="36" t="s">
-        <v>1085</v>
+        <v>1056</v>
       </c>
       <c r="I374" s="2"/>
       <c r="J374" s="18"/>
@@ -26147,23 +26142,23 @@
         <v>100</v>
       </c>
       <c r="B375" s="37" t="s">
-        <v>1311</v>
+        <v>1278</v>
       </c>
       <c r="C375" s="38"/>
       <c r="D375" s="39" t="s">
-        <v>1086</v>
+        <v>1057</v>
       </c>
       <c r="E375" s="39" t="s">
-        <v>1087</v>
+        <v>1058</v>
       </c>
       <c r="F375" s="39" t="s">
-        <v>1088</v>
+        <v>1059</v>
       </c>
       <c r="G375" s="39" t="s">
-        <v>1089</v>
+        <v>1060</v>
       </c>
       <c r="H375" s="39" t="s">
-        <v>1090</v>
+        <v>1061</v>
       </c>
       <c r="I375" s="2"/>
       <c r="J375" s="18"/>
@@ -26177,10 +26172,10 @@
         <v>99</v>
       </c>
       <c r="B376" s="32" t="s">
-        <v>1312</v>
+        <v>1279</v>
       </c>
       <c r="C376" s="33" t="s">
-        <v>1103</v>
+        <v>1074</v>
       </c>
       <c r="D376" s="33"/>
       <c r="E376" s="33"/>
@@ -26201,23 +26196,23 @@
         <v>100</v>
       </c>
       <c r="B377" s="34" t="s">
-        <v>1313</v>
+        <v>1280</v>
       </c>
       <c r="C377" s="35"/>
       <c r="D377" s="36" t="s">
-        <v>1091</v>
+        <v>1062</v>
       </c>
       <c r="E377" s="36" t="s">
-        <v>1092</v>
+        <v>1063</v>
       </c>
       <c r="F377" s="36" t="s">
-        <v>1093</v>
+        <v>1064</v>
       </c>
       <c r="G377" s="36" t="s">
-        <v>1094</v>
+        <v>1065</v>
       </c>
       <c r="H377" s="36" t="s">
-        <v>1095</v>
+        <v>1066</v>
       </c>
       <c r="I377" s="2"/>
       <c r="J377" s="18"/>
@@ -26231,23 +26226,23 @@
         <v>100</v>
       </c>
       <c r="B378" s="37" t="s">
-        <v>1314</v>
+        <v>1281</v>
       </c>
       <c r="C378" s="38"/>
       <c r="D378" s="39" t="s">
-        <v>1096</v>
+        <v>1067</v>
       </c>
       <c r="E378" s="39" t="s">
-        <v>1097</v>
+        <v>1068</v>
       </c>
       <c r="F378" s="39" t="s">
-        <v>1098</v>
+        <v>1069</v>
       </c>
       <c r="G378" s="39" t="s">
-        <v>1099</v>
+        <v>1070</v>
       </c>
       <c r="H378" s="39" t="s">
-        <v>1100</v>
+        <v>1071</v>
       </c>
       <c r="I378" s="2"/>
       <c r="J378" s="18"/>
@@ -26261,23 +26256,23 @@
         <v>98</v>
       </c>
       <c r="B379" s="52" t="s">
-        <v>2079</v>
+        <v>2043</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" s="52" t="s">
-        <v>2093</v>
+        <v>2057</v>
       </c>
       <c r="E379" s="52" t="s">
-        <v>2094</v>
+        <v>2058</v>
       </c>
       <c r="F379" s="52" t="s">
-        <v>2095</v>
+        <v>2059</v>
       </c>
       <c r="G379" s="52" t="s">
-        <v>2096</v>
+        <v>2060</v>
       </c>
       <c r="H379" s="52" t="s">
-        <v>2097</v>
+        <v>2061</v>
       </c>
       <c r="I379" s="2"/>
       <c r="J379" s="18" t="s">
@@ -26295,23 +26290,23 @@
         <v>98</v>
       </c>
       <c r="B380" s="53" t="s">
-        <v>2080</v>
+        <v>2044</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="53" t="s">
-        <v>2098</v>
+        <v>2062</v>
       </c>
       <c r="E380" s="53" t="s">
-        <v>2099</v>
+        <v>2063</v>
       </c>
       <c r="F380" s="53" t="s">
-        <v>2100</v>
+        <v>2064</v>
       </c>
       <c r="G380" s="53" t="s">
-        <v>2101</v>
+        <v>2065</v>
       </c>
       <c r="H380" s="53" t="s">
-        <v>2102</v>
+        <v>2066</v>
       </c>
       <c r="I380" s="2"/>
       <c r="J380" s="18" t="s">
@@ -26329,23 +26324,23 @@
         <v>98</v>
       </c>
       <c r="B381" s="52" t="s">
-        <v>2081</v>
+        <v>2045</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" s="52" t="s">
-        <v>2098</v>
+        <v>2062</v>
       </c>
       <c r="E381" s="52" t="s">
-        <v>2099</v>
+        <v>2063</v>
       </c>
       <c r="F381" s="52" t="s">
-        <v>2100</v>
+        <v>2064</v>
       </c>
       <c r="G381" s="52" t="s">
-        <v>2101</v>
+        <v>2065</v>
       </c>
       <c r="H381" s="52" t="s">
-        <v>2102</v>
+        <v>2066</v>
       </c>
       <c r="I381" s="2"/>
       <c r="J381" s="18" t="s">
@@ -26363,23 +26358,23 @@
         <v>98</v>
       </c>
       <c r="B382" s="53" t="s">
-        <v>2082</v>
+        <v>2046</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" s="53" t="s">
-        <v>2103</v>
+        <v>2067</v>
       </c>
       <c r="E382" s="53" t="s">
-        <v>2104</v>
+        <v>2068</v>
       </c>
       <c r="F382" s="53" t="s">
-        <v>2105</v>
+        <v>2069</v>
       </c>
       <c r="G382" s="53" t="s">
-        <v>2106</v>
+        <v>2070</v>
       </c>
       <c r="H382" s="53" t="s">
-        <v>2107</v>
+        <v>2071</v>
       </c>
       <c r="I382" s="2"/>
       <c r="J382" s="18" t="s">
@@ -26397,23 +26392,23 @@
         <v>98</v>
       </c>
       <c r="B383" s="52" t="s">
-        <v>2083</v>
+        <v>2047</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" s="52" t="s">
-        <v>2108</v>
+        <v>2072</v>
       </c>
       <c r="E383" s="52" t="s">
-        <v>2109</v>
+        <v>2073</v>
       </c>
       <c r="F383" s="52" t="s">
-        <v>2110</v>
+        <v>2074</v>
       </c>
       <c r="G383" s="52" t="s">
-        <v>2111</v>
+        <v>2075</v>
       </c>
       <c r="H383" s="52" t="s">
-        <v>2102</v>
+        <v>2066</v>
       </c>
       <c r="I383" s="2"/>
       <c r="J383" s="18" t="s">
@@ -26431,23 +26426,23 @@
         <v>98</v>
       </c>
       <c r="B384" s="53" t="s">
-        <v>2084</v>
+        <v>2048</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" s="53" t="s">
-        <v>2112</v>
+        <v>2076</v>
       </c>
       <c r="E384" s="53" t="s">
-        <v>2113</v>
+        <v>2077</v>
       </c>
       <c r="F384" s="53" t="s">
-        <v>2114</v>
+        <v>2078</v>
       </c>
       <c r="G384" s="53" t="s">
-        <v>2115</v>
+        <v>2079</v>
       </c>
       <c r="H384" s="53" t="s">
-        <v>2102</v>
+        <v>2066</v>
       </c>
       <c r="I384" s="2"/>
       <c r="J384" s="18" t="s">
@@ -26465,23 +26460,23 @@
         <v>98</v>
       </c>
       <c r="B385" s="52" t="s">
-        <v>2085</v>
+        <v>2049</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" s="52" t="s">
-        <v>2116</v>
+        <v>2080</v>
       </c>
       <c r="E385" s="52" t="s">
-        <v>2117</v>
+        <v>2081</v>
       </c>
       <c r="F385" s="52" t="s">
-        <v>2118</v>
+        <v>2082</v>
       </c>
       <c r="G385" s="52" t="s">
-        <v>2119</v>
+        <v>2083</v>
       </c>
       <c r="H385" s="52" t="s">
-        <v>2097</v>
+        <v>2061</v>
       </c>
       <c r="I385" s="2"/>
       <c r="J385" s="18" t="s">
@@ -26499,23 +26494,23 @@
         <v>98</v>
       </c>
       <c r="B386" s="53" t="s">
-        <v>2086</v>
+        <v>2050</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" s="53" t="s">
-        <v>2120</v>
+        <v>2084</v>
       </c>
       <c r="E386" s="53" t="s">
-        <v>2121</v>
+        <v>2085</v>
       </c>
       <c r="F386" s="53" t="s">
-        <v>2122</v>
+        <v>2086</v>
       </c>
       <c r="G386" s="53" t="s">
-        <v>2123</v>
+        <v>2087</v>
       </c>
       <c r="H386" s="53" t="s">
-        <v>2124</v>
+        <v>2088</v>
       </c>
       <c r="I386" s="2"/>
       <c r="J386" s="18" t="s">
@@ -26533,23 +26528,23 @@
         <v>98</v>
       </c>
       <c r="B387" s="52" t="s">
-        <v>2087</v>
+        <v>2051</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" s="52" t="s">
-        <v>2125</v>
+        <v>2089</v>
       </c>
       <c r="E387" s="52" t="s">
-        <v>2126</v>
+        <v>2090</v>
       </c>
       <c r="F387" s="52" t="s">
-        <v>2127</v>
+        <v>2091</v>
       </c>
       <c r="G387" s="52" t="s">
-        <v>2128</v>
+        <v>2092</v>
       </c>
       <c r="H387" s="52" t="s">
-        <v>2102</v>
+        <v>2066</v>
       </c>
       <c r="I387" s="2"/>
       <c r="J387" s="18" t="s">
@@ -26567,23 +26562,23 @@
         <v>98</v>
       </c>
       <c r="B388" s="53" t="s">
-        <v>2088</v>
+        <v>2052</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" s="53" t="s">
-        <v>2125</v>
+        <v>2089</v>
       </c>
       <c r="E388" s="53" t="s">
-        <v>2126</v>
+        <v>2090</v>
       </c>
       <c r="F388" s="53" t="s">
-        <v>2127</v>
+        <v>2091</v>
       </c>
       <c r="G388" s="53" t="s">
-        <v>2128</v>
+        <v>2092</v>
       </c>
       <c r="H388" s="53" t="s">
-        <v>2102</v>
+        <v>2066</v>
       </c>
       <c r="I388" s="2"/>
       <c r="J388" s="18" t="s">
@@ -26601,23 +26596,23 @@
         <v>98</v>
       </c>
       <c r="B389" s="52" t="s">
-        <v>2089</v>
+        <v>2053</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" s="52" t="s">
-        <v>2129</v>
+        <v>2093</v>
       </c>
       <c r="E389" s="52" t="s">
-        <v>2130</v>
+        <v>2094</v>
       </c>
       <c r="F389" s="52" t="s">
-        <v>2131</v>
+        <v>2095</v>
       </c>
       <c r="G389" s="52" t="s">
-        <v>2132</v>
+        <v>2096</v>
       </c>
       <c r="H389" s="52" t="s">
-        <v>2133</v>
+        <v>2097</v>
       </c>
       <c r="I389" s="2"/>
       <c r="J389" s="18" t="s">
@@ -26635,23 +26630,23 @@
         <v>98</v>
       </c>
       <c r="B390" s="53" t="s">
-        <v>2090</v>
+        <v>2054</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" s="53" t="s">
-        <v>2134</v>
+        <v>2098</v>
       </c>
       <c r="E390" s="53" t="s">
-        <v>2135</v>
+        <v>2099</v>
       </c>
       <c r="F390" s="53" t="s">
-        <v>2136</v>
+        <v>2100</v>
       </c>
       <c r="G390" s="53" t="s">
-        <v>2137</v>
+        <v>2101</v>
       </c>
       <c r="H390" s="53" t="s">
-        <v>2138</v>
+        <v>2102</v>
       </c>
       <c r="I390" s="2"/>
       <c r="J390" s="18" t="s">
@@ -26669,23 +26664,23 @@
         <v>98</v>
       </c>
       <c r="B391" s="52" t="s">
-        <v>2091</v>
+        <v>2055</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" s="52" t="s">
-        <v>2139</v>
+        <v>2103</v>
       </c>
       <c r="E391" s="52" t="s">
-        <v>2140</v>
+        <v>2104</v>
       </c>
       <c r="F391" s="52" t="s">
-        <v>2141</v>
+        <v>2105</v>
       </c>
       <c r="G391" s="52" t="s">
-        <v>2142</v>
+        <v>2106</v>
       </c>
       <c r="H391" s="52" t="s">
-        <v>2138</v>
+        <v>2102</v>
       </c>
       <c r="I391" s="2"/>
       <c r="J391" s="18" t="s">
@@ -26703,23 +26698,23 @@
         <v>98</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2092</v>
+        <v>2056</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" s="53" t="s">
-        <v>2143</v>
+        <v>2107</v>
       </c>
       <c r="E392" s="53" t="s">
-        <v>2144</v>
+        <v>2108</v>
       </c>
       <c r="F392" s="53" t="s">
-        <v>2145</v>
+        <v>2109</v>
       </c>
       <c r="G392" s="53" t="s">
-        <v>2146</v>
+        <v>2110</v>
       </c>
       <c r="H392" s="53" t="s">
-        <v>2133</v>
+        <v>2097</v>
       </c>
       <c r="I392" s="2"/>
       <c r="J392" s="18" t="s">
@@ -27659,7 +27654,7 @@
         <v>99</v>
       </c>
       <c r="B419" s="54" t="s">
-        <v>2260</v>
+        <v>2224</v>
       </c>
       <c r="C419" s="54"/>
       <c r="D419" s="54"/>
@@ -27681,23 +27676,23 @@
         <v>100</v>
       </c>
       <c r="B420" s="54" t="s">
-        <v>2261</v>
+        <v>2225</v>
       </c>
       <c r="C420" s="54"/>
       <c r="D420" s="54" t="s">
-        <v>2147</v>
+        <v>2111</v>
       </c>
       <c r="E420" s="54" t="s">
-        <v>2148</v>
+        <v>2112</v>
       </c>
       <c r="F420" s="54" t="s">
-        <v>2149</v>
+        <v>2113</v>
       </c>
       <c r="G420" s="54" t="s">
-        <v>2150</v>
+        <v>2114</v>
       </c>
       <c r="H420" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I420" s="2"/>
       <c r="J420" s="18"/>
@@ -27711,23 +27706,23 @@
         <v>100</v>
       </c>
       <c r="B421" s="54" t="s">
-        <v>2262</v>
+        <v>2226</v>
       </c>
       <c r="C421" s="54"/>
       <c r="D421" s="54" t="s">
-        <v>2152</v>
+        <v>2116</v>
       </c>
       <c r="E421" s="54" t="s">
-        <v>2153</v>
+        <v>2117</v>
       </c>
       <c r="F421" s="54" t="s">
-        <v>2154</v>
+        <v>2118</v>
       </c>
       <c r="G421" s="54" t="s">
-        <v>2155</v>
+        <v>2119</v>
       </c>
       <c r="H421" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I421" s="2"/>
       <c r="J421" s="18"/>
@@ -27741,23 +27736,23 @@
         <v>100</v>
       </c>
       <c r="B422" s="54" t="s">
-        <v>2263</v>
+        <v>2227</v>
       </c>
       <c r="C422" s="54"/>
       <c r="D422" s="54" t="s">
-        <v>2156</v>
+        <v>2120</v>
       </c>
       <c r="E422" s="54" t="s">
-        <v>2157</v>
+        <v>2121</v>
       </c>
       <c r="F422" s="54" t="s">
-        <v>2158</v>
+        <v>2122</v>
       </c>
       <c r="G422" s="54" t="s">
-        <v>2159</v>
+        <v>2123</v>
       </c>
       <c r="H422" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I422" s="2"/>
       <c r="J422" s="18"/>
@@ -27771,23 +27766,23 @@
         <v>100</v>
       </c>
       <c r="B423" s="54" t="s">
-        <v>2264</v>
+        <v>2228</v>
       </c>
       <c r="C423" s="54"/>
       <c r="D423" s="54" t="s">
-        <v>2160</v>
+        <v>2124</v>
       </c>
       <c r="E423" s="54" t="s">
-        <v>2161</v>
+        <v>2125</v>
       </c>
       <c r="F423" s="54" t="s">
-        <v>2162</v>
+        <v>2126</v>
       </c>
       <c r="G423" s="54" t="s">
-        <v>2163</v>
+        <v>2127</v>
       </c>
       <c r="H423" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I423" s="2"/>
       <c r="J423" s="18"/>
@@ -27801,7 +27796,7 @@
         <v>99</v>
       </c>
       <c r="B424" s="54" t="s">
-        <v>2265</v>
+        <v>2229</v>
       </c>
       <c r="C424" s="54"/>
       <c r="D424" s="54"/>
@@ -27823,23 +27818,23 @@
         <v>100</v>
       </c>
       <c r="B425" s="54" t="s">
-        <v>2266</v>
+        <v>2230</v>
       </c>
       <c r="C425" s="54"/>
       <c r="D425" s="54" t="s">
-        <v>2164</v>
+        <v>2128</v>
       </c>
       <c r="E425" s="54" t="s">
-        <v>2165</v>
+        <v>2129</v>
       </c>
       <c r="F425" s="54" t="s">
-        <v>2166</v>
+        <v>2130</v>
       </c>
       <c r="G425" s="54" t="s">
-        <v>2167</v>
+        <v>2131</v>
       </c>
       <c r="H425" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I425" s="2"/>
       <c r="J425" s="18"/>
@@ -27853,23 +27848,23 @@
         <v>100</v>
       </c>
       <c r="B426" s="54" t="s">
-        <v>2267</v>
+        <v>2231</v>
       </c>
       <c r="C426" s="54"/>
       <c r="D426" s="54" t="s">
-        <v>2168</v>
+        <v>2132</v>
       </c>
       <c r="E426" s="54" t="s">
-        <v>2169</v>
+        <v>2133</v>
       </c>
       <c r="F426" s="54" t="s">
-        <v>2170</v>
+        <v>2134</v>
       </c>
       <c r="G426" s="54" t="s">
-        <v>2171</v>
+        <v>2135</v>
       </c>
       <c r="H426" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I426" s="2"/>
       <c r="J426" s="18"/>
@@ -27883,23 +27878,23 @@
         <v>100</v>
       </c>
       <c r="B427" s="54" t="s">
-        <v>2268</v>
+        <v>2232</v>
       </c>
       <c r="C427" s="54"/>
       <c r="D427" s="54" t="s">
-        <v>2172</v>
+        <v>2136</v>
       </c>
       <c r="E427" s="54" t="s">
-        <v>2173</v>
+        <v>2137</v>
       </c>
       <c r="F427" s="54" t="s">
-        <v>2174</v>
+        <v>2138</v>
       </c>
       <c r="G427" s="54" t="s">
-        <v>2175</v>
+        <v>2139</v>
       </c>
       <c r="H427" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I427" s="2"/>
       <c r="J427" s="18"/>
@@ -27913,23 +27908,23 @@
         <v>100</v>
       </c>
       <c r="B428" s="54" t="s">
-        <v>2269</v>
+        <v>2233</v>
       </c>
       <c r="C428" s="54"/>
       <c r="D428" s="54" t="s">
-        <v>2176</v>
+        <v>2140</v>
       </c>
       <c r="E428" s="54" t="s">
-        <v>2177</v>
+        <v>2141</v>
       </c>
       <c r="F428" s="54" t="s">
-        <v>2178</v>
+        <v>2142</v>
       </c>
       <c r="G428" s="54" t="s">
-        <v>2179</v>
+        <v>2143</v>
       </c>
       <c r="H428" s="55" t="s">
-        <v>2151</v>
+        <v>2115</v>
       </c>
       <c r="I428" s="2"/>
       <c r="J428" s="18"/>
@@ -27943,7 +27938,7 @@
         <v>99</v>
       </c>
       <c r="B429" s="54" t="s">
-        <v>2270</v>
+        <v>2234</v>
       </c>
       <c r="C429" s="54"/>
       <c r="D429" s="54"/>
@@ -27965,23 +27960,23 @@
         <v>100</v>
       </c>
       <c r="B430" s="54" t="s">
-        <v>2271</v>
+        <v>2235</v>
       </c>
       <c r="C430" s="54"/>
       <c r="D430" s="54" t="s">
-        <v>2180</v>
+        <v>2144</v>
       </c>
       <c r="E430" s="54" t="s">
-        <v>2181</v>
+        <v>2145</v>
       </c>
       <c r="F430" s="54" t="s">
-        <v>2182</v>
+        <v>2146</v>
       </c>
       <c r="G430" s="54" t="s">
-        <v>2183</v>
+        <v>2147</v>
       </c>
       <c r="H430" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I430" s="2"/>
       <c r="J430" s="18"/>
@@ -27995,11 +27990,11 @@
         <v>100</v>
       </c>
       <c r="B431" s="54" t="s">
-        <v>2272</v>
+        <v>2236</v>
       </c>
       <c r="C431" s="54"/>
       <c r="D431" s="56" t="s">
-        <v>2185</v>
+        <v>2149</v>
       </c>
       <c r="E431" s="56">
         <v>37</v>
@@ -28011,7 +28006,7 @@
         <v>13516</v>
       </c>
       <c r="H431" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I431" s="2"/>
       <c r="J431" s="18"/>
@@ -28025,23 +28020,23 @@
         <v>100</v>
       </c>
       <c r="B432" s="54" t="s">
-        <v>2273</v>
+        <v>2237</v>
       </c>
       <c r="C432" s="54"/>
       <c r="D432" s="54" t="s">
-        <v>2186</v>
+        <v>2150</v>
       </c>
       <c r="E432" s="54" t="s">
-        <v>2187</v>
+        <v>2151</v>
       </c>
       <c r="F432" s="54" t="s">
-        <v>2188</v>
+        <v>2152</v>
       </c>
       <c r="G432" s="54" t="s">
-        <v>2189</v>
+        <v>2153</v>
       </c>
       <c r="H432" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I432" s="2"/>
       <c r="J432" s="18"/>
@@ -28055,7 +28050,7 @@
         <v>100</v>
       </c>
       <c r="B433" s="54" t="s">
-        <v>2274</v>
+        <v>2238</v>
       </c>
       <c r="C433" s="54"/>
       <c r="D433" s="56">
@@ -28068,10 +28063,10 @@
         <v>43</v>
       </c>
       <c r="G433" s="56" t="s">
-        <v>2190</v>
+        <v>2154</v>
       </c>
       <c r="H433" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I433" s="2"/>
       <c r="J433" s="18"/>
@@ -28085,7 +28080,7 @@
         <v>99</v>
       </c>
       <c r="B434" s="54" t="s">
-        <v>2275</v>
+        <v>2239</v>
       </c>
       <c r="C434" s="54"/>
       <c r="D434" s="54"/>
@@ -28107,23 +28102,23 @@
         <v>100</v>
       </c>
       <c r="B435" s="54" t="s">
-        <v>2276</v>
+        <v>2240</v>
       </c>
       <c r="C435" s="54"/>
       <c r="D435" s="54" t="s">
-        <v>2191</v>
+        <v>2155</v>
       </c>
       <c r="E435" s="54" t="s">
-        <v>2192</v>
+        <v>2156</v>
       </c>
       <c r="F435" s="54" t="s">
-        <v>2193</v>
+        <v>2157</v>
       </c>
       <c r="G435" s="54" t="s">
-        <v>2194</v>
+        <v>2158</v>
       </c>
       <c r="H435" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I435" s="2"/>
       <c r="J435" s="18"/>
@@ -28137,23 +28132,23 @@
         <v>100</v>
       </c>
       <c r="B436" s="54" t="s">
-        <v>2277</v>
+        <v>2241</v>
       </c>
       <c r="C436" s="54"/>
       <c r="D436" s="56" t="s">
-        <v>2010</v>
+        <v>1974</v>
       </c>
       <c r="E436" s="56">
         <v>1</v>
       </c>
       <c r="F436" s="56" t="s">
-        <v>2195</v>
+        <v>2159</v>
       </c>
       <c r="G436" s="56" t="s">
-        <v>2196</v>
+        <v>2160</v>
       </c>
       <c r="H436" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I436" s="2"/>
       <c r="J436" s="18"/>
@@ -28167,23 +28162,23 @@
         <v>98</v>
       </c>
       <c r="B437" s="54" t="s">
-        <v>2278</v>
+        <v>2242</v>
       </c>
       <c r="C437" s="54"/>
       <c r="D437" s="54" t="s">
-        <v>2197</v>
+        <v>2161</v>
       </c>
       <c r="E437" s="54" t="s">
-        <v>2198</v>
+        <v>2162</v>
       </c>
       <c r="F437" s="54" t="s">
-        <v>2199</v>
+        <v>2163</v>
       </c>
       <c r="G437" s="54" t="s">
-        <v>2200</v>
+        <v>2164</v>
       </c>
       <c r="H437" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I437" s="2"/>
       <c r="J437" s="18" t="s">
@@ -28201,23 +28196,23 @@
         <v>98</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2279</v>
+        <v>2243</v>
       </c>
       <c r="C438" s="54"/>
       <c r="D438" s="54" t="s">
-        <v>2202</v>
+        <v>2166</v>
       </c>
       <c r="E438" s="54" t="s">
-        <v>2203</v>
+        <v>2167</v>
       </c>
       <c r="F438" s="54" t="s">
-        <v>2204</v>
+        <v>2168</v>
       </c>
       <c r="G438" s="54" t="s">
-        <v>2205</v>
+        <v>2169</v>
       </c>
       <c r="H438" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I438" s="2"/>
       <c r="J438" s="18" t="s">
@@ -28235,23 +28230,23 @@
         <v>98</v>
       </c>
       <c r="B439" s="54" t="s">
-        <v>2280</v>
+        <v>2244</v>
       </c>
       <c r="C439" s="54"/>
       <c r="D439" s="54" t="s">
-        <v>2206</v>
+        <v>2170</v>
       </c>
       <c r="E439" s="54" t="s">
-        <v>2207</v>
+        <v>2171</v>
       </c>
       <c r="F439" s="54" t="s">
-        <v>2208</v>
+        <v>2172</v>
       </c>
       <c r="G439" s="54" t="s">
-        <v>2209</v>
+        <v>2173</v>
       </c>
       <c r="H439" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I439" s="2"/>
       <c r="J439" s="18" t="s">
@@ -28269,23 +28264,23 @@
         <v>98</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2281</v>
+        <v>2245</v>
       </c>
       <c r="C440" s="54"/>
       <c r="D440" s="54" t="s">
-        <v>2210</v>
+        <v>2174</v>
       </c>
       <c r="E440" s="54" t="s">
-        <v>2211</v>
+        <v>2175</v>
       </c>
       <c r="F440" s="54" t="s">
-        <v>2212</v>
+        <v>2176</v>
       </c>
       <c r="G440" s="54" t="s">
-        <v>2213</v>
+        <v>2177</v>
       </c>
       <c r="H440" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I440" s="2"/>
       <c r="J440" s="18" t="s">
@@ -28303,23 +28298,23 @@
         <v>98</v>
       </c>
       <c r="B441" s="54" t="s">
-        <v>2282</v>
+        <v>2246</v>
       </c>
       <c r="C441" s="54"/>
       <c r="D441" s="54" t="s">
-        <v>2214</v>
+        <v>2178</v>
       </c>
       <c r="E441" s="54" t="s">
-        <v>2215</v>
+        <v>2179</v>
       </c>
       <c r="F441" s="54" t="s">
-        <v>2216</v>
+        <v>2180</v>
       </c>
       <c r="G441" s="54" t="s">
-        <v>2217</v>
+        <v>2181</v>
       </c>
       <c r="H441" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I441" s="2"/>
       <c r="J441" s="18" t="s">
@@ -28337,23 +28332,23 @@
         <v>98</v>
       </c>
       <c r="B442" s="54" t="s">
-        <v>2283</v>
+        <v>2247</v>
       </c>
       <c r="C442" s="54"/>
       <c r="D442" s="54" t="s">
-        <v>2218</v>
+        <v>2182</v>
       </c>
       <c r="E442" s="54" t="s">
-        <v>2219</v>
+        <v>2183</v>
       </c>
       <c r="F442" s="54" t="s">
-        <v>2220</v>
+        <v>2184</v>
       </c>
       <c r="G442" s="54" t="s">
-        <v>2221</v>
+        <v>2185</v>
       </c>
       <c r="H442" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I442" s="2"/>
       <c r="J442" s="18" t="s">
@@ -28371,23 +28366,23 @@
         <v>98</v>
       </c>
       <c r="B443" s="54" t="s">
-        <v>2284</v>
+        <v>2248</v>
       </c>
       <c r="C443" s="54"/>
       <c r="D443" s="54" t="s">
-        <v>2222</v>
+        <v>2186</v>
       </c>
       <c r="E443" s="54" t="s">
-        <v>2223</v>
+        <v>2187</v>
       </c>
       <c r="F443" s="54" t="s">
-        <v>2224</v>
+        <v>2188</v>
       </c>
       <c r="G443" s="54" t="s">
-        <v>2225</v>
+        <v>2189</v>
       </c>
       <c r="H443" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I443" s="2"/>
       <c r="J443" s="18" t="s">
@@ -28405,23 +28400,23 @@
         <v>98</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2285</v>
+        <v>2249</v>
       </c>
       <c r="C444" s="54"/>
       <c r="D444" s="54" t="s">
-        <v>2226</v>
+        <v>2190</v>
       </c>
       <c r="E444" s="54" t="s">
-        <v>2227</v>
+        <v>2191</v>
       </c>
       <c r="F444" s="54" t="s">
-        <v>2228</v>
+        <v>2192</v>
       </c>
       <c r="G444" s="54" t="s">
-        <v>2229</v>
+        <v>2193</v>
       </c>
       <c r="H444" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I444" s="2"/>
       <c r="J444" s="18" t="s">
@@ -28439,7 +28434,7 @@
         <v>99</v>
       </c>
       <c r="B445" s="54" t="s">
-        <v>2230</v>
+        <v>2194</v>
       </c>
       <c r="C445" s="54"/>
       <c r="D445" s="54"/>
@@ -28461,23 +28456,23 @@
         <v>100</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2286</v>
+        <v>2250</v>
       </c>
       <c r="C446" s="54"/>
       <c r="D446" s="54" t="s">
-        <v>2231</v>
+        <v>2195</v>
       </c>
       <c r="E446" s="54" t="s">
-        <v>2232</v>
+        <v>2196</v>
       </c>
       <c r="F446" s="54" t="s">
-        <v>2233</v>
+        <v>2197</v>
       </c>
       <c r="G446" s="54" t="s">
-        <v>2234</v>
+        <v>2198</v>
       </c>
       <c r="H446" s="55" t="s">
-        <v>2235</v>
+        <v>2199</v>
       </c>
       <c r="I446" s="2"/>
       <c r="J446" s="18"/>
@@ -28491,23 +28486,23 @@
         <v>100</v>
       </c>
       <c r="B447" s="54" t="s">
-        <v>2287</v>
+        <v>2251</v>
       </c>
       <c r="C447" s="54"/>
       <c r="D447" s="54" t="s">
-        <v>2236</v>
+        <v>2200</v>
       </c>
       <c r="E447" s="54" t="s">
-        <v>2237</v>
+        <v>2201</v>
       </c>
       <c r="F447" s="54" t="s">
-        <v>2238</v>
+        <v>2202</v>
       </c>
       <c r="G447" s="54" t="s">
-        <v>2239</v>
+        <v>2203</v>
       </c>
       <c r="H447" s="54" t="s">
-        <v>2240</v>
+        <v>2204</v>
       </c>
       <c r="I447" s="2"/>
       <c r="J447" s="18"/>
@@ -28521,23 +28516,23 @@
         <v>100</v>
       </c>
       <c r="B448" s="54" t="s">
-        <v>2288</v>
+        <v>2252</v>
       </c>
       <c r="C448" s="54"/>
       <c r="D448" s="54" t="s">
-        <v>2241</v>
+        <v>2205</v>
       </c>
       <c r="E448" s="54" t="s">
-        <v>2242</v>
+        <v>2206</v>
       </c>
       <c r="F448" s="54" t="s">
-        <v>2243</v>
+        <v>2207</v>
       </c>
       <c r="G448" s="54" t="s">
-        <v>2244</v>
+        <v>2208</v>
       </c>
       <c r="H448" s="55" t="s">
-        <v>2201</v>
+        <v>2165</v>
       </c>
       <c r="I448" s="2"/>
       <c r="J448" s="18"/>
@@ -28551,7 +28546,7 @@
         <v>99</v>
       </c>
       <c r="B449" s="54" t="s">
-        <v>2245</v>
+        <v>2209</v>
       </c>
       <c r="C449" s="54"/>
       <c r="D449" s="54"/>
@@ -28573,23 +28568,23 @@
         <v>100</v>
       </c>
       <c r="B450" s="54" t="s">
-        <v>2289</v>
+        <v>2253</v>
       </c>
       <c r="C450" s="54"/>
       <c r="D450" s="54" t="s">
-        <v>2246</v>
+        <v>2210</v>
       </c>
       <c r="E450" s="54" t="s">
-        <v>2247</v>
+        <v>2211</v>
       </c>
       <c r="F450" s="54" t="s">
-        <v>2248</v>
+        <v>2212</v>
       </c>
       <c r="G450" s="54" t="s">
-        <v>2249</v>
+        <v>2213</v>
       </c>
       <c r="H450" s="55" t="s">
-        <v>2250</v>
+        <v>2214</v>
       </c>
       <c r="I450" s="2"/>
       <c r="J450" s="18"/>
@@ -28603,23 +28598,23 @@
         <v>100</v>
       </c>
       <c r="B451" s="54" t="s">
-        <v>2290</v>
+        <v>2254</v>
       </c>
       <c r="C451" s="54"/>
       <c r="D451" s="54" t="s">
-        <v>2251</v>
+        <v>2215</v>
       </c>
       <c r="E451" s="54" t="s">
-        <v>2252</v>
+        <v>2216</v>
       </c>
       <c r="F451" s="54" t="s">
-        <v>2253</v>
+        <v>2217</v>
       </c>
       <c r="G451" s="54" t="s">
-        <v>2254</v>
+        <v>2218</v>
       </c>
       <c r="H451" s="55" t="s">
-        <v>2184</v>
+        <v>2148</v>
       </c>
       <c r="I451" s="2"/>
       <c r="J451" s="18"/>
@@ -28633,23 +28628,23 @@
         <v>100</v>
       </c>
       <c r="B452" s="54" t="s">
-        <v>2291</v>
+        <v>2255</v>
       </c>
       <c r="C452" s="54"/>
       <c r="D452" s="54" t="s">
-        <v>2255</v>
+        <v>2219</v>
       </c>
       <c r="E452" s="54" t="s">
-        <v>2256</v>
+        <v>2220</v>
       </c>
       <c r="F452" s="54" t="s">
-        <v>2257</v>
+        <v>2221</v>
       </c>
       <c r="G452" s="54" t="s">
-        <v>2258</v>
+        <v>2222</v>
       </c>
       <c r="H452" s="54" t="s">
-        <v>2259</v>
+        <v>2223</v>
       </c>
       <c r="I452" s="2"/>
       <c r="J452" s="18"/>
@@ -29167,7 +29162,7 @@
         <v>100</v>
       </c>
       <c r="B467" s="17" t="s">
-        <v>1344</v>
+        <v>1308</v>
       </c>
       <c r="C467" s="2"/>
       <c r="D467" s="13" t="s">
@@ -29199,30 +29194,30 @@
         <v>98</v>
       </c>
       <c r="B468" s="44" t="s">
-        <v>1357</v>
+        <v>1321</v>
       </c>
       <c r="C468" s="2"/>
       <c r="D468" s="44" t="s">
-        <v>1367</v>
+        <v>1331</v>
       </c>
       <c r="E468" s="44" t="s">
-        <v>1368</v>
+        <v>1332</v>
       </c>
       <c r="F468" s="44" t="s">
-        <v>1369</v>
+        <v>1333</v>
       </c>
       <c r="G468" s="44" t="s">
-        <v>1370</v>
+        <v>1334</v>
       </c>
       <c r="H468" s="44" t="s">
-        <v>1371</v>
+        <v>1335</v>
       </c>
       <c r="I468" s="2"/>
       <c r="J468" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K468" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L468" s="18">
         <v>1</v>
@@ -29233,30 +29228,30 @@
         <v>98</v>
       </c>
       <c r="B469" s="45" t="s">
-        <v>1358</v>
+        <v>1322</v>
       </c>
       <c r="C469" s="2"/>
       <c r="D469" s="45" t="s">
-        <v>1372</v>
+        <v>1336</v>
       </c>
       <c r="E469" s="45" t="s">
-        <v>1373</v>
+        <v>1337</v>
       </c>
       <c r="F469" s="45" t="s">
-        <v>1374</v>
+        <v>1338</v>
       </c>
       <c r="G469" s="45" t="s">
-        <v>1375</v>
+        <v>1339</v>
       </c>
       <c r="H469" s="45" t="s">
-        <v>1376</v>
+        <v>1340</v>
       </c>
       <c r="I469" s="2"/>
       <c r="J469" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K469" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L469" s="18">
         <v>1</v>
@@ -29267,30 +29262,30 @@
         <v>98</v>
       </c>
       <c r="B470" s="44" t="s">
-        <v>1359</v>
+        <v>1323</v>
       </c>
       <c r="C470" s="2"/>
       <c r="D470" s="44" t="s">
-        <v>1377</v>
+        <v>1341</v>
       </c>
       <c r="E470" s="44" t="s">
-        <v>1378</v>
+        <v>1342</v>
       </c>
       <c r="F470" s="44" t="s">
-        <v>1379</v>
+        <v>1343</v>
       </c>
       <c r="G470" s="44" t="s">
-        <v>1380</v>
+        <v>1344</v>
       </c>
       <c r="H470" s="44" t="s">
-        <v>1381</v>
+        <v>1345</v>
       </c>
       <c r="I470" s="2"/>
       <c r="J470" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K470" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L470" s="18">
         <v>1</v>
@@ -29301,30 +29296,30 @@
         <v>98</v>
       </c>
       <c r="B471" s="45" t="s">
-        <v>1360</v>
+        <v>1324</v>
       </c>
       <c r="C471" s="2"/>
       <c r="D471" s="45" t="s">
-        <v>1382</v>
+        <v>1346</v>
       </c>
       <c r="E471" s="45" t="s">
-        <v>1383</v>
+        <v>1347</v>
       </c>
       <c r="F471" s="45" t="s">
-        <v>1384</v>
+        <v>1348</v>
       </c>
       <c r="G471" s="45" t="s">
-        <v>1385</v>
+        <v>1349</v>
       </c>
       <c r="H471" s="45" t="s">
-        <v>1386</v>
+        <v>1350</v>
       </c>
       <c r="I471" s="2"/>
       <c r="J471" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K471" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L471" s="18">
         <v>1</v>
@@ -29335,30 +29330,30 @@
         <v>98</v>
       </c>
       <c r="B472" s="44" t="s">
-        <v>1361</v>
+        <v>1325</v>
       </c>
       <c r="C472" s="2"/>
       <c r="D472" s="44" t="s">
-        <v>1387</v>
+        <v>1351</v>
       </c>
       <c r="E472" s="44" t="s">
-        <v>1388</v>
+        <v>1352</v>
       </c>
       <c r="F472" s="44" t="s">
-        <v>1389</v>
+        <v>1353</v>
       </c>
       <c r="G472" s="44" t="s">
-        <v>1390</v>
+        <v>1354</v>
       </c>
       <c r="H472" s="44" t="s">
-        <v>1391</v>
+        <v>1355</v>
       </c>
       <c r="I472" s="2"/>
       <c r="J472" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K472" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L472" s="18">
         <v>1</v>
@@ -29369,30 +29364,30 @@
         <v>98</v>
       </c>
       <c r="B473" s="45" t="s">
-        <v>1362</v>
+        <v>1326</v>
       </c>
       <c r="C473" s="2"/>
       <c r="D473" s="45" t="s">
-        <v>1392</v>
+        <v>1356</v>
       </c>
       <c r="E473" s="45" t="s">
-        <v>1393</v>
+        <v>1357</v>
       </c>
       <c r="F473" s="45" t="s">
-        <v>1394</v>
+        <v>1358</v>
       </c>
       <c r="G473" s="45" t="s">
-        <v>1395</v>
+        <v>1359</v>
       </c>
       <c r="H473" s="45" t="s">
-        <v>1396</v>
+        <v>1360</v>
       </c>
       <c r="I473" s="2"/>
       <c r="J473" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K473" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L473" s="18">
         <v>1</v>
@@ -29403,30 +29398,30 @@
         <v>98</v>
       </c>
       <c r="B474" s="44" t="s">
-        <v>1363</v>
+        <v>1327</v>
       </c>
       <c r="C474" s="2"/>
       <c r="D474" s="44" t="s">
-        <v>1397</v>
+        <v>1361</v>
       </c>
       <c r="E474" s="44" t="s">
-        <v>1398</v>
+        <v>1362</v>
       </c>
       <c r="F474" s="44" t="s">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="G474" s="44" t="s">
-        <v>1400</v>
+        <v>1364</v>
       </c>
       <c r="H474" s="44" t="s">
-        <v>1401</v>
+        <v>1365</v>
       </c>
       <c r="I474" s="2"/>
       <c r="J474" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K474" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L474" s="18">
         <v>1</v>
@@ -29437,30 +29432,30 @@
         <v>98</v>
       </c>
       <c r="B475" s="45" t="s">
-        <v>1364</v>
+        <v>1328</v>
       </c>
       <c r="C475" s="2"/>
       <c r="D475" s="45" t="s">
-        <v>1402</v>
+        <v>1366</v>
       </c>
       <c r="E475" s="45" t="s">
-        <v>1403</v>
+        <v>1367</v>
       </c>
       <c r="F475" s="45" t="s">
-        <v>1404</v>
+        <v>1368</v>
       </c>
       <c r="G475" s="45" t="s">
-        <v>1405</v>
+        <v>1369</v>
       </c>
       <c r="H475" s="45" t="s">
-        <v>1406</v>
+        <v>1370</v>
       </c>
       <c r="I475" s="2"/>
       <c r="J475" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K475" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L475" s="18">
         <v>1</v>
@@ -29471,30 +29466,30 @@
         <v>98</v>
       </c>
       <c r="B476" s="44" t="s">
-        <v>1365</v>
+        <v>1329</v>
       </c>
       <c r="C476" s="2"/>
       <c r="D476" s="44" t="s">
-        <v>1407</v>
+        <v>1371</v>
       </c>
       <c r="E476" s="44" t="s">
-        <v>1374</v>
+        <v>1338</v>
       </c>
       <c r="F476" s="44" t="s">
-        <v>1376</v>
+        <v>1340</v>
       </c>
       <c r="G476" s="44" t="s">
-        <v>1408</v>
+        <v>1372</v>
       </c>
       <c r="H476" s="44" t="s">
-        <v>1373</v>
+        <v>1337</v>
       </c>
       <c r="I476" s="2"/>
       <c r="J476" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K476" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L476" s="18">
         <v>1</v>
@@ -29505,30 +29500,30 @@
         <v>98</v>
       </c>
       <c r="B477" s="45" t="s">
-        <v>1366</v>
+        <v>1330</v>
       </c>
       <c r="C477" s="2"/>
       <c r="D477" s="45" t="s">
-        <v>1409</v>
+        <v>1373</v>
       </c>
       <c r="E477" s="45" t="s">
-        <v>1410</v>
+        <v>1374</v>
       </c>
       <c r="F477" s="45" t="s">
-        <v>1411</v>
+        <v>1375</v>
       </c>
       <c r="G477" s="45" t="s">
-        <v>1412</v>
+        <v>1376</v>
       </c>
       <c r="H477" s="45" t="s">
-        <v>1413</v>
+        <v>1377</v>
       </c>
       <c r="I477" s="2"/>
       <c r="J477" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K477" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L477" s="18">
         <v>1</v>
@@ -29539,7 +29534,7 @@
         <v>99</v>
       </c>
       <c r="B478" s="44" t="s">
-        <v>2017</v>
+        <v>1981</v>
       </c>
       <c r="C478" s="2"/>
       <c r="D478" s="2"/>
@@ -29552,7 +29547,7 @@
         <v>11</v>
       </c>
       <c r="K478" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L478" s="18"/>
     </row>
@@ -29561,23 +29556,23 @@
         <v>100</v>
       </c>
       <c r="B479" s="44" t="s">
-        <v>2018</v>
+        <v>1982</v>
       </c>
       <c r="C479" s="2"/>
       <c r="D479" s="44" t="s">
-        <v>2019</v>
+        <v>1983</v>
       </c>
       <c r="E479" s="44" t="s">
-        <v>2020</v>
+        <v>1984</v>
       </c>
       <c r="F479" s="44" t="s">
-        <v>2021</v>
+        <v>1985</v>
       </c>
       <c r="G479" s="44" t="s">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="H479" s="44" t="s">
-        <v>2023</v>
+        <v>1987</v>
       </c>
       <c r="I479" s="2"/>
       <c r="J479" s="18"/>
@@ -29591,7 +29586,7 @@
         <v>99</v>
       </c>
       <c r="B480" s="45" t="s">
-        <v>2026</v>
+        <v>1990</v>
       </c>
       <c r="C480" s="2"/>
       <c r="D480" s="2"/>
@@ -29604,7 +29599,7 @@
         <v>11</v>
       </c>
       <c r="K480" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L480" s="18"/>
     </row>
@@ -29613,23 +29608,23 @@
         <v>100</v>
       </c>
       <c r="B481" s="45" t="s">
-        <v>2024</v>
+        <v>1988</v>
       </c>
       <c r="C481" s="2"/>
       <c r="D481" s="45" t="s">
-        <v>2025</v>
+        <v>1989</v>
       </c>
       <c r="E481" s="45" t="s">
-        <v>2027</v>
+        <v>1991</v>
       </c>
       <c r="F481" s="45" t="s">
-        <v>2028</v>
+        <v>1992</v>
       </c>
       <c r="G481" s="45" t="s">
-        <v>2029</v>
+        <v>1993</v>
       </c>
       <c r="H481" s="45" t="s">
-        <v>2030</v>
+        <v>1994</v>
       </c>
       <c r="I481" s="2"/>
       <c r="J481" s="18"/>
@@ -29643,30 +29638,30 @@
         <v>98</v>
       </c>
       <c r="B482" s="44" t="s">
-        <v>2031</v>
+        <v>1995</v>
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="44" t="s">
-        <v>2032</v>
+        <v>1996</v>
       </c>
       <c r="E482" s="44" t="s">
-        <v>2033</v>
+        <v>1997</v>
       </c>
       <c r="F482" s="44" t="s">
-        <v>2034</v>
+        <v>1998</v>
       </c>
       <c r="G482" s="44" t="s">
-        <v>2035</v>
+        <v>1999</v>
       </c>
       <c r="H482" s="44" t="s">
-        <v>2036</v>
+        <v>2000</v>
       </c>
       <c r="I482" s="2"/>
       <c r="J482" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K482" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L482" s="18">
         <v>1</v>
@@ -29677,7 +29672,7 @@
         <v>99</v>
       </c>
       <c r="B483" s="45" t="s">
-        <v>2037</v>
+        <v>2001</v>
       </c>
       <c r="C483" s="2"/>
       <c r="D483" s="2"/>
@@ -29690,7 +29685,7 @@
         <v>11</v>
       </c>
       <c r="K483" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L483" s="18"/>
     </row>
@@ -29699,23 +29694,23 @@
         <v>100</v>
       </c>
       <c r="B484" s="45" t="s">
-        <v>2038</v>
+        <v>2002</v>
       </c>
       <c r="C484" s="2"/>
       <c r="D484" s="45" t="s">
-        <v>2054</v>
+        <v>2018</v>
       </c>
       <c r="E484" s="45" t="s">
-        <v>2050</v>
+        <v>2014</v>
       </c>
       <c r="F484" s="45" t="s">
-        <v>2051</v>
+        <v>2015</v>
       </c>
       <c r="G484" s="45" t="s">
-        <v>2052</v>
+        <v>2016</v>
       </c>
       <c r="H484" s="45" t="s">
-        <v>2053</v>
+        <v>2017</v>
       </c>
       <c r="I484" s="2"/>
       <c r="J484" s="18"/>
@@ -29729,30 +29724,30 @@
         <v>98</v>
       </c>
       <c r="B485" s="44" t="s">
-        <v>2039</v>
+        <v>2003</v>
       </c>
       <c r="C485" s="2"/>
       <c r="D485" s="44" t="s">
-        <v>2055</v>
+        <v>2019</v>
       </c>
       <c r="E485" s="44" t="s">
-        <v>2056</v>
+        <v>2020</v>
       </c>
       <c r="F485" s="44" t="s">
-        <v>2057</v>
+        <v>2021</v>
       </c>
       <c r="G485" s="44" t="s">
-        <v>2058</v>
+        <v>2022</v>
       </c>
       <c r="H485" s="44" t="s">
-        <v>2059</v>
+        <v>2023</v>
       </c>
       <c r="I485" s="2"/>
       <c r="J485" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K485" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L485" s="18">
         <v>1</v>
@@ -29763,30 +29758,30 @@
         <v>98</v>
       </c>
       <c r="B486" s="45" t="s">
-        <v>2040</v>
+        <v>2004</v>
       </c>
       <c r="C486" s="2"/>
       <c r="D486" s="45" t="s">
-        <v>2060</v>
+        <v>2024</v>
       </c>
       <c r="E486" s="45" t="s">
-        <v>2061</v>
+        <v>2025</v>
       </c>
       <c r="F486" s="45" t="s">
-        <v>2062</v>
+        <v>2026</v>
       </c>
       <c r="G486" s="45" t="s">
-        <v>2063</v>
+        <v>2027</v>
       </c>
       <c r="H486" s="45" t="s">
-        <v>1129</v>
+        <v>1100</v>
       </c>
       <c r="I486" s="2"/>
       <c r="J486" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K486" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L486" s="18">
         <v>1</v>
@@ -29797,7 +29792,7 @@
         <v>99</v>
       </c>
       <c r="B487" s="44" t="s">
-        <v>2041</v>
+        <v>2005</v>
       </c>
       <c r="C487" s="2"/>
       <c r="D487" s="2"/>
@@ -29810,7 +29805,7 @@
         <v>11</v>
       </c>
       <c r="K487" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L487" s="18"/>
     </row>
@@ -29819,23 +29814,23 @@
         <v>100</v>
       </c>
       <c r="B488" s="44" t="s">
-        <v>2042</v>
+        <v>2006</v>
       </c>
       <c r="C488" s="2"/>
       <c r="D488" s="44" t="s">
-        <v>2064</v>
+        <v>2028</v>
       </c>
       <c r="E488" s="44" t="s">
-        <v>2065</v>
+        <v>2029</v>
       </c>
       <c r="F488" s="44" t="s">
-        <v>2066</v>
+        <v>2030</v>
       </c>
       <c r="G488" s="44" t="s">
-        <v>2067</v>
+        <v>2031</v>
       </c>
       <c r="H488" s="44" t="s">
-        <v>2068</v>
+        <v>2032</v>
       </c>
       <c r="I488" s="2"/>
       <c r="J488" s="18"/>
@@ -29849,30 +29844,30 @@
         <v>98</v>
       </c>
       <c r="B489" s="45" t="s">
-        <v>2043</v>
+        <v>2007</v>
       </c>
       <c r="C489" s="2"/>
       <c r="D489" s="45" t="s">
-        <v>2069</v>
+        <v>2033</v>
       </c>
       <c r="E489" s="45" t="s">
-        <v>2070</v>
+        <v>2034</v>
       </c>
       <c r="F489" s="45" t="s">
-        <v>2071</v>
+        <v>2035</v>
       </c>
       <c r="G489" s="45" t="s">
-        <v>2072</v>
+        <v>2036</v>
       </c>
       <c r="H489" s="45" t="s">
-        <v>2073</v>
+        <v>2037</v>
       </c>
       <c r="I489" s="2"/>
       <c r="J489" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K489" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L489" s="18">
         <v>1</v>
@@ -29883,7 +29878,7 @@
         <v>99</v>
       </c>
       <c r="B490" s="44" t="s">
-        <v>2044</v>
+        <v>2008</v>
       </c>
       <c r="C490" s="2"/>
       <c r="D490" s="2"/>
@@ -29896,7 +29891,7 @@
         <v>11</v>
       </c>
       <c r="K490" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L490" s="18"/>
     </row>
@@ -29905,23 +29900,23 @@
         <v>100</v>
       </c>
       <c r="B491" s="44" t="s">
-        <v>2045</v>
+        <v>2009</v>
       </c>
       <c r="C491" s="2"/>
       <c r="D491" s="44" t="s">
-        <v>2074</v>
+        <v>2038</v>
       </c>
       <c r="E491" s="44" t="s">
-        <v>2075</v>
+        <v>2039</v>
       </c>
       <c r="F491" s="44" t="s">
-        <v>2076</v>
+        <v>2040</v>
       </c>
       <c r="G491" s="44" t="s">
-        <v>2077</v>
+        <v>2041</v>
       </c>
       <c r="H491" s="44" t="s">
-        <v>2078</v>
+        <v>2042</v>
       </c>
       <c r="I491" s="2"/>
       <c r="J491" s="18"/>
@@ -29935,7 +29930,7 @@
         <v>99</v>
       </c>
       <c r="B492" s="45" t="s">
-        <v>2046</v>
+        <v>2010</v>
       </c>
       <c r="C492" s="2"/>
       <c r="D492" s="2"/>
@@ -29948,7 +29943,7 @@
         <v>11</v>
       </c>
       <c r="K492" s="18" t="s">
-        <v>2377</v>
+        <v>2341</v>
       </c>
       <c r="L492" s="18"/>
     </row>
@@ -29957,23 +29952,23 @@
         <v>100</v>
       </c>
       <c r="B493" s="45" t="s">
-        <v>2047</v>
+        <v>2011</v>
       </c>
       <c r="C493" s="2"/>
       <c r="D493" s="45" t="s">
-        <v>1372</v>
+        <v>1336</v>
       </c>
       <c r="E493" s="45" t="s">
-        <v>2048</v>
+        <v>2012</v>
       </c>
       <c r="F493" s="45" t="s">
-        <v>1407</v>
+        <v>1371</v>
       </c>
       <c r="G493" s="45" t="s">
-        <v>1374</v>
+        <v>1338</v>
       </c>
       <c r="H493" s="45" t="s">
-        <v>2049</v>
+        <v>2013</v>
       </c>
       <c r="I493" s="2"/>
       <c r="J493" s="18"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346D59CD-E175-4AE1-9B54-35E93DB379C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C23BBA-A041-49A8-A17E-9B8E6ED949C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13271,14 +13271,6 @@
 &lt;br&gt;&lt;br&gt;Le pourcentage des individus présentant le caractère dominant à la génération suivante est :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Propagation d'une onde le long d'une corde (5 points)&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt;Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $v$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 s$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.
-&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
-    &lt;img src="/images/M21F1.png" alt="A" class="h-20" /&gt;
-    &lt;img src="/images/M21F2.png" alt="B" class="h-20" /&gt;
-&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>(A) : $\lambda=0,40 \mathrm{~m}$ $\quad$ $v=0,25 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
   </si>
   <si>
@@ -13392,6 +13384,20 @@
   </si>
   <si>
     <t>(E) : $U_{C_{2}}=57 \% E$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Propagation d'une onde le long d'une corde (5 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $v$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 s$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.
+&lt;table style="width: 100%; border-collapse: collapse;"&gt;
+  &lt;tr&gt;
+    &lt;td style="text-align: right; padding-right: 10px;"&gt;
+      &lt;img src="/images/M21F1.png" alt="A" style="height: 80px;" /&gt;
+    &lt;/td&gt;
+    &lt;td style="text-align: right; width: 1px;"&gt;
+      &lt;img src="/images/M21F2_2.png" alt="B" style="height: 80px;" /&gt;
+    &lt;/td&gt;
+  &lt;/tr&gt;
+&lt;/table&gt;</t>
   </si>
 </sst>
 </file>
@@ -18251,12 +18257,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="225">
+    <row r="117" spans="1:12" ht="345">
       <c r="A117" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>2408</v>
+        <v>2437</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -18282,19 +18288,19 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="13" t="s">
+        <v>2408</v>
+      </c>
+      <c r="E118" s="13" t="s">
         <v>2409</v>
       </c>
-      <c r="E118" s="13" t="s">
+      <c r="F118" s="13" t="s">
         <v>2410</v>
       </c>
-      <c r="F118" s="13" t="s">
+      <c r="G118" s="13" t="s">
         <v>2411</v>
       </c>
-      <c r="G118" s="13" t="s">
+      <c r="H118" s="13" t="s">
         <v>2412</v>
-      </c>
-      <c r="H118" s="13" t="s">
-        <v>2413</v>
       </c>
       <c r="I118" s="2"/>
       <c r="J118" s="18"/>
@@ -18368,7 +18374,7 @@
         <v>99</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -18450,7 +18456,7 @@
         <v>99</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -18532,7 +18538,7 @@
         <v>99</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -18726,7 +18732,7 @@
         <v>100</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
@@ -18756,7 +18762,7 @@
         <v>99</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -18782,7 +18788,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="13" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="E136" s="13" t="s">
         <v>940</v>
@@ -18808,23 +18814,23 @@
         <v>100</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="13" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E137" s="13" t="s">
         <v>2421</v>
       </c>
-      <c r="E137" s="13" t="s">
+      <c r="F137" s="13" t="s">
         <v>2422</v>
       </c>
-      <c r="F137" s="13" t="s">
+      <c r="G137" s="13" t="s">
         <v>2423</v>
       </c>
-      <c r="G137" s="13" t="s">
+      <c r="H137" s="13" t="s">
         <v>2424</v>
-      </c>
-      <c r="H137" s="13" t="s">
-        <v>2425</v>
       </c>
       <c r="I137" s="2"/>
       <c r="J137" s="18"/>
@@ -18898,7 +18904,7 @@
         <v>99</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>958</v>
@@ -18926,19 +18932,19 @@
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="13" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E141" s="13" t="s">
         <v>2427</v>
       </c>
-      <c r="E141" s="13" t="s">
+      <c r="F141" s="13" t="s">
         <v>2428</v>
       </c>
-      <c r="F141" s="13" t="s">
+      <c r="G141" s="13" t="s">
         <v>2429</v>
       </c>
-      <c r="G141" s="13" t="s">
+      <c r="H141" s="13" t="s">
         <v>2430</v>
-      </c>
-      <c r="H141" s="13" t="s">
-        <v>2431</v>
       </c>
       <c r="I141" s="2"/>
       <c r="J141" s="18"/>
@@ -18959,7 +18965,7 @@
         <v>954</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="F142" s="13" t="s">
         <v>955</v>
@@ -18986,19 +18992,19 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="13" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E143" s="13" t="s">
         <v>2433</v>
       </c>
-      <c r="E143" s="13" t="s">
+      <c r="F143" s="13" t="s">
         <v>2434</v>
       </c>
-      <c r="F143" s="13" t="s">
+      <c r="G143" s="13" t="s">
         <v>2435</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="H143" s="13" t="s">
         <v>2436</v>
-      </c>
-      <c r="H143" s="13" t="s">
-        <v>2437</v>
       </c>
       <c r="I143" s="2"/>
       <c r="J143" s="18"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C23BBA-A041-49A8-A17E-9B8E6ED949C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB83A66-957C-4385-9938-86AA91C3A6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11238,46 +11238,22 @@
     <t>$K_{A}=1,67.10^{-11}$</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Etude cinétique d'une transformation chimique: (8 points) &lt;/b&gt;&lt;/center&gt;
-Un mélange de volume V=100mL contient initialement $n_{1}(H_{2}O_{2})=3.10^{-3}$ mol d'eau oxygénée, $n_{2}(I^{-})=5.10^{-3}mol$ d'ions iodure et $n_{3}(H^{+})=4.10^{-3}$ mol d'ions hydrogène. La réaction chimique qui se produit est modélisée par l'équation: $H_{2}O_{2(aq)}+2I_{(aq)}^{-}+2H_{(aq)}^{+}\longrightarrow I_{2(aq)}+2H_{2}O_{(l)}$
-Le suivi temporel de la formation de diiode $I_{2(aq)}$ a permis de tracer la courbe $[I_{2(aq)}]=f(t)$ ci-contre.</t>
-  </si>
-  <si>
     <t>La valeur de l'avancement final de la réaction est:</t>
   </si>
   <si>
     <t>La valeur de la vitesse volumique de réaction à $t_{0}=0$ est:</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Suivi temporel d'une transformation chimique (6 poins) &lt;/b&gt;&lt;/center&gt;
-On introduit, à 25 °C, dans un ballon une masse m de carbonate de calcium $CaCO_{3(s)}$ et on y verse à $t=0$, le volume $V_A=15 mL$ d'une solution aqueuse d'acide lactique $C_{3}H_{6}O_{3(aq)}$ de concentration molaire $C_A=8,0.10^{-2} mol.L^{-1}$.
-La transformation chimique qui se produit est modélisée par l'équation: $CaCO_{3(s)}+2C_{3}H_{6}O_{3(aq)}\longrightarrow CO_{2(g)}+Ca_{(aq)}^{2+}+2C_{3}H_{5}O_{3(aq)}^{-}+H_{2}O_{(l)}$
-La courbe ci-contre représente l'évolution de l'avancement de la réaction en fonction du temps $x=f(t)$.
-Données: temps de demi-réaction $t_{1/2}=18s$; $V_m=24L.mol^{-1}$; $M(CaCO_3)=100g.mol^{-1}$;</t>
-  </si>
-  <si>
     <t>La valeur de la masse m est:</t>
   </si>
   <si>
     <t>La valeur du volume de dioxyde de carbone formé à l'instant $t=t_{1/2}$ est:</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;acide acétylsalicylique (7points)&lt;/b&gt;&lt;/center&gt;
- L'acide acétylsalicylique de formule $C_{9}H_{8}O_{4}$, connu sous le nom d'aspirine est utilisé dans de nombreux médicaments pour ses propriétés antalgiques et anti-inflammatoires.
-On dissout un comprimé d'aspirine dans le volume $V=100mL$ d'eau pure pour obtenir une solution aqueuse (S). La conductivité de la solution (S) vaut $\sigma=109 mS.m^{-1}$.
-La transformation chimique qui se produit est modélisée par l'équation: $C_{8}H_{7}O_{2}COOH_{(aq)}+H_{2}O_{(l)}\rightleftharpoons C_{8}H_{7}O_{2}COO_{(aq)}^{-}+H_{3}O_{(aq)}^{+}$
-Données: $\lambda_{(C_8H_7O_2COO^-)}=3,6.10^{-3} S.m^2.mol^{-1}$, $\lambda_{(H_3O^+)}=35,0.10^{-3} S.m^2.mol^{-1}$. On néglige l'effet des ions $HO_{(aq)}^{-}$ sur la conductivité de la solution (S). $M(C_{9}H_{8}O_{4})=180 g.mol^{-1}$, $K_e=10^{-14}$. $\log(2,82)=0,45$ ; $2,82\times38,6\approx109$ ; $9\times27,8\approx250$.</t>
-  </si>
-  <si>
     <t>La valeur de la concentration molaire effective en ions oxonium dans la solution (S) est:</t>
   </si>
   <si>
     <t>La valeur du pH de la solution (S) est:</t>
-  </si>
-  <si>
-    <t>On titre le volume $V_A = 25,0 \text{ mL}$ de la solution $(S)$ par une solution aqueuse d'hydroxyde de sodium $(\text{Na}^+_{\text{(aq)}} + \text{HO}^-_{\text{(aq)}})$ de concentration molaire $C_B = 5,0 \cdot 10^{-2} \text{ mol}\cdot\text{L}^{-1}$. Le volume versé à l'équivalence est $V_{BE} = 27,8 \text{ mL}$.
-La constante d'équilibre associée à l'équation de la réaction du dosage est $K = 3,2 \cdot 10^{7}$. 
-La valeur de la masse d'aspirine contenue dans le comprimé étudié est :</t>
   </si>
   <si>
     <t>La valeur de la constante d'acidité $K_{A}$ du couple acide/base associé à l'acide acétylsalicylique est:</t>
@@ -13286,15 +13262,6 @@
     <t>(E) : $\lambda=0,80 \mathrm{~m}$ $\quad$ $v=10 \mathrm{~m} \cdot \mathrm{~s}^{-1}$</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Comportement des ondes ultrasonores dans deux milieux différents : ( 5 points)&lt;/b&gt;&lt;/center&gt;
- Deux sondes $E_{1}$ et $E_{2}$ émettent, au même instant, des ondes ultrasonores de même fréquence respectivement dans l'air et dans l'eau de mer (figure 1). Le capteur $R_{1}$ capte les ondes se propageant dans l'air et le capteur $R_{2}$ capte les ondes se propageant dans l'eau de mer. Soit $\Delta t$ le retard temporel des ondes reçues par $R_{1}$ par rapport à celles reçues par $R_{2}$, pour une valeur de $d$. La courbe de la figure (2) représente les variations de $\Delta t$ en fonction de $d$. On note $V_{a}$ la vitesse de propagation des ultrasons dans l'air et $V_{e}$ celle des ultrasons dans l'eau de mer. 
-&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
-    &lt;img src="/images/M21F3.png" alt="A" class="h-20" /&gt;
-    &lt;img src="/images/M21F4.png" alt="B" class="h-20" /&gt;
-&lt;/div&gt;
-&lt;br&gt;Données : $V_{a}=340 m \cdot .s^{-1} \quad ; \quad \frac{1}{34}=2,94 \cdot 10^{-2} \quad ; 11 \times 2,27=25 \quad ; 14,92 \times 67=10^{3}$</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Diffraction de la lumiére par une fente : (4 points)&lt;/b&gt;&lt;/center&gt;
 &lt;br&gt; On éclaire une fente de largeur $a$ par une lumière monochromatique de fréquence $N$ émise par un laser. La figure de diffraction est observée sur un écran placé à une distance $D$ de la fente. 
 La largeur de la tache centrale est notée $L$. &lt;br&gt;- Avec un laser émettant une lumière verte de fréquence $N_{v}=5,36.10^{14} \mathrm{~Hz}$, on obtient une tache centrale de largeur $L_{v}=8,6 \mathrm{~mm}$. &lt;br&gt;- Avec un laser émettant une lumière rouge de fréquence $N_{r}=4,74.10^{14} \mathrm{~Hz}$, on obtient une tache centrale de largeur $L_{r}$. 
@@ -13312,15 +13279,6 @@
 &lt;br&gt;Après l'injection, la valeur de l'activité de l'échantillon lorsqu'il devient inactif est :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Charge et décharge d'un condensateur : (9 points)&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt; On considère le montage de la figure (1). À l'instant $t_{0}=0$, on place l'interrupteur $K$ en position (1). La courbe de la figure (2) représente l'évolution de la tension $u_{C}(t)$ aux bornes du condensateur. 
-Donnée : $I_{0}=0,5 \mathrm{~mA}$
-&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
-    &lt;img src="/images/M21F7.png" alt="A" class="h-20" /&gt;
-    &lt;img src="/images/M21F8.png" alt="B" class="h-20" /&gt;
-&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>(A) : $C=5 \mu \mathrm{~F}$</t>
   </si>
   <si>
@@ -13345,59 +13303,89 @@
     <t>(E) : $A=10 \mathrm{~V}$ $\qquad$ $R=1 \Omega$</t>
   </si>
   <si>
+    <t>(A) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,2 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(B) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=0,6 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(C) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(D) : $\tau_{1}=0,6 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(E) : $\tau_{1}=0,9 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
+  </si>
+  <si>
+    <t>(B) : $C_{2}=0,2 . C_{1}$</t>
+  </si>
+  <si>
+    <t>(A) : $U_{C_{2}}=37 \% . E$</t>
+  </si>
+  <si>
+    <t>(B) : $U_{C_{2}}=63 \% . E$</t>
+  </si>
+  <si>
+    <t>(C) : $U_{C_{2}}=67 \% . E$</t>
+  </si>
+  <si>
+    <t>(D) : $U_{C_{2}}=33 \% . E$</t>
+  </si>
+  <si>
+    <t>(E) : $U_{C_{2}}=57 \% E$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Propagation d'une onde le long d'une corde (5 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $v$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 s$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.
+&lt;br&gt;&lt;img src="/images/M21F1&amp;2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Comportement des ondes ultrasonores dans deux milieux différents : ( 5 points)&lt;/b&gt;&lt;/center&gt;
+ Deux sondes $E_{1}$ et $E_{2}$ émettent, au même instant, des ondes ultrasonores de même fréquence respectivement dans l'air et dans l'eau de mer (figure 1). Le capteur $R_{1}$ capte les ondes se propageant dans l'air et le capteur $R_{2}$ capte les ondes se propageant dans l'eau de mer. Soit $\Delta t$ le retard temporel des ondes reçues par $R_{1}$ par rapport à celles reçues par $R_{2}$, pour une valeur de $d$. La courbe de la figure (2) représente les variations de $\Delta t$ en fonction de $d$. On note $V_{a}$ la vitesse de propagation des ultrasons dans l'air et $V_{e}$ celle des ultrasons dans l'eau de mer. 
+&lt;br&gt;&lt;img src="/images/M21F3&amp;4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Données : $V_{a}=340 m \cdot .s^{-1} \quad ; \quad \frac{1}{34}=2,94 \cdot 10^{-2} \quad ; 11 \times 2,27=25 \quad ; 14,92 \times 67=10^{3}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Charge et décharge d'un condensateur : (9 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; On considère le montage de la figure (1). À l'instant $t_{0}=0$, on place l'interrupteur $K$ en position (1). La courbe de la figure (2) représente l'évolution de la tension $u_{C}(t)$ aux bornes du condensateur. 
+Donnée : $I_{0}=0,5 \mathrm{~mA}$
+&lt;br&gt;&lt;img src="/images/M21F7&amp;8.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt;Réponse de dipôles à un échelon de tension (6 points)&lt;/b&gt;&lt;/center&gt;
 &lt;br&gt; Le montage de la figure (1) permet de charger en même temps deux condensateurs de capacité $C_{1}$ et $C_{2}$ tel que $C_{1}&lt;C_{2}$. Les deux conducteurs ohmiques ont la même résistance $R_{1}=R_{2}=R$. À l'instant $t_{0}=0$, on ferme l'interrupteur $K$. Un système d'acquisition permet d'enregistrer l'évolution des tensions $u_{C_{1}}(t)$ et $u_{C_{2}}(t)$ (figure 2).
-&lt;br&gt;&lt;br&gt;&lt;div class="flex justify-end gap-4 my-1"&gt;
-    &lt;img src="/images/M21F10.png" alt="A" class="h-20" /&gt;
-    &lt;img src="/images/M21F11.png" alt="B" class="h-20" /&gt;
-&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>(A) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,2 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(B) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=0,6 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(C) : $\tau_{1}=0,3 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(D) : $\tau_{1}=0,6 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(E) : $\tau_{1}=0,9 \mathrm{~s}$ $\qquad$ $\tau_{2}=1,5 \mathrm{~s}$</t>
-  </si>
-  <si>
-    <t>(B) : $C_{2}=0,2 . C_{1}$</t>
-  </si>
-  <si>
-    <t>(A) : $U_{C_{2}}=37 \% . E$</t>
-  </si>
-  <si>
-    <t>(B) : $U_{C_{2}}=63 \% . E$</t>
-  </si>
-  <si>
-    <t>(C) : $U_{C_{2}}=67 \% . E$</t>
-  </si>
-  <si>
-    <t>(D) : $U_{C_{2}}=33 \% . E$</t>
-  </si>
-  <si>
-    <t>(E) : $U_{C_{2}}=57 \% E$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Propagation d'une onde le long d'une corde (5 points)&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt;Une lame vibrante horizontale, fixée à l'extrémité $S$ d'une corde élastique, génère le long de celle-ci une onde progressive sinusoïdale de célérité $v$. Le mouvement de $S$ débute à l'instant $t_{0}=0$. Les figures (1) et (2) ci-dessous représentent l'élongation d'un point $M$ de la corde, situé à une distance $d$ de $S$, et l'aspect de la corde à l'instant $t_{1}=0,16 s$. Le front d' onde se trouve à l'instant $t_{1}$ à la distance $S F=80 c m$ de $S$.
-&lt;table style="width: 100%; border-collapse: collapse;"&gt;
-  &lt;tr&gt;
-    &lt;td style="text-align: right; padding-right: 10px;"&gt;
-      &lt;img src="/images/M21F1.png" alt="A" style="height: 80px;" /&gt;
-    &lt;/td&gt;
-    &lt;td style="text-align: right; width: 1px;"&gt;
-      &lt;img src="/images/M21F2_2.png" alt="B" style="height: 80px;" /&gt;
-    &lt;/td&gt;
-  &lt;/tr&gt;
-&lt;/table&gt;</t>
+&lt;br&gt;&lt;img src="/images/M21F10&amp;11.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Etude cinétique d'une transformation chimique: (8 points) &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Un mélange de volume V=100mL contient initialement $n_{1}(H_{2}O_{2})=3.10^{-3}$ mol d'eau oxygénée, $n_{2}(I^{-})=5.10^{-3}mol$ d'ions iodure et $n_{3}(H^{+})=4.10^{-3}$ mol d'ions hydrogène. La réaction chimique qui se produit est modélisée par l'équation: 
+&lt;br&gt;$H_{2}O_{2(aq)}+2I_{(aq)}^{-}+2H_{(aq)}^{+}\longrightarrow I_{2(aq)}+2H_{2}O_{(l)}$
+&lt;br&gt;Le suivi temporel de la formation de diiode $I_{2(aq)}$ a permis de tracer la courbe $[I_{2(aq)}]=f(t)$ ci-contre.
+&lt;br&gt;&lt;img src="/images/CH21F1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Suivi temporel d'une transformation chimique (6 poins) &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On introduit, à 25 °C, dans un ballon une masse m de carbonate de calcium $CaCO_{3(s)}$ et on y verse à $t=0$, le volume $V_A=15 mL$ d'une solution aqueuse d'acide lactique $C_{3}H_{6}O_{3(aq)}$ de concentration molaire $C_A=8,0.10^{-2} mol.L^{-1}$.
+La transformation chimique qui se produit est modélisée par l'équation:
+&lt;br&gt; $CaCO_{3(s)}+2C_{3}H_{6}O_{3(aq)}\longrightarrow CO_{2(g)}+Ca_{(aq)}^{2+}+2C_{3}H_{5}O_{3(aq)}^{-}+H_{2}O_{(l)}$
+&lt;br&gt;La courbe ci-contre représente l'évolution de l'avancement de la réaction en fonction du temps $x=f(t)$.
+&lt;br&gt;&lt;img src="/images/CH21F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Données: temps de demi-réaction $t_{1/2}=18s$; $\quad$ $V_m=24L.mol^{-1}$; $\quad$ $M(CaCO_3)=100g.mol^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;acide acétylsalicylique (7points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; L'acide acétylsalicylique de formule $C_{9}H_{8}O_{4}$, connu sous le nom d'aspirine est utilisé dans de nombreux médicaments pour ses propriétés antalgiques et anti-inflammatoires.
+On dissout un comprimé d'aspirine dans le volume $V=100mL$ d'eau pure pour obtenir une solution aqueuse (S). La conductivité de la solution (S) vaut $\sigma=109 mS.m^{-1}$.
+La transformation chimique qui se produit est modélisée par l'équation: 
+&lt;br&gt;$C_{8}H_{7}O_{2}COOH_{(aq)}+H_{2}O_{(l)}\rightleftharpoons C_{8}H_{7}O_{2}COO_{(aq)}^{-}+H_{3}O_{(aq)}^{+}$
+&lt;br&gt;Données: $\lambda_{(C_8H_7O_2COO^-)}=3,6.10^{-3} S.m^2.mol^{-1}$, $\quad$ $\lambda_{(H_3O^+)}=35,0.10^{-3} S.m^2.mol^{-1}$. 
+&lt;br&gt;On néglige l'effet des ions $HO_{(aq)}^{-}$ sur la conductivité de la solution (S). $M(C_{9}H_{8}O_{4})=180 g.mol^{-1}$, $K_e=10^{-14}$. $\log(2,82)=0,45$ ; $2,82\times38,6\approx109$ ; $9\times27,8\approx250$.</t>
+  </si>
+  <si>
+    <t>On titre le volume $V_A = 25,0 \text{ mL}$ de la solution $(S)$ par une solution aqueuse d'hydroxyde de sodium $(\text{Na}^+_{\text{(aq)}} + \text{HO}^-_{\text{(aq)}})$ de concentration molaire $C_B = 5,0 \cdot 10^{-2} \text{ mol}\cdot\text{L}^{-1}$. Le volume versé à l'équivalence est $V_{BE} = 27,8 \text{ mL}$.
+&lt;br&gt;La constante d'équilibre associée à l'équation de la réaction du dosage est $K = 3,2 \cdot 10^{7}$. 
+&lt;br&gt;La valeur de la masse d'aspirine contenue dans le comprimé étudié est :</t>
   </si>
 </sst>
 </file>
@@ -14888,7 +14876,7 @@
         <v>98</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>2351</v>
+        <v>2347</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="46" t="s">
@@ -14924,7 +14912,7 @@
         <v>98</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>2345</v>
+        <v>2341</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="46" t="s">
@@ -14960,7 +14948,7 @@
         <v>98</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="46" t="s">
@@ -15032,7 +15020,7 @@
         <v>98</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="46" t="s">
@@ -15104,7 +15092,7 @@
         <v>98</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>2348</v>
+        <v>2344</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="46" t="s">
@@ -15140,7 +15128,7 @@
         <v>98</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>2349</v>
+        <v>2345</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="46" t="s">
@@ -15176,7 +15164,7 @@
         <v>98</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="46" t="s">
@@ -15212,7 +15200,7 @@
         <v>98</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>2350</v>
+        <v>2346</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="46" t="s">
@@ -15248,7 +15236,7 @@
         <v>99</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>2352</v>
+        <v>2348</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="2"/>
@@ -15270,11 +15258,11 @@
         <v>100</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="13" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>787</v>
@@ -15366,7 +15354,7 @@
         <v>99</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -15388,7 +15376,7 @@
         <v>100</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>2355</v>
+        <v>2351</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="13" t="s">
@@ -15452,7 +15440,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2357</v>
+        <v>2353</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -15522,7 +15510,7 @@
         <v>819</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>2356</v>
+        <v>2352</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>816</v>
@@ -15538,7 +15526,7 @@
         <v>100</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
@@ -15570,7 +15558,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -15592,7 +15580,7 @@
         <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2360</v>
+        <v>2356</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -15624,7 +15612,7 @@
         <v>100</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2361</v>
+        <v>2357</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
@@ -15656,7 +15644,7 @@
         <v>99</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -15678,7 +15666,7 @@
         <v>100</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
@@ -15710,7 +15698,7 @@
         <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
@@ -15742,7 +15730,7 @@
         <v>99</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2364</v>
+        <v>2360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -15764,7 +15752,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="13" t="s">
@@ -15794,7 +15782,7 @@
         <v>100</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="13" t="s">
@@ -15824,26 +15812,26 @@
         <v>98</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>2369</v>
+        <v>2365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="13" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>2369</v>
+      </c>
+      <c r="H42" s="13" t="s">
         <v>2370</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>2371</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>2372</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>2373</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>2374</v>
-      </c>
       <c r="I42" s="13" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="J42" s="18" t="s">
         <v>9</v>
@@ -15860,7 +15848,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -15882,7 +15870,7 @@
         <v>100</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>2376</v>
+        <v>2372</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
@@ -15914,7 +15902,7 @@
         <v>100</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>2377</v>
+        <v>2373</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
@@ -15978,7 +15966,7 @@
         <v>99</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>2378</v>
+        <v>2374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -16064,7 +16052,7 @@
         <v>99</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -16182,7 +16170,7 @@
         <v>99</v>
       </c>
       <c r="B54" s="46" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -16208,22 +16196,22 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="46" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E55" s="46" t="s">
+        <v>2382</v>
+      </c>
+      <c r="F55" s="46" t="s">
+        <v>2383</v>
+      </c>
+      <c r="G55" s="46" t="s">
+        <v>2384</v>
+      </c>
+      <c r="H55" s="46" t="s">
         <v>2385</v>
       </c>
-      <c r="E55" s="46" t="s">
-        <v>2386</v>
-      </c>
-      <c r="F55" s="46" t="s">
-        <v>2387</v>
-      </c>
-      <c r="G55" s="46" t="s">
-        <v>2388</v>
-      </c>
-      <c r="H55" s="46" t="s">
-        <v>2389</v>
-      </c>
       <c r="I55" s="46" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
@@ -16332,7 +16320,7 @@
         <v>99</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -16450,7 +16438,7 @@
         <v>98</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="46" t="s">
@@ -16486,7 +16474,7 @@
         <v>99</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -16572,7 +16560,7 @@
         <v>99</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -16690,7 +16678,7 @@
         <v>99</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>2391</v>
+        <v>2387</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -16776,7 +16764,7 @@
         <v>99</v>
       </c>
       <c r="B74" s="46" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -16934,7 +16922,7 @@
         <v>98</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="13" t="s">
@@ -17078,7 +17066,7 @@
         <v>98</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>2393</v>
+        <v>2389</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="13" t="s">
@@ -17150,7 +17138,7 @@
         <v>98</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="13" t="s">
@@ -17222,7 +17210,7 @@
         <v>98</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>2394</v>
+        <v>2390</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="13" t="s">
@@ -17294,7 +17282,7 @@
         <v>98</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>2395</v>
+        <v>2391</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="13" t="s">
@@ -17366,7 +17354,7 @@
         <v>98</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>2396</v>
+        <v>2392</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="13" t="s">
@@ -17402,7 +17390,7 @@
         <v>98</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>2397</v>
+        <v>2393</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="13" t="s">
@@ -17438,7 +17426,7 @@
         <v>98</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>2398</v>
+        <v>2394</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="13" t="s">
@@ -17922,7 +17910,7 @@
         <v>98</v>
       </c>
       <c r="B107" s="37" t="s">
-        <v>2399</v>
+        <v>2395</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="47" t="s">
@@ -17990,7 +17978,7 @@
         <v>98</v>
       </c>
       <c r="B109" s="37" t="s">
-        <v>2400</v>
+        <v>2396</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="47" t="s">
@@ -18024,7 +18012,7 @@
         <v>98</v>
       </c>
       <c r="B110" s="40" t="s">
-        <v>2401</v>
+        <v>2397</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="48" t="s">
@@ -18058,7 +18046,7 @@
         <v>98</v>
       </c>
       <c r="B111" s="37" t="s">
-        <v>2402</v>
+        <v>2398</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="47" t="s">
@@ -18092,7 +18080,7 @@
         <v>98</v>
       </c>
       <c r="B112" s="40" t="s">
-        <v>2403</v>
+        <v>2399</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="48" t="s">
@@ -18126,7 +18114,7 @@
         <v>98</v>
       </c>
       <c r="B113" s="37" t="s">
-        <v>2404</v>
+        <v>2400</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="47" t="s">
@@ -18160,7 +18148,7 @@
         <v>98</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>2405</v>
+        <v>2401</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="48" t="s">
@@ -18194,7 +18182,7 @@
         <v>98</v>
       </c>
       <c r="B115" s="37" t="s">
-        <v>2406</v>
+        <v>2402</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="47" t="s">
@@ -18228,7 +18216,7 @@
         <v>98</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>2407</v>
+        <v>2403</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="48" t="s">
@@ -18257,12 +18245,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="345">
+    <row r="117" spans="1:12" ht="195">
       <c r="A117" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>2437</v>
+        <v>2430</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -18288,19 +18276,19 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="13" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>2406</v>
+      </c>
+      <c r="G118" s="13" t="s">
+        <v>2407</v>
+      </c>
+      <c r="H118" s="13" t="s">
         <v>2408</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>2409</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>2410</v>
-      </c>
-      <c r="G118" s="13" t="s">
-        <v>2411</v>
-      </c>
-      <c r="H118" s="13" t="s">
-        <v>2412</v>
       </c>
       <c r="I118" s="2"/>
       <c r="J118" s="18"/>
@@ -18369,12 +18357,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="300">
+    <row r="121" spans="1:12" ht="270">
       <c r="A121" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>2413</v>
+        <v>2431</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -18456,7 +18444,7 @@
         <v>99</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>2414</v>
+        <v>2409</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -18538,7 +18526,7 @@
         <v>99</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>2415</v>
+        <v>2410</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -18732,7 +18720,7 @@
         <v>100</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>2416</v>
+        <v>2411</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
@@ -18757,12 +18745,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="165">
+    <row r="135" spans="1:12" ht="135">
       <c r="A135" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>2417</v>
+        <v>2432</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -18788,7 +18776,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="13" t="s">
-        <v>2418</v>
+        <v>2412</v>
       </c>
       <c r="E136" s="13" t="s">
         <v>940</v>
@@ -18814,23 +18802,23 @@
         <v>100</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>2419</v>
+        <v>2413</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="13" t="s">
-        <v>2420</v>
+        <v>2414</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>2421</v>
+        <v>2415</v>
       </c>
       <c r="F137" s="13" t="s">
-        <v>2422</v>
+        <v>2416</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>2423</v>
+        <v>2417</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>2424</v>
+        <v>2418</v>
       </c>
       <c r="I137" s="2"/>
       <c r="J137" s="18"/>
@@ -18899,12 +18887,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="195">
+    <row r="140" spans="1:12" ht="165">
       <c r="A140" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>2425</v>
+        <v>2433</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>958</v>
@@ -18932,19 +18920,19 @@
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="13" t="s">
-        <v>2426</v>
+        <v>2419</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>2427</v>
+        <v>2420</v>
       </c>
       <c r="F141" s="13" t="s">
-        <v>2428</v>
+        <v>2421</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>2429</v>
+        <v>2422</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>2430</v>
+        <v>2423</v>
       </c>
       <c r="I141" s="2"/>
       <c r="J141" s="18"/>
@@ -18965,7 +18953,7 @@
         <v>954</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>2431</v>
+        <v>2424</v>
       </c>
       <c r="F142" s="13" t="s">
         <v>955</v>
@@ -18992,19 +18980,19 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="13" t="s">
-        <v>2432</v>
+        <v>2425</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>2433</v>
+        <v>2426</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>2434</v>
+        <v>2427</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>2435</v>
+        <v>2428</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>2436</v>
+        <v>2429</v>
       </c>
       <c r="I143" s="2"/>
       <c r="J143" s="18"/>
@@ -19013,12 +19001,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="150">
+    <row r="144" spans="1:12" ht="195">
       <c r="A144" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B144" s="46" t="s">
-        <v>1795</v>
+        <v>2434</v>
       </c>
       <c r="C144" s="46"/>
       <c r="D144" s="46"/>
@@ -19040,7 +19028,7 @@
         <v>100</v>
       </c>
       <c r="B145" s="46" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C145" s="46"/>
       <c r="D145" s="46" t="s">
@@ -19100,7 +19088,7 @@
         <v>100</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C147" s="46"/>
       <c r="D147" s="46" t="s">
@@ -19125,12 +19113,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="240">
+    <row r="148" spans="1:12" ht="270">
       <c r="A148" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B148" s="46" t="s">
-        <v>1798</v>
+        <v>2435</v>
       </c>
       <c r="C148" s="46"/>
       <c r="D148" s="46"/>
@@ -19152,7 +19140,7 @@
         <v>100</v>
       </c>
       <c r="B149" s="46" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C149" s="46"/>
       <c r="D149" s="46" t="s">
@@ -19182,7 +19170,7 @@
         <v>100</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="C150" s="46"/>
       <c r="D150" s="46" t="s">
@@ -19212,7 +19200,7 @@
         <v>100</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="C151" s="46"/>
       <c r="D151" s="46" t="s">
@@ -19242,7 +19230,7 @@
         <v>99</v>
       </c>
       <c r="B152" s="46" t="s">
-        <v>1801</v>
+        <v>2436</v>
       </c>
       <c r="C152" s="46"/>
       <c r="D152" s="46"/>
@@ -19264,7 +19252,7 @@
         <v>100</v>
       </c>
       <c r="B153" s="46" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="C153" s="46"/>
       <c r="D153" s="46" t="s">
@@ -19294,7 +19282,7 @@
         <v>100</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="C154" s="46"/>
       <c r="D154" s="46" t="s">
@@ -19324,7 +19312,7 @@
         <v>100</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1804</v>
+        <v>2437</v>
       </c>
       <c r="C155" s="46"/>
       <c r="D155" s="46" t="s">
@@ -19354,7 +19342,7 @@
         <v>100</v>
       </c>
       <c r="B156" s="46" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="C156" s="46"/>
       <c r="D156" s="46" t="s">
@@ -19384,7 +19372,7 @@
         <v>99</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1812</v>
+        <v>1808</v>
       </c>
       <c r="C157" s="46"/>
       <c r="D157" s="2"/>
@@ -19406,7 +19394,7 @@
         <v>100</v>
       </c>
       <c r="B158" s="46" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C158" s="46"/>
       <c r="D158" s="46" t="s">
@@ -19436,7 +19424,7 @@
         <v>100</v>
       </c>
       <c r="B159" s="46" t="s">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="C159" s="46"/>
       <c r="D159" s="46" t="s">
@@ -19466,7 +19454,7 @@
         <v>99</v>
       </c>
       <c r="B160" s="46" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="C160" s="46"/>
       <c r="D160" s="46"/>
@@ -19488,7 +19476,7 @@
         <v>100</v>
       </c>
       <c r="B161" s="46" t="s">
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="C161" s="46"/>
       <c r="D161" s="46" t="s">
@@ -19518,7 +19506,7 @@
         <v>100</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="C162" s="46"/>
       <c r="D162" s="46" t="s">
@@ -19548,7 +19536,7 @@
         <v>100</v>
       </c>
       <c r="B163" s="46" t="s">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="C163" s="46"/>
       <c r="D163" s="46" t="s">
@@ -19578,7 +19566,7 @@
         <v>99</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="C164" s="46"/>
       <c r="D164" s="46"/>
@@ -19600,7 +19588,7 @@
         <v>100</v>
       </c>
       <c r="B165" s="46" t="s">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="C165" s="46"/>
       <c r="D165" s="46" t="s">
@@ -19630,7 +19618,7 @@
         <v>100</v>
       </c>
       <c r="B166" s="46" t="s">
-        <v>1815</v>
+        <v>1811</v>
       </c>
       <c r="C166" s="46"/>
       <c r="D166" s="46" t="s">
@@ -19660,7 +19648,7 @@
         <v>100</v>
       </c>
       <c r="B167" s="46" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="C167" s="46"/>
       <c r="D167" s="46" t="s">
@@ -19690,7 +19678,7 @@
         <v>100</v>
       </c>
       <c r="B168" s="46" t="s">
-        <v>1817</v>
+        <v>1813</v>
       </c>
       <c r="C168" s="46"/>
       <c r="D168" s="46" t="s">
@@ -19720,7 +19708,7 @@
         <v>100</v>
       </c>
       <c r="B169" s="46" t="s">
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="C169" s="46"/>
       <c r="D169" s="46" t="s">
@@ -21092,7 +21080,7 @@
         <v>99</v>
       </c>
       <c r="B210" s="29" t="s">
-        <v>2324</v>
+        <v>2320</v>
       </c>
       <c r="C210" s="58"/>
       <c r="D210" s="2"/>
@@ -21114,23 +21102,23 @@
         <v>100</v>
       </c>
       <c r="B211" s="29" t="s">
-        <v>2325</v>
+        <v>2321</v>
       </c>
       <c r="C211" s="58"/>
       <c r="D211" s="30" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E211" s="30" t="s">
+        <v>2253</v>
+      </c>
+      <c r="F211" s="30" t="s">
+        <v>2254</v>
+      </c>
+      <c r="G211" s="30" t="s">
+        <v>2255</v>
+      </c>
+      <c r="H211" s="30" t="s">
         <v>2256</v>
-      </c>
-      <c r="E211" s="30" t="s">
-        <v>2257</v>
-      </c>
-      <c r="F211" s="30" t="s">
-        <v>2258</v>
-      </c>
-      <c r="G211" s="30" t="s">
-        <v>2259</v>
-      </c>
-      <c r="H211" s="30" t="s">
-        <v>2260</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
@@ -21144,23 +21132,23 @@
         <v>100</v>
       </c>
       <c r="B212" s="59" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="C212" s="60"/>
       <c r="D212" s="31" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E212" s="31" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F212" s="31" t="s">
+        <v>2259</v>
+      </c>
+      <c r="G212" s="31" t="s">
+        <v>2260</v>
+      </c>
+      <c r="H212" s="31" t="s">
         <v>2261</v>
-      </c>
-      <c r="E212" s="31" t="s">
-        <v>2262</v>
-      </c>
-      <c r="F212" s="31" t="s">
-        <v>2263</v>
-      </c>
-      <c r="G212" s="31" t="s">
-        <v>2264</v>
-      </c>
-      <c r="H212" s="31" t="s">
-        <v>2265</v>
       </c>
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
@@ -21174,23 +21162,23 @@
         <v>100</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>2328</v>
+        <v>2324</v>
       </c>
       <c r="C213" s="58"/>
       <c r="D213" s="30" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E213" s="30" t="s">
+        <v>2263</v>
+      </c>
+      <c r="F213" s="30" t="s">
+        <v>2264</v>
+      </c>
+      <c r="G213" s="30" t="s">
+        <v>2265</v>
+      </c>
+      <c r="H213" s="30" t="s">
         <v>2266</v>
-      </c>
-      <c r="E213" s="30" t="s">
-        <v>2267</v>
-      </c>
-      <c r="F213" s="30" t="s">
-        <v>2268</v>
-      </c>
-      <c r="G213" s="30" t="s">
-        <v>2269</v>
-      </c>
-      <c r="H213" s="30" t="s">
-        <v>2270</v>
       </c>
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
@@ -21204,23 +21192,23 @@
         <v>100</v>
       </c>
       <c r="B214" s="59" t="s">
-        <v>2327</v>
+        <v>2323</v>
       </c>
       <c r="C214" s="60"/>
       <c r="D214" s="31" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E214" s="31" t="s">
+        <v>2268</v>
+      </c>
+      <c r="F214" s="31" t="s">
+        <v>2269</v>
+      </c>
+      <c r="G214" s="31" t="s">
+        <v>2270</v>
+      </c>
+      <c r="H214" s="31" t="s">
         <v>2271</v>
-      </c>
-      <c r="E214" s="31" t="s">
-        <v>2272</v>
-      </c>
-      <c r="F214" s="31" t="s">
-        <v>2273</v>
-      </c>
-      <c r="G214" s="31" t="s">
-        <v>2274</v>
-      </c>
-      <c r="H214" s="31" t="s">
-        <v>2275</v>
       </c>
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
@@ -21234,10 +21222,10 @@
         <v>99</v>
       </c>
       <c r="B215" s="29" t="s">
-        <v>2329</v>
+        <v>2325</v>
       </c>
       <c r="C215" s="58" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -21258,23 +21246,23 @@
         <v>100</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="C216" s="58"/>
       <c r="D216" s="30" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E216" s="30" t="s">
+        <v>2274</v>
+      </c>
+      <c r="F216" s="30" t="s">
+        <v>2275</v>
+      </c>
+      <c r="G216" s="30" t="s">
+        <v>2276</v>
+      </c>
+      <c r="H216" s="30" t="s">
         <v>2277</v>
-      </c>
-      <c r="E216" s="30" t="s">
-        <v>2278</v>
-      </c>
-      <c r="F216" s="30" t="s">
-        <v>2279</v>
-      </c>
-      <c r="G216" s="30" t="s">
-        <v>2280</v>
-      </c>
-      <c r="H216" s="30" t="s">
-        <v>2281</v>
       </c>
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
@@ -21288,23 +21276,23 @@
         <v>100</v>
       </c>
       <c r="B217" s="59" t="s">
-        <v>2331</v>
+        <v>2327</v>
       </c>
       <c r="C217" s="60"/>
       <c r="D217" s="31" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E217" s="31" t="s">
+        <v>2279</v>
+      </c>
+      <c r="F217" s="31" t="s">
+        <v>2280</v>
+      </c>
+      <c r="G217" s="31" t="s">
+        <v>2281</v>
+      </c>
+      <c r="H217" s="31" t="s">
         <v>2282</v>
-      </c>
-      <c r="E217" s="31" t="s">
-        <v>2283</v>
-      </c>
-      <c r="F217" s="31" t="s">
-        <v>2284</v>
-      </c>
-      <c r="G217" s="31" t="s">
-        <v>2285</v>
-      </c>
-      <c r="H217" s="31" t="s">
-        <v>2286</v>
       </c>
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
@@ -21318,23 +21306,23 @@
         <v>100</v>
       </c>
       <c r="B218" s="29" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="C218" s="58"/>
       <c r="D218" s="30" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E218" s="30" t="s">
+        <v>2284</v>
+      </c>
+      <c r="F218" s="30" t="s">
+        <v>2285</v>
+      </c>
+      <c r="G218" s="30" t="s">
+        <v>2286</v>
+      </c>
+      <c r="H218" s="30" t="s">
         <v>2287</v>
-      </c>
-      <c r="E218" s="30" t="s">
-        <v>2288</v>
-      </c>
-      <c r="F218" s="30" t="s">
-        <v>2289</v>
-      </c>
-      <c r="G218" s="30" t="s">
-        <v>2290</v>
-      </c>
-      <c r="H218" s="30" t="s">
-        <v>2291</v>
       </c>
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
@@ -21348,10 +21336,10 @@
         <v>99</v>
       </c>
       <c r="B219" s="59" t="s">
-        <v>2339</v>
+        <v>2335</v>
       </c>
       <c r="C219" s="60" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -21372,23 +21360,23 @@
         <v>100</v>
       </c>
       <c r="B220" s="59" t="s">
-        <v>2333</v>
+        <v>2329</v>
       </c>
       <c r="C220" s="60"/>
       <c r="D220" s="31" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E220" s="31" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F220" s="31" t="s">
+        <v>2291</v>
+      </c>
+      <c r="G220" s="31" t="s">
+        <v>2292</v>
+      </c>
+      <c r="H220" s="31" t="s">
         <v>2293</v>
-      </c>
-      <c r="E220" s="31" t="s">
-        <v>2294</v>
-      </c>
-      <c r="F220" s="31" t="s">
-        <v>2295</v>
-      </c>
-      <c r="G220" s="31" t="s">
-        <v>2296</v>
-      </c>
-      <c r="H220" s="31" t="s">
-        <v>2297</v>
       </c>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
@@ -21402,23 +21390,23 @@
         <v>100</v>
       </c>
       <c r="B221" s="59" t="s">
-        <v>2340</v>
+        <v>2336</v>
       </c>
       <c r="C221" s="60"/>
       <c r="D221" s="30" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E221" s="30" t="s">
+        <v>2295</v>
+      </c>
+      <c r="F221" s="30" t="s">
+        <v>2296</v>
+      </c>
+      <c r="G221" s="30" t="s">
+        <v>2297</v>
+      </c>
+      <c r="H221" s="30" t="s">
         <v>2298</v>
-      </c>
-      <c r="E221" s="30" t="s">
-        <v>2299</v>
-      </c>
-      <c r="F221" s="30" t="s">
-        <v>2300</v>
-      </c>
-      <c r="G221" s="30" t="s">
-        <v>2301</v>
-      </c>
-      <c r="H221" s="30" t="s">
-        <v>2302</v>
       </c>
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
@@ -21432,23 +21420,23 @@
         <v>100</v>
       </c>
       <c r="B222" s="59" t="s">
-        <v>2334</v>
+        <v>2330</v>
       </c>
       <c r="C222" s="60"/>
       <c r="D222" s="31" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E222" s="31" t="s">
+        <v>2300</v>
+      </c>
+      <c r="F222" s="31" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G222" s="31" t="s">
+        <v>2302</v>
+      </c>
+      <c r="H222" s="31" t="s">
         <v>2303</v>
-      </c>
-      <c r="E222" s="31" t="s">
-        <v>2304</v>
-      </c>
-      <c r="F222" s="31" t="s">
-        <v>2305</v>
-      </c>
-      <c r="G222" s="31" t="s">
-        <v>2306</v>
-      </c>
-      <c r="H222" s="31" t="s">
-        <v>2307</v>
       </c>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
@@ -21462,10 +21450,10 @@
         <v>99</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
       <c r="C223" s="58" t="s">
-        <v>2308</v>
+        <v>2304</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
@@ -21486,23 +21474,23 @@
         <v>100</v>
       </c>
       <c r="B224" s="29" t="s">
-        <v>2336</v>
+        <v>2332</v>
       </c>
       <c r="C224" s="58"/>
       <c r="D224" s="30" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E224" s="30" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F224" s="30" t="s">
+        <v>2307</v>
+      </c>
+      <c r="G224" s="30" t="s">
+        <v>2308</v>
+      </c>
+      <c r="H224" s="30" t="s">
         <v>2309</v>
-      </c>
-      <c r="E224" s="30" t="s">
-        <v>2310</v>
-      </c>
-      <c r="F224" s="30" t="s">
-        <v>2311</v>
-      </c>
-      <c r="G224" s="30" t="s">
-        <v>2312</v>
-      </c>
-      <c r="H224" s="30" t="s">
-        <v>2313</v>
       </c>
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
@@ -21516,23 +21504,23 @@
         <v>100</v>
       </c>
       <c r="B225" s="59" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
       <c r="C225" s="60"/>
       <c r="D225" s="31" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E225" s="31" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F225" s="31" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G225" s="31" t="s">
+        <v>2313</v>
+      </c>
+      <c r="H225" s="31" t="s">
         <v>2314</v>
-      </c>
-      <c r="E225" s="31" t="s">
-        <v>2315</v>
-      </c>
-      <c r="F225" s="31" t="s">
-        <v>2316</v>
-      </c>
-      <c r="G225" s="31" t="s">
-        <v>2317</v>
-      </c>
-      <c r="H225" s="31" t="s">
-        <v>2318</v>
       </c>
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
@@ -21546,23 +21534,23 @@
         <v>100</v>
       </c>
       <c r="B226" s="29" t="s">
-        <v>2338</v>
+        <v>2334</v>
       </c>
       <c r="C226" s="58"/>
       <c r="D226" s="30" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E226" s="30" t="s">
+        <v>2316</v>
+      </c>
+      <c r="F226" s="30" t="s">
+        <v>2317</v>
+      </c>
+      <c r="G226" s="30" t="s">
+        <v>2318</v>
+      </c>
+      <c r="H226" s="30" t="s">
         <v>2319</v>
-      </c>
-      <c r="E226" s="30" t="s">
-        <v>2320</v>
-      </c>
-      <c r="F226" s="30" t="s">
-        <v>2321</v>
-      </c>
-      <c r="G226" s="30" t="s">
-        <v>2322</v>
-      </c>
-      <c r="H226" s="30" t="s">
-        <v>2323</v>
       </c>
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
@@ -22330,7 +22318,7 @@
         <v>781</v>
       </c>
       <c r="H253" s="13" t="s">
-        <v>2344</v>
+        <v>2340</v>
       </c>
       <c r="I253" s="2"/>
       <c r="J253" s="18"/>
@@ -23064,23 +23052,23 @@
         <v>98</v>
       </c>
       <c r="B274" s="40" t="s">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="C274" s="41"/>
       <c r="D274" s="42" t="s">
+        <v>1816</v>
+      </c>
+      <c r="E274" s="42" t="s">
+        <v>1817</v>
+      </c>
+      <c r="F274" s="42" t="s">
+        <v>1818</v>
+      </c>
+      <c r="G274" s="42" t="s">
+        <v>1819</v>
+      </c>
+      <c r="H274" s="42" t="s">
         <v>1820</v>
-      </c>
-      <c r="E274" s="42" t="s">
-        <v>1821</v>
-      </c>
-      <c r="F274" s="42" t="s">
-        <v>1822</v>
-      </c>
-      <c r="G274" s="42" t="s">
-        <v>1823</v>
-      </c>
-      <c r="H274" s="42" t="s">
-        <v>1824</v>
       </c>
       <c r="I274" s="2"/>
       <c r="J274" s="18" t="s">
@@ -23098,23 +23086,23 @@
         <v>98</v>
       </c>
       <c r="B275" s="37" t="s">
-        <v>1825</v>
+        <v>1821</v>
       </c>
       <c r="C275" s="38"/>
       <c r="D275" s="39" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E275" s="39" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F275" s="39" t="s">
+        <v>1824</v>
+      </c>
+      <c r="G275" s="39" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H275" s="39" t="s">
         <v>1826</v>
-      </c>
-      <c r="E275" s="39" t="s">
-        <v>1827</v>
-      </c>
-      <c r="F275" s="39" t="s">
-        <v>1828</v>
-      </c>
-      <c r="G275" s="39" t="s">
-        <v>1829</v>
-      </c>
-      <c r="H275" s="39" t="s">
-        <v>1830</v>
       </c>
       <c r="I275" s="2"/>
       <c r="J275" s="18" t="s">
@@ -23132,23 +23120,23 @@
         <v>98</v>
       </c>
       <c r="B276" s="40" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="C276" s="41"/>
       <c r="D276" s="42" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E276" s="42" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F276" s="42" t="s">
+        <v>1830</v>
+      </c>
+      <c r="G276" s="42" t="s">
+        <v>1831</v>
+      </c>
+      <c r="H276" s="42" t="s">
         <v>1832</v>
-      </c>
-      <c r="E276" s="42" t="s">
-        <v>1833</v>
-      </c>
-      <c r="F276" s="42" t="s">
-        <v>1834</v>
-      </c>
-      <c r="G276" s="42" t="s">
-        <v>1835</v>
-      </c>
-      <c r="H276" s="42" t="s">
-        <v>1836</v>
       </c>
       <c r="I276" s="2"/>
       <c r="J276" s="18" t="s">
@@ -23166,23 +23154,23 @@
         <v>98</v>
       </c>
       <c r="B277" s="37" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="C277" s="38"/>
       <c r="D277" s="39" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E277" s="39" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F277" s="39" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G277" s="39" t="s">
+        <v>1837</v>
+      </c>
+      <c r="H277" s="39" t="s">
         <v>1838</v>
-      </c>
-      <c r="E277" s="39" t="s">
-        <v>1839</v>
-      </c>
-      <c r="F277" s="39" t="s">
-        <v>1840</v>
-      </c>
-      <c r="G277" s="39" t="s">
-        <v>1841</v>
-      </c>
-      <c r="H277" s="39" t="s">
-        <v>1842</v>
       </c>
       <c r="I277" s="2"/>
       <c r="J277" s="18" t="s">
@@ -23200,23 +23188,23 @@
         <v>98</v>
       </c>
       <c r="B278" s="40" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="C278" s="41"/>
       <c r="D278" s="42" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E278" s="42" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F278" s="42" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G278" s="42" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H278" s="42" t="s">
         <v>1844</v>
-      </c>
-      <c r="E278" s="42" t="s">
-        <v>1845</v>
-      </c>
-      <c r="F278" s="42" t="s">
-        <v>1846</v>
-      </c>
-      <c r="G278" s="42" t="s">
-        <v>1847</v>
-      </c>
-      <c r="H278" s="42" t="s">
-        <v>1848</v>
       </c>
       <c r="I278" s="2"/>
       <c r="J278" s="18" t="s">
@@ -23234,23 +23222,23 @@
         <v>98</v>
       </c>
       <c r="B279" s="37" t="s">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="C279" s="38"/>
       <c r="D279" s="39" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E279" s="39" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F279" s="39" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G279" s="39" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H279" s="39" t="s">
         <v>1850</v>
-      </c>
-      <c r="E279" s="39" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F279" s="39" t="s">
-        <v>1852</v>
-      </c>
-      <c r="G279" s="39" t="s">
-        <v>1853</v>
-      </c>
-      <c r="H279" s="39" t="s">
-        <v>1854</v>
       </c>
       <c r="I279" s="2"/>
       <c r="J279" s="18" t="s">
@@ -23268,23 +23256,23 @@
         <v>98</v>
       </c>
       <c r="B280" s="40" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="C280" s="41"/>
       <c r="D280" s="42" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E280" s="42" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F280" s="42" t="s">
+        <v>1854</v>
+      </c>
+      <c r="G280" s="42" t="s">
+        <v>1855</v>
+      </c>
+      <c r="H280" s="42" t="s">
         <v>1856</v>
-      </c>
-      <c r="E280" s="42" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F280" s="42" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G280" s="42" t="s">
-        <v>1859</v>
-      </c>
-      <c r="H280" s="42" t="s">
-        <v>1860</v>
       </c>
       <c r="I280" s="2"/>
       <c r="J280" s="18" t="s">
@@ -23302,7 +23290,7 @@
         <v>99</v>
       </c>
       <c r="B281" s="49" t="s">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="C281" s="50"/>
       <c r="D281" s="50"/>
@@ -23324,23 +23312,23 @@
         <v>100</v>
       </c>
       <c r="B282" s="37" t="s">
-        <v>1861</v>
+        <v>1857</v>
       </c>
       <c r="C282" s="51"/>
       <c r="D282" s="39" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E282" s="39" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F282" s="39" t="s">
+        <v>1860</v>
+      </c>
+      <c r="G282" s="39" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H282" s="39" t="s">
         <v>1862</v>
-      </c>
-      <c r="E282" s="39" t="s">
-        <v>1863</v>
-      </c>
-      <c r="F282" s="39" t="s">
-        <v>1864</v>
-      </c>
-      <c r="G282" s="39" t="s">
-        <v>1865</v>
-      </c>
-      <c r="H282" s="39" t="s">
-        <v>1866</v>
       </c>
       <c r="I282" s="2"/>
       <c r="J282" s="18"/>
@@ -23354,23 +23342,23 @@
         <v>98</v>
       </c>
       <c r="B283" s="40" t="s">
-        <v>1867</v>
+        <v>1863</v>
       </c>
       <c r="C283" s="41"/>
       <c r="D283" s="42" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E283" s="42" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F283" s="42" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G283" s="42" t="s">
+        <v>1867</v>
+      </c>
+      <c r="H283" s="42" t="s">
         <v>1868</v>
-      </c>
-      <c r="E283" s="42" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F283" s="42" t="s">
-        <v>1870</v>
-      </c>
-      <c r="G283" s="42" t="s">
-        <v>1871</v>
-      </c>
-      <c r="H283" s="42" t="s">
-        <v>1872</v>
       </c>
       <c r="I283" s="2"/>
       <c r="J283" s="18" t="s">
@@ -23388,23 +23376,23 @@
         <v>98</v>
       </c>
       <c r="B284" s="37" t="s">
-        <v>1873</v>
+        <v>1869</v>
       </c>
       <c r="C284" s="38"/>
       <c r="D284" s="39" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E284" s="39" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F284" s="39" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G284" s="39" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H284" s="39" t="s">
         <v>1874</v>
-      </c>
-      <c r="E284" s="39" t="s">
-        <v>1875</v>
-      </c>
-      <c r="F284" s="39" t="s">
-        <v>1876</v>
-      </c>
-      <c r="G284" s="39" t="s">
-        <v>1877</v>
-      </c>
-      <c r="H284" s="39" t="s">
-        <v>1878</v>
       </c>
       <c r="I284" s="2"/>
       <c r="J284" s="18" t="s">
@@ -23422,23 +23410,23 @@
         <v>98</v>
       </c>
       <c r="B285" s="40" t="s">
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="C285" s="41"/>
       <c r="D285" s="42" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E285" s="42" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F285" s="42" t="s">
+        <v>1878</v>
+      </c>
+      <c r="G285" s="42" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H285" s="42" t="s">
         <v>1880</v>
-      </c>
-      <c r="E285" s="42" t="s">
-        <v>1881</v>
-      </c>
-      <c r="F285" s="42" t="s">
-        <v>1882</v>
-      </c>
-      <c r="G285" s="42" t="s">
-        <v>1883</v>
-      </c>
-      <c r="H285" s="42" t="s">
-        <v>1884</v>
       </c>
       <c r="I285" s="2"/>
       <c r="J285" s="18" t="s">
@@ -23456,23 +23444,23 @@
         <v>98</v>
       </c>
       <c r="B286" s="37" t="s">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="C286" s="38"/>
       <c r="D286" s="39" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E286" s="39" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F286" s="39" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G286" s="39" t="s">
+        <v>1885</v>
+      </c>
+      <c r="H286" s="39" t="s">
         <v>1886</v>
-      </c>
-      <c r="E286" s="39" t="s">
-        <v>1887</v>
-      </c>
-      <c r="F286" s="39" t="s">
-        <v>1888</v>
-      </c>
-      <c r="G286" s="39" t="s">
-        <v>1889</v>
-      </c>
-      <c r="H286" s="39" t="s">
-        <v>1890</v>
       </c>
       <c r="I286" s="2"/>
       <c r="J286" s="18" t="s">
@@ -23490,23 +23478,23 @@
         <v>98</v>
       </c>
       <c r="B287" s="40" t="s">
-        <v>1891</v>
+        <v>1887</v>
       </c>
       <c r="C287" s="41"/>
       <c r="D287" s="42" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E287" s="42" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F287" s="42" t="s">
+        <v>1890</v>
+      </c>
+      <c r="G287" s="42" t="s">
+        <v>1891</v>
+      </c>
+      <c r="H287" s="42" t="s">
         <v>1892</v>
-      </c>
-      <c r="E287" s="42" t="s">
-        <v>1893</v>
-      </c>
-      <c r="F287" s="42" t="s">
-        <v>1894</v>
-      </c>
-      <c r="G287" s="42" t="s">
-        <v>1895</v>
-      </c>
-      <c r="H287" s="42" t="s">
-        <v>1896</v>
       </c>
       <c r="I287" s="2"/>
       <c r="J287" s="18" t="s">
@@ -23524,23 +23512,23 @@
         <v>98</v>
       </c>
       <c r="B288" s="37" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="C288" s="38"/>
       <c r="D288" s="39" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E288" s="39" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F288" s="39" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G288" s="39" t="s">
+        <v>1897</v>
+      </c>
+      <c r="H288" s="39" t="s">
         <v>1898</v>
-      </c>
-      <c r="E288" s="39" t="s">
-        <v>1899</v>
-      </c>
-      <c r="F288" s="39" t="s">
-        <v>1900</v>
-      </c>
-      <c r="G288" s="39" t="s">
-        <v>1901</v>
-      </c>
-      <c r="H288" s="39" t="s">
-        <v>1902</v>
       </c>
       <c r="I288" s="2"/>
       <c r="J288" s="18" t="s">
@@ -24176,23 +24164,23 @@
         <v>98</v>
       </c>
       <c r="B312" s="40" t="s">
-        <v>1903</v>
+        <v>1899</v>
       </c>
       <c r="C312" s="41"/>
       <c r="D312" s="42" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E312" s="42" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F312" s="42" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G312" s="42" t="s">
+        <v>1903</v>
+      </c>
+      <c r="H312" s="42" t="s">
         <v>1904</v>
-      </c>
-      <c r="E312" s="42" t="s">
-        <v>1905</v>
-      </c>
-      <c r="F312" s="42" t="s">
-        <v>1906</v>
-      </c>
-      <c r="G312" s="42" t="s">
-        <v>1907</v>
-      </c>
-      <c r="H312" s="42" t="s">
-        <v>1908</v>
       </c>
       <c r="I312" s="2"/>
       <c r="J312" s="18" t="s">
@@ -24210,23 +24198,23 @@
         <v>98</v>
       </c>
       <c r="B313" s="37" t="s">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="C313" s="38"/>
       <c r="D313" s="39" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E313" s="39" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F313" s="39" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G313" s="39" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H313" s="39" t="s">
         <v>1910</v>
-      </c>
-      <c r="E313" s="39" t="s">
-        <v>1911</v>
-      </c>
-      <c r="F313" s="39" t="s">
-        <v>1912</v>
-      </c>
-      <c r="G313" s="39" t="s">
-        <v>1913</v>
-      </c>
-      <c r="H313" s="39" t="s">
-        <v>1914</v>
       </c>
       <c r="I313" s="2"/>
       <c r="J313" s="18" t="s">
@@ -24244,23 +24232,23 @@
         <v>98</v>
       </c>
       <c r="B314" s="40" t="s">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="C314" s="41"/>
       <c r="D314" s="42" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E314" s="42" t="s">
+        <v>1913</v>
+      </c>
+      <c r="F314" s="42" t="s">
+        <v>1914</v>
+      </c>
+      <c r="G314" s="42" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H314" s="42" t="s">
         <v>1916</v>
-      </c>
-      <c r="E314" s="42" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F314" s="42" t="s">
-        <v>1918</v>
-      </c>
-      <c r="G314" s="42" t="s">
-        <v>1919</v>
-      </c>
-      <c r="H314" s="42" t="s">
-        <v>1920</v>
       </c>
       <c r="I314" s="2"/>
       <c r="J314" s="18" t="s">
@@ -24278,23 +24266,23 @@
         <v>98</v>
       </c>
       <c r="B315" s="37" t="s">
-        <v>1921</v>
+        <v>1917</v>
       </c>
       <c r="C315" s="38"/>
       <c r="D315" s="39" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E315" s="39" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F315" s="39" t="s">
+        <v>1920</v>
+      </c>
+      <c r="G315" s="39" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H315" s="39" t="s">
         <v>1922</v>
-      </c>
-      <c r="E315" s="39" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F315" s="39" t="s">
-        <v>1924</v>
-      </c>
-      <c r="G315" s="39" t="s">
-        <v>1925</v>
-      </c>
-      <c r="H315" s="39" t="s">
-        <v>1926</v>
       </c>
       <c r="I315" s="2"/>
       <c r="J315" s="18" t="s">
@@ -24312,7 +24300,7 @@
         <v>99</v>
       </c>
       <c r="B316" s="49" t="s">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="C316" s="50"/>
       <c r="D316" s="50"/>
@@ -24334,23 +24322,23 @@
         <v>100</v>
       </c>
       <c r="B317" s="40" t="s">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="C317" s="41"/>
       <c r="D317" s="42" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E317" s="42" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F317" s="42" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G317" s="42" t="s">
+        <v>1927</v>
+      </c>
+      <c r="H317" s="42" t="s">
         <v>1928</v>
-      </c>
-      <c r="E317" s="42" t="s">
-        <v>1929</v>
-      </c>
-      <c r="F317" s="42" t="s">
-        <v>1930</v>
-      </c>
-      <c r="G317" s="42" t="s">
-        <v>1931</v>
-      </c>
-      <c r="H317" s="42" t="s">
-        <v>1932</v>
       </c>
       <c r="I317" s="2"/>
       <c r="J317" s="18"/>
@@ -24364,23 +24352,23 @@
         <v>100</v>
       </c>
       <c r="B318" s="37" t="s">
-        <v>1933</v>
+        <v>1929</v>
       </c>
       <c r="C318" s="38"/>
       <c r="D318" s="39" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E318" s="39" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F318" s="39" t="s">
+        <v>1932</v>
+      </c>
+      <c r="G318" s="39" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H318" s="39" t="s">
         <v>1934</v>
-      </c>
-      <c r="E318" s="39" t="s">
-        <v>1935</v>
-      </c>
-      <c r="F318" s="39" t="s">
-        <v>1936</v>
-      </c>
-      <c r="G318" s="39" t="s">
-        <v>1937</v>
-      </c>
-      <c r="H318" s="39" t="s">
-        <v>1938</v>
       </c>
       <c r="I318" s="2"/>
       <c r="J318" s="18"/>
@@ -24394,23 +24382,23 @@
         <v>100</v>
       </c>
       <c r="B319" s="40" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="C319" s="41"/>
       <c r="D319" s="42" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E319" s="42" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F319" s="42" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G319" s="42" t="s">
+        <v>1939</v>
+      </c>
+      <c r="H319" s="42" t="s">
         <v>1940</v>
-      </c>
-      <c r="E319" s="42" t="s">
-        <v>1941</v>
-      </c>
-      <c r="F319" s="42" t="s">
-        <v>1942</v>
-      </c>
-      <c r="G319" s="42" t="s">
-        <v>1943</v>
-      </c>
-      <c r="H319" s="42" t="s">
-        <v>1944</v>
       </c>
       <c r="I319" s="2"/>
       <c r="J319" s="18"/>
@@ -24424,7 +24412,7 @@
         <v>99</v>
       </c>
       <c r="B320" s="49" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="C320" s="50"/>
       <c r="D320" s="50"/>
@@ -24446,23 +24434,23 @@
         <v>100</v>
       </c>
       <c r="B321" s="37" t="s">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="C321" s="38"/>
       <c r="D321" s="39" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E321" s="39" t="s">
+        <v>1943</v>
+      </c>
+      <c r="F321" s="39" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G321" s="39" t="s">
+        <v>1945</v>
+      </c>
+      <c r="H321" s="39" t="s">
         <v>1946</v>
-      </c>
-      <c r="E321" s="39" t="s">
-        <v>1947</v>
-      </c>
-      <c r="F321" s="39" t="s">
-        <v>1948</v>
-      </c>
-      <c r="G321" s="39" t="s">
-        <v>1949</v>
-      </c>
-      <c r="H321" s="39" t="s">
-        <v>1950</v>
       </c>
       <c r="I321" s="2"/>
       <c r="J321" s="18"/>
@@ -24476,23 +24464,23 @@
         <v>100</v>
       </c>
       <c r="B322" s="40" t="s">
-        <v>1951</v>
+        <v>1947</v>
       </c>
       <c r="C322" s="41"/>
       <c r="D322" s="42" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E322" s="42" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F322" s="42" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G322" s="42" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H322" s="42" t="s">
         <v>1952</v>
-      </c>
-      <c r="E322" s="42" t="s">
-        <v>1953</v>
-      </c>
-      <c r="F322" s="42" t="s">
-        <v>1954</v>
-      </c>
-      <c r="G322" s="42" t="s">
-        <v>1955</v>
-      </c>
-      <c r="H322" s="42" t="s">
-        <v>1956</v>
       </c>
       <c r="I322" s="2"/>
       <c r="J322" s="18"/>
@@ -24506,7 +24494,7 @@
         <v>99</v>
       </c>
       <c r="B323" s="49" t="s">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="C323" s="50"/>
       <c r="D323" s="50"/>
@@ -24528,23 +24516,23 @@
         <v>100</v>
       </c>
       <c r="B324" s="37" t="s">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="C324" s="51"/>
       <c r="D324" s="39" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E324" s="39" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F324" s="39" t="s">
+        <v>1956</v>
+      </c>
+      <c r="G324" s="39" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H324" s="39" t="s">
         <v>1958</v>
-      </c>
-      <c r="E324" s="39" t="s">
-        <v>1959</v>
-      </c>
-      <c r="F324" s="39" t="s">
-        <v>1960</v>
-      </c>
-      <c r="G324" s="39" t="s">
-        <v>1961</v>
-      </c>
-      <c r="H324" s="39" t="s">
-        <v>1962</v>
       </c>
       <c r="I324" s="2"/>
       <c r="J324" s="18"/>
@@ -24558,23 +24546,23 @@
         <v>100</v>
       </c>
       <c r="B325" s="40" t="s">
-        <v>1963</v>
+        <v>1959</v>
       </c>
       <c r="C325" s="43"/>
       <c r="D325" s="42" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E325" s="42" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F325" s="42" t="s">
+        <v>1956</v>
+      </c>
+      <c r="G325" s="42" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H325" s="42" t="s">
         <v>1958</v>
-      </c>
-      <c r="E325" s="42" t="s">
-        <v>1959</v>
-      </c>
-      <c r="F325" s="42" t="s">
-        <v>1960</v>
-      </c>
-      <c r="G325" s="42" t="s">
-        <v>1961</v>
-      </c>
-      <c r="H325" s="42" t="s">
-        <v>1962</v>
       </c>
       <c r="I325" s="2"/>
       <c r="J325" s="18"/>
@@ -24588,23 +24576,23 @@
         <v>100</v>
       </c>
       <c r="B326" s="37" t="s">
-        <v>1964</v>
+        <v>1960</v>
       </c>
       <c r="C326" s="51"/>
       <c r="D326" s="39" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E326" s="39" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F326" s="39" t="s">
+        <v>1956</v>
+      </c>
+      <c r="G326" s="39" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H326" s="39" t="s">
         <v>1958</v>
-      </c>
-      <c r="E326" s="39" t="s">
-        <v>1959</v>
-      </c>
-      <c r="F326" s="39" t="s">
-        <v>1960</v>
-      </c>
-      <c r="G326" s="39" t="s">
-        <v>1961</v>
-      </c>
-      <c r="H326" s="39" t="s">
-        <v>1962</v>
       </c>
       <c r="I326" s="2"/>
       <c r="J326" s="18"/>
@@ -24618,23 +24606,23 @@
         <v>100</v>
       </c>
       <c r="B327" s="40" t="s">
-        <v>1965</v>
+        <v>1961</v>
       </c>
       <c r="C327" s="41"/>
       <c r="D327" s="42" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E327" s="42" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F327" s="42" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G327" s="42" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H327" s="42" t="s">
         <v>1966</v>
-      </c>
-      <c r="E327" s="42" t="s">
-        <v>1967</v>
-      </c>
-      <c r="F327" s="42" t="s">
-        <v>1968</v>
-      </c>
-      <c r="G327" s="42" t="s">
-        <v>1969</v>
-      </c>
-      <c r="H327" s="42" t="s">
-        <v>1970</v>
       </c>
       <c r="I327" s="2"/>
       <c r="J327" s="18"/>
@@ -24648,23 +24636,23 @@
         <v>100</v>
       </c>
       <c r="B328" s="37" t="s">
-        <v>1971</v>
+        <v>1967</v>
       </c>
       <c r="C328" s="38"/>
       <c r="D328" s="39" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E328" s="39" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F328" s="39" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G328" s="39" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H328" s="39" t="s">
         <v>1972</v>
-      </c>
-      <c r="E328" s="39" t="s">
-        <v>1973</v>
-      </c>
-      <c r="F328" s="39" t="s">
-        <v>1974</v>
-      </c>
-      <c r="G328" s="39" t="s">
-        <v>1975</v>
-      </c>
-      <c r="H328" s="39" t="s">
-        <v>1976</v>
       </c>
       <c r="I328" s="2"/>
       <c r="J328" s="18"/>
@@ -26262,23 +26250,23 @@
         <v>98</v>
       </c>
       <c r="B379" s="52" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" s="52" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E379" s="52" t="s">
+        <v>2054</v>
+      </c>
+      <c r="F379" s="52" t="s">
+        <v>2055</v>
+      </c>
+      <c r="G379" s="52" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H379" s="52" t="s">
         <v>2057</v>
-      </c>
-      <c r="E379" s="52" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F379" s="52" t="s">
-        <v>2059</v>
-      </c>
-      <c r="G379" s="52" t="s">
-        <v>2060</v>
-      </c>
-      <c r="H379" s="52" t="s">
-        <v>2061</v>
       </c>
       <c r="I379" s="2"/>
       <c r="J379" s="18" t="s">
@@ -26296,23 +26284,23 @@
         <v>98</v>
       </c>
       <c r="B380" s="53" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="53" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E380" s="53" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F380" s="53" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G380" s="53" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H380" s="53" t="s">
         <v>2062</v>
-      </c>
-      <c r="E380" s="53" t="s">
-        <v>2063</v>
-      </c>
-      <c r="F380" s="53" t="s">
-        <v>2064</v>
-      </c>
-      <c r="G380" s="53" t="s">
-        <v>2065</v>
-      </c>
-      <c r="H380" s="53" t="s">
-        <v>2066</v>
       </c>
       <c r="I380" s="2"/>
       <c r="J380" s="18" t="s">
@@ -26330,23 +26318,23 @@
         <v>98</v>
       </c>
       <c r="B381" s="52" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" s="52" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E381" s="52" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F381" s="52" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G381" s="52" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H381" s="52" t="s">
         <v>2062</v>
-      </c>
-      <c r="E381" s="52" t="s">
-        <v>2063</v>
-      </c>
-      <c r="F381" s="52" t="s">
-        <v>2064</v>
-      </c>
-      <c r="G381" s="52" t="s">
-        <v>2065</v>
-      </c>
-      <c r="H381" s="52" t="s">
-        <v>2066</v>
       </c>
       <c r="I381" s="2"/>
       <c r="J381" s="18" t="s">
@@ -26364,23 +26352,23 @@
         <v>98</v>
       </c>
       <c r="B382" s="53" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" s="53" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E382" s="53" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F382" s="53" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G382" s="53" t="s">
+        <v>2066</v>
+      </c>
+      <c r="H382" s="53" t="s">
         <v>2067</v>
-      </c>
-      <c r="E382" s="53" t="s">
-        <v>2068</v>
-      </c>
-      <c r="F382" s="53" t="s">
-        <v>2069</v>
-      </c>
-      <c r="G382" s="53" t="s">
-        <v>2070</v>
-      </c>
-      <c r="H382" s="53" t="s">
-        <v>2071</v>
       </c>
       <c r="I382" s="2"/>
       <c r="J382" s="18" t="s">
@@ -26398,23 +26386,23 @@
         <v>98</v>
       </c>
       <c r="B383" s="52" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" s="52" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
       <c r="E383" s="52" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
       <c r="F383" s="52" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
       <c r="G383" s="52" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="H383" s="52" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="I383" s="2"/>
       <c r="J383" s="18" t="s">
@@ -26432,23 +26420,23 @@
         <v>98</v>
       </c>
       <c r="B384" s="53" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" s="53" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
       <c r="E384" s="53" t="s">
-        <v>2077</v>
+        <v>2073</v>
       </c>
       <c r="F384" s="53" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
       <c r="G384" s="53" t="s">
-        <v>2079</v>
+        <v>2075</v>
       </c>
       <c r="H384" s="53" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="I384" s="2"/>
       <c r="J384" s="18" t="s">
@@ -26466,23 +26454,23 @@
         <v>98</v>
       </c>
       <c r="B385" s="52" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" s="52" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
       <c r="E385" s="52" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
       <c r="F385" s="52" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="G385" s="52" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="H385" s="52" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="I385" s="2"/>
       <c r="J385" s="18" t="s">
@@ -26500,23 +26488,23 @@
         <v>98</v>
       </c>
       <c r="B386" s="53" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" s="53" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E386" s="53" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F386" s="53" t="s">
+        <v>2082</v>
+      </c>
+      <c r="G386" s="53" t="s">
+        <v>2083</v>
+      </c>
+      <c r="H386" s="53" t="s">
         <v>2084</v>
-      </c>
-      <c r="E386" s="53" t="s">
-        <v>2085</v>
-      </c>
-      <c r="F386" s="53" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G386" s="53" t="s">
-        <v>2087</v>
-      </c>
-      <c r="H386" s="53" t="s">
-        <v>2088</v>
       </c>
       <c r="I386" s="2"/>
       <c r="J386" s="18" t="s">
@@ -26534,23 +26522,23 @@
         <v>98</v>
       </c>
       <c r="B387" s="52" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" s="52" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="E387" s="52" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="F387" s="52" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="G387" s="52" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
       <c r="H387" s="52" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="I387" s="2"/>
       <c r="J387" s="18" t="s">
@@ -26568,23 +26556,23 @@
         <v>98</v>
       </c>
       <c r="B388" s="53" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" s="53" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="E388" s="53" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="F388" s="53" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="G388" s="53" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
       <c r="H388" s="53" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="I388" s="2"/>
       <c r="J388" s="18" t="s">
@@ -26602,23 +26590,23 @@
         <v>98</v>
       </c>
       <c r="B389" s="52" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" s="52" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E389" s="52" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F389" s="52" t="s">
+        <v>2091</v>
+      </c>
+      <c r="G389" s="52" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H389" s="52" t="s">
         <v>2093</v>
-      </c>
-      <c r="E389" s="52" t="s">
-        <v>2094</v>
-      </c>
-      <c r="F389" s="52" t="s">
-        <v>2095</v>
-      </c>
-      <c r="G389" s="52" t="s">
-        <v>2096</v>
-      </c>
-      <c r="H389" s="52" t="s">
-        <v>2097</v>
       </c>
       <c r="I389" s="2"/>
       <c r="J389" s="18" t="s">
@@ -26636,23 +26624,23 @@
         <v>98</v>
       </c>
       <c r="B390" s="53" t="s">
-        <v>2054</v>
+        <v>2050</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" s="53" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E390" s="53" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F390" s="53" t="s">
+        <v>2096</v>
+      </c>
+      <c r="G390" s="53" t="s">
+        <v>2097</v>
+      </c>
+      <c r="H390" s="53" t="s">
         <v>2098</v>
-      </c>
-      <c r="E390" s="53" t="s">
-        <v>2099</v>
-      </c>
-      <c r="F390" s="53" t="s">
-        <v>2100</v>
-      </c>
-      <c r="G390" s="53" t="s">
-        <v>2101</v>
-      </c>
-      <c r="H390" s="53" t="s">
-        <v>2102</v>
       </c>
       <c r="I390" s="2"/>
       <c r="J390" s="18" t="s">
@@ -26670,23 +26658,23 @@
         <v>98</v>
       </c>
       <c r="B391" s="52" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" s="52" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
       <c r="E391" s="52" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
       <c r="F391" s="52" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="G391" s="52" t="s">
-        <v>2106</v>
+        <v>2102</v>
       </c>
       <c r="H391" s="52" t="s">
-        <v>2102</v>
+        <v>2098</v>
       </c>
       <c r="I391" s="2"/>
       <c r="J391" s="18" t="s">
@@ -26704,23 +26692,23 @@
         <v>98</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2056</v>
+        <v>2052</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" s="53" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="E392" s="53" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="F392" s="53" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="G392" s="53" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="H392" s="53" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="I392" s="2"/>
       <c r="J392" s="18" t="s">
@@ -27660,7 +27648,7 @@
         <v>99</v>
       </c>
       <c r="B419" s="54" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="C419" s="54"/>
       <c r="D419" s="54"/>
@@ -27682,23 +27670,23 @@
         <v>100</v>
       </c>
       <c r="B420" s="54" t="s">
-        <v>2225</v>
+        <v>2221</v>
       </c>
       <c r="C420" s="54"/>
       <c r="D420" s="54" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E420" s="54" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F420" s="54" t="s">
+        <v>2109</v>
+      </c>
+      <c r="G420" s="54" t="s">
+        <v>2110</v>
+      </c>
+      <c r="H420" s="55" t="s">
         <v>2111</v>
-      </c>
-      <c r="E420" s="54" t="s">
-        <v>2112</v>
-      </c>
-      <c r="F420" s="54" t="s">
-        <v>2113</v>
-      </c>
-      <c r="G420" s="54" t="s">
-        <v>2114</v>
-      </c>
-      <c r="H420" s="55" t="s">
-        <v>2115</v>
       </c>
       <c r="I420" s="2"/>
       <c r="J420" s="18"/>
@@ -27712,23 +27700,23 @@
         <v>100</v>
       </c>
       <c r="B421" s="54" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="C421" s="54"/>
       <c r="D421" s="54" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="E421" s="54" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
       <c r="F421" s="54" t="s">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="G421" s="54" t="s">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="H421" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I421" s="2"/>
       <c r="J421" s="18"/>
@@ -27742,23 +27730,23 @@
         <v>100</v>
       </c>
       <c r="B422" s="54" t="s">
-        <v>2227</v>
+        <v>2223</v>
       </c>
       <c r="C422" s="54"/>
       <c r="D422" s="54" t="s">
-        <v>2120</v>
+        <v>2116</v>
       </c>
       <c r="E422" s="54" t="s">
-        <v>2121</v>
+        <v>2117</v>
       </c>
       <c r="F422" s="54" t="s">
-        <v>2122</v>
+        <v>2118</v>
       </c>
       <c r="G422" s="54" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="H422" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I422" s="2"/>
       <c r="J422" s="18"/>
@@ -27772,23 +27760,23 @@
         <v>100</v>
       </c>
       <c r="B423" s="54" t="s">
-        <v>2228</v>
+        <v>2224</v>
       </c>
       <c r="C423" s="54"/>
       <c r="D423" s="54" t="s">
-        <v>2124</v>
+        <v>2120</v>
       </c>
       <c r="E423" s="54" t="s">
-        <v>2125</v>
+        <v>2121</v>
       </c>
       <c r="F423" s="54" t="s">
-        <v>2126</v>
+        <v>2122</v>
       </c>
       <c r="G423" s="54" t="s">
-        <v>2127</v>
+        <v>2123</v>
       </c>
       <c r="H423" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I423" s="2"/>
       <c r="J423" s="18"/>
@@ -27802,7 +27790,7 @@
         <v>99</v>
       </c>
       <c r="B424" s="54" t="s">
-        <v>2229</v>
+        <v>2225</v>
       </c>
       <c r="C424" s="54"/>
       <c r="D424" s="54"/>
@@ -27824,23 +27812,23 @@
         <v>100</v>
       </c>
       <c r="B425" s="54" t="s">
-        <v>2230</v>
+        <v>2226</v>
       </c>
       <c r="C425" s="54"/>
       <c r="D425" s="54" t="s">
-        <v>2128</v>
+        <v>2124</v>
       </c>
       <c r="E425" s="54" t="s">
-        <v>2129</v>
+        <v>2125</v>
       </c>
       <c r="F425" s="54" t="s">
-        <v>2130</v>
+        <v>2126</v>
       </c>
       <c r="G425" s="54" t="s">
-        <v>2131</v>
+        <v>2127</v>
       </c>
       <c r="H425" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I425" s="2"/>
       <c r="J425" s="18"/>
@@ -27854,23 +27842,23 @@
         <v>100</v>
       </c>
       <c r="B426" s="54" t="s">
-        <v>2231</v>
+        <v>2227</v>
       </c>
       <c r="C426" s="54"/>
       <c r="D426" s="54" t="s">
-        <v>2132</v>
+        <v>2128</v>
       </c>
       <c r="E426" s="54" t="s">
-        <v>2133</v>
+        <v>2129</v>
       </c>
       <c r="F426" s="54" t="s">
-        <v>2134</v>
+        <v>2130</v>
       </c>
       <c r="G426" s="54" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="H426" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I426" s="2"/>
       <c r="J426" s="18"/>
@@ -27884,23 +27872,23 @@
         <v>100</v>
       </c>
       <c r="B427" s="54" t="s">
-        <v>2232</v>
+        <v>2228</v>
       </c>
       <c r="C427" s="54"/>
       <c r="D427" s="54" t="s">
-        <v>2136</v>
+        <v>2132</v>
       </c>
       <c r="E427" s="54" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="F427" s="54" t="s">
-        <v>2138</v>
+        <v>2134</v>
       </c>
       <c r="G427" s="54" t="s">
-        <v>2139</v>
+        <v>2135</v>
       </c>
       <c r="H427" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I427" s="2"/>
       <c r="J427" s="18"/>
@@ -27914,23 +27902,23 @@
         <v>100</v>
       </c>
       <c r="B428" s="54" t="s">
-        <v>2233</v>
+        <v>2229</v>
       </c>
       <c r="C428" s="54"/>
       <c r="D428" s="54" t="s">
-        <v>2140</v>
+        <v>2136</v>
       </c>
       <c r="E428" s="54" t="s">
-        <v>2141</v>
+        <v>2137</v>
       </c>
       <c r="F428" s="54" t="s">
-        <v>2142</v>
+        <v>2138</v>
       </c>
       <c r="G428" s="54" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="H428" s="55" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="I428" s="2"/>
       <c r="J428" s="18"/>
@@ -27944,7 +27932,7 @@
         <v>99</v>
       </c>
       <c r="B429" s="54" t="s">
-        <v>2234</v>
+        <v>2230</v>
       </c>
       <c r="C429" s="54"/>
       <c r="D429" s="54"/>
@@ -27966,23 +27954,23 @@
         <v>100</v>
       </c>
       <c r="B430" s="54" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="C430" s="54"/>
       <c r="D430" s="54" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E430" s="54" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F430" s="54" t="s">
+        <v>2142</v>
+      </c>
+      <c r="G430" s="54" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H430" s="55" t="s">
         <v>2144</v>
-      </c>
-      <c r="E430" s="54" t="s">
-        <v>2145</v>
-      </c>
-      <c r="F430" s="54" t="s">
-        <v>2146</v>
-      </c>
-      <c r="G430" s="54" t="s">
-        <v>2147</v>
-      </c>
-      <c r="H430" s="55" t="s">
-        <v>2148</v>
       </c>
       <c r="I430" s="2"/>
       <c r="J430" s="18"/>
@@ -27996,11 +27984,11 @@
         <v>100</v>
       </c>
       <c r="B431" s="54" t="s">
-        <v>2236</v>
+        <v>2232</v>
       </c>
       <c r="C431" s="54"/>
       <c r="D431" s="56" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="E431" s="56">
         <v>37</v>
@@ -28012,7 +28000,7 @@
         <v>13516</v>
       </c>
       <c r="H431" s="55" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="I431" s="2"/>
       <c r="J431" s="18"/>
@@ -28026,23 +28014,23 @@
         <v>100</v>
       </c>
       <c r="B432" s="54" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
       <c r="C432" s="54"/>
       <c r="D432" s="54" t="s">
-        <v>2150</v>
+        <v>2146</v>
       </c>
       <c r="E432" s="54" t="s">
-        <v>2151</v>
+        <v>2147</v>
       </c>
       <c r="F432" s="54" t="s">
-        <v>2152</v>
+        <v>2148</v>
       </c>
       <c r="G432" s="54" t="s">
-        <v>2153</v>
+        <v>2149</v>
       </c>
       <c r="H432" s="55" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="I432" s="2"/>
       <c r="J432" s="18"/>
@@ -28056,7 +28044,7 @@
         <v>100</v>
       </c>
       <c r="B433" s="54" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="C433" s="54"/>
       <c r="D433" s="56">
@@ -28069,10 +28057,10 @@
         <v>43</v>
       </c>
       <c r="G433" s="56" t="s">
-        <v>2154</v>
+        <v>2150</v>
       </c>
       <c r="H433" s="55" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="I433" s="2"/>
       <c r="J433" s="18"/>
@@ -28086,7 +28074,7 @@
         <v>99</v>
       </c>
       <c r="B434" s="54" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="C434" s="54"/>
       <c r="D434" s="54"/>
@@ -28108,23 +28096,23 @@
         <v>100</v>
       </c>
       <c r="B435" s="54" t="s">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="C435" s="54"/>
       <c r="D435" s="54" t="s">
-        <v>2155</v>
+        <v>2151</v>
       </c>
       <c r="E435" s="54" t="s">
-        <v>2156</v>
+        <v>2152</v>
       </c>
       <c r="F435" s="54" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
       <c r="G435" s="54" t="s">
-        <v>2158</v>
+        <v>2154</v>
       </c>
       <c r="H435" s="55" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="I435" s="2"/>
       <c r="J435" s="18"/>
@@ -28138,23 +28126,23 @@
         <v>100</v>
       </c>
       <c r="B436" s="54" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="C436" s="54"/>
       <c r="D436" s="56" t="s">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="E436" s="56">
         <v>1</v>
       </c>
       <c r="F436" s="56" t="s">
-        <v>2159</v>
+        <v>2155</v>
       </c>
       <c r="G436" s="56" t="s">
-        <v>2160</v>
+        <v>2156</v>
       </c>
       <c r="H436" s="55" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="I436" s="2"/>
       <c r="J436" s="18"/>
@@ -28168,23 +28156,23 @@
         <v>98</v>
       </c>
       <c r="B437" s="54" t="s">
-        <v>2242</v>
+        <v>2238</v>
       </c>
       <c r="C437" s="54"/>
       <c r="D437" s="54" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E437" s="54" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F437" s="54" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G437" s="54" t="s">
+        <v>2160</v>
+      </c>
+      <c r="H437" s="55" t="s">
         <v>2161</v>
-      </c>
-      <c r="E437" s="54" t="s">
-        <v>2162</v>
-      </c>
-      <c r="F437" s="54" t="s">
-        <v>2163</v>
-      </c>
-      <c r="G437" s="54" t="s">
-        <v>2164</v>
-      </c>
-      <c r="H437" s="55" t="s">
-        <v>2165</v>
       </c>
       <c r="I437" s="2"/>
       <c r="J437" s="18" t="s">
@@ -28202,23 +28190,23 @@
         <v>98</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2243</v>
+        <v>2239</v>
       </c>
       <c r="C438" s="54"/>
       <c r="D438" s="54" t="s">
-        <v>2166</v>
+        <v>2162</v>
       </c>
       <c r="E438" s="54" t="s">
-        <v>2167</v>
+        <v>2163</v>
       </c>
       <c r="F438" s="54" t="s">
-        <v>2168</v>
+        <v>2164</v>
       </c>
       <c r="G438" s="54" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="H438" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I438" s="2"/>
       <c r="J438" s="18" t="s">
@@ -28236,23 +28224,23 @@
         <v>98</v>
       </c>
       <c r="B439" s="54" t="s">
-        <v>2244</v>
+        <v>2240</v>
       </c>
       <c r="C439" s="54"/>
       <c r="D439" s="54" t="s">
-        <v>2170</v>
+        <v>2166</v>
       </c>
       <c r="E439" s="54" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="F439" s="54" t="s">
-        <v>2172</v>
+        <v>2168</v>
       </c>
       <c r="G439" s="54" t="s">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="H439" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I439" s="2"/>
       <c r="J439" s="18" t="s">
@@ -28270,23 +28258,23 @@
         <v>98</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="C440" s="54"/>
       <c r="D440" s="54" t="s">
-        <v>2174</v>
+        <v>2170</v>
       </c>
       <c r="E440" s="54" t="s">
-        <v>2175</v>
+        <v>2171</v>
       </c>
       <c r="F440" s="54" t="s">
-        <v>2176</v>
+        <v>2172</v>
       </c>
       <c r="G440" s="54" t="s">
-        <v>2177</v>
+        <v>2173</v>
       </c>
       <c r="H440" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I440" s="2"/>
       <c r="J440" s="18" t="s">
@@ -28304,23 +28292,23 @@
         <v>98</v>
       </c>
       <c r="B441" s="54" t="s">
-        <v>2246</v>
+        <v>2242</v>
       </c>
       <c r="C441" s="54"/>
       <c r="D441" s="54" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="E441" s="54" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="F441" s="54" t="s">
-        <v>2180</v>
+        <v>2176</v>
       </c>
       <c r="G441" s="54" t="s">
-        <v>2181</v>
+        <v>2177</v>
       </c>
       <c r="H441" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I441" s="2"/>
       <c r="J441" s="18" t="s">
@@ -28338,23 +28326,23 @@
         <v>98</v>
       </c>
       <c r="B442" s="54" t="s">
-        <v>2247</v>
+        <v>2243</v>
       </c>
       <c r="C442" s="54"/>
       <c r="D442" s="54" t="s">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="E442" s="54" t="s">
-        <v>2183</v>
+        <v>2179</v>
       </c>
       <c r="F442" s="54" t="s">
-        <v>2184</v>
+        <v>2180</v>
       </c>
       <c r="G442" s="54" t="s">
-        <v>2185</v>
+        <v>2181</v>
       </c>
       <c r="H442" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I442" s="2"/>
       <c r="J442" s="18" t="s">
@@ -28372,23 +28360,23 @@
         <v>98</v>
       </c>
       <c r="B443" s="54" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="C443" s="54"/>
       <c r="D443" s="54" t="s">
-        <v>2186</v>
+        <v>2182</v>
       </c>
       <c r="E443" s="54" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="F443" s="54" t="s">
-        <v>2188</v>
+        <v>2184</v>
       </c>
       <c r="G443" s="54" t="s">
-        <v>2189</v>
+        <v>2185</v>
       </c>
       <c r="H443" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I443" s="2"/>
       <c r="J443" s="18" t="s">
@@ -28406,23 +28394,23 @@
         <v>98</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2249</v>
+        <v>2245</v>
       </c>
       <c r="C444" s="54"/>
       <c r="D444" s="54" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="E444" s="54" t="s">
-        <v>2191</v>
+        <v>2187</v>
       </c>
       <c r="F444" s="54" t="s">
-        <v>2192</v>
+        <v>2188</v>
       </c>
       <c r="G444" s="54" t="s">
-        <v>2193</v>
+        <v>2189</v>
       </c>
       <c r="H444" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I444" s="2"/>
       <c r="J444" s="18" t="s">
@@ -28440,7 +28428,7 @@
         <v>99</v>
       </c>
       <c r="B445" s="54" t="s">
-        <v>2194</v>
+        <v>2190</v>
       </c>
       <c r="C445" s="54"/>
       <c r="D445" s="54"/>
@@ -28462,23 +28450,23 @@
         <v>100</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2250</v>
+        <v>2246</v>
       </c>
       <c r="C446" s="54"/>
       <c r="D446" s="54" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E446" s="54" t="s">
+        <v>2192</v>
+      </c>
+      <c r="F446" s="54" t="s">
+        <v>2193</v>
+      </c>
+      <c r="G446" s="54" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H446" s="55" t="s">
         <v>2195</v>
-      </c>
-      <c r="E446" s="54" t="s">
-        <v>2196</v>
-      </c>
-      <c r="F446" s="54" t="s">
-        <v>2197</v>
-      </c>
-      <c r="G446" s="54" t="s">
-        <v>2198</v>
-      </c>
-      <c r="H446" s="55" t="s">
-        <v>2199</v>
       </c>
       <c r="I446" s="2"/>
       <c r="J446" s="18"/>
@@ -28492,23 +28480,23 @@
         <v>100</v>
       </c>
       <c r="B447" s="54" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="C447" s="54"/>
       <c r="D447" s="54" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E447" s="54" t="s">
+        <v>2197</v>
+      </c>
+      <c r="F447" s="54" t="s">
+        <v>2198</v>
+      </c>
+      <c r="G447" s="54" t="s">
+        <v>2199</v>
+      </c>
+      <c r="H447" s="54" t="s">
         <v>2200</v>
-      </c>
-      <c r="E447" s="54" t="s">
-        <v>2201</v>
-      </c>
-      <c r="F447" s="54" t="s">
-        <v>2202</v>
-      </c>
-      <c r="G447" s="54" t="s">
-        <v>2203</v>
-      </c>
-      <c r="H447" s="54" t="s">
-        <v>2204</v>
       </c>
       <c r="I447" s="2"/>
       <c r="J447" s="18"/>
@@ -28522,23 +28510,23 @@
         <v>100</v>
       </c>
       <c r="B448" s="54" t="s">
-        <v>2252</v>
+        <v>2248</v>
       </c>
       <c r="C448" s="54"/>
       <c r="D448" s="54" t="s">
-        <v>2205</v>
+        <v>2201</v>
       </c>
       <c r="E448" s="54" t="s">
-        <v>2206</v>
+        <v>2202</v>
       </c>
       <c r="F448" s="54" t="s">
-        <v>2207</v>
+        <v>2203</v>
       </c>
       <c r="G448" s="54" t="s">
-        <v>2208</v>
+        <v>2204</v>
       </c>
       <c r="H448" s="55" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="I448" s="2"/>
       <c r="J448" s="18"/>
@@ -28552,7 +28540,7 @@
         <v>99</v>
       </c>
       <c r="B449" s="54" t="s">
-        <v>2209</v>
+        <v>2205</v>
       </c>
       <c r="C449" s="54"/>
       <c r="D449" s="54"/>
@@ -28574,23 +28562,23 @@
         <v>100</v>
       </c>
       <c r="B450" s="54" t="s">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="C450" s="54"/>
       <c r="D450" s="54" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E450" s="54" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F450" s="54" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G450" s="54" t="s">
+        <v>2209</v>
+      </c>
+      <c r="H450" s="55" t="s">
         <v>2210</v>
-      </c>
-      <c r="E450" s="54" t="s">
-        <v>2211</v>
-      </c>
-      <c r="F450" s="54" t="s">
-        <v>2212</v>
-      </c>
-      <c r="G450" s="54" t="s">
-        <v>2213</v>
-      </c>
-      <c r="H450" s="55" t="s">
-        <v>2214</v>
       </c>
       <c r="I450" s="2"/>
       <c r="J450" s="18"/>
@@ -28604,23 +28592,23 @@
         <v>100</v>
       </c>
       <c r="B451" s="54" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="C451" s="54"/>
       <c r="D451" s="54" t="s">
-        <v>2215</v>
+        <v>2211</v>
       </c>
       <c r="E451" s="54" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="F451" s="54" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="G451" s="54" t="s">
-        <v>2218</v>
+        <v>2214</v>
       </c>
       <c r="H451" s="55" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="I451" s="2"/>
       <c r="J451" s="18"/>
@@ -28634,23 +28622,23 @@
         <v>100</v>
       </c>
       <c r="B452" s="54" t="s">
-        <v>2255</v>
+        <v>2251</v>
       </c>
       <c r="C452" s="54"/>
       <c r="D452" s="54" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E452" s="54" t="s">
+        <v>2216</v>
+      </c>
+      <c r="F452" s="54" t="s">
+        <v>2217</v>
+      </c>
+      <c r="G452" s="54" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H452" s="54" t="s">
         <v>2219</v>
-      </c>
-      <c r="E452" s="54" t="s">
-        <v>2220</v>
-      </c>
-      <c r="F452" s="54" t="s">
-        <v>2221</v>
-      </c>
-      <c r="G452" s="54" t="s">
-        <v>2222</v>
-      </c>
-      <c r="H452" s="54" t="s">
-        <v>2223</v>
       </c>
       <c r="I452" s="2"/>
       <c r="J452" s="18"/>
@@ -29223,7 +29211,7 @@
         <v>11</v>
       </c>
       <c r="K468" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L468" s="18">
         <v>1</v>
@@ -29257,7 +29245,7 @@
         <v>11</v>
       </c>
       <c r="K469" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L469" s="18">
         <v>1</v>
@@ -29291,7 +29279,7 @@
         <v>11</v>
       </c>
       <c r="K470" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L470" s="18">
         <v>1</v>
@@ -29325,7 +29313,7 @@
         <v>11</v>
       </c>
       <c r="K471" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L471" s="18">
         <v>1</v>
@@ -29359,7 +29347,7 @@
         <v>11</v>
       </c>
       <c r="K472" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L472" s="18">
         <v>1</v>
@@ -29393,7 +29381,7 @@
         <v>11</v>
       </c>
       <c r="K473" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L473" s="18">
         <v>1</v>
@@ -29427,7 +29415,7 @@
         <v>11</v>
       </c>
       <c r="K474" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L474" s="18">
         <v>1</v>
@@ -29461,7 +29449,7 @@
         <v>11</v>
       </c>
       <c r="K475" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L475" s="18">
         <v>1</v>
@@ -29495,7 +29483,7 @@
         <v>11</v>
       </c>
       <c r="K476" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L476" s="18">
         <v>1</v>
@@ -29529,7 +29517,7 @@
         <v>11</v>
       </c>
       <c r="K477" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L477" s="18">
         <v>1</v>
@@ -29540,7 +29528,7 @@
         <v>99</v>
       </c>
       <c r="B478" s="44" t="s">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="C478" s="2"/>
       <c r="D478" s="2"/>
@@ -29553,7 +29541,7 @@
         <v>11</v>
       </c>
       <c r="K478" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L478" s="18"/>
     </row>
@@ -29562,23 +29550,23 @@
         <v>100</v>
       </c>
       <c r="B479" s="44" t="s">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="C479" s="2"/>
       <c r="D479" s="44" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E479" s="44" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F479" s="44" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G479" s="44" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H479" s="44" t="s">
         <v>1983</v>
-      </c>
-      <c r="E479" s="44" t="s">
-        <v>1984</v>
-      </c>
-      <c r="F479" s="44" t="s">
-        <v>1985</v>
-      </c>
-      <c r="G479" s="44" t="s">
-        <v>1986</v>
-      </c>
-      <c r="H479" s="44" t="s">
-        <v>1987</v>
       </c>
       <c r="I479" s="2"/>
       <c r="J479" s="18"/>
@@ -29592,7 +29580,7 @@
         <v>99</v>
       </c>
       <c r="B480" s="45" t="s">
-        <v>1990</v>
+        <v>1986</v>
       </c>
       <c r="C480" s="2"/>
       <c r="D480" s="2"/>
@@ -29605,7 +29593,7 @@
         <v>11</v>
       </c>
       <c r="K480" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L480" s="18"/>
     </row>
@@ -29614,23 +29602,23 @@
         <v>100</v>
       </c>
       <c r="B481" s="45" t="s">
-        <v>1988</v>
+        <v>1984</v>
       </c>
       <c r="C481" s="2"/>
       <c r="D481" s="45" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E481" s="45" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F481" s="45" t="s">
+        <v>1988</v>
+      </c>
+      <c r="G481" s="45" t="s">
         <v>1989</v>
       </c>
-      <c r="E481" s="45" t="s">
-        <v>1991</v>
-      </c>
-      <c r="F481" s="45" t="s">
-        <v>1992</v>
-      </c>
-      <c r="G481" s="45" t="s">
-        <v>1993</v>
-      </c>
       <c r="H481" s="45" t="s">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="I481" s="2"/>
       <c r="J481" s="18"/>
@@ -29644,30 +29632,30 @@
         <v>98</v>
       </c>
       <c r="B482" s="44" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="44" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E482" s="44" t="s">
+        <v>1993</v>
+      </c>
+      <c r="F482" s="44" t="s">
+        <v>1994</v>
+      </c>
+      <c r="G482" s="44" t="s">
+        <v>1995</v>
+      </c>
+      <c r="H482" s="44" t="s">
         <v>1996</v>
-      </c>
-      <c r="E482" s="44" t="s">
-        <v>1997</v>
-      </c>
-      <c r="F482" s="44" t="s">
-        <v>1998</v>
-      </c>
-      <c r="G482" s="44" t="s">
-        <v>1999</v>
-      </c>
-      <c r="H482" s="44" t="s">
-        <v>2000</v>
       </c>
       <c r="I482" s="2"/>
       <c r="J482" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K482" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L482" s="18">
         <v>1</v>
@@ -29678,7 +29666,7 @@
         <v>99</v>
       </c>
       <c r="B483" s="45" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="C483" s="2"/>
       <c r="D483" s="2"/>
@@ -29691,7 +29679,7 @@
         <v>11</v>
       </c>
       <c r="K483" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L483" s="18"/>
     </row>
@@ -29700,23 +29688,23 @@
         <v>100</v>
       </c>
       <c r="B484" s="45" t="s">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="C484" s="2"/>
       <c r="D484" s="45" t="s">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="E484" s="45" t="s">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="F484" s="45" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="G484" s="45" t="s">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="H484" s="45" t="s">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="I484" s="2"/>
       <c r="J484" s="18"/>
@@ -29730,30 +29718,30 @@
         <v>98</v>
       </c>
       <c r="B485" s="44" t="s">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="C485" s="2"/>
       <c r="D485" s="44" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E485" s="44" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F485" s="44" t="s">
+        <v>2017</v>
+      </c>
+      <c r="G485" s="44" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H485" s="44" t="s">
         <v>2019</v>
-      </c>
-      <c r="E485" s="44" t="s">
-        <v>2020</v>
-      </c>
-      <c r="F485" s="44" t="s">
-        <v>2021</v>
-      </c>
-      <c r="G485" s="44" t="s">
-        <v>2022</v>
-      </c>
-      <c r="H485" s="44" t="s">
-        <v>2023</v>
       </c>
       <c r="I485" s="2"/>
       <c r="J485" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K485" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L485" s="18">
         <v>1</v>
@@ -29764,20 +29752,20 @@
         <v>98</v>
       </c>
       <c r="B486" s="45" t="s">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="C486" s="2"/>
       <c r="D486" s="45" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E486" s="45" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F486" s="45" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="G486" s="45" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="H486" s="45" t="s">
         <v>1100</v>
@@ -29787,7 +29775,7 @@
         <v>11</v>
       </c>
       <c r="K486" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L486" s="18">
         <v>1</v>
@@ -29798,7 +29786,7 @@
         <v>99</v>
       </c>
       <c r="B487" s="44" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="C487" s="2"/>
       <c r="D487" s="2"/>
@@ -29811,7 +29799,7 @@
         <v>11</v>
       </c>
       <c r="K487" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L487" s="18"/>
     </row>
@@ -29820,23 +29808,23 @@
         <v>100</v>
       </c>
       <c r="B488" s="44" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="C488" s="2"/>
       <c r="D488" s="44" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E488" s="44" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F488" s="44" t="s">
+        <v>2026</v>
+      </c>
+      <c r="G488" s="44" t="s">
+        <v>2027</v>
+      </c>
+      <c r="H488" s="44" t="s">
         <v>2028</v>
-      </c>
-      <c r="E488" s="44" t="s">
-        <v>2029</v>
-      </c>
-      <c r="F488" s="44" t="s">
-        <v>2030</v>
-      </c>
-      <c r="G488" s="44" t="s">
-        <v>2031</v>
-      </c>
-      <c r="H488" s="44" t="s">
-        <v>2032</v>
       </c>
       <c r="I488" s="2"/>
       <c r="J488" s="18"/>
@@ -29850,30 +29838,30 @@
         <v>98</v>
       </c>
       <c r="B489" s="45" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="C489" s="2"/>
       <c r="D489" s="45" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E489" s="45" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F489" s="45" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G489" s="45" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H489" s="45" t="s">
         <v>2033</v>
-      </c>
-      <c r="E489" s="45" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F489" s="45" t="s">
-        <v>2035</v>
-      </c>
-      <c r="G489" s="45" t="s">
-        <v>2036</v>
-      </c>
-      <c r="H489" s="45" t="s">
-        <v>2037</v>
       </c>
       <c r="I489" s="2"/>
       <c r="J489" s="18" t="s">
         <v>11</v>
       </c>
       <c r="K489" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L489" s="18">
         <v>1</v>
@@ -29884,7 +29872,7 @@
         <v>99</v>
       </c>
       <c r="B490" s="44" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="C490" s="2"/>
       <c r="D490" s="2"/>
@@ -29897,7 +29885,7 @@
         <v>11</v>
       </c>
       <c r="K490" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L490" s="18"/>
     </row>
@@ -29906,23 +29894,23 @@
         <v>100</v>
       </c>
       <c r="B491" s="44" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="C491" s="2"/>
       <c r="D491" s="44" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E491" s="44" t="s">
+        <v>2035</v>
+      </c>
+      <c r="F491" s="44" t="s">
+        <v>2036</v>
+      </c>
+      <c r="G491" s="44" t="s">
+        <v>2037</v>
+      </c>
+      <c r="H491" s="44" t="s">
         <v>2038</v>
-      </c>
-      <c r="E491" s="44" t="s">
-        <v>2039</v>
-      </c>
-      <c r="F491" s="44" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G491" s="44" t="s">
-        <v>2041</v>
-      </c>
-      <c r="H491" s="44" t="s">
-        <v>2042</v>
       </c>
       <c r="I491" s="2"/>
       <c r="J491" s="18"/>
@@ -29936,7 +29924,7 @@
         <v>99</v>
       </c>
       <c r="B492" s="45" t="s">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C492" s="2"/>
       <c r="D492" s="2"/>
@@ -29949,7 +29937,7 @@
         <v>11</v>
       </c>
       <c r="K492" s="18" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="L492" s="18"/>
     </row>
@@ -29958,14 +29946,14 @@
         <v>100</v>
       </c>
       <c r="B493" s="45" t="s">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C493" s="2"/>
       <c r="D493" s="45" t="s">
         <v>1336</v>
       </c>
       <c r="E493" s="45" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="F493" s="45" t="s">
         <v>1371</v>
@@ -29974,7 +29962,7 @@
         <v>1338</v>
       </c>
       <c r="H493" s="45" t="s">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="I493" s="2"/>
       <c r="J493" s="18"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB83A66-957C-4385-9938-86AA91C3A6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F43F9F-93B9-44C4-A63D-FBAAE8A17C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13358,11 +13358,25 @@
 &lt;br&gt;&lt;img src="/images/M21F10&amp;11.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
   <si>
+    <t>On titre le volume $V_A = 25,0 \text{ mL}$ de la solution $(S)$ par une solution aqueuse d'hydroxyde de sodium $(\text{Na}^+_{\text{(aq)}} + \text{HO}^-_{\text{(aq)}})$ de concentration molaire $C_B = 5,0 \cdot 10^{-2} \text{ mol}\cdot\text{L}^{-1}$. Le volume versé à l'équivalence est $V_{BE} = 27,8 \text{ mL}$.
+&lt;br&gt;La constante d'équilibre associée à l'équation de la réaction du dosage est $K = 3,2 \cdot 10^{7}$. 
+&lt;br&gt;La valeur de la masse d'aspirine contenue dans le comprimé étudié est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;acide acétylsalicylique (7points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; L'acide acétylsalicylique de formule $C_{9}H_{8}O_{4}$, connu sous le nom d'aspirine est utilisé dans de nombreux médicaments pour ses propriétés antalgiques et anti-inflammatoires.
+&lt;br&lt;On dissout un comprimé d'aspirine dans le volume $V=100mL$ d'eau pure pour obtenir une solution aqueuse (S). La conductivité de la solution (S) vaut $\sigma=109 mS.m^{-1}$.
+La transformation chimique qui se produit est modélisée par l'équation: 
+&lt;br&gt;$C_{8}H_{7}O_{2}COOH_{(aq)}+H_{2}O_{(l)}\rightleftharpoons C_{8}H_{7}O_{2}COO_{(aq)}^{-}+H_{3}O_{(aq)}^{+}$
+&lt;br&gt;Données: $\lambda_{(C_8H_7O_2COO^-)}=3,6.10^{-3} S.m^2.mol^{-1}$, $\quad$ $\lambda_{(H_3O^+)}=35,0.10^{-3} S.m^2.mol^{-1}$. 
+&lt;br&gt;On néglige l'effet des ions $HO_{(aq)}^{-}$ sur la conductivité de la solution (S). $M(C_{9}H_{8}O_{4})=180 g.mol^{-1}$, $K_e=10^{-14}$. $\log(2,82)=0,45$ ; $2,82\times38,6\approx109$ ; $9\times27,8\approx250$.</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt;Etude cinétique d'une transformation chimique: (8 points) &lt;/b&gt;&lt;/center&gt;
 &lt;br&gt;Un mélange de volume V=100mL contient initialement $n_{1}(H_{2}O_{2})=3.10^{-3}$ mol d'eau oxygénée, $n_{2}(I^{-})=5.10^{-3}mol$ d'ions iodure et $n_{3}(H^{+})=4.10^{-3}$ mol d'ions hydrogène. La réaction chimique qui se produit est modélisée par l'équation: 
 &lt;br&gt;$H_{2}O_{2(aq)}+2I_{(aq)}^{-}+2H_{(aq)}^{+}\longrightarrow I_{2(aq)}+2H_{2}O_{(l)}$
 &lt;br&gt;Le suivi temporel de la formation de diiode $I_{2(aq)}$ a permis de tracer la courbe $[I_{2(aq)}]=f(t)$ ci-contre.
-&lt;br&gt;&lt;img src="/images/CH21F1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+&lt;br&gt;&lt;img src="/images/CH2021F1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Suivi temporel d'une transformation chimique (6 poins) &lt;/b&gt;&lt;/center&gt;
@@ -13370,22 +13384,8 @@
 La transformation chimique qui se produit est modélisée par l'équation:
 &lt;br&gt; $CaCO_{3(s)}+2C_{3}H_{6}O_{3(aq)}\longrightarrow CO_{2(g)}+Ca_{(aq)}^{2+}+2C_{3}H_{5}O_{3(aq)}^{-}+H_{2}O_{(l)}$
 &lt;br&gt;La courbe ci-contre représente l'évolution de l'avancement de la réaction en fonction du temps $x=f(t)$.
-&lt;br&gt;&lt;img src="/images/CH21F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;&lt;img src="/images/CH2021F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;Données: temps de demi-réaction $t_{1/2}=18s$; $\quad$ $V_m=24L.mol^{-1}$; $\quad$ $M(CaCO_3)=100g.mol^{-1}$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;acide acétylsalicylique (7points)&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt; L'acide acétylsalicylique de formule $C_{9}H_{8}O_{4}$, connu sous le nom d'aspirine est utilisé dans de nombreux médicaments pour ses propriétés antalgiques et anti-inflammatoires.
-On dissout un comprimé d'aspirine dans le volume $V=100mL$ d'eau pure pour obtenir une solution aqueuse (S). La conductivité de la solution (S) vaut $\sigma=109 mS.m^{-1}$.
-La transformation chimique qui se produit est modélisée par l'équation: 
-&lt;br&gt;$C_{8}H_{7}O_{2}COOH_{(aq)}+H_{2}O_{(l)}\rightleftharpoons C_{8}H_{7}O_{2}COO_{(aq)}^{-}+H_{3}O_{(aq)}^{+}$
-&lt;br&gt;Données: $\lambda_{(C_8H_7O_2COO^-)}=3,6.10^{-3} S.m^2.mol^{-1}$, $\quad$ $\lambda_{(H_3O^+)}=35,0.10^{-3} S.m^2.mol^{-1}$. 
-&lt;br&gt;On néglige l'effet des ions $HO_{(aq)}^{-}$ sur la conductivité de la solution (S). $M(C_{9}H_{8}O_{4})=180 g.mol^{-1}$, $K_e=10^{-14}$. $\log(2,82)=0,45$ ; $2,82\times38,6\approx109$ ; $9\times27,8\approx250$.</t>
-  </si>
-  <si>
-    <t>On titre le volume $V_A = 25,0 \text{ mL}$ de la solution $(S)$ par une solution aqueuse d'hydroxyde de sodium $(\text{Na}^+_{\text{(aq)}} + \text{HO}^-_{\text{(aq)}})$ de concentration molaire $C_B = 5,0 \cdot 10^{-2} \text{ mol}\cdot\text{L}^{-1}$. Le volume versé à l'équivalence est $V_{BE} = 27,8 \text{ mL}$.
-&lt;br&gt;La constante d'équilibre associée à l'équation de la réaction du dosage est $K = 3,2 \cdot 10^{7}$. 
-&lt;br&gt;La valeur de la masse d'aspirine contenue dans le comprimé étudié est :</t>
   </si>
 </sst>
 </file>
@@ -19006,7 +19006,7 @@
         <v>99</v>
       </c>
       <c r="B144" s="46" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="C144" s="46"/>
       <c r="D144" s="46"/>
@@ -19118,7 +19118,7 @@
         <v>99</v>
       </c>
       <c r="B148" s="46" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="C148" s="46"/>
       <c r="D148" s="46"/>
@@ -19230,7 +19230,7 @@
         <v>99</v>
       </c>
       <c r="B152" s="46" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="C152" s="46"/>
       <c r="D152" s="46"/>
@@ -19312,7 +19312,7 @@
         <v>100</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>2437</v>
+        <v>2434</v>
       </c>
       <c r="C155" s="46"/>
       <c r="D155" s="46" t="s">

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FDC900-F1E3-4D82-8900-E57A58514EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4FE5EA-5330-4252-8FCB-DCEEF24990F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7544,15 +7544,6 @@
     <t>La mucoviscidose est une maladie génétique qui :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;MECANIQUE&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt;&lt;img src="/images/P2025F1.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
-&lt;br&gt;On considère un pendule élastique horizontal constitué d'un ressort de masse négligeable, de raideur K et de spires non jointives. À son extrémité libre est attaché un solide (S) de masse m=200 g. L'autre extrémité du ressort est liée à un support fixe (voir figure 1). 
-&lt;br&gt;&lt;img src="/images/P2025F2.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
-On néglige les frottements et on considère que le centre d'inertie G du solide coïncide à l'équilibre avec l'origine de l'axe (Ox). On écarte le solide (S) de sa position d'équilibre vers le sens négatif et on le lâche sans vitesse initiale à l'instant t=0. 
-La figure 2 représente les variations de l'abscisse x en fonction du temps. 
-&lt;br&gt;On donne : $π^{2}=10$.</t>
-  </si>
-  <si>
     <t>$\ddot{x} + \frac{K}{m}x = 0$</t>
   </si>
   <si>
@@ -7723,6 +7714,15 @@
   </si>
   <si>
     <t>$5⋅10^{14}$ GHz</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;MECANIQUE&lt;/b&gt;&lt;/center&gt;
+&lt;img src="/images/P2025F1.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
+On considère un pendule élastique horizontal constitué d'un ressort de masse négligeable, de raideur K et de spires non jointives. À son extrémité libre est attaché un solide (S) de masse m=200 g. L'autre extrémité du ressort est liée à un support fixe (voir figure 1). 
+&lt;img src="/images/P2025F2.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
+On néglige les frottements et on considère que le centre d'inertie G du solide coïncide à l'équilibre avec l'origine de l'axe (Ox). On écarte le solide (S) de sa position d'équilibre vers le sens négatif et on le lâche sans vitesse initiale à l'instant t=0. 
+La figure 2 représente les variations de l'abscisse x en fonction du temps. 
+On donne : $π^{2}=10$.</t>
   </si>
 </sst>
 </file>
@@ -22369,7 +22369,7 @@
         <v>33</v>
       </c>
       <c r="B437" s="40" t="s">
-        <v>2388</v>
+        <v>2440</v>
       </c>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
@@ -22391,20 +22391,20 @@
         <v>34</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="C438" s="40"/>
       <c r="D438" s="54" t="s">
+        <v>2388</v>
+      </c>
+      <c r="E438" s="54" t="s">
         <v>2389</v>
       </c>
-      <c r="E438" s="54" t="s">
+      <c r="F438" s="54" t="s">
         <v>2390</v>
       </c>
-      <c r="F438" s="54" t="s">
+      <c r="G438" s="54" t="s">
         <v>2391</v>
-      </c>
-      <c r="G438" s="54" t="s">
-        <v>2392</v>
       </c>
       <c r="H438" s="54" t="s">
         <v>1920</v>
@@ -22421,20 +22421,20 @@
         <v>34</v>
       </c>
       <c r="B439" s="55" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="C439" s="40"/>
       <c r="D439" s="55" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E439" s="55" t="s">
         <v>2393</v>
       </c>
-      <c r="E439" s="55" t="s">
+      <c r="F439" s="55" t="s">
         <v>2394</v>
       </c>
-      <c r="F439" s="55" t="s">
+      <c r="G439" s="55" t="s">
         <v>2395</v>
-      </c>
-      <c r="G439" s="55" t="s">
-        <v>2396</v>
       </c>
       <c r="H439" s="55" t="s">
         <v>1920</v>
@@ -22451,20 +22451,20 @@
         <v>34</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="C440" s="40"/>
       <c r="D440" s="54" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E440" s="54" t="s">
         <v>2397</v>
       </c>
-      <c r="E440" s="54" t="s">
+      <c r="F440" s="54" t="s">
         <v>2398</v>
       </c>
-      <c r="F440" s="54" t="s">
+      <c r="G440" s="54" t="s">
         <v>2399</v>
-      </c>
-      <c r="G440" s="54" t="s">
-        <v>2400</v>
       </c>
       <c r="H440" s="54" t="s">
         <v>1920</v>
@@ -22485,16 +22485,16 @@
       </c>
       <c r="C441" s="40"/>
       <c r="D441" s="55" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E441" s="55" t="s">
         <v>2401</v>
       </c>
-      <c r="E441" s="55" t="s">
+      <c r="F441" s="55" t="s">
         <v>2402</v>
       </c>
-      <c r="F441" s="55" t="s">
+      <c r="G441" s="55" t="s">
         <v>2403</v>
-      </c>
-      <c r="G441" s="55" t="s">
-        <v>2404</v>
       </c>
       <c r="H441" s="55" t="s">
         <v>1920</v>
@@ -22511,7 +22511,7 @@
         <v>33</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="C442" s="40"/>
       <c r="D442" s="40"/>
@@ -22533,20 +22533,20 @@
         <v>34</v>
       </c>
       <c r="B443" s="55" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="C443" s="40"/>
       <c r="D443" s="55" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E443" s="55" t="s">
         <v>2413</v>
       </c>
-      <c r="E443" s="55" t="s">
+      <c r="F443" s="55" t="s">
         <v>2414</v>
       </c>
-      <c r="F443" s="55" t="s">
+      <c r="G443" s="55" t="s">
         <v>2415</v>
-      </c>
-      <c r="G443" s="55" t="s">
-        <v>2416</v>
       </c>
       <c r="H443" s="55" t="s">
         <v>1920</v>
@@ -22563,20 +22563,20 @@
         <v>34</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="C444" s="40"/>
       <c r="D444" s="54" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E444" s="54" t="s">
         <v>2417</v>
       </c>
-      <c r="E444" s="54" t="s">
+      <c r="F444" s="54" t="s">
         <v>2418</v>
       </c>
-      <c r="F444" s="54" t="s">
+      <c r="G444" s="54" t="s">
         <v>2419</v>
-      </c>
-      <c r="G444" s="54" t="s">
-        <v>2420</v>
       </c>
       <c r="H444" s="54" t="s">
         <v>1920</v>
@@ -22593,20 +22593,20 @@
         <v>34</v>
       </c>
       <c r="B445" s="55" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="C445" s="40"/>
       <c r="D445" s="55" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E445" s="55" t="s">
         <v>2421</v>
       </c>
-      <c r="E445" s="55" t="s">
+      <c r="F445" s="55" t="s">
         <v>2422</v>
       </c>
-      <c r="F445" s="55" t="s">
+      <c r="G445" s="55" t="s">
         <v>2423</v>
-      </c>
-      <c r="G445" s="55" t="s">
-        <v>2424</v>
       </c>
       <c r="H445" s="55" t="s">
         <v>1920</v>
@@ -22623,20 +22623,20 @@
         <v>34</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="C446" s="40"/>
       <c r="D446" s="54" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E446" s="54" t="s">
         <v>2425</v>
       </c>
-      <c r="E446" s="54" t="s">
+      <c r="F446" s="54" t="s">
         <v>2426</v>
       </c>
-      <c r="F446" s="54" t="s">
+      <c r="G446" s="54" t="s">
         <v>2427</v>
-      </c>
-      <c r="G446" s="54" t="s">
-        <v>2428</v>
       </c>
       <c r="H446" s="54" t="s">
         <v>1920</v>
@@ -22653,7 +22653,7 @@
         <v>33</v>
       </c>
       <c r="B447" s="40" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="C447" s="40"/>
       <c r="D447" s="40"/>
@@ -22705,7 +22705,7 @@
         <v>34</v>
       </c>
       <c r="B449" s="40" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="C449" s="40"/>
       <c r="D449" s="42" t="s">
@@ -22739,16 +22739,16 @@
       </c>
       <c r="C450" s="40"/>
       <c r="D450" s="40" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E450" s="40" t="s">
         <v>2431</v>
       </c>
-      <c r="E450" s="40" t="s">
+      <c r="F450" s="40" t="s">
         <v>2432</v>
       </c>
-      <c r="F450" s="40" t="s">
+      <c r="G450" s="40" t="s">
         <v>2433</v>
-      </c>
-      <c r="G450" s="40" t="s">
-        <v>2434</v>
       </c>
       <c r="H450" s="41" t="s">
         <v>1925</v>
@@ -22765,7 +22765,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="40" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="C451" s="40"/>
       <c r="D451" s="42">
@@ -22795,7 +22795,7 @@
         <v>33</v>
       </c>
       <c r="B452" s="40" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="C452" s="40"/>
       <c r="D452" s="40"/>
@@ -22821,16 +22821,16 @@
       </c>
       <c r="C453" s="40"/>
       <c r="D453" s="40" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E453" s="40" t="s">
         <v>2437</v>
       </c>
-      <c r="E453" s="40" t="s">
+      <c r="F453" s="40" t="s">
         <v>2438</v>
       </c>
-      <c r="F453" s="40" t="s">
+      <c r="G453" s="40" t="s">
         <v>2439</v>
-      </c>
-      <c r="G453" s="40" t="s">
-        <v>2440</v>
       </c>
       <c r="H453" s="41" t="s">
         <v>1925</v>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4FE5EA-5330-4252-8FCB-DCEEF24990F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8880E8AD-3FE6-4777-9872-2B2F4A9AFC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="2441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="2440">
   <si>
     <t>Option 1</t>
   </si>
@@ -6110,15 +6110,7 @@
     <t>Le temps nécessaire pour que cette activité initiale soit réduite au tiers est :</t>
   </si>
   <si>
-    <t>Le calcul donne un nombre d'atomes d'iode 123 injectés N=250⋅109. La ration iodée quotidienne normale en iode 127 étant R=125 μg/j.
-Le nombre d'atomes d'iode 123 injectés représente une fraction q de R égale à :</t>
-  </si>
-  <si>
     <t>La fréquence f de cette radiation dans le vide est :</t>
-  </si>
-  <si>
-    <t>La radiation émise par la source traverse un milieu transparent d'indice n. Un opérateur affirme que la longueur d'onde est maintenant de 400 nm. 
-L'indice n du milieu est égal à :</t>
   </si>
   <si>
     <t>La vitesse d'une transformation chimique est définie comme :</t>
@@ -7550,9 +7542,6 @@
     <t>$\ddot{x} + \frac{m}{K}x = 0$</t>
   </si>
   <si>
-    <t>$x - \frac{K}{m}x = 0$</t>
-  </si>
-  <si>
     <t>$\ddot{x} - \frac{K}{m}x = 0$</t>
   </si>
   <si>
@@ -7612,18 +7601,6 @@
 À l'instant t=0, on ferme l'interrupteur K d'un circuit électrique. On obtient un graphique représentant la variation de dtduR​​ en fonction du temps ou de la tension aux bornes du conducteur ohmique.</t>
   </si>
   <si>
-    <t>Q19. L'équation différentielle que vérifie $U_R$ est :</t>
-  </si>
-  <si>
-    <t>Q20. Les valeurs de l'inductance $L$ et de la force électromotrice $E$ sont :</t>
-  </si>
-  <si>
-    <t>Q21. La valeur de l'intensité du courant ($I_0$) en régime permanent est :</t>
-  </si>
-  <si>
-    <t>Q22. La valeur de l'énergie magnétique ($E_m$) emmagasinée dans la bobine en régime permanent est :</t>
-  </si>
-  <si>
     <t>$\frac{dU_R}{dt} = \frac{R.E}{L} + \frac{L}{R}U_R$</t>
   </si>
   <si>
@@ -7685,18 +7662,10 @@
     <t>$4,2⋅10^{8}$</t>
   </si>
   <si>
-    <t>$4,2⋅10^{9})</t>
-  </si>
-  <si>
     <t>$4,2⋅10^{−9}$</t>
   </si>
   <si>
     <t>$4,2⋅10^{−8}$</t>
-  </si>
-  <si>
-    <t>Dans les explorations de la thyroïde, on dispose d'une source radioactive constituée d'un mélange de 2 radioéléments : iode radioactif 124 et iode radioactif 125, d'activités initiales A et B égales et de demi-vie physiques respectives T1​=4 jours et T2​=60 jours. 
-On donne : $log_{10}​(2)=0,3$ $\quad$ et $\quad$ $\frac{6}{14}$=0,43. 
-Le temps, en jours, au bout duquel l'activité de l'un des radioéléments sera inférieure à 0,1% de celle de l'autre est :</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;ONDES ÉLECTROMAGNÉTIQUES&lt;/b&gt;&lt;/center&gt;
@@ -7716,13 +7685,56 @@
     <t>$5⋅10^{14}$ GHz</t>
   </si>
   <si>
+    <t>Dans les explorations de la thyroïde, on dispose d'une source radioactive constituée d'un mélange de 2 radioéléments : iode radioactif 124 et iode radioactif 125, d'activités initiales A et B égales et de demi-vie physiques respectives T1​=4 jours et T2​=60 jours. 
+&lt;br&gt;On donne : $log_{10}​(2)=0,3$ $\quad$ et $\quad$ $\frac{6}{14}$=0,43. 
+&lt;br&gt;Le temps, en jours, au bout duquel l'activité de l'un des radioéléments sera inférieure à 0,1% de celle de l'autre est :</t>
+  </si>
+  <si>
+    <t>La radiation émise par la source traverse un milieu transparent d'indice n. Un opérateur affirme que la longueur d'onde est maintenant de 400nm. 
+L'indice n du milieu est égal à :</t>
+  </si>
+  <si>
+    <t>Le calcul donne un nombre d'atomes d'iode 123 injectés N=250⋅109. La ration iodée quotidienne normale en iode 127 étant R=125 μg/j.
+&lt;br&gt;Le nombre d'atomes d'iode 123 injectés représente une fraction q de R égale à :</t>
+  </si>
+  <si>
+    <t>$4,2⋅10^{9}$</t>
+  </si>
+  <si>
+    <t>L'équation différentielle que vérifie $U_R$ est :</t>
+  </si>
+  <si>
+    <t>Les valeurs de l'inductance $L$ et de la force électromotrice $E$ sont :</t>
+  </si>
+  <si>
+    <t>La valeur de l'intensité du courant ($I_0$) en régime permanent est :</t>
+  </si>
+  <si>
+    <t>La valeur de l'énergie magnétique ($E_m$) emmagasinée dans la bobine en régime permanent est :</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt;MECANIQUE&lt;/b&gt;&lt;/center&gt;
-&lt;img src="/images/P2025F1.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
-On considère un pendule élastique horizontal constitué d'un ressort de masse négligeable, de raideur K et de spires non jointives. À son extrémité libre est attaché un solide (S) de masse m=200 g. L'autre extrémité du ressort est liée à un support fixe (voir figure 1). 
-&lt;img src="/images/P2025F2.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
-On néglige les frottements et on considère que le centre d'inertie G du solide coïncide à l'équilibre avec l'origine de l'axe (Ox). On écarte le solide (S) de sa position d'équilibre vers le sens négatif et on le lâche sans vitesse initiale à l'instant t=0. 
-La figure 2 représente les variations de l'abscisse x en fonction du temps. 
-On donne : $π^{2}=10$.</t>
+&lt;br&gt;
+&lt;div style="display: flex; justify-content: space-between; align-items: center; width: 100%;"&gt;
+  &lt;div style="flex: 1; padding-right: 15px;"&gt;
+    On considère un pendule élastique horizontal constitué d'un ressort de masse négligeable, de raideur K et de spires non jointives. À son extrémité libre est attaché un solide (S) de masse m=200 g. L'autre extrémité du ressort est liée à un support fixe (voir figure 1). 
+  &lt;/div&gt;
+  &lt;div style="flex-shrink: 0;"&gt;
+    &lt;img src="/images/P2025F1.png" alt="Figure 1" style="height: 80px;" /&gt;
+  &lt;/div&gt;
+&lt;/div&gt;
+&lt;br&gt;
+&lt;div style="display: flex; justify-content: space-between; align-items: center; width: 100%;"&gt;
+  &lt;div style="flex: 1; padding-right: 15px;"&gt;
+    On néglige les frottements et on considère que le centre d'inertie G du solide coïncide à l'équilibre avec l'origine de l'axe (Ox). On écarte le solide (S) de sa position d'équilibre vers le sens négatif et on le lâche sans vitesse initiale à l'instant t=0. 
+    La figure 2 représente les variations de l'abscisse x en fonction du temps. 
+  &lt;/div&gt;
+  &lt;div style="flex-shrink: 0;"&gt;
+    &lt;img src="/images/P2025F2.png" alt="Figure 2" style="height: 80px;" /&gt;
+  &lt;/div&gt;
+&lt;/div&gt;
+&lt;br&gt;
+On donne : $\pi^{2}=10$.</t>
   </si>
 </sst>
 </file>
@@ -8821,7 +8833,7 @@
         <v>32</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="32" t="s">
@@ -8857,7 +8869,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="32" t="s">
@@ -8893,7 +8905,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="32" t="s">
@@ -8965,7 +8977,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="32" t="s">
@@ -9037,7 +9049,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="32" t="s">
@@ -9073,7 +9085,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="32" t="s">
@@ -9109,7 +9121,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="32" t="s">
@@ -9145,7 +9157,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="32" t="s">
@@ -9181,7 +9193,7 @@
         <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="2"/>
@@ -9203,11 +9215,11 @@
         <v>34</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="3" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>666</v>
@@ -9299,7 +9311,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -9321,7 +9333,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="3" t="s">
@@ -9385,7 +9397,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -9455,7 +9467,7 @@
         <v>698</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>695</v>
@@ -9471,7 +9483,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
@@ -9503,7 +9515,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -9525,7 +9537,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -9557,7 +9569,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
@@ -9589,7 +9601,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -9611,7 +9623,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
@@ -9643,7 +9655,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
@@ -9675,7 +9687,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -9697,7 +9709,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="3" t="s">
@@ -9727,7 +9739,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="3" t="s">
@@ -9757,26 +9769,26 @@
         <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>2125</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>2126</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>2127</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>2128</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>2129</v>
-      </c>
       <c r="I42" s="3" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>9</v>
@@ -9793,7 +9805,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -9815,7 +9827,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
@@ -9847,7 +9859,7 @@
         <v>34</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
@@ -9911,7 +9923,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -9997,7 +10009,7 @@
         <v>33</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -10115,7 +10127,7 @@
         <v>33</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -10141,22 +10153,22 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="32" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E55" s="32" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F55" s="32" t="s">
         <v>2140</v>
       </c>
-      <c r="E55" s="32" t="s">
+      <c r="G55" s="32" t="s">
         <v>2141</v>
       </c>
-      <c r="F55" s="32" t="s">
+      <c r="H55" s="32" t="s">
         <v>2142</v>
       </c>
-      <c r="G55" s="32" t="s">
-        <v>2143</v>
-      </c>
-      <c r="H55" s="32" t="s">
-        <v>2144</v>
-      </c>
       <c r="I55" s="32" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
@@ -10265,7 +10277,7 @@
         <v>33</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -10383,7 +10395,7 @@
         <v>32</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="32" t="s">
@@ -10419,7 +10431,7 @@
         <v>33</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -10505,7 +10517,7 @@
         <v>33</v>
       </c>
       <c r="B67" s="32" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -10623,7 +10635,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -10709,7 +10721,7 @@
         <v>33</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -10867,7 +10879,7 @@
         <v>32</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="3" t="s">
@@ -11011,7 +11023,7 @@
         <v>32</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="3" t="s">
@@ -11083,7 +11095,7 @@
         <v>32</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="3" t="s">
@@ -11155,7 +11167,7 @@
         <v>32</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="3" t="s">
@@ -11227,7 +11239,7 @@
         <v>32</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="3" t="s">
@@ -11299,7 +11311,7 @@
         <v>32</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="3" t="s">
@@ -11335,7 +11347,7 @@
         <v>32</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="3" t="s">
@@ -11371,7 +11383,7 @@
         <v>32</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="3" t="s">
@@ -11875,7 +11887,7 @@
         <v>32</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="33" t="s">
@@ -11947,7 +11959,7 @@
         <v>32</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="33" t="s">
@@ -11983,7 +11995,7 @@
         <v>32</v>
       </c>
       <c r="B110" s="26" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="34" t="s">
@@ -12019,7 +12031,7 @@
         <v>32</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="33" t="s">
@@ -12055,7 +12067,7 @@
         <v>32</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="34" t="s">
@@ -12091,7 +12103,7 @@
         <v>32</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="33" t="s">
@@ -12127,7 +12139,7 @@
         <v>32</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="34" t="s">
@@ -12163,7 +12175,7 @@
         <v>32</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="33" t="s">
@@ -12199,7 +12211,7 @@
         <v>32</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="34" t="s">
@@ -12235,7 +12247,7 @@
         <v>33</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -12261,22 +12273,22 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F118" s="3" t="s">
         <v>2163</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="G118" s="3" t="s">
         <v>2164</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="H118" s="3" t="s">
         <v>2165</v>
       </c>
-      <c r="G118" s="3" t="s">
-        <v>2166</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>2167</v>
-      </c>
       <c r="I118" s="3" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
@@ -12353,7 +12365,7 @@
         <v>33</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -12439,7 +12451,7 @@
         <v>33</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -12525,7 +12537,7 @@
         <v>33</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -12729,7 +12741,7 @@
         <v>34</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
@@ -12761,7 +12773,7 @@
         <v>33</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -12787,7 +12799,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="3" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>819</v>
@@ -12815,26 +12827,26 @@
         <v>34</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F137" s="3" t="s">
         <v>2173</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="G137" s="3" t="s">
         <v>2174</v>
       </c>
-      <c r="F137" s="3" t="s">
+      <c r="H137" s="3" t="s">
         <v>2175</v>
       </c>
-      <c r="G137" s="3" t="s">
-        <v>2176</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>2177</v>
-      </c>
       <c r="I137" s="3" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
@@ -12911,7 +12923,7 @@
         <v>33</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>837</v>
@@ -12939,22 +12951,22 @@
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F141" s="3" t="s">
         <v>2178</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="G141" s="3" t="s">
         <v>2179</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="H141" s="3" t="s">
         <v>2180</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>2181</v>
-      </c>
-      <c r="H141" s="3" t="s">
-        <v>2182</v>
-      </c>
       <c r="I141" s="3" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
@@ -12974,7 +12986,7 @@
         <v>833</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>834</v>
@@ -13003,22 +13015,22 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F143" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="G143" s="3" t="s">
         <v>2185</v>
       </c>
-      <c r="F143" s="3" t="s">
+      <c r="H143" s="3" t="s">
         <v>2186</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>2187</v>
-      </c>
-      <c r="H143" s="3" t="s">
-        <v>2188</v>
-      </c>
       <c r="I143" s="3" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
@@ -13031,7 +13043,7 @@
         <v>33</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
@@ -13149,7 +13161,7 @@
         <v>33</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C148" s="32"/>
       <c r="D148" s="32"/>
@@ -13267,7 +13279,7 @@
         <v>33</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
@@ -13353,7 +13365,7 @@
         <v>34</v>
       </c>
       <c r="B155" s="32" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="C155" s="32"/>
       <c r="D155" s="32" t="s">
@@ -13417,7 +13429,7 @@
         <v>33</v>
       </c>
       <c r="B157" s="32" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C157" s="32"/>
       <c r="D157" s="2"/>
@@ -13503,7 +13515,7 @@
         <v>33</v>
       </c>
       <c r="B160" s="32" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="C160" s="32"/>
       <c r="D160" s="32"/>
@@ -13621,7 +13633,7 @@
         <v>33</v>
       </c>
       <c r="B164" s="32" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
@@ -13963,7 +13975,7 @@
         <v>439</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>400</v>
@@ -13999,10 +14011,10 @@
         <v>405</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="J175" s="13" t="s">
         <v>10</v>
@@ -14032,13 +14044,13 @@
         <v>408</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="J176" s="13" t="s">
         <v>10</v>
@@ -14104,13 +14116,13 @@
         <v>416</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="J178" s="13" t="s">
         <v>10</v>
@@ -14131,22 +14143,22 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="3" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="H179" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I179" s="3" t="s">
         <v>2211</v>
-      </c>
-      <c r="I179" s="3" t="s">
-        <v>2213</v>
       </c>
       <c r="J179" s="13" t="s">
         <v>10</v>
@@ -14167,22 +14179,22 @@
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G180" s="3" t="s">
         <v>2207</v>
       </c>
-      <c r="E180" s="3" t="s">
-        <v>2206</v>
-      </c>
-      <c r="F180" s="3" t="s">
+      <c r="H180" s="3" t="s">
         <v>2208</v>
       </c>
-      <c r="G180" s="3" t="s">
-        <v>2209</v>
-      </c>
-      <c r="H180" s="3" t="s">
-        <v>2210</v>
-      </c>
       <c r="I180" s="3" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="J180" s="13" t="s">
         <v>10</v>
@@ -14248,7 +14260,7 @@
         <v>425</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>426</v>
@@ -14323,7 +14335,7 @@
         <v>434</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>409</v>
@@ -14359,7 +14371,7 @@
         <v>435</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>410</v>
@@ -14379,7 +14391,7 @@
         <v>32</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="3" t="s">
@@ -14392,10 +14404,10 @@
         <v>438</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>437</v>
@@ -14451,7 +14463,7 @@
         <v>32</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="3" t="s">
@@ -14494,16 +14506,16 @@
         <v>444</v>
       </c>
       <c r="E189" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="G189" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="F189" s="3" t="s">
+      <c r="H189" s="3" t="s">
         <v>2222</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>2223</v>
-      </c>
-      <c r="H189" s="3" t="s">
-        <v>2224</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>444</v>
@@ -14557,7 +14569,7 @@
         <v>32</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="31" t="s">
@@ -14795,7 +14807,7 @@
         <v>32</v>
       </c>
       <c r="B198" s="30" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="30" t="s">
@@ -14915,7 +14927,7 @@
         <v>33</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -14971,19 +14983,19 @@
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="47" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E204" s="47" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F204" s="47" t="s">
         <v>2229</v>
       </c>
-      <c r="E204" s="47" t="s">
+      <c r="G204" s="47" t="s">
         <v>2230</v>
       </c>
-      <c r="F204" s="47" t="s">
+      <c r="H204" s="47" t="s">
         <v>2231</v>
-      </c>
-      <c r="G204" s="47" t="s">
-        <v>2232</v>
-      </c>
-      <c r="H204" s="47" t="s">
-        <v>2233</v>
       </c>
       <c r="I204" s="2"/>
       <c r="J204" s="6" t="s">
@@ -15001,7 +15013,7 @@
         <v>33</v>
       </c>
       <c r="B205" s="31" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -15057,19 +15069,19 @@
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="30" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E207" s="30" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F207" s="30" t="s">
         <v>2236</v>
       </c>
-      <c r="E207" s="30" t="s">
+      <c r="G207" s="30" t="s">
         <v>2237</v>
       </c>
-      <c r="F207" s="30" t="s">
+      <c r="H207" s="30" t="s">
         <v>2238</v>
-      </c>
-      <c r="G207" s="30" t="s">
-        <v>2239</v>
-      </c>
-      <c r="H207" s="30" t="s">
-        <v>2240</v>
       </c>
       <c r="I207" s="2"/>
       <c r="J207" s="6" t="s">
@@ -15121,7 +15133,7 @@
         <v>33</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -15147,19 +15159,19 @@
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="30" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E210" s="30" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F210" s="30" t="s">
         <v>2242</v>
       </c>
-      <c r="E210" s="30" t="s">
+      <c r="G210" s="30" t="s">
         <v>2243</v>
       </c>
-      <c r="F210" s="30" t="s">
+      <c r="H210" s="30" t="s">
         <v>2244</v>
-      </c>
-      <c r="G210" s="30" t="s">
-        <v>2245</v>
-      </c>
-      <c r="H210" s="30" t="s">
-        <v>2246</v>
       </c>
       <c r="I210" s="2"/>
       <c r="J210" s="6"/>
@@ -15593,7 +15605,7 @@
         <v>33</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="C226" s="44"/>
       <c r="D226" s="2"/>
@@ -15615,23 +15627,23 @@
         <v>34</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="C227" s="44"/>
       <c r="D227" s="16" t="s">
+        <v>2010</v>
+      </c>
+      <c r="E227" s="16" t="s">
+        <v>2011</v>
+      </c>
+      <c r="F227" s="16" t="s">
         <v>2012</v>
       </c>
-      <c r="E227" s="16" t="s">
+      <c r="G227" s="16" t="s">
         <v>2013</v>
       </c>
-      <c r="F227" s="16" t="s">
+      <c r="H227" s="16" t="s">
         <v>2014</v>
-      </c>
-      <c r="G227" s="16" t="s">
-        <v>2015</v>
-      </c>
-      <c r="H227" s="16" t="s">
-        <v>2016</v>
       </c>
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
@@ -15645,23 +15657,23 @@
         <v>34</v>
       </c>
       <c r="B228" s="45" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="C228" s="46"/>
       <c r="D228" s="17" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E228" s="17" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F228" s="17" t="s">
         <v>2017</v>
       </c>
-      <c r="E228" s="17" t="s">
+      <c r="G228" s="17" t="s">
         <v>2018</v>
       </c>
-      <c r="F228" s="17" t="s">
+      <c r="H228" s="17" t="s">
         <v>2019</v>
-      </c>
-      <c r="G228" s="17" t="s">
-        <v>2020</v>
-      </c>
-      <c r="H228" s="17" t="s">
-        <v>2021</v>
       </c>
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
@@ -15675,23 +15687,23 @@
         <v>34</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="C229" s="44"/>
       <c r="D229" s="16" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E229" s="16" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F229" s="16" t="s">
         <v>2022</v>
       </c>
-      <c r="E229" s="16" t="s">
+      <c r="G229" s="16" t="s">
         <v>2023</v>
       </c>
-      <c r="F229" s="16" t="s">
+      <c r="H229" s="16" t="s">
         <v>2024</v>
-      </c>
-      <c r="G229" s="16" t="s">
-        <v>2025</v>
-      </c>
-      <c r="H229" s="16" t="s">
-        <v>2026</v>
       </c>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
@@ -15705,23 +15717,23 @@
         <v>34</v>
       </c>
       <c r="B230" s="45" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="C230" s="46"/>
       <c r="D230" s="17" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E230" s="17" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F230" s="17" t="s">
         <v>2027</v>
       </c>
-      <c r="E230" s="17" t="s">
+      <c r="G230" s="17" t="s">
         <v>2028</v>
       </c>
-      <c r="F230" s="17" t="s">
+      <c r="H230" s="17" t="s">
         <v>2029</v>
-      </c>
-      <c r="G230" s="17" t="s">
-        <v>2030</v>
-      </c>
-      <c r="H230" s="17" t="s">
-        <v>2031</v>
       </c>
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
@@ -15735,10 +15747,10 @@
         <v>33</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="C231" s="44" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -15759,23 +15771,23 @@
         <v>34</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="C232" s="44"/>
       <c r="D232" s="16" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E232" s="16" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F232" s="16" t="s">
         <v>2033</v>
       </c>
-      <c r="E232" s="16" t="s">
+      <c r="G232" s="16" t="s">
         <v>2034</v>
       </c>
-      <c r="F232" s="16" t="s">
+      <c r="H232" s="16" t="s">
         <v>2035</v>
-      </c>
-      <c r="G232" s="16" t="s">
-        <v>2036</v>
-      </c>
-      <c r="H232" s="16" t="s">
-        <v>2037</v>
       </c>
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
@@ -15789,23 +15801,23 @@
         <v>34</v>
       </c>
       <c r="B233" s="45" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="C233" s="46"/>
       <c r="D233" s="17" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E233" s="17" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F233" s="17" t="s">
         <v>2038</v>
       </c>
-      <c r="E233" s="17" t="s">
+      <c r="G233" s="17" t="s">
         <v>2039</v>
       </c>
-      <c r="F233" s="17" t="s">
+      <c r="H233" s="17" t="s">
         <v>2040</v>
-      </c>
-      <c r="G233" s="17" t="s">
-        <v>2041</v>
-      </c>
-      <c r="H233" s="17" t="s">
-        <v>2042</v>
       </c>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
@@ -15819,23 +15831,23 @@
         <v>34</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="C234" s="44"/>
       <c r="D234" s="16" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E234" s="16" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F234" s="16" t="s">
         <v>2043</v>
       </c>
-      <c r="E234" s="16" t="s">
+      <c r="G234" s="16" t="s">
         <v>2044</v>
       </c>
-      <c r="F234" s="16" t="s">
+      <c r="H234" s="16" t="s">
         <v>2045</v>
-      </c>
-      <c r="G234" s="16" t="s">
-        <v>2046</v>
-      </c>
-      <c r="H234" s="16" t="s">
-        <v>2047</v>
       </c>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
@@ -15849,10 +15861,10 @@
         <v>33</v>
       </c>
       <c r="B235" s="45" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="C235" s="46" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -15873,23 +15885,23 @@
         <v>34</v>
       </c>
       <c r="B236" s="45" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="C236" s="46"/>
       <c r="D236" s="17" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E236" s="17" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F236" s="17" t="s">
         <v>2049</v>
       </c>
-      <c r="E236" s="17" t="s">
+      <c r="G236" s="17" t="s">
         <v>2050</v>
       </c>
-      <c r="F236" s="17" t="s">
+      <c r="H236" s="17" t="s">
         <v>2051</v>
-      </c>
-      <c r="G236" s="17" t="s">
-        <v>2052</v>
-      </c>
-      <c r="H236" s="17" t="s">
-        <v>2053</v>
       </c>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
@@ -15903,23 +15915,23 @@
         <v>34</v>
       </c>
       <c r="B237" s="45" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="C237" s="46"/>
       <c r="D237" s="16" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E237" s="16" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F237" s="16" t="s">
         <v>2054</v>
       </c>
-      <c r="E237" s="16" t="s">
+      <c r="G237" s="16" t="s">
         <v>2055</v>
       </c>
-      <c r="F237" s="16" t="s">
+      <c r="H237" s="16" t="s">
         <v>2056</v>
-      </c>
-      <c r="G237" s="16" t="s">
-        <v>2057</v>
-      </c>
-      <c r="H237" s="16" t="s">
-        <v>2058</v>
       </c>
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
@@ -15933,23 +15945,23 @@
         <v>34</v>
       </c>
       <c r="B238" s="45" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="C238" s="46"/>
       <c r="D238" s="17" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E238" s="17" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F238" s="17" t="s">
         <v>2059</v>
       </c>
-      <c r="E238" s="17" t="s">
+      <c r="G238" s="17" t="s">
         <v>2060</v>
       </c>
-      <c r="F238" s="17" t="s">
+      <c r="H238" s="17" t="s">
         <v>2061</v>
-      </c>
-      <c r="G238" s="17" t="s">
-        <v>2062</v>
-      </c>
-      <c r="H238" s="17" t="s">
-        <v>2063</v>
       </c>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
@@ -15963,10 +15975,10 @@
         <v>33</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="C239" s="44" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -15987,23 +15999,23 @@
         <v>34</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="C240" s="44"/>
       <c r="D240" s="16" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E240" s="16" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F240" s="16" t="s">
         <v>2065</v>
       </c>
-      <c r="E240" s="16" t="s">
+      <c r="G240" s="16" t="s">
         <v>2066</v>
       </c>
-      <c r="F240" s="16" t="s">
+      <c r="H240" s="16" t="s">
         <v>2067</v>
-      </c>
-      <c r="G240" s="16" t="s">
-        <v>2068</v>
-      </c>
-      <c r="H240" s="16" t="s">
-        <v>2069</v>
       </c>
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
@@ -16017,23 +16029,23 @@
         <v>34</v>
       </c>
       <c r="B241" s="45" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C241" s="46"/>
       <c r="D241" s="17" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E241" s="17" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F241" s="17" t="s">
         <v>2070</v>
       </c>
-      <c r="E241" s="17" t="s">
+      <c r="G241" s="17" t="s">
         <v>2071</v>
       </c>
-      <c r="F241" s="17" t="s">
+      <c r="H241" s="17" t="s">
         <v>2072</v>
-      </c>
-      <c r="G241" s="17" t="s">
-        <v>2073</v>
-      </c>
-      <c r="H241" s="17" t="s">
-        <v>2074</v>
       </c>
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
@@ -16047,23 +16059,23 @@
         <v>34</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="C242" s="44"/>
       <c r="D242" s="16" t="s">
+        <v>2073</v>
+      </c>
+      <c r="E242" s="16" t="s">
+        <v>2074</v>
+      </c>
+      <c r="F242" s="16" t="s">
         <v>2075</v>
       </c>
-      <c r="E242" s="16" t="s">
+      <c r="G242" s="16" t="s">
         <v>2076</v>
       </c>
-      <c r="F242" s="16" t="s">
+      <c r="H242" s="16" t="s">
         <v>2077</v>
-      </c>
-      <c r="G242" s="16" t="s">
-        <v>2078</v>
-      </c>
-      <c r="H242" s="16" t="s">
-        <v>2079</v>
       </c>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
@@ -16077,7 +16089,7 @@
         <v>33</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -16099,7 +16111,7 @@
         <v>34</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="3" t="s">
@@ -16159,7 +16171,7 @@
         <v>34</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="3" t="s">
@@ -16189,7 +16201,7 @@
         <v>34</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="3" t="s">
@@ -16829,7 +16841,7 @@
         <v>660</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="I269" s="2"/>
       <c r="J269" s="6"/>
@@ -17815,7 +17827,7 @@
         <v>33</v>
       </c>
       <c r="B297" s="35" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="C297" s="36"/>
       <c r="D297" s="36"/>
@@ -18085,7 +18097,7 @@
         <v>33</v>
       </c>
       <c r="B305" s="18" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C305" s="19"/>
       <c r="D305" s="19"/>
@@ -18203,7 +18215,7 @@
         <v>33</v>
       </c>
       <c r="B309" s="18" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="C309" s="19"/>
       <c r="D309" s="19"/>
@@ -18257,7 +18269,7 @@
         <v>33</v>
       </c>
       <c r="B311" s="18" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="C311" s="19"/>
       <c r="D311" s="19"/>
@@ -18279,7 +18291,7 @@
         <v>34</v>
       </c>
       <c r="B312" s="20" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="C312" s="21"/>
       <c r="D312" s="22" t="s">
@@ -18365,7 +18377,7 @@
         <v>33</v>
       </c>
       <c r="B315" s="18" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C315" s="19"/>
       <c r="D315" s="19"/>
@@ -18417,7 +18429,7 @@
         <v>33</v>
       </c>
       <c r="B317" s="18" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C317" s="19"/>
       <c r="D317" s="19"/>
@@ -18469,7 +18481,7 @@
         <v>33</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C319" s="19"/>
       <c r="D319" s="19"/>
@@ -18603,7 +18615,7 @@
         <v>33</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="C324" s="19"/>
       <c r="D324" s="19"/>
@@ -18851,7 +18863,7 @@
         <v>33</v>
       </c>
       <c r="B332" s="35" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="C332" s="36"/>
       <c r="D332" s="36"/>
@@ -18877,19 +18889,19 @@
       </c>
       <c r="C333" s="27"/>
       <c r="D333" s="28" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E333" s="28" t="s">
         <v>2260</v>
       </c>
-      <c r="E333" s="28" t="s">
+      <c r="F333" s="28" t="s">
+        <v>2261</v>
+      </c>
+      <c r="G333" s="28" t="s">
         <v>2262</v>
       </c>
-      <c r="F333" s="28" t="s">
+      <c r="H333" s="28" t="s">
         <v>2263</v>
-      </c>
-      <c r="G333" s="28" t="s">
-        <v>2264</v>
-      </c>
-      <c r="H333" s="28" t="s">
-        <v>2265</v>
       </c>
       <c r="I333" s="2"/>
       <c r="J333" s="6"/>
@@ -18903,7 +18915,7 @@
         <v>34</v>
       </c>
       <c r="B334" s="23" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="C334" s="24"/>
       <c r="D334" s="25" t="s">
@@ -18963,7 +18975,7 @@
         <v>33</v>
       </c>
       <c r="B336" s="35" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="C336" s="36"/>
       <c r="D336" s="36"/>
@@ -19045,7 +19057,7 @@
         <v>33</v>
       </c>
       <c r="B339" s="35" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="C339" s="36"/>
       <c r="D339" s="36"/>
@@ -19071,19 +19083,19 @@
       </c>
       <c r="C340" s="37"/>
       <c r="D340" s="25" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E340" s="25" t="s">
+        <v>2268</v>
+      </c>
+      <c r="F340" s="25" t="s">
         <v>2269</v>
       </c>
-      <c r="E340" s="25" t="s">
+      <c r="G340" s="25" t="s">
         <v>2270</v>
       </c>
-      <c r="F340" s="25" t="s">
+      <c r="H340" s="25" t="s">
         <v>2271</v>
-      </c>
-      <c r="G340" s="25" t="s">
-        <v>2272</v>
-      </c>
-      <c r="H340" s="25" t="s">
-        <v>2273</v>
       </c>
       <c r="I340" s="2"/>
       <c r="J340" s="6"/>
@@ -19101,19 +19113,19 @@
       </c>
       <c r="C341" s="29"/>
       <c r="D341" s="25" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E341" s="25" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F341" s="25" t="s">
         <v>2274</v>
       </c>
-      <c r="E341" s="25" t="s">
+      <c r="G341" s="25" t="s">
         <v>2275</v>
       </c>
-      <c r="F341" s="25" t="s">
+      <c r="H341" s="25" t="s">
         <v>2276</v>
-      </c>
-      <c r="G341" s="25" t="s">
-        <v>2277</v>
-      </c>
-      <c r="H341" s="25" t="s">
-        <v>2278</v>
       </c>
       <c r="I341" s="2"/>
       <c r="J341" s="6"/>
@@ -19131,19 +19143,19 @@
       </c>
       <c r="C342" s="37"/>
       <c r="D342" s="25" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E342" s="25" t="s">
+        <v>2278</v>
+      </c>
+      <c r="F342" s="25" t="s">
         <v>2279</v>
       </c>
-      <c r="E342" s="25" t="s">
+      <c r="G342" s="25" t="s">
         <v>2280</v>
       </c>
-      <c r="F342" s="25" t="s">
+      <c r="H342" s="25" t="s">
         <v>2281</v>
-      </c>
-      <c r="G342" s="25" t="s">
-        <v>2282</v>
-      </c>
-      <c r="H342" s="25" t="s">
-        <v>2283</v>
       </c>
       <c r="I342" s="2"/>
       <c r="J342" s="6"/>
@@ -19397,7 +19409,7 @@
         <v>32</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="3" t="s">
@@ -19557,7 +19569,7 @@
         <v>89</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="I354" s="3" t="s">
         <v>91</v>
@@ -20009,7 +20021,7 @@
         <v>32</v>
       </c>
       <c r="B367" s="26" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="C367" s="29" t="s">
         <v>1088</v>
@@ -20389,7 +20401,7 @@
         <v>33</v>
       </c>
       <c r="B379" s="18" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="C379" s="19"/>
       <c r="D379" s="19"/>
@@ -20415,22 +20427,22 @@
       </c>
       <c r="C380" s="24"/>
       <c r="D380" s="25" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E380" s="25" t="s">
+        <v>2289</v>
+      </c>
+      <c r="F380" s="25" t="s">
+        <v>2287</v>
+      </c>
+      <c r="G380" s="25" t="s">
         <v>2288</v>
       </c>
-      <c r="E380" s="25" t="s">
-        <v>2291</v>
-      </c>
-      <c r="F380" s="25" t="s">
+      <c r="H380" s="25" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I380" s="25" t="s">
         <v>2289</v>
-      </c>
-      <c r="G380" s="25" t="s">
-        <v>2290</v>
-      </c>
-      <c r="H380" s="25" t="s">
-        <v>2292</v>
-      </c>
-      <c r="I380" s="25" t="s">
-        <v>2291</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
@@ -20475,7 +20487,7 @@
         <v>33</v>
       </c>
       <c r="B382" s="18" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="C382" s="19"/>
       <c r="D382" s="19"/>
@@ -20561,7 +20573,7 @@
         <v>33</v>
       </c>
       <c r="B385" s="18" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="C385" s="19" t="s">
         <v>944</v>
@@ -20617,7 +20629,7 @@
         <v>33</v>
       </c>
       <c r="B387" s="18" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="C387" s="19" t="s">
         <v>945</v>
@@ -20737,7 +20749,7 @@
         <v>34</v>
       </c>
       <c r="B391" s="23" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="C391" s="24"/>
       <c r="D391" s="25" t="s">
@@ -20769,7 +20781,7 @@
         <v>33</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="C392" s="19" t="s">
         <v>946</v>
@@ -20857,7 +20869,7 @@
         <v>32</v>
       </c>
       <c r="B395" s="38" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" s="38" t="s">
@@ -21037,7 +21049,7 @@
         <v>32</v>
       </c>
       <c r="B400" s="39" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="39" t="s">
@@ -21145,7 +21157,7 @@
         <v>32</v>
       </c>
       <c r="B403" s="38" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" s="38" t="s">
@@ -21181,7 +21193,7 @@
         <v>32</v>
       </c>
       <c r="B404" s="39" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="39" t="s">
@@ -21217,7 +21229,7 @@
         <v>32</v>
       </c>
       <c r="B405" s="38" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="38" t="s">
@@ -21289,7 +21301,7 @@
         <v>32</v>
       </c>
       <c r="B407" s="38" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" s="38" t="s">
@@ -21325,7 +21337,7 @@
         <v>32</v>
       </c>
       <c r="B408" s="39" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="39" t="s">
@@ -21365,22 +21377,22 @@
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="3" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="E409" s="3" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F409" s="3" t="s">
+        <v>2306</v>
+      </c>
+      <c r="G409" s="3" t="s">
+        <v>2301</v>
+      </c>
+      <c r="H409" s="3" t="s">
         <v>2307</v>
       </c>
-      <c r="F409" s="3" t="s">
-        <v>2308</v>
-      </c>
-      <c r="G409" s="3" t="s">
-        <v>2303</v>
-      </c>
-      <c r="H409" s="3" t="s">
-        <v>2309</v>
-      </c>
       <c r="I409" s="3" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="J409" s="13" t="s">
         <v>10</v>
@@ -21737,7 +21749,7 @@
         <v>244</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="I419" s="3" t="s">
         <v>237</v>
@@ -21800,10 +21812,10 @@
         <v>207</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>249</v>
@@ -21829,23 +21841,23 @@
         <v>32</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" s="3" t="s">
         <v>250</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>255</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="I422" s="3" t="s">
         <v>256</v>
@@ -21865,26 +21877,26 @@
         <v>32</v>
       </c>
       <c r="B423" s="51" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="C423" s="49"/>
       <c r="D423" s="38" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E423" s="38" t="s">
+        <v>2316</v>
+      </c>
+      <c r="F423" s="38" t="s">
         <v>2317</v>
       </c>
-      <c r="E423" s="38" t="s">
+      <c r="G423" s="38" t="s">
         <v>2318</v>
       </c>
-      <c r="F423" s="38" t="s">
+      <c r="H423" s="38" t="s">
         <v>2319</v>
       </c>
-      <c r="G423" s="38" t="s">
-        <v>2320</v>
-      </c>
-      <c r="H423" s="38" t="s">
-        <v>2321</v>
-      </c>
       <c r="I423" s="38" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="J423" s="11" t="s">
         <v>11</v>
@@ -21901,26 +21913,26 @@
         <v>32</v>
       </c>
       <c r="B424" s="52" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="C424" s="50"/>
       <c r="D424" s="39" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E424" s="39" t="s">
+        <v>2321</v>
+      </c>
+      <c r="F424" s="39" t="s">
         <v>2322</v>
       </c>
-      <c r="E424" s="39" t="s">
+      <c r="G424" s="39" t="s">
         <v>2323</v>
       </c>
-      <c r="F424" s="39" t="s">
-        <v>2324</v>
-      </c>
-      <c r="G424" s="39" t="s">
-        <v>2325</v>
-      </c>
       <c r="H424" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I424" s="39" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="J424" s="11" t="s">
         <v>11</v>
@@ -21937,26 +21949,26 @@
         <v>32</v>
       </c>
       <c r="B425" s="51" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="C425" s="49"/>
       <c r="D425" s="38" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E425" s="38" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F425" s="38" t="s">
         <v>2326</v>
       </c>
-      <c r="E425" s="38" t="s">
+      <c r="G425" s="38" t="s">
         <v>2327</v>
       </c>
-      <c r="F425" s="38" t="s">
-        <v>2328</v>
-      </c>
-      <c r="G425" s="38" t="s">
-        <v>2329</v>
-      </c>
       <c r="H425" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I425" s="38" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="J425" s="11" t="s">
         <v>11</v>
@@ -21973,26 +21985,26 @@
         <v>32</v>
       </c>
       <c r="B426" s="52" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="C426" s="50"/>
       <c r="D426" s="39" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E426" s="39" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F426" s="39" t="s">
         <v>2330</v>
       </c>
-      <c r="E426" s="39" t="s">
+      <c r="G426" s="39" t="s">
         <v>2331</v>
       </c>
-      <c r="F426" s="39" t="s">
-        <v>2332</v>
-      </c>
-      <c r="G426" s="39" t="s">
-        <v>2333</v>
-      </c>
       <c r="H426" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I426" s="39" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="J426" s="11" t="s">
         <v>11</v>
@@ -22009,26 +22021,26 @@
         <v>32</v>
       </c>
       <c r="B427" s="51" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="C427" s="49"/>
       <c r="D427" s="38" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E427" s="38" t="s">
+        <v>2333</v>
+      </c>
+      <c r="F427" s="38" t="s">
         <v>2334</v>
       </c>
-      <c r="E427" s="38" t="s">
+      <c r="G427" s="38" t="s">
         <v>2335</v>
       </c>
-      <c r="F427" s="38" t="s">
-        <v>2336</v>
-      </c>
-      <c r="G427" s="38" t="s">
-        <v>2337</v>
-      </c>
       <c r="H427" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I427" s="38" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="J427" s="11" t="s">
         <v>11</v>
@@ -22045,26 +22057,26 @@
         <v>32</v>
       </c>
       <c r="B428" s="52" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="C428" s="50"/>
       <c r="D428" s="39" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E428" s="39" t="s">
+        <v>2337</v>
+      </c>
+      <c r="F428" s="39" t="s">
         <v>2338</v>
       </c>
-      <c r="E428" s="39" t="s">
+      <c r="G428" s="39" t="s">
         <v>2339</v>
       </c>
-      <c r="F428" s="39" t="s">
-        <v>2340</v>
-      </c>
-      <c r="G428" s="39" t="s">
-        <v>2341</v>
-      </c>
       <c r="H428" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I428" s="39" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="J428" s="11" t="s">
         <v>11</v>
@@ -22081,26 +22093,26 @@
         <v>32</v>
       </c>
       <c r="B429" s="51" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="C429" s="49"/>
       <c r="D429" s="38" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E429" s="38" t="s">
+        <v>2341</v>
+      </c>
+      <c r="F429" s="38" t="s">
         <v>2342</v>
       </c>
-      <c r="E429" s="38" t="s">
+      <c r="G429" s="38" t="s">
         <v>2343</v>
       </c>
-      <c r="F429" s="38" t="s">
-        <v>2344</v>
-      </c>
-      <c r="G429" s="38" t="s">
-        <v>2345</v>
-      </c>
       <c r="H429" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I429" s="38" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="J429" s="11" t="s">
         <v>11</v>
@@ -22117,26 +22129,26 @@
         <v>32</v>
       </c>
       <c r="B430" s="52" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="C430" s="50"/>
       <c r="D430" s="39" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E430" s="39" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F430" s="39" t="s">
         <v>2346</v>
       </c>
-      <c r="E430" s="39" t="s">
+      <c r="G430" s="39" t="s">
         <v>2347</v>
       </c>
-      <c r="F430" s="39" t="s">
-        <v>2348</v>
-      </c>
-      <c r="G430" s="39" t="s">
-        <v>2349</v>
-      </c>
       <c r="H430" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I430" s="39" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="J430" s="11" t="s">
         <v>11</v>
@@ -22153,26 +22165,26 @@
         <v>32</v>
       </c>
       <c r="B431" s="51" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="C431" s="49"/>
       <c r="D431" s="38" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E431" s="38" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F431" s="38" t="s">
         <v>2350</v>
       </c>
-      <c r="E431" s="38" t="s">
+      <c r="G431" s="38" t="s">
         <v>2351</v>
       </c>
-      <c r="F431" s="38" t="s">
-        <v>2352</v>
-      </c>
-      <c r="G431" s="38" t="s">
-        <v>2353</v>
-      </c>
       <c r="H431" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I431" s="38" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="J431" s="11" t="s">
         <v>11</v>
@@ -22189,26 +22201,26 @@
         <v>32</v>
       </c>
       <c r="B432" s="52" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C432" s="50"/>
       <c r="D432" s="39" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E432" s="39" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F432" s="39" t="s">
         <v>2354</v>
       </c>
-      <c r="E432" s="39" t="s">
+      <c r="G432" s="39" t="s">
         <v>2355</v>
       </c>
-      <c r="F432" s="39" t="s">
-        <v>2356</v>
-      </c>
-      <c r="G432" s="39" t="s">
-        <v>2357</v>
-      </c>
       <c r="H432" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I432" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="J432" s="11" t="s">
         <v>11</v>
@@ -22225,26 +22237,26 @@
         <v>32</v>
       </c>
       <c r="B433" s="51" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="C433" s="49"/>
       <c r="D433" s="38" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E433" s="38" t="s">
+        <v>2357</v>
+      </c>
+      <c r="F433" s="38" t="s">
         <v>2358</v>
       </c>
-      <c r="E433" s="38" t="s">
+      <c r="G433" s="38" t="s">
         <v>2359</v>
       </c>
-      <c r="F433" s="38" t="s">
-        <v>2360</v>
-      </c>
-      <c r="G433" s="38" t="s">
-        <v>2361</v>
-      </c>
       <c r="H433" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I433" s="38" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="J433" s="11" t="s">
         <v>11</v>
@@ -22261,26 +22273,26 @@
         <v>32</v>
       </c>
       <c r="B434" s="52" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C434" s="50"/>
       <c r="D434" s="39" t="s">
+        <v>2360</v>
+      </c>
+      <c r="E434" s="39" t="s">
+        <v>2361</v>
+      </c>
+      <c r="F434" s="39" t="s">
         <v>2362</v>
       </c>
-      <c r="E434" s="39" t="s">
+      <c r="G434" s="39" t="s">
         <v>2363</v>
       </c>
-      <c r="F434" s="39" t="s">
-        <v>2364</v>
-      </c>
-      <c r="G434" s="39" t="s">
-        <v>2365</v>
-      </c>
       <c r="H434" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I434" s="39" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="J434" s="11" t="s">
         <v>11</v>
@@ -22297,26 +22309,26 @@
         <v>32</v>
       </c>
       <c r="B435" s="51" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="C435" s="49"/>
       <c r="D435" s="38" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E435" s="38" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F435" s="38" t="s">
         <v>2366</v>
       </c>
-      <c r="E435" s="38" t="s">
+      <c r="G435" s="38" t="s">
         <v>2367</v>
       </c>
-      <c r="F435" s="38" t="s">
-        <v>2368</v>
-      </c>
-      <c r="G435" s="38" t="s">
-        <v>2369</v>
-      </c>
       <c r="H435" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I435" s="38" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="J435" s="11" t="s">
         <v>11</v>
@@ -22333,26 +22345,26 @@
         <v>32</v>
       </c>
       <c r="B436" s="52" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="C436" s="50"/>
       <c r="D436" s="39" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E436" s="39" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F436" s="39" t="s">
         <v>2370</v>
       </c>
-      <c r="E436" s="39" t="s">
+      <c r="G436" s="39" t="s">
         <v>2371</v>
       </c>
-      <c r="F436" s="39" t="s">
-        <v>2372</v>
-      </c>
-      <c r="G436" s="39" t="s">
-        <v>2373</v>
-      </c>
       <c r="H436" s="39" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="I436" s="39" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="J436" s="11" t="s">
         <v>11</v>
@@ -22369,7 +22381,7 @@
         <v>33</v>
       </c>
       <c r="B437" s="40" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
@@ -22391,20 +22403,20 @@
         <v>34</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2404</v>
+        <v>2401</v>
       </c>
       <c r="C438" s="40"/>
       <c r="D438" s="54" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E438" s="54" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F438" s="54" t="s">
         <v>2388</v>
       </c>
-      <c r="E438" s="54" t="s">
-        <v>2389</v>
-      </c>
-      <c r="F438" s="54" t="s">
-        <v>2390</v>
-      </c>
       <c r="G438" s="54" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="H438" s="54" t="s">
         <v>1920</v>
@@ -22421,20 +22433,20 @@
         <v>34</v>
       </c>
       <c r="B439" s="55" t="s">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="C439" s="40"/>
       <c r="D439" s="55" t="s">
+        <v>2389</v>
+      </c>
+      <c r="E439" s="55" t="s">
+        <v>2390</v>
+      </c>
+      <c r="F439" s="55" t="s">
+        <v>2391</v>
+      </c>
+      <c r="G439" s="55" t="s">
         <v>2392</v>
-      </c>
-      <c r="E439" s="55" t="s">
-        <v>2393</v>
-      </c>
-      <c r="F439" s="55" t="s">
-        <v>2394</v>
-      </c>
-      <c r="G439" s="55" t="s">
-        <v>2395</v>
       </c>
       <c r="H439" s="55" t="s">
         <v>1920</v>
@@ -22451,20 +22463,20 @@
         <v>34</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
       <c r="C440" s="40"/>
       <c r="D440" s="54" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E440" s="54" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F440" s="54" t="s">
+        <v>2395</v>
+      </c>
+      <c r="G440" s="54" t="s">
         <v>2396</v>
-      </c>
-      <c r="E440" s="54" t="s">
-        <v>2397</v>
-      </c>
-      <c r="F440" s="54" t="s">
-        <v>2398</v>
-      </c>
-      <c r="G440" s="54" t="s">
-        <v>2399</v>
       </c>
       <c r="H440" s="54" t="s">
         <v>1920</v>
@@ -22485,16 +22497,16 @@
       </c>
       <c r="C441" s="40"/>
       <c r="D441" s="55" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E441" s="55" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F441" s="55" t="s">
+        <v>2399</v>
+      </c>
+      <c r="G441" s="55" t="s">
         <v>2400</v>
-      </c>
-      <c r="E441" s="55" t="s">
-        <v>2401</v>
-      </c>
-      <c r="F441" s="55" t="s">
-        <v>2402</v>
-      </c>
-      <c r="G441" s="55" t="s">
-        <v>2403</v>
       </c>
       <c r="H441" s="55" t="s">
         <v>1920</v>
@@ -22511,7 +22523,7 @@
         <v>33</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="C442" s="40"/>
       <c r="D442" s="40"/>
@@ -22533,20 +22545,20 @@
         <v>34</v>
       </c>
       <c r="B443" s="55" t="s">
-        <v>2408</v>
+        <v>2435</v>
       </c>
       <c r="C443" s="40"/>
       <c r="D443" s="55" t="s">
-        <v>2412</v>
+        <v>2405</v>
       </c>
       <c r="E443" s="55" t="s">
-        <v>2413</v>
+        <v>2406</v>
       </c>
       <c r="F443" s="55" t="s">
-        <v>2414</v>
+        <v>2407</v>
       </c>
       <c r="G443" s="55" t="s">
-        <v>2415</v>
+        <v>2408</v>
       </c>
       <c r="H443" s="55" t="s">
         <v>1920</v>
@@ -22563,20 +22575,20 @@
         <v>34</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2409</v>
+        <v>2436</v>
       </c>
       <c r="C444" s="40"/>
       <c r="D444" s="54" t="s">
-        <v>2416</v>
+        <v>2409</v>
       </c>
       <c r="E444" s="54" t="s">
-        <v>2417</v>
+        <v>2410</v>
       </c>
       <c r="F444" s="54" t="s">
-        <v>2418</v>
+        <v>2411</v>
       </c>
       <c r="G444" s="54" t="s">
-        <v>2419</v>
+        <v>2412</v>
       </c>
       <c r="H444" s="54" t="s">
         <v>1920</v>
@@ -22593,20 +22605,20 @@
         <v>34</v>
       </c>
       <c r="B445" s="55" t="s">
-        <v>2410</v>
+        <v>2437</v>
       </c>
       <c r="C445" s="40"/>
       <c r="D445" s="55" t="s">
-        <v>2420</v>
+        <v>2413</v>
       </c>
       <c r="E445" s="55" t="s">
-        <v>2421</v>
+        <v>2414</v>
       </c>
       <c r="F445" s="55" t="s">
-        <v>2422</v>
+        <v>2415</v>
       </c>
       <c r="G445" s="55" t="s">
-        <v>2423</v>
+        <v>2416</v>
       </c>
       <c r="H445" s="55" t="s">
         <v>1920</v>
@@ -22623,20 +22635,20 @@
         <v>34</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2411</v>
+        <v>2438</v>
       </c>
       <c r="C446" s="40"/>
       <c r="D446" s="54" t="s">
-        <v>2424</v>
+        <v>2417</v>
       </c>
       <c r="E446" s="54" t="s">
-        <v>2425</v>
+        <v>2418</v>
       </c>
       <c r="F446" s="54" t="s">
-        <v>2426</v>
+        <v>2419</v>
       </c>
       <c r="G446" s="54" t="s">
-        <v>2427</v>
+        <v>2420</v>
       </c>
       <c r="H446" s="54" t="s">
         <v>1920</v>
@@ -22653,7 +22665,7 @@
         <v>33</v>
       </c>
       <c r="B447" s="40" t="s">
-        <v>2428</v>
+        <v>2421</v>
       </c>
       <c r="C447" s="40"/>
       <c r="D447" s="40"/>
@@ -22705,7 +22717,7 @@
         <v>34</v>
       </c>
       <c r="B449" s="40" t="s">
-        <v>2429</v>
+        <v>2422</v>
       </c>
       <c r="C449" s="40"/>
       <c r="D449" s="42" t="s">
@@ -22735,20 +22747,20 @@
         <v>34</v>
       </c>
       <c r="B450" s="40" t="s">
-        <v>1995</v>
+        <v>2433</v>
       </c>
       <c r="C450" s="40"/>
       <c r="D450" s="40" t="s">
-        <v>2430</v>
+        <v>2423</v>
       </c>
       <c r="E450" s="40" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="F450" s="40" t="s">
-        <v>2432</v>
+        <v>2424</v>
       </c>
       <c r="G450" s="40" t="s">
-        <v>2433</v>
+        <v>2425</v>
       </c>
       <c r="H450" s="41" t="s">
         <v>1925</v>
@@ -22765,7 +22777,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="40" t="s">
-        <v>2434</v>
+        <v>2431</v>
       </c>
       <c r="C451" s="40"/>
       <c r="D451" s="42">
@@ -22795,7 +22807,7 @@
         <v>33</v>
       </c>
       <c r="B452" s="40" t="s">
-        <v>2435</v>
+        <v>2426</v>
       </c>
       <c r="C452" s="40"/>
       <c r="D452" s="40"/>
@@ -22817,20 +22829,20 @@
         <v>34</v>
       </c>
       <c r="B453" s="40" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="C453" s="40"/>
       <c r="D453" s="40" t="s">
-        <v>2436</v>
+        <v>2427</v>
       </c>
       <c r="E453" s="40" t="s">
-        <v>2437</v>
+        <v>2428</v>
       </c>
       <c r="F453" s="40" t="s">
-        <v>2438</v>
+        <v>2429</v>
       </c>
       <c r="G453" s="40" t="s">
-        <v>2439</v>
+        <v>2430</v>
       </c>
       <c r="H453" s="41" t="s">
         <v>1925</v>
@@ -22847,7 +22859,7 @@
         <v>34</v>
       </c>
       <c r="B454" s="40" t="s">
-        <v>1997</v>
+        <v>2432</v>
       </c>
       <c r="C454" s="40"/>
       <c r="D454" s="42" t="s">
@@ -22877,7 +22889,7 @@
         <v>32</v>
       </c>
       <c r="B455" s="40" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C455" s="40"/>
       <c r="D455" s="40" t="s">
@@ -22911,7 +22923,7 @@
         <v>32</v>
       </c>
       <c r="B456" s="40" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C456" s="40"/>
       <c r="D456" s="40" t="s">
@@ -22945,7 +22957,7 @@
         <v>32</v>
       </c>
       <c r="B457" s="40" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C457" s="40"/>
       <c r="D457" s="40" t="s">
@@ -22979,7 +22991,7 @@
         <v>32</v>
       </c>
       <c r="B458" s="40" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C458" s="40"/>
       <c r="D458" s="40" t="s">
@@ -23013,7 +23025,7 @@
         <v>32</v>
       </c>
       <c r="B459" s="40" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C459" s="40"/>
       <c r="D459" s="40" t="s">
@@ -23047,7 +23059,7 @@
         <v>32</v>
       </c>
       <c r="B460" s="40" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C460" s="40"/>
       <c r="D460" s="40" t="s">
@@ -23081,7 +23093,7 @@
         <v>32</v>
       </c>
       <c r="B461" s="40" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C461" s="40"/>
       <c r="D461" s="40" t="s">
@@ -23115,7 +23127,7 @@
         <v>32</v>
       </c>
       <c r="B462" s="40" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C462" s="40"/>
       <c r="D462" s="40" t="s">
@@ -23171,7 +23183,7 @@
         <v>34</v>
       </c>
       <c r="B464" s="40" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C464" s="40"/>
       <c r="D464" s="40" t="s">
@@ -23201,7 +23213,7 @@
         <v>34</v>
       </c>
       <c r="B465" s="40" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C465" s="40"/>
       <c r="D465" s="40" t="s">
@@ -23231,7 +23243,7 @@
         <v>34</v>
       </c>
       <c r="B466" s="40" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C466" s="40"/>
       <c r="D466" s="40" t="s">
@@ -23283,7 +23295,7 @@
         <v>34</v>
       </c>
       <c r="B468" s="40" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C468" s="40"/>
       <c r="D468" s="40" t="s">
@@ -23313,7 +23325,7 @@
         <v>34</v>
       </c>
       <c r="B469" s="40" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C469" s="40"/>
       <c r="D469" s="40" t="s">
@@ -23343,7 +23355,7 @@
         <v>34</v>
       </c>
       <c r="B470" s="40" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C470" s="40"/>
       <c r="D470" s="40" t="s">

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8880E8AD-3FE6-4777-9872-2B2F4A9AFC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CD066A-8522-42C6-BE64-73E8DEB27E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7590,151 +7590,135 @@
     <t>La valeur de la raideur $K$ est :</t>
   </si>
   <si>
+    <t>$\frac{dU_R}{dt} = \frac{R.E}{L} + \frac{L}{R}U_R$</t>
+  </si>
+  <si>
+    <t>$\frac{dU_R}{dt} = \frac{R.E}{L} - \frac{R}{L}U_R$</t>
+  </si>
+  <si>
+    <t>$\frac{dU_R}{dt} = \frac{E}{L} - \frac{R}{L}U_R$</t>
+  </si>
+  <si>
+    <t>$\frac{dU_R}{dt} = \frac{L}{E} - \frac{L}{R}U_R$</t>
+  </si>
+  <si>
+    <t>$L = 1~H$ ; $E = 6~V$</t>
+  </si>
+  <si>
+    <t>$L = 0,5~H$ ; $E = 5~V$</t>
+  </si>
+  <si>
+    <t>$L = 1~H$ ; $E = 5~V$</t>
+  </si>
+  <si>
+    <t>$L = 0,1~H$ ; $E = 10~V$</t>
+  </si>
+  <si>
+    <t>$I_0 = 0,35~A$</t>
+  </si>
+  <si>
+    <t>$I_0 = 0,5~A$</t>
+  </si>
+  <si>
+    <t>$I_0 = 0,25~A$</t>
+  </si>
+  <si>
+    <t>$I_0 = 0,05~A$</t>
+  </si>
+  <si>
+    <t>$E_m = 31,25~mJ$</t>
+  </si>
+  <si>
+    <t>$E_m = 6,25~KJ$</t>
+  </si>
+  <si>
+    <t>$E_m = 31,25~J$</t>
+  </si>
+  <si>
+    <t>$E_m = 6,25~mJ$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;RADIOACTIVITÉ&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Une source radioactive d'iode 123 a une activité de 5 GBq. Sa demi-vie physique $t_{1/2}​=13 h$ et sa constante radioactive $λ=5⋅10^{−2} h^{−1}$. 
+&lt;br&gt;On donne : ln2=0,69 $\quad$ et $\quad$ ln3=1.</t>
+  </si>
+  <si>
+    <t>Pour effectuer une scintigraphie thyroïdienne, on injecte à un patient 100 μCi d'iode 123. 
+&lt;br&gt;On donne : nombre d'Avogadro $N=6,02⋅10^{23}$, $\quad$ 1Ci=37⋅109 Bq, $\quad$ $\frac{125}{127}$=1 $\quad$ et $\quad$ $\frac{25}{6}$=4,2.
+L'activité d'iode 123 injectée exprimée en MBq est :</t>
+  </si>
+  <si>
+    <t>$4,2⋅10^{8}$</t>
+  </si>
+  <si>
+    <t>$4,2⋅10^{−9}$</t>
+  </si>
+  <si>
+    <t>$4,2⋅10^{−8}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;ONDES ÉLECTROMAGNÉTIQUES&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; Une source de lumière émet dans le vide une radiation intense de longueur d'onde λ=600 nm. 
+&lt;br&gt;On donne : célérité de la lumière dans le vide $c=3⋅10^{8}$ m/s.</t>
+  </si>
+  <si>
+    <t>$5⋅10^{14}$ Hz</t>
+  </si>
+  <si>
+    <t>$5⋅10^{14}$ kHz</t>
+  </si>
+  <si>
+    <t>$5⋅10^{14}$ MHz</t>
+  </si>
+  <si>
+    <t>$5⋅10^{14}$ GHz</t>
+  </si>
+  <si>
+    <t>Dans les explorations de la thyroïde, on dispose d'une source radioactive constituée d'un mélange de 2 radioéléments : iode radioactif 124 et iode radioactif 125, d'activités initiales A et B égales et de demi-vie physiques respectives T1​=4 jours et T2​=60 jours. 
+&lt;br&gt;On donne : $log_{10}​(2)=0,3$ $\quad$ et $\quad$ $\frac{6}{14}$=0,43. 
+&lt;br&gt;Le temps, en jours, au bout duquel l'activité de l'un des radioéléments sera inférieure à 0,1% de celle de l'autre est :</t>
+  </si>
+  <si>
+    <t>La radiation émise par la source traverse un milieu transparent d'indice n. Un opérateur affirme que la longueur d'onde est maintenant de 400nm. 
+L'indice n du milieu est égal à :</t>
+  </si>
+  <si>
+    <t>Le calcul donne un nombre d'atomes d'iode 123 injectés N=250⋅109. La ration iodée quotidienne normale en iode 127 étant R=125 μg/j.
+&lt;br&gt;Le nombre d'atomes d'iode 123 injectés représente une fraction q de R égale à :</t>
+  </si>
+  <si>
+    <t>$4,2⋅10^{9}$</t>
+  </si>
+  <si>
+    <t>L'équation différentielle que vérifie $U_R$ est :</t>
+  </si>
+  <si>
+    <t>Les valeurs de l'inductance $L$ et de la force électromotrice $E$ sont :</t>
+  </si>
+  <si>
+    <t>La valeur de l'intensité du courant ($I_0$) en régime permanent est :</t>
+  </si>
+  <si>
+    <t>La valeur de l'énergie magnétique ($E_m$) emmagasinée dans la bobine en régime permanent est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;MECANIQUE&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;    On considère un pendule élastique horizontal constitué d'un ressort de masse négligeable, de raideur K et de spires non jointives. À son extrémité libre est attaché un solide (S) de masse m=200 g. L'autre extrémité du ressort est liée à un support fixe (voir figure 1). 
+&lt;br&gt;
+    On néglige les frottements et on considère que le centre d'inertie G du solide coïncide à l'équilibre avec l'origine de l'axe (Ox). On écarte le solide (S) de sa position d'équilibre vers le sens négatif et on le lâche sans vitesse initiale à l'instant t=0. 
+&lt;br&gt;    La figure 2 représente les variations de l'abscisse x en fonction du temps. 
+&lt;br&gt;&lt;img src="/images/P2025F1F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne : $\pi^{2}=10$.</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt;ELECTRICITE&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt;&lt;img src="/images/P2025F3.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
-On considère un circuit électrique (Figure 1) qui comporte :
+&lt;br&gt;On considère un circuit électrique (Figure 1) qui comporte :
 &lt;br&gt;- Un générateur idéal de tension de force électromotrice E
 &lt;br&gt;- Une bobine idéale d'inductance L et de résistance négligeable
 &lt;br&gt;- Un conducteur ohmique de résistance R = 20 $Ohm$
 &lt;br&gt;- Un interrupteur A
-&lt;br&gt;&lt;img src="/images/P2025F4.png" alt="A" class="h-20 float-right ml-4 my-1" /&gt;
-À l'instant t=0, on ferme l'interrupteur K d'un circuit électrique. On obtient un graphique représentant la variation de dtduR​​ en fonction du temps ou de la tension aux bornes du conducteur ohmique.</t>
-  </si>
-  <si>
-    <t>$\frac{dU_R}{dt} = \frac{R.E}{L} + \frac{L}{R}U_R$</t>
-  </si>
-  <si>
-    <t>$\frac{dU_R}{dt} = \frac{R.E}{L} - \frac{R}{L}U_R$</t>
-  </si>
-  <si>
-    <t>$\frac{dU_R}{dt} = \frac{E}{L} - \frac{R}{L}U_R$</t>
-  </si>
-  <si>
-    <t>$\frac{dU_R}{dt} = \frac{L}{E} - \frac{L}{R}U_R$</t>
-  </si>
-  <si>
-    <t>$L = 1~H$ ; $E = 6~V$</t>
-  </si>
-  <si>
-    <t>$L = 0,5~H$ ; $E = 5~V$</t>
-  </si>
-  <si>
-    <t>$L = 1~H$ ; $E = 5~V$</t>
-  </si>
-  <si>
-    <t>$L = 0,1~H$ ; $E = 10~V$</t>
-  </si>
-  <si>
-    <t>$I_0 = 0,35~A$</t>
-  </si>
-  <si>
-    <t>$I_0 = 0,5~A$</t>
-  </si>
-  <si>
-    <t>$I_0 = 0,25~A$</t>
-  </si>
-  <si>
-    <t>$I_0 = 0,05~A$</t>
-  </si>
-  <si>
-    <t>$E_m = 31,25~mJ$</t>
-  </si>
-  <si>
-    <t>$E_m = 6,25~KJ$</t>
-  </si>
-  <si>
-    <t>$E_m = 31,25~J$</t>
-  </si>
-  <si>
-    <t>$E_m = 6,25~mJ$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;RADIOACTIVITÉ&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt;Une source radioactive d'iode 123 a une activité de 5 GBq. Sa demi-vie physique $t_{1/2}​=13 h$ et sa constante radioactive $λ=5⋅10^{−2} h^{−1}$. 
-&lt;br&gt;On donne : ln2=0,69 $\quad$ et $\quad$ ln3=1.</t>
-  </si>
-  <si>
-    <t>Pour effectuer une scintigraphie thyroïdienne, on injecte à un patient 100 μCi d'iode 123. 
-&lt;br&gt;On donne : nombre d'Avogadro $N=6,02⋅10^{23}$, $\quad$ 1Ci=37⋅109 Bq, $\quad$ $\frac{125}{127}$=1 $\quad$ et $\quad$ $\frac{25}{6}$=4,2.
-L'activité d'iode 123 injectée exprimée en MBq est :</t>
-  </si>
-  <si>
-    <t>$4,2⋅10^{8}$</t>
-  </si>
-  <si>
-    <t>$4,2⋅10^{−9}$</t>
-  </si>
-  <si>
-    <t>$4,2⋅10^{−8}$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;ONDES ÉLECTROMAGNÉTIQUES&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt; Une source de lumière émet dans le vide une radiation intense de longueur d'onde λ=600 nm. 
-&lt;br&gt;On donne : célérité de la lumière dans le vide $c=3⋅10^{8}$ m/s.</t>
-  </si>
-  <si>
-    <t>$5⋅10^{14}$ Hz</t>
-  </si>
-  <si>
-    <t>$5⋅10^{14}$ kHz</t>
-  </si>
-  <si>
-    <t>$5⋅10^{14}$ MHz</t>
-  </si>
-  <si>
-    <t>$5⋅10^{14}$ GHz</t>
-  </si>
-  <si>
-    <t>Dans les explorations de la thyroïde, on dispose d'une source radioactive constituée d'un mélange de 2 radioéléments : iode radioactif 124 et iode radioactif 125, d'activités initiales A et B égales et de demi-vie physiques respectives T1​=4 jours et T2​=60 jours. 
-&lt;br&gt;On donne : $log_{10}​(2)=0,3$ $\quad$ et $\quad$ $\frac{6}{14}$=0,43. 
-&lt;br&gt;Le temps, en jours, au bout duquel l'activité de l'un des radioéléments sera inférieure à 0,1% de celle de l'autre est :</t>
-  </si>
-  <si>
-    <t>La radiation émise par la source traverse un milieu transparent d'indice n. Un opérateur affirme que la longueur d'onde est maintenant de 400nm. 
-L'indice n du milieu est égal à :</t>
-  </si>
-  <si>
-    <t>Le calcul donne un nombre d'atomes d'iode 123 injectés N=250⋅109. La ration iodée quotidienne normale en iode 127 étant R=125 μg/j.
-&lt;br&gt;Le nombre d'atomes d'iode 123 injectés représente une fraction q de R égale à :</t>
-  </si>
-  <si>
-    <t>$4,2⋅10^{9}$</t>
-  </si>
-  <si>
-    <t>L'équation différentielle que vérifie $U_R$ est :</t>
-  </si>
-  <si>
-    <t>Les valeurs de l'inductance $L$ et de la force électromotrice $E$ sont :</t>
-  </si>
-  <si>
-    <t>La valeur de l'intensité du courant ($I_0$) en régime permanent est :</t>
-  </si>
-  <si>
-    <t>La valeur de l'énergie magnétique ($E_m$) emmagasinée dans la bobine en régime permanent est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;MECANIQUE&lt;/b&gt;&lt;/center&gt;
-&lt;br&gt;
-&lt;div style="display: flex; justify-content: space-between; align-items: center; width: 100%;"&gt;
-  &lt;div style="flex: 1; padding-right: 15px;"&gt;
-    On considère un pendule élastique horizontal constitué d'un ressort de masse négligeable, de raideur K et de spires non jointives. À son extrémité libre est attaché un solide (S) de masse m=200 g. L'autre extrémité du ressort est liée à un support fixe (voir figure 1). 
-  &lt;/div&gt;
-  &lt;div style="flex-shrink: 0;"&gt;
-    &lt;img src="/images/P2025F1.png" alt="Figure 1" style="height: 80px;" /&gt;
-  &lt;/div&gt;
-&lt;/div&gt;
-&lt;br&gt;
-&lt;div style="display: flex; justify-content: space-between; align-items: center; width: 100%;"&gt;
-  &lt;div style="flex: 1; padding-right: 15px;"&gt;
-    On néglige les frottements et on considère que le centre d'inertie G du solide coïncide à l'équilibre avec l'origine de l'axe (Ox). On écarte le solide (S) de sa position d'équilibre vers le sens négatif et on le lâche sans vitesse initiale à l'instant t=0. 
-    La figure 2 représente les variations de l'abscisse x en fonction du temps. 
-  &lt;/div&gt;
-  &lt;div style="flex-shrink: 0;"&gt;
-    &lt;img src="/images/P2025F2.png" alt="Figure 2" style="height: 80px;" /&gt;
-  &lt;/div&gt;
-&lt;/div&gt;
-&lt;br&gt;
-On donne : $\pi^{2}=10$.</t>
+À l'instant t=0, on ferme l'interrupteur K d'un circuit électrique. On obtient un graphique représentant la variation de dtduR​​ en fonction du temps ou de la tension aux bornes du conducteur ohmique.
+&lt;br&gt;&lt;img src="/images/P2025F3F4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
 </sst>
 </file>
@@ -22376,12 +22360,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="150" customHeight="1">
+    <row r="437" spans="1:12" ht="209.25" customHeight="1">
       <c r="A437" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B437" s="40" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
@@ -22523,7 +22507,7 @@
         <v>33</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>2404</v>
+        <v>2439</v>
       </c>
       <c r="C442" s="40"/>
       <c r="D442" s="40"/>
@@ -22545,20 +22529,20 @@
         <v>34</v>
       </c>
       <c r="B443" s="55" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="C443" s="40"/>
       <c r="D443" s="55" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E443" s="55" t="s">
         <v>2405</v>
       </c>
-      <c r="E443" s="55" t="s">
+      <c r="F443" s="55" t="s">
         <v>2406</v>
       </c>
-      <c r="F443" s="55" t="s">
+      <c r="G443" s="55" t="s">
         <v>2407</v>
-      </c>
-      <c r="G443" s="55" t="s">
-        <v>2408</v>
       </c>
       <c r="H443" s="55" t="s">
         <v>1920</v>
@@ -22575,20 +22559,20 @@
         <v>34</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="C444" s="40"/>
       <c r="D444" s="54" t="s">
+        <v>2408</v>
+      </c>
+      <c r="E444" s="54" t="s">
         <v>2409</v>
       </c>
-      <c r="E444" s="54" t="s">
+      <c r="F444" s="54" t="s">
         <v>2410</v>
       </c>
-      <c r="F444" s="54" t="s">
+      <c r="G444" s="54" t="s">
         <v>2411</v>
-      </c>
-      <c r="G444" s="54" t="s">
-        <v>2412</v>
       </c>
       <c r="H444" s="54" t="s">
         <v>1920</v>
@@ -22605,20 +22589,20 @@
         <v>34</v>
       </c>
       <c r="B445" s="55" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="C445" s="40"/>
       <c r="D445" s="55" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E445" s="55" t="s">
         <v>2413</v>
       </c>
-      <c r="E445" s="55" t="s">
+      <c r="F445" s="55" t="s">
         <v>2414</v>
       </c>
-      <c r="F445" s="55" t="s">
+      <c r="G445" s="55" t="s">
         <v>2415</v>
-      </c>
-      <c r="G445" s="55" t="s">
-        <v>2416</v>
       </c>
       <c r="H445" s="55" t="s">
         <v>1920</v>
@@ -22635,20 +22619,20 @@
         <v>34</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="C446" s="40"/>
       <c r="D446" s="54" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E446" s="54" t="s">
         <v>2417</v>
       </c>
-      <c r="E446" s="54" t="s">
+      <c r="F446" s="54" t="s">
         <v>2418</v>
       </c>
-      <c r="F446" s="54" t="s">
+      <c r="G446" s="54" t="s">
         <v>2419</v>
-      </c>
-      <c r="G446" s="54" t="s">
-        <v>2420</v>
       </c>
       <c r="H446" s="54" t="s">
         <v>1920</v>
@@ -22665,7 +22649,7 @@
         <v>33</v>
       </c>
       <c r="B447" s="40" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="C447" s="40"/>
       <c r="D447" s="40"/>
@@ -22717,7 +22701,7 @@
         <v>34</v>
       </c>
       <c r="B449" s="40" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="C449" s="40"/>
       <c r="D449" s="42" t="s">
@@ -22747,20 +22731,20 @@
         <v>34</v>
       </c>
       <c r="B450" s="40" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C450" s="40"/>
       <c r="D450" s="40" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E450" s="40" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F450" s="40" t="s">
         <v>2423</v>
       </c>
-      <c r="E450" s="40" t="s">
-        <v>2434</v>
-      </c>
-      <c r="F450" s="40" t="s">
+      <c r="G450" s="40" t="s">
         <v>2424</v>
-      </c>
-      <c r="G450" s="40" t="s">
-        <v>2425</v>
       </c>
       <c r="H450" s="41" t="s">
         <v>1925</v>
@@ -22777,7 +22761,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="40" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="C451" s="40"/>
       <c r="D451" s="42">
@@ -22807,7 +22791,7 @@
         <v>33</v>
       </c>
       <c r="B452" s="40" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="C452" s="40"/>
       <c r="D452" s="40"/>
@@ -22833,16 +22817,16 @@
       </c>
       <c r="C453" s="40"/>
       <c r="D453" s="40" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E453" s="40" t="s">
         <v>2427</v>
       </c>
-      <c r="E453" s="40" t="s">
+      <c r="F453" s="40" t="s">
         <v>2428</v>
       </c>
-      <c r="F453" s="40" t="s">
+      <c r="G453" s="40" t="s">
         <v>2429</v>
-      </c>
-      <c r="G453" s="40" t="s">
-        <v>2430</v>
       </c>
       <c r="H453" s="41" t="s">
         <v>1925</v>
@@ -22859,7 +22843,7 @@
         <v>34</v>
       </c>
       <c r="B454" s="40" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="C454" s="40"/>
       <c r="D454" s="42" t="s">

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CD066A-8522-42C6-BE64-73E8DEB27E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5EF6BB-A553-4CA8-9F53-B564C4522F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6014,81 +6014,24 @@
     <t>Le déplacement de l'équilibre ne dépend pas des concentrations des produits</t>
   </si>
   <si>
-    <t>Énoncé des questions Q37, Q38 et Q39 : On considère deux solutions aqueuses à 25∘C (Ke​=10−14) :- une solution de méthylamine CH3​NH2​ (S1​) de pH=11,3 et de concentration C1​=10−1 mol⋅L−1 ;- une solution d'acide méthanoïque (HCOOH) (S2​) de concentration C2​=10−2 mol⋅L−1 ; pKA​(HCOOH/HCOO−)=3,74. On donne : 10−2,7≈2⋅10−3 et log4=0,6.</t>
-  </si>
-  <si>
     <t>Une base selon Brønsted est une solution susceptible de céder un proton H+</t>
   </si>
   <si>
     <t>Une base faible selon Brønsted est une solution susceptible de céder un proton H+</t>
   </si>
   <si>
-    <t>Une solution aqueuse est basique si [H3​O+]&gt;[HO−]</t>
-  </si>
-  <si>
-    <t>La méthylamine CH3​NH2​ est une base forte</t>
-  </si>
-  <si>
-    <t>La méthylamine CH3​NH2​ est une base faible</t>
-  </si>
-  <si>
     <t>pKA1​=−logKA1​</t>
   </si>
   <si>
-    <t>KA1​=[CH3​NH3+​][CH3​NH2​]⋅[H3​O+]​</t>
-  </si>
-  <si>
-    <t>[HO−]=10−pH+Ke​</t>
-  </si>
-  <si>
     <t>pKA1​&gt;pKA2​</t>
   </si>
   <si>
     <t>pKA1​&lt;pKA2​</t>
   </si>
   <si>
-    <t>CH3​NH2​+HCOOH→CH3​NH3+​+HCOO−</t>
-  </si>
-  <si>
-    <t>CH3​NH2​+HCOOH→CH3​NH2+​+HCOOH−</t>
-  </si>
-  <si>
-    <t>HCOOH+CH3​NH3+​→CH3​NH2​+HCOO−</t>
-  </si>
-  <si>
-    <t>[HCOO−]=V1​+V2​C2​V2​​</t>
-  </si>
-  <si>
-    <t>Énoncé des questions Q40, Q41 et Q42 : On mélange, à un instant t=0, un volume VA​=30 mL d'une solution aqueuse de peroxodisulfate de sodium (Na2​S2​O8​) avec un volume VB​=40 mL d'une solution aqueuse d'iodure de potassium (KI). Les deux solutions ayant la même concentration CA​=CB​=2⋅10−1 mol⋅L−1.</t>
-  </si>
-  <si>
-    <t>2I(aq)−​+S2​O8(aq)2−​→2SO4(aq)2−​+I2(aq)​</t>
-  </si>
-  <si>
-    <t>2Na(aq)+​+2I(aq)−​→2Na(s)​+2I2(aq)​</t>
-  </si>
-  <si>
-    <t>2K(aq)+​+S2​O8(aq)2−​→2SO4(aq)2−​+2K(s)​</t>
-  </si>
-  <si>
-    <t>S2​O8(aq)2−​+I2(aq)​→2I(aq)−​+2SO4(aq)2−​</t>
-  </si>
-  <si>
     <t>Aucune des affirmations ci-dessus n'est correcte.</t>
   </si>
   <si>
-    <t>I(aq)−​</t>
-  </si>
-  <si>
-    <t>S2​O8(aq)2−​</t>
-  </si>
-  <si>
-    <t>SO4(aq)2−​</t>
-  </si>
-  <si>
-    <t>I2(aq)​</t>
-  </si>
-  <si>
     <t>v0​&gt;v1​</t>
   </si>
   <si>
@@ -6138,9 +6081,6 @@
   </si>
   <si>
     <t>Parmi ces propositions, laquelle est juste ?</t>
-  </si>
-  <si>
-    <t>Concernant le couple Acide / CH3​NH2​, laquelle de ces propositions est juste ?</t>
   </si>
   <si>
     <t>On mélange un volume V1​=10 mL de la solution S1​ et un volume V2​=30 mL de la solution S2​ (la réaction est considérée totale). Laquelle de ces propositions est juste ?</t>
@@ -7719,6 +7659,71 @@
 &lt;br&gt;- Un interrupteur A
 À l'instant t=0, on ferme l'interrupteur K d'un circuit électrique. On obtient un graphique représentant la variation de dtduR​​ en fonction du temps ou de la tension aux bornes du conducteur ohmique.
 &lt;br&gt;&lt;img src="/images/P2025F3F4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>$\ddot{x} - \frac{m}{K}x = 0$</t>
+  </si>
+  <si>
+    <t>Énoncé des questions Q37, Q38 et Q39 : 
+br&gt;On considère deux solutions aqueuses à 25∘C (Ke​=10−14) :
+&lt;br&gt;- une solution de méthylamine $CH_{3}​NH_{2}$​ (S1​) de pH=11,3 et de concentration $C_{1}​=10^{−1} mol⋅L−1$ ;
+&lt;br&gt;- une solution d'acide méthanoïque (HCOOH) (S2​) de concentration $C_{2}​=10^{−2} mol⋅L−1$ ; $pKA​(HCOOH/HCOO^{)}=3,74$. 
+&lt;br&gt;On donne : $10^{−2,7} ≈ 2⋅10^{−3}$ $\quad$ et $\quad$ log4=0,6.</t>
+  </si>
+  <si>
+    <t>Une solution aqueuse est basique si $[H_{3}​O^{+}]&gt;[HO^{−}]$</t>
+  </si>
+  <si>
+    <t>La méthylamine $CH_{3}​NH_{2}$​ est une base forte</t>
+  </si>
+  <si>
+    <t>La méthylamine $CH_{3}​NH_{2}$​ est une base faible</t>
+  </si>
+  <si>
+    <t>$[HO^{−}]=10^{−}pH$+Ke​</t>
+  </si>
+  <si>
+    <t>KA1​=$[CH_{3}​NH_{3}^{+}​][CH_{3}​NH_{2}​]⋅[H_{3}​O^{+}]​$</t>
+  </si>
+  <si>
+    <t>Concernant le couple Acide / $CH_{3}​NH_{2}$​, laquelle de ces propositions est juste ?</t>
+  </si>
+  <si>
+    <t>$CH_{3}​NH_{2}$​+HCOOH→$CH_{3}​NH_{3}^{+}$​+$HCOO^{−}$</t>
+  </si>
+  <si>
+    <t>$CH_{3}​NH_{2}$​+HCOOH→$CH_{3}​NH_{2}^{+}$​+$HCOO^{−}$</t>
+  </si>
+  <si>
+    <t>HCOOH+$CH_{3}​NH_{3}$​→$CH_{3}​NH_{2}^{+}$​+$HCOO^{−}$</t>
+  </si>
+  <si>
+    <t>$[HCOO^{−}]$=V1​+V2​C2​V2​​</t>
+  </si>
+  <si>
+    <t>Énoncé des questions Q40, Q41 et Q42 : 
+&lt;br&gt;On mélange, à un instant t=0, un volume VA​=30 mL d'une solution aqueuse de peroxodisulfate de sodium ($Na_{2}​S_{2}​O_{8}​$) avec un volume VB​=40 mL d'une solution aqueuse d'iodure de potassium (KI). Les deux solutions ayant la même concentration CA​=CB​=$2⋅10^{−1} mol⋅L^{−1}$.</t>
+  </si>
+  <si>
+    <t>$2\text{I}_{(aq)}^{-} + \text{S}_2\text{O}_{8(aq)}^{2-} \rightarrow 2\text{SO}_{4(aq)}^{2-} + \text{I}_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$2\text{Na}_{(aq)}^{+} + 2\text{I}_{(aq)}^{-} \rightarrow 2\text{Na}_{(s)} + \text{I}_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$2\text{K}_{(aq)}^{+} + \text{S}_2\text{O}_{8(aq)}^{2-} \rightarrow 2\text{SO}_{4(aq)}^{2-} + 2\text{K}_{(s)}$</t>
+  </si>
+  <si>
+    <t>$$\text{S}_2\text{O}_{8(aq)}^{2-} + \text{I}_{2(aq)} \rightarrow 2\text{I}_{(aq)}^{-} + 2\text{SO}_{4(aq)}^{2-}$$</t>
+  </si>
+  <si>
+    <t>$\text{I}_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$\text{S}_2\text{O}_{8(aq)}^{2-}$</t>
+  </si>
+  <si>
+    <t>$\text{SO}_{4(aq)}^{2-}$</t>
   </si>
 </sst>
 </file>
@@ -8817,7 +8822,7 @@
         <v>32</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>2104</v>
+        <v>2084</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="32" t="s">
@@ -8853,7 +8858,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>2098</v>
+        <v>2078</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="32" t="s">
@@ -8889,7 +8894,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>2099</v>
+        <v>2079</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="32" t="s">
@@ -8961,7 +8966,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>2100</v>
+        <v>2080</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="32" t="s">
@@ -9033,7 +9038,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>2101</v>
+        <v>2081</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="32" t="s">
@@ -9069,7 +9074,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>2102</v>
+        <v>2082</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="32" t="s">
@@ -9105,7 +9110,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>2096</v>
+        <v>2076</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="32" t="s">
@@ -9141,7 +9146,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>2103</v>
+        <v>2083</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="32" t="s">
@@ -9177,7 +9182,7 @@
         <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2105</v>
+        <v>2085</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="2"/>
@@ -9199,11 +9204,11 @@
         <v>34</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2106</v>
+        <v>2086</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="3" t="s">
-        <v>2118</v>
+        <v>2098</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>666</v>
@@ -9295,7 +9300,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2107</v>
+        <v>2087</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -9317,7 +9322,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2108</v>
+        <v>2088</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="3" t="s">
@@ -9381,7 +9386,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2110</v>
+        <v>2090</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -9451,7 +9456,7 @@
         <v>698</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>2109</v>
+        <v>2089</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>695</v>
@@ -9467,7 +9472,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>2111</v>
+        <v>2091</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
@@ -9499,7 +9504,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2112</v>
+        <v>2092</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -9521,7 +9526,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2113</v>
+        <v>2093</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -9553,7 +9558,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2114</v>
+        <v>2094</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
@@ -9585,7 +9590,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2119</v>
+        <v>2099</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -9607,7 +9612,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2115</v>
+        <v>2095</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
@@ -9639,7 +9644,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2116</v>
+        <v>2096</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
@@ -9671,7 +9676,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2117</v>
+        <v>2097</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -9693,7 +9698,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2120</v>
+        <v>2100</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="3" t="s">
@@ -9723,7 +9728,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="3" t="s">
@@ -9753,26 +9758,26 @@
         <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2122</v>
+        <v>2102</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="3" t="s">
-        <v>2123</v>
+        <v>2103</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2124</v>
+        <v>2104</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>2125</v>
+        <v>2105</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>2126</v>
+        <v>2106</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>2127</v>
+        <v>2107</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>2124</v>
+        <v>2104</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>9</v>
@@ -9789,7 +9794,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>2128</v>
+        <v>2108</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -9811,7 +9816,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>2129</v>
+        <v>2109</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
@@ -9843,7 +9848,7 @@
         <v>34</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2130</v>
+        <v>2110</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
@@ -9907,7 +9912,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2131</v>
+        <v>2111</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -9993,7 +9998,7 @@
         <v>33</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>2143</v>
+        <v>2123</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -10111,7 +10116,7 @@
         <v>33</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>2137</v>
+        <v>2117</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -10137,22 +10142,22 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="32" t="s">
-        <v>2138</v>
+        <v>2118</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>2139</v>
+        <v>2119</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>2140</v>
+        <v>2120</v>
       </c>
       <c r="G55" s="32" t="s">
-        <v>2141</v>
+        <v>2121</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>2142</v>
+        <v>2122</v>
       </c>
       <c r="I55" s="32" t="s">
-        <v>2139</v>
+        <v>2119</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
@@ -10261,7 +10266,7 @@
         <v>33</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>2136</v>
+        <v>2116</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -10379,7 +10384,7 @@
         <v>32</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>2135</v>
+        <v>2115</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="32" t="s">
@@ -10415,7 +10420,7 @@
         <v>33</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>2134</v>
+        <v>2114</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -10501,7 +10506,7 @@
         <v>33</v>
       </c>
       <c r="B67" s="32" t="s">
-        <v>2133</v>
+        <v>2113</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -10619,7 +10624,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>2144</v>
+        <v>2124</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -10705,7 +10710,7 @@
         <v>33</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>2132</v>
+        <v>2112</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -10863,7 +10868,7 @@
         <v>32</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>2145</v>
+        <v>2125</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="3" t="s">
@@ -11007,7 +11012,7 @@
         <v>32</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>2146</v>
+        <v>2126</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="3" t="s">
@@ -11079,7 +11084,7 @@
         <v>32</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>2095</v>
+        <v>2075</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="3" t="s">
@@ -11151,7 +11156,7 @@
         <v>32</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2147</v>
+        <v>2127</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="3" t="s">
@@ -11223,7 +11228,7 @@
         <v>32</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>2148</v>
+        <v>2128</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="3" t="s">
@@ -11295,7 +11300,7 @@
         <v>32</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>2149</v>
+        <v>2129</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="3" t="s">
@@ -11331,7 +11336,7 @@
         <v>32</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>2150</v>
+        <v>2130</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="3" t="s">
@@ -11367,7 +11372,7 @@
         <v>32</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>2151</v>
+        <v>2131</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="3" t="s">
@@ -11871,7 +11876,7 @@
         <v>32</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>2152</v>
+        <v>2132</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="33" t="s">
@@ -11943,7 +11948,7 @@
         <v>32</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>2153</v>
+        <v>2133</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="33" t="s">
@@ -11979,7 +11984,7 @@
         <v>32</v>
       </c>
       <c r="B110" s="26" t="s">
-        <v>2154</v>
+        <v>2134</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="34" t="s">
@@ -12015,7 +12020,7 @@
         <v>32</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>2155</v>
+        <v>2135</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="33" t="s">
@@ -12051,7 +12056,7 @@
         <v>32</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>2156</v>
+        <v>2136</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="34" t="s">
@@ -12087,7 +12092,7 @@
         <v>32</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>2157</v>
+        <v>2137</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="33" t="s">
@@ -12123,7 +12128,7 @@
         <v>32</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>2158</v>
+        <v>2138</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="34" t="s">
@@ -12159,7 +12164,7 @@
         <v>32</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>2159</v>
+        <v>2139</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="33" t="s">
@@ -12195,7 +12200,7 @@
         <v>32</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>2160</v>
+        <v>2140</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="34" t="s">
@@ -12231,7 +12236,7 @@
         <v>33</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>2187</v>
+        <v>2167</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -12257,22 +12262,22 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="3" t="s">
-        <v>2161</v>
+        <v>2141</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>2162</v>
+        <v>2142</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>2163</v>
+        <v>2143</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>2164</v>
+        <v>2144</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>2165</v>
+        <v>2145</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>2164</v>
+        <v>2144</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
@@ -12349,7 +12354,7 @@
         <v>33</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>2188</v>
+        <v>2168</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -12435,7 +12440,7 @@
         <v>33</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>2166</v>
+        <v>2146</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -12521,7 +12526,7 @@
         <v>33</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>2167</v>
+        <v>2147</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -12725,7 +12730,7 @@
         <v>34</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>2168</v>
+        <v>2148</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
@@ -12757,7 +12762,7 @@
         <v>33</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>2189</v>
+        <v>2169</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -12783,7 +12788,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="3" t="s">
-        <v>2169</v>
+        <v>2149</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>819</v>
@@ -12811,26 +12816,26 @@
         <v>34</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2170</v>
+        <v>2150</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="3" t="s">
-        <v>2171</v>
+        <v>2151</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>2172</v>
+        <v>2152</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>2173</v>
+        <v>2153</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>2174</v>
+        <v>2154</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>2175</v>
+        <v>2155</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>2174</v>
+        <v>2154</v>
       </c>
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
@@ -12907,7 +12912,7 @@
         <v>33</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>2190</v>
+        <v>2170</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>837</v>
@@ -12935,22 +12940,22 @@
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="3" t="s">
-        <v>2176</v>
+        <v>2156</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>2177</v>
+        <v>2157</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>2178</v>
+        <v>2158</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>2179</v>
+        <v>2159</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>2180</v>
+        <v>2160</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>2178</v>
+        <v>2158</v>
       </c>
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
@@ -12970,7 +12975,7 @@
         <v>833</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>2181</v>
+        <v>2161</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>834</v>
@@ -12999,22 +13004,22 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="3" t="s">
-        <v>2182</v>
+        <v>2162</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>2183</v>
+        <v>2163</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>2184</v>
+        <v>2164</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>2185</v>
+        <v>2165</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>2186</v>
+        <v>2166</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>2183</v>
+        <v>2163</v>
       </c>
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
@@ -13027,7 +13032,7 @@
         <v>33</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>2192</v>
+        <v>2172</v>
       </c>
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
@@ -13145,7 +13150,7 @@
         <v>33</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>2193</v>
+        <v>2173</v>
       </c>
       <c r="C148" s="32"/>
       <c r="D148" s="32"/>
@@ -13263,7 +13268,7 @@
         <v>33</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
@@ -13349,7 +13354,7 @@
         <v>34</v>
       </c>
       <c r="B155" s="32" t="s">
-        <v>2191</v>
+        <v>2171</v>
       </c>
       <c r="C155" s="32"/>
       <c r="D155" s="32" t="s">
@@ -13413,7 +13418,7 @@
         <v>33</v>
       </c>
       <c r="B157" s="32" t="s">
-        <v>2195</v>
+        <v>2175</v>
       </c>
       <c r="C157" s="32"/>
       <c r="D157" s="2"/>
@@ -13499,7 +13504,7 @@
         <v>33</v>
       </c>
       <c r="B160" s="32" t="s">
-        <v>2196</v>
+        <v>2176</v>
       </c>
       <c r="C160" s="32"/>
       <c r="D160" s="32"/>
@@ -13617,7 +13622,7 @@
         <v>33</v>
       </c>
       <c r="B164" s="32" t="s">
-        <v>2197</v>
+        <v>2177</v>
       </c>
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
@@ -13959,7 +13964,7 @@
         <v>439</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>2198</v>
+        <v>2178</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>400</v>
@@ -13995,10 +14000,10 @@
         <v>405</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>2199</v>
+        <v>2179</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>2199</v>
+        <v>2179</v>
       </c>
       <c r="J175" s="13" t="s">
         <v>10</v>
@@ -14028,13 +14033,13 @@
         <v>408</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>2201</v>
+        <v>2181</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>2200</v>
+        <v>2180</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>2200</v>
+        <v>2180</v>
       </c>
       <c r="J176" s="13" t="s">
         <v>10</v>
@@ -14100,13 +14105,13 @@
         <v>416</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>2203</v>
+        <v>2183</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>2202</v>
+        <v>2182</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>2203</v>
+        <v>2183</v>
       </c>
       <c r="J178" s="13" t="s">
         <v>10</v>
@@ -14127,22 +14132,22 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="3" t="s">
-        <v>2213</v>
+        <v>2193</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>2212</v>
+        <v>2192</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>2211</v>
+        <v>2191</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>2209</v>
+        <v>2189</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>2211</v>
+        <v>2191</v>
       </c>
       <c r="J179" s="13" t="s">
         <v>10</v>
@@ -14163,22 +14168,22 @@
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="3" t="s">
-        <v>2205</v>
+        <v>2185</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>2204</v>
+        <v>2184</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>2206</v>
+        <v>2186</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>2207</v>
+        <v>2187</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>2208</v>
+        <v>2188</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>2205</v>
+        <v>2185</v>
       </c>
       <c r="J180" s="13" t="s">
         <v>10</v>
@@ -14244,7 +14249,7 @@
         <v>425</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>2214</v>
+        <v>2194</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>426</v>
@@ -14319,7 +14324,7 @@
         <v>434</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>2215</v>
+        <v>2195</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>409</v>
@@ -14355,7 +14360,7 @@
         <v>435</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>2216</v>
+        <v>2196</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>410</v>
@@ -14375,7 +14380,7 @@
         <v>32</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>2223</v>
+        <v>2203</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="3" t="s">
@@ -14388,10 +14393,10 @@
         <v>438</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>2218</v>
+        <v>2198</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>2217</v>
+        <v>2197</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>437</v>
@@ -14447,7 +14452,7 @@
         <v>32</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>2224</v>
+        <v>2204</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="3" t="s">
@@ -14490,16 +14495,16 @@
         <v>444</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>2219</v>
+        <v>2199</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>2220</v>
+        <v>2200</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>2221</v>
+        <v>2201</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>2222</v>
+        <v>2202</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>444</v>
@@ -14553,7 +14558,7 @@
         <v>32</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>2225</v>
+        <v>2205</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="31" t="s">
@@ -14791,7 +14796,7 @@
         <v>32</v>
       </c>
       <c r="B198" s="30" t="s">
-        <v>2226</v>
+        <v>2206</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="30" t="s">
@@ -14911,7 +14916,7 @@
         <v>33</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>2232</v>
+        <v>2212</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -14967,19 +14972,19 @@
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="47" t="s">
-        <v>2227</v>
+        <v>2207</v>
       </c>
       <c r="E204" s="47" t="s">
-        <v>2228</v>
+        <v>2208</v>
       </c>
       <c r="F204" s="47" t="s">
-        <v>2229</v>
+        <v>2209</v>
       </c>
       <c r="G204" s="47" t="s">
-        <v>2230</v>
+        <v>2210</v>
       </c>
       <c r="H204" s="47" t="s">
-        <v>2231</v>
+        <v>2211</v>
       </c>
       <c r="I204" s="2"/>
       <c r="J204" s="6" t="s">
@@ -14997,7 +15002,7 @@
         <v>33</v>
       </c>
       <c r="B205" s="31" t="s">
-        <v>2233</v>
+        <v>2213</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -15053,19 +15058,19 @@
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="30" t="s">
-        <v>2234</v>
+        <v>2214</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>2235</v>
+        <v>2215</v>
       </c>
       <c r="F207" s="30" t="s">
-        <v>2236</v>
+        <v>2216</v>
       </c>
       <c r="G207" s="30" t="s">
-        <v>2237</v>
+        <v>2217</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>2238</v>
+        <v>2218</v>
       </c>
       <c r="I207" s="2"/>
       <c r="J207" s="6" t="s">
@@ -15117,7 +15122,7 @@
         <v>33</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>2239</v>
+        <v>2219</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -15143,19 +15148,19 @@
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="30" t="s">
-        <v>2240</v>
+        <v>2220</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>2241</v>
+        <v>2221</v>
       </c>
       <c r="F210" s="30" t="s">
-        <v>2242</v>
+        <v>2222</v>
       </c>
       <c r="G210" s="30" t="s">
-        <v>2243</v>
+        <v>2223</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>2244</v>
+        <v>2224</v>
       </c>
       <c r="I210" s="2"/>
       <c r="J210" s="6"/>
@@ -15589,7 +15594,7 @@
         <v>33</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>2078</v>
+        <v>2058</v>
       </c>
       <c r="C226" s="44"/>
       <c r="D226" s="2"/>
@@ -15611,23 +15616,23 @@
         <v>34</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="C227" s="44"/>
       <c r="D227" s="16" t="s">
-        <v>2010</v>
+        <v>1990</v>
       </c>
       <c r="E227" s="16" t="s">
-        <v>2011</v>
+        <v>1991</v>
       </c>
       <c r="F227" s="16" t="s">
-        <v>2012</v>
+        <v>1992</v>
       </c>
       <c r="G227" s="16" t="s">
-        <v>2013</v>
+        <v>1993</v>
       </c>
       <c r="H227" s="16" t="s">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
@@ -15641,23 +15646,23 @@
         <v>34</v>
       </c>
       <c r="B228" s="45" t="s">
-        <v>2080</v>
+        <v>2060</v>
       </c>
       <c r="C228" s="46"/>
       <c r="D228" s="17" t="s">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="E228" s="17" t="s">
-        <v>2016</v>
+        <v>1996</v>
       </c>
       <c r="F228" s="17" t="s">
-        <v>2017</v>
+        <v>1997</v>
       </c>
       <c r="G228" s="17" t="s">
-        <v>2018</v>
+        <v>1998</v>
       </c>
       <c r="H228" s="17" t="s">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
@@ -15671,23 +15676,23 @@
         <v>34</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>2082</v>
+        <v>2062</v>
       </c>
       <c r="C229" s="44"/>
       <c r="D229" s="16" t="s">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>2021</v>
+        <v>2001</v>
       </c>
       <c r="F229" s="16" t="s">
-        <v>2022</v>
+        <v>2002</v>
       </c>
       <c r="G229" s="16" t="s">
-        <v>2023</v>
+        <v>2003</v>
       </c>
       <c r="H229" s="16" t="s">
-        <v>2024</v>
+        <v>2004</v>
       </c>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
@@ -15701,23 +15706,23 @@
         <v>34</v>
       </c>
       <c r="B230" s="45" t="s">
-        <v>2081</v>
+        <v>2061</v>
       </c>
       <c r="C230" s="46"/>
       <c r="D230" s="17" t="s">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="E230" s="17" t="s">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="F230" s="17" t="s">
-        <v>2027</v>
+        <v>2007</v>
       </c>
       <c r="G230" s="17" t="s">
-        <v>2028</v>
+        <v>2008</v>
       </c>
       <c r="H230" s="17" t="s">
-        <v>2029</v>
+        <v>2009</v>
       </c>
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
@@ -15731,10 +15736,10 @@
         <v>33</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>2083</v>
+        <v>2063</v>
       </c>
       <c r="C231" s="44" t="s">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -15755,23 +15760,23 @@
         <v>34</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>2084</v>
+        <v>2064</v>
       </c>
       <c r="C232" s="44"/>
       <c r="D232" s="16" t="s">
-        <v>2031</v>
+        <v>2011</v>
       </c>
       <c r="E232" s="16" t="s">
-        <v>2032</v>
+        <v>2012</v>
       </c>
       <c r="F232" s="16" t="s">
-        <v>2033</v>
+        <v>2013</v>
       </c>
       <c r="G232" s="16" t="s">
-        <v>2034</v>
+        <v>2014</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>2035</v>
+        <v>2015</v>
       </c>
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
@@ -15785,23 +15790,23 @@
         <v>34</v>
       </c>
       <c r="B233" s="45" t="s">
-        <v>2085</v>
+        <v>2065</v>
       </c>
       <c r="C233" s="46"/>
       <c r="D233" s="17" t="s">
-        <v>2036</v>
+        <v>2016</v>
       </c>
       <c r="E233" s="17" t="s">
-        <v>2037</v>
+        <v>2017</v>
       </c>
       <c r="F233" s="17" t="s">
-        <v>2038</v>
+        <v>2018</v>
       </c>
       <c r="G233" s="17" t="s">
-        <v>2039</v>
+        <v>2019</v>
       </c>
       <c r="H233" s="17" t="s">
-        <v>2040</v>
+        <v>2020</v>
       </c>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
@@ -15815,23 +15820,23 @@
         <v>34</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>2086</v>
+        <v>2066</v>
       </c>
       <c r="C234" s="44"/>
       <c r="D234" s="16" t="s">
-        <v>2041</v>
+        <v>2021</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>2042</v>
+        <v>2022</v>
       </c>
       <c r="F234" s="16" t="s">
-        <v>2043</v>
+        <v>2023</v>
       </c>
       <c r="G234" s="16" t="s">
-        <v>2044</v>
+        <v>2024</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>2045</v>
+        <v>2025</v>
       </c>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
@@ -15845,10 +15850,10 @@
         <v>33</v>
       </c>
       <c r="B235" s="45" t="s">
-        <v>2093</v>
+        <v>2073</v>
       </c>
       <c r="C235" s="46" t="s">
-        <v>2046</v>
+        <v>2026</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -15869,23 +15874,23 @@
         <v>34</v>
       </c>
       <c r="B236" s="45" t="s">
-        <v>2087</v>
+        <v>2067</v>
       </c>
       <c r="C236" s="46"/>
       <c r="D236" s="17" t="s">
-        <v>2047</v>
+        <v>2027</v>
       </c>
       <c r="E236" s="17" t="s">
-        <v>2048</v>
+        <v>2028</v>
       </c>
       <c r="F236" s="17" t="s">
-        <v>2049</v>
+        <v>2029</v>
       </c>
       <c r="G236" s="17" t="s">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H236" s="17" t="s">
-        <v>2051</v>
+        <v>2031</v>
       </c>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
@@ -15899,23 +15904,23 @@
         <v>34</v>
       </c>
       <c r="B237" s="45" t="s">
-        <v>2094</v>
+        <v>2074</v>
       </c>
       <c r="C237" s="46"/>
       <c r="D237" s="16" t="s">
-        <v>2052</v>
+        <v>2032</v>
       </c>
       <c r="E237" s="16" t="s">
-        <v>2053</v>
+        <v>2033</v>
       </c>
       <c r="F237" s="16" t="s">
-        <v>2054</v>
+        <v>2034</v>
       </c>
       <c r="G237" s="16" t="s">
-        <v>2055</v>
+        <v>2035</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>2056</v>
+        <v>2036</v>
       </c>
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
@@ -15929,23 +15934,23 @@
         <v>34</v>
       </c>
       <c r="B238" s="45" t="s">
-        <v>2088</v>
+        <v>2068</v>
       </c>
       <c r="C238" s="46"/>
       <c r="D238" s="17" t="s">
-        <v>2057</v>
+        <v>2037</v>
       </c>
       <c r="E238" s="17" t="s">
-        <v>2058</v>
+        <v>2038</v>
       </c>
       <c r="F238" s="17" t="s">
-        <v>2059</v>
+        <v>2039</v>
       </c>
       <c r="G238" s="17" t="s">
-        <v>2060</v>
+        <v>2040</v>
       </c>
       <c r="H238" s="17" t="s">
-        <v>2061</v>
+        <v>2041</v>
       </c>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
@@ -15959,10 +15964,10 @@
         <v>33</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>2089</v>
+        <v>2069</v>
       </c>
       <c r="C239" s="44" t="s">
-        <v>2062</v>
+        <v>2042</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -15983,23 +15988,23 @@
         <v>34</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>2090</v>
+        <v>2070</v>
       </c>
       <c r="C240" s="44"/>
       <c r="D240" s="16" t="s">
-        <v>2063</v>
+        <v>2043</v>
       </c>
       <c r="E240" s="16" t="s">
-        <v>2064</v>
+        <v>2044</v>
       </c>
       <c r="F240" s="16" t="s">
-        <v>2065</v>
+        <v>2045</v>
       </c>
       <c r="G240" s="16" t="s">
-        <v>2066</v>
+        <v>2046</v>
       </c>
       <c r="H240" s="16" t="s">
-        <v>2067</v>
+        <v>2047</v>
       </c>
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
@@ -16013,23 +16018,23 @@
         <v>34</v>
       </c>
       <c r="B241" s="45" t="s">
-        <v>2091</v>
+        <v>2071</v>
       </c>
       <c r="C241" s="46"/>
       <c r="D241" s="17" t="s">
-        <v>2068</v>
+        <v>2048</v>
       </c>
       <c r="E241" s="17" t="s">
-        <v>2069</v>
+        <v>2049</v>
       </c>
       <c r="F241" s="17" t="s">
-        <v>2070</v>
+        <v>2050</v>
       </c>
       <c r="G241" s="17" t="s">
-        <v>2071</v>
+        <v>2051</v>
       </c>
       <c r="H241" s="17" t="s">
-        <v>2072</v>
+        <v>2052</v>
       </c>
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
@@ -16043,23 +16048,23 @@
         <v>34</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>2092</v>
+        <v>2072</v>
       </c>
       <c r="C242" s="44"/>
       <c r="D242" s="16" t="s">
-        <v>2073</v>
+        <v>2053</v>
       </c>
       <c r="E242" s="16" t="s">
-        <v>2074</v>
+        <v>2054</v>
       </c>
       <c r="F242" s="16" t="s">
-        <v>2075</v>
+        <v>2055</v>
       </c>
       <c r="G242" s="16" t="s">
-        <v>2076</v>
+        <v>2056</v>
       </c>
       <c r="H242" s="16" t="s">
-        <v>2077</v>
+        <v>2057</v>
       </c>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
@@ -16073,7 +16078,7 @@
         <v>33</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>2245</v>
+        <v>2225</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -16095,7 +16100,7 @@
         <v>34</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>2246</v>
+        <v>2226</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="3" t="s">
@@ -16155,7 +16160,7 @@
         <v>34</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>2247</v>
+        <v>2227</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="3" t="s">
@@ -16185,7 +16190,7 @@
         <v>34</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>2248</v>
+        <v>2228</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="3" t="s">
@@ -16825,7 +16830,7 @@
         <v>660</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>2097</v>
+        <v>2077</v>
       </c>
       <c r="I269" s="2"/>
       <c r="J269" s="6"/>
@@ -17811,7 +17816,7 @@
         <v>33</v>
       </c>
       <c r="B297" s="35" t="s">
-        <v>2249</v>
+        <v>2229</v>
       </c>
       <c r="C297" s="36"/>
       <c r="D297" s="36"/>
@@ -18081,7 +18086,7 @@
         <v>33</v>
       </c>
       <c r="B305" s="18" t="s">
-        <v>2250</v>
+        <v>2230</v>
       </c>
       <c r="C305" s="19"/>
       <c r="D305" s="19"/>
@@ -18199,7 +18204,7 @@
         <v>33</v>
       </c>
       <c r="B309" s="18" t="s">
-        <v>2251</v>
+        <v>2231</v>
       </c>
       <c r="C309" s="19"/>
       <c r="D309" s="19"/>
@@ -18253,7 +18258,7 @@
         <v>33</v>
       </c>
       <c r="B311" s="18" t="s">
-        <v>2252</v>
+        <v>2232</v>
       </c>
       <c r="C311" s="19"/>
       <c r="D311" s="19"/>
@@ -18275,7 +18280,7 @@
         <v>34</v>
       </c>
       <c r="B312" s="20" t="s">
-        <v>2253</v>
+        <v>2233</v>
       </c>
       <c r="C312" s="21"/>
       <c r="D312" s="22" t="s">
@@ -18361,7 +18366,7 @@
         <v>33</v>
       </c>
       <c r="B315" s="18" t="s">
-        <v>2254</v>
+        <v>2234</v>
       </c>
       <c r="C315" s="19"/>
       <c r="D315" s="19"/>
@@ -18413,7 +18418,7 @@
         <v>33</v>
       </c>
       <c r="B317" s="18" t="s">
-        <v>2255</v>
+        <v>2235</v>
       </c>
       <c r="C317" s="19"/>
       <c r="D317" s="19"/>
@@ -18465,7 +18470,7 @@
         <v>33</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>2256</v>
+        <v>2236</v>
       </c>
       <c r="C319" s="19"/>
       <c r="D319" s="19"/>
@@ -18599,7 +18604,7 @@
         <v>33</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>2257</v>
+        <v>2237</v>
       </c>
       <c r="C324" s="19"/>
       <c r="D324" s="19"/>
@@ -18847,7 +18852,7 @@
         <v>33</v>
       </c>
       <c r="B332" s="35" t="s">
-        <v>2259</v>
+        <v>2239</v>
       </c>
       <c r="C332" s="36"/>
       <c r="D332" s="36"/>
@@ -18873,19 +18878,19 @@
       </c>
       <c r="C333" s="27"/>
       <c r="D333" s="28" t="s">
-        <v>2258</v>
+        <v>2238</v>
       </c>
       <c r="E333" s="28" t="s">
-        <v>2260</v>
+        <v>2240</v>
       </c>
       <c r="F333" s="28" t="s">
-        <v>2261</v>
+        <v>2241</v>
       </c>
       <c r="G333" s="28" t="s">
-        <v>2262</v>
+        <v>2242</v>
       </c>
       <c r="H333" s="28" t="s">
-        <v>2263</v>
+        <v>2243</v>
       </c>
       <c r="I333" s="2"/>
       <c r="J333" s="6"/>
@@ -18899,7 +18904,7 @@
         <v>34</v>
       </c>
       <c r="B334" s="23" t="s">
-        <v>2264</v>
+        <v>2244</v>
       </c>
       <c r="C334" s="24"/>
       <c r="D334" s="25" t="s">
@@ -18959,7 +18964,7 @@
         <v>33</v>
       </c>
       <c r="B336" s="35" t="s">
-        <v>2265</v>
+        <v>2245</v>
       </c>
       <c r="C336" s="36"/>
       <c r="D336" s="36"/>
@@ -19041,7 +19046,7 @@
         <v>33</v>
       </c>
       <c r="B339" s="35" t="s">
-        <v>2266</v>
+        <v>2246</v>
       </c>
       <c r="C339" s="36"/>
       <c r="D339" s="36"/>
@@ -19067,19 +19072,19 @@
       </c>
       <c r="C340" s="37"/>
       <c r="D340" s="25" t="s">
-        <v>2267</v>
+        <v>2247</v>
       </c>
       <c r="E340" s="25" t="s">
-        <v>2268</v>
+        <v>2248</v>
       </c>
       <c r="F340" s="25" t="s">
-        <v>2269</v>
+        <v>2249</v>
       </c>
       <c r="G340" s="25" t="s">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="H340" s="25" t="s">
-        <v>2271</v>
+        <v>2251</v>
       </c>
       <c r="I340" s="2"/>
       <c r="J340" s="6"/>
@@ -19097,19 +19102,19 @@
       </c>
       <c r="C341" s="29"/>
       <c r="D341" s="25" t="s">
-        <v>2272</v>
+        <v>2252</v>
       </c>
       <c r="E341" s="25" t="s">
-        <v>2273</v>
+        <v>2253</v>
       </c>
       <c r="F341" s="25" t="s">
-        <v>2274</v>
+        <v>2254</v>
       </c>
       <c r="G341" s="25" t="s">
-        <v>2275</v>
+        <v>2255</v>
       </c>
       <c r="H341" s="25" t="s">
-        <v>2276</v>
+        <v>2256</v>
       </c>
       <c r="I341" s="2"/>
       <c r="J341" s="6"/>
@@ -19127,19 +19132,19 @@
       </c>
       <c r="C342" s="37"/>
       <c r="D342" s="25" t="s">
-        <v>2277</v>
+        <v>2257</v>
       </c>
       <c r="E342" s="25" t="s">
-        <v>2278</v>
+        <v>2258</v>
       </c>
       <c r="F342" s="25" t="s">
-        <v>2279</v>
+        <v>2259</v>
       </c>
       <c r="G342" s="25" t="s">
-        <v>2280</v>
+        <v>2260</v>
       </c>
       <c r="H342" s="25" t="s">
-        <v>2281</v>
+        <v>2261</v>
       </c>
       <c r="I342" s="2"/>
       <c r="J342" s="6"/>
@@ -19393,7 +19398,7 @@
         <v>32</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>2282</v>
+        <v>2262</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="3" t="s">
@@ -19553,7 +19558,7 @@
         <v>89</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>2283</v>
+        <v>2263</v>
       </c>
       <c r="I354" s="3" t="s">
         <v>91</v>
@@ -20005,7 +20010,7 @@
         <v>32</v>
       </c>
       <c r="B367" s="26" t="s">
-        <v>2284</v>
+        <v>2264</v>
       </c>
       <c r="C367" s="29" t="s">
         <v>1088</v>
@@ -20385,7 +20390,7 @@
         <v>33</v>
       </c>
       <c r="B379" s="18" t="s">
-        <v>2285</v>
+        <v>2265</v>
       </c>
       <c r="C379" s="19"/>
       <c r="D379" s="19"/>
@@ -20411,22 +20416,22 @@
       </c>
       <c r="C380" s="24"/>
       <c r="D380" s="25" t="s">
-        <v>2286</v>
+        <v>2266</v>
       </c>
       <c r="E380" s="25" t="s">
-        <v>2289</v>
+        <v>2269</v>
       </c>
       <c r="F380" s="25" t="s">
-        <v>2287</v>
+        <v>2267</v>
       </c>
       <c r="G380" s="25" t="s">
-        <v>2288</v>
+        <v>2268</v>
       </c>
       <c r="H380" s="25" t="s">
-        <v>2290</v>
+        <v>2270</v>
       </c>
       <c r="I380" s="25" t="s">
-        <v>2289</v>
+        <v>2269</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
@@ -20471,7 +20476,7 @@
         <v>33</v>
       </c>
       <c r="B382" s="18" t="s">
-        <v>2291</v>
+        <v>2271</v>
       </c>
       <c r="C382" s="19"/>
       <c r="D382" s="19"/>
@@ -20557,7 +20562,7 @@
         <v>33</v>
       </c>
       <c r="B385" s="18" t="s">
-        <v>2292</v>
+        <v>2272</v>
       </c>
       <c r="C385" s="19" t="s">
         <v>944</v>
@@ -20613,7 +20618,7 @@
         <v>33</v>
       </c>
       <c r="B387" s="18" t="s">
-        <v>2293</v>
+        <v>2273</v>
       </c>
       <c r="C387" s="19" t="s">
         <v>945</v>
@@ -20733,7 +20738,7 @@
         <v>34</v>
       </c>
       <c r="B391" s="23" t="s">
-        <v>2294</v>
+        <v>2274</v>
       </c>
       <c r="C391" s="24"/>
       <c r="D391" s="25" t="s">
@@ -20765,7 +20770,7 @@
         <v>33</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2295</v>
+        <v>2275</v>
       </c>
       <c r="C392" s="19" t="s">
         <v>946</v>
@@ -20853,7 +20858,7 @@
         <v>32</v>
       </c>
       <c r="B395" s="38" t="s">
-        <v>2296</v>
+        <v>2276</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" s="38" t="s">
@@ -21033,7 +21038,7 @@
         <v>32</v>
       </c>
       <c r="B400" s="39" t="s">
-        <v>2297</v>
+        <v>2277</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="39" t="s">
@@ -21141,7 +21146,7 @@
         <v>32</v>
       </c>
       <c r="B403" s="38" t="s">
-        <v>2311</v>
+        <v>2291</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" s="38" t="s">
@@ -21177,7 +21182,7 @@
         <v>32</v>
       </c>
       <c r="B404" s="39" t="s">
-        <v>2310</v>
+        <v>2290</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="39" t="s">
@@ -21213,7 +21218,7 @@
         <v>32</v>
       </c>
       <c r="B405" s="38" t="s">
-        <v>2298</v>
+        <v>2278</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="38" t="s">
@@ -21285,7 +21290,7 @@
         <v>32</v>
       </c>
       <c r="B407" s="38" t="s">
-        <v>2309</v>
+        <v>2289</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" s="38" t="s">
@@ -21321,7 +21326,7 @@
         <v>32</v>
       </c>
       <c r="B408" s="39" t="s">
-        <v>2308</v>
+        <v>2288</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="39" t="s">
@@ -21361,22 +21366,22 @@
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="3" t="s">
-        <v>2300</v>
+        <v>2280</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>2305</v>
+        <v>2285</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>2306</v>
+        <v>2286</v>
       </c>
       <c r="G409" s="3" t="s">
-        <v>2301</v>
+        <v>2281</v>
       </c>
       <c r="H409" s="3" t="s">
-        <v>2307</v>
+        <v>2287</v>
       </c>
       <c r="I409" s="3" t="s">
-        <v>2305</v>
+        <v>2285</v>
       </c>
       <c r="J409" s="13" t="s">
         <v>10</v>
@@ -21733,7 +21738,7 @@
         <v>244</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>2313</v>
+        <v>2293</v>
       </c>
       <c r="I419" s="3" t="s">
         <v>237</v>
@@ -21796,10 +21801,10 @@
         <v>207</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>2304</v>
+        <v>2284</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>2312</v>
+        <v>2292</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>249</v>
@@ -21825,23 +21830,23 @@
         <v>32</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>2303</v>
+        <v>2283</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" s="3" t="s">
         <v>250</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>2314</v>
+        <v>2294</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>2299</v>
+        <v>2279</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>255</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>2302</v>
+        <v>2282</v>
       </c>
       <c r="I422" s="3" t="s">
         <v>256</v>
@@ -21861,26 +21866,26 @@
         <v>32</v>
       </c>
       <c r="B423" s="51" t="s">
-        <v>2372</v>
+        <v>2352</v>
       </c>
       <c r="C423" s="49"/>
       <c r="D423" s="38" t="s">
-        <v>2315</v>
+        <v>2295</v>
       </c>
       <c r="E423" s="38" t="s">
-        <v>2316</v>
+        <v>2296</v>
       </c>
       <c r="F423" s="38" t="s">
-        <v>2317</v>
+        <v>2297</v>
       </c>
       <c r="G423" s="38" t="s">
-        <v>2318</v>
+        <v>2298</v>
       </c>
       <c r="H423" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I423" s="38" t="s">
-        <v>2317</v>
+        <v>2297</v>
       </c>
       <c r="J423" s="11" t="s">
         <v>11</v>
@@ -21897,26 +21902,26 @@
         <v>32</v>
       </c>
       <c r="B424" s="52" t="s">
-        <v>2373</v>
+        <v>2353</v>
       </c>
       <c r="C424" s="50"/>
       <c r="D424" s="39" t="s">
-        <v>2320</v>
+        <v>2300</v>
       </c>
       <c r="E424" s="39" t="s">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="F424" s="39" t="s">
-        <v>2322</v>
+        <v>2302</v>
       </c>
       <c r="G424" s="39" t="s">
-        <v>2323</v>
+        <v>2303</v>
       </c>
       <c r="H424" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I424" s="39" t="s">
-        <v>2322</v>
+        <v>2302</v>
       </c>
       <c r="J424" s="11" t="s">
         <v>11</v>
@@ -21933,26 +21938,26 @@
         <v>32</v>
       </c>
       <c r="B425" s="51" t="s">
-        <v>2374</v>
+        <v>2354</v>
       </c>
       <c r="C425" s="49"/>
       <c r="D425" s="38" t="s">
-        <v>2324</v>
+        <v>2304</v>
       </c>
       <c r="E425" s="38" t="s">
-        <v>2325</v>
+        <v>2305</v>
       </c>
       <c r="F425" s="38" t="s">
-        <v>2326</v>
+        <v>2306</v>
       </c>
       <c r="G425" s="38" t="s">
-        <v>2327</v>
+        <v>2307</v>
       </c>
       <c r="H425" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I425" s="38" t="s">
-        <v>2327</v>
+        <v>2307</v>
       </c>
       <c r="J425" s="11" t="s">
         <v>11</v>
@@ -21969,26 +21974,26 @@
         <v>32</v>
       </c>
       <c r="B426" s="52" t="s">
-        <v>2375</v>
+        <v>2355</v>
       </c>
       <c r="C426" s="50"/>
       <c r="D426" s="39" t="s">
-        <v>2328</v>
+        <v>2308</v>
       </c>
       <c r="E426" s="39" t="s">
-        <v>2329</v>
+        <v>2309</v>
       </c>
       <c r="F426" s="39" t="s">
-        <v>2330</v>
+        <v>2310</v>
       </c>
       <c r="G426" s="39" t="s">
-        <v>2331</v>
+        <v>2311</v>
       </c>
       <c r="H426" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I426" s="39" t="s">
-        <v>2329</v>
+        <v>2309</v>
       </c>
       <c r="J426" s="11" t="s">
         <v>11</v>
@@ -22005,26 +22010,26 @@
         <v>32</v>
       </c>
       <c r="B427" s="51" t="s">
-        <v>2376</v>
+        <v>2356</v>
       </c>
       <c r="C427" s="49"/>
       <c r="D427" s="38" t="s">
-        <v>2332</v>
+        <v>2312</v>
       </c>
       <c r="E427" s="38" t="s">
-        <v>2333</v>
+        <v>2313</v>
       </c>
       <c r="F427" s="38" t="s">
-        <v>2334</v>
+        <v>2314</v>
       </c>
       <c r="G427" s="38" t="s">
-        <v>2335</v>
+        <v>2315</v>
       </c>
       <c r="H427" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I427" s="38" t="s">
-        <v>2334</v>
+        <v>2314</v>
       </c>
       <c r="J427" s="11" t="s">
         <v>11</v>
@@ -22041,26 +22046,26 @@
         <v>32</v>
       </c>
       <c r="B428" s="52" t="s">
-        <v>2377</v>
+        <v>2357</v>
       </c>
       <c r="C428" s="50"/>
       <c r="D428" s="39" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="E428" s="39" t="s">
-        <v>2337</v>
+        <v>2317</v>
       </c>
       <c r="F428" s="39" t="s">
-        <v>2338</v>
+        <v>2318</v>
       </c>
       <c r="G428" s="39" t="s">
-        <v>2339</v>
+        <v>2319</v>
       </c>
       <c r="H428" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I428" s="39" t="s">
-        <v>2338</v>
+        <v>2318</v>
       </c>
       <c r="J428" s="11" t="s">
         <v>11</v>
@@ -22077,26 +22082,26 @@
         <v>32</v>
       </c>
       <c r="B429" s="51" t="s">
-        <v>2378</v>
+        <v>2358</v>
       </c>
       <c r="C429" s="49"/>
       <c r="D429" s="38" t="s">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="E429" s="38" t="s">
-        <v>2341</v>
+        <v>2321</v>
       </c>
       <c r="F429" s="38" t="s">
-        <v>2342</v>
+        <v>2322</v>
       </c>
       <c r="G429" s="38" t="s">
-        <v>2343</v>
+        <v>2323</v>
       </c>
       <c r="H429" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I429" s="38" t="s">
-        <v>2343</v>
+        <v>2323</v>
       </c>
       <c r="J429" s="11" t="s">
         <v>11</v>
@@ -22113,26 +22118,26 @@
         <v>32</v>
       </c>
       <c r="B430" s="52" t="s">
-        <v>2379</v>
+        <v>2359</v>
       </c>
       <c r="C430" s="50"/>
       <c r="D430" s="39" t="s">
-        <v>2344</v>
+        <v>2324</v>
       </c>
       <c r="E430" s="39" t="s">
-        <v>2345</v>
+        <v>2325</v>
       </c>
       <c r="F430" s="39" t="s">
-        <v>2346</v>
+        <v>2326</v>
       </c>
       <c r="G430" s="39" t="s">
-        <v>2347</v>
+        <v>2327</v>
       </c>
       <c r="H430" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I430" s="39" t="s">
-        <v>2344</v>
+        <v>2324</v>
       </c>
       <c r="J430" s="11" t="s">
         <v>11</v>
@@ -22149,26 +22154,26 @@
         <v>32</v>
       </c>
       <c r="B431" s="51" t="s">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="C431" s="49"/>
       <c r="D431" s="38" t="s">
-        <v>2348</v>
+        <v>2328</v>
       </c>
       <c r="E431" s="38" t="s">
-        <v>2349</v>
+        <v>2329</v>
       </c>
       <c r="F431" s="38" t="s">
-        <v>2350</v>
+        <v>2330</v>
       </c>
       <c r="G431" s="38" t="s">
-        <v>2351</v>
+        <v>2331</v>
       </c>
       <c r="H431" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I431" s="38" t="s">
-        <v>2348</v>
+        <v>2328</v>
       </c>
       <c r="J431" s="11" t="s">
         <v>11</v>
@@ -22185,26 +22190,26 @@
         <v>32</v>
       </c>
       <c r="B432" s="52" t="s">
-        <v>2381</v>
+        <v>2361</v>
       </c>
       <c r="C432" s="50"/>
       <c r="D432" s="39" t="s">
-        <v>2352</v>
+        <v>2332</v>
       </c>
       <c r="E432" s="39" t="s">
-        <v>2353</v>
+        <v>2333</v>
       </c>
       <c r="F432" s="39" t="s">
-        <v>2354</v>
+        <v>2334</v>
       </c>
       <c r="G432" s="39" t="s">
-        <v>2355</v>
+        <v>2335</v>
       </c>
       <c r="H432" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I432" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="J432" s="11" t="s">
         <v>11</v>
@@ -22221,26 +22226,26 @@
         <v>32</v>
       </c>
       <c r="B433" s="51" t="s">
-        <v>2382</v>
+        <v>2362</v>
       </c>
       <c r="C433" s="49"/>
       <c r="D433" s="38" t="s">
-        <v>2356</v>
+        <v>2336</v>
       </c>
       <c r="E433" s="38" t="s">
-        <v>2357</v>
+        <v>2337</v>
       </c>
       <c r="F433" s="38" t="s">
-        <v>2358</v>
+        <v>2338</v>
       </c>
       <c r="G433" s="38" t="s">
-        <v>2359</v>
+        <v>2339</v>
       </c>
       <c r="H433" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I433" s="38" t="s">
-        <v>2359</v>
+        <v>2339</v>
       </c>
       <c r="J433" s="11" t="s">
         <v>11</v>
@@ -22257,26 +22262,26 @@
         <v>32</v>
       </c>
       <c r="B434" s="52" t="s">
-        <v>2383</v>
+        <v>2363</v>
       </c>
       <c r="C434" s="50"/>
       <c r="D434" s="39" t="s">
-        <v>2360</v>
+        <v>2340</v>
       </c>
       <c r="E434" s="39" t="s">
-        <v>2361</v>
+        <v>2341</v>
       </c>
       <c r="F434" s="39" t="s">
-        <v>2362</v>
+        <v>2342</v>
       </c>
       <c r="G434" s="39" t="s">
-        <v>2363</v>
+        <v>2343</v>
       </c>
       <c r="H434" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I434" s="39" t="s">
-        <v>2361</v>
+        <v>2341</v>
       </c>
       <c r="J434" s="11" t="s">
         <v>11</v>
@@ -22293,26 +22298,26 @@
         <v>32</v>
       </c>
       <c r="B435" s="51" t="s">
-        <v>2384</v>
+        <v>2364</v>
       </c>
       <c r="C435" s="49"/>
       <c r="D435" s="38" t="s">
-        <v>2364</v>
+        <v>2344</v>
       </c>
       <c r="E435" s="38" t="s">
-        <v>2365</v>
+        <v>2345</v>
       </c>
       <c r="F435" s="38" t="s">
-        <v>2366</v>
+        <v>2346</v>
       </c>
       <c r="G435" s="38" t="s">
-        <v>2367</v>
+        <v>2347</v>
       </c>
       <c r="H435" s="38" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I435" s="38" t="s">
-        <v>2365</v>
+        <v>2345</v>
       </c>
       <c r="J435" s="11" t="s">
         <v>11</v>
@@ -22329,26 +22334,26 @@
         <v>32</v>
       </c>
       <c r="B436" s="52" t="s">
-        <v>2385</v>
+        <v>2365</v>
       </c>
       <c r="C436" s="50"/>
       <c r="D436" s="39" t="s">
-        <v>2368</v>
+        <v>2348</v>
       </c>
       <c r="E436" s="39" t="s">
-        <v>2369</v>
+        <v>2349</v>
       </c>
       <c r="F436" s="39" t="s">
-        <v>2370</v>
+        <v>2350</v>
       </c>
       <c r="G436" s="39" t="s">
-        <v>2371</v>
+        <v>2351</v>
       </c>
       <c r="H436" s="39" t="s">
-        <v>2319</v>
+        <v>2299</v>
       </c>
       <c r="I436" s="39" t="s">
-        <v>2368</v>
+        <v>2348</v>
       </c>
       <c r="J436" s="11" t="s">
         <v>11</v>
@@ -22365,7 +22370,7 @@
         <v>33</v>
       </c>
       <c r="B437" s="40" t="s">
-        <v>2438</v>
+        <v>2418</v>
       </c>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
@@ -22387,20 +22392,20 @@
         <v>34</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2401</v>
+        <v>2381</v>
       </c>
       <c r="C438" s="40"/>
       <c r="D438" s="54" t="s">
-        <v>2386</v>
+        <v>2366</v>
       </c>
       <c r="E438" s="54" t="s">
-        <v>2387</v>
+        <v>2367</v>
       </c>
       <c r="F438" s="54" t="s">
-        <v>2388</v>
+        <v>2368</v>
       </c>
       <c r="G438" s="54" t="s">
-        <v>2388</v>
+        <v>2420</v>
       </c>
       <c r="H438" s="54" t="s">
         <v>1920</v>
@@ -22417,20 +22422,20 @@
         <v>34</v>
       </c>
       <c r="B439" s="55" t="s">
-        <v>2402</v>
+        <v>2382</v>
       </c>
       <c r="C439" s="40"/>
       <c r="D439" s="55" t="s">
-        <v>2389</v>
+        <v>2369</v>
       </c>
       <c r="E439" s="55" t="s">
-        <v>2390</v>
+        <v>2370</v>
       </c>
       <c r="F439" s="55" t="s">
-        <v>2391</v>
+        <v>2371</v>
       </c>
       <c r="G439" s="55" t="s">
-        <v>2392</v>
+        <v>2372</v>
       </c>
       <c r="H439" s="55" t="s">
         <v>1920</v>
@@ -22447,20 +22452,20 @@
         <v>34</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2403</v>
+        <v>2383</v>
       </c>
       <c r="C440" s="40"/>
       <c r="D440" s="54" t="s">
-        <v>2393</v>
+        <v>2373</v>
       </c>
       <c r="E440" s="54" t="s">
-        <v>2394</v>
+        <v>2374</v>
       </c>
       <c r="F440" s="54" t="s">
-        <v>2395</v>
+        <v>2375</v>
       </c>
       <c r="G440" s="54" t="s">
-        <v>2396</v>
+        <v>2376</v>
       </c>
       <c r="H440" s="54" t="s">
         <v>1920</v>
@@ -22477,20 +22482,20 @@
         <v>34</v>
       </c>
       <c r="B441" s="55" t="s">
-        <v>1993</v>
+        <v>1974</v>
       </c>
       <c r="C441" s="40"/>
       <c r="D441" s="55" t="s">
-        <v>2397</v>
+        <v>2377</v>
       </c>
       <c r="E441" s="55" t="s">
-        <v>2398</v>
+        <v>2378</v>
       </c>
       <c r="F441" s="55" t="s">
-        <v>2399</v>
+        <v>2379</v>
       </c>
       <c r="G441" s="55" t="s">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="H441" s="55" t="s">
         <v>1920</v>
@@ -22507,7 +22512,7 @@
         <v>33</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>2439</v>
+        <v>2419</v>
       </c>
       <c r="C442" s="40"/>
       <c r="D442" s="40"/>
@@ -22529,20 +22534,20 @@
         <v>34</v>
       </c>
       <c r="B443" s="55" t="s">
-        <v>2434</v>
+        <v>2414</v>
       </c>
       <c r="C443" s="40"/>
       <c r="D443" s="55" t="s">
-        <v>2404</v>
+        <v>2384</v>
       </c>
       <c r="E443" s="55" t="s">
-        <v>2405</v>
+        <v>2385</v>
       </c>
       <c r="F443" s="55" t="s">
-        <v>2406</v>
+        <v>2386</v>
       </c>
       <c r="G443" s="55" t="s">
-        <v>2407</v>
+        <v>2387</v>
       </c>
       <c r="H443" s="55" t="s">
         <v>1920</v>
@@ -22559,20 +22564,20 @@
         <v>34</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2435</v>
+        <v>2415</v>
       </c>
       <c r="C444" s="40"/>
       <c r="D444" s="54" t="s">
-        <v>2408</v>
+        <v>2388</v>
       </c>
       <c r="E444" s="54" t="s">
-        <v>2409</v>
+        <v>2389</v>
       </c>
       <c r="F444" s="54" t="s">
-        <v>2410</v>
+        <v>2390</v>
       </c>
       <c r="G444" s="54" t="s">
-        <v>2411</v>
+        <v>2391</v>
       </c>
       <c r="H444" s="54" t="s">
         <v>1920</v>
@@ -22589,20 +22594,20 @@
         <v>34</v>
       </c>
       <c r="B445" s="55" t="s">
-        <v>2436</v>
+        <v>2416</v>
       </c>
       <c r="C445" s="40"/>
       <c r="D445" s="55" t="s">
-        <v>2412</v>
+        <v>2392</v>
       </c>
       <c r="E445" s="55" t="s">
-        <v>2413</v>
+        <v>2393</v>
       </c>
       <c r="F445" s="55" t="s">
-        <v>2414</v>
+        <v>2394</v>
       </c>
       <c r="G445" s="55" t="s">
-        <v>2415</v>
+        <v>2395</v>
       </c>
       <c r="H445" s="55" t="s">
         <v>1920</v>
@@ -22619,20 +22624,20 @@
         <v>34</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2437</v>
+        <v>2417</v>
       </c>
       <c r="C446" s="40"/>
       <c r="D446" s="54" t="s">
-        <v>2416</v>
+        <v>2396</v>
       </c>
       <c r="E446" s="54" t="s">
-        <v>2417</v>
+        <v>2397</v>
       </c>
       <c r="F446" s="54" t="s">
-        <v>2418</v>
+        <v>2398</v>
       </c>
       <c r="G446" s="54" t="s">
-        <v>2419</v>
+        <v>2399</v>
       </c>
       <c r="H446" s="54" t="s">
         <v>1920</v>
@@ -22649,7 +22654,7 @@
         <v>33</v>
       </c>
       <c r="B447" s="40" t="s">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="C447" s="40"/>
       <c r="D447" s="40"/>
@@ -22671,7 +22676,7 @@
         <v>34</v>
       </c>
       <c r="B448" s="40" t="s">
-        <v>1994</v>
+        <v>1975</v>
       </c>
       <c r="C448" s="40"/>
       <c r="D448" s="40" t="s">
@@ -22701,7 +22706,7 @@
         <v>34</v>
       </c>
       <c r="B449" s="40" t="s">
-        <v>2421</v>
+        <v>2401</v>
       </c>
       <c r="C449" s="40"/>
       <c r="D449" s="42" t="s">
@@ -22731,20 +22736,20 @@
         <v>34</v>
       </c>
       <c r="B450" s="40" t="s">
-        <v>2432</v>
+        <v>2412</v>
       </c>
       <c r="C450" s="40"/>
       <c r="D450" s="40" t="s">
-        <v>2422</v>
+        <v>2402</v>
       </c>
       <c r="E450" s="40" t="s">
-        <v>2433</v>
+        <v>2413</v>
       </c>
       <c r="F450" s="40" t="s">
-        <v>2423</v>
+        <v>2403</v>
       </c>
       <c r="G450" s="40" t="s">
-        <v>2424</v>
+        <v>2404</v>
       </c>
       <c r="H450" s="41" t="s">
         <v>1925</v>
@@ -22761,7 +22766,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="40" t="s">
-        <v>2430</v>
+        <v>2410</v>
       </c>
       <c r="C451" s="40"/>
       <c r="D451" s="42">
@@ -22791,7 +22796,7 @@
         <v>33</v>
       </c>
       <c r="B452" s="40" t="s">
-        <v>2425</v>
+        <v>2405</v>
       </c>
       <c r="C452" s="40"/>
       <c r="D452" s="40"/>
@@ -22813,20 +22818,20 @@
         <v>34</v>
       </c>
       <c r="B453" s="40" t="s">
-        <v>1995</v>
+        <v>1976</v>
       </c>
       <c r="C453" s="40"/>
       <c r="D453" s="40" t="s">
-        <v>2426</v>
+        <v>2406</v>
       </c>
       <c r="E453" s="40" t="s">
-        <v>2427</v>
+        <v>2407</v>
       </c>
       <c r="F453" s="40" t="s">
-        <v>2428</v>
+        <v>2408</v>
       </c>
       <c r="G453" s="40" t="s">
-        <v>2429</v>
+        <v>2409</v>
       </c>
       <c r="H453" s="41" t="s">
         <v>1925</v>
@@ -22843,7 +22848,7 @@
         <v>34</v>
       </c>
       <c r="B454" s="40" t="s">
-        <v>2431</v>
+        <v>2411</v>
       </c>
       <c r="C454" s="40"/>
       <c r="D454" s="42" t="s">
@@ -22873,7 +22878,7 @@
         <v>32</v>
       </c>
       <c r="B455" s="40" t="s">
-        <v>1996</v>
+        <v>1977</v>
       </c>
       <c r="C455" s="40"/>
       <c r="D455" s="40" t="s">
@@ -22907,7 +22912,7 @@
         <v>32</v>
       </c>
       <c r="B456" s="40" t="s">
-        <v>1997</v>
+        <v>1978</v>
       </c>
       <c r="C456" s="40"/>
       <c r="D456" s="40" t="s">
@@ -22941,7 +22946,7 @@
         <v>32</v>
       </c>
       <c r="B457" s="40" t="s">
-        <v>1998</v>
+        <v>1979</v>
       </c>
       <c r="C457" s="40"/>
       <c r="D457" s="40" t="s">
@@ -22975,7 +22980,7 @@
         <v>32</v>
       </c>
       <c r="B458" s="40" t="s">
-        <v>1999</v>
+        <v>1980</v>
       </c>
       <c r="C458" s="40"/>
       <c r="D458" s="40" t="s">
@@ -23009,7 +23014,7 @@
         <v>32</v>
       </c>
       <c r="B459" s="40" t="s">
-        <v>2000</v>
+        <v>1981</v>
       </c>
       <c r="C459" s="40"/>
       <c r="D459" s="40" t="s">
@@ -23043,7 +23048,7 @@
         <v>32</v>
       </c>
       <c r="B460" s="40" t="s">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="C460" s="40"/>
       <c r="D460" s="40" t="s">
@@ -23077,7 +23082,7 @@
         <v>32</v>
       </c>
       <c r="B461" s="40" t="s">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="C461" s="40"/>
       <c r="D461" s="40" t="s">
@@ -23111,7 +23116,7 @@
         <v>32</v>
       </c>
       <c r="B462" s="40" t="s">
-        <v>2003</v>
+        <v>1984</v>
       </c>
       <c r="C462" s="40"/>
       <c r="D462" s="40" t="s">
@@ -23140,12 +23145,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="90">
+    <row r="463" spans="1:12" ht="115.5">
       <c r="A463" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B463" s="40" t="s">
-        <v>1963</v>
+        <v>2421</v>
       </c>
       <c r="C463" s="40"/>
       <c r="D463" s="40"/>
@@ -23167,23 +23172,23 @@
         <v>34</v>
       </c>
       <c r="B464" s="40" t="s">
-        <v>2004</v>
+        <v>1985</v>
       </c>
       <c r="C464" s="40"/>
       <c r="D464" s="40" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E464" s="40" t="s">
         <v>1964</v>
       </c>
-      <c r="E464" s="40" t="s">
-        <v>1965</v>
-      </c>
       <c r="F464" s="40" t="s">
-        <v>1966</v>
+        <v>2422</v>
       </c>
       <c r="G464" s="40" t="s">
-        <v>1967</v>
+        <v>2423</v>
       </c>
       <c r="H464" s="41" t="s">
-        <v>1968</v>
+        <v>2424</v>
       </c>
       <c r="I464" s="2"/>
       <c r="J464" s="6"/>
@@ -23197,23 +23202,23 @@
         <v>34</v>
       </c>
       <c r="B465" s="40" t="s">
-        <v>2005</v>
+        <v>2427</v>
       </c>
       <c r="C465" s="40"/>
       <c r="D465" s="40" t="s">
-        <v>1969</v>
+        <v>1965</v>
       </c>
       <c r="E465" s="40" t="s">
-        <v>1970</v>
+        <v>2426</v>
       </c>
       <c r="F465" s="40" t="s">
-        <v>1971</v>
+        <v>2425</v>
       </c>
       <c r="G465" s="40" t="s">
-        <v>1972</v>
+        <v>1966</v>
       </c>
       <c r="H465" s="40" t="s">
-        <v>1973</v>
+        <v>1967</v>
       </c>
       <c r="I465" s="2"/>
       <c r="J465" s="6"/>
@@ -23227,20 +23232,20 @@
         <v>34</v>
       </c>
       <c r="B466" s="40" t="s">
-        <v>2006</v>
+        <v>1986</v>
       </c>
       <c r="C466" s="40"/>
       <c r="D466" s="40" t="s">
-        <v>1974</v>
+        <v>2428</v>
       </c>
       <c r="E466" s="40" t="s">
-        <v>1975</v>
+        <v>2429</v>
       </c>
       <c r="F466" s="40" t="s">
-        <v>1976</v>
+        <v>2430</v>
       </c>
       <c r="G466" s="40" t="s">
-        <v>1977</v>
+        <v>2431</v>
       </c>
       <c r="H466" s="41" t="s">
         <v>1934</v>
@@ -23252,12 +23257,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="64.5">
+    <row r="467" spans="1:12" ht="77.25">
       <c r="A467" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B467" s="40" t="s">
-        <v>1978</v>
+        <v>2432</v>
       </c>
       <c r="C467" s="40"/>
       <c r="D467" s="40"/>
@@ -23274,28 +23279,28 @@
       </c>
       <c r="L467" s="6"/>
     </row>
-    <row r="468" spans="1:12" ht="26.25">
+    <row r="468" spans="1:12" ht="51.75">
       <c r="A468" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B468" s="40" t="s">
-        <v>2007</v>
+        <v>1987</v>
       </c>
       <c r="C468" s="40"/>
       <c r="D468" s="40" t="s">
-        <v>1979</v>
+        <v>2433</v>
       </c>
       <c r="E468" s="40" t="s">
-        <v>1980</v>
+        <v>2434</v>
       </c>
       <c r="F468" s="40" t="s">
-        <v>1981</v>
+        <v>2435</v>
       </c>
       <c r="G468" s="40" t="s">
-        <v>1982</v>
+        <v>2436</v>
       </c>
       <c r="H468" s="41" t="s">
-        <v>1983</v>
+        <v>1968</v>
       </c>
       <c r="I468" s="2"/>
       <c r="J468" s="6"/>
@@ -23304,25 +23309,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:12">
+    <row r="469" spans="1:12" ht="26.25">
       <c r="A469" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B469" s="40" t="s">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="C469" s="40"/>
       <c r="D469" s="40" t="s">
-        <v>1984</v>
+        <v>2437</v>
       </c>
       <c r="E469" s="40" t="s">
-        <v>1985</v>
+        <v>2438</v>
       </c>
       <c r="F469" s="40" t="s">
-        <v>1986</v>
+        <v>2439</v>
       </c>
       <c r="G469" s="40" t="s">
-        <v>1987</v>
+        <v>2437</v>
       </c>
       <c r="H469" s="41" t="s">
         <v>1925</v>
@@ -23339,23 +23344,23 @@
         <v>34</v>
       </c>
       <c r="B470" s="40" t="s">
-        <v>2009</v>
+        <v>1989</v>
       </c>
       <c r="C470" s="40"/>
       <c r="D470" s="40" t="s">
-        <v>1988</v>
+        <v>1969</v>
       </c>
       <c r="E470" s="40" t="s">
-        <v>1989</v>
+        <v>1970</v>
       </c>
       <c r="F470" s="40" t="s">
-        <v>1990</v>
+        <v>1971</v>
       </c>
       <c r="G470" s="40" t="s">
-        <v>1991</v>
+        <v>1972</v>
       </c>
       <c r="H470" s="40" t="s">
-        <v>1992</v>
+        <v>1973</v>
       </c>
       <c r="I470" s="2"/>
       <c r="J470" s="6"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5EF6BB-A553-4CA8-9F53-B564C4522F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B536B8B4-F6D1-4E78-9DEA-1A7C61392397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="2440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3925" uniqueCount="2442">
   <si>
     <t>Option 1</t>
   </si>
@@ -5554,9 +5554,6 @@
     <t>0,56</t>
   </si>
   <si>
-    <t>On a mesuré la variation de la concentration d’ATP, de phosphocréatine au niveau du muscle et la concentration d’acide lactique dans le sang d’un sprinteur au cours d’un échauffement et d’une course de 10s environ. Le document suivant présente les résultats obtenus.</t>
-  </si>
-  <si>
     <t>À partir des données du document et des connaissances, on peut déduire que la régénération de l’ATP chez le sprinteur est assurée essentiellement par la voie de :</t>
   </si>
   <si>
@@ -5611,31 +5608,9 @@
     <t>Si l'on croise un individu [Y] issu du croisement 2 avec une souris [+], la descendance sera constituée d'individus avec les rapports suivants :</t>
   </si>
   <si>
-    <t>Le Phénylthiocarbamide (PTC), a un goût très amer pour certaines personnes et aucun goût pour d’autres.
-Dans une population, soumise à la loi de Hardy Weinberg, on a 70 % des individus sensibles au goût amer du PTC, sachant que la sensibilité à la PTC est liée à un allèle dominant S et l'insensibilité à cette substance est liée à l'allèle récessif s. On donne : \sqrt{0,20}\ =\ 0,45\ -\ \sqrt{0,30}\ =\ 0,55\ -\ \sqrt{0,70}\ =\ 0,83
-Quelles sont les fréquences des allèles et des génotypes dans cette population (on a considéré deux chiffres après la virgule) ?</t>
-  </si>
-  <si>
-    <t>Un laboratoire d’analyses effectue la réaction immunitaire suivante :
-1- 1ère étape : sur une lame de verre, on dépose une goutte de sérum dans chacune des cases :
-   - case 1 : sérum d’un animal atteint de la mononucléose infectieuse.
-   - case 2 : sérum d’un animal non atteint.
-   - case 3 : sérum de monsieur A.
-2- 2ème étape : on ajoute dans chacune de ces cases la même quantité d’hématies de cheval infectées par le virus de la mononucléose et présentant des antigènes du virus à leur surface.
-3- 3ème étape : on observe la lame afin de rechercher si les hématies de cheval ont été agglutinées par des anticorps du sérum. L’agglutination correspond à la formation de complexes immuns.</t>
-  </si>
-  <si>
     <t>A partir des résultats précédents, on peut dire que :</t>
   </si>
   <si>
-    <t>Le document suivant présente la réponse immunitaire contre le VIH.
-Parmi les suggestions suivantes, il y a deux suggestions vraies concernant l’analyse de ce graphique :
-1. L'augmentation du nombre de LT8 est la conséquence d'une immunité humorale.
-2. Les LT8 sont des LTc détruisant les LT4 infectés.
-3. Le VIH reste présent et inactif car le nombre de LT8 reste important.
-4. La diminution du nombre de LT8 est la conséquence d'une immunodéficience.</t>
-  </si>
-  <si>
     <t>Les deux suggestions vraies sont :</t>
   </si>
   <si>
@@ -5672,21 +5647,6 @@
     <t>3/4</t>
   </si>
   <si>
-    <t>f(s)=0.55 / f(S)=0.45 / f(ss)=0.30 / f(Ss)=0.49 / f(SS)=0.20.</t>
-  </si>
-  <si>
-    <t>f(s)=0.55 / f(S)=0.45 / f(ss)=0.30 / f(Ss)=0.20 / f(SS)=0.49.</t>
-  </si>
-  <si>
-    <t>f(s)=0.70 / f(S)=0.30 / f(ss)=0.30 / f(Ss)=0.20 / f(SS)=0.50.</t>
-  </si>
-  <si>
-    <t>f(s)=0.55 / f(S)=0.45 / f(ss)=0.30 / f(Ss)=0.68 / f(SS)=0.02.</t>
-  </si>
-  <si>
-    <t>f(s)=0.83 / f(S)=0.17 / f(ss)=0.70 / f(Ss)=0.44 / f(SS)=0.07.</t>
-  </si>
-  <si>
     <t>l’agglutination des hématies de cheval dans la case 3 résulte d’une réaction immunitaire dont les cellules effectrices sont les lymphocytes T cytotoxiques.</t>
   </si>
   <si>
@@ -6020,33 +5980,9 @@
     <t>Une base faible selon Brønsted est une solution susceptible de céder un proton H+</t>
   </si>
   <si>
-    <t>pKA1​=−logKA1​</t>
-  </si>
-  <si>
-    <t>pKA1​&gt;pKA2​</t>
-  </si>
-  <si>
-    <t>pKA1​&lt;pKA2​</t>
-  </si>
-  <si>
     <t>Aucune des affirmations ci-dessus n'est correcte.</t>
   </si>
   <si>
-    <t>v0​&gt;v1​</t>
-  </si>
-  <si>
-    <t>v0​&lt;v1​</t>
-  </si>
-  <si>
-    <t>v0​=v1​</t>
-  </si>
-  <si>
-    <t>v1​&lt;v2​</t>
-  </si>
-  <si>
-    <t>v0​&lt;vn​</t>
-  </si>
-  <si>
     <t>La valeur de la vitesse du pendule en position d'équilibre est :</t>
   </si>
   <si>
@@ -6090,9 +6026,6 @@
   </si>
   <si>
     <t>Le réactif limitant est :</t>
-  </si>
-  <si>
-    <t>Soit les temps de suivi de la réaction qui a lieu t0​&lt;t1​&lt;t2​&lt;tn​ et v0​,v1​,v2​,vn​ successivement les vitesses de réaction correspondantes, la proposition juste est :</t>
   </si>
   <si>
     <t>$r=50\text{ }\Omega$ ; $C=10\text{ }\mu\text{F}$</t>
@@ -7664,13 +7597,6 @@
     <t>$\ddot{x} - \frac{m}{K}x = 0$</t>
   </si>
   <si>
-    <t>Énoncé des questions Q37, Q38 et Q39 : 
-br&gt;On considère deux solutions aqueuses à 25∘C (Ke​=10−14) :
-&lt;br&gt;- une solution de méthylamine $CH_{3}​NH_{2}$​ (S1​) de pH=11,3 et de concentration $C_{1}​=10^{−1} mol⋅L−1$ ;
-&lt;br&gt;- une solution d'acide méthanoïque (HCOOH) (S2​) de concentration $C_{2}​=10^{−2} mol⋅L−1$ ; $pKA​(HCOOH/HCOO^{)}=3,74$. 
-&lt;br&gt;On donne : $10^{−2,7} ≈ 2⋅10^{−3}$ $\quad$ et $\quad$ log4=0,6.</t>
-  </si>
-  <si>
     <t>Une solution aqueuse est basique si $[H_{3}​O^{+}]&gt;[HO^{−}]$</t>
   </si>
   <si>
@@ -7680,25 +7606,7 @@
     <t>La méthylamine $CH_{3}​NH_{2}$​ est une base faible</t>
   </si>
   <si>
-    <t>$[HO^{−}]=10^{−}pH$+Ke​</t>
-  </si>
-  <si>
-    <t>KA1​=$[CH_{3}​NH_{3}^{+}​][CH_{3}​NH_{2}​]⋅[H_{3}​O^{+}]​$</t>
-  </si>
-  <si>
     <t>Concernant le couple Acide / $CH_{3}​NH_{2}$​, laquelle de ces propositions est juste ?</t>
-  </si>
-  <si>
-    <t>$CH_{3}​NH_{2}$​+HCOOH→$CH_{3}​NH_{3}^{+}$​+$HCOO^{−}$</t>
-  </si>
-  <si>
-    <t>$CH_{3}​NH_{2}$​+HCOOH→$CH_{3}​NH_{2}^{+}$​+$HCOO^{−}$</t>
-  </si>
-  <si>
-    <t>HCOOH+$CH_{3}​NH_{3}$​→$CH_{3}​NH_{2}^{+}$​+$HCOO^{−}$</t>
-  </si>
-  <si>
-    <t>$[HCOO^{−}]$=V1​+V2​C2​V2​​</t>
   </si>
   <si>
     <t>Énoncé des questions Q40, Q41 et Q42 : 
@@ -7714,16 +7622,118 @@
     <t>$2\text{K}_{(aq)}^{+} + \text{S}_2\text{O}_{8(aq)}^{2-} \rightarrow 2\text{SO}_{4(aq)}^{2-} + 2\text{K}_{(s)}$</t>
   </si>
   <si>
-    <t>$$\text{S}_2\text{O}_{8(aq)}^{2-} + \text{I}_{2(aq)} \rightarrow 2\text{I}_{(aq)}^{-} + 2\text{SO}_{4(aq)}^{2-}$$</t>
-  </si>
-  <si>
-    <t>$\text{I}_{2(aq)}$</t>
-  </si>
-  <si>
     <t>$\text{S}_2\text{O}_{8(aq)}^{2-}$</t>
   </si>
   <si>
-    <t>$\text{SO}_{4(aq)}^{2-}$</t>
+    <t>$K_{A1} = \frac{C_1 \cdot 10^{-pH} + K_e}{[HO^-]_{eq}}$</t>
+  </si>
+  <si>
+    <t>$[HCOO^-] = \frac{C_2 V_2}{V_1 + V_2}$</t>
+  </si>
+  <si>
+    <t>$pK_{A1} = \log K_{A1}$</t>
+  </si>
+  <si>
+    <t>$K_{A1} = \frac{(C_1 - [HO^-]_{eq})[H_3O^+]_{eq}}{[HO^-]_{eq}}$</t>
+  </si>
+  <si>
+    <t>$pK_{A1} &gt; pK_{A2}$</t>
+  </si>
+  <si>
+    <t>$pK_{A1} &lt; pK_{A2}$</t>
+  </si>
+  <si>
+    <t>$CH_3NH_2 + HCOOH \longrightarrow CH_3NH_2^+ + HCOO^-$</t>
+  </si>
+  <si>
+    <t>$CH_3NH_2 + HCOOH \longrightarrow CH_3NH_2^+ + HCOOH^-$</t>
+  </si>
+  <si>
+    <t>$HCOOH + CH_3NH_2^+ \longrightarrow CH_3NH_2 + HCOOH^-$</t>
+  </si>
+  <si>
+    <t>$\text{S}_2\text{O}_{8(aq)}^{2-} + \text{I}_{2(aq)} \rightarrow 2\text{I}_{(aq)}^{-} + 2\text{SO}_{4(aq)}^{2-}$</t>
+  </si>
+  <si>
+    <t>$Na^+_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$I^-_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$I_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$K^+_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$V_0 &gt; V_1$</t>
+  </si>
+  <si>
+    <t>$V_0 &lt; V_1$</t>
+  </si>
+  <si>
+    <t>$V_2 &gt; V_1$</t>
+  </si>
+  <si>
+    <t>Énoncé des questions Q37, Q38 et Q39 : 
+&lt;br&gt;On considère deux solutions aqueuses à 25∘C ($Ke​=10^{−14}$) :
+&lt;br&gt;- une solution de méthylamine $CH_{3}​NH_{2}$​ (S1​) de pH=11,3 et de concentration $C_{1}​=10^{−1} mol⋅L^{−1}$ ;
+&lt;br&gt;- une solution d'acide méthanoïque (HCOOH) (S2​) de concentration $C_{2}​=10^{−2} mol⋅L^{−1}$ ; $pKA_{2}​(HCOOH/HCOO^{−})=3,74$. 
+&lt;br&gt;On donne : $10^{−2,7} ≈ 2⋅10^{−3}$ $\quad$ et $\quad$ log4=0,6.</t>
+  </si>
+  <si>
+    <t>$V_0 &lt; V_\infty$</t>
+  </si>
+  <si>
+    <t>$V_2 &lt; V_\infty$</t>
+  </si>
+  <si>
+    <t>Soient les temps de suivi de la réaction qui a lieu $t_{0}$ ​&lt; $t_{1}$ &lt; $t_{2}$​&lt; $t_{\infty}$​ et  $v_{0}$​, $v_{1}$​, $v_{2}$ et $v_{\infty}$​ successivement les vitesses de réaction correspondantes, la proposition juste est :</t>
+  </si>
+  <si>
+    <t>On a mesuré la variation de la concentration d’ATP, de phosphocréatine au niveau du muscle et la concentration d’acide lactique dans le sang d’un sprinteur au cours d’un échauffement et d’une course de 10s environ. Le document suivant présente les résultats obtenus.
+&lt;br&gt;&lt;img src="/images/SVT2022F1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>Le Phénylthiocarbamide (PTC), a un goût très amer pour certaines personnes et aucun goût pour d’autres.
+Dans une population, soumise à la loi de Hardy Weinberg, on a 70 % des individus sensibles au goût amer du PTC, sachant que la sensibilité à la PTC est liée à un allèle dominant S et l'insensibilité à cette substance est liée à l'allèle récessif s. 
+&lt;br&gt;On donne : $\sqrt{0,20}\ =\ 0,45\$; $\quad$  $\sqrt{0,30}\ =\ 0,55\$; $\quad$ $\sqrt{0,70}\ =\ 0,83$
+Quelles sont les fréquences des allèles et des génotypes dans cette population (on a considéré deux chiffres après la virgule) ?</t>
+  </si>
+  <si>
+    <t>Un laboratoire d’analyses effectue la réaction immunitaire suivante :
+&lt;br&gt; 1ère étape : sur une lame de verre, on dépose une goutte de sérum dans chacune des cases :
+&lt;br&gt;   - case 1 : sérum d’un animal atteint de la mononucléose infectieuse.
+&lt;br&gt;   - case 2 : sérum d’un animal non atteint.
+&lt;br&gt;   - case 3 : sérum de monsieur A.
+&lt;br&gt; 2ème étape : on ajoute dans chacune de ces cases la même quantité d’hématies de cheval infectées par le virus de la mononucléose et présentant des antigènes du virus à leur surface.
+&lt;br&gt; 3ème étape : on observe la lame afin de rechercher si les hématies de cheval ont été agglutinées par des anticorps du sérum. L’agglutination correspond à la formation de complexes immuns.
+&lt;br&gt;&lt;img src="/images/SVT2022F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>f(s)=0.55 $\quad$ f(S)=0.45 $\quad$ f(ss)=0.30 $\quad$ f(Ss)=0.49 $\quad$ f(SS)=0.20.</t>
+  </si>
+  <si>
+    <t>f(s)=0.55 $\qud$ f(S)=0.45 $\quad$ f(ss)=0.30 $\quad$ f(Ss)=0.20 $\quad$ f(SS)=0.49.</t>
+  </si>
+  <si>
+    <t>f(s)=0.70 $\quad$ f(S)=0.30 $\quad$ f(ss)=0.30 $\quad$ f(Ss)=0.20 $\quad$ f(SS)=0.50.</t>
+  </si>
+  <si>
+    <t>f(s)=0.55 $\quad$ f(S)=0.45 $\quad$ f(ss)=0.30 $\quad$ f(Ss)=0.68 $\quad$ f(SS)=0.02.</t>
+  </si>
+  <si>
+    <t>f(s)=0.83 $\quad$ f(S)=0.17 $\quad$ f(ss)=0.70 $\quad$ f(Ss)=0.44 $\quad$ f(SS)=0.07.</t>
+  </si>
+  <si>
+    <t>Le document suivant présente la réponse immunitaire contre le VIH.
+&lt;br&gt;&lt;img src="/images/SVT2022F3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+Parmi les suggestions suivantes, il y a deux suggestions vraies concernant l’analyse de ce graphique :
+&lt;br&gt;1. L'augmentation du nombre de LT8 est la conséquence d'une immunité humorale.
+&lt;br&gt;2. Les LT8 sont des LTc détruisant les LT4 infectés.
+&lt;br&gt;3. Le VIH reste présent et inactif car le nombre de LT8 reste important.
+&lt;br&gt;4. La diminution du nombre de LT8 est la conséquence d'une immunodéficience.</t>
   </si>
 </sst>
 </file>
@@ -7933,7 +7943,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -8097,6 +8107,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8822,7 +8838,7 @@
         <v>32</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>2084</v>
+        <v>2066</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="32" t="s">
@@ -8858,7 +8874,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>2078</v>
+        <v>2060</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="32" t="s">
@@ -8894,7 +8910,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>2079</v>
+        <v>2061</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="32" t="s">
@@ -8966,7 +8982,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>2080</v>
+        <v>2062</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="32" t="s">
@@ -9038,7 +9054,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="32" t="s">
@@ -9074,7 +9090,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>2082</v>
+        <v>2064</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="32" t="s">
@@ -9110,7 +9126,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="32" t="s">
@@ -9146,7 +9162,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>2083</v>
+        <v>2065</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="32" t="s">
@@ -9182,7 +9198,7 @@
         <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2085</v>
+        <v>2067</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="2"/>
@@ -9204,11 +9220,11 @@
         <v>34</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2086</v>
+        <v>2068</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="3" t="s">
-        <v>2098</v>
+        <v>2080</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>666</v>
@@ -9300,7 +9316,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2087</v>
+        <v>2069</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -9322,7 +9338,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2088</v>
+        <v>2070</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="3" t="s">
@@ -9386,7 +9402,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2090</v>
+        <v>2072</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -9456,7 +9472,7 @@
         <v>698</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>2089</v>
+        <v>2071</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>695</v>
@@ -9472,7 +9488,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>2091</v>
+        <v>2073</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
@@ -9504,7 +9520,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2092</v>
+        <v>2074</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -9526,7 +9542,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2093</v>
+        <v>2075</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -9558,7 +9574,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>2094</v>
+        <v>2076</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
@@ -9590,7 +9606,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2099</v>
+        <v>2081</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -9612,7 +9628,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>2095</v>
+        <v>2077</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
@@ -9644,7 +9660,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>2096</v>
+        <v>2078</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
@@ -9676,7 +9692,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2097</v>
+        <v>2079</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -9698,7 +9714,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2100</v>
+        <v>2082</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="3" t="s">
@@ -9728,7 +9744,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>2101</v>
+        <v>2083</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="3" t="s">
@@ -9758,26 +9774,26 @@
         <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2102</v>
+        <v>2084</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="3" t="s">
-        <v>2103</v>
+        <v>2085</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2104</v>
+        <v>2086</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>2105</v>
+        <v>2087</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>2106</v>
+        <v>2088</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>2107</v>
+        <v>2089</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>2104</v>
+        <v>2086</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>9</v>
@@ -9794,7 +9810,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>2108</v>
+        <v>2090</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -9816,7 +9832,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>2109</v>
+        <v>2091</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
@@ -9848,7 +9864,7 @@
         <v>34</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2110</v>
+        <v>2092</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
@@ -9912,7 +9928,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2111</v>
+        <v>2093</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -9998,7 +10014,7 @@
         <v>33</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>2123</v>
+        <v>2105</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -10116,7 +10132,7 @@
         <v>33</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>2117</v>
+        <v>2099</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -10142,22 +10158,22 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="32" t="s">
-        <v>2118</v>
+        <v>2100</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>2119</v>
+        <v>2101</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>2120</v>
+        <v>2102</v>
       </c>
       <c r="G55" s="32" t="s">
-        <v>2121</v>
+        <v>2103</v>
       </c>
       <c r="H55" s="32" t="s">
-        <v>2122</v>
+        <v>2104</v>
       </c>
       <c r="I55" s="32" t="s">
-        <v>2119</v>
+        <v>2101</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
@@ -10266,7 +10282,7 @@
         <v>33</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>2116</v>
+        <v>2098</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -10384,7 +10400,7 @@
         <v>32</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>2115</v>
+        <v>2097</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="32" t="s">
@@ -10420,7 +10436,7 @@
         <v>33</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>2114</v>
+        <v>2096</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -10506,7 +10522,7 @@
         <v>33</v>
       </c>
       <c r="B67" s="32" t="s">
-        <v>2113</v>
+        <v>2095</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -10624,7 +10640,7 @@
         <v>33</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>2124</v>
+        <v>2106</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -10710,7 +10726,7 @@
         <v>33</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>2112</v>
+        <v>2094</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -10868,7 +10884,7 @@
         <v>32</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>2125</v>
+        <v>2107</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="3" t="s">
@@ -11012,7 +11028,7 @@
         <v>32</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>2126</v>
+        <v>2108</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="3" t="s">
@@ -11084,7 +11100,7 @@
         <v>32</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>2075</v>
+        <v>2057</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="3" t="s">
@@ -11156,7 +11172,7 @@
         <v>32</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2127</v>
+        <v>2109</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="3" t="s">
@@ -11228,7 +11244,7 @@
         <v>32</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>2128</v>
+        <v>2110</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="3" t="s">
@@ -11300,7 +11316,7 @@
         <v>32</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>2129</v>
+        <v>2111</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="3" t="s">
@@ -11336,7 +11352,7 @@
         <v>32</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>2130</v>
+        <v>2112</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="3" t="s">
@@ -11372,7 +11388,7 @@
         <v>32</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>2131</v>
+        <v>2113</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="3" t="s">
@@ -11876,7 +11892,7 @@
         <v>32</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>2132</v>
+        <v>2114</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="33" t="s">
@@ -11948,7 +11964,7 @@
         <v>32</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>2133</v>
+        <v>2115</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="33" t="s">
@@ -11984,7 +12000,7 @@
         <v>32</v>
       </c>
       <c r="B110" s="26" t="s">
-        <v>2134</v>
+        <v>2116</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="34" t="s">
@@ -12020,7 +12036,7 @@
         <v>32</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>2135</v>
+        <v>2117</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="33" t="s">
@@ -12056,7 +12072,7 @@
         <v>32</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>2136</v>
+        <v>2118</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="34" t="s">
@@ -12092,7 +12108,7 @@
         <v>32</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>2137</v>
+        <v>2119</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="33" t="s">
@@ -12128,7 +12144,7 @@
         <v>32</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>2138</v>
+        <v>2120</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="34" t="s">
@@ -12164,7 +12180,7 @@
         <v>32</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>2139</v>
+        <v>2121</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="33" t="s">
@@ -12200,7 +12216,7 @@
         <v>32</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>2140</v>
+        <v>2122</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="34" t="s">
@@ -12236,7 +12252,7 @@
         <v>33</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>2167</v>
+        <v>2149</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -12262,22 +12278,22 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="3" t="s">
-        <v>2141</v>
+        <v>2123</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>2142</v>
+        <v>2124</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>2143</v>
+        <v>2125</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>2144</v>
+        <v>2126</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>2145</v>
+        <v>2127</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>2144</v>
+        <v>2126</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
@@ -12354,7 +12370,7 @@
         <v>33</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>2168</v>
+        <v>2150</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -12440,7 +12456,7 @@
         <v>33</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>2146</v>
+        <v>2128</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -12526,7 +12542,7 @@
         <v>33</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>2147</v>
+        <v>2129</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -12730,7 +12746,7 @@
         <v>34</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>2148</v>
+        <v>2130</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
@@ -12762,7 +12778,7 @@
         <v>33</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>2169</v>
+        <v>2151</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -12788,7 +12804,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="3" t="s">
-        <v>2149</v>
+        <v>2131</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>819</v>
@@ -12816,26 +12832,26 @@
         <v>34</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2150</v>
+        <v>2132</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="3" t="s">
-        <v>2151</v>
+        <v>2133</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>2152</v>
+        <v>2134</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>2153</v>
+        <v>2135</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>2154</v>
+        <v>2136</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>2155</v>
+        <v>2137</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>2154</v>
+        <v>2136</v>
       </c>
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
@@ -12912,7 +12928,7 @@
         <v>33</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>2170</v>
+        <v>2152</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>837</v>
@@ -12940,22 +12956,22 @@
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="3" t="s">
-        <v>2156</v>
+        <v>2138</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>2157</v>
+        <v>2139</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>2158</v>
+        <v>2140</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>2159</v>
+        <v>2141</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>2160</v>
+        <v>2142</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>2158</v>
+        <v>2140</v>
       </c>
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
@@ -12975,7 +12991,7 @@
         <v>833</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>2161</v>
+        <v>2143</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>834</v>
@@ -13004,22 +13020,22 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="3" t="s">
-        <v>2162</v>
+        <v>2144</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>2163</v>
+        <v>2145</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>2164</v>
+        <v>2146</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>2165</v>
+        <v>2147</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>2166</v>
+        <v>2148</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>2163</v>
+        <v>2145</v>
       </c>
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
@@ -13032,7 +13048,7 @@
         <v>33</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>2172</v>
+        <v>2154</v>
       </c>
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
@@ -13150,7 +13166,7 @@
         <v>33</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>2173</v>
+        <v>2155</v>
       </c>
       <c r="C148" s="32"/>
       <c r="D148" s="32"/>
@@ -13268,7 +13284,7 @@
         <v>33</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>2174</v>
+        <v>2156</v>
       </c>
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
@@ -13354,7 +13370,7 @@
         <v>34</v>
       </c>
       <c r="B155" s="32" t="s">
-        <v>2171</v>
+        <v>2153</v>
       </c>
       <c r="C155" s="32"/>
       <c r="D155" s="32" t="s">
@@ -13418,7 +13434,7 @@
         <v>33</v>
       </c>
       <c r="B157" s="32" t="s">
-        <v>2175</v>
+        <v>2157</v>
       </c>
       <c r="C157" s="32"/>
       <c r="D157" s="2"/>
@@ -13504,7 +13520,7 @@
         <v>33</v>
       </c>
       <c r="B160" s="32" t="s">
-        <v>2176</v>
+        <v>2158</v>
       </c>
       <c r="C160" s="32"/>
       <c r="D160" s="32"/>
@@ -13622,7 +13638,7 @@
         <v>33</v>
       </c>
       <c r="B164" s="32" t="s">
-        <v>2177</v>
+        <v>2159</v>
       </c>
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
@@ -13964,7 +13980,7 @@
         <v>439</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>2178</v>
+        <v>2160</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>400</v>
@@ -14000,10 +14016,10 @@
         <v>405</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>2179</v>
+        <v>2161</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>2179</v>
+        <v>2161</v>
       </c>
       <c r="J175" s="13" t="s">
         <v>10</v>
@@ -14033,13 +14049,13 @@
         <v>408</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>2181</v>
+        <v>2163</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>2180</v>
+        <v>2162</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>2180</v>
+        <v>2162</v>
       </c>
       <c r="J176" s="13" t="s">
         <v>10</v>
@@ -14105,13 +14121,13 @@
         <v>416</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>2183</v>
+        <v>2165</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>2182</v>
+        <v>2164</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>2183</v>
+        <v>2165</v>
       </c>
       <c r="J178" s="13" t="s">
         <v>10</v>
@@ -14132,22 +14148,22 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="3" t="s">
-        <v>2193</v>
+        <v>2175</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>2192</v>
+        <v>2174</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>2191</v>
+        <v>2173</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>2190</v>
+        <v>2172</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>2189</v>
+        <v>2171</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>2191</v>
+        <v>2173</v>
       </c>
       <c r="J179" s="13" t="s">
         <v>10</v>
@@ -14168,22 +14184,22 @@
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="3" t="s">
-        <v>2185</v>
+        <v>2167</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>2184</v>
+        <v>2166</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>2186</v>
+        <v>2168</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>2187</v>
+        <v>2169</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>2188</v>
+        <v>2170</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>2185</v>
+        <v>2167</v>
       </c>
       <c r="J180" s="13" t="s">
         <v>10</v>
@@ -14249,7 +14265,7 @@
         <v>425</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>2194</v>
+        <v>2176</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>426</v>
@@ -14324,7 +14340,7 @@
         <v>434</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>2195</v>
+        <v>2177</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>409</v>
@@ -14360,7 +14376,7 @@
         <v>435</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>2196</v>
+        <v>2178</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>410</v>
@@ -14380,7 +14396,7 @@
         <v>32</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>2203</v>
+        <v>2185</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="3" t="s">
@@ -14393,10 +14409,10 @@
         <v>438</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>2198</v>
+        <v>2180</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>2197</v>
+        <v>2179</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>437</v>
@@ -14452,7 +14468,7 @@
         <v>32</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>2204</v>
+        <v>2186</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="3" t="s">
@@ -14495,16 +14511,16 @@
         <v>444</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>2199</v>
+        <v>2181</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>2200</v>
+        <v>2182</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>2201</v>
+        <v>2183</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>2202</v>
+        <v>2184</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>444</v>
@@ -14558,7 +14574,7 @@
         <v>32</v>
       </c>
       <c r="B191" s="48" t="s">
-        <v>2205</v>
+        <v>2187</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="31" t="s">
@@ -14796,7 +14812,7 @@
         <v>32</v>
       </c>
       <c r="B198" s="30" t="s">
-        <v>2206</v>
+        <v>2188</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="30" t="s">
@@ -14859,12 +14875,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="71.25">
+    <row r="200" spans="1:12" ht="99.75">
       <c r="A200" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B200" s="30" t="s">
-        <v>1815</v>
+        <v>2433</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -14886,23 +14902,23 @@
         <v>34</v>
       </c>
       <c r="B201" s="30" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="30" t="s">
+        <v>1816</v>
+      </c>
+      <c r="E201" s="30" t="s">
         <v>1817</v>
       </c>
-      <c r="E201" s="30" t="s">
+      <c r="F201" s="30" t="s">
         <v>1818</v>
       </c>
-      <c r="F201" s="30" t="s">
+      <c r="G201" s="30" t="s">
         <v>1819</v>
       </c>
-      <c r="G201" s="30" t="s">
+      <c r="H201" s="30" t="s">
         <v>1820</v>
-      </c>
-      <c r="H201" s="30" t="s">
-        <v>1821</v>
       </c>
       <c r="I201" s="2"/>
       <c r="J201" s="6"/>
@@ -14916,7 +14932,7 @@
         <v>33</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>2212</v>
+        <v>2194</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -14938,23 +14954,23 @@
         <v>34</v>
       </c>
       <c r="B203" s="31" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="31" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E203" s="31" t="s">
         <v>1823</v>
       </c>
-      <c r="E203" s="31" t="s">
+      <c r="F203" s="31" t="s">
         <v>1824</v>
       </c>
-      <c r="F203" s="31" t="s">
+      <c r="G203" s="31" t="s">
         <v>1825</v>
       </c>
-      <c r="G203" s="31" t="s">
+      <c r="H203" s="31" t="s">
         <v>1826</v>
-      </c>
-      <c r="H203" s="31" t="s">
-        <v>1827</v>
       </c>
       <c r="I203" s="2"/>
       <c r="J203" s="6"/>
@@ -14968,23 +14984,23 @@
         <v>32</v>
       </c>
       <c r="B204" s="30" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="47" t="s">
-        <v>2207</v>
+        <v>2189</v>
       </c>
       <c r="E204" s="47" t="s">
-        <v>2208</v>
+        <v>2190</v>
       </c>
       <c r="F204" s="47" t="s">
-        <v>2209</v>
+        <v>2191</v>
       </c>
       <c r="G204" s="47" t="s">
-        <v>2210</v>
+        <v>2192</v>
       </c>
       <c r="H204" s="47" t="s">
-        <v>2211</v>
+        <v>2193</v>
       </c>
       <c r="I204" s="2"/>
       <c r="J204" s="6" t="s">
@@ -15002,7 +15018,7 @@
         <v>33</v>
       </c>
       <c r="B205" s="31" t="s">
-        <v>2213</v>
+        <v>2195</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -15024,23 +15040,23 @@
         <v>34</v>
       </c>
       <c r="B206" s="31" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="31" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="E206" s="31" t="s">
-        <v>1840</v>
+        <v>1836</v>
       </c>
       <c r="F206" s="31" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="G206" s="31" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
       <c r="H206" s="31" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="I206" s="2"/>
       <c r="J206" s="6"/>
@@ -15054,23 +15070,23 @@
         <v>32</v>
       </c>
       <c r="B207" s="30" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="30" t="s">
-        <v>2214</v>
+        <v>2196</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>2215</v>
+        <v>2197</v>
       </c>
       <c r="F207" s="30" t="s">
-        <v>2216</v>
+        <v>2198</v>
       </c>
       <c r="G207" s="30" t="s">
-        <v>2217</v>
+        <v>2199</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>2218</v>
+        <v>2200</v>
       </c>
       <c r="I207" s="2"/>
       <c r="J207" s="6" t="s">
@@ -15088,20 +15104,20 @@
         <v>32</v>
       </c>
       <c r="B208" s="31" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="31" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="E208" s="31" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="F208" s="31" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="G208" s="31" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="H208" s="31" t="s">
         <v>971</v>
@@ -15122,7 +15138,7 @@
         <v>33</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>2219</v>
+        <v>2201</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -15144,23 +15160,23 @@
         <v>34</v>
       </c>
       <c r="B210" s="30" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="30" t="s">
-        <v>2220</v>
+        <v>2202</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>2221</v>
+        <v>2203</v>
       </c>
       <c r="F210" s="30" t="s">
-        <v>2222</v>
+        <v>2204</v>
       </c>
       <c r="G210" s="30" t="s">
-        <v>2223</v>
+        <v>2205</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>2224</v>
+        <v>2206</v>
       </c>
       <c r="I210" s="2"/>
       <c r="J210" s="6"/>
@@ -15169,28 +15185,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="128.25">
+    <row r="211" spans="1:12" ht="142.5">
       <c r="A211" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B211" s="31" t="s">
-        <v>1833</v>
+        <v>2434</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="31" t="s">
-        <v>1849</v>
+        <v>2436</v>
       </c>
       <c r="E211" s="31" t="s">
-        <v>1850</v>
+        <v>2437</v>
       </c>
       <c r="F211" s="31" t="s">
-        <v>1851</v>
+        <v>2438</v>
       </c>
       <c r="G211" s="31" t="s">
-        <v>1852</v>
+        <v>2439</v>
       </c>
       <c r="H211" s="31" t="s">
-        <v>1853</v>
+        <v>2440</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="6" t="s">
@@ -15203,12 +15219,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="228">
+    <row r="212" spans="1:12" ht="256.5">
       <c r="A212" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B212" s="30" t="s">
-        <v>1834</v>
+        <v>2435</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -15230,23 +15246,23 @@
         <v>34</v>
       </c>
       <c r="B213" s="30" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" s="30" t="s">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>1855</v>
+        <v>1846</v>
       </c>
       <c r="F213" s="30" t="s">
-        <v>1856</v>
+        <v>1847</v>
       </c>
       <c r="G213" s="30" t="s">
-        <v>1857</v>
+        <v>1848</v>
       </c>
       <c r="H213" s="30" t="s">
-        <v>1858</v>
+        <v>1849</v>
       </c>
       <c r="I213" s="2"/>
       <c r="J213" s="6"/>
@@ -15255,12 +15271,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="156.75">
+    <row r="214" spans="1:12" ht="185.25">
       <c r="A214" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B214" s="31" t="s">
-        <v>1836</v>
+        <v>2441</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -15282,14 +15298,14 @@
         <v>34</v>
       </c>
       <c r="B215" s="31" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="31" t="s">
         <v>1192</v>
       </c>
       <c r="E215" s="31" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="F215" s="31" t="s">
         <v>1227</v>
@@ -15298,7 +15314,7 @@
         <v>1194</v>
       </c>
       <c r="H215" s="31" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="I215" s="2"/>
       <c r="J215" s="6"/>
@@ -15314,9 +15330,7 @@
       <c r="B216" s="15" t="s">
         <v>1122</v>
       </c>
-      <c r="C216" s="2" t="s">
-        <v>665</v>
-      </c>
+      <c r="C216" s="2"/>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
@@ -15594,7 +15608,7 @@
         <v>33</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>2058</v>
+        <v>2040</v>
       </c>
       <c r="C226" s="44"/>
       <c r="D226" s="2"/>
@@ -15616,23 +15630,23 @@
         <v>34</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>2059</v>
+        <v>2041</v>
       </c>
       <c r="C227" s="44"/>
       <c r="D227" s="16" t="s">
-        <v>1990</v>
+        <v>1972</v>
       </c>
       <c r="E227" s="16" t="s">
-        <v>1991</v>
+        <v>1973</v>
       </c>
       <c r="F227" s="16" t="s">
-        <v>1992</v>
+        <v>1974</v>
       </c>
       <c r="G227" s="16" t="s">
-        <v>1993</v>
+        <v>1975</v>
       </c>
       <c r="H227" s="16" t="s">
-        <v>1994</v>
+        <v>1976</v>
       </c>
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
@@ -15646,23 +15660,23 @@
         <v>34</v>
       </c>
       <c r="B228" s="45" t="s">
-        <v>2060</v>
+        <v>2042</v>
       </c>
       <c r="C228" s="46"/>
       <c r="D228" s="17" t="s">
-        <v>1995</v>
+        <v>1977</v>
       </c>
       <c r="E228" s="17" t="s">
-        <v>1996</v>
+        <v>1978</v>
       </c>
       <c r="F228" s="17" t="s">
-        <v>1997</v>
+        <v>1979</v>
       </c>
       <c r="G228" s="17" t="s">
-        <v>1998</v>
+        <v>1980</v>
       </c>
       <c r="H228" s="17" t="s">
-        <v>1999</v>
+        <v>1981</v>
       </c>
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
@@ -15676,23 +15690,23 @@
         <v>34</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>2062</v>
+        <v>2044</v>
       </c>
       <c r="C229" s="44"/>
       <c r="D229" s="16" t="s">
-        <v>2000</v>
+        <v>1982</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>2001</v>
+        <v>1983</v>
       </c>
       <c r="F229" s="16" t="s">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="G229" s="16" t="s">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="H229" s="16" t="s">
-        <v>2004</v>
+        <v>1986</v>
       </c>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
@@ -15706,23 +15720,23 @@
         <v>34</v>
       </c>
       <c r="B230" s="45" t="s">
-        <v>2061</v>
+        <v>2043</v>
       </c>
       <c r="C230" s="46"/>
       <c r="D230" s="17" t="s">
-        <v>2005</v>
+        <v>1987</v>
       </c>
       <c r="E230" s="17" t="s">
-        <v>2006</v>
+        <v>1988</v>
       </c>
       <c r="F230" s="17" t="s">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="G230" s="17" t="s">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="H230" s="17" t="s">
-        <v>2009</v>
+        <v>1991</v>
       </c>
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
@@ -15736,10 +15750,10 @@
         <v>33</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>2063</v>
+        <v>2045</v>
       </c>
       <c r="C231" s="44" t="s">
-        <v>2010</v>
+        <v>1992</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -15760,23 +15774,23 @@
         <v>34</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>2064</v>
+        <v>2046</v>
       </c>
       <c r="C232" s="44"/>
       <c r="D232" s="16" t="s">
-        <v>2011</v>
+        <v>1993</v>
       </c>
       <c r="E232" s="16" t="s">
-        <v>2012</v>
+        <v>1994</v>
       </c>
       <c r="F232" s="16" t="s">
-        <v>2013</v>
+        <v>1995</v>
       </c>
       <c r="G232" s="16" t="s">
-        <v>2014</v>
+        <v>1996</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>2015</v>
+        <v>1997</v>
       </c>
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
@@ -15790,23 +15804,23 @@
         <v>34</v>
       </c>
       <c r="B233" s="45" t="s">
-        <v>2065</v>
+        <v>2047</v>
       </c>
       <c r="C233" s="46"/>
       <c r="D233" s="17" t="s">
-        <v>2016</v>
+        <v>1998</v>
       </c>
       <c r="E233" s="17" t="s">
-        <v>2017</v>
+        <v>1999</v>
       </c>
       <c r="F233" s="17" t="s">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="G233" s="17" t="s">
-        <v>2019</v>
+        <v>2001</v>
       </c>
       <c r="H233" s="17" t="s">
-        <v>2020</v>
+        <v>2002</v>
       </c>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
@@ -15820,23 +15834,23 @@
         <v>34</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>2066</v>
+        <v>2048</v>
       </c>
       <c r="C234" s="44"/>
       <c r="D234" s="16" t="s">
-        <v>2021</v>
+        <v>2003</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="F234" s="16" t="s">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="G234" s="16" t="s">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>2025</v>
+        <v>2007</v>
       </c>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
@@ -15850,10 +15864,10 @@
         <v>33</v>
       </c>
       <c r="B235" s="45" t="s">
-        <v>2073</v>
+        <v>2055</v>
       </c>
       <c r="C235" s="46" t="s">
-        <v>2026</v>
+        <v>2008</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -15874,23 +15888,23 @@
         <v>34</v>
       </c>
       <c r="B236" s="45" t="s">
-        <v>2067</v>
+        <v>2049</v>
       </c>
       <c r="C236" s="46"/>
       <c r="D236" s="17" t="s">
-        <v>2027</v>
+        <v>2009</v>
       </c>
       <c r="E236" s="17" t="s">
-        <v>2028</v>
+        <v>2010</v>
       </c>
       <c r="F236" s="17" t="s">
-        <v>2029</v>
+        <v>2011</v>
       </c>
       <c r="G236" s="17" t="s">
-        <v>2030</v>
+        <v>2012</v>
       </c>
       <c r="H236" s="17" t="s">
-        <v>2031</v>
+        <v>2013</v>
       </c>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
@@ -15904,23 +15918,23 @@
         <v>34</v>
       </c>
       <c r="B237" s="45" t="s">
-        <v>2074</v>
+        <v>2056</v>
       </c>
       <c r="C237" s="46"/>
       <c r="D237" s="16" t="s">
-        <v>2032</v>
+        <v>2014</v>
       </c>
       <c r="E237" s="16" t="s">
-        <v>2033</v>
+        <v>2015</v>
       </c>
       <c r="F237" s="16" t="s">
-        <v>2034</v>
+        <v>2016</v>
       </c>
       <c r="G237" s="16" t="s">
-        <v>2035</v>
+        <v>2017</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>2036</v>
+        <v>2018</v>
       </c>
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
@@ -15934,23 +15948,23 @@
         <v>34</v>
       </c>
       <c r="B238" s="45" t="s">
-        <v>2068</v>
+        <v>2050</v>
       </c>
       <c r="C238" s="46"/>
       <c r="D238" s="17" t="s">
-        <v>2037</v>
+        <v>2019</v>
       </c>
       <c r="E238" s="17" t="s">
-        <v>2038</v>
+        <v>2020</v>
       </c>
       <c r="F238" s="17" t="s">
-        <v>2039</v>
+        <v>2021</v>
       </c>
       <c r="G238" s="17" t="s">
-        <v>2040</v>
+        <v>2022</v>
       </c>
       <c r="H238" s="17" t="s">
-        <v>2041</v>
+        <v>2023</v>
       </c>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
@@ -15964,10 +15978,10 @@
         <v>33</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>2069</v>
+        <v>2051</v>
       </c>
       <c r="C239" s="44" t="s">
-        <v>2042</v>
+        <v>2024</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -15988,23 +16002,23 @@
         <v>34</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>2070</v>
+        <v>2052</v>
       </c>
       <c r="C240" s="44"/>
       <c r="D240" s="16" t="s">
-        <v>2043</v>
+        <v>2025</v>
       </c>
       <c r="E240" s="16" t="s">
-        <v>2044</v>
+        <v>2026</v>
       </c>
       <c r="F240" s="16" t="s">
-        <v>2045</v>
+        <v>2027</v>
       </c>
       <c r="G240" s="16" t="s">
-        <v>2046</v>
+        <v>2028</v>
       </c>
       <c r="H240" s="16" t="s">
-        <v>2047</v>
+        <v>2029</v>
       </c>
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
@@ -16018,23 +16032,23 @@
         <v>34</v>
       </c>
       <c r="B241" s="45" t="s">
-        <v>2071</v>
+        <v>2053</v>
       </c>
       <c r="C241" s="46"/>
       <c r="D241" s="17" t="s">
-        <v>2048</v>
+        <v>2030</v>
       </c>
       <c r="E241" s="17" t="s">
-        <v>2049</v>
+        <v>2031</v>
       </c>
       <c r="F241" s="17" t="s">
-        <v>2050</v>
+        <v>2032</v>
       </c>
       <c r="G241" s="17" t="s">
-        <v>2051</v>
+        <v>2033</v>
       </c>
       <c r="H241" s="17" t="s">
-        <v>2052</v>
+        <v>2034</v>
       </c>
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
@@ -16048,23 +16062,23 @@
         <v>34</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>2072</v>
+        <v>2054</v>
       </c>
       <c r="C242" s="44"/>
       <c r="D242" s="16" t="s">
-        <v>2053</v>
+        <v>2035</v>
       </c>
       <c r="E242" s="16" t="s">
-        <v>2054</v>
+        <v>2036</v>
       </c>
       <c r="F242" s="16" t="s">
-        <v>2055</v>
+        <v>2037</v>
       </c>
       <c r="G242" s="16" t="s">
-        <v>2056</v>
+        <v>2038</v>
       </c>
       <c r="H242" s="16" t="s">
-        <v>2057</v>
+        <v>2039</v>
       </c>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
@@ -16078,7 +16092,7 @@
         <v>33</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>2225</v>
+        <v>2207</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -16100,7 +16114,7 @@
         <v>34</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>2226</v>
+        <v>2208</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="3" t="s">
@@ -16160,7 +16174,7 @@
         <v>34</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>2227</v>
+        <v>2209</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="3" t="s">
@@ -16190,7 +16204,7 @@
         <v>34</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>2228</v>
+        <v>2210</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="3" t="s">
@@ -16830,7 +16844,7 @@
         <v>660</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>2077</v>
+        <v>2059</v>
       </c>
       <c r="I269" s="2"/>
       <c r="J269" s="6"/>
@@ -17816,7 +17830,7 @@
         <v>33</v>
       </c>
       <c r="B297" s="35" t="s">
-        <v>2229</v>
+        <v>2211</v>
       </c>
       <c r="C297" s="36"/>
       <c r="D297" s="36"/>
@@ -18086,7 +18100,7 @@
         <v>33</v>
       </c>
       <c r="B305" s="18" t="s">
-        <v>2230</v>
+        <v>2212</v>
       </c>
       <c r="C305" s="19"/>
       <c r="D305" s="19"/>
@@ -18204,7 +18218,7 @@
         <v>33</v>
       </c>
       <c r="B309" s="18" t="s">
-        <v>2231</v>
+        <v>2213</v>
       </c>
       <c r="C309" s="19"/>
       <c r="D309" s="19"/>
@@ -18258,7 +18272,7 @@
         <v>33</v>
       </c>
       <c r="B311" s="18" t="s">
-        <v>2232</v>
+        <v>2214</v>
       </c>
       <c r="C311" s="19"/>
       <c r="D311" s="19"/>
@@ -18280,7 +18294,7 @@
         <v>34</v>
       </c>
       <c r="B312" s="20" t="s">
-        <v>2233</v>
+        <v>2215</v>
       </c>
       <c r="C312" s="21"/>
       <c r="D312" s="22" t="s">
@@ -18366,7 +18380,7 @@
         <v>33</v>
       </c>
       <c r="B315" s="18" t="s">
-        <v>2234</v>
+        <v>2216</v>
       </c>
       <c r="C315" s="19"/>
       <c r="D315" s="19"/>
@@ -18418,7 +18432,7 @@
         <v>33</v>
       </c>
       <c r="B317" s="18" t="s">
-        <v>2235</v>
+        <v>2217</v>
       </c>
       <c r="C317" s="19"/>
       <c r="D317" s="19"/>
@@ -18470,7 +18484,7 @@
         <v>33</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>2236</v>
+        <v>2218</v>
       </c>
       <c r="C319" s="19"/>
       <c r="D319" s="19"/>
@@ -18604,7 +18618,7 @@
         <v>33</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>2237</v>
+        <v>2219</v>
       </c>
       <c r="C324" s="19"/>
       <c r="D324" s="19"/>
@@ -18852,7 +18866,7 @@
         <v>33</v>
       </c>
       <c r="B332" s="35" t="s">
-        <v>2239</v>
+        <v>2221</v>
       </c>
       <c r="C332" s="36"/>
       <c r="D332" s="36"/>
@@ -18878,19 +18892,19 @@
       </c>
       <c r="C333" s="27"/>
       <c r="D333" s="28" t="s">
-        <v>2238</v>
+        <v>2220</v>
       </c>
       <c r="E333" s="28" t="s">
-        <v>2240</v>
+        <v>2222</v>
       </c>
       <c r="F333" s="28" t="s">
-        <v>2241</v>
+        <v>2223</v>
       </c>
       <c r="G333" s="28" t="s">
-        <v>2242</v>
+        <v>2224</v>
       </c>
       <c r="H333" s="28" t="s">
-        <v>2243</v>
+        <v>2225</v>
       </c>
       <c r="I333" s="2"/>
       <c r="J333" s="6"/>
@@ -18904,7 +18918,7 @@
         <v>34</v>
       </c>
       <c r="B334" s="23" t="s">
-        <v>2244</v>
+        <v>2226</v>
       </c>
       <c r="C334" s="24"/>
       <c r="D334" s="25" t="s">
@@ -18964,7 +18978,7 @@
         <v>33</v>
       </c>
       <c r="B336" s="35" t="s">
-        <v>2245</v>
+        <v>2227</v>
       </c>
       <c r="C336" s="36"/>
       <c r="D336" s="36"/>
@@ -19046,7 +19060,7 @@
         <v>33</v>
       </c>
       <c r="B339" s="35" t="s">
-        <v>2246</v>
+        <v>2228</v>
       </c>
       <c r="C339" s="36"/>
       <c r="D339" s="36"/>
@@ -19072,19 +19086,19 @@
       </c>
       <c r="C340" s="37"/>
       <c r="D340" s="25" t="s">
-        <v>2247</v>
+        <v>2229</v>
       </c>
       <c r="E340" s="25" t="s">
-        <v>2248</v>
+        <v>2230</v>
       </c>
       <c r="F340" s="25" t="s">
-        <v>2249</v>
+        <v>2231</v>
       </c>
       <c r="G340" s="25" t="s">
-        <v>2250</v>
+        <v>2232</v>
       </c>
       <c r="H340" s="25" t="s">
-        <v>2251</v>
+        <v>2233</v>
       </c>
       <c r="I340" s="2"/>
       <c r="J340" s="6"/>
@@ -19102,19 +19116,19 @@
       </c>
       <c r="C341" s="29"/>
       <c r="D341" s="25" t="s">
-        <v>2252</v>
+        <v>2234</v>
       </c>
       <c r="E341" s="25" t="s">
-        <v>2253</v>
+        <v>2235</v>
       </c>
       <c r="F341" s="25" t="s">
-        <v>2254</v>
+        <v>2236</v>
       </c>
       <c r="G341" s="25" t="s">
-        <v>2255</v>
+        <v>2237</v>
       </c>
       <c r="H341" s="25" t="s">
-        <v>2256</v>
+        <v>2238</v>
       </c>
       <c r="I341" s="2"/>
       <c r="J341" s="6"/>
@@ -19132,19 +19146,19 @@
       </c>
       <c r="C342" s="37"/>
       <c r="D342" s="25" t="s">
-        <v>2257</v>
+        <v>2239</v>
       </c>
       <c r="E342" s="25" t="s">
-        <v>2258</v>
+        <v>2240</v>
       </c>
       <c r="F342" s="25" t="s">
-        <v>2259</v>
+        <v>2241</v>
       </c>
       <c r="G342" s="25" t="s">
-        <v>2260</v>
+        <v>2242</v>
       </c>
       <c r="H342" s="25" t="s">
-        <v>2261</v>
+        <v>2243</v>
       </c>
       <c r="I342" s="2"/>
       <c r="J342" s="6"/>
@@ -19398,7 +19412,7 @@
         <v>32</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>2262</v>
+        <v>2244</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="3" t="s">
@@ -19558,7 +19572,7 @@
         <v>89</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>2263</v>
+        <v>2245</v>
       </c>
       <c r="I354" s="3" t="s">
         <v>91</v>
@@ -20010,7 +20024,7 @@
         <v>32</v>
       </c>
       <c r="B367" s="26" t="s">
-        <v>2264</v>
+        <v>2246</v>
       </c>
       <c r="C367" s="29" t="s">
         <v>1088</v>
@@ -20390,7 +20404,7 @@
         <v>33</v>
       </c>
       <c r="B379" s="18" t="s">
-        <v>2265</v>
+        <v>2247</v>
       </c>
       <c r="C379" s="19"/>
       <c r="D379" s="19"/>
@@ -20416,22 +20430,22 @@
       </c>
       <c r="C380" s="24"/>
       <c r="D380" s="25" t="s">
-        <v>2266</v>
+        <v>2248</v>
       </c>
       <c r="E380" s="25" t="s">
-        <v>2269</v>
+        <v>2251</v>
       </c>
       <c r="F380" s="25" t="s">
-        <v>2267</v>
+        <v>2249</v>
       </c>
       <c r="G380" s="25" t="s">
-        <v>2268</v>
+        <v>2250</v>
       </c>
       <c r="H380" s="25" t="s">
-        <v>2270</v>
+        <v>2252</v>
       </c>
       <c r="I380" s="25" t="s">
-        <v>2269</v>
+        <v>2251</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
@@ -20476,7 +20490,7 @@
         <v>33</v>
       </c>
       <c r="B382" s="18" t="s">
-        <v>2271</v>
+        <v>2253</v>
       </c>
       <c r="C382" s="19"/>
       <c r="D382" s="19"/>
@@ -20562,7 +20576,7 @@
         <v>33</v>
       </c>
       <c r="B385" s="18" t="s">
-        <v>2272</v>
+        <v>2254</v>
       </c>
       <c r="C385" s="19" t="s">
         <v>944</v>
@@ -20618,7 +20632,7 @@
         <v>33</v>
       </c>
       <c r="B387" s="18" t="s">
-        <v>2273</v>
+        <v>2255</v>
       </c>
       <c r="C387" s="19" t="s">
         <v>945</v>
@@ -20738,7 +20752,7 @@
         <v>34</v>
       </c>
       <c r="B391" s="23" t="s">
-        <v>2274</v>
+        <v>2256</v>
       </c>
       <c r="C391" s="24"/>
       <c r="D391" s="25" t="s">
@@ -20770,7 +20784,7 @@
         <v>33</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2275</v>
+        <v>2257</v>
       </c>
       <c r="C392" s="19" t="s">
         <v>946</v>
@@ -20858,26 +20872,26 @@
         <v>32</v>
       </c>
       <c r="B395" s="38" t="s">
-        <v>2276</v>
+        <v>2258</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" s="38" t="s">
-        <v>1866</v>
+        <v>1857</v>
       </c>
       <c r="E395" s="38" t="s">
-        <v>1867</v>
+        <v>1858</v>
       </c>
       <c r="F395" s="38" t="s">
-        <v>1868</v>
+        <v>1859</v>
       </c>
       <c r="G395" s="38" t="s">
-        <v>1869</v>
+        <v>1860</v>
       </c>
       <c r="H395" s="38" t="s">
-        <v>1870</v>
+        <v>1861</v>
       </c>
       <c r="I395" s="38" t="s">
-        <v>1868</v>
+        <v>1859</v>
       </c>
       <c r="J395" s="6" t="s">
         <v>543</v>
@@ -20894,26 +20908,26 @@
         <v>32</v>
       </c>
       <c r="B396" s="39" t="s">
-        <v>1859</v>
+        <v>1850</v>
       </c>
       <c r="C396" s="2"/>
       <c r="D396" s="39" t="s">
-        <v>1871</v>
+        <v>1862</v>
       </c>
       <c r="E396" s="39" t="s">
-        <v>1872</v>
+        <v>1863</v>
       </c>
       <c r="F396" s="39" t="s">
-        <v>1873</v>
+        <v>1864</v>
       </c>
       <c r="G396" s="39" t="s">
-        <v>1874</v>
+        <v>1865</v>
       </c>
       <c r="H396" s="39" t="s">
-        <v>1875</v>
+        <v>1866</v>
       </c>
       <c r="I396" s="39" t="s">
-        <v>1872</v>
+        <v>1863</v>
       </c>
       <c r="J396" s="6" t="s">
         <v>543</v>
@@ -20930,26 +20944,26 @@
         <v>32</v>
       </c>
       <c r="B397" s="38" t="s">
-        <v>1860</v>
+        <v>1851</v>
       </c>
       <c r="C397" s="2"/>
       <c r="D397" s="38" t="s">
-        <v>1871</v>
+        <v>1862</v>
       </c>
       <c r="E397" s="38" t="s">
-        <v>1872</v>
+        <v>1863</v>
       </c>
       <c r="F397" s="38" t="s">
-        <v>1873</v>
+        <v>1864</v>
       </c>
       <c r="G397" s="38" t="s">
-        <v>1874</v>
+        <v>1865</v>
       </c>
       <c r="H397" s="38" t="s">
-        <v>1875</v>
+        <v>1866</v>
       </c>
       <c r="I397" s="38" t="s">
-        <v>1873</v>
+        <v>1864</v>
       </c>
       <c r="J397" s="6" t="s">
         <v>543</v>
@@ -20966,26 +20980,26 @@
         <v>32</v>
       </c>
       <c r="B398" s="39" t="s">
-        <v>1861</v>
+        <v>1852</v>
       </c>
       <c r="C398" s="2"/>
       <c r="D398" s="39" t="s">
-        <v>1876</v>
+        <v>1867</v>
       </c>
       <c r="E398" s="39" t="s">
-        <v>1877</v>
+        <v>1868</v>
       </c>
       <c r="F398" s="39" t="s">
-        <v>1878</v>
+        <v>1869</v>
       </c>
       <c r="G398" s="39" t="s">
-        <v>1879</v>
+        <v>1870</v>
       </c>
       <c r="H398" s="39" t="s">
-        <v>1880</v>
+        <v>1871</v>
       </c>
       <c r="I398" s="38" t="s">
-        <v>1871</v>
+        <v>1862</v>
       </c>
       <c r="J398" s="6" t="s">
         <v>543</v>
@@ -21002,26 +21016,26 @@
         <v>32</v>
       </c>
       <c r="B399" s="38" t="s">
-        <v>1862</v>
+        <v>1853</v>
       </c>
       <c r="C399" s="2"/>
       <c r="D399" s="38" t="s">
-        <v>1881</v>
+        <v>1872</v>
       </c>
       <c r="E399" s="38" t="s">
-        <v>1882</v>
+        <v>1873</v>
       </c>
       <c r="F399" s="38" t="s">
-        <v>1883</v>
+        <v>1874</v>
       </c>
       <c r="G399" s="38" t="s">
-        <v>1884</v>
+        <v>1875</v>
       </c>
       <c r="H399" s="38" t="s">
-        <v>1875</v>
+        <v>1866</v>
       </c>
       <c r="I399" s="39" t="s">
-        <v>1876</v>
+        <v>1867</v>
       </c>
       <c r="J399" s="6" t="s">
         <v>543</v>
@@ -21038,26 +21052,26 @@
         <v>32</v>
       </c>
       <c r="B400" s="39" t="s">
-        <v>2277</v>
+        <v>2259</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="39" t="s">
-        <v>1885</v>
+        <v>1876</v>
       </c>
       <c r="E400" s="39" t="s">
-        <v>1886</v>
+        <v>1877</v>
       </c>
       <c r="F400" s="39" t="s">
-        <v>1887</v>
+        <v>1878</v>
       </c>
       <c r="G400" s="39" t="s">
-        <v>1888</v>
+        <v>1879</v>
       </c>
       <c r="H400" s="39" t="s">
+        <v>1866</v>
+      </c>
+      <c r="I400" s="38" t="s">
         <v>1875</v>
-      </c>
-      <c r="I400" s="38" t="s">
-        <v>1884</v>
       </c>
       <c r="J400" s="6" t="s">
         <v>543</v>
@@ -21074,26 +21088,26 @@
         <v>32</v>
       </c>
       <c r="B401" s="38" t="s">
-        <v>1863</v>
+        <v>1854</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" s="38" t="s">
-        <v>1889</v>
+        <v>1880</v>
       </c>
       <c r="E401" s="38" t="s">
-        <v>1890</v>
+        <v>1881</v>
       </c>
       <c r="F401" s="38" t="s">
-        <v>1891</v>
+        <v>1882</v>
       </c>
       <c r="G401" s="38" t="s">
-        <v>1892</v>
+        <v>1883</v>
       </c>
       <c r="H401" s="38" t="s">
-        <v>1870</v>
+        <v>1861</v>
       </c>
       <c r="I401" s="39" t="s">
-        <v>1885</v>
+        <v>1876</v>
       </c>
       <c r="J401" s="6" t="s">
         <v>543</v>
@@ -21110,26 +21124,26 @@
         <v>32</v>
       </c>
       <c r="B402" s="39" t="s">
-        <v>1864</v>
+        <v>1855</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" s="39" t="s">
-        <v>1893</v>
+        <v>1884</v>
       </c>
       <c r="E402" s="39" t="s">
-        <v>1894</v>
+        <v>1885</v>
       </c>
       <c r="F402" s="39" t="s">
-        <v>1895</v>
+        <v>1886</v>
       </c>
       <c r="G402" s="39" t="s">
-        <v>1896</v>
+        <v>1887</v>
       </c>
       <c r="H402" s="39" t="s">
-        <v>1897</v>
+        <v>1888</v>
       </c>
       <c r="I402" s="38" t="s">
-        <v>1889</v>
+        <v>1880</v>
       </c>
       <c r="J402" s="6" t="s">
         <v>543</v>
@@ -21146,26 +21160,26 @@
         <v>32</v>
       </c>
       <c r="B403" s="38" t="s">
-        <v>2291</v>
+        <v>2273</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" s="38" t="s">
-        <v>1898</v>
+        <v>1889</v>
       </c>
       <c r="E403" s="38" t="s">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="F403" s="38" t="s">
-        <v>1900</v>
+        <v>1891</v>
       </c>
       <c r="G403" s="38" t="s">
-        <v>1901</v>
+        <v>1892</v>
       </c>
       <c r="H403" s="38" t="s">
-        <v>1875</v>
+        <v>1866</v>
       </c>
       <c r="I403" s="39" t="s">
-        <v>1893</v>
+        <v>1884</v>
       </c>
       <c r="J403" s="6" t="s">
         <v>543</v>
@@ -21182,26 +21196,26 @@
         <v>32</v>
       </c>
       <c r="B404" s="39" t="s">
-        <v>2290</v>
+        <v>2272</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="39" t="s">
-        <v>1898</v>
+        <v>1889</v>
       </c>
       <c r="E404" s="39" t="s">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="F404" s="39" t="s">
-        <v>1900</v>
+        <v>1891</v>
       </c>
       <c r="G404" s="39" t="s">
-        <v>1901</v>
+        <v>1892</v>
       </c>
       <c r="H404" s="39" t="s">
-        <v>1875</v>
+        <v>1866</v>
       </c>
       <c r="I404" s="38" t="s">
-        <v>1898</v>
+        <v>1889</v>
       </c>
       <c r="J404" s="6" t="s">
         <v>543</v>
@@ -21218,26 +21232,26 @@
         <v>32</v>
       </c>
       <c r="B405" s="38" t="s">
-        <v>2278</v>
+        <v>2260</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="38" t="s">
-        <v>1902</v>
+        <v>1893</v>
       </c>
       <c r="E405" s="38" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="F405" s="38" t="s">
-        <v>1904</v>
+        <v>1895</v>
       </c>
       <c r="G405" s="38" t="s">
-        <v>1905</v>
+        <v>1896</v>
       </c>
       <c r="H405" s="38" t="s">
-        <v>1906</v>
+        <v>1897</v>
       </c>
       <c r="I405" s="39" t="s">
-        <v>1898</v>
+        <v>1889</v>
       </c>
       <c r="J405" s="6" t="s">
         <v>543</v>
@@ -21254,26 +21268,26 @@
         <v>32</v>
       </c>
       <c r="B406" s="39" t="s">
-        <v>1865</v>
+        <v>1856</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" s="39" t="s">
-        <v>1907</v>
+        <v>1898</v>
       </c>
       <c r="E406" s="39" t="s">
-        <v>1908</v>
+        <v>1899</v>
       </c>
       <c r="F406" s="39" t="s">
-        <v>1909</v>
+        <v>1900</v>
       </c>
       <c r="G406" s="39" t="s">
-        <v>1910</v>
+        <v>1901</v>
       </c>
       <c r="H406" s="39" t="s">
-        <v>1911</v>
+        <v>1902</v>
       </c>
       <c r="I406" s="38" t="s">
-        <v>1902</v>
+        <v>1893</v>
       </c>
       <c r="J406" s="6" t="s">
         <v>543</v>
@@ -21290,26 +21304,26 @@
         <v>32</v>
       </c>
       <c r="B407" s="38" t="s">
-        <v>2289</v>
+        <v>2271</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" s="38" t="s">
-        <v>1912</v>
+        <v>1903</v>
       </c>
       <c r="E407" s="38" t="s">
-        <v>1913</v>
+        <v>1904</v>
       </c>
       <c r="F407" s="38" t="s">
-        <v>1914</v>
+        <v>1905</v>
       </c>
       <c r="G407" s="38" t="s">
-        <v>1915</v>
+        <v>1906</v>
       </c>
       <c r="H407" s="38" t="s">
-        <v>1911</v>
+        <v>1902</v>
       </c>
       <c r="I407" s="39" t="s">
-        <v>1907</v>
+        <v>1898</v>
       </c>
       <c r="J407" s="6" t="s">
         <v>543</v>
@@ -21326,26 +21340,26 @@
         <v>32</v>
       </c>
       <c r="B408" s="39" t="s">
-        <v>2288</v>
+        <v>2270</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="39" t="s">
-        <v>1916</v>
+        <v>1907</v>
       </c>
       <c r="E408" s="39" t="s">
-        <v>1917</v>
+        <v>1908</v>
       </c>
       <c r="F408" s="39" t="s">
-        <v>1918</v>
+        <v>1909</v>
       </c>
       <c r="G408" s="39" t="s">
-        <v>1919</v>
+        <v>1910</v>
       </c>
       <c r="H408" s="39" t="s">
+        <v>1897</v>
+      </c>
+      <c r="I408" s="38" t="s">
         <v>1906</v>
-      </c>
-      <c r="I408" s="38" t="s">
-        <v>1915</v>
       </c>
       <c r="J408" s="6" t="s">
         <v>543</v>
@@ -21366,22 +21380,22 @@
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="3" t="s">
-        <v>2280</v>
+        <v>2262</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>2285</v>
+        <v>2267</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>2286</v>
+        <v>2268</v>
       </c>
       <c r="G409" s="3" t="s">
-        <v>2281</v>
+        <v>2263</v>
       </c>
       <c r="H409" s="3" t="s">
-        <v>2287</v>
+        <v>2269</v>
       </c>
       <c r="I409" s="3" t="s">
-        <v>2285</v>
+        <v>2267</v>
       </c>
       <c r="J409" s="13" t="s">
         <v>10</v>
@@ -21738,7 +21752,7 @@
         <v>244</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>2293</v>
+        <v>2275</v>
       </c>
       <c r="I419" s="3" t="s">
         <v>237</v>
@@ -21801,10 +21815,10 @@
         <v>207</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>2284</v>
+        <v>2266</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>2292</v>
+        <v>2274</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>249</v>
@@ -21830,23 +21844,23 @@
         <v>32</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>2283</v>
+        <v>2265</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" s="3" t="s">
         <v>250</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>2294</v>
+        <v>2276</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>2279</v>
+        <v>2261</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>255</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>2282</v>
+        <v>2264</v>
       </c>
       <c r="I422" s="3" t="s">
         <v>256</v>
@@ -21866,26 +21880,26 @@
         <v>32</v>
       </c>
       <c r="B423" s="51" t="s">
-        <v>2352</v>
+        <v>2334</v>
       </c>
       <c r="C423" s="49"/>
       <c r="D423" s="38" t="s">
-        <v>2295</v>
+        <v>2277</v>
       </c>
       <c r="E423" s="38" t="s">
-        <v>2296</v>
+        <v>2278</v>
       </c>
       <c r="F423" s="38" t="s">
-        <v>2297</v>
+        <v>2279</v>
       </c>
       <c r="G423" s="38" t="s">
-        <v>2298</v>
+        <v>2280</v>
       </c>
       <c r="H423" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I423" s="38" t="s">
-        <v>2297</v>
+        <v>2279</v>
       </c>
       <c r="J423" s="11" t="s">
         <v>11</v>
@@ -21902,26 +21916,26 @@
         <v>32</v>
       </c>
       <c r="B424" s="52" t="s">
-        <v>2353</v>
+        <v>2335</v>
       </c>
       <c r="C424" s="50"/>
       <c r="D424" s="39" t="s">
-        <v>2300</v>
+        <v>2282</v>
       </c>
       <c r="E424" s="39" t="s">
-        <v>2301</v>
+        <v>2283</v>
       </c>
       <c r="F424" s="39" t="s">
-        <v>2302</v>
+        <v>2284</v>
       </c>
       <c r="G424" s="39" t="s">
-        <v>2303</v>
+        <v>2285</v>
       </c>
       <c r="H424" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I424" s="39" t="s">
-        <v>2302</v>
+        <v>2284</v>
       </c>
       <c r="J424" s="11" t="s">
         <v>11</v>
@@ -21938,26 +21952,26 @@
         <v>32</v>
       </c>
       <c r="B425" s="51" t="s">
-        <v>2354</v>
+        <v>2336</v>
       </c>
       <c r="C425" s="49"/>
       <c r="D425" s="38" t="s">
-        <v>2304</v>
+        <v>2286</v>
       </c>
       <c r="E425" s="38" t="s">
-        <v>2305</v>
+        <v>2287</v>
       </c>
       <c r="F425" s="38" t="s">
-        <v>2306</v>
+        <v>2288</v>
       </c>
       <c r="G425" s="38" t="s">
-        <v>2307</v>
+        <v>2289</v>
       </c>
       <c r="H425" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I425" s="38" t="s">
-        <v>2307</v>
+        <v>2289</v>
       </c>
       <c r="J425" s="11" t="s">
         <v>11</v>
@@ -21974,26 +21988,26 @@
         <v>32</v>
       </c>
       <c r="B426" s="52" t="s">
-        <v>2355</v>
+        <v>2337</v>
       </c>
       <c r="C426" s="50"/>
       <c r="D426" s="39" t="s">
-        <v>2308</v>
+        <v>2290</v>
       </c>
       <c r="E426" s="39" t="s">
-        <v>2309</v>
+        <v>2291</v>
       </c>
       <c r="F426" s="39" t="s">
-        <v>2310</v>
+        <v>2292</v>
       </c>
       <c r="G426" s="39" t="s">
-        <v>2311</v>
+        <v>2293</v>
       </c>
       <c r="H426" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I426" s="39" t="s">
-        <v>2309</v>
+        <v>2291</v>
       </c>
       <c r="J426" s="11" t="s">
         <v>11</v>
@@ -22010,26 +22024,26 @@
         <v>32</v>
       </c>
       <c r="B427" s="51" t="s">
-        <v>2356</v>
+        <v>2338</v>
       </c>
       <c r="C427" s="49"/>
       <c r="D427" s="38" t="s">
-        <v>2312</v>
+        <v>2294</v>
       </c>
       <c r="E427" s="38" t="s">
-        <v>2313</v>
+        <v>2295</v>
       </c>
       <c r="F427" s="38" t="s">
-        <v>2314</v>
+        <v>2296</v>
       </c>
       <c r="G427" s="38" t="s">
-        <v>2315</v>
+        <v>2297</v>
       </c>
       <c r="H427" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I427" s="38" t="s">
-        <v>2314</v>
+        <v>2296</v>
       </c>
       <c r="J427" s="11" t="s">
         <v>11</v>
@@ -22046,26 +22060,26 @@
         <v>32</v>
       </c>
       <c r="B428" s="52" t="s">
-        <v>2357</v>
+        <v>2339</v>
       </c>
       <c r="C428" s="50"/>
       <c r="D428" s="39" t="s">
-        <v>2316</v>
+        <v>2298</v>
       </c>
       <c r="E428" s="39" t="s">
-        <v>2317</v>
+        <v>2299</v>
       </c>
       <c r="F428" s="39" t="s">
-        <v>2318</v>
+        <v>2300</v>
       </c>
       <c r="G428" s="39" t="s">
-        <v>2319</v>
+        <v>2301</v>
       </c>
       <c r="H428" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I428" s="39" t="s">
-        <v>2318</v>
+        <v>2300</v>
       </c>
       <c r="J428" s="11" t="s">
         <v>11</v>
@@ -22082,26 +22096,26 @@
         <v>32</v>
       </c>
       <c r="B429" s="51" t="s">
-        <v>2358</v>
+        <v>2340</v>
       </c>
       <c r="C429" s="49"/>
       <c r="D429" s="38" t="s">
-        <v>2320</v>
+        <v>2302</v>
       </c>
       <c r="E429" s="38" t="s">
-        <v>2321</v>
+        <v>2303</v>
       </c>
       <c r="F429" s="38" t="s">
-        <v>2322</v>
+        <v>2304</v>
       </c>
       <c r="G429" s="38" t="s">
-        <v>2323</v>
+        <v>2305</v>
       </c>
       <c r="H429" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I429" s="38" t="s">
-        <v>2323</v>
+        <v>2305</v>
       </c>
       <c r="J429" s="11" t="s">
         <v>11</v>
@@ -22118,26 +22132,26 @@
         <v>32</v>
       </c>
       <c r="B430" s="52" t="s">
-        <v>2359</v>
+        <v>2341</v>
       </c>
       <c r="C430" s="50"/>
       <c r="D430" s="39" t="s">
-        <v>2324</v>
+        <v>2306</v>
       </c>
       <c r="E430" s="39" t="s">
-        <v>2325</v>
+        <v>2307</v>
       </c>
       <c r="F430" s="39" t="s">
-        <v>2326</v>
+        <v>2308</v>
       </c>
       <c r="G430" s="39" t="s">
-        <v>2327</v>
+        <v>2309</v>
       </c>
       <c r="H430" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I430" s="39" t="s">
-        <v>2324</v>
+        <v>2306</v>
       </c>
       <c r="J430" s="11" t="s">
         <v>11</v>
@@ -22154,26 +22168,26 @@
         <v>32</v>
       </c>
       <c r="B431" s="51" t="s">
-        <v>2360</v>
+        <v>2342</v>
       </c>
       <c r="C431" s="49"/>
       <c r="D431" s="38" t="s">
-        <v>2328</v>
+        <v>2310</v>
       </c>
       <c r="E431" s="38" t="s">
-        <v>2329</v>
+        <v>2311</v>
       </c>
       <c r="F431" s="38" t="s">
-        <v>2330</v>
+        <v>2312</v>
       </c>
       <c r="G431" s="38" t="s">
-        <v>2331</v>
+        <v>2313</v>
       </c>
       <c r="H431" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I431" s="38" t="s">
-        <v>2328</v>
+        <v>2310</v>
       </c>
       <c r="J431" s="11" t="s">
         <v>11</v>
@@ -22190,26 +22204,26 @@
         <v>32</v>
       </c>
       <c r="B432" s="52" t="s">
-        <v>2361</v>
+        <v>2343</v>
       </c>
       <c r="C432" s="50"/>
       <c r="D432" s="39" t="s">
-        <v>2332</v>
+        <v>2314</v>
       </c>
       <c r="E432" s="39" t="s">
-        <v>2333</v>
+        <v>2315</v>
       </c>
       <c r="F432" s="39" t="s">
-        <v>2334</v>
+        <v>2316</v>
       </c>
       <c r="G432" s="39" t="s">
-        <v>2335</v>
+        <v>2317</v>
       </c>
       <c r="H432" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I432" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="J432" s="11" t="s">
         <v>11</v>
@@ -22226,26 +22240,26 @@
         <v>32</v>
       </c>
       <c r="B433" s="51" t="s">
-        <v>2362</v>
+        <v>2344</v>
       </c>
       <c r="C433" s="49"/>
       <c r="D433" s="38" t="s">
-        <v>2336</v>
+        <v>2318</v>
       </c>
       <c r="E433" s="38" t="s">
-        <v>2337</v>
+        <v>2319</v>
       </c>
       <c r="F433" s="38" t="s">
-        <v>2338</v>
+        <v>2320</v>
       </c>
       <c r="G433" s="38" t="s">
-        <v>2339</v>
+        <v>2321</v>
       </c>
       <c r="H433" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I433" s="38" t="s">
-        <v>2339</v>
+        <v>2321</v>
       </c>
       <c r="J433" s="11" t="s">
         <v>11</v>
@@ -22262,26 +22276,26 @@
         <v>32</v>
       </c>
       <c r="B434" s="52" t="s">
-        <v>2363</v>
+        <v>2345</v>
       </c>
       <c r="C434" s="50"/>
       <c r="D434" s="39" t="s">
-        <v>2340</v>
+        <v>2322</v>
       </c>
       <c r="E434" s="39" t="s">
-        <v>2341</v>
+        <v>2323</v>
       </c>
       <c r="F434" s="39" t="s">
-        <v>2342</v>
+        <v>2324</v>
       </c>
       <c r="G434" s="39" t="s">
-        <v>2343</v>
+        <v>2325</v>
       </c>
       <c r="H434" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I434" s="39" t="s">
-        <v>2341</v>
+        <v>2323</v>
       </c>
       <c r="J434" s="11" t="s">
         <v>11</v>
@@ -22298,26 +22312,26 @@
         <v>32</v>
       </c>
       <c r="B435" s="51" t="s">
-        <v>2364</v>
+        <v>2346</v>
       </c>
       <c r="C435" s="49"/>
       <c r="D435" s="38" t="s">
-        <v>2344</v>
+        <v>2326</v>
       </c>
       <c r="E435" s="38" t="s">
-        <v>2345</v>
+        <v>2327</v>
       </c>
       <c r="F435" s="38" t="s">
-        <v>2346</v>
+        <v>2328</v>
       </c>
       <c r="G435" s="38" t="s">
-        <v>2347</v>
+        <v>2329</v>
       </c>
       <c r="H435" s="38" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I435" s="38" t="s">
-        <v>2345</v>
+        <v>2327</v>
       </c>
       <c r="J435" s="11" t="s">
         <v>11</v>
@@ -22334,26 +22348,26 @@
         <v>32</v>
       </c>
       <c r="B436" s="52" t="s">
-        <v>2365</v>
+        <v>2347</v>
       </c>
       <c r="C436" s="50"/>
       <c r="D436" s="39" t="s">
-        <v>2348</v>
+        <v>2330</v>
       </c>
       <c r="E436" s="39" t="s">
-        <v>2349</v>
+        <v>2331</v>
       </c>
       <c r="F436" s="39" t="s">
-        <v>2350</v>
+        <v>2332</v>
       </c>
       <c r="G436" s="39" t="s">
-        <v>2351</v>
+        <v>2333</v>
       </c>
       <c r="H436" s="39" t="s">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="I436" s="39" t="s">
-        <v>2348</v>
+        <v>2330</v>
       </c>
       <c r="J436" s="11" t="s">
         <v>11</v>
@@ -22370,7 +22384,7 @@
         <v>33</v>
       </c>
       <c r="B437" s="40" t="s">
-        <v>2418</v>
+        <v>2400</v>
       </c>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
@@ -22392,23 +22406,23 @@
         <v>34</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2381</v>
+        <v>2363</v>
       </c>
       <c r="C438" s="40"/>
       <c r="D438" s="54" t="s">
-        <v>2366</v>
+        <v>2348</v>
       </c>
       <c r="E438" s="54" t="s">
-        <v>2367</v>
+        <v>2349</v>
       </c>
       <c r="F438" s="54" t="s">
-        <v>2368</v>
+        <v>2350</v>
       </c>
       <c r="G438" s="54" t="s">
-        <v>2420</v>
+        <v>2402</v>
       </c>
       <c r="H438" s="54" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I438" s="2"/>
       <c r="J438" s="6"/>
@@ -22422,23 +22436,23 @@
         <v>34</v>
       </c>
       <c r="B439" s="55" t="s">
-        <v>2382</v>
+        <v>2364</v>
       </c>
       <c r="C439" s="40"/>
       <c r="D439" s="55" t="s">
-        <v>2369</v>
+        <v>2351</v>
       </c>
       <c r="E439" s="55" t="s">
-        <v>2370</v>
+        <v>2352</v>
       </c>
       <c r="F439" s="55" t="s">
-        <v>2371</v>
+        <v>2353</v>
       </c>
       <c r="G439" s="55" t="s">
-        <v>2372</v>
+        <v>2354</v>
       </c>
       <c r="H439" s="55" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I439" s="2"/>
       <c r="J439" s="6"/>
@@ -22452,23 +22466,23 @@
         <v>34</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2383</v>
+        <v>2365</v>
       </c>
       <c r="C440" s="40"/>
       <c r="D440" s="54" t="s">
-        <v>2373</v>
+        <v>2355</v>
       </c>
       <c r="E440" s="54" t="s">
-        <v>2374</v>
+        <v>2356</v>
       </c>
       <c r="F440" s="54" t="s">
-        <v>2375</v>
+        <v>2357</v>
       </c>
       <c r="G440" s="54" t="s">
-        <v>2376</v>
+        <v>2358</v>
       </c>
       <c r="H440" s="54" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I440" s="2"/>
       <c r="J440" s="6"/>
@@ -22482,23 +22496,23 @@
         <v>34</v>
       </c>
       <c r="B441" s="55" t="s">
-        <v>1974</v>
+        <v>1957</v>
       </c>
       <c r="C441" s="40"/>
       <c r="D441" s="55" t="s">
-        <v>2377</v>
+        <v>2359</v>
       </c>
       <c r="E441" s="55" t="s">
-        <v>2378</v>
+        <v>2360</v>
       </c>
       <c r="F441" s="55" t="s">
-        <v>2379</v>
+        <v>2361</v>
       </c>
       <c r="G441" s="55" t="s">
-        <v>2380</v>
+        <v>2362</v>
       </c>
       <c r="H441" s="55" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I441" s="2"/>
       <c r="J441" s="6"/>
@@ -22512,7 +22526,7 @@
         <v>33</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>2419</v>
+        <v>2401</v>
       </c>
       <c r="C442" s="40"/>
       <c r="D442" s="40"/>
@@ -22534,23 +22548,23 @@
         <v>34</v>
       </c>
       <c r="B443" s="55" t="s">
-        <v>2414</v>
+        <v>2396</v>
       </c>
       <c r="C443" s="40"/>
       <c r="D443" s="55" t="s">
-        <v>2384</v>
+        <v>2366</v>
       </c>
       <c r="E443" s="55" t="s">
-        <v>2385</v>
+        <v>2367</v>
       </c>
       <c r="F443" s="55" t="s">
-        <v>2386</v>
+        <v>2368</v>
       </c>
       <c r="G443" s="55" t="s">
-        <v>2387</v>
+        <v>2369</v>
       </c>
       <c r="H443" s="55" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I443" s="2"/>
       <c r="J443" s="6"/>
@@ -22564,23 +22578,23 @@
         <v>34</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2415</v>
+        <v>2397</v>
       </c>
       <c r="C444" s="40"/>
       <c r="D444" s="54" t="s">
-        <v>2388</v>
+        <v>2370</v>
       </c>
       <c r="E444" s="54" t="s">
-        <v>2389</v>
+        <v>2371</v>
       </c>
       <c r="F444" s="54" t="s">
-        <v>2390</v>
+        <v>2372</v>
       </c>
       <c r="G444" s="54" t="s">
-        <v>2391</v>
+        <v>2373</v>
       </c>
       <c r="H444" s="54" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I444" s="2"/>
       <c r="J444" s="6"/>
@@ -22594,23 +22608,23 @@
         <v>34</v>
       </c>
       <c r="B445" s="55" t="s">
-        <v>2416</v>
+        <v>2398</v>
       </c>
       <c r="C445" s="40"/>
       <c r="D445" s="55" t="s">
-        <v>2392</v>
+        <v>2374</v>
       </c>
       <c r="E445" s="55" t="s">
-        <v>2393</v>
+        <v>2375</v>
       </c>
       <c r="F445" s="55" t="s">
-        <v>2394</v>
+        <v>2376</v>
       </c>
       <c r="G445" s="55" t="s">
-        <v>2395</v>
+        <v>2377</v>
       </c>
       <c r="H445" s="55" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I445" s="2"/>
       <c r="J445" s="6"/>
@@ -22624,23 +22638,23 @@
         <v>34</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2417</v>
+        <v>2399</v>
       </c>
       <c r="C446" s="40"/>
       <c r="D446" s="54" t="s">
-        <v>2396</v>
+        <v>2378</v>
       </c>
       <c r="E446" s="54" t="s">
-        <v>2397</v>
+        <v>2379</v>
       </c>
       <c r="F446" s="54" t="s">
-        <v>2398</v>
+        <v>2380</v>
       </c>
       <c r="G446" s="54" t="s">
-        <v>2399</v>
+        <v>2381</v>
       </c>
       <c r="H446" s="54" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="I446" s="2"/>
       <c r="J446" s="6"/>
@@ -22654,7 +22668,7 @@
         <v>33</v>
       </c>
       <c r="B447" s="40" t="s">
-        <v>2400</v>
+        <v>2382</v>
       </c>
       <c r="C447" s="40"/>
       <c r="D447" s="40"/>
@@ -22676,23 +22690,23 @@
         <v>34</v>
       </c>
       <c r="B448" s="40" t="s">
-        <v>1975</v>
+        <v>1958</v>
       </c>
       <c r="C448" s="40"/>
       <c r="D448" s="40" t="s">
-        <v>1921</v>
+        <v>1912</v>
       </c>
       <c r="E448" s="40" t="s">
-        <v>1922</v>
+        <v>1913</v>
       </c>
       <c r="F448" s="40" t="s">
-        <v>1923</v>
+        <v>1914</v>
       </c>
       <c r="G448" s="40" t="s">
-        <v>1924</v>
+        <v>1915</v>
       </c>
       <c r="H448" s="41" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="I448" s="2"/>
       <c r="J448" s="6"/>
@@ -22706,11 +22720,11 @@
         <v>34</v>
       </c>
       <c r="B449" s="40" t="s">
-        <v>2401</v>
+        <v>2383</v>
       </c>
       <c r="C449" s="40"/>
       <c r="D449" s="42" t="s">
-        <v>1926</v>
+        <v>1917</v>
       </c>
       <c r="E449" s="42">
         <v>37</v>
@@ -22722,7 +22736,7 @@
         <v>13516</v>
       </c>
       <c r="H449" s="41" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="I449" s="2"/>
       <c r="J449" s="6"/>
@@ -22736,23 +22750,23 @@
         <v>34</v>
       </c>
       <c r="B450" s="40" t="s">
-        <v>2412</v>
+        <v>2394</v>
       </c>
       <c r="C450" s="40"/>
       <c r="D450" s="40" t="s">
-        <v>2402</v>
+        <v>2384</v>
       </c>
       <c r="E450" s="40" t="s">
-        <v>2413</v>
+        <v>2395</v>
       </c>
       <c r="F450" s="40" t="s">
-        <v>2403</v>
+        <v>2385</v>
       </c>
       <c r="G450" s="40" t="s">
-        <v>2404</v>
+        <v>2386</v>
       </c>
       <c r="H450" s="41" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="I450" s="2"/>
       <c r="J450" s="6"/>
@@ -22766,7 +22780,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="40" t="s">
-        <v>2410</v>
+        <v>2392</v>
       </c>
       <c r="C451" s="40"/>
       <c r="D451" s="42">
@@ -22779,10 +22793,10 @@
         <v>43</v>
       </c>
       <c r="G451" s="42" t="s">
-        <v>1927</v>
+        <v>1918</v>
       </c>
       <c r="H451" s="41" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="I451" s="2"/>
       <c r="J451" s="6"/>
@@ -22796,7 +22810,7 @@
         <v>33</v>
       </c>
       <c r="B452" s="40" t="s">
-        <v>2405</v>
+        <v>2387</v>
       </c>
       <c r="C452" s="40"/>
       <c r="D452" s="40"/>
@@ -22818,23 +22832,23 @@
         <v>34</v>
       </c>
       <c r="B453" s="40" t="s">
-        <v>1976</v>
+        <v>1959</v>
       </c>
       <c r="C453" s="40"/>
       <c r="D453" s="40" t="s">
-        <v>2406</v>
+        <v>2388</v>
       </c>
       <c r="E453" s="40" t="s">
-        <v>2407</v>
+        <v>2389</v>
       </c>
       <c r="F453" s="40" t="s">
-        <v>2408</v>
+        <v>2390</v>
       </c>
       <c r="G453" s="40" t="s">
-        <v>2409</v>
+        <v>2391</v>
       </c>
       <c r="H453" s="41" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="I453" s="2"/>
       <c r="J453" s="6"/>
@@ -22848,7 +22862,7 @@
         <v>34</v>
       </c>
       <c r="B454" s="40" t="s">
-        <v>2411</v>
+        <v>2393</v>
       </c>
       <c r="C454" s="40"/>
       <c r="D454" s="42" t="s">
@@ -22858,13 +22872,13 @@
         <v>1</v>
       </c>
       <c r="F454" s="42" t="s">
-        <v>1928</v>
+        <v>1919</v>
       </c>
       <c r="G454" s="42" t="s">
-        <v>1929</v>
+        <v>1920</v>
       </c>
       <c r="H454" s="41" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="I454" s="2"/>
       <c r="J454" s="6"/>
@@ -22878,23 +22892,23 @@
         <v>32</v>
       </c>
       <c r="B455" s="40" t="s">
-        <v>1977</v>
+        <v>1960</v>
       </c>
       <c r="C455" s="40"/>
       <c r="D455" s="40" t="s">
-        <v>1930</v>
+        <v>1921</v>
       </c>
       <c r="E455" s="40" t="s">
-        <v>1931</v>
+        <v>1922</v>
       </c>
       <c r="F455" s="40" t="s">
-        <v>1932</v>
+        <v>1923</v>
       </c>
       <c r="G455" s="40" t="s">
-        <v>1933</v>
+        <v>1924</v>
       </c>
       <c r="H455" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I455" s="2"/>
       <c r="J455" s="6" t="s">
@@ -22912,23 +22926,23 @@
         <v>32</v>
       </c>
       <c r="B456" s="40" t="s">
-        <v>1978</v>
+        <v>1961</v>
       </c>
       <c r="C456" s="40"/>
       <c r="D456" s="40" t="s">
-        <v>1935</v>
+        <v>1926</v>
       </c>
       <c r="E456" s="40" t="s">
-        <v>1936</v>
+        <v>1927</v>
       </c>
       <c r="F456" s="40" t="s">
-        <v>1937</v>
+        <v>1928</v>
       </c>
       <c r="G456" s="40" t="s">
-        <v>1938</v>
+        <v>1929</v>
       </c>
       <c r="H456" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I456" s="2"/>
       <c r="J456" s="6" t="s">
@@ -22946,23 +22960,23 @@
         <v>32</v>
       </c>
       <c r="B457" s="40" t="s">
-        <v>1979</v>
+        <v>1962</v>
       </c>
       <c r="C457" s="40"/>
       <c r="D457" s="40" t="s">
-        <v>1939</v>
+        <v>1930</v>
       </c>
       <c r="E457" s="40" t="s">
-        <v>1940</v>
+        <v>1931</v>
       </c>
       <c r="F457" s="40" t="s">
-        <v>1941</v>
+        <v>1932</v>
       </c>
       <c r="G457" s="40" t="s">
-        <v>1942</v>
+        <v>1933</v>
       </c>
       <c r="H457" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I457" s="2"/>
       <c r="J457" s="6" t="s">
@@ -22980,23 +22994,23 @@
         <v>32</v>
       </c>
       <c r="B458" s="40" t="s">
-        <v>1980</v>
+        <v>1963</v>
       </c>
       <c r="C458" s="40"/>
       <c r="D458" s="40" t="s">
-        <v>1943</v>
+        <v>1934</v>
       </c>
       <c r="E458" s="40" t="s">
-        <v>1944</v>
+        <v>1935</v>
       </c>
       <c r="F458" s="40" t="s">
-        <v>1945</v>
+        <v>1936</v>
       </c>
       <c r="G458" s="40" t="s">
-        <v>1946</v>
+        <v>1937</v>
       </c>
       <c r="H458" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I458" s="2"/>
       <c r="J458" s="6" t="s">
@@ -23014,23 +23028,23 @@
         <v>32</v>
       </c>
       <c r="B459" s="40" t="s">
-        <v>1981</v>
+        <v>1964</v>
       </c>
       <c r="C459" s="40"/>
       <c r="D459" s="40" t="s">
-        <v>1947</v>
+        <v>1938</v>
       </c>
       <c r="E459" s="40" t="s">
-        <v>1948</v>
+        <v>1939</v>
       </c>
       <c r="F459" s="40" t="s">
-        <v>1949</v>
+        <v>1940</v>
       </c>
       <c r="G459" s="40" t="s">
-        <v>1950</v>
+        <v>1941</v>
       </c>
       <c r="H459" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I459" s="2"/>
       <c r="J459" s="6" t="s">
@@ -23048,23 +23062,23 @@
         <v>32</v>
       </c>
       <c r="B460" s="40" t="s">
-        <v>1982</v>
+        <v>1965</v>
       </c>
       <c r="C460" s="40"/>
       <c r="D460" s="40" t="s">
-        <v>1951</v>
+        <v>1942</v>
       </c>
       <c r="E460" s="40" t="s">
-        <v>1952</v>
+        <v>1943</v>
       </c>
       <c r="F460" s="40" t="s">
-        <v>1953</v>
+        <v>1944</v>
       </c>
       <c r="G460" s="40" t="s">
-        <v>1954</v>
+        <v>1945</v>
       </c>
       <c r="H460" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I460" s="2"/>
       <c r="J460" s="6" t="s">
@@ -23082,23 +23096,23 @@
         <v>32</v>
       </c>
       <c r="B461" s="40" t="s">
-        <v>1983</v>
+        <v>1966</v>
       </c>
       <c r="C461" s="40"/>
       <c r="D461" s="40" t="s">
-        <v>1955</v>
+        <v>1946</v>
       </c>
       <c r="E461" s="40" t="s">
-        <v>1956</v>
+        <v>1947</v>
       </c>
       <c r="F461" s="40" t="s">
-        <v>1957</v>
+        <v>1948</v>
       </c>
       <c r="G461" s="40" t="s">
-        <v>1958</v>
+        <v>1949</v>
       </c>
       <c r="H461" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I461" s="2"/>
       <c r="J461" s="6" t="s">
@@ -23116,23 +23130,23 @@
         <v>32</v>
       </c>
       <c r="B462" s="40" t="s">
-        <v>1984</v>
+        <v>1967</v>
       </c>
       <c r="C462" s="40"/>
       <c r="D462" s="40" t="s">
-        <v>1959</v>
+        <v>1950</v>
       </c>
       <c r="E462" s="40" t="s">
-        <v>1960</v>
+        <v>1951</v>
       </c>
       <c r="F462" s="40" t="s">
-        <v>1961</v>
+        <v>1952</v>
       </c>
       <c r="G462" s="40" t="s">
-        <v>1962</v>
+        <v>1953</v>
       </c>
       <c r="H462" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I462" s="2"/>
       <c r="J462" s="6" t="s">
@@ -23145,12 +23159,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="115.5">
+    <row r="463" spans="1:12" ht="128.25">
       <c r="A463" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B463" s="40" t="s">
-        <v>2421</v>
+        <v>2429</v>
       </c>
       <c r="C463" s="40"/>
       <c r="D463" s="40"/>
@@ -23172,23 +23186,23 @@
         <v>34</v>
       </c>
       <c r="B464" s="40" t="s">
-        <v>1985</v>
+        <v>1968</v>
       </c>
       <c r="C464" s="40"/>
       <c r="D464" s="40" t="s">
-        <v>1963</v>
+        <v>1954</v>
       </c>
       <c r="E464" s="40" t="s">
-        <v>1964</v>
+        <v>1955</v>
       </c>
       <c r="F464" s="40" t="s">
-        <v>2422</v>
+        <v>2403</v>
       </c>
       <c r="G464" s="40" t="s">
-        <v>2423</v>
+        <v>2404</v>
       </c>
       <c r="H464" s="41" t="s">
-        <v>2424</v>
+        <v>2405</v>
       </c>
       <c r="I464" s="2"/>
       <c r="J464" s="6"/>
@@ -23197,28 +23211,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="26.25">
+    <row r="465" spans="1:12" ht="45">
       <c r="A465" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B465" s="40" t="s">
-        <v>2427</v>
+        <v>2406</v>
       </c>
       <c r="C465" s="40"/>
-      <c r="D465" s="40" t="s">
-        <v>1965</v>
-      </c>
-      <c r="E465" s="40" t="s">
-        <v>2426</v>
-      </c>
-      <c r="F465" s="40" t="s">
-        <v>2425</v>
-      </c>
-      <c r="G465" s="40" t="s">
-        <v>1966</v>
-      </c>
-      <c r="H465" s="40" t="s">
-        <v>1967</v>
+      <c r="D465" s="57" t="s">
+        <v>2414</v>
+      </c>
+      <c r="E465" s="57" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F465" s="57" t="s">
+        <v>2412</v>
+      </c>
+      <c r="G465" s="57" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H465" s="57" t="s">
+        <v>2417</v>
       </c>
       <c r="I465" s="2"/>
       <c r="J465" s="6"/>
@@ -23227,28 +23241,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="39">
+    <row r="466" spans="1:12" ht="45">
       <c r="A466" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B466" s="40" t="s">
-        <v>1986</v>
+        <v>1969</v>
       </c>
       <c r="C466" s="40"/>
-      <c r="D466" s="40" t="s">
-        <v>2428</v>
-      </c>
-      <c r="E466" s="40" t="s">
-        <v>2429</v>
-      </c>
-      <c r="F466" s="40" t="s">
-        <v>2430</v>
-      </c>
-      <c r="G466" s="40" t="s">
-        <v>2431</v>
+      <c r="D466" s="56" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E466" s="56" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F466" s="56" t="s">
+        <v>2420</v>
+      </c>
+      <c r="G466" s="56" t="s">
+        <v>2413</v>
       </c>
       <c r="H466" s="41" t="s">
-        <v>1934</v>
+        <v>1925</v>
       </c>
       <c r="I466" s="2"/>
       <c r="J466" s="6"/>
@@ -23262,7 +23276,7 @@
         <v>33</v>
       </c>
       <c r="B467" s="40" t="s">
-        <v>2432</v>
+        <v>2407</v>
       </c>
       <c r="C467" s="40"/>
       <c r="D467" s="40"/>
@@ -23284,23 +23298,23 @@
         <v>34</v>
       </c>
       <c r="B468" s="40" t="s">
-        <v>1987</v>
+        <v>1970</v>
       </c>
       <c r="C468" s="40"/>
       <c r="D468" s="40" t="s">
-        <v>2433</v>
+        <v>2408</v>
       </c>
       <c r="E468" s="40" t="s">
-        <v>2434</v>
+        <v>2409</v>
       </c>
       <c r="F468" s="40" t="s">
-        <v>2435</v>
+        <v>2410</v>
       </c>
       <c r="G468" s="40" t="s">
-        <v>2436</v>
+        <v>2421</v>
       </c>
       <c r="H468" s="41" t="s">
-        <v>1968</v>
+        <v>1956</v>
       </c>
       <c r="I468" s="2"/>
       <c r="J468" s="6"/>
@@ -23314,23 +23328,23 @@
         <v>34</v>
       </c>
       <c r="B469" s="40" t="s">
-        <v>1988</v>
+        <v>1971</v>
       </c>
       <c r="C469" s="40"/>
-      <c r="D469" s="40" t="s">
-        <v>2437</v>
+      <c r="D469" s="57" t="s">
+        <v>2422</v>
       </c>
       <c r="E469" s="40" t="s">
-        <v>2438</v>
-      </c>
-      <c r="F469" s="40" t="s">
-        <v>2439</v>
-      </c>
-      <c r="G469" s="40" t="s">
-        <v>2437</v>
-      </c>
-      <c r="H469" s="41" t="s">
-        <v>1925</v>
+        <v>2411</v>
+      </c>
+      <c r="F469" s="57" t="s">
+        <v>2423</v>
+      </c>
+      <c r="G469" s="57" t="s">
+        <v>2424</v>
+      </c>
+      <c r="H469" s="57" t="s">
+        <v>2425</v>
       </c>
       <c r="I469" s="2"/>
       <c r="J469" s="6"/>
@@ -23339,28 +23353,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="39">
+    <row r="470" spans="1:12" ht="51.75">
       <c r="A470" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B470" s="40" t="s">
-        <v>1989</v>
+        <v>2432</v>
       </c>
       <c r="C470" s="40"/>
-      <c r="D470" s="40" t="s">
-        <v>1969</v>
-      </c>
-      <c r="E470" s="40" t="s">
-        <v>1970</v>
-      </c>
-      <c r="F470" s="40" t="s">
-        <v>1971</v>
-      </c>
-      <c r="G470" s="40" t="s">
-        <v>1972</v>
-      </c>
-      <c r="H470" s="40" t="s">
-        <v>1973</v>
+      <c r="D470" s="56" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E470" s="56" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F470" s="56" t="s">
+        <v>2428</v>
+      </c>
+      <c r="G470" s="56" t="s">
+        <v>2431</v>
+      </c>
+      <c r="H470" s="56" t="s">
+        <v>2430</v>
       </c>
       <c r="I470" s="2"/>
       <c r="J470" s="6"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B536B8B4-F6D1-4E78-9DEA-1A7C61392397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C876D407-43B1-4A52-A1C4-121917D4C53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6882,14 +6882,6 @@
     <t>tacheté long : 6/16 $\quad$ gris court : 3/16 $\quad$ blanc long : 3/16 $\quad$ tacheté court : 2/16 $\quad$ gris long : 1/16 $\quad$ blanc court : 1/16.</t>
   </si>
   <si>
-    <t>Le tableau suivant présente les composantes de la chaîne respiratoire au niveau de la mitochondrie avec les valeurs de potentiel d’oxydoréduction (mV) de chaque composante :
-&lt;br&gt;&lt;img src="/images/SVT22F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>X, Y et Z sont trois gènes de la drosophile. Les fréquences de recombinaison pour deux de ces trois gènes sont indiquées ci-dessous  :
-&lt;br&gt;&lt;img src="/images/SVT22F3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
     <t>G : 34% $\quad$ A : 24,5% $\quad$ T : 24,5%</t>
   </si>
   <si>
@@ -7734,6 +7726,14 @@
 &lt;br&gt;2. Les LT8 sont des LTc détruisant les LT4 infectés.
 &lt;br&gt;3. Le VIH reste présent et inactif car le nombre de LT8 reste important.
 &lt;br&gt;4. La diminution du nombre de LT8 est la conséquence d'une immunodéficience.</t>
+  </si>
+  <si>
+    <t>Le tableau suivant présente les composantes de la chaîne respiratoire au niveau de la mitochondrie avec les valeurs de potentiel d’oxydoréduction (mV) de chaque composante :
+&lt;br&gt;&lt;img src="/images/SVT22Q12.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>X, Y et Z sont trois gènes de la drosophile. Les fréquences de recombinaison pour deux de ces trois gènes sont indiquées ci-dessous  :
+&lt;br&gt;&lt;img src="/images/SVT22Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
 </sst>
 </file>
@@ -14880,7 +14880,7 @@
         <v>33</v>
       </c>
       <c r="B200" s="30" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -14932,7 +14932,7 @@
         <v>33</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>2194</v>
+        <v>2440</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -15018,7 +15018,7 @@
         <v>33</v>
       </c>
       <c r="B205" s="31" t="s">
-        <v>2195</v>
+        <v>2441</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -15074,19 +15074,19 @@
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="30" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E207" s="30" t="s">
+        <v>2195</v>
+      </c>
+      <c r="F207" s="30" t="s">
         <v>2196</v>
       </c>
-      <c r="E207" s="30" t="s">
+      <c r="G207" s="30" t="s">
         <v>2197</v>
       </c>
-      <c r="F207" s="30" t="s">
+      <c r="H207" s="30" t="s">
         <v>2198</v>
-      </c>
-      <c r="G207" s="30" t="s">
-        <v>2199</v>
-      </c>
-      <c r="H207" s="30" t="s">
-        <v>2200</v>
       </c>
       <c r="I207" s="2"/>
       <c r="J207" s="6" t="s">
@@ -15138,7 +15138,7 @@
         <v>33</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -15164,19 +15164,19 @@
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="30" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E210" s="30" t="s">
+        <v>2201</v>
+      </c>
+      <c r="F210" s="30" t="s">
         <v>2202</v>
       </c>
-      <c r="E210" s="30" t="s">
+      <c r="G210" s="30" t="s">
         <v>2203</v>
       </c>
-      <c r="F210" s="30" t="s">
+      <c r="H210" s="30" t="s">
         <v>2204</v>
-      </c>
-      <c r="G210" s="30" t="s">
-        <v>2205</v>
-      </c>
-      <c r="H210" s="30" t="s">
-        <v>2206</v>
       </c>
       <c r="I210" s="2"/>
       <c r="J210" s="6"/>
@@ -15190,23 +15190,23 @@
         <v>32</v>
       </c>
       <c r="B211" s="31" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="31" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E211" s="31" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F211" s="31" t="s">
         <v>2436</v>
       </c>
-      <c r="E211" s="31" t="s">
+      <c r="G211" s="31" t="s">
         <v>2437</v>
       </c>
-      <c r="F211" s="31" t="s">
+      <c r="H211" s="31" t="s">
         <v>2438</v>
-      </c>
-      <c r="G211" s="31" t="s">
-        <v>2439</v>
-      </c>
-      <c r="H211" s="31" t="s">
-        <v>2440</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="6" t="s">
@@ -15224,7 +15224,7 @@
         <v>33</v>
       </c>
       <c r="B212" s="30" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -15276,7 +15276,7 @@
         <v>33</v>
       </c>
       <c r="B214" s="31" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -16092,7 +16092,7 @@
         <v>33</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -16114,7 +16114,7 @@
         <v>34</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="3" t="s">
@@ -16174,7 +16174,7 @@
         <v>34</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="3" t="s">
@@ -16204,7 +16204,7 @@
         <v>34</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="3" t="s">
@@ -17830,7 +17830,7 @@
         <v>33</v>
       </c>
       <c r="B297" s="35" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="C297" s="36"/>
       <c r="D297" s="36"/>
@@ -18100,7 +18100,7 @@
         <v>33</v>
       </c>
       <c r="B305" s="18" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="C305" s="19"/>
       <c r="D305" s="19"/>
@@ -18218,7 +18218,7 @@
         <v>33</v>
       </c>
       <c r="B309" s="18" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="C309" s="19"/>
       <c r="D309" s="19"/>
@@ -18272,7 +18272,7 @@
         <v>33</v>
       </c>
       <c r="B311" s="18" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C311" s="19"/>
       <c r="D311" s="19"/>
@@ -18294,7 +18294,7 @@
         <v>34</v>
       </c>
       <c r="B312" s="20" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="C312" s="21"/>
       <c r="D312" s="22" t="s">
@@ -18380,7 +18380,7 @@
         <v>33</v>
       </c>
       <c r="B315" s="18" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C315" s="19"/>
       <c r="D315" s="19"/>
@@ -18432,7 +18432,7 @@
         <v>33</v>
       </c>
       <c r="B317" s="18" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="C317" s="19"/>
       <c r="D317" s="19"/>
@@ -18484,7 +18484,7 @@
         <v>33</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="C319" s="19"/>
       <c r="D319" s="19"/>
@@ -18618,7 +18618,7 @@
         <v>33</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="C324" s="19"/>
       <c r="D324" s="19"/>
@@ -18866,7 +18866,7 @@
         <v>33</v>
       </c>
       <c r="B332" s="35" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="C332" s="36"/>
       <c r="D332" s="36"/>
@@ -18892,19 +18892,19 @@
       </c>
       <c r="C333" s="27"/>
       <c r="D333" s="28" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E333" s="28" t="s">
         <v>2220</v>
       </c>
-      <c r="E333" s="28" t="s">
+      <c r="F333" s="28" t="s">
+        <v>2221</v>
+      </c>
+      <c r="G333" s="28" t="s">
         <v>2222</v>
       </c>
-      <c r="F333" s="28" t="s">
+      <c r="H333" s="28" t="s">
         <v>2223</v>
-      </c>
-      <c r="G333" s="28" t="s">
-        <v>2224</v>
-      </c>
-      <c r="H333" s="28" t="s">
-        <v>2225</v>
       </c>
       <c r="I333" s="2"/>
       <c r="J333" s="6"/>
@@ -18918,7 +18918,7 @@
         <v>34</v>
       </c>
       <c r="B334" s="23" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="C334" s="24"/>
       <c r="D334" s="25" t="s">
@@ -18978,7 +18978,7 @@
         <v>33</v>
       </c>
       <c r="B336" s="35" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C336" s="36"/>
       <c r="D336" s="36"/>
@@ -19060,7 +19060,7 @@
         <v>33</v>
       </c>
       <c r="B339" s="35" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="C339" s="36"/>
       <c r="D339" s="36"/>
@@ -19086,19 +19086,19 @@
       </c>
       <c r="C340" s="37"/>
       <c r="D340" s="25" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E340" s="25" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F340" s="25" t="s">
         <v>2229</v>
       </c>
-      <c r="E340" s="25" t="s">
+      <c r="G340" s="25" t="s">
         <v>2230</v>
       </c>
-      <c r="F340" s="25" t="s">
+      <c r="H340" s="25" t="s">
         <v>2231</v>
-      </c>
-      <c r="G340" s="25" t="s">
-        <v>2232</v>
-      </c>
-      <c r="H340" s="25" t="s">
-        <v>2233</v>
       </c>
       <c r="I340" s="2"/>
       <c r="J340" s="6"/>
@@ -19116,19 +19116,19 @@
       </c>
       <c r="C341" s="29"/>
       <c r="D341" s="25" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E341" s="25" t="s">
+        <v>2233</v>
+      </c>
+      <c r="F341" s="25" t="s">
         <v>2234</v>
       </c>
-      <c r="E341" s="25" t="s">
+      <c r="G341" s="25" t="s">
         <v>2235</v>
       </c>
-      <c r="F341" s="25" t="s">
+      <c r="H341" s="25" t="s">
         <v>2236</v>
-      </c>
-      <c r="G341" s="25" t="s">
-        <v>2237</v>
-      </c>
-      <c r="H341" s="25" t="s">
-        <v>2238</v>
       </c>
       <c r="I341" s="2"/>
       <c r="J341" s="6"/>
@@ -19146,19 +19146,19 @@
       </c>
       <c r="C342" s="37"/>
       <c r="D342" s="25" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E342" s="25" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F342" s="25" t="s">
         <v>2239</v>
       </c>
-      <c r="E342" s="25" t="s">
+      <c r="G342" s="25" t="s">
         <v>2240</v>
       </c>
-      <c r="F342" s="25" t="s">
+      <c r="H342" s="25" t="s">
         <v>2241</v>
-      </c>
-      <c r="G342" s="25" t="s">
-        <v>2242</v>
-      </c>
-      <c r="H342" s="25" t="s">
-        <v>2243</v>
       </c>
       <c r="I342" s="2"/>
       <c r="J342" s="6"/>
@@ -19412,7 +19412,7 @@
         <v>32</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="3" t="s">
@@ -19572,7 +19572,7 @@
         <v>89</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="I354" s="3" t="s">
         <v>91</v>
@@ -20024,7 +20024,7 @@
         <v>32</v>
       </c>
       <c r="B367" s="26" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="C367" s="29" t="s">
         <v>1088</v>
@@ -20404,7 +20404,7 @@
         <v>33</v>
       </c>
       <c r="B379" s="18" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="C379" s="19"/>
       <c r="D379" s="19"/>
@@ -20430,22 +20430,22 @@
       </c>
       <c r="C380" s="24"/>
       <c r="D380" s="25" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E380" s="25" t="s">
+        <v>2249</v>
+      </c>
+      <c r="F380" s="25" t="s">
+        <v>2247</v>
+      </c>
+      <c r="G380" s="25" t="s">
         <v>2248</v>
       </c>
-      <c r="E380" s="25" t="s">
-        <v>2251</v>
-      </c>
-      <c r="F380" s="25" t="s">
+      <c r="H380" s="25" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I380" s="25" t="s">
         <v>2249</v>
-      </c>
-      <c r="G380" s="25" t="s">
-        <v>2250</v>
-      </c>
-      <c r="H380" s="25" t="s">
-        <v>2252</v>
-      </c>
-      <c r="I380" s="25" t="s">
-        <v>2251</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
@@ -20490,7 +20490,7 @@
         <v>33</v>
       </c>
       <c r="B382" s="18" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="C382" s="19"/>
       <c r="D382" s="19"/>
@@ -20576,7 +20576,7 @@
         <v>33</v>
       </c>
       <c r="B385" s="18" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="C385" s="19" t="s">
         <v>944</v>
@@ -20632,7 +20632,7 @@
         <v>33</v>
       </c>
       <c r="B387" s="18" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="C387" s="19" t="s">
         <v>945</v>
@@ -20752,7 +20752,7 @@
         <v>34</v>
       </c>
       <c r="B391" s="23" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C391" s="24"/>
       <c r="D391" s="25" t="s">
@@ -20784,7 +20784,7 @@
         <v>33</v>
       </c>
       <c r="B392" s="53" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C392" s="19" t="s">
         <v>946</v>
@@ -20872,7 +20872,7 @@
         <v>32</v>
       </c>
       <c r="B395" s="38" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" s="38" t="s">
@@ -21052,7 +21052,7 @@
         <v>32</v>
       </c>
       <c r="B400" s="39" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="39" t="s">
@@ -21160,7 +21160,7 @@
         <v>32</v>
       </c>
       <c r="B403" s="38" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" s="38" t="s">
@@ -21196,7 +21196,7 @@
         <v>32</v>
       </c>
       <c r="B404" s="39" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="39" t="s">
@@ -21232,7 +21232,7 @@
         <v>32</v>
       </c>
       <c r="B405" s="38" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="38" t="s">
@@ -21304,7 +21304,7 @@
         <v>32</v>
       </c>
       <c r="B407" s="38" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" s="38" t="s">
@@ -21340,7 +21340,7 @@
         <v>32</v>
       </c>
       <c r="B408" s="39" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="39" t="s">
@@ -21380,22 +21380,22 @@
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="3" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="E409" s="3" t="s">
+        <v>2265</v>
+      </c>
+      <c r="F409" s="3" t="s">
+        <v>2266</v>
+      </c>
+      <c r="G409" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H409" s="3" t="s">
         <v>2267</v>
       </c>
-      <c r="F409" s="3" t="s">
-        <v>2268</v>
-      </c>
-      <c r="G409" s="3" t="s">
-        <v>2263</v>
-      </c>
-      <c r="H409" s="3" t="s">
-        <v>2269</v>
-      </c>
       <c r="I409" s="3" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="J409" s="13" t="s">
         <v>10</v>
@@ -21752,7 +21752,7 @@
         <v>244</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="I419" s="3" t="s">
         <v>237</v>
@@ -21815,10 +21815,10 @@
         <v>207</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>249</v>
@@ -21844,23 +21844,23 @@
         <v>32</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" s="3" t="s">
         <v>250</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>255</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="I422" s="3" t="s">
         <v>256</v>
@@ -21880,26 +21880,26 @@
         <v>32</v>
       </c>
       <c r="B423" s="51" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="C423" s="49"/>
       <c r="D423" s="38" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E423" s="38" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F423" s="38" t="s">
         <v>2277</v>
       </c>
-      <c r="E423" s="38" t="s">
+      <c r="G423" s="38" t="s">
         <v>2278</v>
       </c>
-      <c r="F423" s="38" t="s">
+      <c r="H423" s="38" t="s">
         <v>2279</v>
       </c>
-      <c r="G423" s="38" t="s">
-        <v>2280</v>
-      </c>
-      <c r="H423" s="38" t="s">
-        <v>2281</v>
-      </c>
       <c r="I423" s="38" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="J423" s="11" t="s">
         <v>11</v>
@@ -21916,26 +21916,26 @@
         <v>32</v>
       </c>
       <c r="B424" s="52" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="C424" s="50"/>
       <c r="D424" s="39" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E424" s="39" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F424" s="39" t="s">
         <v>2282</v>
       </c>
-      <c r="E424" s="39" t="s">
+      <c r="G424" s="39" t="s">
         <v>2283</v>
       </c>
-      <c r="F424" s="39" t="s">
-        <v>2284</v>
-      </c>
-      <c r="G424" s="39" t="s">
-        <v>2285</v>
-      </c>
       <c r="H424" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I424" s="39" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="J424" s="11" t="s">
         <v>11</v>
@@ -21952,26 +21952,26 @@
         <v>32</v>
       </c>
       <c r="B425" s="51" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="C425" s="49"/>
       <c r="D425" s="38" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E425" s="38" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F425" s="38" t="s">
         <v>2286</v>
       </c>
-      <c r="E425" s="38" t="s">
+      <c r="G425" s="38" t="s">
         <v>2287</v>
       </c>
-      <c r="F425" s="38" t="s">
-        <v>2288</v>
-      </c>
-      <c r="G425" s="38" t="s">
-        <v>2289</v>
-      </c>
       <c r="H425" s="38" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I425" s="38" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="J425" s="11" t="s">
         <v>11</v>
@@ -21988,26 +21988,26 @@
         <v>32</v>
       </c>
       <c r="B426" s="52" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="C426" s="50"/>
       <c r="D426" s="39" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E426" s="39" t="s">
+        <v>2289</v>
+      </c>
+      <c r="F426" s="39" t="s">
         <v>2290</v>
       </c>
-      <c r="E426" s="39" t="s">
+      <c r="G426" s="39" t="s">
         <v>2291</v>
       </c>
-      <c r="F426" s="39" t="s">
-        <v>2292</v>
-      </c>
-      <c r="G426" s="39" t="s">
-        <v>2293</v>
-      </c>
       <c r="H426" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I426" s="39" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="J426" s="11" t="s">
         <v>11</v>
@@ -22024,26 +22024,26 @@
         <v>32</v>
       </c>
       <c r="B427" s="51" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="C427" s="49"/>
       <c r="D427" s="38" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E427" s="38" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F427" s="38" t="s">
         <v>2294</v>
       </c>
-      <c r="E427" s="38" t="s">
+      <c r="G427" s="38" t="s">
         <v>2295</v>
       </c>
-      <c r="F427" s="38" t="s">
-        <v>2296</v>
-      </c>
-      <c r="G427" s="38" t="s">
-        <v>2297</v>
-      </c>
       <c r="H427" s="38" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I427" s="38" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="J427" s="11" t="s">
         <v>11</v>
@@ -22060,26 +22060,26 @@
         <v>32</v>
       </c>
       <c r="B428" s="52" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="C428" s="50"/>
       <c r="D428" s="39" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E428" s="39" t="s">
+        <v>2297</v>
+      </c>
+      <c r="F428" s="39" t="s">
         <v>2298</v>
       </c>
-      <c r="E428" s="39" t="s">
+      <c r="G428" s="39" t="s">
         <v>2299</v>
       </c>
-      <c r="F428" s="39" t="s">
-        <v>2300</v>
-      </c>
-      <c r="G428" s="39" t="s">
-        <v>2301</v>
-      </c>
       <c r="H428" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I428" s="39" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="J428" s="11" t="s">
         <v>11</v>
@@ -22096,26 +22096,26 @@
         <v>32</v>
       </c>
       <c r="B429" s="51" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="C429" s="49"/>
       <c r="D429" s="38" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E429" s="38" t="s">
+        <v>2301</v>
+      </c>
+      <c r="F429" s="38" t="s">
         <v>2302</v>
       </c>
-      <c r="E429" s="38" t="s">
+      <c r="G429" s="38" t="s">
         <v>2303</v>
       </c>
-      <c r="F429" s="38" t="s">
-        <v>2304</v>
-      </c>
-      <c r="G429" s="38" t="s">
-        <v>2305</v>
-      </c>
       <c r="H429" s="38" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I429" s="38" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="J429" s="11" t="s">
         <v>11</v>
@@ -22132,26 +22132,26 @@
         <v>32</v>
       </c>
       <c r="B430" s="52" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="C430" s="50"/>
       <c r="D430" s="39" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E430" s="39" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F430" s="39" t="s">
         <v>2306</v>
       </c>
-      <c r="E430" s="39" t="s">
+      <c r="G430" s="39" t="s">
         <v>2307</v>
       </c>
-      <c r="F430" s="39" t="s">
-        <v>2308</v>
-      </c>
-      <c r="G430" s="39" t="s">
-        <v>2309</v>
-      </c>
       <c r="H430" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I430" s="39" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="J430" s="11" t="s">
         <v>11</v>
@@ -22168,26 +22168,26 @@
         <v>32</v>
       </c>
       <c r="B431" s="51" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="C431" s="49"/>
       <c r="D431" s="38" t="s">
+        <v>2308</v>
+      </c>
+      <c r="E431" s="38" t="s">
+        <v>2309</v>
+      </c>
+      <c r="F431" s="38" t="s">
         <v>2310</v>
       </c>
-      <c r="E431" s="38" t="s">
+      <c r="G431" s="38" t="s">
         <v>2311</v>
       </c>
-      <c r="F431" s="38" t="s">
-        <v>2312</v>
-      </c>
-      <c r="G431" s="38" t="s">
-        <v>2313</v>
-      </c>
       <c r="H431" s="38" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I431" s="38" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="J431" s="11" t="s">
         <v>11</v>
@@ -22204,26 +22204,26 @@
         <v>32</v>
       </c>
       <c r="B432" s="52" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="C432" s="50"/>
       <c r="D432" s="39" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E432" s="39" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F432" s="39" t="s">
         <v>2314</v>
       </c>
-      <c r="E432" s="39" t="s">
+      <c r="G432" s="39" t="s">
         <v>2315</v>
       </c>
-      <c r="F432" s="39" t="s">
-        <v>2316</v>
-      </c>
-      <c r="G432" s="39" t="s">
-        <v>2317</v>
-      </c>
       <c r="H432" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I432" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="J432" s="11" t="s">
         <v>11</v>
@@ -22240,26 +22240,26 @@
         <v>32</v>
       </c>
       <c r="B433" s="51" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="C433" s="49"/>
       <c r="D433" s="38" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E433" s="38" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F433" s="38" t="s">
         <v>2318</v>
       </c>
-      <c r="E433" s="38" t="s">
+      <c r="G433" s="38" t="s">
         <v>2319</v>
       </c>
-      <c r="F433" s="38" t="s">
-        <v>2320</v>
-      </c>
-      <c r="G433" s="38" t="s">
-        <v>2321</v>
-      </c>
       <c r="H433" s="38" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I433" s="38" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="J433" s="11" t="s">
         <v>11</v>
@@ -22276,26 +22276,26 @@
         <v>32</v>
       </c>
       <c r="B434" s="52" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="C434" s="50"/>
       <c r="D434" s="39" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E434" s="39" t="s">
+        <v>2321</v>
+      </c>
+      <c r="F434" s="39" t="s">
         <v>2322</v>
       </c>
-      <c r="E434" s="39" t="s">
+      <c r="G434" s="39" t="s">
         <v>2323</v>
       </c>
-      <c r="F434" s="39" t="s">
-        <v>2324</v>
-      </c>
-      <c r="G434" s="39" t="s">
-        <v>2325</v>
-      </c>
       <c r="H434" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I434" s="39" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="J434" s="11" t="s">
         <v>11</v>
@@ -22312,26 +22312,26 @@
         <v>32</v>
       </c>
       <c r="B435" s="51" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="C435" s="49"/>
       <c r="D435" s="38" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E435" s="38" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F435" s="38" t="s">
         <v>2326</v>
       </c>
-      <c r="E435" s="38" t="s">
+      <c r="G435" s="38" t="s">
         <v>2327</v>
       </c>
-      <c r="F435" s="38" t="s">
-        <v>2328</v>
-      </c>
-      <c r="G435" s="38" t="s">
-        <v>2329</v>
-      </c>
       <c r="H435" s="38" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I435" s="38" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="J435" s="11" t="s">
         <v>11</v>
@@ -22348,26 +22348,26 @@
         <v>32</v>
       </c>
       <c r="B436" s="52" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="C436" s="50"/>
       <c r="D436" s="39" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E436" s="39" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F436" s="39" t="s">
         <v>2330</v>
       </c>
-      <c r="E436" s="39" t="s">
+      <c r="G436" s="39" t="s">
         <v>2331</v>
       </c>
-      <c r="F436" s="39" t="s">
-        <v>2332</v>
-      </c>
-      <c r="G436" s="39" t="s">
-        <v>2333</v>
-      </c>
       <c r="H436" s="39" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="I436" s="39" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="J436" s="11" t="s">
         <v>11</v>
@@ -22384,7 +22384,7 @@
         <v>33</v>
       </c>
       <c r="B437" s="40" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
@@ -22406,20 +22406,20 @@
         <v>34</v>
       </c>
       <c r="B438" s="54" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="C438" s="40"/>
       <c r="D438" s="54" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E438" s="54" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F438" s="54" t="s">
         <v>2348</v>
       </c>
-      <c r="E438" s="54" t="s">
-        <v>2349</v>
-      </c>
-      <c r="F438" s="54" t="s">
-        <v>2350</v>
-      </c>
       <c r="G438" s="54" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="H438" s="54" t="s">
         <v>1911</v>
@@ -22436,20 +22436,20 @@
         <v>34</v>
       </c>
       <c r="B439" s="55" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="C439" s="40"/>
       <c r="D439" s="55" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E439" s="55" t="s">
+        <v>2350</v>
+      </c>
+      <c r="F439" s="55" t="s">
         <v>2351</v>
       </c>
-      <c r="E439" s="55" t="s">
+      <c r="G439" s="55" t="s">
         <v>2352</v>
-      </c>
-      <c r="F439" s="55" t="s">
-        <v>2353</v>
-      </c>
-      <c r="G439" s="55" t="s">
-        <v>2354</v>
       </c>
       <c r="H439" s="55" t="s">
         <v>1911</v>
@@ -22466,20 +22466,20 @@
         <v>34</v>
       </c>
       <c r="B440" s="54" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="C440" s="40"/>
       <c r="D440" s="54" t="s">
+        <v>2353</v>
+      </c>
+      <c r="E440" s="54" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F440" s="54" t="s">
         <v>2355</v>
       </c>
-      <c r="E440" s="54" t="s">
+      <c r="G440" s="54" t="s">
         <v>2356</v>
-      </c>
-      <c r="F440" s="54" t="s">
-        <v>2357</v>
-      </c>
-      <c r="G440" s="54" t="s">
-        <v>2358</v>
       </c>
       <c r="H440" s="54" t="s">
         <v>1911</v>
@@ -22500,16 +22500,16 @@
       </c>
       <c r="C441" s="40"/>
       <c r="D441" s="55" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E441" s="55" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F441" s="55" t="s">
         <v>2359</v>
       </c>
-      <c r="E441" s="55" t="s">
+      <c r="G441" s="55" t="s">
         <v>2360</v>
-      </c>
-      <c r="F441" s="55" t="s">
-        <v>2361</v>
-      </c>
-      <c r="G441" s="55" t="s">
-        <v>2362</v>
       </c>
       <c r="H441" s="55" t="s">
         <v>1911</v>
@@ -22526,7 +22526,7 @@
         <v>33</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="C442" s="40"/>
       <c r="D442" s="40"/>
@@ -22548,20 +22548,20 @@
         <v>34</v>
       </c>
       <c r="B443" s="55" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="C443" s="40"/>
       <c r="D443" s="55" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E443" s="55" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F443" s="55" t="s">
         <v>2366</v>
       </c>
-      <c r="E443" s="55" t="s">
+      <c r="G443" s="55" t="s">
         <v>2367</v>
-      </c>
-      <c r="F443" s="55" t="s">
-        <v>2368</v>
-      </c>
-      <c r="G443" s="55" t="s">
-        <v>2369</v>
       </c>
       <c r="H443" s="55" t="s">
         <v>1911</v>
@@ -22578,20 +22578,20 @@
         <v>34</v>
       </c>
       <c r="B444" s="54" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="C444" s="40"/>
       <c r="D444" s="54" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E444" s="54" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F444" s="54" t="s">
         <v>2370</v>
       </c>
-      <c r="E444" s="54" t="s">
+      <c r="G444" s="54" t="s">
         <v>2371</v>
-      </c>
-      <c r="F444" s="54" t="s">
-        <v>2372</v>
-      </c>
-      <c r="G444" s="54" t="s">
-        <v>2373</v>
       </c>
       <c r="H444" s="54" t="s">
         <v>1911</v>
@@ -22608,20 +22608,20 @@
         <v>34</v>
       </c>
       <c r="B445" s="55" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="C445" s="40"/>
       <c r="D445" s="55" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E445" s="55" t="s">
+        <v>2373</v>
+      </c>
+      <c r="F445" s="55" t="s">
         <v>2374</v>
       </c>
-      <c r="E445" s="55" t="s">
+      <c r="G445" s="55" t="s">
         <v>2375</v>
-      </c>
-      <c r="F445" s="55" t="s">
-        <v>2376</v>
-      </c>
-      <c r="G445" s="55" t="s">
-        <v>2377</v>
       </c>
       <c r="H445" s="55" t="s">
         <v>1911</v>
@@ -22638,20 +22638,20 @@
         <v>34</v>
       </c>
       <c r="B446" s="54" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="C446" s="40"/>
       <c r="D446" s="54" t="s">
+        <v>2376</v>
+      </c>
+      <c r="E446" s="54" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F446" s="54" t="s">
         <v>2378</v>
       </c>
-      <c r="E446" s="54" t="s">
+      <c r="G446" s="54" t="s">
         <v>2379</v>
-      </c>
-      <c r="F446" s="54" t="s">
-        <v>2380</v>
-      </c>
-      <c r="G446" s="54" t="s">
-        <v>2381</v>
       </c>
       <c r="H446" s="54" t="s">
         <v>1911</v>
@@ -22668,7 +22668,7 @@
         <v>33</v>
       </c>
       <c r="B447" s="40" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="C447" s="40"/>
       <c r="D447" s="40"/>
@@ -22720,7 +22720,7 @@
         <v>34</v>
       </c>
       <c r="B449" s="40" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C449" s="40"/>
       <c r="D449" s="42" t="s">
@@ -22750,20 +22750,20 @@
         <v>34</v>
       </c>
       <c r="B450" s="40" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="C450" s="40"/>
       <c r="D450" s="40" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E450" s="40" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F450" s="40" t="s">
+        <v>2383</v>
+      </c>
+      <c r="G450" s="40" t="s">
         <v>2384</v>
-      </c>
-      <c r="E450" s="40" t="s">
-        <v>2395</v>
-      </c>
-      <c r="F450" s="40" t="s">
-        <v>2385</v>
-      </c>
-      <c r="G450" s="40" t="s">
-        <v>2386</v>
       </c>
       <c r="H450" s="41" t="s">
         <v>1916</v>
@@ -22780,7 +22780,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="40" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="C451" s="40"/>
       <c r="D451" s="42">
@@ -22810,7 +22810,7 @@
         <v>33</v>
       </c>
       <c r="B452" s="40" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="C452" s="40"/>
       <c r="D452" s="40"/>
@@ -22836,16 +22836,16 @@
       </c>
       <c r="C453" s="40"/>
       <c r="D453" s="40" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E453" s="40" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F453" s="40" t="s">
         <v>2388</v>
       </c>
-      <c r="E453" s="40" t="s">
+      <c r="G453" s="40" t="s">
         <v>2389</v>
-      </c>
-      <c r="F453" s="40" t="s">
-        <v>2390</v>
-      </c>
-      <c r="G453" s="40" t="s">
-        <v>2391</v>
       </c>
       <c r="H453" s="41" t="s">
         <v>1916</v>
@@ -22862,7 +22862,7 @@
         <v>34</v>
       </c>
       <c r="B454" s="40" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C454" s="40"/>
       <c r="D454" s="42" t="s">
@@ -23164,7 +23164,7 @@
         <v>33</v>
       </c>
       <c r="B463" s="40" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="C463" s="40"/>
       <c r="D463" s="40"/>
@@ -23196,13 +23196,13 @@
         <v>1955</v>
       </c>
       <c r="F464" s="40" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G464" s="40" t="s">
+        <v>2402</v>
+      </c>
+      <c r="H464" s="41" t="s">
         <v>2403</v>
-      </c>
-      <c r="G464" s="40" t="s">
-        <v>2404</v>
-      </c>
-      <c r="H464" s="41" t="s">
-        <v>2405</v>
       </c>
       <c r="I464" s="2"/>
       <c r="J464" s="6"/>
@@ -23216,23 +23216,23 @@
         <v>34</v>
       </c>
       <c r="B465" s="40" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C465" s="40"/>
       <c r="D465" s="57" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E465" s="57" t="s">
+        <v>2413</v>
+      </c>
+      <c r="F465" s="57" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G465" s="57" t="s">
         <v>2414</v>
       </c>
-      <c r="E465" s="57" t="s">
+      <c r="H465" s="57" t="s">
         <v>2415</v>
-      </c>
-      <c r="F465" s="57" t="s">
-        <v>2412</v>
-      </c>
-      <c r="G465" s="57" t="s">
-        <v>2416</v>
-      </c>
-      <c r="H465" s="57" t="s">
-        <v>2417</v>
       </c>
       <c r="I465" s="2"/>
       <c r="J465" s="6"/>
@@ -23250,16 +23250,16 @@
       </c>
       <c r="C466" s="40"/>
       <c r="D466" s="56" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E466" s="56" t="s">
+        <v>2417</v>
+      </c>
+      <c r="F466" s="56" t="s">
         <v>2418</v>
       </c>
-      <c r="E466" s="56" t="s">
-        <v>2419</v>
-      </c>
-      <c r="F466" s="56" t="s">
-        <v>2420</v>
-      </c>
       <c r="G466" s="56" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="H466" s="41" t="s">
         <v>1925</v>
@@ -23276,7 +23276,7 @@
         <v>33</v>
       </c>
       <c r="B467" s="40" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="C467" s="40"/>
       <c r="D467" s="40"/>
@@ -23302,16 +23302,16 @@
       </c>
       <c r="C468" s="40"/>
       <c r="D468" s="40" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E468" s="40" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F468" s="40" t="s">
         <v>2408</v>
       </c>
-      <c r="E468" s="40" t="s">
-        <v>2409</v>
-      </c>
-      <c r="F468" s="40" t="s">
-        <v>2410</v>
-      </c>
       <c r="G468" s="40" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="H468" s="41" t="s">
         <v>1956</v>
@@ -23332,19 +23332,19 @@
       </c>
       <c r="C469" s="40"/>
       <c r="D469" s="57" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E469" s="40" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F469" s="57" t="s">
+        <v>2421</v>
+      </c>
+      <c r="G469" s="57" t="s">
         <v>2422</v>
       </c>
-      <c r="E469" s="40" t="s">
-        <v>2411</v>
-      </c>
-      <c r="F469" s="57" t="s">
+      <c r="H469" s="57" t="s">
         <v>2423</v>
-      </c>
-      <c r="G469" s="57" t="s">
-        <v>2424</v>
-      </c>
-      <c r="H469" s="57" t="s">
-        <v>2425</v>
       </c>
       <c r="I469" s="2"/>
       <c r="J469" s="6"/>
@@ -23358,23 +23358,23 @@
         <v>34</v>
       </c>
       <c r="B470" s="40" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="C470" s="40"/>
       <c r="D470" s="56" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E470" s="56" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F470" s="56" t="s">
         <v>2426</v>
       </c>
-      <c r="E470" s="56" t="s">
-        <v>2427</v>
-      </c>
-      <c r="F470" s="56" t="s">
+      <c r="G470" s="56" t="s">
+        <v>2429</v>
+      </c>
+      <c r="H470" s="56" t="s">
         <v>2428</v>
-      </c>
-      <c r="G470" s="56" t="s">
-        <v>2431</v>
-      </c>
-      <c r="H470" s="56" t="s">
-        <v>2430</v>
       </c>
       <c r="I470" s="2"/>
       <c r="J470" s="6"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C876D407-43B1-4A52-A1C4-121917D4C53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811A664E-2C9A-4AF1-80BC-7DC878D76620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7688,12 +7688,6 @@
 &lt;br&gt;&lt;img src="/images/SVT2022F1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
   <si>
-    <t>Le Phénylthiocarbamide (PTC), a un goût très amer pour certaines personnes et aucun goût pour d’autres.
-Dans une population, soumise à la loi de Hardy Weinberg, on a 70 % des individus sensibles au goût amer du PTC, sachant que la sensibilité à la PTC est liée à un allèle dominant S et l'insensibilité à cette substance est liée à l'allèle récessif s. 
-&lt;br&gt;On donne : $\sqrt{0,20}\ =\ 0,45\$; $\quad$  $\sqrt{0,30}\ =\ 0,55\$; $\quad$ $\sqrt{0,70}\ =\ 0,83$
-Quelles sont les fréquences des allèles et des génotypes dans cette population (on a considéré deux chiffres après la virgule) ?</t>
-  </si>
-  <si>
     <t>Un laboratoire d’analyses effectue la réaction immunitaire suivante :
 &lt;br&gt; 1ère étape : sur une lame de verre, on dépose une goutte de sérum dans chacune des cases :
 &lt;br&gt;   - case 1 : sérum d’un animal atteint de la mononucléose infectieuse.
@@ -7734,6 +7728,12 @@
   <si>
     <t>X, Y et Z sont trois gènes de la drosophile. Les fréquences de recombinaison pour deux de ces trois gènes sont indiquées ci-dessous  :
 &lt;br&gt;&lt;img src="/images/SVT22Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>Le Phénylthiocarbamide (PTC), a un goût très amer pour certaines personnes et aucun goût pour d’autres.
+Dans une population, soumise à la loi de Hardy Weinberg, on a 70 % des individus sensibles au goût amer du PTC, sachant que la sensibilité à la PTC est liée à un allèle dominant S et l'insensibilité à cette substance est liée à l'allèle récessif s. 
+&lt;br&gt;On donne : $\sqrt{0,20} = 0,45$ ; $\quad \sqrt{0,30} = 0,55$ ; $\quad \sqrt{0,70} = 0,83$
+&lt;br&gt;Quelles sont les fréquences des allèles et des génotypes dans cette population (on a considéré deux chiffres après la virgule) ?</t>
   </si>
 </sst>
 </file>
@@ -14932,7 +14932,7 @@
         <v>33</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -15018,7 +15018,7 @@
         <v>33</v>
       </c>
       <c r="B205" s="31" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -15185,28 +15185,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="142.5">
+    <row r="211" spans="1:12" ht="156.75">
       <c r="A211" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B211" s="31" t="s">
-        <v>2432</v>
+        <v>2441</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="31" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E211" s="31" t="s">
         <v>2434</v>
       </c>
-      <c r="E211" s="31" t="s">
+      <c r="F211" s="31" t="s">
         <v>2435</v>
       </c>
-      <c r="F211" s="31" t="s">
+      <c r="G211" s="31" t="s">
         <v>2436</v>
       </c>
-      <c r="G211" s="31" t="s">
+      <c r="H211" s="31" t="s">
         <v>2437</v>
-      </c>
-      <c r="H211" s="31" t="s">
-        <v>2438</v>
       </c>
       <c r="I211" s="2"/>
       <c r="J211" s="6" t="s">
@@ -15224,7 +15224,7 @@
         <v>33</v>
       </c>
       <c r="B212" s="30" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -15276,7 +15276,7 @@
         <v>33</v>
       </c>
       <c r="B214" s="31" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>

--- a/Template_Questions.xlsx
+++ b/Template_Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811A664E-2C9A-4AF1-80BC-7DC878D76620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CC9883-8790-4901-B8B3-A00BDFD0BB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3458,41 +3458,13 @@
     <t xml:space="preserve"> À la fin du régime transitoire de la charge du condensateur de capacité $C_{1}$, la tension aux bornes du condensateur de capacité $C_{2}$ est :</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Ondes à la surface de l'eau (5 points)&lt;/b&gt;&lt;/center&gt;
-Sur la surface de l'eau contenue dans une cuve à ondes, on crée à l'instant $t_{0}=0$, une onde progressive sinusoïdale de fréquence $N$, en un point $S$ à l'aide d'une pointe liée à un vibreur. Cette onde se propage sans amortissement et sans réflexion avec une vitesse constante. Le document représente une section de la surface de l'eau suivant un plan vertical passant par le point $S$ à un instant $t_1$.
-L'élongation de la source est : $y_{s}(t) = 10^{-2} \cdot \sin(100\cdot\pi t)$ (m).
-Données : $N = 50\text{ Hz}$ ; $AB = 10\text{ cm}$.
-</t>
-  </si>
-  <si>
     <t>La valeur de l'instant $t_1$ est :</t>
   </si>
   <si>
-    <t>On considère un point $P$ de la surface de l'eau. À l'instant $t_1$, $P$ appartient à la crête numéro 4.
-L'élongation du point $P$ à l'instant $t$ est :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Diffraction de la lumière par une fente (4 points)&lt;/b&gt;&lt;/center&gt;
-On réalise la diffraction de la lumière en utilisant un dispositif de diffraction par une fente de largeur $a$. On réalise dans l'air, quatre expériences en utilisant deux lasers produisant deux radiations de longueurs d'onde respectives $\lambda_{1}$ et $\lambda_{2}$.
-Expérience 1 : $\lambda_{1}$, $a_{1}=a$, $D$, $l_{1}=3,2\text{ cm}$, $\theta_{1}=10^{-2}\text{ rad}$
-Expérience 2 : $\lambda_{2}=632,8\text{ nm}$, $a_{2}=a$, $D$, $l_{2}=5,0\text{ cm}$, $\theta_{2}$
-Expérience 3 : $\lambda_{2}=632,8\text{ nm}$, $a_{3}=\dfrac{a}{2}$, $D$, $l_{3}=2 \cdot l_{2}$, $\theta_{3}$
-Expérience 4 : $\lambda_{2}=632,8\text{ nm}$, $a_{4}=2a$, $D$, $l_{4}=\dfrac{l_{2}}{2}$, $\theta_{4}$
-Données : $\tan \theta \approx \theta \text{ (rad)}$ ; $\dfrac{632,8 \times 3,2}{2} \approx 10^3$.
-</t>
-  </si>
-  <si>
     <t>La valeur de la largeur $a$ de la fente est :</t>
   </si>
   <si>
     <t>Les écarts angulaires de diffraction dans les quatre expériences sont tels que :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Radioactivité du thorium (6 points)&lt;/b&gt;&lt;/center&gt;
-Le noyau de thorium $\ce{^{230}_{90}Th}$ subit une série de désintégrations successives de types $\alpha$ et $\beta^{-}$ qui conduisent à la formation du noyau de plomb $\ce{^{206}_{82}Pb}$, stable. L'équation globale s'écrit :
-$$\ce{^{230}_{90}Th -&gt; ^{206}_{82}Pb} + x\alpha + y\beta^{-}$$On dispose d'un échantillon contenant $N_{0}$ noyaux de thorium à l'instant $t_{0}=0$. L'échantillon contient à un instant $t$, après une série de désintégrations, $0,25\text{ mmol}$ de thorium $\ce{Th}$ et $0,75\text{ mmol}$ de $\ce{^{206}_{82}Pb}$.
-Données : Constante radioactive du thorium : $\lambda = 8,7 \cdot 10^{-6}\text{ ans}^{-1}$ ; $\ln 2 = 0,7$.
-</t>
   </si>
   <si>
     <t>Les valeurs de $x$ et $y$ sont :</t>
@@ -6232,12 +6204,6 @@
     <t>$v_{max}=0,28\text{ m}\cdot\text{s}^{-1}$</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Charge et décharge d'un condensateur (7 points)&lt;/b&gt;&lt;/center&gt;
-On considère le montage schématisé sur la figure suivante. À l'instant $t_{0}=0$, on place l'interrupteur K en position (1). Un système d'acquisition donne l'expression numérique de l'intensité du courant qui circule dans le circuit : $i(t) = 6 \cdot 10^{-3} \cdot e^{-1000 t}\text{ (A)}$.
-Données : $E = 6,0\text{ V}$ ; $R = 0,95\text{ k}\Omega$.
-</t>
-  </si>
-  <si>
     <t>Les valeurs de la résistance r et de la capacité C sont :</t>
   </si>
   <si>
@@ -6247,15 +6213,6 @@
     <t xml:space="preserve"> La valeur de la tension aux bornes du conducteur ohmique de résistance R à $t_{0}=0$ est :</t>
   </si>
   <si>
-    <t>Lorsque le condensateur devient totalement chargé, on bascule K en position (2), à un instant  pris comme nouvelle origine des dates ($t_{0}=0$). 
-L'expression numérique de la tension aux bornes du condensateur est :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&lt;Réponse d'un dipôle RL (7 points)&lt;/b&gt;&lt;/center&gt;
-On réalise un circuit électrique série comportant une bobine d'inductance $L$ et de résistance $r$, un conducteur ohmique de résistance $R = 50\text{ }\Omega$, un générateur de tension de f.é.m E et un interrupteur K. À l'instant $t_{0}=0$, on ferme K. Un système d'acquisition donne l'évolution de la tension $u_{R}(t)$ aux bornes du conducteur ohmique et l'énergie magnétique $\mathcal{E}_{m}(t)$ emmagasinée dans la bobine.
-</t>
-  </si>
-  <si>
     <t>L'équation différentielle vérifiée par l'intensité du courant qui traverse le circuit est :</t>
   </si>
   <si>
@@ -6271,13 +6228,6 @@
     <t>L'expression de l'ordonnée du sommet S de la trajectoire du skieur est :</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Etude d'un oscillateur mécanique (6 points)&lt;/b&gt;&lt;/center&gt;
-On considère l'oscillateur (solide (S) - ressort) d'axe horizontal, de masse négligeable et de raideur K. On étudie le mouvement du centre d'inertie G du solide (S) de masse m dans un repère $(O, \vec{i})$ lié à la Terre supposé galiléen. On écarte (S) de sa position d'équilibre et on l'abandonne sans vitesse initiale. À l'instant $t_{0}=0$, l'abscisse de G est $x_{0G} = -2\text{ cm}$ et la coordonnée de sa vitesse est $v_{0G} = 0,2\text{ m}\cdot\text{s}^{-1}$.
-On choisit l'état non déformé comme référence de $E_{pe}$ et le plan horizontal comme référence de $E_{pp}$.
-Données : $m = 100\text{ g}$ ; $K = 10\text{ N}\cdot\text{m}^{-1}$ ; les frottements sont négligeables.
-</t>
-  </si>
-  <si>
     <t>La valeur de l'énergie mécanique de l'oscillateur est :</t>
   </si>
   <si>
@@ -6285,17 +6235,6 @@
   </si>
   <si>
     <t>La valeur de la vitesse de passage de G par la position d'équilibre dans le sens positif est :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Sauts à ski (6 points)&lt;/b&gt;&lt;/center&gt;
-Un skieur de masse m désire franchir l'espace entre deux tremplins symétriques ABI et CDJ. 
-Pour cela, il aborde le premier tremplin en $A$ avec une vitesse $\vec{v}_{A}$ tangente à $(AB)$. Tous les frottements sont négligeables au cours de son mouvement.
-Données : $g = 10\text{ m}\cdot\text{s}^{-2}$ ; $v_{A} = 20\text{ m}\cdot\text{s}^{-1}$ ; $\alpha = 30^{\circ}$ ; $\sin 60^{\circ} = 0,866$ ; $BI = h = 10\text{ m}$.
-</t>
-  </si>
-  <si>
-    <t>Le skieur chute sur le deuxième tremplin dans la position $C$ avec une vitesse $v_{C}$ tangente à $(CD)$. Le mouvement est étudié dans le repère $(I, \vec{\imath}, \vec{\jmath})$ supposé galiléen.
-La valeur de la distance BC entre les deux tremplins est :</t>
   </si>
   <si>
     <t>Si $\left(u_{n}\right)_{n \in N^{*}}$ est une suite géométrique de premier terme $u_{1}=2$ et de raison $q=\frac{1}{3}$, alors le produit $u_{1} \times u_{2} \times u_{3} \times \cdots \times u_{n}(n \leq 1)$ est égal à:</t>
@@ -7734,6 +7673,78 @@
 Dans une population, soumise à la loi de Hardy Weinberg, on a 70 % des individus sensibles au goût amer du PTC, sachant que la sensibilité à la PTC est liée à un allèle dominant S et l'insensibilité à cette substance est liée à l'allèle récessif s. 
 &lt;br&gt;On donne : $\sqrt{0,20} = 0,45$ ; $\quad \sqrt{0,30} = 0,55$ ; $\quad \sqrt{0,70} = 0,83$
 &lt;br&gt;Quelles sont les fréquences des allèles et des génotypes dans cette population (on a considéré deux chiffres après la virgule) ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Etude d'un oscillateur mécanique (6 points)&lt;/b&gt;&lt;/center&gt;
+On considère l'oscillateur (solide (S) - ressort) représenté sur la figure. Le ressort est à spires non jointives d'axe horizontal, de masse négligeable et de raideur K.
+&lt;br&gt;&lt;img src="/images/P22F8.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+ On étudie le mouvement du centre d'inertie G du solide (S) de masse m dans un repère $(O, \vec{i})$ lié à la Terre supposé galiléen. 
+&lt;br&gt;On écarte (S) de sa position d'équilibre et on l'abandonne sans vitesse initiale. À l'instant $t_{0}=0$, choisi comme origine des dates, l'abscisse de G est $x_{0G} = -2\text{ cm}$ et la coordonnée de sa vitesse dans le repère $(O, \vec{i})$ est $v_{0G} = 0,2\text{ m}\cdot\text{s}^{-1}$.
+&lt;br&gt;On choisit l'état où le ressort n'est pas déformé comme référence de l'énergie potentielle $E_{pe}$ et le plan horizontal contenant G comme état de référence de l'énergie potentielle de pesanteur $E_{pp}$.
+&lt;br&gt;Données : $m = 100\text{ g}$ ; $K = 10\text{ N}\cdot\text{m}^{-1}$ ; les frottements sont négligeables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Sauts à ski (6 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Un skieur de masse m désire franchir l'espace entre deux tremplins symétriques ABI et CDJ (figure ci-dessous)
+&lt;br&gt;&lt;img src="/images/P22F7.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+Pour cela, il aborde le premier tremplin en $A$ avec une vitesse $\vec{v}_{A}$ tangente à $(AB)$. Tous les frottements sont négligeables au cours de son mouvement.
+Données : $g = 10\text{ m}\cdot\text{s}^{-2}$ ; $v_{A} = 20\text{ m}\cdot\text{s}^{-1}$ ; $\alpha = 30^{\circ}$ ; $\sin 60^{\circ} = 0,866$ ; $BI = h = 10\text{ m}$.
+</t>
+  </si>
+  <si>
+    <t>Le skieur chute sur le deuxième tremplin dans la position $C$ avec une vitesse $v_{C}$ tangente à $(CD)$. Le mouvement est étudié dans le repère $(I, \vec{\imath}, \vec{\jmath})$ supposé galiléen.
+&lt;br&gt;La valeur de la distance BC entre les deux tremplins est :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&lt;Réponse d'un dipôle RL (7 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On réalise un circuit électrique série comportant une bobine d'inductance $L$ et de résistance $r$, un conducteur ohmique de résistance $R = 50\text{ }\Omega$, un générateur de tension de f.é.m E et un interrupteur K. &lt;br&gt;À l'instant $t_{0}=0$, on ferme K. Un système d'acquisition donne l'évolution de la tension $u_{R}(t)$ aux bornes du conducteur ohmique et l'énergie magnétique $\mathcal{E}_{m}(t)$ emmagasinée dans la bobine (voir document suivant)
+&lt;br&gt;&lt;img src="/images/P22F5F6.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Charge et décharge d'un condensateur (7 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On considère le montage schématisé sur la figure suivante. 
+&lt;br&gt;&lt;img src="/images/P22F4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;b&gt;À l'instant $t_{0}=0$, on place l'interrupteur K en position (1). Un système d'acquisition donne l'expression numérique de l'intensité du courant qui circule dans le circuit : $i(t) = 6 \cdot 10^{-3} \cdot e^{-1000 t}\text{ (A)}$.
+&lt;br&gt;Données : $E = 6,0\text{ V}$ ; $R = 0,95\text{ k}\Omega$.
+</t>
+  </si>
+  <si>
+    <t>Lorsque le condensateur devient totalement chargé, on bascule K en position (2), à un instant  pris comme nouvelle origine des dates ($t_{0}=0$). 
+&lt;br&gt;L'expression numérique de la tension aux bornes du condensateur est :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Radioactivité du thorium (6 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Le noyau de thorium $\ce{^{230}_{90}Th}$ subit une série de désintégrations successives de types $\alpha$ et $\beta^{-}$ qui conduisent à la formation du noyau de plomb $\ce{^{206}_{82}Pb}$, stable. 
+&lt;br&gt;L'équation globale des désintégrations subies par le thorium s'écrit :
+$$\ce{^{230}_{90}Th -&gt; ^{206}_{82}Pb} + x\alpha + y\beta^{-}$$
+&lt;br&gt;On dispose d'un échantillon contenant $N_{0}$ noyaux de thorium à l'instant $t_{0}=0$. 
+&lt;br&gt;L'échantillon contient à un instant $t$, après une série de désintégrations, $0,25\text{ mmol}$ de thorium $\ce{^{230}_{90}Th}$ et $0,75\text{ mmol}$ de $\ce{^{206}_{82}Pb}$.
+&lt;br&gt;Données : Constante radioactive du thorium : $\lambda = 8,7 \cdot 10^{-6}\text{ ans}^{-1}$ ; $\quad$ $\ln 2 = 0,7$.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Diffraction de la lumière par une fente (4 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On réalise la diffraction de la lumière en utilisant le dispositif ci-contre.
+&lt;br&gt;&lt;img src="/images/P22F2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt; On réalise dans l'air, quatre expériences en utilisant deux lasers produisant deux radiations de longueurs d'onde respectives $\lambda_{1}$ et $\lambda_{2}$. Pour différentes valeurs de la largeur $a$ de la fente, on obtient les résultats indiqués dans le tableau ci-dessous.
+&lt;br&gt;&lt;img src="/images/P22F3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Données : $\tan \theta \approx \theta \text{ (rad)}$ ; $\quad$ $\dfrac{632,8 \times 3,2}{2} \approx 10^3$.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Onde à la surface de l'eau (5 points)&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Sur la surface de l'eau contenue dans une cuve à onde, on crée à l'instant $t_{0}=0$, une onde progressive sinusoïdale de fréquence $N$, en un point $S$ à l'aide d'une pointe liée à un vibreur. Cette onde se propage sans amortissement et sans réflexion avec une vitesse constante. 
+&lt;br&gt;Le document ci-dessous représente une section de la surface de l'eau suivant un plan vertical passant par le point $S$ à un instant $t_1$.
+L'élongation de la source est : $y_{s}(t) = 10^{-2} \cdot \sin(100\cdot\pi t)$ (m).
+&lt;br&gt;&lt;img src="/images/P22F1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Données : $N = 50\text{ Hz}$ ; $\quad$ $AB = 10\text{ cm}$.
+</t>
+  </si>
+  <si>
+    <t>On considère un point $P$ de la surface de l'eau. À l'instant $t$, $P$ appartient à la crête numéro 4.
+L'élongation du point $P$ à l'instant $t$ est :</t>
   </si>
 </sst>
 </file>
@@ -8478,26 +8489,26 @@
         <v>32</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="32" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H2" s="32" t="s">
         <v>1234</v>
       </c>
-      <c r="E2" s="32" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>1237</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>1238</v>
-      </c>
       <c r="I2" s="32" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>11</v>
@@ -8514,26 +8525,26 @@
         <v>32</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="32" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H3" s="32" t="s">
         <v>1239</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>1242</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>1243</v>
-      </c>
       <c r="I3" s="32" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>11</v>
@@ -8550,26 +8561,26 @@
         <v>32</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="32" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H4" s="32" t="s">
         <v>1244</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>1247</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>1248</v>
-      </c>
       <c r="I4" s="32" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>11</v>
@@ -8586,26 +8597,26 @@
         <v>32</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="32" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H5" s="32" t="s">
         <v>1249</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>1250</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>1253</v>
-      </c>
       <c r="I5" s="32" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>11</v>
@@ -8622,26 +8633,26 @@
         <v>32</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="32" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>1254</v>
       </c>
-      <c r="E6" s="32" t="s">
-        <v>1255</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>1258</v>
-      </c>
       <c r="I6" s="32" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>11</v>
@@ -8658,26 +8669,26 @@
         <v>32</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="32" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H7" s="32" t="s">
         <v>1259</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>1260</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>1262</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>1263</v>
-      </c>
       <c r="I7" s="32" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>11</v>
@@ -8694,26 +8705,26 @@
         <v>32</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="32" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H8" s="32" t="s">
         <v>1264</v>
       </c>
-      <c r="E8" s="32" t="s">
-        <v>1265</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>1266</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>1267</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>1268</v>
-      </c>
       <c r="I8" s="32" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>11</v>
@@ -8730,26 +8741,26 @@
         <v>32</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="32" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H9" s="32" t="s">
         <v>1269</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>1270</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>1272</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>1273</v>
-      </c>
       <c r="I9" s="32" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>11</v>
@@ -8766,26 +8777,26 @@
         <v>32</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="32" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H10" s="32" t="s">
         <v>1274</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>1276</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>1277</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>1278</v>
-      </c>
       <c r="I10" s="32" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>11</v>
@@ -8802,26 +8813,26 @@
         <v>32</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="32" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H11" s="32" t="s">
         <v>1279</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>1280</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>1281</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>1282</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>1283</v>
-      </c>
       <c r="I11" s="32" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>11</v>
@@ -8838,26 +8849,26 @@
         <v>32</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>2066</v>
+        <v>2056</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="32" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H12" s="32" t="s">
         <v>1284</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>1286</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>1287</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>1288</v>
-      </c>
       <c r="I12" s="32" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>11</v>
@@ -8874,26 +8885,26 @@
         <v>32</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="32" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H13" s="32" t="s">
         <v>1289</v>
       </c>
-      <c r="E13" s="32" t="s">
-        <v>1290</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>1291</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>1292</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>1293</v>
-      </c>
       <c r="I13" s="32" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>11</v>
@@ -8910,26 +8921,26 @@
         <v>32</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>2061</v>
+        <v>2051</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="32" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H14" s="32" t="s">
         <v>1294</v>
       </c>
-      <c r="E14" s="32" t="s">
-        <v>1295</v>
-      </c>
-      <c r="F14" s="32" t="s">
-        <v>1296</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>1297</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>1298</v>
-      </c>
       <c r="I14" s="32" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>11</v>
@@ -8946,26 +8957,26 @@
         <v>32</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="32" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H15" s="32" t="s">
         <v>1299</v>
       </c>
-      <c r="E15" s="32" t="s">
-        <v>1300</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>1302</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>1303</v>
-      </c>
       <c r="I15" s="32" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>11</v>
@@ -8982,26 +8993,26 @@
         <v>32</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>2062</v>
+        <v>2052</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="32" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H16" s="32" t="s">
         <v>1304</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>1305</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>1306</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>1308</v>
-      </c>
       <c r="I16" s="32" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>11</v>
@@ -9018,26 +9029,26 @@
         <v>32</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="32" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H17" s="32" t="s">
         <v>1309</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>1310</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>1312</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>1313</v>
-      </c>
       <c r="I17" s="32" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>11</v>
@@ -9054,26 +9065,26 @@
         <v>32</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>2063</v>
+        <v>2053</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="32" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H18" s="32" t="s">
         <v>1314</v>
       </c>
-      <c r="E18" s="32" t="s">
-        <v>1315</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>1316</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>1317</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>1318</v>
-      </c>
       <c r="I18" s="32" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>11</v>
@@ -9090,26 +9101,26 @@
         <v>32</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>2064</v>
+        <v>2054</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="32" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H19" s="32" t="s">
         <v>1319</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>1320</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>1321</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>1322</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>1323</v>
-      </c>
       <c r="I19" s="32" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>11</v>
@@ -9126,26 +9137,26 @@
         <v>32</v>
  